--- a/outputs/audi-repair-first-review/Audi-repair-first-fitment-review.xlsx
+++ b/outputs/audi-repair-first-review/Audi-repair-first-fitment-review.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R1c8fac298b5b4d47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audi Review" sheetId="2" r:id="R276e8740d92c4dc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Queue" sheetId="3" r:id="R3868b7fb68a248d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" r:id="Rbbe1adf4ade8429b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R418bf19a57044f3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audi Review" sheetId="2" r:id="Re4cbc34205a440a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Queue" sheetId="3" r:id="Rd9126246985f4582"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" r:id="Re82e4b5bb1414dea"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -484,7 +484,7 @@
         <x:v>Reviewed in this batch</x:v>
       </x:c>
       <x:c r="B5" s="13" t="n">
-        <x:v>150</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C5" s="11"/>
       <x:c r="D5" s="11"/>
@@ -498,7 +498,7 @@
         <x:v>Remaining queue</x:v>
       </x:c>
       <x:c r="B6" s="13" t="n">
-        <x:v>239</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C6" s="11"/>
       <x:c r="D6" s="11"/>
@@ -512,7 +512,7 @@
         <x:v>Issues with destinations</x:v>
       </x:c>
       <x:c r="B7" s="13" t="n">
-        <x:v>146</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C7" s="11"/>
       <x:c r="D7" s="11"/>
@@ -526,7 +526,7 @@
         <x:v>Destination entries</x:v>
       </x:c>
       <x:c r="B8" s="13" t="n">
-        <x:v>266</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="C8" s="11"/>
       <x:c r="D8" s="11"/>
@@ -540,7 +540,7 @@
         <x:v>Distinct URLs</x:v>
       </x:c>
       <x:c r="B9" s="13" t="n">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C9" s="11"/>
       <x:c r="D9" s="11"/>
@@ -9869,28 +9869,2800 @@
       </x:c>
     </x:row>
     <x:row r="271" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A271" s="42" t="str"/>
-      <x:c r="B271" s="43" t="str"/>
-      <x:c r="C271" s="43" t="str"/>
-      <x:c r="D271" s="43" t="str"/>
-      <x:c r="E271" s="43" t="str"/>
-      <x:c r="F271" s="43" t="str"/>
-      <x:c r="G271" s="43" t="str"/>
-      <x:c r="H271" s="43" t="str">
+      <x:c r="A271" s="40" t="str"/>
+      <x:c r="B271" s="9" t="str"/>
+      <x:c r="C271" s="9" t="str"/>
+      <x:c r="D271" s="9" t="str"/>
+      <x:c r="E271" s="9" t="str"/>
+      <x:c r="F271" s="9" t="str"/>
+      <x:c r="G271" s="9" t="str"/>
+      <x:c r="H271" s="9" t="str">
         <x:v>NHTSA recall lookup</x:v>
       </x:c>
-      <x:c r="I271" s="43" t="str">
+      <x:c r="I271" s="9" t="str">
         <x:v>https://www.nhtsa.gov/recalls</x:v>
       </x:c>
-      <x:c r="J271" s="43" t="str">
+      <x:c r="J271" s="9" t="str">
         <x:v>25V227 VIN history</x:v>
       </x:c>
-      <x:c r="K271" s="43" t="str">
+      <x:c r="K271" s="9" t="str">
         <x:v>government recall lookup</x:v>
       </x:c>
-      <x:c r="L271" s="43" t="str"/>
-      <x:c r="M271" s="43" t="str"/>
-      <x:c r="N271" s="44" t="str"/>
+      <x:c r="L271" s="9" t="str"/>
+      <x:c r="M271" s="9" t="str"/>
+      <x:c r="N271" s="41" t="str"/>
+    </x:row>
+    <x:row r="272" ht="673.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A272" s="40" t="n">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B272" s="9" t="str">
+        <x:v>audi-etron-gt-software-2022</x:v>
+      </x:c>
+      <x:c r="C272" s="9" t="str">
+        <x:v>2022-2022 | Audi | e-tron GT</x:v>
+      </x:c>
+      <x:c r="D272" s="9" t="str">
+        <x:v>2022 e-tron GT Audi connect Inoperative after 91DZ - TSB 2068824/2</x:v>
+      </x:c>
+      <x:c r="E272" s="9" t="str">
+        <x:v>Confirm that the failure began after 91DZ and matches the Audi connect/SOS-LED condition. An Audi technician should use ODIS Guided Fault Finding and run SVM Check Module Configuration for diagnostic address 0019, J533. Manual coding is no longer required. Escalate a continuing Audi connect failure through Audi support after the guided coding procedure rather than buying hardware or a retail software service.</x:v>
+      </x:c>
+      <x:c r="F272" s="9" t="str">
+        <x:v>Confirm post-91DZ Audi connect/SOS condition; ODIS GFF plus SVM Check Module Configuration for J533/address 0019; Audi escalation if persistent</x:v>
+      </x:c>
+      <x:c r="G272" s="9" t="str">
+        <x:v>SOFTWARE / GUIDED-CODING SERVICE</x:v>
+      </x:c>
+      <x:c r="H272" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I272" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J272" s="9" t="str">
+        <x:v>2022 e-tron GT TSB 2068824/2 ODIS/SVM procedure</x:v>
+      </x:c>
+      <x:c r="K272" s="9" t="str">
+        <x:v>manufacturer software service</x:v>
+      </x:c>
+      <x:c r="L272" s="9" t="str"/>
+      <x:c r="M272" s="9" t="str">
+        <x:v>The repair is guided module configuration, not hardware.</x:v>
+      </x:c>
+      <x:c r="N272" s="41" t="str">
+        <x:v>Do not link a module or retail coding service; manual coding is no longer directed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273" ht="858" hidden="0" customHeight="1">
+      <x:c r="A273" s="40" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="B273" s="9" t="str">
+        <x:v>audi-etron-hv-coolant-2019</x:v>
+      </x:c>
+      <x:c r="C273" s="9" t="str">
+        <x:v>2019-2022 | Audi | e-tron | e-tron quattro (2019, 2021-2022); e-tron Sportback quattro (2020-2022); e-tron S (2022) | Battery-electric; confirm coolant valve N632 part number by scan tool</x:v>
+      </x:c>
+      <x:c r="D273" s="9" t="str">
+        <x:v>2019-2022 e-tron Coolant Valve N632 Leak in Cold Conditions - Diagnosis Required</x:v>
+      </x:c>
+      <x:c r="E273" s="9" t="str">
+        <x:v>Do not open or add fluid to a high-voltage cooling circuit unless you are trained and have the Audi procedure. Have an Audi-qualified technician confirm that coolant valve N632 is the leak source and identify the installed valve with the scan tool. If index K or index Q is fitted and the TSB criteria apply, replace the valve if necessary under Audi TSB 2067941/3. A coolant warning, overheating warning or active high-voltage fault requires prompt professional diagnosis; do not order the former coolant product from this card.</x:v>
+      </x:c>
+      <x:c r="F273" s="9" t="str">
+        <x:v>Audi-qualified confirmation of N632 leak and scan-tool valve identity; conditional index K/Q replacement per TSB 2067941/3</x:v>
+      </x:c>
+      <x:c r="G273" s="9" t="str">
+        <x:v>HIGH-VOLTAGE / VALVE-INDEX SERVICE</x:v>
+      </x:c>
+      <x:c r="H273" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I273" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J273" s="9" t="str">
+        <x:v>2019-2022 e-tron covered models; N632 identity, leak and TSB service</x:v>
+      </x:c>
+      <x:c r="K273" s="9" t="str">
+        <x:v>authorized EV thermal service</x:v>
+      </x:c>
+      <x:c r="L273" s="9" t="str"/>
+      <x:c r="M273" s="9" t="str">
+        <x:v>High-voltage coolant work and replacement depend on exact valve index and leak proof.</x:v>
+      </x:c>
+      <x:c r="N273" s="41" t="str">
+        <x:v>Do not add coolant or link valve/fluid for owner repair.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274" ht="818.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A274" s="40" t="n">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B274" s="9" t="str">
+        <x:v>audi-etron-onboard-charger-2019</x:v>
+      </x:c>
+      <x:c r="C274" s="9" t="str">
+        <x:v>2021-2021 | Audi | e-tron | e-tron quattro and e-tron Sportback; confirm J1050 software level and matching DTC | Battery-electric</x:v>
+      </x:c>
+      <x:c r="D274" s="9" t="str">
+        <x:v>2021 e-tron Charging Interruptions with Onboard-Charger Software 0070 - Diagnosis Required</x:v>
+      </x:c>
+      <x:c r="E274" s="9" t="str">
+        <x:v>Record whether the failure is AC, DC or station-specific and have J1050 scanned before parts. If the vehicle has the matching condition and software level 0070, Audi directs an SVM update to software 0079 or higher. After the update, reproduce the concern and follow the guided test plan for any new active DTC. Do not infer hardware failure merely because one charging mode works, and do not order the former charger, 12-volt battery, relay, meter or portable EVSE from this card.</x:v>
+      </x:c>
+      <x:c r="F274" s="9" t="str">
+        <x:v>Classify AC/DC/station-specific failure; scan J1050; matching software 0070 to 0079+ SVM update; reproduce and guided-test remaining DTC</x:v>
+      </x:c>
+      <x:c r="G274" s="9" t="str">
+        <x:v>SOURCE-YEAR MISMATCH / SOFTWARE-FIRST SERVICE</x:v>
+      </x:c>
+      <x:c r="H274" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I274" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J274" s="9" t="str">
+        <x:v>2021 e-tron J1050 software and guided charging diagnosis</x:v>
+      </x:c>
+      <x:c r="K274" s="9" t="str">
+        <x:v>authorized EV software service</x:v>
+      </x:c>
+      <x:c r="L274" s="9" t="str"/>
+      <x:c r="M274" s="9" t="str">
+        <x:v>One working charge mode does not prove hardware failure.</x:v>
+      </x:c>
+      <x:c r="N274" s="41" t="str">
+        <x:v>Identifier says 2019; align to 2021 and do not link charger, battery, relay, meter or EVSE.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275" ht="264" hidden="0" customHeight="1">
+      <x:c r="A275" s="40" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="B275" s="9" t="str">
+        <x:v>audi-etron-ota-software-2019</x:v>
+      </x:c>
+      <x:c r="C275" s="9" t="str">
+        <x:v>2019-2024 | Audi | e-tron</x:v>
+      </x:c>
+      <x:c r="D275" s="9" t="str">
+        <x:v>OTA Software Update and Infotainment Issues</x:v>
+      </x:c>
+      <x:c r="E275" s="9" t="str">
+        <x:v>Hard reset infotainment system. Visit dealer for manual software update. Ensure stable WiFi connection for OTA updates.</x:v>
+      </x:c>
+      <x:c r="F275" s="9" t="str">
+        <x:v>Document exact infotainment/OTA symptom and software; safe reboot only per manual; VIN/version-specific dealer update and module diagnosis if persistent</x:v>
+      </x:c>
+      <x:c r="G275" s="9" t="str">
+        <x:v>OVERBROAD SOFTWARE SERVICE</x:v>
+      </x:c>
+      <x:c r="H275" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I275" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J275" s="9" t="str">
+        <x:v>2019-2024 e-tron VIN/software-level diagnosis and updates</x:v>
+      </x:c>
+      <x:c r="K275" s="9" t="str">
+        <x:v>manufacturer software service</x:v>
+      </x:c>
+      <x:c r="L275" s="9" t="str"/>
+      <x:c r="M275" s="9" t="str">
+        <x:v>The source combines multiple software symptoms without version or DTC.</x:v>
+      </x:c>
+      <x:c r="N275" s="41" t="str">
+        <x:v>Do not promise Wi-Fi or a generic hard reset fixes OTA issues; no product link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276" ht="396" hidden="0" customHeight="1">
+      <x:c r="A276" s="40" t="n">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="B276" s="9" t="str">
+        <x:v>audi-q2-coolant-water-pump-leak-tfsi-engines</x:v>
+      </x:c>
+      <x:c r="C276" s="9" t="str">
+        <x:v>2016-2021 | Audi | Q2 | TFSI petrol | 1.4 TFSI, 2.0 TFSI, 1.0 TFSI, TFSI petrol</x:v>
+      </x:c>
+      <x:c r="D276" s="9" t="str">
+        <x:v>Coolant / water pump leak on TFSI engines (cracked plastic pump housing)</x:v>
+      </x:c>
+      <x:c r="E276" s="9" t="str">
+        <x:v>Replace the water pump and thermostat housing (typically an updated revised unit) and refill/bleed with the correct G13 coolant; many shops do this together with the timing belt service. Inspect related coolant hoses/thermostat at the same time.</x:v>
+      </x:c>
+      <x:c r="F276" s="9" t="str">
+        <x:v>Local-market VIN/engine-code pressure test; exact pump/thermostat/housing source; current coolant and bleed; timing service only when that engine/procedure overlaps</x:v>
+      </x:c>
+      <x:c r="G276" s="9" t="str">
+        <x:v>NON-US-MARKET / ENGINE LEAK-SOURCE GATE</x:v>
+      </x:c>
+      <x:c r="H276" s="9" t="str">
+        <x:v>Audi UK service and maintenance</x:v>
+      </x:c>
+      <x:c r="I276" s="9" t="str">
+        <x:v>https://www.audi.co.uk/en/owners/service-and-maintenance/</x:v>
+      </x:c>
+      <x:c r="J276" s="9" t="str">
+        <x:v>2016-2021 Q2 TFSI local-market leak diagnosis and VIN parts</x:v>
+      </x:c>
+      <x:c r="K276" s="9" t="str">
+        <x:v>manufacturer-market service</x:v>
+      </x:c>
+      <x:c r="L276" s="9" t="str"/>
+      <x:c r="M276" s="9" t="str">
+        <x:v>Q2 was not sold in the US and 1.0/1.4/2.0 systems differ.</x:v>
+      </x:c>
+      <x:c r="N276" s="41" t="str">
+        <x:v>Do not bundle pump, thermostat or G13 universally or assume timing-belt labor overlap.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277" ht="528" hidden="0" customHeight="1">
+      <x:c r="A277" s="40" t="n">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B277" s="9" t="str">
+        <x:v>audi-q2-diesel-particulate-filter-clogging-tdi-engines-used-short-tr</x:v>
+      </x:c>
+      <x:c r="C277" s="9" t="str">
+        <x:v>2016-2020 | Audi | Q2 | TDI diesel | 1.6 TDI, 2.0 TDI</x:v>
+      </x:c>
+      <x:c r="D277" s="9" t="str">
+        <x:v>Diesel particulate filter (DPF) clogging on TDI engines used for short trips</x:v>
+      </x:c>
+      <x:c r="E277" s="9" t="str">
+        <x:v>Drive at a steady speed (&gt;60 km/h / ~40 mph) under moderate load for 15–30 minutes to allow regeneration to complete; if blocked, the dealer performs a forced/static regeneration with diagnostic equipment. Severely blocked filters need professional DPF cleaning or replacement. Long-term: avoid exclusively short trips.</x:v>
+      </x:c>
+      <x:c r="F277" s="9" t="str">
+        <x:v>TDI fault/live-data diagnosis; distinguish soot, ash and sensor faults; approved guided regeneration, professional cleaning or replacement by measured condition</x:v>
+      </x:c>
+      <x:c r="G277" s="9" t="str">
+        <x:v>NON-US-MARKET / PROFESSIONAL DPF SERVICE</x:v>
+      </x:c>
+      <x:c r="H277" s="9" t="str">
+        <x:v>Audi UK service and maintenance</x:v>
+      </x:c>
+      <x:c r="I277" s="9" t="str">
+        <x:v>https://www.audi.co.uk/en/owners/service-and-maintenance/</x:v>
+      </x:c>
+      <x:c r="J277" s="9" t="str">
+        <x:v>2016-2020 Q2 TDI local-market DPF diagnosis/service</x:v>
+      </x:c>
+      <x:c r="K277" s="9" t="str">
+        <x:v>manufacturer-market service</x:v>
+      </x:c>
+      <x:c r="L277" s="9" t="str"/>
+      <x:c r="M277" s="9" t="str">
+        <x:v>A drive cycle may be unsafe/ineffective with excessive soot or active faults.</x:v>
+      </x:c>
+      <x:c r="N277" s="41" t="str">
+        <x:v>Do not prescribe uncontrolled road regeneration or a DPF product before diagnosis.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278" ht="422.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A278" s="40" t="n">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="B278" s="9" t="str">
+        <x:v>audi-q2-electro-mechanical-parking-brake-can-release-its-own</x:v>
+      </x:c>
+      <x:c r="C278" s="9" t="str">
+        <x:v>2017-2018 | Audi | Q2</x:v>
+      </x:c>
+      <x:c r="D278" s="9" t="str">
+        <x:v>2017-2018 Audi Q2 Parking-Brake Software Recall 45H4</x:v>
+      </x:c>
+      <x:c r="E278" s="9" t="str">
+        <x:v>Check the VIN and campaign-completion history with Audi. The recall remedy is an authorised-dealer software update to the brake control unit. Until eligibility and completion are confirmed, leave the transmission in gear or Park and avoid relying on the parking brake alone on a slope.</x:v>
+      </x:c>
+      <x:c r="F278" s="9" t="str">
+        <x:v>Selling-market VIN/45H4 completion check; authorized brake-control software update; secure vehicle in Park/gear</x:v>
+      </x:c>
+      <x:c r="G278" s="9" t="str">
+        <x:v>NON-US RECALL ROUTE</x:v>
+      </x:c>
+      <x:c r="H278" s="9" t="str">
+        <x:v>Audi UK service and maintenance</x:v>
+      </x:c>
+      <x:c r="I278" s="9" t="str">
+        <x:v>https://www.audi.co.uk/en/owners/service-and-maintenance/</x:v>
+      </x:c>
+      <x:c r="J278" s="9" t="str">
+        <x:v>2017-2018 Q2 local-market recall/Audi Centre route</x:v>
+      </x:c>
+      <x:c r="K278" s="9" t="str">
+        <x:v>manufacturer-market recall route</x:v>
+      </x:c>
+      <x:c r="L278" s="9" t="str"/>
+      <x:c r="M278" s="9" t="str">
+        <x:v>The remedy is campaign software.</x:v>
+      </x:c>
+      <x:c r="N278" s="41" t="str">
+        <x:v>Do not link parking-brake hardware.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279" ht="475.20001220703125" hidden="0" customHeight="1">
+      <x:c r="A279" s="40" t="n">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="B279" s="9" t="str">
+        <x:v>audi-q2-fuse-carrier-power-connector-recall-engine-instrument-cluste</x:v>
+      </x:c>
+      <x:c r="C279" s="9" t="str">
+        <x:v>2021-2023 | Audi | Q2 | 35 TFSI, 35 TDI</x:v>
+      </x:c>
+      <x:c r="D279" s="9" t="str">
+        <x:v>2021-2023 Audi Q2 Interior Fuse-Carrier Recall GAI-3692</x:v>
+      </x:c>
+      <x:c r="E279" s="9" t="str">
+        <x:v>Check the VIN and open-campaign status with an authorised Audi dealer in the vehicle’s market. The campaign remedy is dealer inspection and correction of the fuse-carrier power connection. Do not replace a fuse box or wiring harness solely from a warning lamp or this model-year summary.</x:v>
+      </x:c>
+      <x:c r="F279" s="9" t="str">
+        <x:v>Selling-market VIN/GAI-3692 check; dealer fuse-carrier power-connection inspection/correction</x:v>
+      </x:c>
+      <x:c r="G279" s="9" t="str">
+        <x:v>NON-US RECALL ROUTE</x:v>
+      </x:c>
+      <x:c r="H279" s="9" t="str">
+        <x:v>Audi UK service and maintenance</x:v>
+      </x:c>
+      <x:c r="I279" s="9" t="str">
+        <x:v>https://www.audi.co.uk/en/owners/service-and-maintenance/</x:v>
+      </x:c>
+      <x:c r="J279" s="9" t="str">
+        <x:v>2021-2023 Q2 local-market campaign/Audi Centre route</x:v>
+      </x:c>
+      <x:c r="K279" s="9" t="str">
+        <x:v>manufacturer-market recall route</x:v>
+      </x:c>
+      <x:c r="L279" s="9" t="str"/>
+      <x:c r="M279" s="9" t="str">
+        <x:v>The campaign controls the connection remedy.</x:v>
+      </x:c>
+      <x:c r="N279" s="41" t="str">
+        <x:v>Do not sell a fuse box or harness from a warning lamp.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280" ht="435.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A280" s="40" t="n">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B280" s="9" t="str">
+        <x:v>audi-q2-mmi-infotainment-freezing-rebooting-intermittent-electrical</x:v>
+      </x:c>
+      <x:c r="C280" s="9" t="str">
+        <x:v>2016-2022 | Audi | Q2</x:v>
+      </x:c>
+      <x:c r="D280" s="9" t="str">
+        <x:v>MMI infotainment freezing/rebooting and intermittent electrical glitches</x:v>
+      </x:c>
+      <x:c r="E280" s="9" t="str">
+        <x:v>Apply the latest MMI software update at an Audi dealer; clear/re-pair the phone if corrupt phone data triggers it. A manual MMI reboot (press-and-hold the power/volume knob ~10 seconds) clears temporary glitches. Persistent faults may require a head-unit or module replacement.</x:v>
+      </x:c>
+      <x:c r="F280" s="9" t="str">
+        <x:v>Record symptom/DTC/software and phone-data trigger; safe reboot; market/VIN software update; head unit only if diagnosed</x:v>
+      </x:c>
+      <x:c r="G280" s="9" t="str">
+        <x:v>NON-US-MARKET / SOFTWARE-FIRST SERVICE</x:v>
+      </x:c>
+      <x:c r="H280" s="9" t="str">
+        <x:v>Audi UK service and maintenance</x:v>
+      </x:c>
+      <x:c r="I280" s="9" t="str">
+        <x:v>https://www.audi.co.uk/en/owners/service-and-maintenance/</x:v>
+      </x:c>
+      <x:c r="J280" s="9" t="str">
+        <x:v>2016-2022 Q2 MMI diagnosis/update</x:v>
+      </x:c>
+      <x:c r="K280" s="9" t="str">
+        <x:v>manufacturer-market software service</x:v>
+      </x:c>
+      <x:c r="L280" s="9" t="str"/>
+      <x:c r="M280" s="9" t="str">
+        <x:v>Temporary data/software faults do not establish head-unit failure.</x:v>
+      </x:c>
+      <x:c r="N280" s="41" t="str">
+        <x:v>Do not link a head unit or promise a universal reset.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281" ht="554.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A281" s="40" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B281" s="9" t="str">
+        <x:v>audi-q2-premature-timing-belt-failure-1-0-1-4-tfsi-petrol-engines</x:v>
+      </x:c>
+      <x:c r="C281" s="9" t="str">
+        <x:v>2016-2021 | Audi | Q2 | 1.0 TFSI, 1.4 TFSI, 30 TFSI, 35 TFSI | 1.0 TFSI (3-cyl), 1.4 TFSI, TFSI petrol</x:v>
+      </x:c>
+      <x:c r="D281" s="9" t="str">
+        <x:v>Premature timing belt failure on 1.0 / 1.4 TFSI petrol engines</x:v>
+      </x:c>
+      <x:c r="E281" s="9" t="str">
+        <x:v>Replace the timing belt, tensioner, idlers and water pump as a kit well before the stated interval (many owners now do it at 4 years / 40k-50k miles as a precaution); if the belt has already failed, the usual outcome is a replacement engine (often a reconditioned/used unit) plus a new belt kit. Pursue Audi goodwill via the dealer/ombudsman if full service history exists.</x:v>
+      </x:c>
+      <x:c r="F281" s="9" t="str">
+        <x:v>Confirm engine code and documented belt interval/condition; exact belt/tensioner/idler/pump scope; post-failure compression/valve/engine assessment</x:v>
+      </x:c>
+      <x:c r="G281" s="9" t="str">
+        <x:v>NON-US-MARKET / ENGINE TIMING GATE</x:v>
+      </x:c>
+      <x:c r="H281" s="9" t="str">
+        <x:v>Audi UK service and maintenance</x:v>
+      </x:c>
+      <x:c r="I281" s="9" t="str">
+        <x:v>https://www.audi.co.uk/en/owners/service-and-maintenance/</x:v>
+      </x:c>
+      <x:c r="J281" s="9" t="str">
+        <x:v>2016-2021 Q2 1.0/1.4 TFSI interval and engine-code timing service</x:v>
+      </x:c>
+      <x:c r="K281" s="9" t="str">
+        <x:v>manufacturer-market service</x:v>
+      </x:c>
+      <x:c r="L281" s="9" t="str"/>
+      <x:c r="M281" s="9" t="str">
+        <x:v>No evidence supports one 4-year/40k-50k interval or engine replacement outcome for both engines.</x:v>
+      </x:c>
+      <x:c r="N281" s="41" t="str">
+        <x:v>Do not publish a universal kit/interval or goodwill promise.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282" ht="369.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A282" s="40" t="n">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="B282" s="9" t="str">
+        <x:v>audi-q2-rear-hub-carrier-fracture-recall</x:v>
+      </x:c>
+      <x:c r="C282" s="9" t="str">
+        <x:v>2017-2017 | Audi | Q2</x:v>
+      </x:c>
+      <x:c r="D282" s="9" t="str">
+        <x:v>2017 Audi Q2 Rear Wheel-Bearing Housing Recall R/2017/311</x:v>
+      </x:c>
+      <x:c r="E282" s="9" t="str">
+        <x:v>Check the VIN and campaign-completion history with Audi. The recall remedy replaces both rear wheel-bearing housings at an authorised dealer. If rear-wheel noise, looseness or unusual tyre wear is present, avoid continued driving until the vehicle is inspected.</x:v>
+      </x:c>
+      <x:c r="F282" s="9" t="str">
+        <x:v>Selling-market VIN/R2017-311 check; dealer both rear bearing-housing remedy; stop for looseness/noise</x:v>
+      </x:c>
+      <x:c r="G282" s="9" t="str">
+        <x:v>NON-US RECALL ROUTE</x:v>
+      </x:c>
+      <x:c r="H282" s="9" t="str">
+        <x:v>Audi UK service and maintenance</x:v>
+      </x:c>
+      <x:c r="I282" s="9" t="str">
+        <x:v>https://www.audi.co.uk/en/owners/service-and-maintenance/</x:v>
+      </x:c>
+      <x:c r="J282" s="9" t="str">
+        <x:v>2017 Q2 VIN recall/Audi Centre route</x:v>
+      </x:c>
+      <x:c r="K282" s="9" t="str">
+        <x:v>manufacturer-market recall route</x:v>
+      </x:c>
+      <x:c r="L282" s="9" t="str"/>
+      <x:c r="M282" s="9" t="str">
+        <x:v>Both housings are campaign-controlled.</x:v>
+      </x:c>
+      <x:c r="N282" s="41" t="str">
+        <x:v>Do not link a retail bearing/hub.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" ht="435.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A283" s="40" t="n">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="B283" s="9" t="str">
+        <x:v>audi-q2-s-tronic-dual-clutch-transmission-jerking-hesitation-delayed</x:v>
+      </x:c>
+      <x:c r="C283" s="9" t="str">
+        <x:v>2016-2022 | Audi | Q2 | S tronic / DSG (7-speed) | TFSI S tronic, TDI S tronic</x:v>
+      </x:c>
+      <x:c r="D283" s="9" t="str">
+        <x:v>S tronic (DSG) dual-clutch transmission jerking, hesitation and delayed shifts</x:v>
+      </x:c>
+      <x:c r="E283" s="9" t="str">
+        <x:v>Start with a transmission software/adaption update and a DSG mechatronic fluid-and-filter service at the correct interval; if symptoms persist, diagnose and replace the clutch pack or mechatronic unit as required. Address promptly to avoid limp-mode and further wear.</x:v>
+      </x:c>
+      <x:c r="F283" s="9" t="str">
+        <x:v>Identify exact 7-speed transmission code/wet-dry design; software/adaptation, exact fluid/filter service where applicable, clutch/mechatronic branch by diagnosis</x:v>
+      </x:c>
+      <x:c r="G283" s="9" t="str">
+        <x:v>NON-US-MARKET / TRANSMISSION-CODE GATE</x:v>
+      </x:c>
+      <x:c r="H283" s="9" t="str">
+        <x:v>Audi UK service and maintenance</x:v>
+      </x:c>
+      <x:c r="I283" s="9" t="str">
+        <x:v>https://www.audi.co.uk/en/owners/service-and-maintenance/</x:v>
+      </x:c>
+      <x:c r="J283" s="9" t="str">
+        <x:v>2016-2022 Q2 S tronic code, software and service diagnosis</x:v>
+      </x:c>
+      <x:c r="K283" s="9" t="str">
+        <x:v>manufacturer-market transmission service</x:v>
+      </x:c>
+      <x:c r="L283" s="9" t="str"/>
+      <x:c r="M283" s="9" t="str">
+        <x:v>Not every 7-speed uses the same fluid/filter or mechatronic.</x:v>
+      </x:c>
+      <x:c r="N283" s="41" t="str">
+        <x:v>Do not prescribe a fluid service or component until transmission code and fault branch are known.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284" ht="541.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A284" s="40" t="n">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="B284" s="9" t="str">
+        <x:v>audi-q3-brake-pedal-recall-2019</x:v>
+      </x:c>
+      <x:c r="C284" s="9" t="str">
+        <x:v>2020-2020 | Audi | Q3</x:v>
+      </x:c>
+      <x:c r="D284" s="9" t="str">
+        <x:v>2020 Audi Q3 Brake-Pedal Recall 46i7 / NHTSA 20V786</x:v>
+      </x:c>
+      <x:c r="E284" s="9" t="str">
+        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. The free recall remedy inspects the weld between the pedal and pedal plate and replaces the complete brake pedal when required. Do not buy pads or rotors for this campaign; if the pedal feels loose, bent or abnormal, stop driving and arrange dealer inspection.</x:v>
+      </x:c>
+      <x:c r="F284" s="9" t="str">
+        <x:v>VIN/46i7/20V786 completion check; dealer pedal-weld inspection and conditional complete pedal replacement; stop for abnormal pedal</x:v>
+      </x:c>
+      <x:c r="G284" s="9" t="str">
+        <x:v>SOURCE-YEAR MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H284" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I284" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J284" s="9" t="str">
+        <x:v>2020 Q3 VIN check for 46i7</x:v>
+      </x:c>
+      <x:c r="K284" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L284" s="9" t="str"/>
+      <x:c r="M284" s="9" t="str">
+        <x:v>This is a 2020 pedal recall, not brake friction service.</x:v>
+      </x:c>
+      <x:c r="N284" s="41" t="str">
+        <x:v>Identifier says 2019; do not link pads/rotors.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A285" s="40" t="str"/>
+      <x:c r="B285" s="9" t="str"/>
+      <x:c r="C285" s="9" t="str"/>
+      <x:c r="D285" s="9" t="str"/>
+      <x:c r="E285" s="9" t="str"/>
+      <x:c r="F285" s="9" t="str"/>
+      <x:c r="G285" s="9" t="str"/>
+      <x:c r="H285" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I285" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J285" s="9" t="str">
+        <x:v>20V786 VIN history</x:v>
+      </x:c>
+      <x:c r="K285" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L285" s="9" t="str"/>
+      <x:c r="M285" s="9" t="str"/>
+      <x:c r="N285" s="41" t="str"/>
+    </x:row>
+    <x:row r="286" ht="871.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A286" s="40" t="n">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="B286" s="9" t="str">
+        <x:v>audi-q3-carbon-buildup-2015</x:v>
+      </x:c>
+      <x:c r="C286" s="9" t="str">
+        <x:v>2015-2023 | Audi | Q3 | 2.0 TFSI</x:v>
+      </x:c>
+      <x:c r="D286" s="9" t="str">
+        <x:v>Carbon Buildup on Intake Valves (Direct Injection)</x:v>
+      </x:c>
+      <x:c r="E286" s="9" t="str">
+        <x:v>WALNUT BLASTING: Remove intake manifold and blast crushed walnut shells through intake ports ($700-$1,200). Requires specialized equipment—not DIY-friendly. Dealers charge $1,200-$1,500; independent Audi shops charge less. Repeat every 60,000-80,000 miles. PREVENTION: Install catch can ($300-$500) to filter PCV oil vapors before they reach valves—extends cleaning interval to 100k+ miles. Add Liqui Moly Intake Valve Cleaner to every oil change ($15). Perform "Italian tune-up" monthly (spirited highway driving to high RPM to burn carbon).</x:v>
+      </x:c>
+      <x:c r="F286" s="9" t="str">
+        <x:v>Confirm engine and deposits after ignition/fuel/air/compression diagnosis and intake inspection; engine-specific cleaning/service seals</x:v>
+      </x:c>
+      <x:c r="G286" s="9" t="str">
+        <x:v>ENGINE / CONFIRMED-DEPOSIT SERVICE</x:v>
+      </x:c>
+      <x:c r="H286" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I286" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J286" s="9" t="str">
+        <x:v>2015-2023 Q3 2.0 TFSI intake diagnosis/cleaning</x:v>
+      </x:c>
+      <x:c r="K286" s="9" t="str">
+        <x:v>specialist intake service</x:v>
+      </x:c>
+      <x:c r="L286" s="9" t="str"/>
+      <x:c r="M286" s="9" t="str">
+        <x:v>Symptoms and mileage alone do not prove intake deposits.</x:v>
+      </x:c>
+      <x:c r="N286" s="41" t="str">
+        <x:v>Remove universal interval, catch-can/cleaner and Italian-tune-up claims.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287" ht="422.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A287" s="40" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="B287" s="9" t="str">
+        <x:v>audi-q3-electrical-infotainment-2019</x:v>
+      </x:c>
+      <x:c r="C287" s="9" t="str">
+        <x:v>2022-2022 | Audi | Q3</x:v>
+      </x:c>
+      <x:c r="D287" s="9" t="str">
+        <x:v>2022 Audi Q3 Rearview-Camera Recall 91Ei / NHTSA 22V806</x:v>
+      </x:c>
+      <x:c r="E287" s="9" t="str">
+        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. The recall remedy replaces the infotainment main unit at no charge. Until repaired, use mirrors and direct observation with extra care while reversing; do not order a refurbished head unit from this summary.</x:v>
+      </x:c>
+      <x:c r="F287" s="9" t="str">
+        <x:v>VIN/91Ei/22V806 completion check; dealer infotainment main-unit remedy; reverse with direct observation</x:v>
+      </x:c>
+      <x:c r="G287" s="9" t="str">
+        <x:v>SOURCE-YEAR MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H287" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I287" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J287" s="9" t="str">
+        <x:v>2022 Q3 VIN check for 91Ei</x:v>
+      </x:c>
+      <x:c r="K287" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L287" s="9" t="str"/>
+      <x:c r="M287" s="9" t="str">
+        <x:v>The record is a 2022 recall.</x:v>
+      </x:c>
+      <x:c r="N287" s="41" t="str">
+        <x:v>Identifier says 2019; do not link refurbished head unit.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A288" s="40" t="str"/>
+      <x:c r="B288" s="9" t="str"/>
+      <x:c r="C288" s="9" t="str"/>
+      <x:c r="D288" s="9" t="str"/>
+      <x:c r="E288" s="9" t="str"/>
+      <x:c r="F288" s="9" t="str"/>
+      <x:c r="G288" s="9" t="str"/>
+      <x:c r="H288" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I288" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J288" s="9" t="str">
+        <x:v>22V806 VIN history</x:v>
+      </x:c>
+      <x:c r="K288" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L288" s="9" t="str"/>
+      <x:c r="M288" s="9" t="str"/>
+      <x:c r="N288" s="41" t="str"/>
+    </x:row>
+    <x:row r="289" ht="831.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A289" s="40" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="B289" s="9" t="str">
+        <x:v>audi-q3-oil-consumption-2015</x:v>
+      </x:c>
+      <x:c r="C289" s="9" t="str">
+        <x:v>2015-2018 | Audi | Q3 | EA888 Gen 2, EA888 Gen 3</x:v>
+      </x:c>
+      <x:c r="D289" s="9" t="str">
+        <x:v>Excessive Oil Consumption (2.0 TFSI Engine)</x:v>
+      </x:c>
+      <x:c r="E289" s="9" t="str">
+        <x:v>For SEVERE consumption (over 1 qt/1,000 mi): Piston ring replacement or short block replacement ($4,000-$7,000). Check Audi's extended warranty program for 2015-2018 Q3 models. For MODERATE consumption: Replace PCV valve ($150), clean carbon with walnut blasting ($800), switch to thicker oil (5W-40). PREVENTION: Check oil level WEEKLY, change oil every 5,000 miles (NOT 10,000), avoid 2015-2017 models when buying used. 2019+ Gen 3 EA888 engines are far more reliable.</x:v>
+      </x:c>
+      <x:c r="F289" s="9" t="str">
+        <x:v>Measured consumption after leak/oil-spec/PCV/turbo checks; engine-code/generation split; pistons/rings/short block only after mechanical diagnosis</x:v>
+      </x:c>
+      <x:c r="G289" s="9" t="str">
+        <x:v>ENGINE / MEASURED-CONSUMPTION GATE</x:v>
+      </x:c>
+      <x:c r="H289" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I289" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J289" s="9" t="str">
+        <x:v>2015-2018 Q3 2.0 TFSI measured consumption and root-cause diagnosis</x:v>
+      </x:c>
+      <x:c r="K289" s="9" t="str">
+        <x:v>specialist engine service</x:v>
+      </x:c>
+      <x:c r="L289" s="9" t="str"/>
+      <x:c r="M289" s="9" t="str">
+        <x:v>PCV, leaks, turbo and internal wear are separate branches.</x:v>
+      </x:c>
+      <x:c r="N289" s="41" t="str">
+        <x:v>Do not prescribe thicker oil, walnut blasting, pistons or coverage without evidence.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A290" s="40" t="str"/>
+      <x:c r="B290" s="9" t="str"/>
+      <x:c r="C290" s="9" t="str"/>
+      <x:c r="D290" s="9" t="str"/>
+      <x:c r="E290" s="9" t="str"/>
+      <x:c r="F290" s="9" t="str"/>
+      <x:c r="G290" s="9" t="str"/>
+      <x:c r="H290" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I290" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J290" s="9" t="str">
+        <x:v>VIN engine revision, historical coverage and oil spec</x:v>
+      </x:c>
+      <x:c r="K290" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L290" s="9" t="str"/>
+      <x:c r="M290" s="9" t="str"/>
+      <x:c r="N290" s="41" t="str"/>
+    </x:row>
+    <x:row r="291" ht="435.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A291" s="40" t="n">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="B291" s="9" t="str">
+        <x:v>audi-q3-panoramic-roof-2015</x:v>
+      </x:c>
+      <x:c r="C291" s="9" t="str">
+        <x:v>2015-2015 | Audi | Q3</x:v>
+      </x:c>
+      <x:c r="D291" s="9" t="str">
+        <x:v>2015 Audi Q3 Sunroof-Control Recall 60C1 / NHTSA 15V200</x:v>
+      </x:c>
+      <x:c r="E291" s="9" t="str">
+        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. The recall remedy updates the sunroof control-module software at no charge. Keep hands and objects clear of the moving panel and do not use battery, relay or generic electrical parts as a substitute for the campaign.</x:v>
+      </x:c>
+      <x:c r="F291" s="9" t="str">
+        <x:v>VIN/60C1/15V200 completion check; dealer sunroof-control software update; keep clear of moving panel</x:v>
+      </x:c>
+      <x:c r="G291" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H291" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I291" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J291" s="9" t="str">
+        <x:v>2015 Q3 VIN check for 60C1</x:v>
+      </x:c>
+      <x:c r="K291" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L291" s="9" t="str"/>
+      <x:c r="M291" s="9" t="str">
+        <x:v>The remedy is software.</x:v>
+      </x:c>
+      <x:c r="N291" s="41" t="str">
+        <x:v>Do not substitute battery, relay or electrical parts.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A292" s="40" t="str"/>
+      <x:c r="B292" s="9" t="str"/>
+      <x:c r="C292" s="9" t="str"/>
+      <x:c r="D292" s="9" t="str"/>
+      <x:c r="E292" s="9" t="str"/>
+      <x:c r="F292" s="9" t="str"/>
+      <x:c r="G292" s="9" t="str"/>
+      <x:c r="H292" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I292" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J292" s="9" t="str">
+        <x:v>15V200 VIN history</x:v>
+      </x:c>
+      <x:c r="K292" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L292" s="9" t="str"/>
+      <x:c r="M292" s="9" t="str"/>
+      <x:c r="N292" s="41" t="str"/>
+    </x:row>
+    <x:row r="293" ht="382.79998779296875" hidden="0" customHeight="1">
+      <x:c r="A293" s="40" t="n">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="B293" s="9" t="str">
+        <x:v>audi-q3-steering-lock-recall-2019</x:v>
+      </x:c>
+      <x:c r="C293" s="9" t="str">
+        <x:v>2019-2019 | Audi | Q3</x:v>
+      </x:c>
+      <x:c r="D293" s="9" t="str">
+        <x:v>2019 Audi Q3 Steering-Rack Recall 48P7 / NHTSA 21V027</x:v>
+      </x:c>
+      <x:c r="E293" s="9" t="str">
+        <x:v>Check the VIN and campaign history with Audi or NHTSA. The recall remedy replaces the steering rack at no charge. If steering binds or locks, stop driving and arrange recovery; do not infer that another Q3 is affected from model year alone.</x:v>
+      </x:c>
+      <x:c r="F293" s="9" t="str">
+        <x:v>VIN/48P7/21V027 completion check; free dealer steering-rack remedy; recovery for binding/locking</x:v>
+      </x:c>
+      <x:c r="G293" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H293" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I293" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J293" s="9" t="str">
+        <x:v>2019 Q3 VIN check for 48P7</x:v>
+      </x:c>
+      <x:c r="K293" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L293" s="9" t="str"/>
+      <x:c r="M293" s="9" t="str">
+        <x:v>Eligibility and rack replacement are VIN-controlled.</x:v>
+      </x:c>
+      <x:c r="N293" s="41" t="str">
+        <x:v>Do not infer all 2019 Q3 vehicles or link a retail rack.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A294" s="40" t="str"/>
+      <x:c r="B294" s="9" t="str"/>
+      <x:c r="C294" s="9" t="str"/>
+      <x:c r="D294" s="9" t="str"/>
+      <x:c r="E294" s="9" t="str"/>
+      <x:c r="F294" s="9" t="str"/>
+      <x:c r="G294" s="9" t="str"/>
+      <x:c r="H294" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I294" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J294" s="9" t="str">
+        <x:v>21V027 VIN history</x:v>
+      </x:c>
+      <x:c r="K294" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L294" s="9" t="str"/>
+      <x:c r="M294" s="9" t="str"/>
+      <x:c r="N294" s="41" t="str"/>
+    </x:row>
+    <x:row r="295" ht="435.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A295" s="40" t="n">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="B295" s="9" t="str">
+        <x:v>audi-q3-timing-chain-2015</x:v>
+      </x:c>
+      <x:c r="C295" s="9" t="str">
+        <x:v>2015-2018 | Audi | Q3 | Premium, Premium Plus, Prestige | 2.0T</x:v>
+      </x:c>
+      <x:c r="D295" s="9" t="str">
+        <x:v>EA888 Timing Chain Tensioner Failure</x:v>
+      </x:c>
+      <x:c r="E295" s="9" t="str">
+        <x:v>Replace the timing chain, tensioner, guides, and related hardware as a complete kit. Use the latest OEM revised tensioner part number. Preventive replacement is recommended at 80,000-100,000 miles. Cold-start rattle is the critical warning sign that should not be ignored.</x:v>
+      </x:c>
+      <x:c r="F295" s="9" t="str">
+        <x:v>Confirm engine code/generation and chain/tensioner condition; exact complete timing kit/current revision; post-jump mechanical assessment</x:v>
+      </x:c>
+      <x:c r="G295" s="9" t="str">
+        <x:v>ENGINE / TIMING-CONDITION GATE</x:v>
+      </x:c>
+      <x:c r="H295" s="9" t="str">
+        <x:v>Audi Q3 timing-chain catalog</x:v>
+      </x:c>
+      <x:c r="I295" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/Q3-Quattro/Timing-Chain-Kit/</x:v>
+      </x:c>
+      <x:c r="J295" s="9" t="str">
+        <x:v>2015-2018 Q3 2.0T; exact engine/VIN and kit completeness</x:v>
+      </x:c>
+      <x:c r="K295" s="9" t="str">
+        <x:v>engine-specific timing catalog</x:v>
+      </x:c>
+      <x:c r="L295" s="9" t="str"/>
+      <x:c r="M295" s="9" t="str">
+        <x:v>Revision and repair scope depend on engine and measured condition.</x:v>
+      </x:c>
+      <x:c r="N295" s="41" t="str">
+        <x:v>Do not impose a universal 80k-100k interval.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A296" s="40" t="str"/>
+      <x:c r="B296" s="9" t="str"/>
+      <x:c r="C296" s="9" t="str"/>
+      <x:c r="D296" s="9" t="str"/>
+      <x:c r="E296" s="9" t="str"/>
+      <x:c r="F296" s="9" t="str"/>
+      <x:c r="G296" s="9" t="str"/>
+      <x:c r="H296" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I296" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J296" s="9" t="str">
+        <x:v>cold-start rattle/adaptation and timing diagnosis</x:v>
+      </x:c>
+      <x:c r="K296" s="9" t="str">
+        <x:v>specialist engine service</x:v>
+      </x:c>
+      <x:c r="L296" s="9" t="str"/>
+      <x:c r="M296" s="9" t="str"/>
+      <x:c r="N296" s="41" t="str"/>
+    </x:row>
+    <x:row r="297" ht="1029.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A297" s="40" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="B297" s="9" t="str">
+        <x:v>audi-q3-timing-chain-tensioner-2015</x:v>
+      </x:c>
+      <x:c r="C297" s="9" t="str">
+        <x:v>2015-2020 | Audi | Q3 | EA888</x:v>
+      </x:c>
+      <x:c r="D297" s="9" t="str">
+        <x:v>Timing Chain Tensioner Failure (2.0 TFSI Engine)</x:v>
+      </x:c>
+      <x:c r="E297" s="9" t="str">
+        <x:v>PREVENTIVE REPLACEMENT: Replace timing chain, tensioners, and guides at 80,000-100,000 miles BEFORE rattling starts ($2,000-$3,000). If rattling has started, DO NOT delay—chain can jump at any moment. Repair requires removing front engine cover, water pump, thermostat. Labor is 8-12 hours. Use ONLY OEM Audi parts—aftermarket tensioners fail quickly. Change oil every 5,000 miles and check oil level weekly to prevent accelerated tensioner wear. If catastrophic failure occurs, engine replacement ($6,000-$10,000) is often more cost-effective than rebuild. 2021+ Q3 models have updated parts and are more reliable.</x:v>
+      </x:c>
+      <x:c r="F297" s="9" t="str">
+        <x:v>Split 2015-2018 and 2019-2020 engine generations; exact timing diagnosis/kit; post-failure damage assessment</x:v>
+      </x:c>
+      <x:c r="G297" s="9" t="str">
+        <x:v>MULTI-GENERATION TIMING GATE</x:v>
+      </x:c>
+      <x:c r="H297" s="9" t="str">
+        <x:v>Audi Q3 timing-chain catalog</x:v>
+      </x:c>
+      <x:c r="I297" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/Q3-Quattro/Timing-Chain-Kit/</x:v>
+      </x:c>
+      <x:c r="J297" s="9" t="str">
+        <x:v>2015-2020 Q3; exact generation/engine/VIN and kit contents</x:v>
+      </x:c>
+      <x:c r="K297" s="9" t="str">
+        <x:v>engine-specific timing catalog</x:v>
+      </x:c>
+      <x:c r="L297" s="9" t="str"/>
+      <x:c r="M297" s="9" t="str">
+        <x:v>The range crosses platforms/EA888 revisions.</x:v>
+      </x:c>
+      <x:c r="N297" s="41" t="str">
+        <x:v>Remove universal interval, labor, aftermarket-failure and water-pump/thermostat claims.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A298" s="40" t="str"/>
+      <x:c r="B298" s="9" t="str"/>
+      <x:c r="C298" s="9" t="str"/>
+      <x:c r="D298" s="9" t="str"/>
+      <x:c r="E298" s="9" t="str"/>
+      <x:c r="F298" s="9" t="str"/>
+      <x:c r="G298" s="9" t="str"/>
+      <x:c r="H298" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I298" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J298" s="9" t="str">
+        <x:v>generation-specific timing diagnosis</x:v>
+      </x:c>
+      <x:c r="K298" s="9" t="str">
+        <x:v>specialist engine service</x:v>
+      </x:c>
+      <x:c r="L298" s="9" t="str"/>
+      <x:c r="M298" s="9" t="str"/>
+      <x:c r="N298" s="41" t="str"/>
+    </x:row>
+    <x:row r="299" ht="567.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A299" s="40" t="n">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="B299" s="9" t="str">
+        <x:v>audi-q3-water-pump-2015</x:v>
+      </x:c>
+      <x:c r="C299" s="9" t="str">
+        <x:v>2015-2018 | Audi | Q3 | 2.0 TFSI</x:v>
+      </x:c>
+      <x:c r="D299" s="9" t="str">
+        <x:v>2015-2018 Audi Q3 Coolant-Module Leak TSB 2061604/5</x:v>
+      </x:c>
+      <x:c r="E299" s="9" t="str">
+        <x:v>Pressure-test the cooling system and document the leak. Replace only the component that is leaking—the coolant pump or thermostat housing—then align the two components flush, torque the connecting bolts as specified and verify the pump-belt tension is within Audi’s procedure. Confirm current parts and warranty coverage with Audi; do not order by model year alone.</x:v>
+      </x:c>
+      <x:c r="F299" s="9" t="str">
+        <x:v>Pressure-test/document; replace confirmed pump or thermostat housing only; align/torque/belt tension per Audi; VIN/current parts and coverage</x:v>
+      </x:c>
+      <x:c r="G299" s="9" t="str">
+        <x:v>TSB LEAK-SOURCE GATE</x:v>
+      </x:c>
+      <x:c r="H299" s="9" t="str">
+        <x:v>Audi Q3 water-pump catalog</x:v>
+      </x:c>
+      <x:c r="I299" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/Q3-Quattro/Water-Pump/</x:v>
+      </x:c>
+      <x:c r="J299" s="9" t="str">
+        <x:v>2015-2018 Q3 2.0 TFSI; confirmed component and VIN only</x:v>
+      </x:c>
+      <x:c r="K299" s="9" t="str">
+        <x:v>conditional pump catalog</x:v>
+      </x:c>
+      <x:c r="L299" s="9" t="str"/>
+      <x:c r="M299" s="9" t="str">
+        <x:v>Pump and housing are separate repair branches.</x:v>
+      </x:c>
+      <x:c r="N299" s="41" t="str">
+        <x:v>Do not order by model year or bundle both.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A300" s="40" t="str"/>
+      <x:c r="B300" s="9" t="str"/>
+      <x:c r="C300" s="9" t="str"/>
+      <x:c r="D300" s="9" t="str"/>
+      <x:c r="E300" s="9" t="str"/>
+      <x:c r="F300" s="9" t="str"/>
+      <x:c r="G300" s="9" t="str"/>
+      <x:c r="H300" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I300" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J300" s="9" t="str">
+        <x:v>TSB 2061604/5 parts/procedure/coverage</x:v>
+      </x:c>
+      <x:c r="K300" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L300" s="9" t="str"/>
+      <x:c r="M300" s="9" t="str"/>
+      <x:c r="N300" s="41" t="str"/>
+    </x:row>
+    <x:row r="301" ht="580.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A301" s="40" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="B301" s="9" t="str">
+        <x:v>audi-q3-water-pump-coolant-2015</x:v>
+      </x:c>
+      <x:c r="C301" s="9" t="str">
+        <x:v>2020-2024 | Audi | Q3 | 2.0 TFSI</x:v>
+      </x:c>
+      <x:c r="D301" s="9" t="str">
+        <x:v>2020-2024 Audi Q3 Coolant-Pump Leak TSB 2071515/1</x:v>
+      </x:c>
+      <x:c r="E301" s="9" t="str">
+        <x:v>Document the suspected leak, clean and dry all coolant traces, fill the system to the correct level and reassess after driving a few miles. If no fresh leak returns, continue observing without replacing parts. If leakage recurs, replace only the component causing it under the exact VIN, engine and part criteria. Outside applicable warranty, Audi states the bulletin is informational.</x:v>
+      </x:c>
+      <x:c r="F301" s="9" t="str">
+        <x:v>Clean/dry/fill and reassess after driving; exact recurring leak source/VIN component only; coverage check</x:v>
+      </x:c>
+      <x:c r="G301" s="9" t="str">
+        <x:v>SOURCE-YEAR MISMATCH / TSB LEAK-CONFIRMATION</x:v>
+      </x:c>
+      <x:c r="H301" s="9" t="str">
+        <x:v>Audi Q3 water-pump catalog</x:v>
+      </x:c>
+      <x:c r="I301" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/Q3-Quattro/Water-Pump/</x:v>
+      </x:c>
+      <x:c r="J301" s="9" t="str">
+        <x:v>2020-2024 Q3 2.0 TFSI after fresh recurring leak confirmation</x:v>
+      </x:c>
+      <x:c r="K301" s="9" t="str">
+        <x:v>conditional pump catalog</x:v>
+      </x:c>
+      <x:c r="L301" s="9" t="str"/>
+      <x:c r="M301" s="9" t="str">
+        <x:v>No fresh leak means observation, not parts.</x:v>
+      </x:c>
+      <x:c r="N301" s="41" t="str">
+        <x:v>Identifier says 2015; align to 2020-2024.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302" ht="66" hidden="0" customHeight="1">
+      <x:c r="A302" s="40" t="str"/>
+      <x:c r="B302" s="9" t="str"/>
+      <x:c r="C302" s="9" t="str"/>
+      <x:c r="D302" s="9" t="str"/>
+      <x:c r="E302" s="9" t="str"/>
+      <x:c r="F302" s="9" t="str"/>
+      <x:c r="G302" s="9" t="str"/>
+      <x:c r="H302" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I302" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J302" s="9" t="str">
+        <x:v>TSB 2071515/1 diagnosis/coverage</x:v>
+      </x:c>
+      <x:c r="K302" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L302" s="9" t="str"/>
+      <x:c r="M302" s="9" t="str"/>
+      <x:c r="N302" s="41" t="str"/>
+    </x:row>
+    <x:row r="303" ht="396" hidden="0" customHeight="1">
+      <x:c r="A303" s="40" t="n">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B303" s="9" t="str">
+        <x:v>audi-q4-etron-brake-rollaway-2022</x:v>
+      </x:c>
+      <x:c r="C303" s="9" t="str">
+        <x:v>2022-2023 | Audi | Q4 e-tron</x:v>
+      </x:c>
+      <x:c r="D303" s="9" t="str">
+        <x:v>2022-2023 Audi Q4 e-tron Rollaway Recall 454R / NHTSA 25V120</x:v>
+      </x:c>
+      <x:c r="E303" s="9" t="str">
+        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. The free recall remedy updates the brake-control-unit software. Until completed, verify the selected gear and always engage the parking brake before leaving the vehicle.</x:v>
+      </x:c>
+      <x:c r="F303" s="9" t="str">
+        <x:v>VIN/454R/25V120 completion check; dealer brake-control software update; always Park/parking brake until complete</x:v>
+      </x:c>
+      <x:c r="G303" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H303" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I303" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J303" s="9" t="str">
+        <x:v>2022-2023 Q4 e-tron VIN check for 454R</x:v>
+      </x:c>
+      <x:c r="K303" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L303" s="9" t="str"/>
+      <x:c r="M303" s="9" t="str">
+        <x:v>The remedy is software.</x:v>
+      </x:c>
+      <x:c r="N303" s="41" t="str">
+        <x:v>Do not link brake or parking components.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A304" s="40" t="str"/>
+      <x:c r="B304" s="9" t="str"/>
+      <x:c r="C304" s="9" t="str"/>
+      <x:c r="D304" s="9" t="str"/>
+      <x:c r="E304" s="9" t="str"/>
+      <x:c r="F304" s="9" t="str"/>
+      <x:c r="G304" s="9" t="str"/>
+      <x:c r="H304" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I304" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J304" s="9" t="str">
+        <x:v>25V120 VIN history</x:v>
+      </x:c>
+      <x:c r="K304" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L304" s="9" t="str"/>
+      <x:c r="M304" s="9" t="str"/>
+      <x:c r="N304" s="41" t="str"/>
+    </x:row>
+    <x:row r="305" ht="528" hidden="0" customHeight="1">
+      <x:c r="A305" s="40" t="n">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="B305" s="9" t="str">
+        <x:v>audi-q4-etron-charging-port-2022</x:v>
+      </x:c>
+      <x:c r="C305" s="9" t="str">
+        <x:v>2022-2024 | Audi | Q4 e-tron</x:v>
+      </x:c>
+      <x:c r="D305" s="9" t="str">
+        <x:v>2022-2024 Audi Q4 e-tron Charging-Cable Recall 93U6/93U8 / NHTSA 23V842</x:v>
+      </x:c>
+      <x:c r="E305" s="9" t="str">
+        <x:v>Check the VIN and campaign instructions with Audi or NHTSA. The recall advises owners not to use the affected 220V/240V compact cable and to use the 110V cable or public charging until Audi supplies the replacement 220V/240V cable with an incorporated temperature sensor at no charge. Do not order a charging inlet from this card.</x:v>
+      </x:c>
+      <x:c r="F305" s="9" t="str">
+        <x:v>VIN/93U6/93U8/23V842 instructions; stop affected 220/240V cable; temporary 110V/public charging; free sensor-equipped replacement cable</x:v>
+      </x:c>
+      <x:c r="G305" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H305" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I305" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J305" s="9" t="str">
+        <x:v>2022-2024 Q4 e-tron VIN/cable recall check</x:v>
+      </x:c>
+      <x:c r="K305" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L305" s="9" t="str"/>
+      <x:c r="M305" s="9" t="str">
+        <x:v>The recalled item is the cable, not the vehicle inlet.</x:v>
+      </x:c>
+      <x:c r="N305" s="41" t="str">
+        <x:v>Do not link a charging inlet or retail cable substitute.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A306" s="40" t="str"/>
+      <x:c r="B306" s="9" t="str"/>
+      <x:c r="C306" s="9" t="str"/>
+      <x:c r="D306" s="9" t="str"/>
+      <x:c r="E306" s="9" t="str"/>
+      <x:c r="F306" s="9" t="str"/>
+      <x:c r="G306" s="9" t="str"/>
+      <x:c r="H306" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I306" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J306" s="9" t="str">
+        <x:v>23V842 VIN history</x:v>
+      </x:c>
+      <x:c r="K306" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L306" s="9" t="str"/>
+      <x:c r="M306" s="9" t="str"/>
+      <x:c r="N306" s="41" t="str"/>
+    </x:row>
+    <x:row r="307" ht="1003.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A307" s="40" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="B307" s="9" t="str">
+        <x:v>audi-q4-etron-cold-weather-range-2022</x:v>
+      </x:c>
+      <x:c r="C307" s="9" t="str">
+        <x:v>2023-2024 | Audi | Q4 e-tron</x:v>
+      </x:c>
+      <x:c r="D307" s="9" t="str">
+        <x:v>Severe Cold Weather Range Loss (Models Without Heat Pump)</x:v>
+      </x:c>
+      <x:c r="E307" s="9" t="str">
+        <x:v>Check your build sheet or window sticker to determine if your Q4 e-tron has a heat pump - vehicles built after February 2023 likely do NOT have one. For non-heat-pump models: use seat heaters and steering wheel heater instead of cabin air heater to preserve range. Pre-condition the cabin while plugged in before departing. Set cabin temperature to 68F or lower. Enable eco mode for climate. Use range-optimized route planning. For heat pump equipped models experiencing issues: dealer service may need specialized R-744 (CO2) refrigerant which many shops don't stock - call ahead. Aftermarket heat pump installation is NOT feasible.</x:v>
+      </x:c>
+      <x:c r="F307" s="9" t="str">
+        <x:v>Verify heat-pump equipment by VIN/build; owner-manual preconditioning/climate/range practices; Audi-qualified R744 diagnosis only for equipped malfunction</x:v>
+      </x:c>
+      <x:c r="G307" s="9" t="str">
+        <x:v>EQUIPMENT / CLIMATE-SERVICE SPLIT</x:v>
+      </x:c>
+      <x:c r="H307" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I307" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J307" s="9" t="str">
+        <x:v>2023-2024 Q4 e-tron VIN heat-pump equipment and R744 service</x:v>
+      </x:c>
+      <x:c r="K307" s="9" t="str">
+        <x:v>manufacturer EV climate service</x:v>
+      </x:c>
+      <x:c r="L307" s="9" t="str"/>
+      <x:c r="M307" s="9" t="str">
+        <x:v>Normal cold-weather range loss and a failed heat pump are different cases.</x:v>
+      </x:c>
+      <x:c r="N307" s="41" t="str">
+        <x:v>Do not infer equipment from February 2023 alone or link aftermarket heat-pump parts.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308" ht="382.79998779296875" hidden="0" customHeight="1">
+      <x:c r="A308" s="40" t="n">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="B308" s="9" t="str">
+        <x:v>audi-q4-etron-headlight-module-2022</x:v>
+      </x:c>
+      <x:c r="C308" s="9" t="str">
+        <x:v>2022-2024 | Audi | Q4 e-tron</x:v>
+      </x:c>
+      <x:c r="D308" s="9" t="str">
+        <x:v>2022-2024 Audi Q4 e-tron Headlight Recall 941L / NHTSA 24V361</x:v>
+      </x:c>
+      <x:c r="E308" s="9" t="str">
+        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. The free remedy updates the headlight-control module with a corrected data set. Do not substitute relays, bulbs, a multimeter or a headlight assembly for the campaign software update.</x:v>
+      </x:c>
+      <x:c r="F308" s="9" t="str">
+        <x:v>VIN/941L/24V361 check; dealer corrected headlight-control data set</x:v>
+      </x:c>
+      <x:c r="G308" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H308" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I308" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J308" s="9" t="str">
+        <x:v>2022-2024 Q4 e-tron 941L</x:v>
+      </x:c>
+      <x:c r="K308" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L308" s="9" t="str"/>
+      <x:c r="M308" s="9" t="str">
+        <x:v>Software is the free remedy.</x:v>
+      </x:c>
+      <x:c r="N308" s="41" t="str">
+        <x:v>Do not link bulbs, relays, meter or headlamp.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A309" s="40" t="str"/>
+      <x:c r="B309" s="9" t="str"/>
+      <x:c r="C309" s="9" t="str"/>
+      <x:c r="D309" s="9" t="str"/>
+      <x:c r="E309" s="9" t="str"/>
+      <x:c r="F309" s="9" t="str"/>
+      <x:c r="G309" s="9" t="str"/>
+      <x:c r="H309" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I309" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J309" s="9" t="str">
+        <x:v>24V361 VIN history</x:v>
+      </x:c>
+      <x:c r="K309" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L309" s="9" t="str"/>
+      <x:c r="M309" s="9" t="str"/>
+      <x:c r="N309" s="41" t="str"/>
+    </x:row>
+    <x:row r="310" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A310" s="40" t="n">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="B310" s="9" t="str">
+        <x:v>audi-q4-etron-hv-coolant-2022</x:v>
+      </x:c>
+      <x:c r="C310" s="9" t="str">
+        <x:v>2022-2024 | Audi | Q4 e-tron</x:v>
+      </x:c>
+      <x:c r="D310" s="9" t="str">
+        <x:v>Battery Cooling System Efficiency Issues</x:v>
+      </x:c>
+      <x:c r="E310" s="9" t="str">
+        <x:v>Bleed HV coolant circuit of air. Check coolant pump operation. Dealer service required for HV system work.</x:v>
+      </x:c>
+      <x:c r="F310" s="9" t="str">
+        <x:v>Audi-qualified HV coolant bleed and pump/circuit diagnosis</x:v>
+      </x:c>
+      <x:c r="G310" s="9" t="str">
+        <x:v>HIGH-VOLTAGE SERVICE ONLY</x:v>
+      </x:c>
+      <x:c r="H310" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I310" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J310" s="9" t="str">
+        <x:v>2022-2024 Q4 e-tron HV thermal system</x:v>
+      </x:c>
+      <x:c r="K310" s="9" t="str">
+        <x:v>authorized EV service</x:v>
+      </x:c>
+      <x:c r="L310" s="9" t="str"/>
+      <x:c r="M310" s="9" t="str">
+        <x:v>Source requires dealer HV work and names no exact failed part.</x:v>
+      </x:c>
+      <x:c r="N310" s="41" t="str">
+        <x:v>No owner coolant/pump link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311" ht="198" hidden="0" customHeight="1">
+      <x:c r="A311" s="40" t="n">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="B311" s="9" t="str">
+        <x:v>audi-q4-etron-ota-software-2022</x:v>
+      </x:c>
+      <x:c r="C311" s="9" t="str">
+        <x:v>2022-2024 | Audi | Q4 e-tron</x:v>
+      </x:c>
+      <x:c r="D311" s="9" t="str">
+        <x:v>OTA Updates and Software Glitches</x:v>
+      </x:c>
+      <x:c r="E311" s="9" t="str">
+        <x:v>Perform hard reset. Check dealer for latest software version. Some issues require dealer-applied updates only.</x:v>
+      </x:c>
+      <x:c r="F311" s="9" t="str">
+        <x:v>Document symptom/version; safe reboot; VIN-specific dealer update</x:v>
+      </x:c>
+      <x:c r="G311" s="9" t="str">
+        <x:v>SOFTWARE SERVICE ONLY</x:v>
+      </x:c>
+      <x:c r="H311" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I311" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J311" s="9" t="str">
+        <x:v>2022-2024 Q4 e-tron software diagnosis/update</x:v>
+      </x:c>
+      <x:c r="K311" s="9" t="str">
+        <x:v>manufacturer software service</x:v>
+      </x:c>
+      <x:c r="L311" s="9" t="str"/>
+      <x:c r="M311" s="9" t="str">
+        <x:v>No exact hardware repair is identified.</x:v>
+      </x:c>
+      <x:c r="N311" s="41" t="str">
+        <x:v>Do not promise a hard reset fixes persistent faults.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312" ht="501.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A312" s="40" t="n">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B312" s="9" t="str">
+        <x:v>audi-q4-etron-software-glitches-2022</x:v>
+      </x:c>
+      <x:c r="C312" s="9" t="str">
+        <x:v>2024-2025 | Audi | Q4 e-tron</x:v>
+      </x:c>
+      <x:c r="D312" s="9" t="str">
+        <x:v>2024-2025 Audi Q4 e-tron On-Board-Charger Recall 93FR / NHTSA 25V125</x:v>
+      </x:c>
+      <x:c r="E312" s="9" t="str">
+        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. The free remedy replaces the on-board charger. If the vehicle warns of an electrical-system fault or loses drive power, move out of traffic safely and arrange Audi recovery/inspection; do not buy a 12-volt battery or generic electrical parts from this summary.</x:v>
+      </x:c>
+      <x:c r="F312" s="9" t="str">
+        <x:v>VIN/93FR/25V125 check; free on-board charger replacement; recovery for drive-power warning</x:v>
+      </x:c>
+      <x:c r="G312" s="9" t="str">
+        <x:v>SOURCE-ID MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H312" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I312" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J312" s="9" t="str">
+        <x:v>2024-2025 Q4 e-tron 93FR</x:v>
+      </x:c>
+      <x:c r="K312" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L312" s="9" t="str"/>
+      <x:c r="M312" s="9" t="str">
+        <x:v>This is charger recall, not generic glitches.</x:v>
+      </x:c>
+      <x:c r="N312" s="41" t="str">
+        <x:v>Rename/re-key; no 12V battery link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A313" s="40" t="str"/>
+      <x:c r="B313" s="9" t="str"/>
+      <x:c r="C313" s="9" t="str"/>
+      <x:c r="D313" s="9" t="str"/>
+      <x:c r="E313" s="9" t="str"/>
+      <x:c r="F313" s="9" t="str"/>
+      <x:c r="G313" s="9" t="str"/>
+      <x:c r="H313" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I313" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J313" s="9" t="str">
+        <x:v>25V125 VIN history</x:v>
+      </x:c>
+      <x:c r="K313" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L313" s="9" t="str"/>
+      <x:c r="M313" s="9" t="str"/>
+      <x:c r="N313" s="41" t="str"/>
+    </x:row>
+    <x:row r="314" ht="805.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A314" s="40" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="B314" s="9" t="str">
+        <x:v>audi-q5-carbon-buildup-2009</x:v>
+      </x:c>
+      <x:c r="C314" s="9" t="str">
+        <x:v>2009-2025 | Audi | Q5</x:v>
+      </x:c>
+      <x:c r="D314" s="9" t="str">
+        <x:v>2009-2025 Q5 Gasoline-Quality Deposit Diagnosis - TSB 2014753/13</x:v>
+      </x:c>
+      <x:c r="E314" s="9" t="str">
+        <x:v>Confirm the exact gasoline-powered vehicle, fuel quality, symptoms and stored DTCs before cleaning or replacing components. If contaminated gasoline is suspected, change fuel source; if detergent quality is suspect, Audi recommends Top Tier detergent gasoline. Continue guided diagnosis if the condition persists and identify the actual deposit location before selecting any cleaning procedure. Do not prescribe routine walnut blasting, a catch can, chemical cleaner or high-RPM driving from this record.</x:v>
+      </x:c>
+      <x:c r="F314" s="9" t="str">
+        <x:v>Fuel quality, symptoms and DTC diagnosis; Top Tier fuel when applicable; locate deposits before cleaning</x:v>
+      </x:c>
+      <x:c r="G314" s="9" t="str">
+        <x:v>FUEL-QUALITY TSB / NO CLEANER LINK</x:v>
+      </x:c>
+      <x:c r="H314" s="9" t="str">
+        <x:v>Top Tier gasoline stations</x:v>
+      </x:c>
+      <x:c r="I314" s="9" t="str">
+        <x:v>https://www.toptiergas.com/gasoline-brands/</x:v>
+      </x:c>
+      <x:c r="J314" s="9" t="str">
+        <x:v>US detergent-fuel route recommended by Audi when applicable</x:v>
+      </x:c>
+      <x:c r="K314" s="9" t="str">
+        <x:v>approved fuel-quality route</x:v>
+      </x:c>
+      <x:c r="L314" s="9" t="str"/>
+      <x:c r="M314" s="9" t="str">
+        <x:v>TSB does not establish intake carbon.</x:v>
+      </x:c>
+      <x:c r="N314" s="41" t="str">
+        <x:v>No walnut blast, catch can, chemical or high-RPM prescription.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A315" s="40" t="str"/>
+      <x:c r="B315" s="9" t="str"/>
+      <x:c r="C315" s="9" t="str"/>
+      <x:c r="D315" s="9" t="str"/>
+      <x:c r="E315" s="9" t="str"/>
+      <x:c r="F315" s="9" t="str"/>
+      <x:c r="G315" s="9" t="str"/>
+      <x:c r="H315" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I315" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J315" s="9" t="str">
+        <x:v>2009-2025 Q5 deposit diagnosis</x:v>
+      </x:c>
+      <x:c r="K315" s="9" t="str">
+        <x:v>specialist service</x:v>
+      </x:c>
+      <x:c r="L315" s="9" t="str"/>
+      <x:c r="M315" s="9" t="str"/>
+      <x:c r="N315" s="41" t="str"/>
+    </x:row>
+    <x:row r="316" ht="712.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A316" s="40" t="n">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="B316" s="9" t="str">
+        <x:v>audi-q5-coolant-leaks-2009</x:v>
+      </x:c>
+      <x:c r="C316" s="9" t="str">
+        <x:v>2011-2017 | Audi | Q5</x:v>
+      </x:c>
+      <x:c r="D316" s="9" t="str">
+        <x:v>2011-2017 Q5 2.0T Coolant Leak at Pump or Thermostat - TSB 2061604/5</x:v>
+      </x:c>
+      <x:c r="E316" s="9" t="str">
+        <x:v>Photograph the leak with date and VIN reference and pressure-test the cooling system according to Audi workshop instructions. Replace only the component confirmed to be leaking: the coolant pump or the thermostat housing. Follow Elsa for removal, assembly, belt-tension checking and current ETKA fitment. Do not replace every plastic cooling component, buy a bundled module or infer the source from a warning or puddle alone.</x:v>
+      </x:c>
+      <x:c r="F316" s="9" t="str">
+        <x:v>Photo/pressure test; confirmed pump or thermostat housing only; Elsa assembly/belt check and ETKA fitment</x:v>
+      </x:c>
+      <x:c r="G316" s="9" t="str">
+        <x:v>SOURCE-YEAR MISMATCH / LEAK-SOURCE TSB</x:v>
+      </x:c>
+      <x:c r="H316" s="9" t="str">
+        <x:v>Audi Q5 water-pump catalog</x:v>
+      </x:c>
+      <x:c r="I316" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/Q5/Water-Pump/</x:v>
+      </x:c>
+      <x:c r="J316" s="9" t="str">
+        <x:v>2011-2017 Q5 2.0T confirmed component/VIN</x:v>
+      </x:c>
+      <x:c r="K316" s="9" t="str">
+        <x:v>conditional pump catalog</x:v>
+      </x:c>
+      <x:c r="L316" s="9" t="str"/>
+      <x:c r="M316" s="9" t="str">
+        <x:v>Pump and housing are separate branches.</x:v>
+      </x:c>
+      <x:c r="N316" s="41" t="str">
+        <x:v>Identifier says 2009; do not bundle modules.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="317" ht="66" hidden="0" customHeight="1">
+      <x:c r="A317" s="40" t="str"/>
+      <x:c r="B317" s="9" t="str"/>
+      <x:c r="C317" s="9" t="str"/>
+      <x:c r="D317" s="9" t="str"/>
+      <x:c r="E317" s="9" t="str"/>
+      <x:c r="F317" s="9" t="str"/>
+      <x:c r="G317" s="9" t="str"/>
+      <x:c r="H317" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I317" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J317" s="9" t="str">
+        <x:v>TSB 2061604/5 procedure</x:v>
+      </x:c>
+      <x:c r="K317" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L317" s="9" t="str"/>
+      <x:c r="M317" s="9" t="str"/>
+      <x:c r="N317" s="41" t="str"/>
+    </x:row>
+    <x:row r="318" ht="831.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A318" s="40" t="n">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="B318" s="9" t="str">
+        <x:v>audi-q5-oil-consumption-2010</x:v>
+      </x:c>
+      <x:c r="C318" s="9" t="str">
+        <x:v>2011-2011 | Audi | Q5</x:v>
+      </x:c>
+      <x:c r="D318" s="9" t="str">
+        <x:v>2011 Q5 2.0T CAEB Oil-Consumption Procedure - TSB 2027731/7</x:v>
+      </x:c>
+      <x:c r="E318" s="9" t="str">
+        <x:v>Verify the VIN and CAEB engine, document actual oil use and have an Audi-capable shop follow TSB 2027731/7. Check the crankcase-pressure regulating valve, use the current ETKA valve when required, replace the specified front seal and bolt, perform the Q5 SVM software update and run the electronic oil-consumption measurement exactly as directed. If the low-oil warning appears during the test, return for evaluation rather than adding oil. Do not replace pistons, rings, a turbo or a PCV part from this record alone.</x:v>
+      </x:c>
+      <x:c r="F318" s="9" t="str">
+        <x:v>2011 CAEB VIN and measured TSB procedure; conditional PCV, front seal/bolt, SVM and electronic test</x:v>
+      </x:c>
+      <x:c r="G318" s="9" t="str">
+        <x:v>SOURCE-YEAR MISMATCH / TSB MEASUREMENT</x:v>
+      </x:c>
+      <x:c r="H318" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I318" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J318" s="9" t="str">
+        <x:v>2011 Q5 CAEB TSB 2027731/7</x:v>
+      </x:c>
+      <x:c r="K318" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L318" s="9" t="str"/>
+      <x:c r="M318" s="9" t="str">
+        <x:v>Staged procedure precedes internal repair.</x:v>
+      </x:c>
+      <x:c r="N318" s="41" t="str">
+        <x:v>Do not link pistons, turbo or PCV alone.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319" ht="501.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A319" s="40" t="n">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B319" s="9" t="str">
+        <x:v>audi-q5-sportback-connecting-rod-bearing-failure</x:v>
+      </x:c>
+      <x:c r="C319" s="9" t="str">
+        <x:v>2021-2023 | Audi | Q5 Sportback</x:v>
+      </x:c>
+      <x:c r="D319" s="9" t="str">
+        <x:v>2021-2023 Audi Q5 Sportback Engine Recall 13i5 / NHTSA 22V753</x:v>
+      </x:c>
+      <x:c r="E319" s="9" t="str">
+        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. Dealers inspect eligible vehicles and replace an affected engine when necessary at no charge. If the engine develops severe knocking, warning messages, smoke, oil leakage or a stall, stop safely and arrange dealer recovery rather than continuing to drive.</x:v>
+      </x:c>
+      <x:c r="F319" s="9" t="str">
+        <x:v>VIN/13i5/22V753 check; dealer inspection/conditional engine; stop/recover for severe symptoms</x:v>
+      </x:c>
+      <x:c r="G319" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H319" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I319" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J319" s="9" t="str">
+        <x:v>2021-2023 Q5 Sportback 13i5</x:v>
+      </x:c>
+      <x:c r="K319" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L319" s="9" t="str"/>
+      <x:c r="M319" s="9" t="str">
+        <x:v>Engine remedy is campaign-controlled.</x:v>
+      </x:c>
+      <x:c r="N319" s="41" t="str">
+        <x:v>No bearing/engine commerce link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A320" s="40" t="str"/>
+      <x:c r="B320" s="9" t="str"/>
+      <x:c r="C320" s="9" t="str"/>
+      <x:c r="D320" s="9" t="str"/>
+      <x:c r="E320" s="9" t="str"/>
+      <x:c r="F320" s="9" t="str"/>
+      <x:c r="G320" s="9" t="str"/>
+      <x:c r="H320" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I320" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J320" s="9" t="str">
+        <x:v>22V753 VIN history</x:v>
+      </x:c>
+      <x:c r="K320" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L320" s="9" t="str"/>
+      <x:c r="M320" s="9" t="str"/>
+      <x:c r="N320" s="41" t="str"/>
+    </x:row>
+    <x:row r="321" ht="580.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A321" s="40" t="n">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="B321" s="9" t="str">
+        <x:v>audi-q5-sportback-ea888-water-pump-thermostat-housing-coolant-leak</x:v>
+      </x:c>
+      <x:c r="C321" s="9" t="str">
+        <x:v>2021-2024 | Audi | Q5 Sportback | 2.0 TFSI</x:v>
+      </x:c>
+      <x:c r="D321" s="9" t="str">
+        <x:v>2021-2024 Audi Q5 Sportback Coolant-Pump Leak TSB 2071515/1</x:v>
+      </x:c>
+      <x:c r="E321" s="9" t="str">
+        <x:v>Document the suspected leak, clean and dry all coolant traces, fill the system correctly and reassess after driving a few miles. If no fresh leak returns, continue observing without replacing parts. If leakage recurs, replace only the component causing it under the exact VIN, engine and part criteria. Confirm current coverage with Audi; do not order by model year alone.</x:v>
+      </x:c>
+      <x:c r="F321" s="9" t="str">
+        <x:v>Clean/dry/fill/road reassess; exact recurring leak component/VIN only</x:v>
+      </x:c>
+      <x:c r="G321" s="9" t="str">
+        <x:v>TSB LEAK-CONFIRMATION</x:v>
+      </x:c>
+      <x:c r="H321" s="9" t="str">
+        <x:v>Audi Q5 water-pump catalog</x:v>
+      </x:c>
+      <x:c r="I321" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/Q5/Water-Pump/</x:v>
+      </x:c>
+      <x:c r="J321" s="9" t="str">
+        <x:v>2021-2024 Q5 Sportback after fresh leak confirmation</x:v>
+      </x:c>
+      <x:c r="K321" s="9" t="str">
+        <x:v>conditional pump catalog</x:v>
+      </x:c>
+      <x:c r="L321" s="9" t="str"/>
+      <x:c r="M321" s="9" t="str">
+        <x:v>No fresh leak means no parts.</x:v>
+      </x:c>
+      <x:c r="N321" s="41" t="str">
+        <x:v>Do not order by model year.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="322" ht="66" hidden="0" customHeight="1">
+      <x:c r="A322" s="40" t="str"/>
+      <x:c r="B322" s="9" t="str"/>
+      <x:c r="C322" s="9" t="str"/>
+      <x:c r="D322" s="9" t="str"/>
+      <x:c r="E322" s="9" t="str"/>
+      <x:c r="F322" s="9" t="str"/>
+      <x:c r="G322" s="9" t="str"/>
+      <x:c r="H322" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I322" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J322" s="9" t="str">
+        <x:v>TSB 2071515/1</x:v>
+      </x:c>
+      <x:c r="K322" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L322" s="9" t="str"/>
+      <x:c r="M322" s="9" t="str"/>
+      <x:c r="N322" s="41" t="str"/>
+    </x:row>
+    <x:row r="323" ht="528" hidden="0" customHeight="1">
+      <x:c r="A323" s="40" t="n">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="B323" s="9" t="str">
+        <x:v>audi-q5-sportback-excessive-engine-oil-consumption</x:v>
+      </x:c>
+      <x:c r="C323" s="9" t="str">
+        <x:v>2021-2025 | Audi | Q5 Sportback | 2.0T TFSI 45 TFSI (EA888)</x:v>
+      </x:c>
+      <x:c r="D323" s="9" t="str">
+        <x:v>Excessive Engine Oil Consumption (2.0 TFSI EA888)</x:v>
+      </x:c>
+      <x:c r="E323" s="9" t="str">
+        <x:v>Confirm consumption with a documented Audi oil-consumption test. Remedies range from PCV/oil-separator service and updated piston rings to, in severe cases, piston/ring replacement; walnut-blasting addresses associated intake-valve carbon. Owners should monitor oil level frequently between service intervals as a safeguard.</x:v>
+      </x:c>
+      <x:c r="F323" s="9" t="str">
+        <x:v>Documented consumption; leak/oil/PCV/turbo/mechanical branches; internal parts only after proof</x:v>
+      </x:c>
+      <x:c r="G323" s="9" t="str">
+        <x:v>MEASURED-CONSUMPTION GATE</x:v>
+      </x:c>
+      <x:c r="H323" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I323" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J323" s="9" t="str">
+        <x:v>2021-2025 Q5 Sportback root-cause diagnosis</x:v>
+      </x:c>
+      <x:c r="K323" s="9" t="str">
+        <x:v>specialist engine service</x:v>
+      </x:c>
+      <x:c r="L323" s="9" t="str"/>
+      <x:c r="M323" s="9" t="str">
+        <x:v>PCV, wear and carbon are different concerns.</x:v>
+      </x:c>
+      <x:c r="N323" s="41" t="str">
+        <x:v>No rings or walnut link from consumption alone.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="324" ht="541.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A324" s="40" t="n">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="B324" s="9" t="str">
+        <x:v>audi-q5-sportback-front-assist-phantom-braking-false-emergency-braking</x:v>
+      </x:c>
+      <x:c r="C324" s="9" t="str">
+        <x:v>2021-2025 | Audi | Q5 Sportback</x:v>
+      </x:c>
+      <x:c r="D324" s="9" t="str">
+        <x:v>Front Assist Phantom Braking / False Emergency Braking (ADAS)</x:v>
+      </x:c>
+      <x:c r="E324" s="9" t="str">
+        <x:v>Have the dealer scan for ADAS faults and apply any available radar/camera control-module software updates and sensor recalibration; check for and clear obstructions/misalignment of the front radar. Persistent cases may require sensor replacement. Document incidents and file an NHTSA complaint, as ongoing investigations can drive a recall.</x:v>
+      </x:c>
+      <x:c r="F324" s="9" t="str">
+        <x:v>Document events; scan ADAS; inspect radar/mount/alignment; applicable software/calibration; sensor only if failed</x:v>
+      </x:c>
+      <x:c r="G324" s="9" t="str">
+        <x:v>ADAS DIAGNOSIS SERVICE</x:v>
+      </x:c>
+      <x:c r="H324" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I324" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J324" s="9" t="str">
+        <x:v>2021-2025 Q5 Sportback ADAS diagnosis/calibration</x:v>
+      </x:c>
+      <x:c r="K324" s="9" t="str">
+        <x:v>manufacturer ADAS service</x:v>
+      </x:c>
+      <x:c r="L324" s="9" t="str"/>
+      <x:c r="M324" s="9" t="str">
+        <x:v>Obstruction, alignment, software and sensor faults differ.</x:v>
+      </x:c>
+      <x:c r="N324" s="41" t="str">
+        <x:v>Do not promise recall or link sensor.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325" ht="66" hidden="0" customHeight="1">
+      <x:c r="A325" s="40" t="str"/>
+      <x:c r="B325" s="9" t="str"/>
+      <x:c r="C325" s="9" t="str"/>
+      <x:c r="D325" s="9" t="str"/>
+      <x:c r="E325" s="9" t="str"/>
+      <x:c r="F325" s="9" t="str"/>
+      <x:c r="G325" s="9" t="str"/>
+      <x:c r="H325" s="9" t="str">
+        <x:v>NHTSA complaint portal</x:v>
+      </x:c>
+      <x:c r="I325" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/report-a-safety-problem</x:v>
+      </x:c>
+      <x:c r="J325" s="9" t="str">
+        <x:v>persistent safety incidents</x:v>
+      </x:c>
+      <x:c r="K325" s="9" t="str">
+        <x:v>government reporting</x:v>
+      </x:c>
+      <x:c r="L325" s="9" t="str"/>
+      <x:c r="M325" s="9" t="str"/>
+      <x:c r="N325" s="41" t="str"/>
+    </x:row>
+    <x:row r="326" ht="396" hidden="0" customHeight="1">
+      <x:c r="A326" s="40" t="n">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B326" s="9" t="str">
+        <x:v>audi-q5-sportback-loose-cylinder-head-cover-screws-causing-oil-leak-fire-risk</x:v>
+      </x:c>
+      <x:c r="C326" s="9" t="str">
+        <x:v>2022-2024 | Audi | Q5 Sportback</x:v>
+      </x:c>
+      <x:c r="D326" s="9" t="str">
+        <x:v>2022-2024 Audi Q5 Sportback Head-Cover Recall 15ZK / NHTSA 25V294</x:v>
+      </x:c>
+      <x:c r="E326" s="9" t="str">
+        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. Dealers inspect and replace the screws as necessary at no charge. If oil odor, smoke or visible leakage occurs, stop safely, switch the vehicle off and arrange Audi inspection.</x:v>
+      </x:c>
+      <x:c r="F326" s="9" t="str">
+        <x:v>VIN/15ZK/25V294 check; dealer screw inspection/replacement; stop for oil/smoke</x:v>
+      </x:c>
+      <x:c r="G326" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H326" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I326" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J326" s="9" t="str">
+        <x:v>2022-2024 Q5 Sportback 15ZK</x:v>
+      </x:c>
+      <x:c r="K326" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L326" s="9" t="str"/>
+      <x:c r="M326" s="9" t="str">
+        <x:v>Recall controls remedy.</x:v>
+      </x:c>
+      <x:c r="N326" s="41" t="str">
+        <x:v>No retail screw/cover link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A327" s="40" t="str"/>
+      <x:c r="B327" s="9" t="str"/>
+      <x:c r="C327" s="9" t="str"/>
+      <x:c r="D327" s="9" t="str"/>
+      <x:c r="E327" s="9" t="str"/>
+      <x:c r="F327" s="9" t="str"/>
+      <x:c r="G327" s="9" t="str"/>
+      <x:c r="H327" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I327" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J327" s="9" t="str">
+        <x:v>25V294 VIN history</x:v>
+      </x:c>
+      <x:c r="K327" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L327" s="9" t="str"/>
+      <x:c r="M327" s="9" t="str"/>
+      <x:c r="N327" s="41" t="str"/>
+    </x:row>
+    <x:row r="328" ht="488.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A328" s="40" t="n">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="B328" s="9" t="str">
+        <x:v>audi-q5-sportback-mild-hybrid-electrical-fault-start-stop-failure</x:v>
+      </x:c>
+      <x:c r="C328" s="9" t="str">
+        <x:v>2021-2022 | Audi | Q5 Sportback</x:v>
+      </x:c>
+      <x:c r="D328" s="9" t="str">
+        <x:v>2021-2022 Audi Q5 Sportback Gateway Recall 90S9 / NHTSA 21V947</x:v>
+      </x:c>
+      <x:c r="E328" s="9" t="str">
+        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. The free remedy installs a protective gateway-module cover and seals the underbody seam when necessary. If multiple warnings appear or engine power drops, move out of traffic safely and arrange dealer inspection; do not order a 12-volt battery from this card.</x:v>
+      </x:c>
+      <x:c r="F328" s="9" t="str">
+        <x:v>VIN/90S9/21V947 check; gateway cover and seam seal; safe response to reduced power</x:v>
+      </x:c>
+      <x:c r="G328" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H328" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I328" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J328" s="9" t="str">
+        <x:v>2021-2022 Q5 Sportback 90S9</x:v>
+      </x:c>
+      <x:c r="K328" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L328" s="9" t="str"/>
+      <x:c r="M328" s="9" t="str">
+        <x:v>Gateway protection is the remedy.</x:v>
+      </x:c>
+      <x:c r="N328" s="41" t="str">
+        <x:v>No 12V battery link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A329" s="40" t="str"/>
+      <x:c r="B329" s="9" t="str"/>
+      <x:c r="C329" s="9" t="str"/>
+      <x:c r="D329" s="9" t="str"/>
+      <x:c r="E329" s="9" t="str"/>
+      <x:c r="F329" s="9" t="str"/>
+      <x:c r="G329" s="9" t="str"/>
+      <x:c r="H329" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I329" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J329" s="9" t="str">
+        <x:v>21V947 VIN history</x:v>
+      </x:c>
+      <x:c r="K329" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L329" s="9" t="str"/>
+      <x:c r="M329" s="9" t="str"/>
+      <x:c r="N329" s="41" t="str"/>
+    </x:row>
+    <x:row r="330" ht="514.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A330" s="40" t="n">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="B330" s="9" t="str">
+        <x:v>audi-q5-sportback-phev-high-voltage-battery-overheating-fire-risk</x:v>
+      </x:c>
+      <x:c r="C330" s="9" t="str">
+        <x:v>2021-2024 | Audi | Q5 Sportback | 55 TFSI e quattro, Q5 Sportback TFSI e PHEV | 2.0T TFSI e plug-in hybrid</x:v>
+      </x:c>
+      <x:c r="D330" s="9" t="str">
+        <x:v>PHEV High-Voltage Battery Overheating / Fire Risk (Recall 25V080000)</x:v>
+      </x:c>
+      <x:c r="E330" s="9" t="str">
+        <x:v>Audi installs advanced diagnostic/monitoring software as the final remedy and replaces individual battery modules or the entire high-voltage pack where defective cells are detected, free of charge. Affected owners should follow the do-not-charge guidance until inspected and confirm recall status by VIN.</x:v>
+      </x:c>
+      <x:c r="F330" s="9" t="str">
+        <x:v>VIN/25V080 check; dealer monitoring software and module/pack remedy; follow do-not-charge guidance</x:v>
+      </x:c>
+      <x:c r="G330" s="9" t="str">
+        <x:v>HIGH-VOLTAGE RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H330" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I330" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J330" s="9" t="str">
+        <x:v>Q5 Sportback PHEV VIN check</x:v>
+      </x:c>
+      <x:c r="K330" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L330" s="9" t="str"/>
+      <x:c r="M330" s="9" t="str">
+        <x:v>HV remedy is VIN-controlled.</x:v>
+      </x:c>
+      <x:c r="N330" s="41" t="str">
+        <x:v>No owner battery/charger link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A331" s="40" t="str"/>
+      <x:c r="B331" s="9" t="str"/>
+      <x:c r="C331" s="9" t="str"/>
+      <x:c r="D331" s="9" t="str"/>
+      <x:c r="E331" s="9" t="str"/>
+      <x:c r="F331" s="9" t="str"/>
+      <x:c r="G331" s="9" t="str"/>
+      <x:c r="H331" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I331" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J331" s="9" t="str">
+        <x:v>25V080 VIN history</x:v>
+      </x:c>
+      <x:c r="K331" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L331" s="9" t="str"/>
+      <x:c r="M331" s="9" t="str"/>
+      <x:c r="N331" s="41" t="str"/>
+    </x:row>
+    <x:row r="332" ht="514.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A332" s="40" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="B332" s="9" t="str">
+        <x:v>audi-q5-sportback-rear-brake-squeal-2021</x:v>
+      </x:c>
+      <x:c r="C332" s="9" t="str">
+        <x:v>2021-2026 | Audi | Q5 Sportback | Premium, Premium Plus, Prestige | 2.0T</x:v>
+      </x:c>
+      <x:c r="D332" s="9" t="str">
+        <x:v>Rear Brake Squeal and Premature Pad Wear</x:v>
+      </x:c>
+      <x:c r="E332" s="9" t="str">
+        <x:v>Replace rear brake pads with aftermarket ceramic compound pads that eliminate the metallic resonance squeal. Apply brake pad shims and caliper slide pin lubricant. Have the electronic parking brake calibrated via scan tool to reduce unnecessary auto-apply frequency. Replace rotors if they show scoring or are below minimum thickness.</x:v>
+      </x:c>
+      <x:c r="F332" s="9" t="str">
+        <x:v>Classify noise/wear; measure pads/rotors/hardware; exact PR-code friction part if confirmed; EPB procedure only as required</x:v>
+      </x:c>
+      <x:c r="G332" s="9" t="str">
+        <x:v>BRAKE MEASUREMENT GATE</x:v>
+      </x:c>
+      <x:c r="H332" s="9" t="str">
+        <x:v>Audi Q5 brake-pad catalog</x:v>
+      </x:c>
+      <x:c r="I332" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/Q5/Brake-Pads/</x:v>
+      </x:c>
+      <x:c r="J332" s="9" t="str">
+        <x:v>2021-2026 exact VIN/brake PR code/axle</x:v>
+      </x:c>
+      <x:c r="K332" s="9" t="str">
+        <x:v>vehicle-specific brake catalog</x:v>
+      </x:c>
+      <x:c r="L332" s="9" t="str"/>
+      <x:c r="M332" s="9" t="str">
+        <x:v>Ceramic pads are not universal cure.</x:v>
+      </x:c>
+      <x:c r="N332" s="41" t="str">
+        <x:v>No rotor replacement without measurement; no EPB frequency tweak.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A333" s="40" t="str"/>
+      <x:c r="B333" s="9" t="str"/>
+      <x:c r="C333" s="9" t="str"/>
+      <x:c r="D333" s="9" t="str"/>
+      <x:c r="E333" s="9" t="str"/>
+      <x:c r="F333" s="9" t="str"/>
+      <x:c r="G333" s="9" t="str"/>
+      <x:c r="H333" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I333" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J333" s="9" t="str">
+        <x:v>noise/wear/EPB diagnosis</x:v>
+      </x:c>
+      <x:c r="K333" s="9" t="str">
+        <x:v>specialist brake service</x:v>
+      </x:c>
+      <x:c r="L333" s="9" t="str"/>
+      <x:c r="M333" s="9" t="str"/>
+      <x:c r="N333" s="41" t="str"/>
+    </x:row>
+    <x:row r="334" ht="316.79998779296875" hidden="0" customHeight="1">
+      <x:c r="A334" s="40" t="n">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="B334" s="9" t="str">
+        <x:v>audi-q5-sportback-sunroof-rattle-2021</x:v>
+      </x:c>
+      <x:c r="C334" s="9" t="str">
+        <x:v>2021-2025 | Audi | Q5 Sportback</x:v>
+      </x:c>
+      <x:c r="D334" s="9" t="str">
+        <x:v>Panoramic Sunroof Wind Noise and Rattle</x:v>
+      </x:c>
+      <x:c r="E334" s="9" t="str">
+        <x:v>Clean and lubricate sunroof rails and seals with Krytox or silicone grease. Adjust sunroof alignment via dealer. Replace wind deflector if cracked. In some cases, the sunroof cassette requires re-indexing via scan tool.</x:v>
+      </x:c>
+      <x:c r="F334" s="9" t="str">
+        <x:v>Trace wind/rattle; approved cleaning/lubricant; alignment/deflector/cassette branch</x:v>
+      </x:c>
+      <x:c r="G334" s="9" t="str">
+        <x:v>ROOT-CAUSE BODY SERVICE</x:v>
+      </x:c>
+      <x:c r="H334" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I334" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J334" s="9" t="str">
+        <x:v>2021-2025 Q5 Sportback roof diagnosis</x:v>
+      </x:c>
+      <x:c r="K334" s="9" t="str">
+        <x:v>manufacturer body service</x:v>
+      </x:c>
+      <x:c r="L334" s="9" t="str"/>
+      <x:c r="M334" s="9" t="str">
+        <x:v>Seal, rail, deflector and cassette faults differ.</x:v>
+      </x:c>
+      <x:c r="N334" s="41" t="str">
+        <x:v>No generic grease or scan-tool indexing claim.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335" ht="448.79998779296875" hidden="0" customHeight="1">
+      <x:c r="A335" s="40" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="B335" s="9" t="str">
+        <x:v>audi-q5-sportback-virtual-cockpit-2021</x:v>
+      </x:c>
+      <x:c r="C335" s="9" t="str">
+        <x:v>2021-2021 | Audi | Q5 Sportback</x:v>
+      </x:c>
+      <x:c r="D335" s="9" t="str">
+        <x:v>2021 Audi Q5 Sportback Rearview-Camera Recall 91DZ / NHTSA 22V742</x:v>
+      </x:c>
+      <x:c r="E335" s="9" t="str">
+        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. The free remedy updates the infotainment-unit software. Until repaired, use mirrors and direct observation with extra care while reversing. Do not order a replacement instrument cluster or generic scan tool from this summary.</x:v>
+      </x:c>
+      <x:c r="F335" s="9" t="str">
+        <x:v>VIN/91DZ/22V742 check; dealer infotainment software; direct reverse observation</x:v>
+      </x:c>
+      <x:c r="G335" s="9" t="str">
+        <x:v>SOURCE-ID MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H335" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I335" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J335" s="9" t="str">
+        <x:v>2021 Q5 Sportback 91DZ</x:v>
+      </x:c>
+      <x:c r="K335" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L335" s="9" t="str"/>
+      <x:c r="M335" s="9" t="str">
+        <x:v>Camera software, not cluster hardware.</x:v>
+      </x:c>
+      <x:c r="N335" s="41" t="str">
+        <x:v>No cluster/scanner link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A336" s="40" t="str"/>
+      <x:c r="B336" s="9" t="str"/>
+      <x:c r="C336" s="9" t="str"/>
+      <x:c r="D336" s="9" t="str"/>
+      <x:c r="E336" s="9" t="str"/>
+      <x:c r="F336" s="9" t="str"/>
+      <x:c r="G336" s="9" t="str"/>
+      <x:c r="H336" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I336" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J336" s="9" t="str">
+        <x:v>22V742 VIN history</x:v>
+      </x:c>
+      <x:c r="K336" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L336" s="9" t="str"/>
+      <x:c r="M336" s="9" t="str"/>
+      <x:c r="N336" s="41" t="str"/>
+    </x:row>
+    <x:row r="337" ht="924" hidden="0" customHeight="1">
+      <x:c r="A337" s="40" t="n">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B337" s="9" t="str">
+        <x:v>audi-q5-sunroof-drain-clogs-2009</x:v>
+      </x:c>
+      <x:c r="C337" s="9" t="str">
+        <x:v>2011-2023 | Audi | Q5</x:v>
+      </x:c>
+      <x:c r="D337" s="9" t="str">
+        <x:v>2011-2023 Q5 Panoramic-Sunroof Water Entry - Recall 69P1 / TSB 2075969/2</x:v>
+      </x:c>
+      <x:c r="E337" s="9" t="str">
+        <x:v>For a 2011-2017 panoramic-roof Q5, check the VIN for Recall 69P1 first and follow Audi’s dealer precautions and remedy; until an open recall is completed, do not use the second row and seek prompt inspection if headliner or rear-cabin leakage is visible. For a 2018-2023 panoramic-roof Q5, have the drain hoses inspected under TSB 2075969/2; the workshop lowers the headliner, replaces kinked hoses and cleans all four hoses with the specified tool when substantial dirt is present. Do not use compressed air, weed-trimmer line or a generic drain-tube kit from this record.</x:v>
+      </x:c>
+      <x:c r="F337" s="9" t="str">
+        <x:v>2011-2017 VIN/69P1 remedy; 2018-2023 TSB hose inspection/kink repair/specified cleaning</x:v>
+      </x:c>
+      <x:c r="G337" s="9" t="str">
+        <x:v>YEAR-SPLIT RECALL / TSB</x:v>
+      </x:c>
+      <x:c r="H337" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I337" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J337" s="9" t="str">
+        <x:v>2011-2017 Q5 69P1</x:v>
+      </x:c>
+      <x:c r="K337" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L337" s="9" t="str"/>
+      <x:c r="M337" s="9" t="str">
+        <x:v>Two populations have different actions.</x:v>
+      </x:c>
+      <x:c r="N337" s="41" t="str">
+        <x:v>No compressed air, trimmer line or generic tube kit.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="338" ht="66" hidden="0" customHeight="1">
+      <x:c r="A338" s="40" t="str"/>
+      <x:c r="B338" s="9" t="str"/>
+      <x:c r="C338" s="9" t="str"/>
+      <x:c r="D338" s="9" t="str"/>
+      <x:c r="E338" s="9" t="str"/>
+      <x:c r="F338" s="9" t="str"/>
+      <x:c r="G338" s="9" t="str"/>
+      <x:c r="H338" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I338" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J338" s="9" t="str">
+        <x:v>2018-2023 TSB 2075969/2</x:v>
+      </x:c>
+      <x:c r="K338" s="9" t="str">
+        <x:v>manufacturer body service</x:v>
+      </x:c>
+      <x:c r="L338" s="9" t="str"/>
+      <x:c r="M338" s="9" t="str"/>
+      <x:c r="N338" s="41" t="str"/>
+    </x:row>
+    <x:row r="339" ht="475.20001220703125" hidden="0" customHeight="1">
+      <x:c r="A339" s="40" t="n">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="B339" s="9" t="str">
+        <x:v>audi-q5-timing-chain-2009</x:v>
+      </x:c>
+      <x:c r="C339" s="9" t="str">
+        <x:v>2009-2017 | Audi | Q5 | Premium, Premium Plus, Prestige | 2.0T</x:v>
+      </x:c>
+      <x:c r="D339" s="9" t="str">
+        <x:v>EA888 Timing Chain Tensioner Failure</x:v>
+      </x:c>
+      <x:c r="E339" s="9" t="str">
+        <x:v>Replace timing chain, tensioner (latest revision 06K109467K), guides, and upper chain tensioner as a complete kit. The Q5 requires more labor than the A4 due to engine bay packaging. Preventive replacement at 80,000 miles is strongly recommended, especially on pre-2013 engines.</x:v>
+      </x:c>
+      <x:c r="F339" s="9" t="str">
+        <x:v>Engine-code/generation timing diagnosis; exact chain/tensioner/guides/current revision</x:v>
+      </x:c>
+      <x:c r="G339" s="9" t="str">
+        <x:v>ENGINE TIMING GATE</x:v>
+      </x:c>
+      <x:c r="H339" s="9" t="str">
+        <x:v>Audi Q5 timing-chain catalog</x:v>
+      </x:c>
+      <x:c r="I339" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/Q5/Timing-Chain-Kit/</x:v>
+      </x:c>
+      <x:c r="J339" s="9" t="str">
+        <x:v>2009-2017 Q5 2.0T exact engine/VIN/kit</x:v>
+      </x:c>
+      <x:c r="K339" s="9" t="str">
+        <x:v>engine-specific timing catalog</x:v>
+      </x:c>
+      <x:c r="L339" s="9" t="str"/>
+      <x:c r="M339" s="9" t="str">
+        <x:v>06K109467K is not universal.</x:v>
+      </x:c>
+      <x:c r="N339" s="41" t="str">
+        <x:v>Remove one 80k interval.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="340" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A340" s="40" t="str"/>
+      <x:c r="B340" s="9" t="str"/>
+      <x:c r="C340" s="9" t="str"/>
+      <x:c r="D340" s="9" t="str"/>
+      <x:c r="E340" s="9" t="str"/>
+      <x:c r="F340" s="9" t="str"/>
+      <x:c r="G340" s="9" t="str"/>
+      <x:c r="H340" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I340" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J340" s="9" t="str">
+        <x:v>timing diagnosis</x:v>
+      </x:c>
+      <x:c r="K340" s="9" t="str">
+        <x:v>specialist engine service</x:v>
+      </x:c>
+      <x:c r="L340" s="9" t="str"/>
+      <x:c r="M340" s="9" t="str"/>
+      <x:c r="N340" s="41" t="str"/>
+    </x:row>
+    <x:row r="341" ht="752.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A341" s="40" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="B341" s="9" t="str">
+        <x:v>audi-q5-timing-chain-tensioner-2011</x:v>
+      </x:c>
+      <x:c r="C341" s="9" t="str">
+        <x:v>2011-2012 | Audi | Q5</x:v>
+      </x:c>
+      <x:c r="D341" s="9" t="str">
+        <x:v>2011-2012 Q5 Timing Chain/Tensioner Diagnosis - Warranty Key U35</x:v>
+      </x:c>
+      <x:c r="E341" s="9" t="str">
+        <x:v>If timing noise, a timing fault, a no-start or suspected mechanical timing damage is present, stop driving when safe operation is uncertain and obtain engine-specific diagnosis. Ask an Audi dealer to check the VIN, Warranty Key U35 history and repair history, but do not assume current settlement coverage. Repair only after the chain, tensioner, timing relationship and any consequential engine damage are confirmed; do not buy a tensioner or kit from this record.</x:v>
+      </x:c>
+      <x:c r="F341" s="9" t="str">
+        <x:v>VIN/U35 history; confirm chain/tensioner/timing and damage before repair</x:v>
+      </x:c>
+      <x:c r="G341" s="9" t="str">
+        <x:v>DIAGNOSIS / HISTORICAL COVERAGE</x:v>
+      </x:c>
+      <x:c r="H341" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I341" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J341" s="9" t="str">
+        <x:v>2011-2012 Q5 U35/history</x:v>
+      </x:c>
+      <x:c r="K341" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L341" s="9" t="str"/>
+      <x:c r="M341" s="9" t="str">
+        <x:v>Coverage and failed part cannot be assumed.</x:v>
+      </x:c>
+      <x:c r="N341" s="41" t="str">
+        <x:v>No timing kit link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A342" s="40" t="str"/>
+      <x:c r="B342" s="9" t="str"/>
+      <x:c r="C342" s="9" t="str"/>
+      <x:c r="D342" s="9" t="str"/>
+      <x:c r="E342" s="9" t="str"/>
+      <x:c r="F342" s="9" t="str"/>
+      <x:c r="G342" s="9" t="str"/>
+      <x:c r="H342" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I342" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J342" s="9" t="str">
+        <x:v>mechanical timing diagnosis</x:v>
+      </x:c>
+      <x:c r="K342" s="9" t="str">
+        <x:v>specialist engine service</x:v>
+      </x:c>
+      <x:c r="L342" s="9" t="str"/>
+      <x:c r="M342" s="9" t="str"/>
+      <x:c r="N342" s="41" t="str"/>
+    </x:row>
+    <x:row r="343" ht="1240.800048828125" hidden="0" customHeight="1">
+      <x:c r="A343" s="40" t="n">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="B343" s="9" t="str">
+        <x:v>audi-q5-transmission-mechatronic-2009</x:v>
+      </x:c>
+      <x:c r="C343" s="9" t="str">
+        <x:v>2011-2012 | Audi | Q5</x:v>
+      </x:c>
+      <x:c r="D343" s="9" t="str">
+        <x:v>2011-2012 Q5 2.0T Hesitation or Harsh-Shift Service - TSB 2032812/9</x:v>
+      </x:c>
+      <x:c r="E343" s="9" t="str">
+        <x:v>Reproduce the exact hesitation or harsh-shift concern and confirm the 2.0L/0BK-8-speed application. Check the installed crankcase-pressure regulating valve first: if 06H103495AE is already fitted, do not replace those parts; otherwise TSB 2032812/9 directs replacement with 06H103495AE plus front crankshaft seal 06L103085B and bolt WHT001760 before the software update. Check both TCM and ECM software levels and apply only matching SVM updates. For model year 2011, clear adaptations and perform the GFF test-drive adaptation; for 2012, perform the standstill adaptation. Continue diagnosis if the condition or any separate DTC remains. Do not replace a mechatronic unit, valve body or transmission or prescribe a fluid interval from this record.</x:v>
+      </x:c>
+      <x:c r="F343" s="9" t="str">
+        <x:v>Confirm 2011-2012 2.0L/0BK; PCV/seal/bolt branch then matching ECM/TCM SVM and year adaptation</x:v>
+      </x:c>
+      <x:c r="G343" s="9" t="str">
+        <x:v>SOURCE-ID MISMATCH / TSB SOFTWARE-FIRST</x:v>
+      </x:c>
+      <x:c r="H343" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I343" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J343" s="9" t="str">
+        <x:v>TSB 2032812/9</x:v>
+      </x:c>
+      <x:c r="K343" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L343" s="9" t="str"/>
+      <x:c r="M343" s="9" t="str">
+        <x:v>TSB does not direct mechatronic replacement.</x:v>
+      </x:c>
+      <x:c r="N343" s="41" t="str">
+        <x:v>No valve body/transmission/fluid link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344" ht="778.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A344" s="40" t="n">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="B344" s="9" t="str">
+        <x:v>audi-q5-water-pump-failure-2009</x:v>
+      </x:c>
+      <x:c r="C344" s="9" t="str">
+        <x:v>2013-2017 | Audi | Q5</x:v>
+      </x:c>
+      <x:c r="D344" s="9" t="str">
+        <x:v>2013-2017 Q5 After-Run Coolant Pump Campaign 19N8 - VIN Check Required</x:v>
+      </x:c>
+      <x:c r="E344" s="9" t="str">
+        <x:v>Check the VIN and current open-action status with an Audi dealer. When Service Action 19N8 is open, Audi directs installation of the revised electric after-run coolant pump and an ECM software update. An EPC warning can indicate a blocked pump on vehicles with the relevant software; contact a dealer without delay. Do not buy a main pump, thermostat module, impeller kit or generic replacement from this campaign card, and do not infer eligibility from model year alone.</x:v>
+      </x:c>
+      <x:c r="F344" s="9" t="str">
+        <x:v>VIN/open 19N8 check; electric after-run pump and ECM update</x:v>
+      </x:c>
+      <x:c r="G344" s="9" t="str">
+        <x:v>CAMPAIGN ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H344" s="9" t="str">
+        <x:v>Audi recall and campaign lookup</x:v>
+      </x:c>
+      <x:c r="I344" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J344" s="9" t="str">
+        <x:v>2013-2017 Q5 19N8</x:v>
+      </x:c>
+      <x:c r="K344" s="9" t="str">
+        <x:v>manufacturer campaign lookup</x:v>
+      </x:c>
+      <x:c r="L344" s="9" t="str"/>
+      <x:c r="M344" s="9" t="str">
+        <x:v>Not main pump/thermostat.</x:v>
+      </x:c>
+      <x:c r="N344" s="41" t="str">
+        <x:v>Identifier says 2009; no generic pump link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="345" ht="66" hidden="0" customHeight="1">
+      <x:c r="A345" s="40" t="str"/>
+      <x:c r="B345" s="9" t="str"/>
+      <x:c r="C345" s="9" t="str"/>
+      <x:c r="D345" s="9" t="str"/>
+      <x:c r="E345" s="9" t="str"/>
+      <x:c r="F345" s="9" t="str"/>
+      <x:c r="G345" s="9" t="str"/>
+      <x:c r="H345" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I345" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J345" s="9" t="str">
+        <x:v>campaign remedy</x:v>
+      </x:c>
+      <x:c r="K345" s="9" t="str">
+        <x:v>authorized service</x:v>
+      </x:c>
+      <x:c r="L345" s="9" t="str"/>
+      <x:c r="M345" s="9" t="str"/>
+      <x:c r="N345" s="41" t="str"/>
+    </x:row>
+    <x:row r="346" ht="633.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A346" s="40" t="n">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B346" s="9" t="str">
+        <x:v>audi-q7-air-suspension-2007</x:v>
+      </x:c>
+      <x:c r="C346" s="9" t="str">
+        <x:v>2007-2015 | Audi | Q7 | Premium, Premium Plus, Prestige | 3.0T, 3.6L, 4.2L, 3.0 TDI</x:v>
+      </x:c>
+      <x:c r="D346" s="9" t="str">
+        <x:v>Air Suspension System Failure (Compressor and Springs)</x:v>
+      </x:c>
+      <x:c r="E346" s="9" t="str">
+        <x:v>Replace all four air springs and the compressor as a complete system overhaul for best results. If budget is limited, replace the leaking spring(s) and compressor together. Always replace the compressor relay. Arnott aftermarket air springs are popular and cost 50-60% less than OEM. Some owners convert to coilover suspension ($2,000-$3,000) to eliminate the air system entirely.</x:v>
+      </x:c>
+      <x:c r="F346" s="9" t="str">
+        <x:v>Sag/leak/runtime/output diagnosis; exact spring/strut, valve, relay, compressor or controls by proof; calibration</x:v>
+      </x:c>
+      <x:c r="G346" s="9" t="str">
+        <x:v>SYSTEM DIAGNOSIS GATE</x:v>
+      </x:c>
+      <x:c r="H346" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I346" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J346" s="9" t="str">
+        <x:v>2007-2015 Q7 air suspension</x:v>
+      </x:c>
+      <x:c r="K346" s="9" t="str">
+        <x:v>specialist suspension service</x:v>
+      </x:c>
+      <x:c r="L346" s="9" t="str"/>
+      <x:c r="M346" s="9" t="str">
+        <x:v>Whole-system replacement is not universal.</x:v>
+      </x:c>
+      <x:c r="N346" s="41" t="str">
+        <x:v>Hold aftermarket/conversion links until full fitment/safety plan.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="347" ht="831.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A347" s="40" t="n">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="B347" s="9" t="str">
+        <x:v>audi-q7-air-suspension-failure-2007</x:v>
+      </x:c>
+      <x:c r="C347" s="9" t="str">
+        <x:v>2007-2015 | Audi | Q7</x:v>
+      </x:c>
+      <x:c r="D347" s="9" t="str">
+        <x:v>Air Suspension Strut Failure and Compressor Issues</x:v>
+      </x:c>
+      <x:c r="E347" s="9" t="str">
+        <x:v>Leaking strut: Replace air strut ($800-1,500 per corner). All four corners worn: Replace all four struts ($3,000-5,500). Failed compressor: Replace air suspension compressor ($1,200-2,000). Control module fault: Replace suspension control module ($800-1,500). Alternative: Convert to coil spring suspension ($1,500-2,500 all corners) - eliminates air suspension issues permanently. AudiWorld recommends Arnott or Strutmasters air struts (cheaper than OEM, good quality).</x:v>
+      </x:c>
+      <x:c r="F347" s="9" t="str">
+        <x:v>Per-corner leak, compressor output, relay/valve/module/wiring diagnosis; exact component or engineered conversion</x:v>
+      </x:c>
+      <x:c r="G347" s="9" t="str">
+        <x:v>SYSTEM DIAGNOSIS GATE</x:v>
+      </x:c>
+      <x:c r="H347" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I347" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J347" s="9" t="str">
+        <x:v>2007-2015 Q7 diagnosis/calibration</x:v>
+      </x:c>
+      <x:c r="K347" s="9" t="str">
+        <x:v>specialist suspension service</x:v>
+      </x:c>
+      <x:c r="L347" s="9" t="str"/>
+      <x:c r="M347" s="9" t="str">
+        <x:v>Source lists mutually exclusive repairs by price.</x:v>
+      </x:c>
+      <x:c r="N347" s="41" t="str">
+        <x:v>No part/conversion before failure and VIN confirmation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348" ht="633.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A348" s="40" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="B348" s="9" t="str">
+        <x:v>audi-q7-carbon-buildup-3.0t-2011</x:v>
+      </x:c>
+      <x:c r="C348" s="9" t="str">
+        <x:v>2011-2016 | Audi | Q7 | 3.0 TFSI</x:v>
+      </x:c>
+      <x:c r="D348" s="9" t="str">
+        <x:v>2011-2016 Q7 3.0 TFSI Secondary-Air Carbon Restriction - P0491/P0492</x:v>
+      </x:c>
+      <x:c r="E348" s="9" t="str">
+        <x:v>Have an Audi-trained technician confirm that P0491 and P0492 are present together, test the secondary-air pump and hose routing, and measure secondary-air flow using the bulletin procedure. If the measured flow and checks match the bulletin, the cylinder-head secondary-air ports are cleaned with Audi tools and training. Do not buy a PCV assembly, catch can or intake-cleaning product from this card.</x:v>
+      </x:c>
+      <x:c r="F348" s="9" t="str">
+        <x:v>Confirm P0491/P0492 together; pump/hose and measured SAI flow; trained head-port cleaning only when bulletin matches</x:v>
+      </x:c>
+      <x:c r="G348" s="9" t="str">
+        <x:v>SAI MEASUREMENT SERVICE</x:v>
+      </x:c>
+      <x:c r="H348" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I348" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J348" s="9" t="str">
+        <x:v>2011-2016 Q7 3.0 TFSI SAI test/clean</x:v>
+      </x:c>
+      <x:c r="K348" s="9" t="str">
+        <x:v>manufacturer emissions service</x:v>
+      </x:c>
+      <x:c r="L348" s="9" t="str"/>
+      <x:c r="M348" s="9" t="str">
+        <x:v>Intake products do not address SAI ports.</x:v>
+      </x:c>
+      <x:c r="N348" s="41" t="str">
+        <x:v>No PCV/catch-can/intake-cleaner link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="349" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A349" s="42" t="str"/>
+      <x:c r="B349" s="43" t="str"/>
+      <x:c r="C349" s="43" t="str"/>
+      <x:c r="D349" s="43" t="str"/>
+      <x:c r="E349" s="43" t="str"/>
+      <x:c r="F349" s="43" t="str"/>
+      <x:c r="G349" s="43" t="str"/>
+      <x:c r="H349" s="43" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I349" s="43" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J349" s="43" t="str">
+        <x:v>trained VAG SAI diagnosis</x:v>
+      </x:c>
+      <x:c r="K349" s="43" t="str">
+        <x:v>specialist emissions service</x:v>
+      </x:c>
+      <x:c r="L349" s="43" t="str"/>
+      <x:c r="M349" s="43" t="str"/>
+      <x:c r="N349" s="44" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9933,21 +12705,21 @@
         <x:v>Queue status</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="2" ht="712.7999877929688" hidden="0" customHeight="1">
       <x:c r="A2" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="9" t="str">
-        <x:v>audi-etron-gt-software-2022</x:v>
+        <x:v>audi-q7-supercharger-failure-2011</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
-        <x:v>2022-2022 | Audi | e-tron GT</x:v>
+        <x:v>2011-2015 | Audi | Q7 | Premium, Premium Plus, Prestige, S line, SQ7 | 3.0T</x:v>
       </x:c>
       <x:c r="D2" s="9" t="str">
-        <x:v>2022 e-tron GT Audi connect Inoperative after 91DZ - TSB 2068824/2</x:v>
+        <x:v>Supercharger Bearing Failure and Boost Leaks (3.0T)</x:v>
       </x:c>
       <x:c r="E2" s="9" t="str">
-        <x:v>Confirm that the failure began after 91DZ and matches the Audi connect/SOS-LED condition. An Audi technician should use ODIS Guided Fault Finding and run SVM Check Module Configuration for diagnostic address 0019, J533. Manual coding is no longer required. Escalate a continuing Audi connect failure through Audi support after the guided coding procedure rather than buying hardware or a retail software service.</x:v>
+        <x:v>Worn bearings: Supercharger rebuild with new bearings ($1,500-2,500) or replacement supercharger ($3,000-5,000). Bypass valve: Replace supercharger bypass valve ($300-600). Boost leaks: Inspect all boost hoses/clamps, replace cracked hoses ($150-400). Use OEM Audi or quality aftermarket (INA) supercharger bearings. AudiWorld recommends catch can installation ($300-500) to reduce oil vapor damage to supercharger.</x:v>
       </x:c>
       <x:c r="F2" s="9" t="n">
         <x:v>0</x:v>
@@ -9956,21 +12728,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="858" hidden="0" customHeight="1">
+    <x:row r="3" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A3" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
-        <x:v>audi-etron-hv-coolant-2019</x:v>
+        <x:v>audi-q7-tdi-emissions-scandal-2009</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
-        <x:v>2019-2022 | Audi | e-tron | e-tron quattro (2019, 2021-2022); e-tron Sportback quattro (2020-2022); e-tron S (2022) | Battery-electric; confirm coolant valve N632 part number by scan tool</x:v>
+        <x:v>2009-2015 | Audi | Q7 | 3.0 TDI</x:v>
       </x:c>
       <x:c r="D3" s="9" t="str">
-        <x:v>2019-2022 e-tron Coolant Valve N632 Leak in Cold Conditions - Diagnosis Required</x:v>
+        <x:v>2009-2015 Q7 3.0 TDI Emissions Settlement and Modification History</x:v>
       </x:c>
       <x:c r="E3" s="9" t="str">
-        <x:v>Do not open or add fluid to a high-voltage cooling circuit unless you are trained and have the Audi procedure. Have an Audi-qualified technician confirm that coolant valve N632 is the leak source and identify the installed valve with the scan tool. If index K or index Q is fitted and the TSB criteria apply, replace the valve if necessary under Audi TSB 2067941/3. A coolant warning, overheating warning or active high-voltage fault requires prompt professional diagnosis; do not order the former coolant product from this card.</x:v>
+        <x:v>Check the VIN and service history with an authorized Audi dealer and use current EPA or Audi settlement information to determine whether an emissions modification was completed and what extended emissions warranty, if any, applies to that vehicle. Diagnose any present warning or drivability concern separately. Do not buy a scan tool or generic repair manual as a settlement remedy.</x:v>
       </x:c>
       <x:c r="F3" s="9" t="n">
         <x:v>0</x:v>
@@ -9979,21 +12751,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="4" ht="594" hidden="0" customHeight="1">
       <x:c r="A4" s="40" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>audi-etron-onboard-charger-2019</x:v>
+        <x:v>audi-q7-tdi-oil-cooler-leak-2013</x:v>
       </x:c>
       <x:c r="C4" s="9" t="str">
-        <x:v>2021-2021 | Audi | e-tron | e-tron quattro and e-tron Sportback; confirm J1050 software level and matching DTC | Battery-electric</x:v>
+        <x:v>2013-2013 | Audi | Q7 | 3.0 TDI</x:v>
       </x:c>
       <x:c r="D4" s="9" t="str">
-        <x:v>2021 e-tron Charging Interruptions with Onboard-Charger Software 0070 - Diagnosis Required</x:v>
+        <x:v>2013 Q7 TDI Brake-Booster Vacuum-Line Recall 47L8 (14V516)</x:v>
       </x:c>
       <x:c r="E4" s="9" t="str">
-        <x:v>Record whether the failure is AC, DC or station-specific and have J1050 scanned before parts. If the vehicle has the matching condition and software level 0070, Audi directs an SVM update to software 0079 or higher. After the update, reproduce the concern and follow the guided test plan for any new active DTC. Do not infer hardware failure merely because one charging mode works, and do not order the former charger, 12-volt battery, relay, meter or portable EVSE from this card.</x:v>
+        <x:v>Check the VIN for open recall 47L8 with Audi. The dealer remedy replaces the specified vacuum line and inspects the vacuum line and brake booster for oil contamination. Additional vacuum-line or brake-booster components are replaced when contamination is found. The recall repair is dealer work and is not a reason to buy an oil cooler, scan tool or manual.</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
         <x:v>0</x:v>
@@ -10002,21 +12774,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="198" hidden="0" customHeight="1">
+    <x:row r="5" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A5" s="40" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>audi-etron-ota-software-2019</x:v>
+        <x:v>audi-q7-timing-chain-tensioner-2007</x:v>
       </x:c>
       <x:c r="C5" s="9" t="str">
-        <x:v>2019-2024 | Audi | e-tron</x:v>
+        <x:v>2011-2015 | Audi | Q7 | 3.0 TFSI</x:v>
       </x:c>
       <x:c r="D5" s="9" t="str">
-        <x:v>OTA Software Update and Infotainment Issues</x:v>
+        <x:v>2011-2015 Q7 3.0 TFSI Brief Cold-Start Timing-Chain Rattle - TSB 2039995/2</x:v>
       </x:c>
       <x:c r="E5" s="9" t="str">
-        <x:v>Hard reset infotainment system. Visit dealer for manual software update. Ensure stable WiFi connection for OTA updates.</x:v>
+        <x:v>Confirm that the concern is the bulletin-defined one-to-three-second first-start rattle and have an Audi technician follow TSB 2039995/2 and current repair information. A longer, persistent or different noise, warning light or drivability concern requires separate diagnosis. Do not order a timing kit from this card.</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
         <x:v>0</x:v>
@@ -10025,21 +12797,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="396" hidden="0" customHeight="1">
+    <x:row r="6" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A6" s="40" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>audi-q2-coolant-water-pump-leak-tfsi-engines</x:v>
+        <x:v>audi-q7-transfer-case-2007</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
-        <x:v>2016-2021 | Audi | Q2 | TFSI petrol | 1.4 TFSI, 2.0 TFSI, 1.0 TFSI, TFSI petrol</x:v>
+        <x:v>2007-2019 | Audi | Q7 | Premium, Premium Plus, Prestige | 3.0T, 3.6L, 4.2L, 3.0 TDI</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
-        <x:v>Coolant / water pump leak on TFSI engines (cracked plastic pump housing)</x:v>
+        <x:v>Transfer Case Fluid Leak and Failure</x:v>
       </x:c>
       <x:c r="E6" s="9" t="str">
-        <x:v>Replace the water pump and thermostat housing (typically an updated revised unit) and refill/bleed with the correct G13 coolant; many shops do this together with the timing belt service. Inspect related coolant hoses/thermostat at the same time.</x:v>
+        <x:v>Replace leaking seals and refill with correct fluid (75W-90 GL-5 or Audi specification). If grinding is present, the transfer case may need rebuild or replacement. Regular fluid changes every 60,000 miles can prevent internal damage. Check for leaks at every oil change.</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
         <x:v>0</x:v>
@@ -10048,21 +12820,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="528" hidden="0" customHeight="1">
+    <x:row r="7" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A7" s="40" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>audi-q2-diesel-particulate-filter-clogging-tdi-engines-used-short-tr</x:v>
+        <x:v>audi-q7-water-pump-failure-2007</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
-        <x:v>2016-2020 | Audi | Q2 | TDI diesel | 1.6 TDI, 2.0 TDI</x:v>
+        <x:v>2007-2015 | Audi | Q7</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
-        <x:v>Diesel particulate filter (DPF) clogging on TDI engines used for short trips</x:v>
+        <x:v>Water Pump and Thermostat Failure (Overheating)</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
-        <x:v>Drive at a steady speed (&gt;60 km/h / ~40 mph) under moderate load for 15–30 minutes to allow regeneration to complete; if blocked, the dealer performs a forced/static regeneration with diagnostic equipment. Severely blocked filters need professional DPF cleaning or replacement. Long-term: avoid exclusively short trips.</x:v>
+        <x:v>IMMEDIATE if overheating: Pull over, turn off engine, DO NOT continue - engine damage occurs in minutes. Preventive: Replace water pump/thermostat assembly at 60k-80k miles ($800-1,500) to avoid catastrophic failure. Failed pump: Replace water pump/thermostat ($800-1,500). If overheated: Cylinder head inspection, possible head gasket replacement ($2,500-5,000). Use OEM Audi or premium Geba/Meyle parts.</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
         <x:v>0</x:v>
@@ -10071,21 +12843,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="422.3999938964844" hidden="0" customHeight="1">
+    <x:row r="8" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A8" s="40" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>audi-q2-electro-mechanical-parking-brake-can-release-its-own</x:v>
+        <x:v>audi-q8-48v-system-2019</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
-        <x:v>2017-2018 | Audi | Q2</x:v>
+        <x:v>2019-2024 | Audi | Q8</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>2017-2018 Audi Q2 Parking-Brake Software Recall 45H4</x:v>
+        <x:v>2019-2024 Q8 Starter-Alternator Service Action 27BQ - Check VIN</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history with Audi. The recall remedy is an authorised-dealer software update to the brake control unit. Until eligibility and completion are confirmed, leave the transmission in gear or Park and avoid relying on the parking brake alone on a slope.</x:v>
+        <x:v>Check the VIN and current campaign status with an Audi dealer. If 27BQ is open, the dealer follows the campaign procedure and replaces the starter-alternator at no cost when directed. If the action is not open, use Audi guided diagnostics: current bulletins distinguish a replacement result from sensor and CAN faults that replacement will not fix. Do not buy a 12V battery, charger or starter from this card.</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
         <x:v>0</x:v>
@@ -10094,21 +12866,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="475.20001220703125" hidden="0" customHeight="1">
+    <x:row r="9" ht="422.3999938964844" hidden="0" customHeight="1">
       <x:c r="A9" s="40" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>audi-q2-fuse-carrier-power-connector-recall-engine-instrument-cluste</x:v>
+        <x:v>audi-q8-8-speed-tiptronic-harsh-shifting-jolt-delayed-engagement</x:v>
       </x:c>
       <x:c r="C9" s="9" t="str">
-        <x:v>2021-2023 | Audi | Q2 | 35 TFSI, 35 TDI</x:v>
+        <x:v>2019-2023 | Audi | Q8 | Q8 55 TFSI, SQ8, RS Q8, 50 TDI</x:v>
       </x:c>
       <x:c r="D9" s="9" t="str">
-        <x:v>2021-2023 Audi Q2 Interior Fuse-Carrier Recall GAI-3692</x:v>
+        <x:v>8-Speed Tiptronic Harsh Shifting, Jolt and Delayed Engagement</x:v>
       </x:c>
       <x:c r="E9" s="9" t="str">
-        <x:v>Check the VIN and open-campaign status with an authorised Audi dealer in the vehicle’s market. The campaign remedy is dealer inspection and correction of the fuse-carrier power connection. Do not replace a fuse box or wiring harness solely from a warning lamp or this model-year summary.</x:v>
+        <x:v>Perform a full ZF 8HP transmission fluid and filter (pan) service with the correct Audi-spec fluid, then run the gearbox adaptation/relearn procedure. Update the transmission control module software if a TSB applies. Inspect transmission and engine mounts and replace if collapsed.</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
         <x:v>0</x:v>
@@ -10117,21 +12889,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="10" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A10" s="40" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>audi-q2-mmi-infotainment-freezing-rebooting-intermittent-electrical</x:v>
+        <x:v>audi-q8-air-suspension-2019</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
-        <x:v>2016-2022 | Audi | Q2</x:v>
+        <x:v>2019-2025 | Audi | Q8</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>MMI infotainment freezing/rebooting and intermittent electrical glitches</x:v>
+        <x:v>2019-2025 Q8 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
-        <x:v>Apply the latest MMI software update at an Audi dealer; clear/re-pair the phone if corrupt phone data triggers it. A manual MMI reboot (press-and-hold the power/volume knob ~10 seconds) clears temporary glitches. Persistent faults may require a head-unit or module replacement.</x:v>
+        <x:v>Inspect the wiring and connector contacts between J775 and J1135 before replacing a component. For a first passive or sporadic occurrence, clear the fault and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after wiring inspection, Audi directs replacement of J1135 under current repair and parts information. Do not buy struts, springs, a compressor or a conversion kit solely from this warning.</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
         <x:v>0</x:v>
@@ -10140,21 +12912,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="11" ht="607.2000122070312" hidden="0" customHeight="1">
       <x:c r="A11" s="40" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>audi-q2-premature-timing-belt-failure-1-0-1-4-tfsi-petrol-engines</x:v>
+        <x:v>audi-q8-carbon-buildup-2019</x:v>
       </x:c>
       <x:c r="C11" s="9" t="str">
-        <x:v>2016-2021 | Audi | Q2 | 1.0 TFSI, 1.4 TFSI, 30 TFSI, 35 TFSI | 1.0 TFSI (3-cyl), 1.4 TFSI, TFSI petrol</x:v>
+        <x:v>2019-2023 | Audi | Q8</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>Premature timing belt failure on 1.0 / 1.4 TFSI petrol engines</x:v>
+        <x:v>Severe Carbon Buildup on Intake Valves (3.0T)</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
-        <x:v>Replace the timing belt, tensioner, idlers and water pump as a kit well before the stated interval (many owners now do it at 4 years / 40k-50k miles as a precaution); if the belt has already failed, the usual outcome is a replacement engine (often a reconditioned/used unit) plus a new belt kit. Pursue Audi goodwill via the dealer/ombudsman if full service history exists.</x:v>
+        <x:v>WALNUT BLASTING: Remove intake manifold and blast walnut shells through intake ports ($900-$1,500). Requires specialized equipment. Repeat every 60,000 miles as PREVENTIVE maintenance. PREVENTION: Install catch can ($400-$600) to filter PCV vapors—extends interval to 100k+ miles. Add Liqui Moly Intake Valve Cleaner to every oil change. Change oil every 5,000 miles.</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
         <x:v>0</x:v>
@@ -10163,21 +12935,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="369.6000061035156" hidden="0" customHeight="1">
+    <x:row r="12" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A12" s="40" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="9" t="str">
-        <x:v>audi-q2-rear-hub-carrier-fracture-recall</x:v>
+        <x:v>audi-q8-e-tron-brake-pedal-to-booster-pushrod-screw-joint-detachment</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
-        <x:v>2017-2017 | Audi | Q2</x:v>
+        <x:v>2023-2024 | Audi | Q8 e-tron</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>2017 Audi Q2 Rear Wheel-Bearing Housing Recall R/2017/311</x:v>
+        <x:v>2023-2024 Audi Q8 e-tron Brake-Pedal Recall 46P7 / NHTSA 26V240</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history with Audi. The recall remedy replaces both rear wheel-bearing housings at an authorised dealer. If rear-wheel noise, looseness or unusual tyre wear is present, avoid continued driving until the vehicle is inspected.</x:v>
+        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. Dealers inspect and tighten the brake-booster pushrod screw joint as necessary at no charge. If the brake pedal makes an unusual noise, fails to return or feels abnormal, do not continue driving; contact Audi for recovery and follow the owner’s manual emergency-braking instructions.</x:v>
       </x:c>
       <x:c r="F12" s="9" t="n">
         <x:v>0</x:v>
@@ -10186,21 +12958,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="13" ht="594" hidden="0" customHeight="1">
       <x:c r="A13" s="40" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="9" t="str">
-        <x:v>audi-q2-s-tronic-dual-clutch-transmission-jerking-hesitation-delayed</x:v>
+        <x:v>audi-q8-e-tron-dc-fast-charging-handshake-timeout-failure-to-initiate-sessi</x:v>
       </x:c>
       <x:c r="C13" s="9" t="str">
-        <x:v>2016-2022 | Audi | Q2 | S tronic / DSG (7-speed) | TFSI S tronic, TDI S tronic</x:v>
+        <x:v>2023-2024 | Audi | Q8 e-tron</x:v>
       </x:c>
       <x:c r="D13" s="9" t="str">
-        <x:v>S tronic (DSG) dual-clutch transmission jerking, hesitation and delayed shifts</x:v>
+        <x:v>2023-2024 Audi Q8 e-tron Plug &amp; Charge TSB 2071345/1</x:v>
       </x:c>
       <x:c r="E13" s="9" t="str">
-        <x:v>Start with a transmission software/adaption update and a DSG mechatronic fluid-and-filter service at the correct interval; if symptoms persist, diagnose and replace the clutch pack or mechatronic unit as required. Address promptly to avoid limp-mode and further wear.</x:v>
+        <x:v>Confirm that the failure repeats at the same station, AC charging works and U15AF00 symptom 2097297 is present. Temporarily disable Plug &amp; Charge in the MMI or use another compatible charging station. Do not replace vehicle charging hardware solely from this symptom; follow current Audi guidance if the failure also occurs with Plug &amp; Charge disabled or at multiple stations.</x:v>
       </x:c>
       <x:c r="F13" s="9" t="n">
         <x:v>0</x:v>
@@ -10209,21 +12981,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="14" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A14" s="40" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="9" t="str">
-        <x:v>audi-q3-brake-pedal-recall-2019</x:v>
+        <x:v>audi-q8-e-tron-front-passenger-occupant-detection-system-deactivates-airbag</x:v>
       </x:c>
       <x:c r="C14" s="9" t="str">
-        <x:v>2020-2020 | Audi | Q3</x:v>
+        <x:v>2024-2024 | Audi | Q8 e-tron</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
-        <x:v>2020 Audi Q3 Brake-Pedal Recall 46i7 / NHTSA 20V786</x:v>
+        <x:v>2024 Audi Q8 e-tron Passenger-Airbag Recall 69GU / NHTSA 24V251</x:v>
       </x:c>
       <x:c r="E14" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. The free recall remedy inspects the weld between the pedal and pedal plate and replaces the complete brake pedal when required. Do not buy pads or rotors for this campaign; if the pedal feels loose, bent or abnormal, stop driving and arrange dealer inspection.</x:v>
+        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. The free remedy replaces the passenger-seat occupant-detection control module. If the passenger-airbag warning or AIRBAG OFF indicator behaves unexpectedly, avoid using that seat until Audi inspects it. Do not buy an ODS module from this summary.</x:v>
       </x:c>
       <x:c r="F14" s="9" t="n">
         <x:v>0</x:v>
@@ -10232,21 +13004,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="871.2000122070312" hidden="0" customHeight="1">
+    <x:row r="15" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A15" s="40" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="9" t="str">
-        <x:v>audi-q3-carbon-buildup-2015</x:v>
+        <x:v>audi-q8-e-tron-over-torqued-brake-pressure-line-failure-fluid-leak</x:v>
       </x:c>
       <x:c r="C15" s="9" t="str">
-        <x:v>2015-2023 | Audi | Q3 | 2.0 TFSI</x:v>
+        <x:v>2024-2024 | Audi | Q8 e-tron</x:v>
       </x:c>
       <x:c r="D15" s="9" t="str">
-        <x:v>Carbon Buildup on Intake Valves (Direct Injection)</x:v>
+        <x:v>2024 Audi Q8 e-tron Brake-Line Recall 47DE / NHTSA 24V428</x:v>
       </x:c>
       <x:c r="E15" s="9" t="str">
-        <x:v>WALNUT BLASTING: Remove intake manifold and blast crushed walnut shells through intake ports ($700-$1,200). Requires specialized equipment—not DIY-friendly. Dealers charge $1,200-$1,500; independent Audi shops charge less. Repeat every 60,000-80,000 miles. PREVENTION: Install catch can ($300-$500) to filter PCV oil vapors before they reach valves—extends cleaning interval to 100k+ miles. Add Liqui Moly Intake Valve Cleaner to every oil change ($15). Perform "Italian tune-up" monthly (spirited highway driving to high RPM to burn carbon).</x:v>
+        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. Dealers inspect and replace the brake-pressure line when necessary at no charge. If the brake warning appears, pedal travel increases or fluid is visible, stop driving and arrange recovery.</x:v>
       </x:c>
       <x:c r="F15" s="9" t="n">
         <x:v>0</x:v>
@@ -10255,21 +13027,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="422.3999938964844" hidden="0" customHeight="1">
+    <x:row r="16" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A16" s="40" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="9" t="str">
-        <x:v>audi-q3-electrical-infotainment-2019</x:v>
+        <x:v>audi-q8-e-tron-panoramic-glass-roof-water-leak-into-cabin</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
-        <x:v>2022-2022 | Audi | Q3</x:v>
+        <x:v>2023-2024 | Audi | Q8 e-tron | Q8 e-tron (panoramic roof equipped), Q8 Sportback e-tron</x:v>
       </x:c>
       <x:c r="D16" s="9" t="str">
-        <x:v>2022 Audi Q3 Rearview-Camera Recall 91Ei / NHTSA 22V806</x:v>
+        <x:v>Panoramic Glass Roof Water Leak into Cabin (TSB MC-10182485-0001)</x:v>
       </x:c>
       <x:c r="E16" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. The recall remedy replaces the infotainment main unit at no charge. Until repaired, use mirrors and direct observation with extra care while reversing; do not order a refurbished head unit from this summary.</x:v>
+        <x:v>Have the dealer diagnose per the panoramic roof TSB. Repair depends on the root cause: clear or re-route clogged/pinched drain tubes, correct a pinched-shut rear drain, or replace/reseal the cracked plastic water channel. Dry out and inspect saturated carpet/underlay to prevent mold and electrical corrosion. Audi performs the repair reactively (only after water ingress is confirmed); some owners report the factory fix failing and needing a second visit.</x:v>
       </x:c>
       <x:c r="F16" s="9" t="n">
         <x:v>0</x:v>
@@ -10278,21 +13050,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="831.5999755859375" hidden="0" customHeight="1">
+    <x:row r="17" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A17" s="40" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="9" t="str">
-        <x:v>audi-q3-oil-consumption-2015</x:v>
+        <x:v>audi-q8-e-tron-premature-brake-pad-rotor-wear-brake-vibration-pulsation</x:v>
       </x:c>
       <x:c r="C17" s="9" t="str">
-        <x:v>2015-2018 | Audi | Q3 | EA888 Gen 2, EA888 Gen 3</x:v>
+        <x:v>2023-2024 | Audi | Q8 e-tron | Q8 e-tron, Q8 Sportback e-tron, SQ8 e-tron</x:v>
       </x:c>
       <x:c r="D17" s="9" t="str">
-        <x:v>Excessive Oil Consumption (2.0 TFSI Engine)</x:v>
+        <x:v>Premature Brake Pad/Rotor Wear and Brake Vibration/Pulsation</x:v>
       </x:c>
       <x:c r="E17" s="9" t="str">
-        <x:v>For SEVERE consumption (over 1 qt/1,000 mi): Piston ring replacement or short block replacement ($4,000-$7,000). Check Audi's extended warranty program for 2015-2018 Q3 models. For MODERATE consumption: Replace PCV valve ($150), clean carbon with walnut blasting ($800), switch to thicker oil (5W-40). PREVENTION: Check oil level WEEKLY, change oil every 5,000 miles (NOT 10,000), avoid 2015-2017 models when buying used. 2019+ Gen 3 EA888 engines are far more reliable.</x:v>
+        <x:v>Have a dealer or independent measure rotor runout/thickness variation and machine or replace rotors with correct torque and bedding-in. Verify pad hardware and caliper slides. Using a stronger regenerative-braking setting reduces friction-brake duty and corrosion. If vibration returns shortly after a full brake job, escalate for a deeper inspection of hubs/wheel bearings and calibration.</x:v>
       </x:c>
       <x:c r="F17" s="9" t="n">
         <x:v>0</x:v>
@@ -10301,21 +13073,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="18" ht="303.6000061035156" hidden="0" customHeight="1">
       <x:c r="A18" s="40" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="9" t="str">
-        <x:v>audi-q3-panoramic-roof-2015</x:v>
+        <x:v>audi-q8-e-tron-rearview-camera-image-fails-is-delayed-when-shifting-to-reve</x:v>
       </x:c>
       <x:c r="C18" s="9" t="str">
-        <x:v>2015-2015 | Audi | Q3</x:v>
+        <x:v>2023-2024 | Audi | Q8 e-tron</x:v>
       </x:c>
       <x:c r="D18" s="9" t="str">
-        <x:v>2015 Audi Q3 Sunroof-Control Recall 60C1 / NHTSA 15V200</x:v>
+        <x:v>2023-2024 Audi Q8 e-tron Camera Recall 90TV / NHTSA 25V900</x:v>
       </x:c>
       <x:c r="E18" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. The recall remedy updates the sunroof control-module software at no charge. Keep hands and objects clear of the moving panel and do not use battery, relay or generic electrical parts as a substitute for the campaign.</x:v>
+        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. Dealers update the software at no charge. Until completed, use mirrors and direct observation with extra care while reversing.</x:v>
       </x:c>
       <x:c r="F18" s="9" t="n">
         <x:v>0</x:v>
@@ -10324,21 +13096,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="382.79998779296875" hidden="0" customHeight="1">
+    <x:row r="19" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A19" s="40" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="9" t="str">
-        <x:v>audi-q3-steering-lock-recall-2019</x:v>
+        <x:v>audi-q8-e-tron-severe-cold-weather-range-loss-reduced-dc-charge-speed</x:v>
       </x:c>
       <x:c r="C19" s="9" t="str">
-        <x:v>2019-2019 | Audi | Q3</x:v>
+        <x:v>2023-2024 | Audi | Q8 e-tron | Q8 e-tron, Q8 Sportback e-tron, SQ8 e-tron</x:v>
       </x:c>
       <x:c r="D19" s="9" t="str">
-        <x:v>2019 Audi Q3 Steering-Rack Recall 48P7 / NHTSA 21V027</x:v>
+        <x:v>Severe Cold-Weather Range Loss and Reduced DC Charge Speed (Cold Battery)</x:v>
       </x:c>
       <x:c r="E19" s="9" t="str">
-        <x:v>Check the VIN and campaign history with Audi or NHTSA. The recall remedy replaces the steering rack at no charge. If steering binds or locks, stop driving and arrange recovery; do not infer that another Q3 is affected from model year alone.</x:v>
+        <x:v>Use route-based battery preconditioning: enter the DC fast charger as a navigation destination so the car warms the pack en route, restoring charge speed. Precondition the cabin while still plugged in at home, use seat/steering heaters over cabin heat, and rely on Level 2 home charging (40-60A) to absorb seasonal losses overnight. No repair is needed unless range/charge limits persist in mild weather, which warrants a dealer battery-health check.</x:v>
       </x:c>
       <x:c r="F19" s="9" t="n">
         <x:v>0</x:v>
@@ -10347,21 +13119,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="20" ht="660" hidden="0" customHeight="1">
       <x:c r="A20" s="40" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="9" t="str">
-        <x:v>audi-q3-timing-chain-2015</x:v>
+        <x:v>audi-q8-ea839-3-0t-water-pump-internal-leak-coolant-loss</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>2015-2018 | Audi | Q3 | Premium, Premium Plus, Prestige | 2.0T</x:v>
+        <x:v>2019-2024 | Audi | Q8 | V6 TFSI</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>EA888 Timing Chain Tensioner Failure</x:v>
+        <x:v>2019-2024 Q8 V6 Coolant-Pump Leak Diagnosis - TSB 2070349/4</x:v>
       </x:c>
       <x:c r="E20" s="9" t="str">
-        <x:v>Replace the timing chain, tensioner, guides, and related hardware as a complete kit. Use the latest OEM revised tensioner part number. Preventive replacement is recommended at 80,000-100,000 miles. Cold-start rattle is the critical warning sign that should not be ignored.</x:v>
+        <x:v>Have the suspected area cleaned and dried, fill the cooling system correctly, inspect at idle and up to about 2,500 rpm, and pressure-test it per Audi repair information. If no leak returns, continue to observe without replacing parts. Replace only the component proven to leak and inspect the vacuum path and N649 when P0299 is present. Do not order a pump from this card without confirmation.</x:v>
       </x:c>
       <x:c r="F20" s="9" t="n">
         <x:v>0</x:v>
@@ -10370,21 +13142,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="1029.5999755859375" hidden="0" customHeight="1">
+    <x:row r="21" ht="382.79998779296875" hidden="0" customHeight="1">
       <x:c r="A21" s="40" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="9" t="str">
-        <x:v>audi-q3-timing-chain-tensioner-2015</x:v>
+        <x:v>audi-q8-etron-12v-battery-drain-2023</x:v>
       </x:c>
       <x:c r="C21" s="9" t="str">
-        <x:v>2015-2020 | Audi | Q3 | EA888</x:v>
+        <x:v>2023-2025 | Audi | Q8 e-tron</x:v>
       </x:c>
       <x:c r="D21" s="9" t="str">
-        <x:v>Timing Chain Tensioner Failure (2.0 TFSI Engine)</x:v>
+        <x:v>12V Auxiliary Battery Excessive Drain</x:v>
       </x:c>
       <x:c r="E21" s="9" t="str">
-        <x:v>PREVENTIVE REPLACEMENT: Replace timing chain, tensioners, and guides at 80,000-100,000 miles BEFORE rattling starts ($2,000-$3,000). If rattling has started, DO NOT delay—chain can jump at any moment. Repair requires removing front engine cover, water pump, thermostat. Labor is 8-12 hours. Use ONLY OEM Audi parts—aftermarket tensioners fail quickly. Change oil every 5,000 miles and check oil level weekly to prevent accelerated tensioner wear. If catastrophic failure occurs, engine replacement ($6,000-$10,000) is often more cost-effective than rebuild. 2021+ Q3 models have updated parts and are more reliable.</x:v>
+        <x:v>Update vehicle software to latest version via dealer. If drain persists, have dealer perform parasitic draw test to identify module staying awake. 12V battery replacement with AGM type may be needed if battery was deeply discharged.</x:v>
       </x:c>
       <x:c r="F21" s="9" t="n">
         <x:v>0</x:v>
@@ -10393,21 +13165,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="22" ht="501.6000061035156" hidden="0" customHeight="1">
       <x:c r="A22" s="40" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="9" t="str">
-        <x:v>audi-q3-water-pump-2015</x:v>
+        <x:v>audi-q8-etron-12v-battery-drain-2024</x:v>
       </x:c>
       <x:c r="C22" s="9" t="str">
-        <x:v>2015-2018 | Audi | Q3 | 2.0 TFSI</x:v>
+        <x:v>2024-2026 | Audi | Q8 e-tron | Premium, Premium Plus, Prestige, Sportback Premium, Sportback Premium Plus, Sportback Prestige | Electric</x:v>
       </x:c>
       <x:c r="D22" s="9" t="str">
-        <x:v>2015-2018 Audi Q3 Coolant-Module Leak TSB 2061604/5</x:v>
+        <x:v>12V Auxiliary Battery Parasitic Drain</x:v>
       </x:c>
       <x:c r="E22" s="9" t="str">
-        <x:v>Pressure-test the cooling system and document the leak. Replace only the component that is leaking—the coolant pump or thermostat housing—then align the two components flush, torque the connecting bolts as specified and verify the pump-belt tension is within Audi’s procedure. Confirm current parts and warranty coverage with Audi; do not order by model year alone.</x:v>
+        <x:v>Update the vehicle software to the latest version which includes revised module sleep timing. If the 12V battery has been deeply discharged multiple times, it may need replacement as lead-acid batteries are damaged by deep discharge cycles. Connect a 12V trickle charger if the vehicle will sit for more than a week.</x:v>
       </x:c>
       <x:c r="F22" s="9" t="n">
         <x:v>0</x:v>
@@ -10416,21 +13188,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="23" ht="462" hidden="0" customHeight="1">
       <x:c r="A23" s="40" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="9" t="str">
-        <x:v>audi-q3-water-pump-coolant-2015</x:v>
+        <x:v>audi-q8-etron-charge-port-actuator-2024</x:v>
       </x:c>
       <x:c r="C23" s="9" t="str">
-        <x:v>2020-2024 | Audi | Q3 | 2.0 TFSI</x:v>
+        <x:v>2024-2026 | Audi | Q8 e-tron | Premium, Premium Plus, Prestige, Sportback Premium, Sportback Premium Plus, Sportback Prestige | Electric</x:v>
       </x:c>
       <x:c r="D23" s="9" t="str">
-        <x:v>2020-2024 Audi Q3 Coolant-Pump Leak TSB 2071515/1</x:v>
+        <x:v>Charge Port Door Actuator and Locking Mechanism Failure</x:v>
       </x:c>
       <x:c r="E23" s="9" t="str">
-        <x:v>Document the suspected leak, clean and dry all coolant traces, fill the system to the correct level and reassess after driving a few miles. If no fresh leak returns, continue observing without replacing parts. If leakage recurs, replace only the component causing it under the exact VIN, engine and part criteria. Outside applicable warranty, Audi states the bulletin is informational.</x:v>
+        <x:v>Replace the charge port door actuator and/or latch mechanism. In an emergency, there is a manual cable release in the cargo area to free a stuck charging cable. The actuator replacement is a straightforward repair that can be done by an independent shop if comfortable with the charge port housing.</x:v>
       </x:c>
       <x:c r="F23" s="9" t="n">
         <x:v>0</x:v>
@@ -10439,21 +13211,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="396" hidden="0" customHeight="1">
+    <x:row r="24" ht="316.79998779296875" hidden="0" customHeight="1">
       <x:c r="A24" s="40" t="n">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="9" t="str">
-        <x:v>audi-q4-etron-brake-rollaway-2022</x:v>
+        <x:v>audi-q8-etron-charge-port-lid-2023</x:v>
       </x:c>
       <x:c r="C24" s="9" t="str">
-        <x:v>2022-2023 | Audi | Q4 e-tron</x:v>
+        <x:v>2023-2025 | Audi | Q8 e-tron</x:v>
       </x:c>
       <x:c r="D24" s="9" t="str">
-        <x:v>2022-2023 Audi Q4 e-tron Rollaway Recall 454R / NHTSA 25V120</x:v>
+        <x:v>Charge Port Door Actuator Failure</x:v>
       </x:c>
       <x:c r="E24" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. The free recall remedy updates the brake-control-unit software. Until completed, verify the selected gear and always engage the parking brake before leaving the vehicle.</x:v>
+        <x:v>Replace charge port door actuator assembly. Check for debris or ice in the mechanism. Software update may improve actuator control logic. Manual release is accessible from inside the cargo area.</x:v>
       </x:c>
       <x:c r="F24" s="9" t="n">
         <x:v>0</x:v>
@@ -10462,21 +13234,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="528" hidden="0" customHeight="1">
+    <x:row r="25" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A25" s="40" t="n">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="9" t="str">
-        <x:v>audi-q4-etron-charging-port-2022</x:v>
+        <x:v>audi-q8-etron-hvac-compressor-2024</x:v>
       </x:c>
       <x:c r="C25" s="9" t="str">
-        <x:v>2022-2024 | Audi | Q4 e-tron</x:v>
+        <x:v>2024-2024 | Audi | Q8 e-tron</x:v>
       </x:c>
       <x:c r="D25" s="9" t="str">
-        <x:v>2022-2024 Audi Q4 e-tron Charging-Cable Recall 93U6/93U8 / NHTSA 23V842</x:v>
+        <x:v>2024 Audi Q8 e-tron A/C Compressor-Area Noise TSB 2063467/6</x:v>
       </x:c>
       <x:c r="E25" s="9" t="str">
-        <x:v>Check the VIN and campaign instructions with Audi or NHTSA. The recall advises owners not to use the affected 220V/240V compact cable and to use the 110V cable or public charging until Audi supplies the replacement 220V/240V cable with an incorporated temperature sensor at no charge. Do not order a charging inlet from this card.</x:v>
+        <x:v>Reproduce the exact noise with the A/C compressor active and confirm that it stops when A/C is switched off. Inspect the bulletin’s refrigerant-line contact points and hood-release cable clip and perform only the branch that matches the confirmed contact. Diagnose non-reproducible noise or loss of heating/cooling separately; do not buy a battery, maintainer or portable EVSE from this card.</x:v>
       </x:c>
       <x:c r="F25" s="9" t="n">
         <x:v>0</x:v>
@@ -10485,21 +13257,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="1003.2000122070312" hidden="0" customHeight="1">
+    <x:row r="26" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A26" s="40" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="9" t="str">
-        <x:v>audi-q4-etron-cold-weather-range-2022</x:v>
+        <x:v>audi-q8-front-brake-rotor-corrosion-premature-pad-rotor-wear</x:v>
       </x:c>
       <x:c r="C26" s="9" t="str">
-        <x:v>2023-2024 | Audi | Q4 e-tron</x:v>
+        <x:v>2019-2024 | Audi | Q8</x:v>
       </x:c>
       <x:c r="D26" s="9" t="str">
-        <x:v>Severe Cold Weather Range Loss (Models Without Heat Pump)</x:v>
+        <x:v>Front Brake Rotor Corrosion and Premature Pad/Rotor Wear</x:v>
       </x:c>
       <x:c r="E26" s="9" t="str">
-        <x:v>Check your build sheet or window sticker to determine if your Q4 e-tron has a heat pump - vehicles built after February 2023 likely do NOT have one. For non-heat-pump models: use seat heaters and steering wheel heater instead of cabin air heater to preserve range. Pre-condition the cabin while plugged in before departing. Set cabin temperature to 68F or lower. Enable eco mode for climate. Use range-optimized route planning. For heat pump equipped models experiencing issues: dealer service may need specialized R-744 (CO2) refrigerant which many shops don't stock - call ahead. Aftermarket heat pump installation is NOT feasible.</x:v>
+        <x:v>For light surface rust, normal braking usually clears it; for noise, refinish or replace rotors and fit OEM-spec pads with proper bedding-in. Apply high-temp anti-seize/lubricant on contact points and ensure caliper slides move freely. Replace warped or deeply corroded rotors in axle sets.</x:v>
       </x:c>
       <x:c r="F26" s="9" t="n">
         <x:v>0</x:v>
@@ -10508,21 +13280,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="382.79998779296875" hidden="0" customHeight="1">
+    <x:row r="27" ht="422.3999938964844" hidden="0" customHeight="1">
       <x:c r="A27" s="40" t="n">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="9" t="str">
-        <x:v>audi-q4-etron-headlight-module-2022</x:v>
+        <x:v>audi-q8-front-shock-absorber-fork-cracking</x:v>
       </x:c>
       <x:c r="C27" s="9" t="str">
-        <x:v>2022-2024 | Audi | Q4 e-tron</x:v>
+        <x:v>2019-2019 | Audi | Q8</x:v>
       </x:c>
       <x:c r="D27" s="9" t="str">
-        <x:v>2022-2024 Audi Q4 e-tron Headlight Recall 941L / NHTSA 24V361</x:v>
+        <x:v>2019 Q8 Front Shock-Absorber Fork Recall 40O4 (19V114) - Check VIN</x:v>
       </x:c>
       <x:c r="E27" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. The free remedy updates the headlight-control module with a corrected data set. Do not substitute relays, bulbs, a multimeter or a headlight assembly for the campaign software update.</x:v>
+        <x:v>Check the VIN for open recall 40O4 with Audi or NHTSA and contact an authorized Audi dealer. The dealer replaces the affected front shock-absorber fork free of charge. Do not buy a fork from this card or assume a generic suspension noise proves the recall condition.</x:v>
       </x:c>
       <x:c r="F27" s="9" t="n">
         <x:v>0</x:v>
@@ -10531,21 +13303,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="28" ht="422.3999938964844" hidden="0" customHeight="1">
       <x:c r="A28" s="40" t="n">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="9" t="str">
-        <x:v>audi-q4-etron-hv-coolant-2022</x:v>
+        <x:v>audi-q8-fuel-pump-internal-failure-causing-engine-stall</x:v>
       </x:c>
       <x:c r="C28" s="9" t="str">
-        <x:v>2022-2024 | Audi | Q4 e-tron</x:v>
+        <x:v>2019-2021 | Audi | Q8 | V6</x:v>
       </x:c>
       <x:c r="D28" s="9" t="str">
-        <x:v>Battery Cooling System Efficiency Issues</x:v>
+        <x:v>2019-2021 Q8 V6 Fuel-Delivery-Module Recall 20DR (22V516)</x:v>
       </x:c>
       <x:c r="E28" s="9" t="str">
-        <x:v>Bleed HV coolant circuit of air. Check coolant pump operation. Dealer service required for HV system work.</x:v>
+        <x:v>Check the VIN for open recall 20DR and contact an authorized Audi dealer. The recall remedy replaces the fuel-delivery module with the improved version. Do not purchase the old or improved module from this card or attempt an in-tank repair based only on the model year.</x:v>
       </x:c>
       <x:c r="F28" s="9" t="n">
         <x:v>0</x:v>
@@ -10554,21 +13326,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="198" hidden="0" customHeight="1">
+    <x:row r="29" ht="356.3999938964844" hidden="0" customHeight="1">
       <x:c r="A29" s="40" t="n">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="9" t="str">
-        <x:v>audi-q4-etron-ota-software-2022</x:v>
+        <x:v>audi-q8-mmi-electrical-2019</x:v>
       </x:c>
       <x:c r="C29" s="9" t="str">
-        <x:v>2022-2024 | Audi | Q4 e-tron</x:v>
+        <x:v>2019-2023 | Audi | Q8</x:v>
       </x:c>
       <x:c r="D29" s="9" t="str">
-        <x:v>OTA Updates and Software Glitches</x:v>
+        <x:v>MMI Infotainment and Electrical Issues</x:v>
       </x:c>
       <x:c r="E29" s="9" t="str">
-        <x:v>Perform hard reset. Check dealer for latest software version. Some issues require dealer-applied updates only.</x:v>
+        <x:v>MMI hard reset (hold power + volume up 10 seconds). If persistent, dealer software update ($150-$300). For severe cases: MMI replacement ($2,000-$3,500). Most covered under 4-year/50k warranty.</x:v>
       </x:c>
       <x:c r="F29" s="9" t="n">
         <x:v>0</x:v>
@@ -10577,21 +13349,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="501.6000061035156" hidden="0" customHeight="1">
+    <x:row r="30" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A30" s="40" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="9" t="str">
-        <x:v>audi-q4-etron-software-glitches-2022</x:v>
+        <x:v>audi-q8-mmi-infotainment-2019</x:v>
       </x:c>
       <x:c r="C30" s="9" t="str">
-        <x:v>2024-2025 | Audi | Q4 e-tron</x:v>
+        <x:v>2019-2026 | Audi | Q8</x:v>
       </x:c>
       <x:c r="D30" s="9" t="str">
-        <x:v>2024-2025 Audi Q4 e-tron On-Board-Charger Recall 93FR / NHTSA 25V125</x:v>
+        <x:v>2019-2026 Q8 Rearview-Camera Software Recall 90TV (25V900)</x:v>
       </x:c>
       <x:c r="E30" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. The free remedy replaces the on-board charger. If the vehicle warns of an electrical-system fault or loses drive power, move out of traffic safely and arrange Audi recovery/inspection; do not buy a 12-volt battery or generic electrical parts from this summary.</x:v>
+        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers install more robust driver-assistance software free of charge. Until repaired, use extra caution when reversing. A hard reset, scan tool, relay, multimeter or temporary image recovery is not completion of the recall.</x:v>
       </x:c>
       <x:c r="F30" s="9" t="n">
         <x:v>0</x:v>
@@ -10600,21 +13372,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="805.2000122070312" hidden="0" customHeight="1">
+    <x:row r="31" ht="382.79998779296875" hidden="0" customHeight="1">
       <x:c r="A31" s="40" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="9" t="str">
-        <x:v>audi-q5-carbon-buildup-2009</x:v>
+        <x:v>audi-q8-oil-separator-pcv-valve-failure-elevated-oil-consumption</x:v>
       </x:c>
       <x:c r="C31" s="9" t="str">
-        <x:v>2009-2025 | Audi | Q5</x:v>
+        <x:v>2019-2023 | Audi | Q8 | 3.0L V6 TFSI (EA839)</x:v>
       </x:c>
       <x:c r="D31" s="9" t="str">
-        <x:v>2009-2025 Q5 Gasoline-Quality Deposit Diagnosis - TSB 2014753/13</x:v>
+        <x:v>Oil Separator / PCV Valve Failure and Elevated Oil Consumption (3.0T)</x:v>
       </x:c>
       <x:c r="E31" s="9" t="str">
-        <x:v>Confirm the exact gasoline-powered vehicle, fuel quality, symptoms and stored DTCs before cleaning or replacing components. If contaminated gasoline is suspected, change fuel source; if detergent quality is suspect, Audi recommends Top Tier detergent gasoline. Continue guided diagnosis if the condition persists and identify the actual deposit location before selecting any cleaning procedure. Do not prescribe routine walnut blasting, a catch can, chemical cleaner or high-RPM driving from this record.</x:v>
+        <x:v>Replace the cracked oil separator / PCV valve assembly with the updated part, inspect the intake and spark plugs for oil fouling, and reseal the intake manifold. Monitor oil level between services; perform a consumption test if usage exceeds Audi's threshold.</x:v>
       </x:c>
       <x:c r="F31" s="9" t="n">
         <x:v>0</x:v>
@@ -10623,44 +13395,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="712.7999877929688" hidden="0" customHeight="1">
+    <x:row r="32" ht="607.2000122070312" hidden="0" customHeight="1">
       <x:c r="A32" s="40" t="n">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="9" t="str">
-        <x:v>audi-q5-coolant-leaks-2009</x:v>
+        <x:v>audi-q8-panoramic-sunroof-water-leak-into-cabin</x:v>
       </x:c>
       <x:c r="C32" s="9" t="str">
-        <x:v>2011-2017 | Audi | Q5</x:v>
+        <x:v>2019-2021 | Audi | Q8</x:v>
       </x:c>
       <x:c r="D32" s="9" t="str">
-        <x:v>2011-2017 Q5 2.0T Coolant Leak at Pump or Thermostat - TSB 2061604/5</x:v>
+        <x:v>2019-2021 Q8 Water Entry from Sunroof Area - TSB 2056944/10</x:v>
       </x:c>
       <x:c r="E32" s="9" t="str">
-        <x:v>Photograph the leak with date and VIN reference and pressure-test the cooling system according to Audi workshop instructions. Replace only the component confirmed to be leaking: the coolant pump or the thermostat housing. Follow Elsa for removal, assembly, belt-tension checking and current ETKA fitment. Do not replace every plastic cooling component, buy a bundled module or infer the source from a warning or puddle alone.</x:v>
+        <x:v>Have all four bulletin branches inspected and water-flow tested. Clear a drain obstruction or replace a damaged hose or valve, replace a damaged opening seal, correct glass adjustment, and perform the specified wind-deflector and channel modifications when applicable. Replace the sunroof frame only when actual structural damage is found. Do not order a frame from this card.</x:v>
       </x:c>
       <x:c r="F32" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G32" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="831.5999755859375" hidden="0" customHeight="1">
+    <x:row r="33" ht="752.4000244140625" hidden="0" customHeight="1">
       <x:c r="A33" s="40" t="n">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="9" t="str">
-        <x:v>audi-q5-oil-consumption-2010</x:v>
+        <x:v>audi-r8-5-2-v10-excessive-oil-consumption</x:v>
       </x:c>
       <x:c r="C33" s="9" t="str">
-        <x:v>2011-2011 | Audi | Q5</x:v>
+        <x:v>2009-2023 | Audi | R8 | 5.2L V10 FSI</x:v>
       </x:c>
       <x:c r="D33" s="9" t="str">
-        <x:v>2011 Q5 2.0T CAEB Oil-Consumption Procedure - TSB 2027731/7</x:v>
+        <x:v>5.2 V10 Excessive Oil Consumption</x:v>
       </x:c>
       <x:c r="E33" s="9" t="str">
-        <x:v>Verify the VIN and CAEB engine, document actual oil use and have an Audi-capable shop follow TSB 2027731/7. Check the crankcase-pressure regulating valve, use the current ETKA valve when required, replace the specified front seal and bolt, perform the Q5 SVM software update and run the electronic oil-consumption measurement exactly as directed. If the low-oil warning appears during the test, return for evaluation rather than adding oil. Do not replace pistons, rings, a turbo or a PCV part from this record alone.</x:v>
+        <x:v>Establish a documented consumption baseline (measured quarts over measured miles) and inspect the plugs/exhaust for oil fouling. Use a manufacturer-approved oil of the correct viscosity (owners report fewer issues with a quality 502/505-approved synthetic); some go to a heavier grade only with caution. Truly excessive consumption with smoke requires teardown for rings/valve seals, an engine-out job. Keep the oil topped between changes to protect the engine.</x:v>
       </x:c>
       <x:c r="F33" s="9" t="n">
         <x:v>0</x:v>
@@ -10669,21 +13441,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="501.6000061035156" hidden="0" customHeight="1">
+    <x:row r="34" ht="726" hidden="0" customHeight="1">
       <x:c r="A34" s="40" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="9" t="str">
-        <x:v>audi-q5-sportback-connecting-rod-bearing-failure</x:v>
+        <x:v>audi-r8-5-2-v10-oil-pump-driveshaft-seal-timing-case-oil-leak</x:v>
       </x:c>
       <x:c r="C34" s="9" t="str">
-        <x:v>2021-2023 | Audi | Q5 Sportback</x:v>
+        <x:v>2009-2023 | Audi | R8 | R8 V10, R8 V10 Plus, R8 V10 Performance, R8 V10 Spyder | 5.2L V10 FSI</x:v>
       </x:c>
       <x:c r="D34" s="9" t="str">
-        <x:v>2021-2023 Audi Q5 Sportback Engine Recall 13i5 / NHTSA 22V753</x:v>
+        <x:v>5.2 V10 Oil Pump Driveshaft Seal Timing-Case Oil Leak</x:v>
       </x:c>
       <x:c r="E34" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. Dealers inspect eligible vehicles and replace an affected engine when necessary at no charge. If the engine develops severe knocking, warning messages, smoke, oil leakage or a stall, stop safely and arrange dealer recovery rather than continuing to drive.</x:v>
+        <x:v>Confirm the source (timing-case oil-pump driveshaft seal, not valve covers or oil cooler). Repair involves removing the oil pump and renewing the oil-pump drive-shaft seal and associated O-rings/gaskets; a full reseal kit (e.g. RKX/Steso) is commonly used. It is mostly a labor and gasket/seal job rather than replacing the pump, though the pump can be replaced if worn. Fresh oil and coolant and a proper fill/bleed are required because both systems are opened.</x:v>
       </x:c>
       <x:c r="F34" s="9" t="n">
         <x:v>0</x:v>
@@ -10692,44 +13464,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="35" ht="1042.800048828125" hidden="0" customHeight="1">
       <x:c r="A35" s="40" t="n">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="9" t="str">
-        <x:v>audi-q5-sportback-ea888-water-pump-thermostat-housing-coolant-leak</x:v>
+        <x:v>audi-r8-ac-compressor-v8-2008</x:v>
       </x:c>
       <x:c r="C35" s="9" t="str">
-        <x:v>2021-2024 | Audi | Q5 Sportback | 2.0 TFSI</x:v>
+        <x:v>2008-2012 | Audi | R8 | 4.2 | 4.2 V8</x:v>
       </x:c>
       <x:c r="D35" s="9" t="str">
-        <x:v>2021-2024 Audi Q5 Sportback Coolant-Pump Leak TSB 2071515/1</x:v>
+        <x:v>A/C Compressor Failure Requiring Engine-Out Repair (4.2 V8)</x:v>
       </x:c>
       <x:c r="E35" s="9" t="str">
-        <x:v>Document the suspected leak, clean and dry all coolant traces, fill the system correctly and reassess after driving a few miles. If no fresh leak returns, continue observing without replacing parts. If leakage recurs, replace only the component causing it under the exact VIN, engine and part criteria. Confirm current coverage with Audi; do not order by model year alone.</x:v>
+        <x:v>A/C COMPRESSOR REPLACEMENT: Requires ENGINE REMOVAL on the V8 model. Total repair cost $5,000-$8,000 ($1,000-$1,500 for parts, $4,000-$6,500 for labor). When the engine is out, strongly recommended to also address: motor mounts, clutch inspection, and any other components that benefit from engine-out access. ALTERNATIVE: Some specialty R8 shops have developed methods to access the compressor with partial disassembly (removing subframe) rather than full engine removal, potentially reducing labor to $3,000-$4,000. PREVENTION: Run the A/C regularly (even in winter for 5-10 minutes monthly) to keep compressor seals lubricated.</x:v>
       </x:c>
       <x:c r="F35" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G35" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="528" hidden="0" customHeight="1">
+    <x:row r="36" ht="976.7999877929688" hidden="0" customHeight="1">
       <x:c r="A36" s="40" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="9" t="str">
-        <x:v>audi-q5-sportback-excessive-engine-oil-consumption</x:v>
+        <x:v>audi-r8-carbon-buildup-2008</x:v>
       </x:c>
       <x:c r="C36" s="9" t="str">
-        <x:v>2021-2025 | Audi | Q5 Sportback | 2.0T TFSI 45 TFSI (EA888)</x:v>
+        <x:v>2008-2015 | Audi | R8 | 4.2, 5.2 | 4.2 FSI V8, 5.2 FSI V10</x:v>
       </x:c>
       <x:c r="D36" s="9" t="str">
-        <x:v>Excessive Engine Oil Consumption (2.0 TFSI EA888)</x:v>
+        <x:v>Carbon Buildup on Intake Valves (4.2 V8 FSI and 5.2 V10 FSI)</x:v>
       </x:c>
       <x:c r="E36" s="9" t="str">
-        <x:v>Confirm consumption with a documented Audi oil-consumption test. Remedies range from PCV/oil-separator service and updated piston rings to, in severe cases, piston/ring replacement; walnut-blasting addresses associated intake-valve carbon. Owners should monitor oil level frequently between service intervals as a safeguard.</x:v>
+        <x:v>WALNUT BLASTING: Remove intake manifolds and blast all intake ports with walnut shells. V8 (4.2L): $800-$1,200. V10 (5.2L): $1,200-$2,000 due to 10 cylinders. Perform a leak-down test BEFORE walnut blasting to ensure intake valves seat properly. Repeat every 50,000-70,000 miles. CHEMICAL CLEANING: Less effective than walnut blasting but some owners use intake valve cleaners (BG Products, CRC) as interim maintenance. DRIVING HABITS: Regular high-RPM driving (the R8's natural habitat) helps slow carbon accumulation. PREVENTION: Use quality fuel (91+ octane) and change oil every 5,000 miles.</x:v>
       </x:c>
       <x:c r="F36" s="9" t="n">
         <x:v>0</x:v>
@@ -10738,21 +13510,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="37" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A37" s="40" t="n">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="9" t="str">
-        <x:v>audi-q5-sportback-front-assist-phantom-braking-false-emergency-braking</x:v>
+        <x:v>audi-r8-carbon-fiber-sideblade-trim-clear-coat-peeling</x:v>
       </x:c>
       <x:c r="C37" s="9" t="str">
-        <x:v>2021-2025 | Audi | Q5 Sportback</x:v>
+        <x:v>2008-2015 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
       </x:c>
       <x:c r="D37" s="9" t="str">
-        <x:v>Front Assist Phantom Braking / False Emergency Braking (ADAS)</x:v>
+        <x:v>Carbon Fiber Sideblade and Trim Clear-Coat Peeling</x:v>
       </x:c>
       <x:c r="E37" s="9" t="str">
-        <x:v>Have the dealer scan for ADAS faults and apply any available radar/camera control-module software updates and sensor recalibration; check for and clear obstructions/misalignment of the front radar. Persistent cases may require sensor replacement. Document incidents and file an NHTSA complaint, as ongoing investigations can drive a recall.</x:v>
+        <x:v>Refinish the affected panel: carefully sand back the failed lacquer without cutting into the carbon weave, then re-clear with a UV-stabilized automotive clear coat (best done by a shop experienced with carbon). To prevent recurrence, protect the finish with paint-protection film (clear wrap) or a ceramic coating, which also guards against stone chips.</x:v>
       </x:c>
       <x:c r="F37" s="9" t="n">
         <x:v>0</x:v>
@@ -10761,21 +13533,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="396" hidden="0" customHeight="1">
+    <x:row r="38" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A38" s="40" t="n">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="9" t="str">
-        <x:v>audi-q5-sportback-loose-cylinder-head-cover-screws-causing-oil-leak-fire-risk</x:v>
+        <x:v>audi-r8-catalytic-converter-failure-requiring-engine-out-replacement</x:v>
       </x:c>
       <x:c r="C38" s="9" t="str">
-        <x:v>2022-2024 | Audi | Q5 Sportback</x:v>
+        <x:v>2008-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
       </x:c>
       <x:c r="D38" s="9" t="str">
-        <x:v>2022-2024 Audi Q5 Sportback Head-Cover Recall 15ZK / NHTSA 25V294</x:v>
+        <x:v>Catalytic Converter Failure Requiring Engine-Out Replacement</x:v>
       </x:c>
       <x:c r="E38" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. Dealers inspect and replace the screws as necessary at no charge. If oil odor, smoke or visible leakage occurs, stop safely, switch the vehicle off and arrange Audi inspection.</x:v>
+        <x:v>Confirm the failed bank with O2/catalyst-efficiency data and a back-pressure check before condemning. OEM repair means replacing the catalytic-converter-with-integrated-manifold assembly (engine-out labor); many owners opt for high-flow aftermarket or de-catted manifolds where legal. Verify no upstream misfire/oil-consumption issue is destroying the new cats.</x:v>
       </x:c>
       <x:c r="F38" s="9" t="n">
         <x:v>0</x:v>
@@ -10784,21 +13556,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="488.3999938964844" hidden="0" customHeight="1">
+    <x:row r="39" ht="422.3999938964844" hidden="0" customHeight="1">
       <x:c r="A39" s="40" t="n">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="9" t="str">
-        <x:v>audi-q5-sportback-mild-hybrid-electrical-fault-start-stop-failure</x:v>
+        <x:v>audi-r8-clutch-pack-2008</x:v>
       </x:c>
       <x:c r="C39" s="9" t="str">
-        <x:v>2021-2022 | Audi | Q5 Sportback</x:v>
+        <x:v>2021-2022 | Audi | R8</x:v>
       </x:c>
       <x:c r="D39" s="9" t="str">
-        <x:v>2021-2022 Audi Q5 Sportback Gateway Recall 90S9 / NHTSA 21V947</x:v>
+        <x:v>Gearbox Underfilled: Clutch Slippage or Transmission-Oil Leak (Recall 22V225 / 37O1)</x:v>
       </x:c>
       <x:c r="E39" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. The free remedy installs a protective gateway-module cover and seals the underbody seam when necessary. If multiple warnings appear or engine power drops, move out of traffic safely and arrange dealer inspection; do not order a 12-volt battery from this card.</x:v>
+        <x:v>Check the VIN and campaign history with Audi or NHTSA. Under campaign 37O1, an Audi dealer inspects and corrects the transmission-oil level free of charge. If drive power drops, a clutch slips, or oil/smoke is noticed, stop safely and arrange dealer inspection.</x:v>
       </x:c>
       <x:c r="F39" s="9" t="n">
         <x:v>0</x:v>
@@ -10807,21 +13579,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="40" ht="1042.800048828125" hidden="0" customHeight="1">
       <x:c r="A40" s="40" t="n">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="9" t="str">
-        <x:v>audi-q5-sportback-phev-high-voltage-battery-overheating-fire-risk</x:v>
+        <x:v>audi-r8-clutch-wear-2008</x:v>
       </x:c>
       <x:c r="C40" s="9" t="str">
-        <x:v>2021-2024 | Audi | Q5 Sportback | 55 TFSI e quattro, Q5 Sportback TFSI e PHEV | 2.0T TFSI e plug-in hybrid</x:v>
+        <x:v>2008-2015 | Audi | R8 | 4.2, 5.2</x:v>
       </x:c>
       <x:c r="D40" s="9" t="str">
-        <x:v>PHEV High-Voltage Battery Overheating / Fire Risk (Recall 25V080000)</x:v>
+        <x:v>R-Tronic Clutch Premature Wear and Expensive Replacement</x:v>
       </x:c>
       <x:c r="E40" s="9" t="str">
-        <x:v>Audi installs advanced diagnostic/monitoring software as the final remedy and replaces individual battery modules or the entire high-voltage pack where defective cells are detected, free of charge. Affected owners should follow the do-not-charge guidance until inspected and confirm recall status by VIN.</x:v>
+        <x:v>CLUTCH REPLACEMENT: Replace clutch disc, pressure plate, throwout bearing, and resurface/replace flywheel ($5,500-$9,000 at dealer, $4,000-$6,000 at independent specialist). The mid-engine layout requires dropping the transmission—8-12 hours of labor. DRIVING TECHNIQUE: Minimize R-Tronic slip by avoiding creeping in traffic (use brake hold instead). Use manual mode in stop-and-go traffic. Avoid reverse on steep inclines. For TRACK USE: Budget for clutch replacement every 10,000-20,000 miles—R-Tronic track driving is hard on clutches. ALTERNATIVE: S-Tronic (Gen 2 R8) wet dual-clutch is significantly more durable for daily driving.</x:v>
       </x:c>
       <x:c r="F40" s="9" t="n">
         <x:v>0</x:v>
@@ -10830,21 +13602,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="41" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A41" s="40" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="9" t="str">
-        <x:v>audi-q5-sportback-rear-brake-squeal-2021</x:v>
+        <x:v>audi-r8-coolant-expansion-tank-cracking-cooling-system-leaks</x:v>
       </x:c>
       <x:c r="C41" s="9" t="str">
-        <x:v>2021-2026 | Audi | Q5 Sportback | Premium, Premium Plus, Prestige | 2.0T</x:v>
+        <x:v>2008-2015 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
       </x:c>
       <x:c r="D41" s="9" t="str">
-        <x:v>Rear Brake Squeal and Premature Pad Wear</x:v>
+        <x:v>Coolant Expansion Tank Cracking and Cooling System Leaks</x:v>
       </x:c>
       <x:c r="E41" s="9" t="str">
-        <x:v>Replace rear brake pads with aftermarket ceramic compound pads that eliminate the metallic resonance squeal. Apply brake pad shims and caliper slide pin lubricant. Have the electronic parking brake calibrated via scan tool to reduce unnecessary auto-apply frequency. Replace rotors if they show scoring or are below minimum thickness.</x:v>
+        <x:v>Pressure-test the cooling system to pinpoint the leak. Replace the cracked expansion/overflow tank with the updated design and renew brittle hose clamps/connections; inspect the radiator and cap. Refill with the correct Audi G13/G12 coolant specification and bleed the system fully. Address any weeping hose fittings at the same time.</x:v>
       </x:c>
       <x:c r="F41" s="9" t="n">
         <x:v>0</x:v>
@@ -10853,21 +13625,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="316.79998779296875" hidden="0" customHeight="1">
+    <x:row r="42" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A42" s="40" t="n">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="9" t="str">
-        <x:v>audi-q5-sportback-sunroof-rattle-2021</x:v>
+        <x:v>audi-r8-direct-injection-fuel-injector-failure</x:v>
       </x:c>
       <x:c r="C42" s="9" t="str">
-        <x:v>2021-2025 | Audi | Q5 Sportback</x:v>
+        <x:v>2008-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
       </x:c>
       <x:c r="D42" s="9" t="str">
-        <x:v>Panoramic Sunroof Wind Noise and Rattle</x:v>
+        <x:v>Direct-Injection Fuel Injector Failure</x:v>
       </x:c>
       <x:c r="E42" s="9" t="str">
-        <x:v>Clean and lubricate sunroof rails and seals with Krytox or silicone grease. Adjust sunroof alignment via dealer. Replace wind deflector if cracked. In some cases, the sunroof cassette requires re-indexing via scan tool.</x:v>
+        <x:v>Confirm the failing cylinder with misfire and fuel-trim data and, where possible, injector-specific fault codes rather than replacing coils blindly. Replace the failed injector(s) with OEM FSI units; many owners replace as a bank or full set given shared age and mileage, and clean or address intake-valve carbon at the same service. Expect roughly $2,900 for a multi-injector job including labor per owner reports.</x:v>
       </x:c>
       <x:c r="F42" s="9" t="n">
         <x:v>0</x:v>
@@ -10876,21 +13648,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="43" ht="528" hidden="0" customHeight="1">
       <x:c r="A43" s="40" t="n">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="9" t="str">
-        <x:v>audi-q5-sportback-virtual-cockpit-2021</x:v>
+        <x:v>audi-r8-front-axle-hydraulic-lift-system-pump-failure</x:v>
       </x:c>
       <x:c r="C43" s="9" t="str">
-        <x:v>2021-2021 | Audi | Q5 Sportback</x:v>
+        <x:v>2017-2023 | Audi | R8 | 5.2L V10 FSI</x:v>
       </x:c>
       <x:c r="D43" s="9" t="str">
-        <x:v>2021 Audi Q5 Sportback Rearview-Camera Recall 91DZ / NHTSA 22V742</x:v>
+        <x:v>Front Axle Hydraulic Lift System Pump Failure</x:v>
       </x:c>
       <x:c r="E43" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. The free remedy updates the infotainment-unit software. Until repaired, use mirrors and direct observation with extra care while reversing. Do not order a replacement instrument cluster or generic scan tool from this summary.</x:v>
+        <x:v>Diagnose the lift pump/hydraulic circuit; a failed pump is the usual culprit. A new dealer pump assembly runs over $3,000, so many owners fit a good used OEM pump or an independent rebuild as a cost-effective alternative. Until repaired, approach inclines and speed bumps at an angle and very slowly to avoid front-end damage.</x:v>
       </x:c>
       <x:c r="F43" s="9" t="n">
         <x:v>0</x:v>
@@ -10899,21 +13671,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="924" hidden="0" customHeight="1">
+    <x:row r="44" ht="316.79998779296875" hidden="0" customHeight="1">
       <x:c r="A44" s="40" t="n">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="9" t="str">
-        <x:v>audi-q5-sunroof-drain-clogs-2009</x:v>
+        <x:v>audi-r8-front-passenger-airbag-inflator-rupture</x:v>
       </x:c>
       <x:c r="C44" s="9" t="str">
-        <x:v>2011-2023 | Audi | Q5</x:v>
+        <x:v>2016-2016 | Audi | R8</x:v>
       </x:c>
       <x:c r="D44" s="9" t="str">
-        <x:v>2011-2023 Q5 Panoramic-Sunroof Water Entry - Recall 69P1 / TSB 2075969/2</x:v>
+        <x:v>Front-Passenger Airbag Module May Explode or Deploy Improperly (Recall 22V543 / 69DY)</x:v>
       </x:c>
       <x:c r="E44" s="9" t="str">
-        <x:v>For a 2011-2017 panoramic-roof Q5, check the VIN for Recall 69P1 first and follow Audi’s dealer precautions and remedy; until an open recall is completed, do not use the second row and seek prompt inspection if headliner or rear-cabin leakage is visible. For a 2018-2023 panoramic-roof Q5, have the drain hoses inspected under TSB 2075969/2; the workshop lowers the headliner, replaces kinked hoses and cleans all four hoses with the specified tool when substantial dirt is present. Do not use compressed air, weed-trimmer line or a generic drain-tube kit from this record.</x:v>
+        <x:v>Check the VIN with Audi or NHTSA. Audi dealers replace the front-passenger airbag module free of charge under campaign 69DY/61C1. Do not source a used airbag module from this summary.</x:v>
       </x:c>
       <x:c r="F44" s="9" t="n">
         <x:v>0</x:v>
@@ -10922,21 +13694,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="475.20001220703125" hidden="0" customHeight="1">
+    <x:row r="45" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A45" s="40" t="n">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="9" t="str">
-        <x:v>audi-q5-timing-chain-2009</x:v>
+        <x:v>audi-r8-fuel-supply-line-chafing-heat-shield</x:v>
       </x:c>
       <x:c r="C45" s="9" t="str">
-        <x:v>2009-2017 | Audi | Q5 | Premium, Premium Plus, Prestige | 2.0T</x:v>
+        <x:v>2011-2012 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
       </x:c>
       <x:c r="D45" s="9" t="str">
-        <x:v>EA888 Timing Chain Tensioner Failure</x:v>
+        <x:v>R8 Spyder Fuel Supply Line Can Chafe on Heat Shield (Recall 11V390 / 20Q8)</x:v>
       </x:c>
       <x:c r="E45" s="9" t="str">
-        <x:v>Replace timing chain, tensioner (latest revision 06K109467K), guides, and upper chain tensioner as a complete kit. The Q5 requires more labor than the A4 due to engine bay packaging. Preventive replacement at 80,000 miles is strongly recommended, especially on pre-2013 engines.</x:v>
+        <x:v>Check the VIN and recall status. Audi dealers inspect the line, replace it if damaged, and adjust the fuel line and heat shield for proper clearance free of charge. If fuel odor or leakage is present, stop driving and arrange immediate inspection.</x:v>
       </x:c>
       <x:c r="F45" s="9" t="n">
         <x:v>0</x:v>
@@ -10945,44 +13717,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="752.4000244140625" hidden="0" customHeight="1">
+    <x:row r="46" ht="792" hidden="0" customHeight="1">
       <x:c r="A46" s="40" t="n">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="9" t="str">
-        <x:v>audi-q5-timing-chain-tensioner-2011</x:v>
+        <x:v>audi-r8-ignition-coil-pack-failure-causing-misfires</x:v>
       </x:c>
       <x:c r="C46" s="9" t="str">
-        <x:v>2011-2012 | Audi | Q5</x:v>
+        <x:v>2008-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
       </x:c>
       <x:c r="D46" s="9" t="str">
-        <x:v>2011-2012 Q5 Timing Chain/Tensioner Diagnosis - Warranty Key U35</x:v>
+        <x:v>Ignition Coil Pack Failure Causing Misfires</x:v>
       </x:c>
       <x:c r="E46" s="9" t="str">
-        <x:v>If timing noise, a timing fault, a no-start or suspected mechanical timing damage is present, stop driving when safe operation is uncertain and obtain engine-specific diagnosis. Ask an Audi dealer to check the VIN, Warranty Key U35 history and repair history, but do not assume current settlement coverage. Repair only after the chain, tensioner, timing relationship and any consequential engine damage are confirmed; do not buy a tensioner or kit from this record.</x:v>
+        <x:v>Diagnose the misfiring cylinder(s) via the stored misfire counters, then replace the failed coil(s) along with spark plugs; most specialists replace the full set of 8 (V8) or 10 (V10) plus plugs to avoid repeat visits. The canonical 4.2 V8 coil is the revision-'T' red coil, Audi/VW PN 077905115T (superseded family, aftermarket cross-reference 06E905115E). The Gen-2 5.2 V10 uses Audi PN 07L905115B. Address any valve-cover or plug-tube oil leak at the same time so new coils are not contaminated.</x:v>
       </x:c>
       <x:c r="F46" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G46" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="1240.800048828125" hidden="0" customHeight="1">
+    <x:row r="47" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A47" s="40" t="n">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="9" t="str">
-        <x:v>audi-q5-transmission-mechatronic-2009</x:v>
+        <x:v>audi-r8-led-headlight-drl-module-failure-flickering</x:v>
       </x:c>
       <x:c r="C47" s="9" t="str">
-        <x:v>2011-2012 | Audi | Q5</x:v>
+        <x:v>2014-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
       </x:c>
       <x:c r="D47" s="9" t="str">
-        <x:v>2011-2012 Q5 2.0T Hesitation or Harsh-Shift Service - TSB 2032812/9</x:v>
+        <x:v>LED Headlight / DRL Module Failure and Flickering</x:v>
       </x:c>
       <x:c r="E47" s="9" t="str">
-        <x:v>Reproduce the exact hesitation or harsh-shift concern and confirm the 2.0L/0BK-8-speed application. Check the installed crankcase-pressure regulating valve first: if 06H103495AE is already fitted, do not replace those parts; otherwise TSB 2032812/9 directs replacement with 06H103495AE plus front crankshaft seal 06L103085B and bolt WHT001760 before the software update. Check both TCM and ECM software levels and apply only matching SVM updates. For model year 2011, clear adaptations and perform the GFF test-drive adaptation; for 2012, perform the standstill adaptation. Continue diagnosis if the condition or any separate DTC remains. Do not replace a mechatronic unit, valve body or transmission or prescribe a fluid interval from this record.</x:v>
+        <x:v>Inspect the headlight for moisture and corroded connectors; a failed LED driver module usually requires replacing the headlight assembly (used units run roughly £1,600-1,800, new from Audi around £2,800), followed by headlight aiming/auto-leveling calibration with a diagnostic tool. Reseal or replace cracked housings to stop repeat water damage. Some independent specialists can repair the driver board at lower cost.</x:v>
       </x:c>
       <x:c r="F47" s="9" t="n">
         <x:v>0</x:v>
@@ -10991,21 +13763,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="48" ht="264" hidden="0" customHeight="1">
       <x:c r="A48" s="40" t="n">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="9" t="str">
-        <x:v>audi-q5-water-pump-failure-2009</x:v>
+        <x:v>audi-r8-magnetic-ride-2008</x:v>
       </x:c>
       <x:c r="C48" s="9" t="str">
-        <x:v>2013-2017 | Audi | Q5</x:v>
+        <x:v>2008-2024 | Audi | R8</x:v>
       </x:c>
       <x:c r="D48" s="9" t="str">
-        <x:v>2013-2017 Q5 After-Run Coolant Pump Campaign 19N8 - VIN Check Required</x:v>
+        <x:v>Magnetic Ride Damper Fluid Leaks</x:v>
       </x:c>
       <x:c r="E48" s="9" t="str">
-        <x:v>Check the VIN and current open-action status with an Audi dealer. When Service Action 19N8 is open, Audi directs installation of the revised electric after-run coolant pump and an ECM software update. An EPC warning can indicate a blocked pump on vehicles with the relevant software; contact a dealer without delay. Do not buy a main pump, thermostat module, impeller kit or generic replacement from this campaign card, and do not infer eligibility from model year alone.</x:v>
+        <x:v>Replace magnetic ride dampers. OEM replacements are very expensive. KW or Bilstein aftermarket coilovers are popular track-oriented alternatives.</x:v>
       </x:c>
       <x:c r="F48" s="9" t="n">
         <x:v>0</x:v>
@@ -11014,21 +13786,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="49" ht="1227.5999755859375" hidden="0" customHeight="1">
       <x:c r="A49" s="40" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" s="9" t="str">
-        <x:v>audi-q7-air-suspension-2007</x:v>
+        <x:v>audi-r8-magnetic-ride-leak-2008</x:v>
       </x:c>
       <x:c r="C49" s="9" t="str">
-        <x:v>2007-2015 | Audi | Q7 | Premium, Premium Plus, Prestige | 3.0T, 3.6L, 4.2L, 3.0 TDI</x:v>
+        <x:v>2008-2015 | Audi | R8 | 4.2, 5.2</x:v>
       </x:c>
       <x:c r="D49" s="9" t="str">
-        <x:v>Air Suspension System Failure (Compressor and Springs)</x:v>
+        <x:v>Magnetic Ride Suspension Damper Leak and Premature Failure</x:v>
       </x:c>
       <x:c r="E49" s="9" t="str">
-        <x:v>Replace all four air springs and the compressor as a complete system overhaul for best results. If budget is limited, replace the leaking spring(s) and compressor together. Always replace the compressor relay. Arnott aftermarket air springs are popular and cost 50-60% less than OEM. Some owners convert to coilover suspension ($2,000-$3,000) to eliminate the air system entirely.</x:v>
+        <x:v>OEM REPLACEMENT: Replace leaking magnetic ride shocks ($1,800 each, $5,100-$8,000+ for full set installed). OEM replacements use the same technology and will eventually fail again. REFURBISHED OPTION: Refurbished magnetic ride dampers from specialty rebuilders (approximately $1,000-$1,400 each). PASSIVE CONVERSION: Convert to R8 Plus passive shocks ($3,000-$4,000 for set—less than 2 OEM magnetic ride shocks) or aftermarket coilovers ($2,500-$5,000 for quality kit like KW, JRZ, or Ohlins). Passive conversion eliminates the failure mode permanently but removes adaptive ride control. PREVENTION: Limited—magnetic fluid degradation is inherent to the technology. Budget for replacement every 30,000-50,000 miles if keeping magnetic ride.</x:v>
       </x:c>
       <x:c r="F49" s="9" t="n">
         <x:v>0</x:v>
@@ -11037,21 +13809,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="831.5999755859375" hidden="0" customHeight="1">
+    <x:row r="50" ht="1003.2000122070312" hidden="0" customHeight="1">
       <x:c r="A50" s="40" t="n">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B50" s="9" t="str">
-        <x:v>audi-q7-air-suspension-failure-2007</x:v>
+        <x:v>audi-r8-r-tronic-hydraulic-pump-pressure-accumulator-failure</x:v>
       </x:c>
       <x:c r="C50" s="9" t="str">
-        <x:v>2007-2015 | Audi | Q7</x:v>
+        <x:v>2008-2015 | Audi | R8 | R8 4.2 R tronic, R8 V10 R tronic, R8 V10 Plus R tronic | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
       </x:c>
       <x:c r="D50" s="9" t="str">
-        <x:v>Air Suspension Strut Failure and Compressor Issues</x:v>
+        <x:v>R tronic Hydraulic Pump and Pressure Accumulator Failure</x:v>
       </x:c>
       <x:c r="E50" s="9" t="str">
-        <x:v>Leaking strut: Replace air strut ($800-1,500 per corner). All four corners worn: Replace all four struts ($3,000-5,500). Failed compressor: Replace air suspension compressor ($1,200-2,000). Control module fault: Replace suspension control module ($800-1,500). Alternative: Convert to coil spring suspension ($1,500-2,500 all corners) - eliminates air suspension issues permanently. AudiWorld recommends Arnott or Strutmasters air struts (cheaper than OEM, good quality).</x:v>
+        <x:v>Diagnose with a scan tool: a failing accumulator/pump typically stores P17BF (hydraulic pump play protection) and/or P0944 (loss of hydraulic pressure). Standard repair order is to renew the relatively inexpensive pressure accumulator first; if pressure loss persists, replace the hydraulic pump (and its relay/fuse), and only then suspect the hydraulic clutch/gear actuator or the solenoid-valve O-rings. Fresh, correct-spec hydraulic fluid and a proper bleed with a diagnostic tool are required. Owners are advised not to drive the car (except directly to a shop) once the pump is heard running continuously or shifting becomes intermittent.</x:v>
       </x:c>
       <x:c r="F50" s="9" t="n">
         <x:v>0</x:v>
@@ -11060,21 +13832,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="51" ht="198" hidden="0" customHeight="1">
       <x:c r="A51" s="40" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B51" s="9" t="str">
-        <x:v>audi-q7-carbon-buildup-3.0t-2011</x:v>
+        <x:v>audi-r8-s-tronic-actuator-2008</x:v>
       </x:c>
       <x:c r="C51" s="9" t="str">
-        <x:v>2011-2016 | Audi | Q7 | 3.0 TFSI</x:v>
+        <x:v>2008-2024 | Audi | R8</x:v>
       </x:c>
       <x:c r="D51" s="9" t="str">
-        <x:v>2011-2016 Q7 3.0 TFSI Secondary-Air Carbon Restriction - P0491/P0492</x:v>
+        <x:v>S-tronic Transmission Actuator Failure</x:v>
       </x:c>
       <x:c r="E51" s="9" t="str">
-        <x:v>Have an Audi-trained technician confirm that P0491 and P0492 are present together, test the secondary-air pump and hose routing, and measure secondary-air flow using the bulletin procedure. If the measured flow and checks match the bulletin, the cylinder-head secondary-air ports are cleaned with Audi tools and training. Do not buy a PCV assembly, catch can or intake-cleaning product from this card.</x:v>
+        <x:v>Replace S-tronic actuators. Full transmission service with correct S-tronic fluid is critical. Dealer or specialist only repair.</x:v>
       </x:c>
       <x:c r="F51" s="9" t="n">
         <x:v>0</x:v>
@@ -11083,21 +13855,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="712.7999877929688" hidden="0" customHeight="1">
+    <x:row r="52" ht="330" hidden="0" customHeight="1">
       <x:c r="A52" s="40" t="n">
         <x:v>51</x:v>
       </x:c>
       <x:c r="B52" s="9" t="str">
-        <x:v>audi-q7-supercharger-failure-2011</x:v>
+        <x:v>audi-r8-s-tronic-gearbox-ventilation-hose-transmission-fluid-leak</x:v>
       </x:c>
       <x:c r="C52" s="9" t="str">
-        <x:v>2011-2015 | Audi | Q7 | Premium, Premium Plus, Prestige, S line, SQ7 | 3.0T</x:v>
+        <x:v>2017-2018 | Audi | R8 | 5.2L V10 FSI</x:v>
       </x:c>
       <x:c r="D52" s="9" t="str">
-        <x:v>Supercharger Bearing Failure and Boost Leaks (3.0T)</x:v>
+        <x:v>Gearbox Ventilation Hose Can Leak Fluid Near Hot Engine Parts (Recall 18V639 / 34J1)</x:v>
       </x:c>
       <x:c r="E52" s="9" t="str">
-        <x:v>Worn bearings: Supercharger rebuild with new bearings ($1,500-2,500) or replacement supercharger ($3,000-5,000). Bypass valve: Replace supercharger bypass valve ($300-600). Boost leaks: Inspect all boost hoses/clamps, replace cracked hoses ($150-400). Use OEM Audi or quality aftermarket (INA) supercharger bearings. AudiWorld recommends catch can installation ($300-500) to reduce oil vapor damage to supercharger.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the single gearbox ventilation hose with the higher-volume double hose free of charge under campaign 34J1. Stop driving if hot-oil odor or smoke appears.</x:v>
       </x:c>
       <x:c r="F52" s="9" t="n">
         <x:v>0</x:v>
@@ -11106,21 +13878,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="53" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A53" s="40" t="n">
         <x:v>52</x:v>
       </x:c>
       <x:c r="B53" s="9" t="str">
-        <x:v>audi-q7-tdi-emissions-scandal-2009</x:v>
+        <x:v>audi-r8-spyder-convertible-top-hydraulic-pump-failure</x:v>
       </x:c>
       <x:c r="C53" s="9" t="str">
-        <x:v>2009-2015 | Audi | Q7 | 3.0 TDI</x:v>
+        <x:v>2011-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
       </x:c>
       <x:c r="D53" s="9" t="str">
-        <x:v>2009-2015 Q7 3.0 TDI Emissions Settlement and Modification History</x:v>
+        <x:v>Spyder Convertible Top Hydraulic Pump Failure</x:v>
       </x:c>
       <x:c r="E53" s="9" t="str">
-        <x:v>Check the VIN and service history with an authorized Audi dealer and use current EPA or Audi settlement information to determine whether an emissions modification was completed and what extended emissions warranty, if any, applies to that vehicle. Diagnose any present warning or drivability concern separately. Do not buy a scan tool or generic repair manual as a settlement remedy.</x:v>
+        <x:v>Scan for the specific fault (pump vs. sensor vs. latch) before parting; a mis-reading position sensor can mimic a dead pump. Replace the hydraulic pump/motor assembly (Audi R8 Spyder convertible-top hydraulic pump PN 427871791 for 2010-2016 cars) and top up/refill the correct hydraulic fluid, or replace the failed cylinder/sensor. Leaking lines and worn seals should be renewed together. Independent hydraulic rebuild services exist as a lower-cost alternative to a full dealer pump.</x:v>
       </x:c>
       <x:c r="F53" s="9" t="n">
         <x:v>0</x:v>
@@ -11129,21 +13901,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="594" hidden="0" customHeight="1">
+    <x:row r="54" ht="1122" hidden="0" customHeight="1">
       <x:c r="A54" s="40" t="n">
         <x:v>53</x:v>
       </x:c>
       <x:c r="B54" s="9" t="str">
-        <x:v>audi-q7-tdi-oil-cooler-leak-2013</x:v>
+        <x:v>audi-r8-v8-engine-bearing-2008</x:v>
       </x:c>
       <x:c r="C54" s="9" t="str">
-        <x:v>2013-2013 | Audi | Q7 | 3.0 TDI</x:v>
+        <x:v>2008-2015 | Audi | R8 | 4.2 | 4.2 FSI</x:v>
       </x:c>
       <x:c r="D54" s="9" t="str">
-        <x:v>2013 Q7 TDI Brake-Booster Vacuum-Line Recall 47L8 (14V516)</x:v>
+        <x:v>Rod Bearing Wear and Engine Failure Risk (4.2 V8 FSI)</x:v>
       </x:c>
       <x:c r="E54" s="9" t="str">
-        <x:v>Check the VIN for open recall 47L8 with Audi. The dealer remedy replaces the specified vacuum line and inspects the vacuum line and brake booster for oil contamination. Additional vacuum-line or brake-booster components are replaced when contamination is found. The recall repair is dealer work and is not a reason to buy an oil cooler, scan tool or manual.</x:v>
+        <x:v>EARLY DETECTION (knocking noise only): Rod bearing replacement ($2,000-$5,000). Must be caught EARLY before bearing material migrates through oil system. Cut open every oil filter at oil change to inspect for metallic debris. CATASTROPHIC FAILURE: Engine replacement ($13,000+ Audi exchange, $8,000-$15,000 rebuilt from AMTuned or specialist rebuilder). ARP 2000 reinforced connecting rod bolts are available as a preventive upgrade during any engine-out service. PREVENTION: Use ONLY premium 5W-40 synthetic oil. Change oil every 5,000 miles maximum. NEVER exceed oil change intervals—the high-revving V8 is extremely sensitive to oil condition. For track use, change oil after every 2-3 track days.</x:v>
       </x:c>
       <x:c r="F54" s="9" t="n">
         <x:v>0</x:v>
@@ -11152,21 +13924,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="488.3999938964844" hidden="0" customHeight="1">
+    <x:row r="55" ht="924" hidden="0" customHeight="1">
       <x:c r="A55" s="40" t="n">
         <x:v>54</x:v>
       </x:c>
       <x:c r="B55" s="9" t="str">
-        <x:v>audi-q7-timing-chain-tensioner-2007</x:v>
+        <x:v>audi-rs-etron-gt-battery-short-2022</x:v>
       </x:c>
       <x:c r="C55" s="9" t="str">
-        <x:v>2011-2015 | Audi | Q7 | 3.0 TFSI</x:v>
+        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
       </x:c>
       <x:c r="D55" s="9" t="str">
-        <x:v>2011-2015 Q7 3.0 TFSI Brief Cold-Start Timing-Chain Rattle - TSB 2039995/2</x:v>
+        <x:v>2022-2024 RS e-tron GT High-Voltage Battery Recall 931A/931B (24V726)</x:v>
       </x:c>
       <x:c r="E55" s="9" t="str">
-        <x:v>Confirm that the concern is the bulletin-defined one-to-three-second first-start rattle and have an Audi technician follow TSB 2039995/2 and current repair information. A longer, persistent or different noise, warning light or drivability concern requires separate diagnosis. Do not order a timing kit from this card.</x:v>
+        <x:v>Check the VIN for open Audi campaign 931A or 931B and complete the authorized dealer remedy. Under 931A, enrolled vehicles can be monitored through online battery data; Audi contacts owners if a module appears critical. Under 931B, the dealer performs diagnostic procedures until the final monitoring software is installed. Audi installs the onboard diagnostic software and replaces affected battery modules at no cost when anomalies are identified. Follow any vehicle- or dealer-specific 80-percent charging instruction; the filing does not direct every 931A vehicle to use that limit.</x:v>
       </x:c>
       <x:c r="F55" s="9" t="n">
         <x:v>0</x:v>
@@ -11175,21 +13947,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="56" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A56" s="40" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="B56" s="9" t="str">
-        <x:v>audi-q7-transfer-case-2007</x:v>
+        <x:v>audi-rs-etron-gt-brake-hose-2022</x:v>
       </x:c>
       <x:c r="C56" s="9" t="str">
-        <x:v>2007-2019 | Audi | Q7 | Premium, Premium Plus, Prestige | 3.0T, 3.6L, 4.2L, 3.0 TDI</x:v>
+        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
       </x:c>
       <x:c r="D56" s="9" t="str">
-        <x:v>Transfer Case Fluid Leak and Failure</x:v>
+        <x:v>2022-2024 RS e-tron GT Front Brake-Hose Recall 47UP (24V465)</x:v>
       </x:c>
       <x:c r="E56" s="9" t="str">
-        <x:v>Replace leaking seals and refill with correct fluid (75W-90 GL-5 or Audi specification). If grinding is present, the transfer case may need rebuild or replacement. Regular fluid changes every 60,000 miles can prevent internal damage. Check for leaks at every oil change.</x:v>
+        <x:v>Check the VIN for an open 47UP action and have an authorized Audi dealer replace both front brake hoses and holders free of charge. If pedal travel increases or the vehicle displays a warning related to reduced brake fluid, contact an Audi dealer for diagnosis without delay. Do not buy a single hose or substitute generic brake lines from the prior links; the campaign controls the complete criteria-specific repair.</x:v>
       </x:c>
       <x:c r="F56" s="9" t="n">
         <x:v>0</x:v>
@@ -11198,21 +13970,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="57" ht="726" hidden="0" customHeight="1">
       <x:c r="A57" s="40" t="n">
         <x:v>56</x:v>
       </x:c>
       <x:c r="B57" s="9" t="str">
-        <x:v>audi-q7-water-pump-failure-2007</x:v>
+        <x:v>audi-rs-etron-gt-charging-port-2022</x:v>
       </x:c>
       <x:c r="C57" s="9" t="str">
-        <x:v>2007-2015 | Audi | Q7</x:v>
+        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
       </x:c>
       <x:c r="D57" s="9" t="str">
-        <x:v>Water Pump and Thermostat Failure (Overheating)</x:v>
+        <x:v>2022-2024 RS e-tron GT Red Charging LED or Fast-Charging Abort - Audi 91VT</x:v>
       </x:c>
       <x:c r="E57" s="9" t="str">
-        <x:v>IMMEDIATE if overheating: Pull over, turn off engine, DO NOT continue - engine damage occurs in minutes. Preventive: Replace water pump/thermostat assembly at 60k-80k miles ($800-1,500) to avoid catastrophic failure. Failed pump: Replace water pump/thermostat ($800-1,500). If overheated: Cylinder head inspection, possible head gasket replacement ($2,500-5,000). Use OEM Audi or premium Geba/Meyle parts.</x:v>
+        <x:v>Have an Audi dealer check the VIN and assigned 91VT criterion in the campaign/action system. For the charging-related criteria, the authorized remedy updates the high-voltage battery control-module software, with the convenience-system control module also updated where the assigned criterion requires it. Diagnose charging failures outside that exact campaign branch rather than replacing the charging socket or module from symptoms alone.</x:v>
       </x:c>
       <x:c r="F57" s="9" t="n">
         <x:v>0</x:v>
@@ -11221,21 +13993,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="58" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A58" s="40" t="n">
         <x:v>57</x:v>
       </x:c>
       <x:c r="B58" s="9" t="str">
-        <x:v>audi-q8-48v-system-2019</x:v>
+        <x:v>audi-rs-etron-gt-software-2022</x:v>
       </x:c>
       <x:c r="C58" s="9" t="str">
-        <x:v>2019-2024 | Audi | Q8</x:v>
+        <x:v>2022-2022 | Audi | RS e-tron GT</x:v>
       </x:c>
       <x:c r="D58" s="9" t="str">
-        <x:v>2019-2024 Q8 Starter-Alternator Service Action 27BQ - Check VIN</x:v>
+        <x:v>2022 RS e-tron GT Audi connect Inoperative after 91DZ - TSB 2068824/2</x:v>
       </x:c>
       <x:c r="E58" s="9" t="str">
-        <x:v>Check the VIN and current campaign status with an Audi dealer. If 27BQ is open, the dealer follows the campaign procedure and replaces the starter-alternator at no cost when directed. If the action is not open, use Audi guided diagnostics: current bulletins distinguish a replacement result from sensor and CAN faults that replacement will not fix. Do not buy a 12V battery, charger or starter from this card.</x:v>
+        <x:v>Confirm that the failure began after 91DZ and matches the Audi connect/SOS-LED condition. An Audi technician should use ODIS Guided Fault Finding and run SVM Check Module Configuration for diagnostic address 0019, J533. Manual coding is no longer required. Escalate a continuing Audi connect failure through Audi support after the guided coding procedure rather than buying hardware or a retail software service.</x:v>
       </x:c>
       <x:c r="F58" s="9" t="n">
         <x:v>0</x:v>
@@ -11244,21 +14016,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" ht="422.3999938964844" hidden="0" customHeight="1">
+    <x:row r="59" ht="937.2000122070312" hidden="0" customHeight="1">
       <x:c r="A59" s="40" t="n">
         <x:v>58</x:v>
       </x:c>
       <x:c r="B59" s="9" t="str">
-        <x:v>audi-q8-8-speed-tiptronic-harsh-shifting-jolt-delayed-engagement</x:v>
+        <x:v>audi-rs-etron-gt-tire-wear-2022</x:v>
       </x:c>
       <x:c r="C59" s="9" t="str">
-        <x:v>2019-2023 | Audi | Q8 | Q8 55 TFSI, SQ8, RS Q8, 50 TDI</x:v>
+        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
       </x:c>
       <x:c r="D59" s="9" t="str">
-        <x:v>8-Speed Tiptronic Harsh Shifting, Jolt and Delayed Engagement</x:v>
+        <x:v>Accelerated Tire Wear and Alignment Sensitivity</x:v>
       </x:c>
       <x:c r="E59" s="9" t="str">
-        <x:v>Perform a full ZF 8HP transmission fluid and filter (pan) service with the correct Audi-spec fluid, then run the gearbox adaptation/relearn procedure. Update the transmission control module software if a TSB applies. Inspect transmission and engine mounts and replace if collapsed.</x:v>
+        <x:v>Rotate front-to-back every 3,000-5,000 miles (only possible if sizes permit, which staggered setups often do not). Check alignment every 5,000 miles or after any pothole impact - even 0.1 degree of toe deviation causes rapid edge wear on these wide tires. Consider switching to Michelin Pilot Sport 4S or Pirelli P Zero PZ4 for improved tread life over the OE Continental SportContact 6. Budget $1,400-$2,000 for a set of four replacement tires. Aggressive driving with launch control dramatically reduces tire life. For better longevity, use Comfort mode instead of Dynamic for daily driving.</x:v>
       </x:c>
       <x:c r="F59" s="9" t="n">
         <x:v>0</x:v>
@@ -11272,13 +14044,13 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B60" s="9" t="str">
-        <x:v>audi-q8-air-suspension-2019</x:v>
+        <x:v>audi-rs-q8-air-suspension-2020</x:v>
       </x:c>
       <x:c r="C60" s="9" t="str">
-        <x:v>2019-2025 | Audi | Q8</x:v>
+        <x:v>2020-2025 | Audi | RS Q8</x:v>
       </x:c>
       <x:c r="D60" s="9" t="str">
-        <x:v>2019-2025 Q8 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
+        <x:v>2020-2025 RS Q8 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
       </x:c>
       <x:c r="E60" s="9" t="str">
         <x:v>Inspect the wiring and connector contacts between J775 and J1135 before replacing a component. For a first passive or sporadic occurrence, clear the fault and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after wiring inspection, Audi directs replacement of J1135 under current repair and parts information. Do not buy struts, springs, a compressor or a conversion kit solely from this warning.</x:v>
@@ -11290,21 +14062,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="607.2000122070312" hidden="0" customHeight="1">
+    <x:row r="61" ht="184.8000030517578" hidden="0" customHeight="1">
       <x:c r="A61" s="40" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="B61" s="9" t="str">
-        <x:v>audi-q8-carbon-buildup-2019</x:v>
+        <x:v>audi-rs3-carbon-buildup-2017</x:v>
       </x:c>
       <x:c r="C61" s="9" t="str">
-        <x:v>2019-2023 | Audi | Q8</x:v>
+        <x:v>2017-2025 | Audi | RS3 | 2.5T</x:v>
       </x:c>
       <x:c r="D61" s="9" t="str">
-        <x:v>Severe Carbon Buildup on Intake Valves (3.0T)</x:v>
+        <x:v>2.5T Five-Cylinder Carbon Buildup</x:v>
       </x:c>
       <x:c r="E61" s="9" t="str">
-        <x:v>WALNUT BLASTING: Remove intake manifold and blast walnut shells through intake ports ($900-$1,500). Requires specialized equipment. Repeat every 60,000 miles as PREVENTIVE maintenance. PREVENTION: Install catch can ($400-$600) to filter PCV vapors—extends interval to 100k+ miles. Add Liqui Moly Intake Valve Cleaner to every oil change. Change oil every 5,000 miles.</x:v>
+        <x:v>Walnut blast intake valves every 30,000-40,000 miles. Install catch can immediately on new vehicles.</x:v>
       </x:c>
       <x:c r="F61" s="9" t="n">
         <x:v>0</x:v>
@@ -11313,21 +14085,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="62" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A62" s="40" t="n">
         <x:v>61</x:v>
       </x:c>
       <x:c r="B62" s="9" t="str">
-        <x:v>audi-q8-e-tron-brake-pedal-to-booster-pushrod-screw-joint-detachment</x:v>
+        <x:v>audi-rs3-dsg-transmission-2015</x:v>
       </x:c>
       <x:c r="C62" s="9" t="str">
-        <x:v>2023-2024 | Audi | Q8 e-tron</x:v>
+        <x:v>2023-2023 | Audi | RS3</x:v>
       </x:c>
       <x:c r="D62" s="9" t="str">
-        <x:v>2023-2024 Audi Q8 e-tron Brake-Pedal Recall 46P7 / NHTSA 26V240</x:v>
+        <x:v>2023 RS3 TCM Software Emissions Recall 37P3 - VIN Check Required</x:v>
       </x:c>
       <x:c r="E62" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. Dealers inspect and tighten the brake-booster pushrod screw joint as necessary at no charge. If the brake pedal makes an unusual noise, fails to return or feels abnormal, do not continue driving; contact Audi for recovery and follow the owner’s manual emergency-braking instructions.</x:v>
+        <x:v>Ask an Audi dealer to check whether Emissions Recall 37P3 is currently open for the VIN in Elsa. When open, the dealer updates the transmission-control-module software under the campaign; the published remedy requires no parts. Diagnose and repair the underlying fault separately before expecting its stored entry or MIL to clear. Do not buy a mechatronic unit, clutch pack, filter or upgraded DQ500 part for this software campaign.</x:v>
       </x:c>
       <x:c r="F62" s="9" t="n">
         <x:v>0</x:v>
@@ -11336,21 +14108,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" ht="594" hidden="0" customHeight="1">
+    <x:row r="63" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A63" s="40" t="n">
         <x:v>62</x:v>
       </x:c>
       <x:c r="B63" s="9" t="str">
-        <x:v>audi-q8-e-tron-dc-fast-charging-handshake-timeout-failure-to-initiate-sessi</x:v>
+        <x:v>audi-rs3-hpfp-2017</x:v>
       </x:c>
       <x:c r="C63" s="9" t="str">
-        <x:v>2023-2024 | Audi | Q8 e-tron</x:v>
+        <x:v>2017-2023 | Audi | RS3</x:v>
       </x:c>
       <x:c r="D63" s="9" t="str">
-        <x:v>2023-2024 Audi Q8 e-tron Plug &amp; Charge TSB 2071345/1</x:v>
+        <x:v>2017-2020 / 2022-2023 RS3 Drive-System Warning or No-Start Diagnosis - TSB 2067757/3</x:v>
       </x:c>
       <x:c r="E63" s="9" t="str">
-        <x:v>Confirm that the failure repeats at the same station, AC charging works and U15AF00 symptom 2097297 is present. Temporarily disable Plug &amp; Charge in the MMI or use another compatible charging station. Do not replace vehicle charging hardware solely from this symptom; follow current Audi guidance if the failure also occurs with Plug &amp; Charge disabled or at multiple stations.</x:v>
+        <x:v>Reproduce and document the complaint, scan the vehicle with current ODIS and complete Guided Fault Finding. When one of the listed DTC/symptom combinations is stored but GFF produces no result, manually add and complete the G265 intermediate-shaft-speed-sensor test plan. Repair only the component identified by that diagnosis. Do not replace or upgrade the high-pressure fuel pump from this warning or DTC set alone.</x:v>
       </x:c>
       <x:c r="F63" s="9" t="n">
         <x:v>0</x:v>
@@ -11359,21 +14131,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="488.3999938964844" hidden="0" customHeight="1">
+    <x:row r="64" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A64" s="40" t="n">
         <x:v>63</x:v>
       </x:c>
       <x:c r="B64" s="9" t="str">
-        <x:v>audi-q8-e-tron-front-passenger-occupant-detection-system-deactivates-airbag</x:v>
+        <x:v>audi-rs3-magnetic-ride-2017</x:v>
       </x:c>
       <x:c r="C64" s="9" t="str">
-        <x:v>2024-2024 | Audi | Q8 e-tron</x:v>
+        <x:v>2015-2019 | Audi | RS3</x:v>
       </x:c>
       <x:c r="D64" s="9" t="str">
-        <x:v>2024 Audi Q8 e-tron Passenger-Airbag Recall 69GU / NHTSA 24V251</x:v>
+        <x:v>2015-2018 / Certain 2019 RS3 Magnetic-Ride Rear Shock Noise - TSB 2059240/1</x:v>
       </x:c>
       <x:c r="E64" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. The free remedy replaces the passenger-seat occupant-detection control module. If the passenger-airbag warning or AIRBAG OFF indicator behaves unexpectedly, avoid using that seat until Audi inspects it. Do not buy an ODS module from this summary.</x:v>
+        <x:v>Confirm magnetic-ride equipment, the exact model-year/VIN boundary and that the noise originates at the rear shock absorbers. When every bulletin criterion matches, replace both rear shock absorbers according to Audi workshop instructions and order the correct units by VIN. Do not replace dampers or convert the suspension from visible residue, ride feel or noise alone without this diagnosis.</x:v>
       </x:c>
       <x:c r="F64" s="9" t="n">
         <x:v>0</x:v>
@@ -11382,21 +14154,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="65" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A65" s="40" t="n">
         <x:v>64</x:v>
       </x:c>
       <x:c r="B65" s="9" t="str">
-        <x:v>audi-q8-e-tron-over-torqued-brake-pressure-line-failure-fluid-leak</x:v>
+        <x:v>audi-rs3-ttrs-carbon-buildup-2015</x:v>
       </x:c>
       <x:c r="C65" s="9" t="str">
-        <x:v>2024-2024 | Audi | Q8 e-tron</x:v>
+        <x:v>2015-2023 | Audi | RS3 | 2.5T EA855</x:v>
       </x:c>
       <x:c r="D65" s="9" t="str">
-        <x:v>2024 Audi Q8 e-tron Brake-Line Recall 47DE / NHTSA 24V428</x:v>
+        <x:v>Severe Carbon Buildup on Intake Valves (2.5T 5-Cylinder)</x:v>
       </x:c>
       <x:c r="E65" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. Dealers inspect and replace the brake-pressure line when necessary at no charge. If the brake warning appears, pedal travel increases or fluid is visible, stop driving and arrange recovery.</x:v>
+        <x:v>WALNUT BLASTING: Remove intake manifold and blast walnut shells through intake ports ($800-$1,500). Repeat every 30,000-40,000 miles—MORE frequent than base models due to high performance. PREVENTION: Install catch can ($400-$700) to filter PCV vapors. Add Liqui Moly Intake Valve Cleaner to every oil change. Change oil every 5,000 miles. Drive car hard regularly—Audi's own recommendation to burn off carbon.</x:v>
       </x:c>
       <x:c r="F65" s="9" t="n">
         <x:v>0</x:v>
@@ -11405,21 +14177,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="66" ht="792" hidden="0" customHeight="1">
       <x:c r="A66" s="40" t="n">
         <x:v>65</x:v>
       </x:c>
       <x:c r="B66" s="9" t="str">
-        <x:v>audi-q8-e-tron-panoramic-glass-roof-water-leak-into-cabin</x:v>
+        <x:v>audi-rs3-ttrs-injector-failure-2015</x:v>
       </x:c>
       <x:c r="C66" s="9" t="str">
-        <x:v>2023-2024 | Audi | Q8 e-tron | Q8 e-tron (panoramic roof equipped), Q8 Sportback e-tron</x:v>
+        <x:v>2015-2023 | Audi | RS3 | EA855</x:v>
       </x:c>
       <x:c r="D66" s="9" t="str">
-        <x:v>Panoramic Glass Roof Water Leak into Cabin (TSB MC-10182485-0001)</x:v>
+        <x:v>Fuel Injector Failure and "Torch Effect" (2.5T)</x:v>
       </x:c>
       <x:c r="E66" s="9" t="str">
-        <x:v>Have the dealer diagnose per the panoramic roof TSB. Repair depends on the root cause: clear or re-route clogged/pinched drain tubes, correct a pinched-shut rear drain, or replace/reseal the cracked plastic water channel. Dry out and inspect saturated carpet/underlay to prevent mold and electrical corrosion. Audi performs the repair reactively (only after water ingress is confirmed); some owners report the factory fix failing and needing a second visit.</x:v>
+        <x:v>PREVENTIVE REPLACEMENT: Replace all fuel injectors every 60,000 km (37,000 miles) with OEM Audi injectors ($1,500-$2,500 installed). If engine misfires or runs rough: Inspect injectors IMMEDIATELY—do NOT continue driving. Failed injector can destroy engine in minutes. If piston is melted: Engine replacement required ($15,000-$25,000). Consider extended warranty or aftermarket warranty for out-of-warranty RS3/TT RS. This is the most serious reliability issue with the 2.5T engine.</x:v>
       </x:c>
       <x:c r="F66" s="9" t="n">
         <x:v>0</x:v>
@@ -11428,21 +14200,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="67" ht="937.2000122070312" hidden="0" customHeight="1">
       <x:c r="A67" s="40" t="n">
         <x:v>66</x:v>
       </x:c>
       <x:c r="B67" s="9" t="str">
-        <x:v>audi-q8-e-tron-premature-brake-pad-rotor-wear-brake-vibration-pulsation</x:v>
+        <x:v>audi-rs4-b7-carbon-buildup-2007</x:v>
       </x:c>
       <x:c r="C67" s="9" t="str">
-        <x:v>2023-2024 | Audi | Q8 e-tron | Q8 e-tron, Q8 Sportback e-tron, SQ8 e-tron</x:v>
+        <x:v>2007-2008 | Audi | RS4 | 4.2L FSI V8</x:v>
       </x:c>
       <x:c r="D67" s="9" t="str">
-        <x:v>Premature Brake Pad/Rotor Wear and Brake Vibration/Pulsation</x:v>
+        <x:v>2007-2008 RS4 Deposit-Related Cold-Start Misfire - Diagnose Before Cleaning</x:v>
       </x:c>
       <x:c r="E67" s="9" t="str">
-        <x:v>Have a dealer or independent measure rotor runout/thickness variation and machine or replace rotors with correct torque and bedding-in. Verify pad hardware and caliper slides. Using a stronger regenerative-braking setting reduces friction-brake duty and corrosion. If vibration returns shortly after a full brake job, escalate for a deeper inspection of hubs/wheel bearings and calibration.</x:v>
+        <x:v>Have the cold-start event and stored faults diagnosed before authorizing intake cleaning. The B7 RS4 bulletin first checks whether its fuel-additive and follow-up procedure resolves injector-deposit misfires. Current TSB 2014753/13 warns that gasoline additive can clean FSI injectors and combustion chambers but not FSI intake valves. If the misfire remains, the shop should continue guided diagnosis and confirm inlet-valve deposits before using the applicable mechanical-cleaning procedure. Do not buy a scanner, oil bundle or cleaning service solely from this card.</x:v>
       </x:c>
       <x:c r="F67" s="9" t="n">
         <x:v>0</x:v>
@@ -11451,21 +14223,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" ht="303.6000061035156" hidden="0" customHeight="1">
+    <x:row r="68" ht="963.5999755859375" hidden="0" customHeight="1">
       <x:c r="A68" s="40" t="n">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B68" s="9" t="str">
-        <x:v>audi-q8-e-tron-rearview-camera-image-fails-is-delayed-when-shifting-to-reve</x:v>
+        <x:v>audi-rs4-rs5-carbon-buildup-2018</x:v>
       </x:c>
       <x:c r="C68" s="9" t="str">
-        <x:v>2023-2024 | Audi | Q8 e-tron</x:v>
+        <x:v>2018-2023 | Audi | RS4 | 2.9T</x:v>
       </x:c>
       <x:c r="D68" s="9" t="str">
-        <x:v>2023-2024 Audi Q8 e-tron Camera Recall 90TV / NHTSA 25V900</x:v>
+        <x:v>2018-2023 RS4 2.9T Cold-Start Misfire from Confirmed Inlet Deposits</x:v>
       </x:c>
       <x:c r="E68" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. Dealers update the software at no charge. Until completed, use mirrors and direct observation with extra care while reversing.</x:v>
+        <x:v>Confirm the cold-start complaint, review the engine-control-unit event memory and verify inlet-port or inlet-valve deposits before cleaning. When that condition is confirmed, Audi TSB 2075530/1 directs the shop to remove the intake manifold or compressor and clean the inlet valves and ports by walnut blasting; the cylinder head remains installed. The cited Audi guidance does not support a mandatory 60,000-mile interval, a fixed price, dual catch cans, additive at every oil change, a 5,000-mile oil interval or a drive-hard prescription. Do not buy a catch can or cleaning product solely from this card.</x:v>
       </x:c>
       <x:c r="F68" s="9" t="n">
         <x:v>0</x:v>
@@ -11474,21 +14246,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="69" ht="1227.5999755859375" hidden="0" customHeight="1">
       <x:c r="A69" s="40" t="n">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B69" s="9" t="str">
-        <x:v>audi-q8-e-tron-severe-cold-weather-range-loss-reduced-dc-charge-speed</x:v>
+        <x:v>audi-rs5-b8-carbon-buildup-2013</x:v>
       </x:c>
       <x:c r="C69" s="9" t="str">
-        <x:v>2023-2024 | Audi | Q8 e-tron | Q8 e-tron, Q8 Sportback e-tron, SQ8 e-tron</x:v>
+        <x:v>2013-2015 | Audi | RS5 | 4.2L V8</x:v>
       </x:c>
       <x:c r="D69" s="9" t="str">
-        <x:v>Severe Cold-Weather Range Loss and Reduced DC Charge Speed (Cold Battery)</x:v>
+        <x:v>4.2L V8 Carbon Buildup and High-Rev Issues</x:v>
       </x:c>
       <x:c r="E69" s="9" t="str">
-        <x:v>Use route-based battery preconditioning: enter the DC fast charger as a navigation destination so the car warms the pack en route, restoring charge speed. Precondition the cabin while still plugged in at home, use seat/steering heaters over cabin heat, and rely on Level 2 home charging (40-60A) to absorb seasonal losses overnight. No repair is needed unless range/charge limits persist in mild weather, which warrants a dealer battery-health check.</x:v>
+        <x:v>Confirm carbon buildup by scanning for misfire/fuel-trim faults, reviewing live data, and inspecting the intake valves with a borescope after removing the intake manifold. The proper repair is an intake-valve carbon cleaning service—typically walnut-shell blasting or manual chemical cleaning—while replacing the intake manifold gaskets, injector seals/O-rings, and PCV-related breather components if leaking or contributing to oil vapor. After reassembly, clear adaptations, perform a throttle-body/basic setting relearn, and road test to verify restored high-RPM pull and smooth idle. Independent shops typically charge about $800-$1,500 for a carbon clean on the 4.2 FSI V8, while dealer pricing can run roughly $1,500-$2,500 depending on how many seals and ancillary parts are replaced.</x:v>
       </x:c>
       <x:c r="F69" s="9" t="n">
         <x:v>0</x:v>
@@ -11497,21 +14269,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" ht="660" hidden="0" customHeight="1">
+    <x:row r="70" ht="1122" hidden="0" customHeight="1">
       <x:c r="A70" s="40" t="n">
         <x:v>69</x:v>
       </x:c>
       <x:c r="B70" s="9" t="str">
-        <x:v>audi-q8-ea839-3-0t-water-pump-internal-leak-coolant-loss</x:v>
+        <x:v>audi-rs5-carbon-buildup-2018</x:v>
       </x:c>
       <x:c r="C70" s="9" t="str">
-        <x:v>2019-2024 | Audi | Q8 | V6 TFSI</x:v>
+        <x:v>2018-2026 | Audi | RS5</x:v>
       </x:c>
       <x:c r="D70" s="9" t="str">
-        <x:v>2019-2024 Q8 V6 Coolant-Pump Leak Diagnosis - TSB 2070349/4</x:v>
+        <x:v>Direct Injection Carbon Buildup on Intake Valves</x:v>
       </x:c>
       <x:c r="E70" s="9" t="str">
-        <x:v>Have the suspected area cleaned and dried, fill the cooling system correctly, inspect at idle and up to about 2,500 rpm, and pressure-test it per Audi repair information. If no leak returns, continue to observe without replacing parts. Replace only the component proven to leak and inspect the vacuum path and N649 when P0299 is present. Do not order a pump from this card without confirmation.</x:v>
+        <x:v>Confirm intake-valve carbon buildup by scanning for misfire faults, reviewing fuel trims, and inspecting the intake valves with a borescope through the intake ports after removing the intake manifold. The proper repair is an intake-valve cleaning service, typically walnut-shell blasting each intake port with the valves closed, then replacing the intake manifold gaskets and any disturbed PCV or breather seals before clearing adaptations and road-testing. If misfires persist, inspect and replace worn spark plugs or ignition coils as needed, since heavy deposits can foul plugs and mimic ignition faults. Typical cost is about $800-$1,500 depending on labor rates and how much disassembly is required.</x:v>
       </x:c>
       <x:c r="F70" s="9" t="n">
         <x:v>0</x:v>
@@ -11520,21 +14292,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="382.79998779296875" hidden="0" customHeight="1">
+    <x:row r="71" ht="1003.2000122070312" hidden="0" customHeight="1">
       <x:c r="A71" s="40" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="B71" s="9" t="str">
-        <x:v>audi-q8-etron-12v-battery-drain-2023</x:v>
+        <x:v>audi-rs5-turbo-coolant-2018</x:v>
       </x:c>
       <x:c r="C71" s="9" t="str">
-        <x:v>2023-2025 | Audi | Q8 e-tron</x:v>
+        <x:v>2021-2024 | Audi | RS5 | 2.9L V6 TFSI</x:v>
       </x:c>
       <x:c r="D71" s="9" t="str">
-        <x:v>12V Auxiliary Battery Excessive Drain</x:v>
+        <x:v>2021-2024 RS5 V6 Coolant-Pump Leak Diagnosis - TSB 2070349/4</x:v>
       </x:c>
       <x:c r="E71" s="9" t="str">
-        <x:v>Update vehicle software to latest version via dealer. If drain persists, have dealer perform parasitic draw test to identify module staying awake. 12V battery replacement with AGM type may be needed if battery was deeply discharged.</x:v>
+        <x:v>Locate the leak before replacing parts. Clean and dry the area, fill the cooling system to maximum, inspect at idle and at engine speeds up to about 2,500 rpm, and perform the Workshop Manual cooling-system leak test. If no further leak is detected, continue observation without replacing parts. If a leak recurs, replace only the component or components causing the leak and document the finding with clear photos or video; a pump-leak repair also requires a photo of the pump production date. Inspect the vacuum circuit and N649 when contamination or P0299 is present, following current Audi workshop and parts information.</x:v>
       </x:c>
       <x:c r="F71" s="9" t="n">
         <x:v>0</x:v>
@@ -11543,21 +14315,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="501.6000061035156" hidden="0" customHeight="1">
+    <x:row r="72" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A72" s="40" t="n">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B72" s="9" t="str">
-        <x:v>audi-q8-etron-12v-battery-drain-2024</x:v>
+        <x:v>audi-rs6-air-suspension-2020</x:v>
       </x:c>
       <x:c r="C72" s="9" t="str">
-        <x:v>2024-2026 | Audi | Q8 e-tron | Premium, Premium Plus, Prestige, Sportback Premium, Sportback Premium Plus, Sportback Prestige | Electric</x:v>
+        <x:v>2021-2024 | Audi | RS6</x:v>
       </x:c>
       <x:c r="D72" s="9" t="str">
-        <x:v>12V Auxiliary Battery Parasitic Drain</x:v>
+        <x:v>2021-2024 RS6 Air-Suspension Warning - Check C1260F0 or U112100</x:v>
       </x:c>
       <x:c r="E72" s="9" t="str">
-        <x:v>Update the vehicle software to the latest version which includes revised module sleep timing. If the 12V battery has been deeply discharged multiple times, it may need replacement as lead-acid batteries are damaged by deep discharge cycles. Connect a 12V trickle charger if the vehicle will sit for more than a week.</x:v>
+        <x:v>Have the wiring and connector contacts between suspension controller J775 and compressor controller J1135 inspected first. Audi says to clear a first passive or sporadic occurrence and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after the wiring check, the bulletin directs replacement of J1135 under the applicable service procedure. Do not replace air struts, a compressor or an unverified aftermarket assembly solely from this warning card.</x:v>
       </x:c>
       <x:c r="F72" s="9" t="n">
         <x:v>0</x:v>
@@ -11566,21 +14338,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" ht="462" hidden="0" customHeight="1">
+    <x:row r="73" ht="831.5999755859375" hidden="0" customHeight="1">
       <x:c r="A73" s="40" t="n">
         <x:v>72</x:v>
       </x:c>
       <x:c r="B73" s="9" t="str">
-        <x:v>audi-q8-etron-charge-port-actuator-2024</x:v>
+        <x:v>audi-rs6-carbon-buildup-2020</x:v>
       </x:c>
       <x:c r="C73" s="9" t="str">
-        <x:v>2024-2026 | Audi | Q8 e-tron | Premium, Premium Plus, Prestige, Sportback Premium, Sportback Premium Plus, Sportback Prestige | Electric</x:v>
+        <x:v>2021-2024 | Audi | RS6 | 4.0T V8</x:v>
       </x:c>
       <x:c r="D73" s="9" t="str">
-        <x:v>Charge Port Door Actuator and Locking Mechanism Failure</x:v>
+        <x:v>2021-2024 RS6 4.0T Cold-Start Misfire from Confirmed Inlet Deposits</x:v>
       </x:c>
       <x:c r="E73" s="9" t="str">
-        <x:v>Replace the charge port door actuator and/or latch mechanism. In an emergency, there is a manual cable release in the cargo area to free a stuck charging cable. The actuator replacement is a straightforward repair that can be done by an independent shop if comfortable with the charge port housing.</x:v>
+        <x:v>Confirm the cold-start complaint, review the engine-control-unit event memory and verify inlet-port or inlet-valve deposits before cleaning. When that condition is confirmed, Audi TSB 2075530/1 directs the shop to remove the intake manifold or compressor and clean the inlet valves and ports by walnut blasting; the cylinder head remains installed. The cited Audi guidance does not specify a 30,000-40,000-mile interval, a fixed price or a mandatory catch can. Do not buy a catch can or cleaning product solely from this card.</x:v>
       </x:c>
       <x:c r="F73" s="9" t="n">
         <x:v>0</x:v>
@@ -11589,21 +14361,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="316.79998779296875" hidden="0" customHeight="1">
+    <x:row r="74" ht="528" hidden="0" customHeight="1">
       <x:c r="A74" s="40" t="n">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B74" s="9" t="str">
-        <x:v>audi-q8-etron-charge-port-lid-2023</x:v>
+        <x:v>audi-rs6-rs7-carbon-buildup-2013</x:v>
       </x:c>
       <x:c r="C74" s="9" t="str">
-        <x:v>2023-2025 | Audi | Q8 e-tron</x:v>
+        <x:v>2013-2023 | Audi | RS6 | 4.0T V8</x:v>
       </x:c>
       <x:c r="D74" s="9" t="str">
-        <x:v>Charge Port Door Actuator Failure</x:v>
+        <x:v>Severe Carbon Buildup on Intake Valves (4.0T V8)</x:v>
       </x:c>
       <x:c r="E74" s="9" t="str">
-        <x:v>Replace charge port door actuator assembly. Check for debris or ice in the mechanism. Software update may improve actuator control logic. Manual release is accessible from inside the cargo area.</x:v>
+        <x:v>WALNUT BLASTING: Remove both intake manifolds and blast walnut shells through all intake ports ($1,200-$2,000 for V8). Repeat every 60,000 miles. PREVENTION: Install catch can ($500-$800 for twin-turbo setup). Add Liqui Moly Intake Valve Cleaner to every oil change. Change oil every 5,000 miles. Drive car hard regularly.</x:v>
       </x:c>
       <x:c r="F74" s="9" t="n">
         <x:v>0</x:v>
@@ -11617,16 +14389,16 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B75" s="9" t="str">
-        <x:v>audi-q8-etron-hvac-compressor-2024</x:v>
+        <x:v>audi-rs6-rs7-motor-mounts-2013</x:v>
       </x:c>
       <x:c r="C75" s="9" t="str">
-        <x:v>2024-2024 | Audi | Q8 e-tron</x:v>
+        <x:v>2013-2023 | Audi | RS6 | 4.0T V8</x:v>
       </x:c>
       <x:c r="D75" s="9" t="str">
-        <x:v>2024 Audi Q8 e-tron A/C Compressor-Area Noise TSB 2063467/6</x:v>
+        <x:v>Premature Motor Mount Failure (4.0T V8)</x:v>
       </x:c>
       <x:c r="E75" s="9" t="str">
-        <x:v>Reproduce the exact noise with the A/C compressor active and confirm that it stops when A/C is switched off. Inspect the bulletin’s refrigerant-line contact points and hood-release cable clip and perform only the branch that matches the confirmed contact. Diagnose non-reproducible noise or loss of heating/cooling separately; do not buy a battery, maintainer or portable EVSE from this card.</x:v>
+        <x:v>Replace failed motor mounts with OEM or upgraded mounts ($800-$1,500 for all mounts). Upgraded aftermarket mounts (034 Motorsport, ECS) offer better durability for high-torque engines ($400-$600 per mount). If you drive aggressively or track the car, consider upgrading to performance mounts preventively. Monitor for vibrations and clunking—early replacement prevents driveline damage.</x:v>
       </x:c>
       <x:c r="F75" s="9" t="n">
         <x:v>0</x:v>
@@ -11635,21 +14407,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="76" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A76" s="40" t="n">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B76" s="9" t="str">
-        <x:v>audi-q8-front-brake-rotor-corrosion-premature-pad-rotor-wear</x:v>
+        <x:v>audi-rs7-air-suspension-2014</x:v>
       </x:c>
       <x:c r="C76" s="9" t="str">
-        <x:v>2019-2024 | Audi | Q8</x:v>
+        <x:v>2021-2025 | Audi | RS7</x:v>
       </x:c>
       <x:c r="D76" s="9" t="str">
-        <x:v>Front Brake Rotor Corrosion and Premature Pad/Rotor Wear</x:v>
+        <x:v>2021-2025 RS7 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
       </x:c>
       <x:c r="E76" s="9" t="str">
-        <x:v>For light surface rust, normal braking usually clears it; for noise, refinish or replace rotors and fit OEM-spec pads with proper bedding-in. Apply high-temp anti-seize/lubricant on contact points and ensure caliper slides move freely. Replace warped or deeply corroded rotors in axle sets.</x:v>
+        <x:v>Inspect the wiring and connectors between J775 and J1135 before replacing a component. For a first passive/sporadic occurrence, clear the fault and release the vehicle. If the fault is active/static after wiring and connector inspection, or the same passive/sporadic fault returns a second time, replace J1135 using current Audi repair and parts information. Audi notes that improved J1135 software remains under development.</x:v>
       </x:c>
       <x:c r="F76" s="9" t="n">
         <x:v>0</x:v>
@@ -11658,21 +14430,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" ht="422.3999938964844" hidden="0" customHeight="1">
+    <x:row r="77" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A77" s="40" t="n">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B77" s="9" t="str">
-        <x:v>audi-q8-front-shock-absorber-fork-cracking</x:v>
+        <x:v>audi-rs7-carbon-buildup-2014</x:v>
       </x:c>
       <x:c r="C77" s="9" t="str">
-        <x:v>2019-2019 | Audi | Q8</x:v>
+        <x:v>2014-2026 | Audi | RS7 | 4.0T</x:v>
       </x:c>
       <x:c r="D77" s="9" t="str">
-        <x:v>2019 Q8 Front Shock-Absorber Fork Recall 40O4 (19V114) - Check VIN</x:v>
+        <x:v>4.0T Carbon Deposit Accumulation</x:v>
       </x:c>
       <x:c r="E77" s="9" t="str">
-        <x:v>Check the VIN for open recall 40O4 with Audi or NHTSA and contact an authorized Audi dealer. The dealer replaces the affected front shock-absorber fork free of charge. Do not buy a fork from this card or assume a generic suspension noise proves the recall condition.</x:v>
+        <x:v>Walnut blast every 30,000-40,000 miles. Install dual catch can setup for both turbo sides.</x:v>
       </x:c>
       <x:c r="F77" s="9" t="n">
         <x:v>0</x:v>
@@ -11681,21 +14453,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" ht="422.3999938964844" hidden="0" customHeight="1">
+    <x:row r="78" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A78" s="40" t="n">
         <x:v>77</x:v>
       </x:c>
       <x:c r="B78" s="9" t="str">
-        <x:v>audi-q8-fuel-pump-internal-failure-causing-engine-stall</x:v>
+        <x:v>audi-rs7-turbo-coolant-2014</x:v>
       </x:c>
       <x:c r="C78" s="9" t="str">
-        <x:v>2019-2021 | Audi | Q8 | V6</x:v>
+        <x:v>2014-2026 | Audi | RS7 | 4.0T</x:v>
       </x:c>
       <x:c r="D78" s="9" t="str">
-        <x:v>2019-2021 Q8 V6 Fuel-Delivery-Module Recall 20DR (22V516)</x:v>
+        <x:v>4.0T Twin-Turbo Coolant System Degradation</x:v>
       </x:c>
       <x:c r="E78" s="9" t="str">
-        <x:v>Check the VIN for open recall 20DR and contact an authorized Audi dealer. The recall remedy replaces the fuel-delivery module with the improved version. Do not purchase the old or improved module from this card or attempt an in-tank repair based only on the model year.</x:v>
+        <x:v>Replace turbo coolant lines proactively at 50,000 miles. Upgrade to silicone lines where possible.</x:v>
       </x:c>
       <x:c r="F78" s="9" t="n">
         <x:v>0</x:v>
@@ -11704,21 +14476,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" ht="356.3999938964844" hidden="0" customHeight="1">
+    <x:row r="79" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A79" s="40" t="n">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B79" s="9" t="str">
-        <x:v>audi-q8-mmi-electrical-2019</x:v>
+        <x:v>audi-rs7-turbo-wastegate-2014</x:v>
       </x:c>
       <x:c r="C79" s="9" t="str">
-        <x:v>2019-2023 | Audi | Q8</x:v>
+        <x:v>2014-2017 | Audi | RS7 | 4.0L TFSI twin-turbo V8</x:v>
       </x:c>
       <x:c r="D79" s="9" t="str">
-        <x:v>MMI Infotainment and Electrical Issues</x:v>
+        <x:v>2014-2017 RS7 Turbocharger Oil-Strainer Safety Recall 21H7 / 22V178 - Check VIN</x:v>
       </x:c>
       <x:c r="E79" s="9" t="str">
-        <x:v>MMI hard reset (hold power + volume up 10 seconds). If persistent, dealer software update ($150-$300). For severe cases: MMI replacement ($2,000-$3,500). Most covered under 4-year/50k warranty.</x:v>
+        <x:v>Check the VIN for open Audi campaign 21H7 in Elsa or the NHTSA recall lookup. The authorized dealer replaces the turbocharger oil strainer, changes the engine oil and filter, and performs the campaign scan-tool turbo/boost-system check at no charge. Follow the campaign procedure for any damage found; do not buy a turbocharger, actuator or gasket kit from this card.</x:v>
       </x:c>
       <x:c r="F79" s="9" t="n">
         <x:v>0</x:v>
@@ -11727,21 +14499,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" ht="488.3999938964844" hidden="0" customHeight="1">
+    <x:row r="80" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A80" s="40" t="n">
         <x:v>79</x:v>
       </x:c>
       <x:c r="B80" s="9" t="str">
-        <x:v>audi-q8-mmi-infotainment-2019</x:v>
+        <x:v>audi-rsq8-4.0t-coolant-2020</x:v>
       </x:c>
       <x:c r="C80" s="9" t="str">
-        <x:v>2019-2026 | Audi | Q8</x:v>
+        <x:v>2020-2021 | Audi | RS Q8 | 4.0T V8</x:v>
       </x:c>
       <x:c r="D80" s="9" t="str">
-        <x:v>2019-2026 Q8 Rearview-Camera Software Recall 90TV (25V900)</x:v>
+        <x:v>2020-Early 2021 RS Q8 Red Coolant Warning - Check G407 per TSB 2062951/4</x:v>
       </x:c>
       <x:c r="E80" s="9" t="str">
-        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers install more robust driver-assistance software free of charge. Until repaired, use extra caution when reversing. A hard reset, scan tool, relay, multimeter or temporary image recovery is not completion of the recall.</x:v>
+        <x:v>Have the vehicle checked with Audi Guided Fault Finding and inspect G407 and its O-ring. Replace G407 only if the O-ring is damaged or pinched and the diagnosis matches the bulletin; follow the related Audi diagnostic path if additional listed faults are stored. Do not replace turbo coolant hoses, pumps or other cooling parts from this card alone.</x:v>
       </x:c>
       <x:c r="F80" s="9" t="n">
         <x:v>0</x:v>
@@ -11750,21 +14522,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="382.79998779296875" hidden="0" customHeight="1">
+    <x:row r="81" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A81" s="40" t="n">
         <x:v>80</x:v>
       </x:c>
       <x:c r="B81" s="9" t="str">
-        <x:v>audi-q8-oil-separator-pcv-valve-failure-elevated-oil-consumption</x:v>
+        <x:v>audi-rsq8-air-suspension-2020</x:v>
       </x:c>
       <x:c r="C81" s="9" t="str">
-        <x:v>2019-2023 | Audi | Q8 | 3.0L V6 TFSI (EA839)</x:v>
+        <x:v>2020-2026 | Audi | RS Q8</x:v>
       </x:c>
       <x:c r="D81" s="9" t="str">
-        <x:v>Oil Separator / PCV Valve Failure and Elevated Oil Consumption (3.0T)</x:v>
+        <x:v>Adaptive Air Suspension Failure Under SUV Weight</x:v>
       </x:c>
       <x:c r="E81" s="9" t="str">
-        <x:v>Replace the cracked oil separator / PCV valve assembly with the updated part, inspect the intake and spark plugs for oil fouling, and reseal the intake manifold. Monitor oil level between services; perform a consumption test if usage exceeds Audi's threshold.</x:v>
+        <x:v>Replace air struts as they fail. Budget for compressor replacement. Consider heavy-duty aftermarket options designed for the RS Q8 weight.</x:v>
       </x:c>
       <x:c r="F81" s="9" t="n">
         <x:v>0</x:v>
@@ -11773,22 +14545,20 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="607.2000122070312" hidden="0" customHeight="1">
+    <x:row r="82" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A82" s="40" t="n">
         <x:v>81</x:v>
       </x:c>
       <x:c r="B82" s="9" t="str">
-        <x:v>audi-q8-panoramic-sunroof-water-leak-into-cabin</x:v>
+        <x:v>audi-rsq8-air-suspension-leak-2020</x:v>
       </x:c>
       <x:c r="C82" s="9" t="str">
-        <x:v>2019-2021 | Audi | Q8</x:v>
+        <x:v>2020-2026 | Audi | RS Q8</x:v>
       </x:c>
       <x:c r="D82" s="9" t="str">
-        <x:v>2019-2021 Q8 Water Entry from Sunroof Area - TSB 2056944/10</x:v>
-      </x:c>
-      <x:c r="E82" s="9" t="str">
-        <x:v>Have all four bulletin branches inspected and water-flow tested. Clear a drain obstruction or replace a damaged hose or valve, replace a damaged opening seal, correct glass adjustment, and perform the specified wind-deflector and channel modifications when applicable. Replace the sunroof frame only when actual structural damage is found. Do not order a frame from this card.</x:v>
-      </x:c>
+        <x:v>Adaptive Air Suspension Air Spring Leaks</x:v>
+      </x:c>
+      <x:c r="E82" s="9" t="str"/>
       <x:c r="F82" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -11796,21 +14566,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="752.4000244140625" hidden="0" customHeight="1">
+    <x:row r="83" ht="607.2000122070312" hidden="0" customHeight="1">
       <x:c r="A83" s="40" t="n">
         <x:v>82</x:v>
       </x:c>
       <x:c r="B83" s="9" t="str">
-        <x:v>audi-r8-5-2-v10-excessive-oil-consumption</x:v>
+        <x:v>audi-rsq8-brake-wear-2020</x:v>
       </x:c>
       <x:c r="C83" s="9" t="str">
-        <x:v>2009-2023 | Audi | R8 | 5.2L V10 FSI</x:v>
+        <x:v>2020-2021 | Audi | RS Q8</x:v>
       </x:c>
       <x:c r="D83" s="9" t="str">
-        <x:v>5.2 V10 Excessive Oil Consumption</x:v>
+        <x:v>2020-2021 RS Q8 Front Steel-Brake Squeal - TSB 2062052/1</x:v>
       </x:c>
       <x:c r="E83" s="9" t="str">
-        <x:v>Establish a documented consumption baseline (measured quarts over measured miles) and inspect the plugs/exhaust for oil fouling. Use a manufacturer-approved oil of the correct viscosity (owners report fewer issues with a quality 502/505-approved synthetic); some go to a heavier grade only with caution. Truly excessive consumption with smoke requires teardown for rings/valve seals, an engine-out job. Keep the oil topped between changes to protect the engine.</x:v>
+        <x:v>Confirm the frequency and operating conditions and inspect the discs for corrosion, grooves or glazing. When the bulletin applies, Audi directs replacement of the front pad set using current parts information followed by the specified bedding procedure. Do not perform ABS stops for bedding, and do not replace rotors or buy aftermarket pads solely from the prior wear narrative.</x:v>
       </x:c>
       <x:c r="F83" s="9" t="n">
         <x:v>0</x:v>
@@ -11819,21 +14589,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="726" hidden="0" customHeight="1">
+    <x:row r="84" ht="897.5999755859375" hidden="0" customHeight="1">
       <x:c r="A84" s="40" t="n">
         <x:v>83</x:v>
       </x:c>
       <x:c r="B84" s="9" t="str">
-        <x:v>audi-r8-5-2-v10-oil-pump-driveshaft-seal-timing-case-oil-leak</x:v>
+        <x:v>audi-s3-carbon-buildup-2015</x:v>
       </x:c>
       <x:c r="C84" s="9" t="str">
-        <x:v>2009-2023 | Audi | R8 | R8 V10, R8 V10 Plus, R8 V10 Performance, R8 V10 Spyder | 5.2L V10 FSI</x:v>
+        <x:v>2015-2019 | Audi | S3 | S3 | EA888 Gen 3</x:v>
       </x:c>
       <x:c r="D84" s="9" t="str">
-        <x:v>5.2 V10 Oil Pump Driveshaft Seal Timing-Case Oil Leak</x:v>
+        <x:v>Carbon Buildup on Intake Valves (Pre-Dual Injection EA888 Gen 3)</x:v>
       </x:c>
       <x:c r="E84" s="9" t="str">
-        <x:v>Confirm the source (timing-case oil-pump driveshaft seal, not valve covers or oil cooler). Repair involves removing the oil pump and renewing the oil-pump drive-shaft seal and associated O-rings/gaskets; a full reseal kit (e.g. RKX/Steso) is commonly used. It is mostly a labor and gasket/seal job rather than replacing the pump, though the pump can be replaced if worn. Fresh oil and coolant and a proper fill/bleed are required because both systems are opened.</x:v>
+        <x:v>WALNUT BLASTING: Remove intake manifold and blast intake valve ports with crushed walnut shells ($500-$1,000). Repeat every 40,000-60,000 miles. CATCH CAN: Install an oil catch can ($200-$400) to capture PCV vapors before they reach intake valves—significantly slows carbon buildup. OIL CHANGES: Use high-quality synthetic oil and change every 5,000 miles. DRIVING HABITS: Regular spirited driving helps burn off some deposits. NOTE: 2020+ S3 models with EA888 Gen 3B dual injection are largely immune to this issue.</x:v>
       </x:c>
       <x:c r="F84" s="9" t="n">
         <x:v>0</x:v>
@@ -11842,44 +14612,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="1042.800048828125" hidden="0" customHeight="1">
+    <x:row r="85" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A85" s="40" t="n">
         <x:v>84</x:v>
       </x:c>
       <x:c r="B85" s="9" t="str">
-        <x:v>audi-r8-ac-compressor-v8-2008</x:v>
+        <x:v>audi-s3-dq250-mechatronic-2015</x:v>
       </x:c>
       <x:c r="C85" s="9" t="str">
-        <x:v>2008-2012 | Audi | R8 | 4.2 | 4.2 V8</x:v>
+        <x:v>2015-2024 | Audi | S3</x:v>
       </x:c>
       <x:c r="D85" s="9" t="str">
-        <x:v>A/C Compressor Failure Requiring Engine-Out Repair (4.2 V8)</x:v>
+        <x:v>DQ250 DSG Mechatronic Unit Failure</x:v>
       </x:c>
       <x:c r="E85" s="9" t="str">
-        <x:v>A/C COMPRESSOR REPLACEMENT: Requires ENGINE REMOVAL on the V8 model. Total repair cost $5,000-$8,000 ($1,000-$1,500 for parts, $4,000-$6,500 for labor). When the engine is out, strongly recommended to also address: motor mounts, clutch inspection, and any other components that benefit from engine-out access. ALTERNATIVE: Some specialty R8 shops have developed methods to access the compressor with partial disassembly (removing subframe) rather than full engine removal, potentially reducing labor to $3,000-$4,000. PREVENTION: Run the A/C regularly (even in winter for 5-10 minutes monthly) to keep compressor seals lubricated.</x:v>
+        <x:v>Replace or rebuild mechatronic unit. Regular DSG fluid changes every 40,000 miles help prevent premature failure.</x:v>
       </x:c>
       <x:c r="F85" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G85" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" ht="976.7999877929688" hidden="0" customHeight="1">
+    <x:row r="86" ht="897.5999755859375" hidden="0" customHeight="1">
       <x:c r="A86" s="40" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="B86" s="9" t="str">
-        <x:v>audi-r8-carbon-buildup-2008</x:v>
+        <x:v>audi-s3-dsg-mechatronic-2015</x:v>
       </x:c>
       <x:c r="C86" s="9" t="str">
-        <x:v>2008-2015 | Audi | R8 | 4.2, 5.2 | 4.2 FSI V8, 5.2 FSI V10</x:v>
+        <x:v>2015-2024 | Audi | S3 | S3</x:v>
       </x:c>
       <x:c r="D86" s="9" t="str">
-        <x:v>Carbon Buildup on Intake Valves (4.2 V8 FSI and 5.2 V10 FSI)</x:v>
+        <x:v>DQ381 S-Tronic Mechatronic Unit Failure</x:v>
       </x:c>
       <x:c r="E86" s="9" t="str">
-        <x:v>WALNUT BLASTING: Remove intake manifolds and blast all intake ports with walnut shells. V8 (4.2L): $800-$1,200. V10 (5.2L): $1,200-$2,000 due to 10 cylinders. Perform a leak-down test BEFORE walnut blasting to ensure intake valves seat properly. Repeat every 50,000-70,000 miles. CHEMICAL CLEANING: Less effective than walnut blasting but some owners use intake valve cleaners (BG Products, CRC) as interim maintenance. DRIVING HABITS: Regular high-RPM driving (the R8's natural habitat) helps slow carbon accumulation. PREVENTION: Use quality fuel (91+ octane) and change oil every 5,000 miles.</x:v>
+        <x:v>EARLY SYMPTOMS (jerky shifts): DSG fluid and filter service ($500-$700) plus dealer software update. This may resolve early-stage issues. MECHATRONIC FAILURE: Replace mechatronic unit ($2,000-$4,000 installed) plus TCU coding. Remanufactured units available for $1,500-$2,500. CLUTCH PACK FAILURE: Replace dual clutch pack ($3,000-$5,000). PREVENTION: Service DSG fluid every 40,000 miles—ignore Audi's 'lifetime fill' claim. Use ONLY OEM Audi DSG fluid (G 052 182 A2) or approved Pentosin FFL-2. Avoid aggressive launches and excessive clutch slip in traffic.</x:v>
       </x:c>
       <x:c r="F86" s="9" t="n">
         <x:v>0</x:v>
@@ -11888,21 +14658,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="87" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A87" s="40" t="n">
         <x:v>86</x:v>
       </x:c>
       <x:c r="B87" s="9" t="str">
-        <x:v>audi-r8-carbon-fiber-sideblade-trim-clear-coat-peeling</x:v>
+        <x:v>audi-s3-ea888-carbon-2015</x:v>
       </x:c>
       <x:c r="C87" s="9" t="str">
-        <x:v>2008-2015 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+        <x:v>2015-2024 | Audi | S3 | EA888</x:v>
       </x:c>
       <x:c r="D87" s="9" t="str">
-        <x:v>Carbon Fiber Sideblade and Trim Clear-Coat Peeling</x:v>
+        <x:v>EA888 Carbon Buildup on Intake Valves</x:v>
       </x:c>
       <x:c r="E87" s="9" t="str">
-        <x:v>Refinish the affected panel: carefully sand back the failed lacquer without cutting into the carbon weave, then re-clear with a UV-stabilized automotive clear coat (best done by a shop experienced with carbon). To prevent recurrence, protect the finish with paint-protection film (clear wrap) or a ceramic coating, which also guards against stone chips.</x:v>
+        <x:v>Walnut blast intake valves every 40,000-60,000 miles or install a catch can to reduce buildup rate.</x:v>
       </x:c>
       <x:c r="F87" s="9" t="n">
         <x:v>0</x:v>
@@ -11911,21 +14681,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="88" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A88" s="40" t="n">
         <x:v>87</x:v>
       </x:c>
       <x:c r="B88" s="9" t="str">
-        <x:v>audi-r8-catalytic-converter-failure-requiring-engine-out-replacement</x:v>
+        <x:v>audi-s3-hpfp-2015</x:v>
       </x:c>
       <x:c r="C88" s="9" t="str">
-        <x:v>2008-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+        <x:v>2015-2024 | Audi | S3 | EA888</x:v>
       </x:c>
       <x:c r="D88" s="9" t="str">
-        <x:v>Catalytic Converter Failure Requiring Engine-Out Replacement</x:v>
+        <x:v>High-Pressure Fuel Pump (HPFP) Failure</x:v>
       </x:c>
       <x:c r="E88" s="9" t="str">
-        <x:v>Confirm the failed bank with O2/catalyst-efficiency data and a back-pressure check before condemning. OEM repair means replacing the catalytic-converter-with-integrated-manifold assembly (engine-out labor); many owners opt for high-flow aftermarket or de-catted manifolds where legal. Verify no upstream misfire/oil-consumption issue is destroying the new cats.</x:v>
+        <x:v>Replace HPFP with updated revision. Check cam follower for wear during replacement.</x:v>
       </x:c>
       <x:c r="F88" s="9" t="n">
         <x:v>0</x:v>
@@ -11934,21 +14704,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="422.3999938964844" hidden="0" customHeight="1">
+    <x:row r="89" ht="1122" hidden="0" customHeight="1">
       <x:c r="A89" s="40" t="n">
         <x:v>88</x:v>
       </x:c>
       <x:c r="B89" s="9" t="str">
-        <x:v>audi-r8-clutch-pack-2008</x:v>
+        <x:v>audi-s3-turbo-wastegate-rattle-2015</x:v>
       </x:c>
       <x:c r="C89" s="9" t="str">
-        <x:v>2021-2022 | Audi | R8</x:v>
+        <x:v>2015-2020 | Audi | S3 | S3</x:v>
       </x:c>
       <x:c r="D89" s="9" t="str">
-        <x:v>Gearbox Underfilled: Clutch Slippage or Transmission-Oil Leak (Recall 22V225 / 37O1)</x:v>
+        <x:v>IS20 Turbocharger Wastegate Rattle and Actuator Failure</x:v>
       </x:c>
       <x:c r="E89" s="9" t="str">
-        <x:v>Check the VIN and campaign history with Audi or NHTSA. Under campaign 37O1, an Audi dealer inspects and corrects the transmission-oil level free of charge. If drive power drops, a clutch slips, or oil/smoke is noticed, stop safely and arrange dealer inspection.</x:v>
+        <x:v>EARLY STAGE (rattle only, no power loss): Audi TSB 2027585/3 prescribes installation of a metal retaining clip (part 06J145220A) to tighten wastegate arm play ($200-$400 if under warranty, $500-$800 out of pocket). UPGRADED DIVERTER VALVE: Replace with revision 'D' diverter valve to improve boost control. SEVERE (actuator failure or power loss): Replace complete IS20 turbocharger ($2,500-$4,000 installed). The IS20 actuator is integrated and not serviceable separately. Upgraded IS38 turbo swap ($3,500-$5,000) from Golf R is a popular option if replacing turbo anyway. PREVENTION: Avoid short trips that don't fully heat the turbo. Change oil every 5,000 miles with high-quality synthetic.</x:v>
       </x:c>
       <x:c r="F89" s="9" t="n">
         <x:v>0</x:v>
@@ -11957,21 +14727,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" ht="1042.800048828125" hidden="0" customHeight="1">
+    <x:row r="90" ht="594" hidden="0" customHeight="1">
       <x:c r="A90" s="40" t="n">
         <x:v>89</x:v>
       </x:c>
       <x:c r="B90" s="9" t="str">
-        <x:v>audi-r8-clutch-wear-2008</x:v>
+        <x:v>audi-s3-water-pump-thermostat-2015</x:v>
       </x:c>
       <x:c r="C90" s="9" t="str">
-        <x:v>2008-2015 | Audi | R8 | 4.2, 5.2</x:v>
+        <x:v>2020-2024 | Audi | S3 | 2.0L TFSI</x:v>
       </x:c>
       <x:c r="D90" s="9" t="str">
-        <x:v>R-Tronic Clutch Premature Wear and Expensive Replacement</x:v>
+        <x:v>2020/2022-2024 Audi S3 2.0 TFSI Coolant-Pump Leak Diagnosis</x:v>
       </x:c>
       <x:c r="E90" s="9" t="str">
-        <x:v>CLUTCH REPLACEMENT: Replace clutch disc, pressure plate, throwout bearing, and resurface/replace flywheel ($5,500-$9,000 at dealer, $4,000-$6,000 at independent specialist). The mid-engine layout requires dropping the transmission—8-12 hours of labor. DRIVING TECHNIQUE: Minimize R-Tronic slip by avoiding creeping in traffic (use brake hold instead). Use manual mode in stop-and-go traffic. Avoid reverse on steep inclines. For TRACK USE: Budget for clutch replacement every 10,000-20,000 miles—R-Tronic track driving is hard on clutches. ALTERNATIVE: S-Tronic (Gen 2 R8) wet dual-clutch is significantly more durable for daily driving.</x:v>
+        <x:v>Document the suspected leak, clean and dry all traces, fill the cooling system to the correct level and reassess after driving a few miles. If no fresh leak appears, continue observing without replacing parts. If leakage recurs, replace only the component causing the damage under the exact VIN, engine and part criteria. Outside applicable warranty, Audi states the bulletin is informational.</x:v>
       </x:c>
       <x:c r="F90" s="9" t="n">
         <x:v>0</x:v>
@@ -11980,21 +14750,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="91" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A91" s="40" t="n">
         <x:v>90</x:v>
       </x:c>
       <x:c r="B91" s="9" t="str">
-        <x:v>audi-r8-coolant-expansion-tank-cracking-cooling-system-leaks</x:v>
+        <x:v>audi-s4-b5-timing-chain-2000</x:v>
       </x:c>
       <x:c r="C91" s="9" t="str">
-        <x:v>2008-2015 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+        <x:v>2000-2002 | Audi | S4</x:v>
       </x:c>
       <x:c r="D91" s="9" t="str">
-        <x:v>Coolant Expansion Tank Cracking and Cooling System Leaks</x:v>
+        <x:v>Driver Airbag Inflator May Deploy Improperly (Recall 21V470 / 69CJ)</x:v>
       </x:c>
       <x:c r="E91" s="9" t="str">
-        <x:v>Pressure-test the cooling system to pinpoint the leak. Replace the cracked expansion/overflow tank with the updated design and renew brittle hose clamps/connections; inspect the radiator and cap. Refill with the correct Audi G13/G12 coolant specification and bleed the system fully. Address any weeping hose fittings at the same time.</x:v>
+        <x:v>Check the VIN with Audi or NHTSA. Audi dealers replace the driver frontal-airbag inflator with an alternative inflator free of charge under campaign 69CJ.</x:v>
       </x:c>
       <x:c r="F91" s="9" t="n">
         <x:v>0</x:v>
@@ -12003,21 +14773,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="92" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A92" s="40" t="n">
         <x:v>91</x:v>
       </x:c>
       <x:c r="B92" s="9" t="str">
-        <x:v>audi-r8-direct-injection-fuel-injector-failure</x:v>
+        <x:v>audi-s4-b5-turbo-failure-2000</x:v>
       </x:c>
       <x:c r="C92" s="9" t="str">
-        <x:v>2008-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+        <x:v>2003-2004 | Audi | S4</x:v>
       </x:c>
       <x:c r="D92" s="9" t="str">
-        <x:v>Direct-Injection Fuel Injector Failure</x:v>
+        <x:v>Xenon Headlamp Reflector Coating Can Reduce Light Output (Recall 05V096)</x:v>
       </x:c>
       <x:c r="E92" s="9" t="str">
-        <x:v>Confirm the failing cylinder with misfire and fuel-trim data and, where possible, injector-specific fault codes rather than replacing coils blindly. Replace the failed injector(s) with OEM FSI units; many owners replace as a bank or full set given shared age and mileage, and clean or address intake-valve carbon at the same service. Expect roughly $2,900 for a multi-injector job including labor per owner reports.</x:v>
+        <x:v>Verify VIN eligibility and campaign completion with Audi. Dealers replace both xenon headlamp reflectors free of charge under recall 05V096.</x:v>
       </x:c>
       <x:c r="F92" s="9" t="n">
         <x:v>0</x:v>
@@ -12026,21 +14796,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="528" hidden="0" customHeight="1">
+    <x:row r="93" ht="303.6000061035156" hidden="0" customHeight="1">
       <x:c r="A93" s="40" t="n">
         <x:v>92</x:v>
       </x:c>
       <x:c r="B93" s="9" t="str">
-        <x:v>audi-r8-front-axle-hydraulic-lift-system-pump-failure</x:v>
+        <x:v>audi-s4-b6-timing-chain-2004</x:v>
       </x:c>
       <x:c r="C93" s="9" t="str">
-        <x:v>2017-2023 | Audi | R8 | 5.2L V10 FSI</x:v>
+        <x:v>2005-2009 | Audi | S4</x:v>
       </x:c>
       <x:c r="D93" s="9" t="str">
-        <x:v>Front Axle Hydraulic Lift System Pump Failure</x:v>
+        <x:v>Passenger Airbag Inflator Can Rupture (Recall 18V427 / 69R7)</x:v>
       </x:c>
       <x:c r="E93" s="9" t="str">
-        <x:v>Diagnose the lift pump/hydraulic circuit; a failed pump is the usual culprit. A new dealer pump assembly runs over $3,000, so many owners fit a good used OEM pump or an independent rebuild as a cost-effective alternative. Until repaired, approach inclines and speed bumps at an angle and very slowly to avoid front-end damage.</x:v>
+        <x:v>Check VIN eligibility because body style and original registration history affect scope. Audi dealers replace the passenger frontal-airbag remedy part free of charge under campaign 69R7.</x:v>
       </x:c>
       <x:c r="F93" s="9" t="n">
         <x:v>0</x:v>
@@ -12049,21 +14819,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="316.79998779296875" hidden="0" customHeight="1">
+    <x:row r="94" ht="356.3999938964844" hidden="0" customHeight="1">
       <x:c r="A94" s="40" t="n">
         <x:v>93</x:v>
       </x:c>
       <x:c r="B94" s="9" t="str">
-        <x:v>audi-r8-front-passenger-airbag-inflator-rupture</x:v>
+        <x:v>audi-s4-carbon-buildup-2010</x:v>
       </x:c>
       <x:c r="C94" s="9" t="str">
-        <x:v>2016-2016 | Audi | R8</x:v>
+        <x:v>2011-2012 | Audi | S4 | 3.0 TFSI</x:v>
       </x:c>
       <x:c r="D94" s="9" t="str">
-        <x:v>Front-Passenger Airbag Module May Explode or Deploy Improperly (Recall 22V543 / 69DY)</x:v>
+        <x:v>Fuel Rail or Seal Leak Creates Fire Risk (Recall 15V019 / 24AP)</x:v>
       </x:c>
       <x:c r="E94" s="9" t="str">
-        <x:v>Check the VIN with Audi or NHTSA. Audi dealers replace the front-passenger airbag module free of charge under campaign 69DY/61C1. Do not source a used airbag module from this summary.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel rails and corresponding seals free of charge under campaign 24AP. If fuel odor or leakage is present, stop driving and arrange immediate inspection.</x:v>
       </x:c>
       <x:c r="F94" s="9" t="n">
         <x:v>0</x:v>
@@ -12072,21 +14842,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="95" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A95" s="40" t="n">
         <x:v>94</x:v>
       </x:c>
       <x:c r="B95" s="9" t="str">
-        <x:v>audi-r8-fuel-supply-line-chafing-heat-shield</x:v>
+        <x:v>audi-s4-supercharger-nose-2010</x:v>
       </x:c>
       <x:c r="C95" s="9" t="str">
-        <x:v>2011-2012 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+        <x:v>2013-2015 | Audi | S4</x:v>
       </x:c>
       <x:c r="D95" s="9" t="str">
-        <x:v>R8 Spyder Fuel Supply Line Can Chafe on Heat Shield (Recall 11V390 / 20Q8)</x:v>
+        <x:v>Airbag-Control Software May Miss Front-Airbag Deployment After a Second Impact (Recall 14V667 / 69K5)</x:v>
       </x:c>
       <x:c r="E95" s="9" t="str">
-        <x:v>Check the VIN and recall status. Audi dealers inspect the line, replace it if damaged, and adjust the fuel line and heat shield for proper clearance free of charge. If fuel odor or leakage is present, stop driving and arrange immediate inspection.</x:v>
+        <x:v>Check VIN eligibility and completion history. Audi dealers update the airbag control-unit software free of charge under campaign 69K5.</x:v>
       </x:c>
       <x:c r="F95" s="9" t="n">
         <x:v>0</x:v>
@@ -12095,21 +14865,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" ht="792" hidden="0" customHeight="1">
+    <x:row r="96" ht="198" hidden="0" customHeight="1">
       <x:c r="A96" s="40" t="n">
         <x:v>95</x:v>
       </x:c>
       <x:c r="B96" s="9" t="str">
-        <x:v>audi-r8-ignition-coil-pack-failure-causing-misfires</x:v>
+        <x:v>audi-s4-thermostat-2010</x:v>
       </x:c>
       <x:c r="C96" s="9" t="str">
-        <x:v>2008-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+        <x:v>2010-2025 | Audi | S4 | 3.0T</x:v>
       </x:c>
       <x:c r="D96" s="9" t="str">
-        <x:v>Ignition Coil Pack Failure Causing Misfires</x:v>
+        <x:v>Thermostat Housing Failure and Coolant Leak</x:v>
       </x:c>
       <x:c r="E96" s="9" t="str">
-        <x:v>Diagnose the misfiring cylinder(s) via the stored misfire counters, then replace the failed coil(s) along with spark plugs; most specialists replace the full set of 8 (V8) or 10 (V10) plus plugs to avoid repeat visits. The canonical 4.2 V8 coil is the revision-'T' red coil, Audi/VW PN 077905115T (superseded family, aftermarket cross-reference 06E905115E). The Gen-2 5.2 V10 uses Audi PN 07L905115B. Address any valve-cover or plug-tube oil leak at the same time so new coils are not contaminated.</x:v>
+        <x:v>Replace thermostat housing assembly with updated part. Use OEM or quality aftermarket housing with metal reinforcement.</x:v>
       </x:c>
       <x:c r="F96" s="9" t="n">
         <x:v>1</x:v>
@@ -12118,21 +14888,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="97" ht="963.5999755859375" hidden="0" customHeight="1">
       <x:c r="A97" s="40" t="n">
         <x:v>96</x:v>
       </x:c>
       <x:c r="B97" s="9" t="str">
-        <x:v>audi-r8-led-headlight-drl-module-failure-flickering</x:v>
+        <x:v>audi-s5-b9-water-pump-2018</x:v>
       </x:c>
       <x:c r="C97" s="9" t="str">
-        <x:v>2014-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+        <x:v>2018-2018 | Audi | S5 | 3.0L V6 TFSI EA839</x:v>
       </x:c>
       <x:c r="D97" s="9" t="str">
-        <x:v>LED Headlight / DRL Module Failure and Flickering</x:v>
+        <x:v>2018 S5 3.0L Mechanical Coolant-Pump Fault P000000/33688 - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E97" s="9" t="str">
-        <x:v>Inspect the headlight for moisture and corroded connectors; a failed LED driver module usually requires replacing the headlight assembly (used units run roughly £1,600-1,800, new from Audi around £2,800), followed by headlight aiming/auto-leveling calibration with a diagnostic tool. Reseal or replace cracked housings to stop repeat water damage. Some independent specialists can repair the driver board at lower cost.</x:v>
+        <x:v>Follow the bulletin in order. Verify coolant level; if low, inspect the cooling system for a leak and repair only the identified source or top up per Audi instructions when no leak is found. Check the ECM software level and apply the specified SVM update only when required. If the concern returns or software is current, test vacuum at N649 and inspect the solenoid and hoses. If the vacuum system works, apply vacuum to the pump hose and verify that the pump sleeve clicks; replace the mechanical coolant pump only when the sleeve does not operate. Use current Audi workshop and parts information.</x:v>
       </x:c>
       <x:c r="F97" s="9" t="n">
         <x:v>0</x:v>
@@ -12141,21 +14911,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" ht="264" hidden="0" customHeight="1">
+    <x:row r="98" ht="184.8000030517578" hidden="0" customHeight="1">
       <x:c r="A98" s="40" t="n">
         <x:v>97</x:v>
       </x:c>
       <x:c r="B98" s="9" t="str">
-        <x:v>audi-r8-magnetic-ride-2008</x:v>
+        <x:v>audi-s5-carbon-buildup-2008</x:v>
       </x:c>
       <x:c r="C98" s="9" t="str">
-        <x:v>2008-2024 | Audi | R8</x:v>
+        <x:v>2008-2025 | Audi | S5</x:v>
       </x:c>
       <x:c r="D98" s="9" t="str">
-        <x:v>Magnetic Ride Damper Fluid Leaks</x:v>
+        <x:v>Direct Injection Carbon Buildup</x:v>
       </x:c>
       <x:c r="E98" s="9" t="str">
-        <x:v>Replace magnetic ride dampers. OEM replacements are very expensive. KW or Bilstein aftermarket coilovers are popular track-oriented alternatives.</x:v>
+        <x:v>Walnut blast intake valves every 40,000-60,000 miles. Install oil catch can to reduce oil vapor reaching valves.</x:v>
       </x:c>
       <x:c r="F98" s="9" t="n">
         <x:v>0</x:v>
@@ -12164,44 +14934,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="1227.5999755859375" hidden="0" customHeight="1">
+    <x:row r="99" ht="937.2000122070312" hidden="0" customHeight="1">
       <x:c r="A99" s="40" t="n">
         <x:v>98</x:v>
       </x:c>
       <x:c r="B99" s="9" t="str">
-        <x:v>audi-r8-magnetic-ride-leak-2008</x:v>
+        <x:v>audi-s5-crankshaft-pulley-2010</x:v>
       </x:c>
       <x:c r="C99" s="9" t="str">
-        <x:v>2008-2015 | Audi | R8 | 4.2, 5.2</x:v>
+        <x:v>2010-2017 | Audi | S5 | Premium Plus, Prestige | 3.0T</x:v>
       </x:c>
       <x:c r="D99" s="9" t="str">
-        <x:v>Magnetic Ride Suspension Damper Leak and Premature Failure</x:v>
+        <x:v>Crankshaft Pulley (Harmonic Balancer) Failure (3.0T)</x:v>
       </x:c>
       <x:c r="E99" s="9" t="str">
-        <x:v>OEM REPLACEMENT: Replace leaking magnetic ride shocks ($1,800 each, $5,100-$8,000+ for full set installed). OEM replacements use the same technology and will eventually fail again. REFURBISHED OPTION: Refurbished magnetic ride dampers from specialty rebuilders (approximately $1,000-$1,400 each). PASSIVE CONVERSION: Convert to R8 Plus passive shocks ($3,000-$4,000 for set—less than 2 OEM magnetic ride shocks) or aftermarket coilovers ($2,500-$5,000 for quality kit like KW, JRZ, or Ohlins). Passive conversion eliminates the failure mode permanently but removes adaptive ride control. PREVENTION: Limited—magnetic fluid degradation is inherent to the technology. Budget for replacement every 30,000-50,000 miles if keeping magnetic ride.</x:v>
+        <x:v>Replace crankshaft pulley/harmonic balancer with LATEST REVISION (revision F or later) part ($300-$600 for part, $800-$1,700 with labor). This is NOT a DIY-friendly repair—requires specialized holding tools and precise torque. If belts are damaged, replace serpentine belt and tensioner ($200-$400 additional). INSPECT: Check for collateral damage to supercharger snout, idler pulleys, and timing. If timing was affected, expect $3,000-$5,000 additional repair. PREVENTIVE: Inspect pulley for wobble at every oil change. Consider preemptive replacement at 80,000 miles on 2010-2013 models.</x:v>
       </x:c>
       <x:c r="F99" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G99" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="1003.2000122070312" hidden="0" customHeight="1">
+    <x:row r="100" ht="844.7999877929688" hidden="0" customHeight="1">
       <x:c r="A100" s="40" t="n">
         <x:v>99</x:v>
       </x:c>
       <x:c r="B100" s="9" t="str">
-        <x:v>audi-r8-r-tronic-hydraulic-pump-pressure-accumulator-failure</x:v>
+        <x:v>audi-s5-pcv-valve-failure-2010</x:v>
       </x:c>
       <x:c r="C100" s="9" t="str">
-        <x:v>2008-2015 | Audi | R8 | R8 4.2 R tronic, R8 V10 R tronic, R8 V10 Plus R tronic | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+        <x:v>2010-2017 | Audi | S5 | 3.0L supercharged V6</x:v>
       </x:c>
       <x:c r="D100" s="9" t="str">
-        <x:v>R tronic Hydraulic Pump and Pressure Accumulator Failure</x:v>
+        <x:v>2010-2017 S5 3.0L Crankcase-Breather P052E00 - Body/Year Diagnosis</x:v>
       </x:c>
       <x:c r="E100" s="9" t="str">
-        <x:v>Diagnose with a scan tool: a failing accumulator/pump typically stores P17BF (hydraulic pump play protection) and/or P0944 (loss of hydraulic pressure). Standard repair order is to renew the relatively inexpensive pressure accumulator first; if pressure loss persists, replace the hydraulic pump (and its relay/fuse), and only then suspect the hydraulic clutch/gear actuator or the solenoid-valve O-rings. Fresh, correct-spec hydraulic fluid and a proper bleed with a diagnostic tool are required. Owners are advised not to drive the car (except directly to a shop) once the pump is heard running continuously or shifting becomes intermittent.</x:v>
+        <x:v>Verify the body style, model year and P052E00 condition first. For the applicable membrane branch, use the specified hand-vacuum test, then inspect the membrane and metal plates after compressor/intake-manifold removal; replace only the faulted membrane/plate repair kit or crankcase breather per current Audi instructions. If testing identifies the elbow branch, replace the elbow and hose clip as directed by TSB 2060259/1. Do not assume that both branches or unrelated cooling parts require replacement.</x:v>
       </x:c>
       <x:c r="F100" s="9" t="n">
         <x:v>0</x:v>
@@ -12210,21 +14980,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="198" hidden="0" customHeight="1">
+    <x:row r="101" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A101" s="40" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="B101" s="9" t="str">
-        <x:v>audi-r8-s-tronic-actuator-2008</x:v>
+        <x:v>audi-s5-supercharger-2008</x:v>
       </x:c>
       <x:c r="C101" s="9" t="str">
-        <x:v>2008-2024 | Audi | R8</x:v>
+        <x:v>2008-2025 | Audi | S5 | 3.0T</x:v>
       </x:c>
       <x:c r="D101" s="9" t="str">
-        <x:v>S-tronic Transmission Actuator Failure</x:v>
+        <x:v>3.0T Supercharger Intercooler Pump Failure</x:v>
       </x:c>
       <x:c r="E101" s="9" t="str">
-        <x:v>Replace S-tronic actuators. Full transmission service with correct S-tronic fluid is critical. Dealer or specialist only repair.</x:v>
+        <x:v>Replace intercooler coolant pump. Check intercooler lines for leaks and flush the circuit during replacement.</x:v>
       </x:c>
       <x:c r="F101" s="9" t="n">
         <x:v>0</x:v>
@@ -12233,21 +15003,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="330" hidden="0" customHeight="1">
+    <x:row r="102" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A102" s="40" t="n">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B102" s="9" t="str">
-        <x:v>audi-r8-s-tronic-gearbox-ventilation-hose-transmission-fluid-leak</x:v>
+        <x:v>audi-s5-thermostat-2008</x:v>
       </x:c>
       <x:c r="C102" s="9" t="str">
-        <x:v>2017-2018 | Audi | R8 | 5.2L V10 FSI</x:v>
+        <x:v>2008-2025 | Audi | S5 | 3.0T</x:v>
       </x:c>
       <x:c r="D102" s="9" t="str">
-        <x:v>Gearbox Ventilation Hose Can Leak Fluid Near Hot Engine Parts (Recall 18V639 / 34J1)</x:v>
+        <x:v>Thermostat and Water Pump Assembly Failure</x:v>
       </x:c>
       <x:c r="E102" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the single gearbox ventilation hose with the higher-volume double hose free of charge under campaign 34J1. Stop driving if hot-oil odor or smoke appears.</x:v>
+        <x:v>Replace thermostat/water pump assembly. Upgrade to revised housing if available.</x:v>
       </x:c>
       <x:c r="F102" s="9" t="n">
         <x:v>0</x:v>
@@ -12256,21 +15026,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="103" ht="818.4000244140625" hidden="0" customHeight="1">
       <x:c r="A103" s="40" t="n">
         <x:v>102</x:v>
       </x:c>
       <x:c r="B103" s="9" t="str">
-        <x:v>audi-r8-spyder-convertible-top-hydraulic-pump-failure</x:v>
+        <x:v>audi-s6-air-suspension-2013</x:v>
       </x:c>
       <x:c r="C103" s="9" t="str">
-        <x:v>2011-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+        <x:v>2013-2013 | Audi | S6 | 4.0T</x:v>
       </x:c>
       <x:c r="D103" s="9" t="str">
-        <x:v>Spyder Convertible Top Hydraulic Pump Failure</x:v>
+        <x:v>2013 Audi S6 Air-Suspension Compressor or Relay Fault - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E103" s="9" t="str">
-        <x:v>Scan for the specific fault (pump vs. sensor vs. latch) before parting; a mis-reading position sensor can mimic a dead pump. Replace the hydraulic pump/motor assembly (Audi R8 Spyder convertible-top hydraulic pump PN 427871791 for 2010-2016 cars) and top up/refill the correct hydraulic fluid, or replace the failed cylinder/sensor. Leaking lines and worn seals should be renewed together. Independent hydraulic rebuild services exist as a lower-cost alternative to a full dealer pump.</x:v>
+        <x:v>Have an Audi-qualified technician test the air-suspension compressor and inspect relay J403. Audi directs replacement of both the compressor and relay when the relay has severe contact erosion or an overheated strand; when the compressor sounds normal and the relay has only minor contact marks, replace the relay only. A sagging corner or leak-down condition requires separate leak localization before any strut is replaced. Do not order the former strut or compressor recommendations from this card.</x:v>
       </x:c>
       <x:c r="F103" s="9" t="n">
         <x:v>0</x:v>
@@ -12279,21 +15049,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="1122" hidden="0" customHeight="1">
+    <x:row r="104" ht="1359.5999755859375" hidden="0" customHeight="1">
       <x:c r="A104" s="40" t="n">
         <x:v>103</x:v>
       </x:c>
       <x:c r="B104" s="9" t="str">
-        <x:v>audi-r8-v8-engine-bearing-2008</x:v>
+        <x:v>audi-s6-c7-carbon-buildup-2013</x:v>
       </x:c>
       <x:c r="C104" s="9" t="str">
-        <x:v>2008-2015 | Audi | R8 | 4.2 | 4.2 FSI</x:v>
+        <x:v>2013-2018 | Audi | S6 | 4.0T</x:v>
       </x:c>
       <x:c r="D104" s="9" t="str">
-        <x:v>Rod Bearing Wear and Engine Failure Risk (4.2 V8 FSI)</x:v>
+        <x:v>4.0T Carbon Buildup on Intake Valves</x:v>
       </x:c>
       <x:c r="E104" s="9" t="str">
-        <x:v>EARLY DETECTION (knocking noise only): Rod bearing replacement ($2,000-$5,000). Must be caught EARLY before bearing material migrates through oil system. Cut open every oil filter at oil change to inspect for metallic debris. CATASTROPHIC FAILURE: Engine replacement ($13,000+ Audi exchange, $8,000-$15,000 rebuilt from AMTuned or specialist rebuilder). ARP 2000 reinforced connecting rod bolts are available as a preventive upgrade during any engine-out service. PREVENTION: Use ONLY premium 5W-40 synthetic oil. Change oil every 5,000 miles maximum. NEVER exceed oil change intervals—the high-revving V8 is extremely sensitive to oil condition. For track use, change oil after every 2-3 track days.</x:v>
+        <x:v>Confirm carbon buildup by scanning for misfire faults (commonly random/multiple or cylinder-specific misfires), reviewing fuel trims, and inspecting the intake valves with a borescope after removing the intake manifold or accessing the ports. The proper repair is an intake valve carbon cleaning, typically walnut shell blasting each intake port with the valves closed, then replacing intake manifold gaskets, injector seals/O-rings or any disturbed PCV-related seals as needed and clearing/adapting the ECU afterward. If buildup is severe or returns quickly, inspect the PCV/oil separator system and crankcase ventilation hoses for excessive oil carryover. Independent shops typically charge about $800-$1,500 for a full walnut blast service on the 4.0T, while dealer pricing can run roughly $1,500-$2,500 depending on labor and gasket/seal replacement.</x:v>
       </x:c>
       <x:c r="F104" s="9" t="n">
         <x:v>0</x:v>
@@ -12302,21 +15072,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="924" hidden="0" customHeight="1">
+    <x:row r="105" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A105" s="40" t="n">
         <x:v>104</x:v>
       </x:c>
       <x:c r="B105" s="9" t="str">
-        <x:v>audi-rs-etron-gt-battery-short-2022</x:v>
+        <x:v>audi-s6-carbon-buildup-2013</x:v>
       </x:c>
       <x:c r="C105" s="9" t="str">
-        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
+        <x:v>2013-2024 | Audi | S6 | 4.0T</x:v>
       </x:c>
       <x:c r="D105" s="9" t="str">
-        <x:v>2022-2024 RS e-tron GT High-Voltage Battery Recall 931A/931B (24V726)</x:v>
+        <x:v>4.0T Direct Injection Carbon Buildup</x:v>
       </x:c>
       <x:c r="E105" s="9" t="str">
-        <x:v>Check the VIN for open Audi campaign 931A or 931B and complete the authorized dealer remedy. Under 931A, enrolled vehicles can be monitored through online battery data; Audi contacts owners if a module appears critical. Under 931B, the dealer performs diagnostic procedures until the final monitoring software is installed. Audi installs the onboard diagnostic software and replaces affected battery modules at no cost when anomalies are identified. Follow any vehicle- or dealer-specific 80-percent charging instruction; the filing does not direct every 931A vehicle to use that limit.</x:v>
+        <x:v>Walnut blast all eight intake runners. Dual-injection models (2019+) are less affected.</x:v>
       </x:c>
       <x:c r="F105" s="9" t="n">
         <x:v>0</x:v>
@@ -12325,21 +15095,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="106" ht="462" hidden="0" customHeight="1">
       <x:c r="A106" s="40" t="n">
         <x:v>105</x:v>
       </x:c>
       <x:c r="B106" s="9" t="str">
-        <x:v>audi-rs-etron-gt-brake-hose-2022</x:v>
+        <x:v>audi-s6-rearview-camera-image-failure-from-software-error</x:v>
       </x:c>
       <x:c r="C106" s="9" t="str">
-        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
+        <x:v>2020-2025 | Audi | S6</x:v>
       </x:c>
       <x:c r="D106" s="9" t="str">
-        <x:v>2022-2024 RS e-tron GT Front Brake-Hose Recall 47UP (24V465)</x:v>
+        <x:v>2020-2025 Audi S6 Rearview Camera Software Recall 25V900 / 90TV</x:v>
       </x:c>
       <x:c r="E106" s="9" t="str">
-        <x:v>Check the VIN for an open 47UP action and have an authorized Audi dealer replace both front brake hoses and holders free of charge. If pedal travel increases or the vehicle displays a warning related to reduced brake fluid, contact an Audi dealer for diagnosis without delay. Do not buy a single hose or substitute generic brake lines from the prior links; the campaign controls the complete criteria-specific repair.</x:v>
+        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install the more robust driver-assistance software update free of charge. Until repaired, use extra caution when reversing and do not treat a restart or temporary image recovery as completion of the recall.</x:v>
       </x:c>
       <x:c r="F106" s="9" t="n">
         <x:v>0</x:v>
@@ -12348,21 +15118,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" ht="726" hidden="0" customHeight="1">
+    <x:row r="107" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A107" s="40" t="n">
         <x:v>106</x:v>
       </x:c>
       <x:c r="B107" s="9" t="str">
-        <x:v>audi-rs-etron-gt-charging-port-2022</x:v>
+        <x:v>audi-s6-takata-passenger-airbag-inflator-recall</x:v>
       </x:c>
       <x:c r="C107" s="9" t="str">
-        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
+        <x:v>2007-2011 | Audi | S6</x:v>
       </x:c>
       <x:c r="D107" s="9" t="str">
-        <x:v>2022-2024 RS e-tron GT Red Charging LED or Fast-Charging Abort - Audi 91VT</x:v>
+        <x:v>2007-2011 Audi S6 Takata Passenger-Airbag Recall 18V427 / 69R7</x:v>
       </x:c>
       <x:c r="E107" s="9" t="str">
-        <x:v>Have an Audi dealer check the VIN and assigned 91VT criterion in the campaign/action system. For the charging-related criteria, the authorized remedy updates the high-voltage battery control-module software, with the convenience-system control module also updated where the assigned criterion requires it. Diagnose charging failures outside that exact campaign branch rather than replacing the charging socket or module from symptoms alone.</x:v>
+        <x:v>Check the VIN for recall 18V427/69R7 and arrange the free final passenger-frontal-airbag replacement with an Audi dealer. Do not use an airbag warning light to determine recall eligibility; Audi states that the warning light is unrelated to this inflator defect.</x:v>
       </x:c>
       <x:c r="F107" s="9" t="n">
         <x:v>0</x:v>
@@ -12371,22 +15141,20 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="108" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A108" s="40" t="n">
         <x:v>107</x:v>
       </x:c>
       <x:c r="B108" s="9" t="str">
-        <x:v>audi-rs-etron-gt-software-2022</x:v>
+        <x:v>audi-s6-transmission-valve-body-2002</x:v>
       </x:c>
       <x:c r="C108" s="9" t="str">
-        <x:v>2022-2022 | Audi | RS e-tron GT</x:v>
+        <x:v>2002-2004 | Audi | S6</x:v>
       </x:c>
       <x:c r="D108" s="9" t="str">
-        <x:v>2022 RS e-tron GT Audi connect Inoperative after 91DZ - TSB 2068824/2</x:v>
-      </x:c>
-      <x:c r="E108" s="9" t="str">
-        <x:v>Confirm that the failure began after 91DZ and matches the Audi connect/SOS-LED condition. An Audi technician should use ODIS Guided Fault Finding and run SVM Check Module Configuration for diagnostic address 0019, J533. Manual coding is no longer required. Escalate a continuing Audi connect failure through Audi support after the guided coding procedure rather than buying hardware or a retail software service.</x:v>
-      </x:c>
+        <x:v>ZF 5HP24 Tiptronic Transmission Valve Body Failure</x:v>
+      </x:c>
+      <x:c r="E108" s="9" t="str"/>
       <x:c r="F108" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -12394,21 +15162,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="109" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A109" s="40" t="n">
         <x:v>108</x:v>
       </x:c>
       <x:c r="B109" s="9" t="str">
-        <x:v>audi-rs-etron-gt-tire-wear-2022</x:v>
+        <x:v>audi-s6-turbo-coolant-2013</x:v>
       </x:c>
       <x:c r="C109" s="9" t="str">
-        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
+        <x:v>2013-2013 | Audi | S6 | 4.0T</x:v>
       </x:c>
       <x:c r="D109" s="9" t="str">
-        <x:v>Accelerated Tire Wear and Alignment Sensitivity</x:v>
+        <x:v>2013 Audi S6 Turbocharger Coolant-Pipe Seepage - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E109" s="9" t="str">
-        <x:v>Rotate front-to-back every 3,000-5,000 miles (only possible if sizes permit, which staggered setups often do not). Check alignment every 5,000 miles or after any pothole impact - even 0.1 degree of toe deviation causes rapid edge wear on these wide tires. Consider switching to Michelin Pilot Sport 4S or Pirelli P Zero PZ4 for improved tread life over the OE Continental SportContact 6. Budget $1,400-$2,000 for a set of four replacement tires. Aggressive driving with launch control dramatically reduces tire life. For better longevity, use Comfort mode instead of Dynamic for daily driving.</x:v>
+        <x:v>Confirm the leak source and VIN applicability before ordering parts. For the TSB condition, Audi specifies replacing the coolant feed and return pipes on both cylinder banks, replacing the disturbed oil-feed-pipe O-rings, then refilling and bleeding the cooling system. Service Action 21F7 was VIN-specific and expired in 2019, so current coverage must not be assumed. Do not order the former single pipe or alleged silicone-line kit from this card.</x:v>
       </x:c>
       <x:c r="F109" s="9" t="n">
         <x:v>0</x:v>
@@ -12417,21 +15185,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="110" ht="290.3999938964844" hidden="0" customHeight="1">
       <x:c r="A110" s="40" t="n">
         <x:v>109</x:v>
       </x:c>
       <x:c r="B110" s="9" t="str">
-        <x:v>audi-rs-q8-air-suspension-2020</x:v>
+        <x:v>audi-s7-air-suspension-2012</x:v>
       </x:c>
       <x:c r="C110" s="9" t="str">
-        <x:v>2020-2025 | Audi | RS Q8</x:v>
+        <x:v>2020-2021 | Audi | S7</x:v>
       </x:c>
       <x:c r="D110" s="9" t="str">
-        <x:v>2020-2025 RS Q8 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
+        <x:v>Rear-Axle Lock Nut and Alignment Recall Follow-Up (21V295 / 22V034)</x:v>
       </x:c>
       <x:c r="E110" s="9" t="str">
-        <x:v>Inspect the wiring and connector contacts between J775 and J1135 before replacing a component. For a first passive or sporadic occurrence, clear the fault and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after wiring inspection, Audi directs replacement of J1135 under current repair and parts information. Do not buy struts, springs, a compressor or a conversion kit solely from this warning.</x:v>
+        <x:v>Check the VIN for both campaigns 42L1 and 42L5. Audi dealers replace affected nuts and bolts, inspect and adjust rear alignment, and replace qualifying unevenly worn tires free of charge.</x:v>
       </x:c>
       <x:c r="F110" s="9" t="n">
         <x:v>0</x:v>
@@ -12440,21 +15208,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" ht="184.8000030517578" hidden="0" customHeight="1">
+    <x:row r="111" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A111" s="40" t="n">
         <x:v>110</x:v>
       </x:c>
       <x:c r="B111" s="9" t="str">
-        <x:v>audi-rs3-carbon-buildup-2017</x:v>
+        <x:v>audi-s7-biturbo-coolant-2012</x:v>
       </x:c>
       <x:c r="C111" s="9" t="str">
-        <x:v>2017-2025 | Audi | RS3 | 2.5T</x:v>
+        <x:v>2013-2014 | Audi | S7 | 4.0 TFSI</x:v>
       </x:c>
       <x:c r="D111" s="9" t="str">
-        <x:v>2.5T Five-Cylinder Carbon Buildup</x:v>
+        <x:v>4.0L Fuel Line Can Leak and Create a Fire Risk (Recall 13V450 / 20U6)</x:v>
       </x:c>
       <x:c r="E111" s="9" t="str">
-        <x:v>Walnut blast intake valves every 30,000-40,000 miles. Install catch can immediately on new vehicles.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel line free of charge under campaign 20U6/L8. Stop driving if fuel odor or leakage is present.</x:v>
       </x:c>
       <x:c r="F111" s="9" t="n">
         <x:v>0</x:v>
@@ -12463,21 +15231,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" ht="686.4000244140625" hidden="0" customHeight="1">
+    <x:row r="112" ht="264" hidden="0" customHeight="1">
       <x:c r="A112" s="40" t="n">
         <x:v>111</x:v>
       </x:c>
       <x:c r="B112" s="9" t="str">
-        <x:v>audi-rs3-dsg-transmission-2015</x:v>
+        <x:v>audi-s7-carbon-buildup-4.0t-2012</x:v>
       </x:c>
       <x:c r="C112" s="9" t="str">
-        <x:v>2023-2023 | Audi | RS3</x:v>
+        <x:v>2021-2021 | Audi | S7</x:v>
       </x:c>
       <x:c r="D112" s="9" t="str">
-        <x:v>2023 RS3 TCM Software Emissions Recall 37P3 - VIN Check Required</x:v>
+        <x:v>Rear Seat-Belt Retractor Can Release a Child Restraint Early (Recall 21V606 / 69CS)</x:v>
       </x:c>
       <x:c r="E112" s="9" t="str">
-        <x:v>Ask an Audi dealer to check whether Emissions Recall 37P3 is currently open for the VIN in Elsa. When open, the dealer updates the transmission-control-module software under the campaign; the published remedy requires no parts. Diagnose and repair the underlying fault separately before expecting its stored entry or MIL to clear. Do not buy a mechatronic unit, clutch pack, filter or upgraded DQ500 part for this software campaign.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers inspect and replace the affected middle-rear seat-belt assembly as necessary free of charge under campaign 69CS.</x:v>
       </x:c>
       <x:c r="F112" s="9" t="n">
         <x:v>0</x:v>
@@ -12486,21 +15254,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="113" ht="686.4000244140625" hidden="0" customHeight="1">
+    <x:row r="113" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A113" s="40" t="n">
         <x:v>112</x:v>
       </x:c>
       <x:c r="B113" s="9" t="str">
-        <x:v>audi-rs3-hpfp-2017</x:v>
+        <x:v>audi-s7-cylinder-demand-rough-running-hesitation</x:v>
       </x:c>
       <x:c r="C113" s="9" t="str">
-        <x:v>2017-2023 | Audi | RS3</x:v>
+        <x:v>2021-2021 | Audi | S7</x:v>
       </x:c>
       <x:c r="D113" s="9" t="str">
-        <x:v>2017-2020 / 2022-2023 RS3 Drive-System Warning or No-Start Diagnosis - TSB 2067757/3</x:v>
+        <x:v>Instrument Panel May Fail to Display Critical Safety Information (Recall 25V201 / 90VC)</x:v>
       </x:c>
       <x:c r="E113" s="9" t="str">
-        <x:v>Reproduce and document the complaint, scan the vehicle with current ODIS and complete Guided Fault Finding. When one of the listed DTC/symptom combinations is stored but GFF produces no result, manually add and complete the G265 intermediate-shaft-speed-sensor test plan. Repair only the component identified by that diagnosis. Do not replace or upgrade the high-pressure fuel pump from this warning or DTC set alone.</x:v>
+        <x:v>Check the VIN and campaign-completion history. Audi dealers update the instrument-panel module software free of charge under campaign 90VC.</x:v>
       </x:c>
       <x:c r="F113" s="9" t="n">
         <x:v>0</x:v>
@@ -12509,21 +15277,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="114" ht="316.79998779296875" hidden="0" customHeight="1">
       <x:c r="A114" s="40" t="n">
         <x:v>113</x:v>
       </x:c>
       <x:c r="B114" s="9" t="str">
-        <x:v>audi-rs3-magnetic-ride-2017</x:v>
+        <x:v>audi-s7-ea839-2-9t-v6-water-pump-internal-leak-overheating</x:v>
       </x:c>
       <x:c r="C114" s="9" t="str">
-        <x:v>2015-2019 | Audi | RS3</x:v>
+        <x:v>2020-2024 | Audi | S7</x:v>
       </x:c>
       <x:c r="D114" s="9" t="str">
-        <x:v>2015-2018 / Certain 2019 RS3 Magnetic-Ride Rear Shock Noise - TSB 2059240/1</x:v>
+        <x:v>Rearview Camera Image May Not Display (Recall 25V900 / 90TV)</x:v>
       </x:c>
       <x:c r="E114" s="9" t="str">
-        <x:v>Confirm magnetic-ride equipment, the exact model-year/VIN boundary and that the noise originates at the rear shock absorbers. When every bulletin criterion matches, replace both rear shock absorbers according to Audi workshop instructions and order the correct units by VIN. Do not replace dampers or convert the suspension from visible residue, ride feel or noise alone without this diagnosis.</x:v>
+        <x:v>Check the VIN and campaign-completion history. Audi dealers update the relevant software free of charge under campaign 90TV. Continue direct visual checks when reversing until repaired.</x:v>
       </x:c>
       <x:c r="F114" s="9" t="n">
         <x:v>0</x:v>
@@ -12532,21 +15300,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="115" ht="343.20001220703125" hidden="0" customHeight="1">
       <x:c r="A115" s="40" t="n">
         <x:v>114</x:v>
       </x:c>
       <x:c r="B115" s="9" t="str">
-        <x:v>audi-rs3-ttrs-carbon-buildup-2015</x:v>
+        <x:v>audi-s7-electromechanical-steering-rack-torque-sensor-failure-causin</x:v>
       </x:c>
       <x:c r="C115" s="9" t="str">
-        <x:v>2015-2023 | Audi | RS3 | 2.5T EA855</x:v>
+        <x:v>2021-2021 | Audi | S7</x:v>
       </x:c>
       <x:c r="D115" s="9" t="str">
-        <x:v>Severe Carbon Buildup on Intake Valves (2.5T 5-Cylinder)</x:v>
+        <x:v>Incorrect Brake-Fluid Reservoir Cap Label (Recall 23V601 / 47T9)</x:v>
       </x:c>
       <x:c r="E115" s="9" t="str">
-        <x:v>WALNUT BLASTING: Remove intake manifold and blast walnut shells through intake ports ($800-$1,500). Repeat every 30,000-40,000 miles—MORE frequent than base models due to high performance. PREVENTION: Install catch can ($400-$700) to filter PCV vapors. Add Liqui Moly Intake Valve Cleaner to every oil change. Change oil every 5,000 miles. Drive car hard regularly—Audi's own recommendation to burn off carbon.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers inspect the reservoir cap and replace it when necessary free of charge under campaign 47T9. Use only the brake-fluid specification in the owner and service information.</x:v>
       </x:c>
       <x:c r="F115" s="9" t="n">
         <x:v>0</x:v>
@@ -12555,44 +15323,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" ht="792" hidden="0" customHeight="1">
+    <x:row r="116" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A116" s="40" t="n">
         <x:v>115</x:v>
       </x:c>
       <x:c r="B116" s="9" t="str">
-        <x:v>audi-rs3-ttrs-injector-failure-2015</x:v>
+        <x:v>audi-s7-front-control-arm-bushing-ball-joint-failure</x:v>
       </x:c>
       <x:c r="C116" s="9" t="str">
-        <x:v>2015-2023 | Audi | RS3 | EA855</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
       </x:c>
       <x:c r="D116" s="9" t="str">
-        <x:v>Fuel Injector Failure and "Torch Effect" (2.5T)</x:v>
+        <x:v>Front Control Arm Bushing and Ball Joint Failure (C7 Suspension)</x:v>
       </x:c>
       <x:c r="E116" s="9" t="str">
-        <x:v>PREVENTIVE REPLACEMENT: Replace all fuel injectors every 60,000 km (37,000 miles) with OEM Audi injectors ($1,500-$2,500 installed). If engine misfires or runs rough: Inspect injectors IMMEDIATELY—do NOT continue driving. Failed injector can destroy engine in minutes. If piston is melted: Engine replacement required ($15,000-$25,000). Consider extended warranty or aftermarket warranty for out-of-warranty RS3/TT RS. This is the most serious reliability issue with the 2.5T engine.</x:v>
+        <x:v>Inspect all front control arms for play in the bushings and ball joints. Replace worn arms — many owners do the full front control-arm set (commonly a 16-piece kit covering both sides) to avoid repeat visits since the labor overlaps. Critical install notes: torque the bushing bolts at ride height (not with the suspension hanging) to avoid pre-loading and destroying the new bushings, and perform a four-wheel alignment afterward.</x:v>
       </x:c>
       <x:c r="F116" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G116" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="117" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="117" ht="396" hidden="0" customHeight="1">
       <x:c r="A117" s="40" t="n">
         <x:v>116</x:v>
       </x:c>
       <x:c r="B117" s="9" t="str">
-        <x:v>audi-rs4-b7-carbon-buildup-2007</x:v>
+        <x:v>audi-s7-fuel-injector-deposits-failure-causing-misfire-rough-running</x:v>
       </x:c>
       <x:c r="C117" s="9" t="str">
-        <x:v>2007-2008 | Audi | RS4 | 4.2L FSI V8</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
       </x:c>
       <x:c r="D117" s="9" t="str">
-        <x:v>2007-2008 RS4 Deposit-Related Cold-Start Misfire - Diagnose Before Cleaning</x:v>
+        <x:v>Fuel Injector Deposits / Failure Causing Misfire and Rough Running (4.0T V8)</x:v>
       </x:c>
       <x:c r="E117" s="9" t="str">
-        <x:v>Have the cold-start event and stored faults diagnosed before authorizing intake cleaning. The B7 RS4 bulletin first checks whether its fuel-additive and follow-up procedure resolves injector-deposit misfires. Current TSB 2014753/13 warns that gasoline additive can clean FSI injectors and combustion chambers but not FSI intake valves. If the misfire remains, the shop should continue guided diagnosis and confirm inlet-valve deposits before using the applicable mechanical-cleaning procedure. Do not buy a scanner, oil bundle or cleaning service solely from this card.</x:v>
+        <x:v>Pull misfire counts per cylinder to localize the fault. Inspect/replace failed or leaking injectors and renew injector seals; replace spark plugs and any weak coils as a set. Confirm fuel trims return to normal and clear codes; address intake carbon if present.</x:v>
       </x:c>
       <x:c r="F117" s="9" t="n">
         <x:v>0</x:v>
@@ -12601,21 +15369,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" ht="963.5999755859375" hidden="0" customHeight="1">
+    <x:row r="118" ht="396" hidden="0" customHeight="1">
       <x:c r="A118" s="40" t="n">
         <x:v>117</x:v>
       </x:c>
       <x:c r="B118" s="9" t="str">
-        <x:v>audi-rs4-rs5-carbon-buildup-2018</x:v>
+        <x:v>audi-s7-gateway-control-module-shutdown-from-rear-seat-liquid-spill</x:v>
       </x:c>
       <x:c r="C118" s="9" t="str">
-        <x:v>2018-2023 | Audi | RS4 | 2.9T</x:v>
+        <x:v>2020-2022 | Audi | S7 | 2.9 TFSI</x:v>
       </x:c>
       <x:c r="D118" s="9" t="str">
-        <x:v>2018-2023 RS4 2.9T Cold-Start Misfire from Confirmed Inlet Deposits</x:v>
+        <x:v>Rear-Seat Liquid Spill Can Shut Down Gateway Module (Recall 22V861 / 90V2)</x:v>
       </x:c>
       <x:c r="E118" s="9" t="str">
-        <x:v>Confirm the cold-start complaint, review the engine-control-unit event memory and verify inlet-port or inlet-valve deposits before cleaning. When that condition is confirmed, Audi TSB 2075530/1 directs the shop to remove the intake manifold or compressor and clean the inlet valves and ports by walnut blasting; the cylinder head remains installed. The cited Audi guidance does not support a mandatory 60,000-mile interval, a fixed price, dual catch cans, additive at every oil change, a 5,000-mile oil interval or a drive-hard prescription. Do not buy a catch can or cleaning product solely from this card.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers install a protective gateway-module cover free of charge under campaign 90V2. If multiple warnings or reduced power occur after a spill, move out of traffic safely and arrange dealer inspection.</x:v>
       </x:c>
       <x:c r="F118" s="9" t="n">
         <x:v>0</x:v>
@@ -12624,21 +15392,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="119" ht="1227.5999755859375" hidden="0" customHeight="1">
+    <x:row r="119" ht="528" hidden="0" customHeight="1">
       <x:c r="A119" s="40" t="n">
         <x:v>118</x:v>
       </x:c>
       <x:c r="B119" s="9" t="str">
-        <x:v>audi-rs5-b8-carbon-buildup-2013</x:v>
+        <x:v>audi-s7-high-pressure-fuel-pump-failure-causing-hard-start-power-los</x:v>
       </x:c>
       <x:c r="C119" s="9" t="str">
-        <x:v>2013-2015 | Audi | RS5 | 4.2L V8</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
       </x:c>
       <x:c r="D119" s="9" t="str">
-        <x:v>4.2L V8 Carbon Buildup and High-Rev Issues</x:v>
+        <x:v>High-Pressure Fuel Pump (HPFP) Failure Causing Hard Start and Power Loss (4.0T V8)</x:v>
       </x:c>
       <x:c r="E119" s="9" t="str">
-        <x:v>Confirm carbon buildup by scanning for misfire/fuel-trim faults, reviewing live data, and inspecting the intake valves with a borescope after removing the intake manifold. The proper repair is an intake-valve carbon cleaning service—typically walnut-shell blasting or manual chemical cleaning—while replacing the intake manifold gaskets, injector seals/O-rings, and PCV-related breather components if leaking or contributing to oil vapor. After reassembly, clear adaptations, perform a throttle-body/basic setting relearn, and road test to verify restored high-RPM pull and smooth idle. Independent shops typically charge about $800-$1,500 for a carbon clean on the 4.2 FSI V8, while dealer pricing can run roughly $1,500-$2,500 depending on how many seals and ancillary parts are replaced.</x:v>
+        <x:v>Diagnose with live fuel-rail pressure data before condemning the pump, as a faulty low-pressure sensor or in-tank pump can set the same codes. Replace the failed high-pressure pump (the affected bank, or both as a set on high-mileage cars) together with the cam follower and seals. Verify low-pressure (in-tank) supply is within spec.</x:v>
       </x:c>
       <x:c r="F119" s="9" t="n">
         <x:v>0</x:v>
@@ -12647,44 +15415,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="120" ht="1122" hidden="0" customHeight="1">
+    <x:row r="120" ht="660" hidden="0" customHeight="1">
       <x:c r="A120" s="40" t="n">
         <x:v>119</x:v>
       </x:c>
       <x:c r="B120" s="9" t="str">
-        <x:v>audi-rs5-carbon-buildup-2018</x:v>
+        <x:v>audi-s7-ignition-coil-pack-failure-causing-misfires</x:v>
       </x:c>
       <x:c r="C120" s="9" t="str">
-        <x:v>2018-2026 | Audi | RS5</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
       </x:c>
       <x:c r="D120" s="9" t="str">
-        <x:v>Direct Injection Carbon Buildup on Intake Valves</x:v>
+        <x:v>Ignition Coil Pack Failure Causing Misfires (4.0T V8)</x:v>
       </x:c>
       <x:c r="E120" s="9" t="str">
-        <x:v>Confirm intake-valve carbon buildup by scanning for misfire faults, reviewing fuel trims, and inspecting the intake valves with a borescope through the intake ports after removing the intake manifold. The proper repair is an intake-valve cleaning service, typically walnut-shell blasting each intake port with the valves closed, then replacing the intake manifold gaskets and any disturbed PCV or breather seals before clearing adaptations and road-testing. If misfires persist, inspect and replace worn spark plugs or ignition coils as needed, since heavy deposits can foul plugs and mimic ignition faults. Typical cost is about $800-$1,500 depending on labor rates and how much disassembly is required.</x:v>
+        <x:v>Confirm the failing cylinder, then swap the suspect coil to another cylinder to verify the fault follows the coil. Replace the failed coil; best practice on the 4.0T is to replace all eight coils and the spark plugs as a set since the access labor is shared and mixed-age coils tend to fail in sequence. Use OE or quality OE-equivalent coils (the 4.0T uses the 079905110-series coil). Inspect spark plugs for fouling/oil that could indicate a secondary issue.</x:v>
       </x:c>
       <x:c r="F120" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G120" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="121" ht="1003.2000122070312" hidden="0" customHeight="1">
+    <x:row r="121" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A121" s="40" t="n">
         <x:v>120</x:v>
       </x:c>
       <x:c r="B121" s="9" t="str">
-        <x:v>audi-rs5-turbo-coolant-2018</x:v>
+        <x:v>audi-s7-motor-mount-failure-2012</x:v>
       </x:c>
       <x:c r="C121" s="9" t="str">
-        <x:v>2021-2024 | Audi | RS5 | 2.9L V6 TFSI</x:v>
+        <x:v>2013-2018 | Audi | S7</x:v>
       </x:c>
       <x:c r="D121" s="9" t="str">
-        <x:v>2021-2024 RS5 V6 Coolant-Pump Leak Diagnosis - TSB 2070349/4</x:v>
+        <x:v>Passenger Occupant Detection Mat Can Disable the Airbag (Recall 18V370 / 74D5)</x:v>
       </x:c>
       <x:c r="E121" s="9" t="str">
-        <x:v>Locate the leak before replacing parts. Clean and dry the area, fill the cooling system to maximum, inspect at idle and at engine speeds up to about 2,500 rpm, and perform the Workshop Manual cooling-system leak test. If no further leak is detected, continue observation without replacing parts. If a leak recurs, replace only the component or components causing the leak and document the finding with clear photos or video; a pump-leak repair also requires a photo of the pump production date. Inspect the vacuum circuit and N649 when contamination or P0299 is present, following current Audi workshop and parts information.</x:v>
+        <x:v>Check VIN eligibility because seat equipment affects scope. Audi dealers install the occupant-detection repair kit free of charge under campaign 74D5.</x:v>
       </x:c>
       <x:c r="F121" s="9" t="n">
         <x:v>0</x:v>
@@ -12693,21 +15461,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="122" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="122" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A122" s="40" t="n">
         <x:v>121</x:v>
       </x:c>
       <x:c r="B122" s="9" t="str">
-        <x:v>audi-rs6-air-suspension-2020</x:v>
+        <x:v>audi-s7-pcv-oil-separator-failure-causing-oil-consumption-whistling</x:v>
       </x:c>
       <x:c r="C122" s="9" t="str">
-        <x:v>2021-2024 | Audi | RS6</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
       </x:c>
       <x:c r="D122" s="9" t="str">
-        <x:v>2021-2024 RS6 Air-Suspension Warning - Check C1260F0 or U112100</x:v>
+        <x:v>PCV / Oil Separator (Ölabscheider) Failure Causing Oil Consumption and Whistling (4.0T V8)</x:v>
       </x:c>
       <x:c r="E122" s="9" t="str">
-        <x:v>Have the wiring and connector contacts between suspension controller J775 and compressor controller J1135 inspected first. Audi says to clear a first passive or sporadic occurrence and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after the wiring check, the bulletin directs replacement of J1135 under the applicable service procedure. Do not replace air struts, a compressor or an unverified aftermarket assembly solely from this warning card.</x:v>
+        <x:v>Replace the failed oil separator / PCV assembly and the associated breather hose with the latest revised part. An ECM update may accompany the new part on some VINs. Confirm with a smoke test for intake-side vacuum leaks; inspect the rear main seal if oil consumption is severe, as a failed PCV is a common cause of rear main seal damage on these engines.</x:v>
       </x:c>
       <x:c r="F122" s="9" t="n">
         <x:v>0</x:v>
@@ -12716,21 +15484,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="123" ht="831.5999755859375" hidden="0" customHeight="1">
+    <x:row r="123" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A123" s="40" t="n">
         <x:v>122</x:v>
       </x:c>
       <x:c r="B123" s="9" t="str">
-        <x:v>audi-rs6-carbon-buildup-2020</x:v>
+        <x:v>audi-s7-power-liftgate-motor-gas-strut-failure</x:v>
       </x:c>
       <x:c r="C123" s="9" t="str">
-        <x:v>2021-2024 | Audi | RS6 | 4.0T V8</x:v>
+        <x:v>2013-2022 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824), 2.9T TFSI Biturbo V6 (EA839)</x:v>
       </x:c>
       <x:c r="D123" s="9" t="str">
-        <x:v>2021-2024 RS6 4.0T Cold-Start Misfire from Confirmed Inlet Deposits</x:v>
+        <x:v>Power Liftgate Motor and Gas Strut Failure (Sportback Tailgate)</x:v>
       </x:c>
       <x:c r="E123" s="9" t="str">
-        <x:v>Confirm the cold-start complaint, review the engine-control-unit event memory and verify inlet-port or inlet-valve deposits before cleaning. When that condition is confirmed, Audi TSB 2075530/1 directs the shop to remove the intake manifold or compressor and clean the inlet valves and ports by walnut blasting; the cylinder head remains installed. The cited Audi guidance does not specify a 30,000-40,000-mile interval, a fixed price or a mandatory catch can. Do not buy a catch can or cleaning product solely from this card.</x:v>
+        <x:v>Diagnose whether the fault is the gas struts (won't stay up / weak lift), the spindle lift motors (slow or struggling travel), or the latch/cinching motor (won't release or won't pull closed — see TSB 2072431/1). Replace worn gas struts in pairs; replace failed lift or cinching motors as needed. After repair, perform the power-liftgate relearn/reset procedure so travel limits recalibrate.</x:v>
       </x:c>
       <x:c r="F123" s="9" t="n">
         <x:v>0</x:v>
@@ -12739,21 +15507,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="124" ht="528" hidden="0" customHeight="1">
+    <x:row r="124" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A124" s="40" t="n">
         <x:v>123</x:v>
       </x:c>
       <x:c r="B124" s="9" t="str">
-        <x:v>audi-rs6-rs7-carbon-buildup-2013</x:v>
+        <x:v>audi-s7-premature-front-brake-rotor-warping-pad-wear</x:v>
       </x:c>
       <x:c r="C124" s="9" t="str">
-        <x:v>2013-2023 | Audi | RS6 | 4.0T V8</x:v>
+        <x:v>2013-2022 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824), 2.9T TFSI Biturbo V6 (EA839)</x:v>
       </x:c>
       <x:c r="D124" s="9" t="str">
-        <x:v>Severe Carbon Buildup on Intake Valves (4.0T V8)</x:v>
+        <x:v>Premature Front Brake Rotor Warping and Pad Wear</x:v>
       </x:c>
       <x:c r="E124" s="9" t="str">
-        <x:v>WALNUT BLASTING: Remove both intake manifolds and blast walnut shells through all intake ports ($1,200-$2,000 for V8). Repeat every 60,000 miles. PREVENTION: Install catch can ($500-$800 for twin-turbo setup). Add Liqui Moly Intake Valve Cleaner to every oil change. Change oil every 5,000 miles. Drive car hard regularly.</x:v>
+        <x:v>Replace warped/below-spec rotors and pads together; consider higher-quality coated or upgraded rotors that resist warping better than the soft OEM units. Bed in new pads/rotors properly and avoid riding the brakes to prevent uneven deposits. Ensure caliper guide pins/slides move freely so pads engage evenly. For repeat warping, an upgraded rotor-and-pad package is the durable fix; address any pulsation early before it damages new components.</x:v>
       </x:c>
       <x:c r="F124" s="9" t="n">
         <x:v>0</x:v>
@@ -12762,21 +15530,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="125" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="125" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A125" s="40" t="n">
         <x:v>124</x:v>
       </x:c>
       <x:c r="B125" s="9" t="str">
-        <x:v>audi-rs6-rs7-motor-mounts-2013</x:v>
+        <x:v>audi-s7-rear-differential-mount-driveshaft-center-bearing-wear-causi</x:v>
       </x:c>
       <x:c r="C125" s="9" t="str">
-        <x:v>2013-2023 | Audi | RS6 | 4.0T V8</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
       </x:c>
       <x:c r="D125" s="9" t="str">
-        <x:v>Premature Motor Mount Failure (4.0T V8)</x:v>
+        <x:v>Rear Differential Mount and Driveshaft Center Bearing Wear Causing Drivetrain Clunk (C7)</x:v>
       </x:c>
       <x:c r="E125" s="9" t="str">
-        <x:v>Replace failed motor mounts with OEM or upgraded mounts ($800-$1,500 for all mounts). Upgraded aftermarket mounts (034 Motorsport, ECS) offer better durability for high-torque engines ($400-$600 per mount). If you drive aggressively or track the car, consider upgrading to performance mounts preventively. Monitor for vibrations and clunking—early replacement prevents driveline damage.</x:v>
+        <x:v>Inspect the rear differential mount and driveshaft center support bearing for play and torn rubber. Replace worn components with OE parts, or fit billet aluminum diff/transmission mount inserts that fill the factory voids to remove the slop without adding harshness. On 4.0T cars, also check for the separate active-engine-mount software TSB before condemning a mount for a 1,000-3,000 RPM cruise vibration. Reassess the clunk after each fix since multiple sources can contribute.</x:v>
       </x:c>
       <x:c r="F125" s="9" t="n">
         <x:v>0</x:v>
@@ -12785,21 +15553,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="126" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="126" ht="462" hidden="0" customHeight="1">
       <x:c r="A126" s="40" t="n">
         <x:v>125</x:v>
       </x:c>
       <x:c r="B126" s="9" t="str">
-        <x:v>audi-rs7-air-suspension-2014</x:v>
+        <x:v>audi-s7-rear-view-camera-mmi-flex-harness-black-screen</x:v>
       </x:c>
       <x:c r="C126" s="9" t="str">
-        <x:v>2021-2025 | Audi | RS7</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7 (C7), A7 (C7) | 4.0 TFSI V8 (EA824)</x:v>
       </x:c>
       <x:c r="D126" s="9" t="str">
-        <x:v>2021-2025 RS7 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
+        <x:v>Rear-View Camera / MMI Flex Harness Black Screen</x:v>
       </x:c>
       <x:c r="E126" s="9" t="str">
-        <x:v>Inspect the wiring and connectors between J775 and J1135 before replacing a component. For a first passive/sporadic occurrence, clear the fault and release the vehicle. If the fault is active/static after wiring and connector inspection, or the same passive/sporadic fault returns a second time, replace J1135 using current Audi repair and parts information. Audi notes that improved J1135 software remains under development.</x:v>
+        <x:v>Diagnose with a scan and continuity check of the tailgate-to-body flex harness before replacing the camera. Repair or replace the broken hinge-side loom conductors; if confirmed faulty, replace the camera module. For MMI freezes, apply the latest software update or reset the unit.</x:v>
       </x:c>
       <x:c r="F126" s="9" t="n">
         <x:v>0</x:v>
@@ -12808,21 +15576,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="127" ht="158.39999389648438" hidden="0" customHeight="1">
+    <x:row r="127" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A127" s="40" t="n">
         <x:v>126</x:v>
       </x:c>
       <x:c r="B127" s="9" t="str">
-        <x:v>audi-rs7-carbon-buildup-2014</x:v>
+        <x:v>audi-s7-s-tronic-7-speed-dual-clutch-mechatronic-clutch-wear</x:v>
       </x:c>
       <x:c r="C127" s="9" t="str">
-        <x:v>2014-2026 | Audi | RS7 | 4.0T</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T (S-tronic / 0B5 DL501) | 4.0 TFSI V8 (EA824)</x:v>
       </x:c>
       <x:c r="D127" s="9" t="str">
-        <x:v>4.0T Carbon Deposit Accumulation</x:v>
+        <x:v>S-tronic 7-Speed Dual-Clutch (DL501/0B5) Mechatronic and Clutch Wear</x:v>
       </x:c>
       <x:c r="E127" s="9" t="str">
-        <x:v>Walnut blast every 30,000-40,000 miles. Install dual catch can setup for both turbo sides.</x:v>
+        <x:v>Perform the S-tronic gearbox oil and filter service on schedule (roughly every 40,000-60,000 km). For judder/jerking, have the mechatronic unit tested; recondition or replace the valve body with the superseded design and adapt/replace the clutch packs as needed. Software adaptation resets can temporarily improve drivability but do not fix worn hardware.</x:v>
       </x:c>
       <x:c r="F127" s="9" t="n">
         <x:v>0</x:v>
@@ -12831,21 +15599,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="128" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="128" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A128" s="40" t="n">
         <x:v>127</x:v>
       </x:c>
       <x:c r="B128" s="9" t="str">
-        <x:v>audi-rs7-turbo-coolant-2014</x:v>
+        <x:v>audi-s7-shark-fin-roof-antenna-water-intrusion-causing-gps-satellite</x:v>
       </x:c>
       <x:c r="C128" s="9" t="str">
-        <x:v>2014-2026 | Audi | RS7 | 4.0T</x:v>
+        <x:v>2013-2018 | Audi | S7 | Prestige, Premium Plus | 4.0T Biturbo V8 (4.0 TFSI)</x:v>
       </x:c>
       <x:c r="D128" s="9" t="str">
-        <x:v>4.0T Twin-Turbo Coolant System Degradation</x:v>
+        <x:v>Shark-Fin Roof Antenna Water Intrusion Causing GPS / Satellite Radio Reception Loss (C7)</x:v>
       </x:c>
       <x:c r="E128" s="9" t="str">
-        <x:v>Replace turbo coolant lines proactively at 50,000 miles. Upgrade to silicone lines where possible.</x:v>
+        <x:v>Test/replace the shark-fin antenna module with a matching OEM part number and renew the base gasket to restore a watertight seal; in many cases the official fix is a repair kit with a new FAKRA connector and adapter cable rather than a whole new antenna. Access requires partially dropping the rear headliner to reach the single mounting nut and reconnect the coax leads. Inspecting and reseating a corroded coax connection sometimes restores reception without full replacement.</x:v>
       </x:c>
       <x:c r="F128" s="9" t="n">
         <x:v>0</x:v>
@@ -12854,21 +15622,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="129" ht="752.4000244140625" hidden="0" customHeight="1">
       <x:c r="A129" s="40" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="B129" s="9" t="str">
-        <x:v>audi-rs7-turbo-wastegate-2014</x:v>
+        <x:v>audi-s7-sunroof-panoramic-roof-drain-clog-causing-water-intrusion-el</x:v>
       </x:c>
       <x:c r="C129" s="9" t="str">
-        <x:v>2014-2017 | Audi | RS7 | 4.0L TFSI twin-turbo V8</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
       </x:c>
       <x:c r="D129" s="9" t="str">
-        <x:v>2014-2017 RS7 Turbocharger Oil-Strainer Safety Recall 21H7 / 22V178 - Check VIN</x:v>
+        <x:v>Sunroof / Panoramic Roof Drain Clog Causing Water Intrusion and Electronics Damage (C7)</x:v>
       </x:c>
       <x:c r="E129" s="9" t="str">
-        <x:v>Check the VIN for open Audi campaign 21H7 in Elsa or the NHTSA recall lookup. The authorized dealer replaces the turbocharger oil strainer, changes the engine oil and filter, and performs the campaign scan-tool turbo/boost-system check at no charge. Follow the campaign procedure for any damage found; do not buy a turbocharger, actuator or gasket kit from this card.</x:v>
+        <x:v>Test the drains by slowly pouring water into the channels at each corner of the sunroof and watching where it exits beneath the A- and C-pillars. Clear clogged tubes with low-pressure air or a soft trimmer line (avoid stiff wire that can puncture the tube) and reseat/secure any loose drain-tube connectors at the sunroof frame. Dry out any soaked carpet/insulation promptly and inspect floor-mounted modules for corrosion. Periodic drain cleaning is the best prevention.</x:v>
       </x:c>
       <x:c r="F129" s="9" t="n">
         <x:v>0</x:v>
@@ -12877,21 +15645,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="130" ht="422.3999938964844" hidden="0" customHeight="1">
       <x:c r="A130" s="40" t="n">
         <x:v>129</x:v>
       </x:c>
       <x:c r="B130" s="9" t="str">
-        <x:v>audi-rsq8-4.0t-coolant-2020</x:v>
+        <x:v>audi-s7-turbo-oil-strainer-2012</x:v>
       </x:c>
       <x:c r="C130" s="9" t="str">
-        <x:v>2020-2021 | Audi | RS Q8 | 4.0T V8</x:v>
+        <x:v>2013-2017 | Audi | S7 | 4.0 TFSI</x:v>
       </x:c>
       <x:c r="D130" s="9" t="str">
-        <x:v>2020-Early 2021 RS Q8 Red Coolant Warning - Check G407 per TSB 2062951/4</x:v>
+        <x:v>Turbocharger Oil-Supply Strainer Can Block and Cause Engine Stall (Recall 22V178 / 21H7)</x:v>
       </x:c>
       <x:c r="E130" s="9" t="str">
-        <x:v>Have the vehicle checked with Audi Guided Fault Finding and inspect G407 and its O-ring. Replace G407 only if the O-ring is damaged or pinched and the diagnosis matches the bulletin; follow the related Audi diagnostic path if additional listed faults are stored. Do not replace turbo coolant hoses, pumps or other cooling parts from this card alone.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the oil strainer and perform an oil change free of charge under campaign 21H7. If abnormal turbo noise, loss of power, or an engine warning occurs, stop safely and arrange dealer inspection.</x:v>
       </x:c>
       <x:c r="F130" s="9" t="n">
         <x:v>0</x:v>
@@ -12900,21 +15668,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" ht="237.60000610351562" hidden="0" customHeight="1">
+    <x:row r="131" ht="726" hidden="0" customHeight="1">
       <x:c r="A131" s="40" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="B131" s="9" t="str">
-        <x:v>audi-rsq8-air-suspension-2020</x:v>
+        <x:v>audi-s7-turbocharger-wastegate-linkage-rattle-underboost</x:v>
       </x:c>
       <x:c r="C131" s="9" t="str">
-        <x:v>2020-2026 | Audi | RS Q8</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
       </x:c>
       <x:c r="D131" s="9" t="str">
-        <x:v>Adaptive Air Suspension Failure Under SUV Weight</x:v>
+        <x:v>Turbocharger Wastegate Linkage Rattle and Underboost (4.0T V8)</x:v>
       </x:c>
       <x:c r="E131" s="9" t="str">
-        <x:v>Replace air struts as they fail. Budget for compressor replacement. Consider heavy-duty aftermarket options designed for the RS Q8 weight.</x:v>
+        <x:v>Diagnose the rattle and any boost faults to confirm wastegate-arm play versus a loose heat shield. Minor play can sometimes be mitigated with a clip, but the durable factory fix is turbocharger replacement. When replacing a hot-V turbo, it is mandatory to also replace the oil feed and return lines and to prime the new unit with oil before first start to prevent immediate bearing failure. Regular oil changes and allowing turbo cool-down help reduce coking-related wear.</x:v>
       </x:c>
       <x:c r="F131" s="9" t="n">
         <x:v>0</x:v>
@@ -12923,20 +15691,22 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="132" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="132" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A132" s="40" t="n">
         <x:v>131</x:v>
       </x:c>
       <x:c r="B132" s="9" t="str">
-        <x:v>audi-rsq8-air-suspension-leak-2020</x:v>
+        <x:v>audi-s8-5-2-v10-timing-chain-tensioner-guide-wear</x:v>
       </x:c>
       <x:c r="C132" s="9" t="str">
-        <x:v>2020-2026 | Audi | RS Q8</x:v>
+        <x:v>2007-2012 | Audi | S8 | 5.2L FSI V10 (BSM)</x:v>
       </x:c>
       <x:c r="D132" s="9" t="str">
-        <x:v>Adaptive Air Suspension Air Spring Leaks</x:v>
-      </x:c>
-      <x:c r="E132" s="9" t="str"/>
+        <x:v>5.2 V10 Timing Chain Tensioner / Guide Wear (D3 Cold-Start Rattle)</x:v>
+      </x:c>
+      <x:c r="E132" s="9" t="str">
+        <x:v>Investigate any cold-start rattle promptly: inspect tensioner travel and guide condition. Replace the timing chains, tensioners, and plastic guides as a set with updated genuine parts; this is a major, labor-intensive repair (often engine-out). Strictly follow short oil-change intervals with the correct grade to maximize tensioner/guide life, and address any low-oil-pressure condition immediately. Do not drive a V10 with a persistent timing rattle.</x:v>
+      </x:c>
       <x:c r="F132" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -12944,21 +15714,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="133" ht="607.2000122070312" hidden="0" customHeight="1">
+    <x:row r="133" ht="198" hidden="0" customHeight="1">
       <x:c r="A133" s="40" t="n">
         <x:v>132</x:v>
       </x:c>
       <x:c r="B133" s="9" t="str">
-        <x:v>audi-rsq8-brake-wear-2020</x:v>
+        <x:v>audi-s8-air-suspension-2013</x:v>
       </x:c>
       <x:c r="C133" s="9" t="str">
-        <x:v>2020-2021 | Audi | RS Q8</x:v>
+        <x:v>2013-2024 | Audi | S8</x:v>
       </x:c>
       <x:c r="D133" s="9" t="str">
-        <x:v>2020-2021 RS Q8 Front Steel-Brake Squeal - TSB 2062052/1</x:v>
+        <x:v>Adaptive Air Suspension Multi-Point Failure</x:v>
       </x:c>
       <x:c r="E133" s="9" t="str">
-        <x:v>Confirm the frequency and operating conditions and inspect the discs for corrosion, grooves or glazing. When the bulletin applies, Audi directs replacement of the front pad set using current parts information followed by the specified bedding procedure. Do not perform ABS stops for bedding, and do not replace rotors or buy aftermarket pads solely from the prior wear narrative.</x:v>
+        <x:v>Replace air struts as they fail. Budget for full system refresh at 80,000 miles. Arnott aftermarket struts offer cost savings.</x:v>
       </x:c>
       <x:c r="F133" s="9" t="n">
         <x:v>0</x:v>
@@ -12967,21 +15737,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="134" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="134" ht="726" hidden="0" customHeight="1">
       <x:c r="A134" s="40" t="n">
         <x:v>133</x:v>
       </x:c>
       <x:c r="B134" s="9" t="str">
-        <x:v>audi-s3-carbon-buildup-2015</x:v>
+        <x:v>audi-s8-air-suspension-failure-2013</x:v>
       </x:c>
       <x:c r="C134" s="9" t="str">
-        <x:v>2015-2019 | Audi | S3 | S3 | EA888 Gen 3</x:v>
+        <x:v>2020-2024 | Audi | S8</x:v>
       </x:c>
       <x:c r="D134" s="9" t="str">
-        <x:v>Carbon Buildup on Intake Valves (Pre-Dual Injection EA888 Gen 3)</x:v>
+        <x:v>2020-2024 S8 Air-Suspension Malfunction with J1135 Communication Fault - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E134" s="9" t="str">
-        <x:v>WALNUT BLASTING: Remove intake manifold and blast intake valve ports with crushed walnut shells ($500-$1,000). Repeat every 40,000-60,000 miles. CATCH CAN: Install an oil catch can ($200-$400) to capture PCV vapors before they reach intake valves—significantly slows carbon buildup. OIL CHANGES: Use high-quality synthetic oil and change every 5,000 miles. DRIVING HABITS: Regular spirited driving helps burn off some deposits. NOTE: 2020+ S3 models with EA888 Gen 3B dual injection are largely immune to this issue.</x:v>
+        <x:v>Read the suspension-controller DTC and symptom code, then inspect wiring, terminals and connectors between J775 and J1135 exactly as Audi specifies. If the fault is passive/sporadic, clear it and verify operation. If it remains active/static after the electrical inspection and key cycle, follow Audi testing for J1135 replacement. Diagnose vehicle sag or leak-down separately; do not order air struts, a compressor or a coil-conversion kit from the former card.</x:v>
       </x:c>
       <x:c r="F134" s="9" t="n">
         <x:v>0</x:v>
@@ -12990,21 +15760,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="135" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="135" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A135" s="40" t="n">
         <x:v>134</x:v>
       </x:c>
       <x:c r="B135" s="9" t="str">
-        <x:v>audi-s3-dq250-mechatronic-2015</x:v>
+        <x:v>audi-s8-battery-management-energy-control-module-faults-parasitic-dr</x:v>
       </x:c>
       <x:c r="C135" s="9" t="str">
-        <x:v>2015-2024 | Audi | S3</x:v>
+        <x:v>2020-2020 | Audi | S8 | VIN-specific Emissions Service Action 27BQ; verify open action in Audi campaign lookup | 4.0T TFSI V8 mild-hybrid</x:v>
       </x:c>
       <x:c r="D135" s="9" t="str">
-        <x:v>DQ250 DSG Mechatronic Unit Failure</x:v>
+        <x:v>2020 S8 Starter-Alternator Emissions Service Action 27BQ - VIN Check Required</x:v>
       </x:c>
       <x:c r="E135" s="9" t="str">
-        <x:v>Replace or rebuild mechatronic unit. Regular DSG fluid changes every 40,000 miles help prevent premature failure.</x:v>
+        <x:v>Check the VIN in Audi’s recall/service-campaign lookup or ask an Audi dealer to verify 27BQ in Elsa. If open, the dealer replaces the starter-alternator under the action. Electrical-system warnings, a discharged battery, abnormal charging or overnight draw outside this exact action require battery/charging tests and a measured sleep-current diagnosis; do not replace a battery monitor, gateway or MMI module from the former card.</x:v>
       </x:c>
       <x:c r="F135" s="9" t="n">
         <x:v>0</x:v>
@@ -13013,21 +15783,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="136" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="136" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A136" s="40" t="n">
         <x:v>135</x:v>
       </x:c>
       <x:c r="B136" s="9" t="str">
-        <x:v>audi-s3-dsg-mechatronic-2015</x:v>
+        <x:v>audi-s8-biturbo-coolant-2013</x:v>
       </x:c>
       <x:c r="C136" s="9" t="str">
-        <x:v>2015-2024 | Audi | S3 | S3</x:v>
+        <x:v>2013-2024 | Audi | S8 | 4.0T</x:v>
       </x:c>
       <x:c r="D136" s="9" t="str">
-        <x:v>DQ381 S-Tronic Mechatronic Unit Failure</x:v>
+        <x:v>4.0T Turbo Coolant System Degradation</x:v>
       </x:c>
       <x:c r="E136" s="9" t="str">
-        <x:v>EARLY SYMPTOMS (jerky shifts): DSG fluid and filter service ($500-$700) plus dealer software update. This may resolve early-stage issues. MECHATRONIC FAILURE: Replace mechatronic unit ($2,000-$4,000 installed) plus TCU coding. Remanufactured units available for $1,500-$2,500. CLUTCH PACK FAILURE: Replace dual clutch pack ($3,000-$5,000). PREVENTION: Service DSG fluid every 40,000 miles—ignore Audi's 'lifetime fill' claim. Use ONLY OEM Audi DSG fluid (G 052 182 A2) or approved Pentosin FFL-2. Avoid aggressive launches and excessive clutch slip in traffic.</x:v>
+        <x:v>Replace all turbo coolant and oil feed lines preventatively at 60,000 miles. Monitor coolant levels closely.</x:v>
       </x:c>
       <x:c r="F136" s="9" t="n">
         <x:v>0</x:v>
@@ -13036,21 +15806,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="137" ht="158.39999389648438" hidden="0" customHeight="1">
+    <x:row r="137" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A137" s="40" t="n">
         <x:v>136</x:v>
       </x:c>
       <x:c r="B137" s="9" t="str">
-        <x:v>audi-s3-ea888-carbon-2015</x:v>
+        <x:v>audi-s8-clogged-sunroof-plenum-drains-causing-water-intrusion-electr</x:v>
       </x:c>
       <x:c r="C137" s="9" t="str">
-        <x:v>2015-2024 | Audi | S3 | EA888</x:v>
+        <x:v>2007-2018 | Audi | S8 | S8, S8 Plus | 5.2 FSI V10, 4.0 TFSI twin-turbo V8 (4.0T)</x:v>
       </x:c>
       <x:c r="D137" s="9" t="str">
-        <x:v>EA888 Carbon Buildup on Intake Valves</x:v>
+        <x:v>Clogged Sunroof / Plenum Drains Causing Water Intrusion and Electronics Damage</x:v>
       </x:c>
       <x:c r="E137" s="9" t="str">
-        <x:v>Walnut blast intake valves every 40,000-60,000 miles or install a catch can to reduce buildup rate.</x:v>
+        <x:v>Clear and flush all sunroof and plenum/cowl drains; replace cracked drain hoses, grommets, or channel connectors. Dry out saturated carpet/insulation and inspect plenum-area modules for corrosion, replacing any water-damaged control units. Preventively clean the drains at least annually and keep the cowl area free of leaves/debris.</x:v>
       </x:c>
       <x:c r="F137" s="9" t="n">
         <x:v>0</x:v>
@@ -13059,21 +15829,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="138" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="138" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A138" s="40" t="n">
         <x:v>137</x:v>
       </x:c>
       <x:c r="B138" s="9" t="str">
-        <x:v>audi-s3-hpfp-2015</x:v>
+        <x:v>audi-s8-coolant-thermostat-leak-2013</x:v>
       </x:c>
       <x:c r="C138" s="9" t="str">
-        <x:v>2015-2024 | Audi | S3 | EA888</x:v>
+        <x:v>2020-2021 | Audi | S8 | 2021 applicability ends at VIN 012194; confirm VIN and coolant-pump leak before repair | 4.0T TFSI V8</x:v>
       </x:c>
       <x:c r="D138" s="9" t="str">
-        <x:v>High-Pressure Fuel Pump (HPFP) Failure</x:v>
+        <x:v>2020-Early 2021 S8 Coolant-Pump Leak - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E138" s="9" t="str">
-        <x:v>Replace HPFP with updated revision. Check cam follower for wear during replacement.</x:v>
+        <x:v>Do not drive an overheating vehicle. Record coolant warning and temperature behavior, pressure-test the cooling system when safe, and locate the leak. Confirm the 2021 VIN boundary and apply TSB 2065040/4 only when the coolant pump is the identified source. Other thermostat, hose, turbo-line, heat-exchanger or internal-loss causes require separate diagnosis; do not order the former thermostat/water-pump bundle from this card.</x:v>
       </x:c>
       <x:c r="F138" s="9" t="n">
         <x:v>0</x:v>
@@ -13082,21 +15852,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="139" ht="1122" hidden="0" customHeight="1">
+    <x:row r="139" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A139" s="40" t="n">
         <x:v>138</x:v>
       </x:c>
       <x:c r="B139" s="9" t="str">
-        <x:v>audi-s3-turbo-wastegate-rattle-2015</x:v>
+        <x:v>audi-s8-cylinder-demand-active-engine-mount-failure-4-cylinder-mode</x:v>
       </x:c>
       <x:c r="C139" s="9" t="str">
-        <x:v>2015-2020 | Audi | S3 | S3</x:v>
+        <x:v>2013-2015 | Audi | S8 | 4.0 TFSI vehicles with reproducible 1000-3000 rpm vibration; diagnose J931 before mount replacement | 4.0T TFSI V8</x:v>
       </x:c>
       <x:c r="D139" s="9" t="str">
-        <x:v>IS20 Turbocharger Wastegate Rattle and Actuator Failure</x:v>
+        <x:v>2013-2015 S8 COD Vibration with J931 Basic-Setting Fault - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E139" s="9" t="str">
-        <x:v>EARLY STAGE (rattle only, no power loss): Audi TSB 2027585/3 prescribes installation of a metal retaining clip (part 06J145220A) to tighten wastegate arm play ($200-$400 if under warranty, $500-$800 out of pocket). UPGRADED DIVERTER VALVE: Replace with revision 'D' diverter valve to improve boost control. SEVERE (actuator failure or power loss): Replace complete IS20 turbocharger ($2,500-$4,000 installed). The IS20 actuator is integrated and not serviceable separately. Upgraded IS38 turbo swap ($3,500-$5,000) from Golf R is a popular option if replacing turbo anyway. PREVENTION: Avoid short trips that don't fully heat the turbo. Change oil every 5,000 miles with high-quality synthetic.</x:v>
+        <x:v>Reproduce the vibration under Audi’s specified driving conditions and scan J931. If the bulletin applies, verify J931 software, perform the required SVM update and basic settings, align the exhaust without tension, repeat basic settings and follow the referenced diagnosis if vibration remains. Inspect mount hardware only after the software, calibration and exhaust path. Do not disable cylinder-on-demand or replace both mounts from the former card.</x:v>
       </x:c>
       <x:c r="F139" s="9" t="n">
         <x:v>0</x:v>
@@ -13105,44 +15875,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" ht="594" hidden="0" customHeight="1">
+    <x:row r="140" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A140" s="40" t="n">
         <x:v>139</x:v>
       </x:c>
       <x:c r="B140" s="9" t="str">
-        <x:v>audi-s3-water-pump-thermostat-2015</x:v>
+        <x:v>audi-s8-d2-4-2-v8-timing-belt-tensioner-service</x:v>
       </x:c>
       <x:c r="C140" s="9" t="str">
-        <x:v>2020-2024 | Audi | S3 | 2.0L TFSI</x:v>
+        <x:v>2001-2003 | Audi | S8 | 4.2L 40V V8 (AYS)</x:v>
       </x:c>
       <x:c r="D140" s="9" t="str">
-        <x:v>2020/2022-2024 Audi S3 2.0 TFSI Coolant-Pump Leak Diagnosis</x:v>
+        <x:v>D2 4.2 V8 Timing Belt and Tensioner Service (Interference Engine)</x:v>
       </x:c>
       <x:c r="E140" s="9" t="str">
-        <x:v>Document the suspected leak, clean and dry all traces, fill the cooling system to the correct level and reassess after driving a few miles. If no fresh leak appears, continue observing without replacing parts. If leakage recurs, replace only the component causing the damage under the exact VIN, engine and part criteria. Outside applicable warranty, Audi states the bulletin is informational.</x:v>
+        <x:v>Replace the timing belt as a complete kit — belt, tensioner, idler/guide rollers, and water pump — at or before Audi's interval (and by age regardless of mileage). Use genuine/OE-quality components and set cam/crank timing precisely with the correct locking tools; this is a front-of-engine ('service position') job. Inspect the exhaust-side chain tensioners while in there. Always confirm timing-belt history (with receipts) before buying a D2 S8; if unknown, do it immediately.</x:v>
       </x:c>
       <x:c r="F140" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G140" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="141" ht="250.8000030517578" hidden="0" customHeight="1">
+    <x:row r="141" ht="844.7999877929688" hidden="0" customHeight="1">
       <x:c r="A141" s="40" t="n">
         <x:v>140</x:v>
       </x:c>
       <x:c r="B141" s="9" t="str">
-        <x:v>audi-s4-b5-timing-chain-2000</x:v>
+        <x:v>audi-s8-direct-injection-carbon-buildup-intake-valves</x:v>
       </x:c>
       <x:c r="C141" s="9" t="str">
-        <x:v>2000-2002 | Audi | S4</x:v>
+        <x:v>2013-2018 | Audi | S8 | 4.0T TFSI V8 (CTFA/CGTA/CWUC)</x:v>
       </x:c>
       <x:c r="D141" s="9" t="str">
-        <x:v>Driver Airbag Inflator May Deploy Improperly (Recall 21V470 / 69CJ)</x:v>
+        <x:v>Direct-Injection Carbon Buildup on Intake Valves (Misfires / Rough Idle)</x:v>
       </x:c>
       <x:c r="E141" s="9" t="str">
-        <x:v>Check the VIN with Audi or NHTSA. Audi dealers replace the driver frontal-airbag inflator with an alternative inflator free of charge under campaign 69CJ.</x:v>
+        <x:v>Confirm via borescope of the intake valves (and rule out coils/plugs/PCV first). The accepted repair is walnut-shell blasting: remove the intake manifold and media-blast the carbon off the valves and ports with crushed walnut shells, then reinstall with new intake gaskets. Replace spark plugs and inspect coils while the manifold is off. Preventively, keep up with oil changes, fix any PCV/oil-burning source, and consider periodic cleaning every ~40,000-60,000 miles. Catch-can solutions reduce future accumulation.</x:v>
       </x:c>
       <x:c r="F141" s="9" t="n">
         <x:v>0</x:v>
@@ -13151,21 +15921,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="142" ht="237.60000610351562" hidden="0" customHeight="1">
+    <x:row r="142" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A142" s="40" t="n">
         <x:v>141</x:v>
       </x:c>
       <x:c r="B142" s="9" t="str">
-        <x:v>audi-s4-b5-turbo-failure-2000</x:v>
+        <x:v>audi-s8-front-suspension-control-arm-bushing-sway-bar-link-wear</x:v>
       </x:c>
       <x:c r="C142" s="9" t="str">
-        <x:v>2003-2004 | Audi | S4</x:v>
+        <x:v>2020-2021 | Audi | S8 | 2021 applicability through VIN 028090; localize noise acoustically before parts | 4.0T TFSI V8 mild-hybrid</x:v>
       </x:c>
       <x:c r="D142" s="9" t="str">
-        <x:v>Xenon Headlamp Reflector Coating Can Reduce Light Output (Recall 05V096)</x:v>
+        <x:v>2020-Early 2021 S8 Front Lower Guide-Link Hydro-Bushing Noise - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E142" s="9" t="str">
-        <x:v>Verify VIN eligibility and campaign completion with Audi. Dealers replace both xenon headlamp reflectors free of charge under recall 05V096.</x:v>
+        <x:v>Confirm the VIN boundary, reproduce the noise and localize it with acoustic diagnostic equipment. Inspect the lower guide-link hydro-bushings and surrounding joints. If the hydro-bushing is confirmed, follow Audi’s paired replacement procedure; complete guide links may be required when prior pressing or rework prevents the specified repair. Align the vehicle as required. Do not order a ten-arm kit or sway-bar links from the former card.</x:v>
       </x:c>
       <x:c r="F142" s="9" t="n">
         <x:v>0</x:v>
@@ -13174,21 +15944,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="143" ht="303.6000061035156" hidden="0" customHeight="1">
+    <x:row r="143" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A143" s="40" t="n">
         <x:v>142</x:v>
       </x:c>
       <x:c r="B143" s="9" t="str">
-        <x:v>audi-s4-b6-timing-chain-2004</x:v>
+        <x:v>audi-s8-high-pressure-fuel-pump-injector-internal-leak-causing-hard</x:v>
       </x:c>
       <x:c r="C143" s="9" t="str">
-        <x:v>2005-2009 | Audi | S4</x:v>
+        <x:v>2013-2018 | Audi | S8 | 4.0 TFSI; diagnosis requires ODIS values, software check and pressure-hold testing | 4.0T TFSI V8</x:v>
       </x:c>
       <x:c r="D143" s="9" t="str">
-        <x:v>Passenger Airbag Inflator Can Rupture (Recall 18V427 / 69R7)</x:v>
+        <x:v>2013-2018 S8 Warm-Soak Long-Crank or No-Start - Fuel Diagnosis Required</x:v>
       </x:c>
       <x:c r="E143" s="9" t="str">
-        <x:v>Check VIN eligibility because body style and original registration history affect scope. Audi dealers replace the passenger frontal-airbag remedy part free of charge under campaign 69R7.</x:v>
+        <x:v>Have the dealer read DTCs and ODIS fuel-in-oil value, verify ECM software and perform Audi’s high- and low-pressure holding tests. If high-pressure behavior is abnormal, borescope the combustion chamber to identify a leaking injector. If low-side pressure builds correctly but drops more than 1.5 bar in the first 15 minutes, Audi says at least one HPFP may be leaking and directs replacement of both pumps plus an oil change. Select no pump or injector until the test identifies the path.</x:v>
       </x:c>
       <x:c r="F143" s="9" t="n">
         <x:v>0</x:v>
@@ -13197,21 +15967,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="144" ht="356.3999938964844" hidden="0" customHeight="1">
+    <x:row r="144" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A144" s="40" t="n">
         <x:v>143</x:v>
       </x:c>
       <x:c r="B144" s="9" t="str">
-        <x:v>audi-s4-carbon-buildup-2010</x:v>
+        <x:v>audi-s8-mmi-upper-display-backup-camera-black-screen</x:v>
       </x:c>
       <x:c r="C144" s="9" t="str">
-        <x:v>2011-2012 | Audi | S4 | 3.0 TFSI</x:v>
+        <x:v>2020-2026 | Audi | S8 | VIN-specific NHTSA 25V900 / Audi 90TV; verify open recall | 4.0T TFSI V8 mild-hybrid</x:v>
       </x:c>
       <x:c r="D144" s="9" t="str">
-        <x:v>Fuel Rail or Seal Leak Creates Fire Risk (Recall 15V019 / 24AP)</x:v>
+        <x:v>2020-2026 S8 Rearview/Top-View Camera Image May Not Display - Recall 25V900</x:v>
       </x:c>
       <x:c r="E144" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel rails and corresponding seals free of charge under campaign 24AP. If fuel odor or leakage is present, stop driving and arrange immediate inspection.</x:v>
+        <x:v>Check the VIN in Audi’s recall/service-campaign lookup and schedule the free 90TV software remedy if open. Use extra care when reversing until repaired and visually check the area around the vehicle. A completely dead or rebooting MMI display, missing instrument-cluster data, wiring fault or hardware failure requires separate diagnosis and must not be attributed to this recall without VIN and symptom confirmation.</x:v>
       </x:c>
       <x:c r="F144" s="9" t="n">
         <x:v>0</x:v>
@@ -13220,21 +15990,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="145" ht="224.39999389648438" hidden="0" customHeight="1">
+    <x:row r="145" ht="792" hidden="0" customHeight="1">
       <x:c r="A145" s="40" t="n">
         <x:v>144</x:v>
       </x:c>
       <x:c r="B145" s="9" t="str">
-        <x:v>audi-s4-supercharger-nose-2010</x:v>
+        <x:v>audi-s8-oil-consumption-2013</x:v>
       </x:c>
       <x:c r="C145" s="9" t="str">
-        <x:v>2013-2015 | Audi | S4</x:v>
+        <x:v>2020-2023 | Audi | S8 | EA825 4.0L; confirm VIN, engine and measured consumption under Audi procedure | 4.0T TFSI V8 mild-hybrid (EA825)</x:v>
       </x:c>
       <x:c r="D145" s="9" t="str">
-        <x:v>Airbag-Control Software May Miss Front-Airbag Deployment After a Second Impact (Recall 14V667 / 69K5)</x:v>
+        <x:v>2020-2023 S8 High Oil Consumption and Updated Piston Rings - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E145" s="9" t="str">
-        <x:v>Check VIN eligibility and completion history. Audi dealers update the airbag control-unit software free of charge under campaign 69K5.</x:v>
+        <x:v>Document oil-level warnings, mileage, top-up quantity, leaks and oil specification, then have an Audi dealer perform the authorized oil-consumption measurement. Repair is justified only when the measured result exceeds the applicable owner-manual limit and other leakage or operating causes are excluded. If TSB 2071114 applies, follow its VIN/engine-specific piston, ring and connecting-rod procedure. Do not change oil viscosity or authorize internal-engine work solely from the former card.</x:v>
       </x:c>
       <x:c r="F145" s="9" t="n">
         <x:v>0</x:v>
@@ -13243,44 +16013,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="146" ht="198" hidden="0" customHeight="1">
+    <x:row r="146" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A146" s="40" t="n">
         <x:v>145</x:v>
       </x:c>
       <x:c r="B146" s="9" t="str">
-        <x:v>audi-s4-thermostat-2010</x:v>
+        <x:v>audi-s8-pcv-oil-separator-failure-excessive-crankcase-vacuum</x:v>
       </x:c>
       <x:c r="C146" s="9" t="str">
-        <x:v>2010-2025 | Audi | S4 | 3.0T</x:v>
+        <x:v>2013-2016 | Audi | S8 | 4.0 TFSI; confirm warm-idle sound and filler-cap response before oil-separator replacement | 4.0T TFSI V8</x:v>
       </x:c>
       <x:c r="D146" s="9" t="str">
-        <x:v>Thermostat Housing Failure and Coolant Leak</x:v>
+        <x:v>2013-2016 S8 Warm-Idle Whistle from Crankcase Breather Leak - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E146" s="9" t="str">
-        <x:v>Replace thermostat housing assembly with updated part. Use OEM or quality aftermarket housing with metal reinforcement.</x:v>
+        <x:v>Compare the sound with Audi’s reference condition and check whether opening the oil filler cap changes it. Read P2279/P0507 and rule out other intake leaks. When the sound matches and is affected by the filler-cap check, follow Audi’s oil-separator breather replacement procedure and renew required seals/consumables by VIN. Do not diagnose by oil-cap feel alone or order the former five-item parts list.</x:v>
       </x:c>
       <x:c r="F146" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G146" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="147" ht="963.5999755859375" hidden="0" customHeight="1">
+    <x:row r="147" ht="594" hidden="0" customHeight="1">
       <x:c r="A147" s="40" t="n">
         <x:v>146</x:v>
       </x:c>
       <x:c r="B147" s="9" t="str">
-        <x:v>audi-s5-b9-water-pump-2018</x:v>
+        <x:v>audi-s8-porous-high-pressure-fuel-supply-line-recall-nhtsa-19v057000</x:v>
       </x:c>
       <x:c r="C147" s="9" t="str">
-        <x:v>2018-2018 | Audi | S5 | 3.0L V6 TFSI EA839</x:v>
+        <x:v>2013-2016 | Audi | S8 | VIN-specific NHTSA 19V057 / Audi 20BM; verify open recall | 4.0T TFSI V8</x:v>
       </x:c>
       <x:c r="D147" s="9" t="str">
-        <x:v>2018 S5 3.0L Mechanical Coolant-Pump Fault P000000/33688 - Diagnosis Required</x:v>
+        <x:v>2013-2016 S8 Porous Fuel-Pump Supply Line / Fire Risk - Recall 19V057</x:v>
       </x:c>
       <x:c r="E147" s="9" t="str">
-        <x:v>Follow the bulletin in order. Verify coolant level; if low, inspect the cooling system for a leak and repair only the identified source or top up per Audi instructions when no leak is found. Check the ECM software level and apply the specified SVM update only when required. If the concern returns or software is current, test vacuum at N649 and inspect the solenoid and hoses. If the vacuum system works, apply vacuum to the pump hose and verify that the pump sleeve clicks; replace the mechanical coolant pump only when the sleeve does not operate. Use current Audi workshop and parts information.</x:v>
+        <x:v>Check the VIN for open recall 20BM and contact an Audi dealer without delay. The free remedy installs a fuel-pressure damper in the low-pressure fuel supply inside the tank. If fuel odor or visible leakage is present, avoid ignition sources, do not continue driving, and arrange dealer inspection/towing as appropriate. Do not buy a retail line or damper from the former card.</x:v>
       </x:c>
       <x:c r="F147" s="9" t="n">
         <x:v>0</x:v>
@@ -13289,21 +16059,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="148" ht="184.8000030517578" hidden="0" customHeight="1">
+    <x:row r="148" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A148" s="40" t="n">
         <x:v>147</x:v>
       </x:c>
       <x:c r="B148" s="9" t="str">
-        <x:v>audi-s5-carbon-buildup-2008</x:v>
+        <x:v>audi-s8-torque-converter-2013</x:v>
       </x:c>
       <x:c r="C148" s="9" t="str">
-        <x:v>2008-2025 | Audi | S5</x:v>
+        <x:v>2013-2024 | Audi | S8</x:v>
       </x:c>
       <x:c r="D148" s="9" t="str">
-        <x:v>Direct Injection Carbon Buildup</x:v>
+        <x:v>ZF 8-Speed Torque Converter and Valve Body Issues</x:v>
       </x:c>
       <x:c r="E148" s="9" t="str">
-        <x:v>Walnut blast intake valves every 40,000-60,000 miles. Install oil catch can to reduce oil vapor reaching valves.</x:v>
+        <x:v>Replace torque converter and service valve body. Full ZF fluid and filter change every 50,000 miles extends transmission life.</x:v>
       </x:c>
       <x:c r="F148" s="9" t="n">
         <x:v>0</x:v>
@@ -13312,44 +16082,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="149" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="149" ht="712.7999877929688" hidden="0" customHeight="1">
       <x:c r="A149" s="40" t="n">
         <x:v>148</x:v>
       </x:c>
       <x:c r="B149" s="9" t="str">
-        <x:v>audi-s5-crankshaft-pulley-2010</x:v>
+        <x:v>audi-s8-turbo-oil-strainer-2013</x:v>
       </x:c>
       <x:c r="C149" s="9" t="str">
-        <x:v>2010-2017 | Audi | S5 | Premium Plus, Prestige | 3.0T</x:v>
+        <x:v>2013-2017 | Audi | S8 | VIN-specific NHTSA 22V178 / Audi 21H7; verify open recall | 4.0T TFSI V8</x:v>
       </x:c>
       <x:c r="D149" s="9" t="str">
-        <x:v>Crankshaft Pulley (Harmonic Balancer) Failure (3.0T)</x:v>
+        <x:v>2013-2017 S8 Blocked Turbocharger Oil Strainer / Stall Risk - Recall 22V178</x:v>
       </x:c>
       <x:c r="E149" s="9" t="str">
-        <x:v>Replace crankshaft pulley/harmonic balancer with LATEST REVISION (revision F or later) part ($300-$600 for part, $800-$1,700 with labor). This is NOT a DIY-friendly repair—requires specialized holding tools and precise torque. If belts are damaged, replace serpentine belt and tensioner ($200-$400 additional). INSPECT: Check for collateral damage to supercharger snout, idler pulleys, and timing. If timing was affected, expect $3,000-$5,000 additional repair. PREVENTIVE: Inspect pulley for wobble at every oil change. Consider preemptive replacement at 80,000 miles on 2010-2013 models.</x:v>
+        <x:v>Check the VIN for open recall 21H7 and schedule the free Audi dealer remedy, which replaces the oil strainer and performs an oil change. If EPC, MIL or oil warning lights appear with unusual turbo noise, extended cranking, rough idle, loss of power or stalling, stop safely and arrange diagnosis. Turbo damage, warranty eligibility and any additional repair must be assessed by VIN and inspection; do not buy the former retail strainer.</x:v>
       </x:c>
       <x:c r="F149" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G149" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="150" ht="844.7999877929688" hidden="0" customHeight="1">
+    <x:row r="150" ht="950.4000244140625" hidden="0" customHeight="1">
       <x:c r="A150" s="40" t="n">
         <x:v>149</x:v>
       </x:c>
       <x:c r="B150" s="9" t="str">
-        <x:v>audi-s5-pcv-valve-failure-2010</x:v>
+        <x:v>audi-s8-water-to-air-intercooler-internal-coolant-leak</x:v>
       </x:c>
       <x:c r="C150" s="9" t="str">
-        <x:v>2010-2017 | Audi | S5 | 3.0L supercharged V6</x:v>
+        <x:v>2013-2018 | Audi | S8 | 4.0T TFSI V8 (CTFA/CGTA/CWUC)</x:v>
       </x:c>
       <x:c r="D150" s="9" t="str">
-        <x:v>2010-2017 S5 3.0L Crankcase-Breather P052E00 - Body/Year Diagnosis</x:v>
+        <x:v>Water-to-Air Intercooler Internal Coolant Leak (Coolant into Intake)</x:v>
       </x:c>
       <x:c r="E150" s="9" t="str">
-        <x:v>Verify the body style, model year and P052E00 condition first. For the applicable membrane branch, use the specified hand-vacuum test, then inspect the membrane and metal plates after compressor/intake-manifold removal; replace only the faulted membrane/plate repair kit or crankcase breather per current Audi instructions. If testing identifies the elbow branch, replace the elbow and hose clip as directed by TSB 2060259/1. Do not assume that both branches or unrelated cooling parts require replacement.</x:v>
+        <x:v>Confirm the source: pressure-test the cooling system and inspect the charge piping/intercooler outlet for coolant residue; scope for white smoke and coolant on the intake side rather than an external leak. Replace the water-to-air intercooler/charge-air cooler unit (genuine OEM core). Because access requires removing intake components in the valley, it is standard practice to also replace the turbo oil strainer, coolant valves, and PCV/oil separator while in there. Refill and bleed the cooling system per procedure. This is a high-difficulty job typically done by a specialist or dealer.</x:v>
       </x:c>
       <x:c r="F150" s="9" t="n">
         <x:v>0</x:v>
@@ -13358,21 +16128,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="151" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="151" ht="475.20001220703125" hidden="0" customHeight="1">
       <x:c r="A151" s="40" t="n">
         <x:v>150</x:v>
       </x:c>
       <x:c r="B151" s="9" t="str">
-        <x:v>audi-s5-supercharger-2008</x:v>
+        <x:v>audi-sq2-ea888-2-0-tfsi-coolant-leak-from-water-pump-thermostat-housi</x:v>
       </x:c>
       <x:c r="C151" s="9" t="str">
-        <x:v>2008-2025 | Audi | S5 | 3.0T</x:v>
+        <x:v>2019-2024 | Audi | SQ2 | 2.0 TFSI quattro | EA888 2.0 TFSI Gen3</x:v>
       </x:c>
       <x:c r="D151" s="9" t="str">
-        <x:v>3.0T Supercharger Intercooler Pump Failure</x:v>
+        <x:v>EA888 2.0 TFSI coolant leak from water pump / thermostat housing</x:v>
       </x:c>
       <x:c r="E151" s="9" t="str">
-        <x:v>Replace intercooler coolant pump. Check intercooler lines for leaks and flush the circuit during replacement.</x:v>
+        <x:v>Replace the failed water pump / thermostat housing assembly, ideally with the latest revised, more heat-resistant unit; many shops fit an upgraded repair kit and a new gasket. Catch it early by watching for slowly dropping coolant level and a faint sweet smell. Combine with a coolant flush and refill.</x:v>
       </x:c>
       <x:c r="F151" s="9" t="n">
         <x:v>0</x:v>
@@ -13381,21 +16151,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="152" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="152" ht="396" hidden="0" customHeight="1">
       <x:c r="A152" s="40" t="n">
         <x:v>151</x:v>
       </x:c>
       <x:c r="B152" s="9" t="str">
-        <x:v>audi-s5-thermostat-2008</x:v>
+        <x:v>audi-sq2-electro-mechanical-parking-brake-brake-pedal-weld-recalls</x:v>
       </x:c>
       <x:c r="C152" s="9" t="str">
-        <x:v>2008-2025 | Audi | S5 | 3.0T</x:v>
+        <x:v>2019-2020 | Audi | SQ2</x:v>
       </x:c>
       <x:c r="D152" s="9" t="str">
-        <x:v>Thermostat and Water Pump Assembly Failure</x:v>
+        <x:v>Electro-mechanical parking brake and brake-pedal weld recalls (early build)</x:v>
       </x:c>
       <x:c r="E152" s="9" t="str">
-        <x:v>Replace thermostat/water pump assembly. Upgrade to revised housing if available.</x:v>
+        <x:v>These are recall items — have the VIN checked against the Audi/DVSA recall database and any open campaign rectified free of charge at a dealer. Report any abnormal parking-brake behaviour or a soft/abnormal brake pedal immediately.</x:v>
       </x:c>
       <x:c r="F152" s="9" t="n">
         <x:v>0</x:v>
@@ -13404,21 +16174,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="153" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="153" ht="475.20001220703125" hidden="0" customHeight="1">
       <x:c r="A153" s="40" t="n">
         <x:v>152</x:v>
       </x:c>
       <x:c r="B153" s="9" t="str">
-        <x:v>audi-s6-air-suspension-2013</x:v>
+        <x:v>audi-sq2-internal-fuse-box-wiring-harness-can-work-loose-causing-sudd</x:v>
       </x:c>
       <x:c r="C153" s="9" t="str">
-        <x:v>2013-2013 | Audi | S6 | 4.0T</x:v>
+        <x:v>2022-2023 | Audi | SQ2 | 2.0 TFSI</x:v>
       </x:c>
       <x:c r="D153" s="9" t="str">
-        <x:v>2013 Audi S6 Air-Suspension Compressor or Relay Fault - Diagnosis Required</x:v>
+        <x:v>2022-2023 Audi SQ2 Interior Fuse-Carrier Recall GAI-3692</x:v>
       </x:c>
       <x:c r="E153" s="9" t="str">
-        <x:v>Have an Audi-qualified technician test the air-suspension compressor and inspect relay J403. Audi directs replacement of both the compressor and relay when the relay has severe contact erosion or an overheated strand; when the compressor sounds normal and the relay has only minor contact marks, replace the relay only. A sagging corner or leak-down condition requires separate leak localization before any strut is replaced. Do not order the former strut or compressor recommendations from this card.</x:v>
+        <x:v>Check the VIN and open-campaign status with an authorised Audi dealer in the vehicle’s market. The campaign remedy is dealer inspection and correction of the fuse-carrier power connection. Do not replace a fuse box or wiring harness solely from a warning lamp or this model-year summary.</x:v>
       </x:c>
       <x:c r="F153" s="9" t="n">
         <x:v>0</x:v>
@@ -13427,21 +16197,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="154" ht="1359.5999755859375" hidden="0" customHeight="1">
+    <x:row r="154" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A154" s="40" t="n">
         <x:v>153</x:v>
       </x:c>
       <x:c r="B154" s="9" t="str">
-        <x:v>audi-s6-c7-carbon-buildup-2013</x:v>
+        <x:v>audi-sq2-mmi-infotainment-freezing-rebooting-lost-settings</x:v>
       </x:c>
       <x:c r="C154" s="9" t="str">
-        <x:v>2013-2018 | Audi | S6 | 4.0T</x:v>
+        <x:v>2019-2024 | Audi | SQ2</x:v>
       </x:c>
       <x:c r="D154" s="9" t="str">
-        <x:v>4.0T Carbon Buildup on Intake Valves</x:v>
+        <x:v>MMI infotainment freezing, rebooting and lost settings</x:v>
       </x:c>
       <x:c r="E154" s="9" t="str">
-        <x:v>Confirm carbon buildup by scanning for misfire faults (commonly random/multiple or cylinder-specific misfires), reviewing fuel trims, and inspecting the intake valves with a borescope after removing the intake manifold or accessing the ports. The proper repair is an intake valve carbon cleaning, typically walnut shell blasting each intake port with the valves closed, then replacing intake manifold gaskets, injector seals/O-rings or any disturbed PCV-related seals as needed and clearing/adapting the ECU afterward. If buildup is severe or returns quickly, inspect the PCV/oil separator system and crankcase ventilation hoses for excessive oil carryover. Independent shops typically charge about $800-$1,500 for a full walnut blast service on the 4.0T, while dealer pricing can run roughly $1,500-$2,500 depending on labor and gasket/seal replacement.</x:v>
+        <x:v>A forced MMI restart (press and hold the on/off or volume control ~10 seconds until it reboots) clears many transient faults. Persistent issues are usually resolved by a dealer software/firmware update; check for any applicable MMI update campaigns. Only in rare cases is the MMI head unit itself replaced.</x:v>
       </x:c>
       <x:c r="F154" s="9" t="n">
         <x:v>0</x:v>
@@ -13450,21 +16220,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="155" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="155" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A155" s="40" t="n">
         <x:v>154</x:v>
       </x:c>
       <x:c r="B155" s="9" t="str">
-        <x:v>audi-s6-carbon-buildup-2013</x:v>
+        <x:v>audi-sq2-pcv-crankcase-ventilation-valve-diaphragm-failure-causing-ro</x:v>
       </x:c>
       <x:c r="C155" s="9" t="str">
-        <x:v>2013-2024 | Audi | S6 | 4.0T</x:v>
+        <x:v>2019-2024 | Audi | SQ2 | EA888 2.0 TFSI Gen3</x:v>
       </x:c>
       <x:c r="D155" s="9" t="str">
-        <x:v>4.0T Direct Injection Carbon Buildup</x:v>
+        <x:v>PCV / crankcase ventilation valve diaphragm failure causing rough idle and lean-running codes</x:v>
       </x:c>
       <x:c r="E155" s="9" t="str">
-        <x:v>Walnut blast all eight intake runners. Dual-injection models (2019+) are less affected.</x:v>
+        <x:v>Replace the PCV valve (or the valve-cover assembly that integrates it) with the latest revised part; some owners fit a catch-can to reduce recurrence. A quick field test — briefly covering the bleeder hole on the cap to see if idle stabilises or whistling stops — helps confirm before replacement.</x:v>
       </x:c>
       <x:c r="F155" s="9" t="n">
         <x:v>0</x:v>
@@ -13473,21 +16243,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" ht="462" hidden="0" customHeight="1">
+    <x:row r="156" ht="752.4000244140625" hidden="0" customHeight="1">
       <x:c r="A156" s="40" t="n">
         <x:v>155</x:v>
       </x:c>
       <x:c r="B156" s="9" t="str">
-        <x:v>audi-s6-rearview-camera-image-failure-from-software-error</x:v>
+        <x:v>audi-sq2-s-tronic-7-speed-wet-clutch-transmission-jerky-low-speed-shi</x:v>
       </x:c>
       <x:c r="C156" s="9" t="str">
-        <x:v>2020-2025 | Audi | S6</x:v>
+        <x:v>2019-2024 | Audi | SQ2 | 7-speed S tronic | DQ381 / 0GC 7-speed wet-clutch S tronic</x:v>
       </x:c>
       <x:c r="D156" s="9" t="str">
-        <x:v>2020-2025 Audi S6 Rearview Camera Software Recall 25V900 / 90TV</x:v>
+        <x:v>S tronic (DQ381) 7-speed wet-clutch transmission: jerky low-speed shifts, hesitation and limp mode</x:v>
       </x:c>
       <x:c r="E156" s="9" t="str">
-        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install the more robust driver-assistance software update free of charge. Until repaired, use extra caution when reversing and do not treat a restart or temporary image recovery as completion of the recall.</x:v>
+        <x:v>First step is a proper DSG fluid-and-filter service (the wet-clutch unit needs periodic transmission oil changes — many owners do it around 40k miles even though intervals can be longer). Have the TCU scanned for stored codes; sensor or mechatronic valve replacement and re-coding/adaptation resolves many cases, while severe cases need a full mechatronic unit or clutch-pack replacement. Insist on a software/adaptation update at the dealer for driveability complaints.</x:v>
       </x:c>
       <x:c r="F156" s="9" t="n">
         <x:v>0</x:v>
@@ -13496,21 +16266,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="157" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="157" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A157" s="40" t="n">
         <x:v>156</x:v>
       </x:c>
       <x:c r="B157" s="9" t="str">
-        <x:v>audi-s6-takata-passenger-airbag-inflator-recall</x:v>
+        <x:v>audi-sq5-air-suspension-2018</x:v>
       </x:c>
       <x:c r="C157" s="9" t="str">
-        <x:v>2007-2011 | Audi | S6</x:v>
+        <x:v>2018-2025 | Audi | SQ5</x:v>
       </x:c>
       <x:c r="D157" s="9" t="str">
-        <x:v>2007-2011 Audi S6 Takata Passenger-Airbag Recall 18V427 / 69R7</x:v>
+        <x:v>Air-Suspension Warning with C1260F0 or U112100 Communication Fault</x:v>
       </x:c>
       <x:c r="E157" s="9" t="str">
-        <x:v>Check the VIN for recall 18V427/69R7 and arrange the free final passenger-frontal-airbag replacement with an Audi dealer. Do not use an airbag warning light to determine recall eligibility; Audi states that the warning light is unrelated to this inflator defect.</x:v>
+        <x:v>Inspect the wiring and connector contacts between J775 and J1135 first. If no wiring fault is found, clear a first passive or sporadic fault and release the vehicle. Replace J1135 for an active or static fault, or when the same passive or sporadic fault returns a second time, following Audi workshop information and VIN-specific ETKA data.</x:v>
       </x:c>
       <x:c r="F157" s="9" t="n">
         <x:v>0</x:v>
@@ -13519,20 +16289,22 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="158" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="158" ht="924" hidden="0" customHeight="1">
       <x:c r="A158" s="40" t="n">
         <x:v>157</x:v>
       </x:c>
       <x:c r="B158" s="9" t="str">
-        <x:v>audi-s6-transmission-valve-body-2002</x:v>
+        <x:v>audi-sq5-carbon-buildup-2014</x:v>
       </x:c>
       <x:c r="C158" s="9" t="str">
-        <x:v>2002-2004 | Audi | S6</x:v>
+        <x:v>2014-2025 | Audi | SQ5 | 3.0T Supercharged, 3.0T</x:v>
       </x:c>
       <x:c r="D158" s="9" t="str">
-        <x:v>ZF 5HP24 Tiptronic Transmission Valve Body Failure</x:v>
-      </x:c>
-      <x:c r="E158" s="9" t="str"/>
+        <x:v>Fuel-Quality or Deposit-Related Rough Running and Misfire Diagnosis</x:v>
+      </x:c>
+      <x:c r="E158" s="9" t="str">
+        <x:v>Confirm fuel quality, symptoms and stored DTCs before replacing or cleaning components. If contaminated gasoline is suspected, advise changing the fuel source; if low detergent quality is suspected, Audi recommends Top Tier detergent gasoline. Continue workshop diagnosis if symptoms persist. On 2018-2025 EA839 SQ5 models, do not recommend unapproved cleaners or additives; follow the owner manual and use only Audi-approved petrol additives. Do not prescribe routine walnut blasting, a catch can or chemical cleaning from this record.</x:v>
+      </x:c>
       <x:c r="F158" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -13540,21 +16312,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="159" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="159" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A159" s="40" t="n">
         <x:v>158</x:v>
       </x:c>
       <x:c r="B159" s="9" t="str">
-        <x:v>audi-s6-turbo-coolant-2013</x:v>
+        <x:v>audi-sq5-pcv-valve-2014</x:v>
       </x:c>
       <x:c r="C159" s="9" t="str">
-        <x:v>2013-2013 | Audi | S6 | 4.0T</x:v>
+        <x:v>2014-2017 | Audi | SQ5 | 3.0T Supercharged</x:v>
       </x:c>
       <x:c r="D159" s="9" t="str">
-        <x:v>2013 Audi S6 Turbocharger Coolant-Pipe Seepage - Diagnosis Required</x:v>
+        <x:v>P052E00 Crankcase-Breather Membrane or Elbow Fault</x:v>
       </x:c>
       <x:c r="E159" s="9" t="str">
-        <x:v>Confirm the leak source and VIN applicability before ordering parts. For the TSB condition, Audi specifies replacing the coolant feed and return pipes on both cylinder banks, replacing the disturbed oil-feed-pipe O-rings, then refilling and bleeding the cooling system. Service Action 21F7 was VIN-specific and expired in 2019, so current coverage must not be assumed. Do not order the former single pipe or alleged silicone-line kit from this card.</x:v>
+        <x:v>Use Audi hand-vacuum test to distinguish a membrane leak from an elbow fault. If indicated, remove the compressor or intake manifold and inspect the membrane and the breather two metal plates. Use repair kit 06E103772H only for a confirmed membrane or plate fault. For a confirmed elbow fault, replace elbow 06E103402 and spring clip N10769401 rather than automatically replacing the complete breather. Verify current part data in ETKA before ordering.</x:v>
       </x:c>
       <x:c r="F159" s="9" t="n">
         <x:v>0</x:v>
@@ -13563,21 +16335,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="160" ht="290.3999938964844" hidden="0" customHeight="1">
+    <x:row r="160" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A160" s="40" t="n">
         <x:v>159</x:v>
       </x:c>
       <x:c r="B160" s="9" t="str">
-        <x:v>audi-s7-air-suspension-2012</x:v>
+        <x:v>audi-sq5-supercharger-2014</x:v>
       </x:c>
       <x:c r="C160" s="9" t="str">
-        <x:v>2020-2021 | Audi | S7</x:v>
+        <x:v>2014-2018 | Audi | SQ5 | 3.0T</x:v>
       </x:c>
       <x:c r="D160" s="9" t="str">
-        <x:v>Rear-Axle Lock Nut and Alignment Recall Follow-Up (21V295 / 22V034)</x:v>
+        <x:v>3.0T Supercharger Bearing and Intercooler Pump Failure</x:v>
       </x:c>
       <x:c r="E160" s="9" t="str">
-        <x:v>Check the VIN for both campaigns 42L1 and 42L5. Audi dealers replace affected nuts and bolts, inspect and adjust rear alignment, and replace qualifying unevenly worn tires free of charge.</x:v>
+        <x:v>Replace supercharger nose bearing kit. Replace intercooler pump if failing. Service supercharger belt tension.</x:v>
       </x:c>
       <x:c r="F160" s="9" t="n">
         <x:v>0</x:v>
@@ -13586,21 +16358,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="161" ht="237.60000610351562" hidden="0" customHeight="1">
+    <x:row r="161" ht="844.7999877929688" hidden="0" customHeight="1">
       <x:c r="A161" s="40" t="n">
         <x:v>160</x:v>
       </x:c>
       <x:c r="B161" s="9" t="str">
-        <x:v>audi-s7-biturbo-coolant-2012</x:v>
+        <x:v>audi-sq5-supercharger-oil-leak-2014</x:v>
       </x:c>
       <x:c r="C161" s="9" t="str">
-        <x:v>2013-2014 | Audi | S7 | 4.0 TFSI</x:v>
+        <x:v>2014-2017 | Audi | SQ5 | Premium Plus, Prestige | 3.0T Supercharged, 3.0T</x:v>
       </x:c>
       <x:c r="D161" s="9" t="str">
-        <x:v>4.0L Fuel Line Can Leak and Create a Fire Risk (Recall 13V450 / 20U6)</x:v>
+        <x:v>Supercharger Seal and Gasket Oil Leaks (3.0T)</x:v>
       </x:c>
       <x:c r="E161" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel line free of charge under campaign 20U6/L8. Stop driving if fuel odor or leakage is present.</x:v>
+        <x:v>JHM Motorsports sells a complete supercharger replacement seal and gasket kit for the Eaton unit in the 3.0T. Replacing all seals at once is recommended since the supercharger must be removed for access. Nose cone seal, rotor shaft seals, and manifold gaskets should all be replaced together ($300-$500 in parts, $600-$1,200 labor). While the supercharger is off, also replace the PCV valve and perform carbon cleaning. For valve cover gasket leaks (separate issue), budget $400-$800 parts and labor. Monitor oil level weekly if leaks are present.</x:v>
       </x:c>
       <x:c r="F161" s="9" t="n">
         <x:v>0</x:v>
@@ -13609,21 +16381,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="162" ht="264" hidden="0" customHeight="1">
+    <x:row r="162" ht="1122" hidden="0" customHeight="1">
       <x:c r="A162" s="40" t="n">
         <x:v>161</x:v>
       </x:c>
       <x:c r="B162" s="9" t="str">
-        <x:v>audi-s7-carbon-buildup-4.0t-2012</x:v>
+        <x:v>audi-sq5-water-pump-2018</x:v>
       </x:c>
       <x:c r="C162" s="9" t="str">
-        <x:v>2021-2021 | Audi | S7</x:v>
+        <x:v>2018-2024 | Audi | SQ5 | 3.0T</x:v>
       </x:c>
       <x:c r="D162" s="9" t="str">
-        <x:v>Rear Seat-Belt Retractor Can Release a Child Restraint Early (Recall 21V606 / 69CS)</x:v>
+        <x:v>Mechanical Coolant-Pump Leak with Possible N649 Vacuum-System Contamination</x:v>
       </x:c>
       <x:c r="E162" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers inspect and replace the affected middle-rear seat-belt assembly as necessary free of charge under campaign 69CS.</x:v>
+        <x:v>Confirm the complaint and exact vehicle criteria first. Inspect the vacuum line and N649 for coolant, then clean and dry suspected leakage, fill the cooling system correctly, inspect at idle and around 2,500 rpm, and pressure-test according to Audi workshop information. If no leak is reproduced, observe the vehicle without replacing parts. If the pump leak is confirmed, replace the failed component and document it. If fresh coolant has entered the vacuum system, inspect the remaining Audi checkpoints and replace only contaminated components; if the downstream checkpoints are clean, replace N649 and clean the line between the pump and N649 as directed by TSB 2070349/5.</x:v>
       </x:c>
       <x:c r="F162" s="9" t="n">
         <x:v>0</x:v>
@@ -13632,21 +16404,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="163" ht="237.60000610351562" hidden="0" customHeight="1">
+    <x:row r="163" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A163" s="40" t="n">
         <x:v>162</x:v>
       </x:c>
       <x:c r="B163" s="9" t="str">
-        <x:v>audi-s7-cylinder-demand-rough-running-hesitation</x:v>
+        <x:v>audi-sq7-air-susp-strut-2020</x:v>
       </x:c>
       <x:c r="C163" s="9" t="str">
-        <x:v>2021-2021 | Audi | S7</x:v>
+        <x:v>2020-2025 | Audi | SQ7 | 4.0T</x:v>
       </x:c>
       <x:c r="D163" s="9" t="str">
-        <x:v>Instrument Panel May Fail to Display Critical Safety Information (Recall 25V201 / 90VC)</x:v>
+        <x:v>2020-2025 SQ7 Air-Suspension C1260F0/U112100 Communication Fault - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E163" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history. Audi dealers update the instrument-panel module software free of charge under campaign 90VC.</x:v>
+        <x:v>Inspect the wiring and connector contacts between J775 and J1135 first. If no wiring fault is found, clear a first passive or sporadic fault and release the vehicle. Replace J1135 for an active or static fault, or when the same passive or sporadic fault returns a second time, following Audi workshop information and VIN-specific ETKA data. Do not replace an air spring, strut or compressor assembly solely from the warning.</x:v>
       </x:c>
       <x:c r="F163" s="9" t="n">
         <x:v>0</x:v>
@@ -13655,21 +16427,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="164" ht="316.79998779296875" hidden="0" customHeight="1">
+    <x:row r="164" ht="1122" hidden="0" customHeight="1">
       <x:c r="A164" s="40" t="n">
         <x:v>163</x:v>
       </x:c>
       <x:c r="B164" s="9" t="str">
-        <x:v>audi-s7-ea839-2-9t-v6-water-pump-internal-leak-overheating</x:v>
+        <x:v>audi-sq7-air-suspension-2020</x:v>
       </x:c>
       <x:c r="C164" s="9" t="str">
-        <x:v>2020-2024 | Audi | S7</x:v>
+        <x:v>2020-2024 | Audi | SQ7 | Premium Plus, Prestige | 4.0T</x:v>
       </x:c>
       <x:c r="D164" s="9" t="str">
-        <x:v>Rearview Camera Image May Not Display (Recall 25V900 / 90TV)</x:v>
+        <x:v>Adaptive Air Suspension Compressor and Air Spring Failures</x:v>
       </x:c>
       <x:c r="E164" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history. Audi dealers update the relevant software free of charge under campaign 90TV. Continue direct visual checks when reversing until repaired.</x:v>
+        <x:v>Diagnose specific failed component: air springs leak most commonly, followed by compressor burnout, valve block faults, and height sensor failures. Air spring replacement ($800-$1,500 per corner at independent shop). Compressor replacement ($1,200-$2,500 installed). Valve block: $500-$1,000. Height sensor: $200-$400. Check for air leaks first using soapy water spray before replacing the compressor - a $200 air spring seal may be causing a $2,000 compressor to overwork and fail. Aftermarket solutions from Arnott offer cost savings. Converting to conventional springs ($1,500-$2,500) eliminates future air suspension costs but sacrifices ride height adjustment.</x:v>
       </x:c>
       <x:c r="F164" s="9" t="n">
         <x:v>0</x:v>
@@ -13678,21 +16450,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="165" ht="343.20001220703125" hidden="0" customHeight="1">
+    <x:row r="165" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A165" s="40" t="n">
         <x:v>164</x:v>
       </x:c>
       <x:c r="B165" s="9" t="str">
-        <x:v>audi-s7-electromechanical-steering-rack-torque-sensor-failure-causin</x:v>
+        <x:v>audi-sq7-mmi-mib3-freeze-2020</x:v>
       </x:c>
       <x:c r="C165" s="9" t="str">
-        <x:v>2021-2021 | Audi | S7</x:v>
+        <x:v>2020-2026 | Audi | SQ7</x:v>
       </x:c>
       <x:c r="D165" s="9" t="str">
-        <x:v>Incorrect Brake-Fluid Reservoir Cap Label (Recall 23V601 / 47T9)</x:v>
+        <x:v>2020-2026 Audi SQ7 Rearview Camera Software Recall 25V900 / 90TV</x:v>
       </x:c>
       <x:c r="E165" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers inspect the reservoir cap and replace it when necessary free of charge under campaign 47T9. Use only the brake-fluid specification in the owner and service information.</x:v>
+        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install the more robust driver-assistance software update free of charge. Until repaired, use extra caution when reversing and do not treat a restart, bus sleep or temporary image recovery as completion of the recall.</x:v>
       </x:c>
       <x:c r="F165" s="9" t="n">
         <x:v>0</x:v>
@@ -13701,44 +16473,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="166" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="166" ht="990" hidden="0" customHeight="1">
       <x:c r="A166" s="40" t="n">
         <x:v>165</x:v>
       </x:c>
       <x:c r="B166" s="9" t="str">
-        <x:v>audi-s7-front-control-arm-bushing-ball-joint-failure</x:v>
+        <x:v>audi-sq7-valve-cover-oil-leak-2020</x:v>
       </x:c>
       <x:c r="C166" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+        <x:v>2020-2024 | Audi | SQ7 | 4.0T</x:v>
       </x:c>
       <x:c r="D166" s="9" t="str">
-        <x:v>Front Control Arm Bushing and Ball Joint Failure (C7 Suspension)</x:v>
+        <x:v>2020-2024 SQ7 4.0L High Oil Consumption and Piston-Ring Diagnosis - TSB 2071114/5</x:v>
       </x:c>
       <x:c r="E166" s="9" t="str">
-        <x:v>Inspect all front control arms for play in the bushings and ball joints. Replace worn arms — many owners do the full front control-arm set (commonly a 16-piece kit covering both sides) to avoid repeat visits since the labor overlaps. Critical install notes: torque the bushing bolts at ride height (not with the suspension hanging) to avoid pre-loading and destroying the new bushings, and perform a four-wheel alignment afterward.</x:v>
+        <x:v>First inspect for visible engine-oil traces or leaks. Have an Audi dealer perform the authorized ODIS oil-consumption measurement, preserve and upload both test logs, and document the requested driving-profile data. Internal-engine repair is justified only when measured consumption exceeds the applicable limit and no other cause is found. If every TSB gate is met, follow Audi's VIN-, engine-code- and power-class-specific procedure for replacement of all eight pistons and piston rings, using current ETKA and ELSA information. Do not diagnose valve-cover gaskets or turbocharger seals from oil consumption alone.</x:v>
       </x:c>
       <x:c r="F166" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G166" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="167" ht="396" hidden="0" customHeight="1">
+    <x:row r="167" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A167" s="40" t="n">
         <x:v>166</x:v>
       </x:c>
       <x:c r="B167" s="9" t="str">
-        <x:v>audi-s7-fuel-injector-deposits-failure-causing-misfire-rough-running</x:v>
+        <x:v>audi-sq8-air-susp-compressor-2020</x:v>
       </x:c>
       <x:c r="C167" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
+        <x:v>2020-2025 | Audi | SQ8</x:v>
       </x:c>
       <x:c r="D167" s="9" t="str">
-        <x:v>Fuel Injector Deposits / Failure Causing Misfire and Rough Running (4.0T V8)</x:v>
+        <x:v>2020-2025 SQ8 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
       </x:c>
       <x:c r="E167" s="9" t="str">
-        <x:v>Pull misfire counts per cylinder to localize the fault. Inspect/replace failed or leaking injectors and renew injector seals; replace spark plugs and any weak coils as a set. Confirm fuel trims return to normal and clear codes; address intake carbon if present.</x:v>
+        <x:v>Inspect the wiring and connector contacts between J775 and J1135 before replacing a component. For a first passive or sporadic occurrence, clear the fault and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after wiring inspection, Audi directs replacement of J1135 under current repair and parts information. Do not buy struts, springs or a compressor solely from this warning.</x:v>
       </x:c>
       <x:c r="F167" s="9" t="n">
         <x:v>0</x:v>
@@ -13747,21 +16519,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="168" ht="396" hidden="0" customHeight="1">
+    <x:row r="168" ht="831.5999755859375" hidden="0" customHeight="1">
       <x:c r="A168" s="40" t="n">
         <x:v>167</x:v>
       </x:c>
       <x:c r="B168" s="9" t="str">
-        <x:v>audi-s7-gateway-control-module-shutdown-from-rear-seat-liquid-spill</x:v>
+        <x:v>audi-sq8-air-suspension-2020</x:v>
       </x:c>
       <x:c r="C168" s="9" t="str">
-        <x:v>2020-2022 | Audi | S7 | 2.9 TFSI</x:v>
+        <x:v>2020-2024 | Audi | SQ8 | Premium Plus, Prestige | 4.0T</x:v>
       </x:c>
       <x:c r="D168" s="9" t="str">
-        <x:v>Rear-Seat Liquid Spill Can Shut Down Gateway Module (Recall 22V861 / 90V2)</x:v>
+        <x:v>Adaptive Air Suspension Compressor and Air Spring Failures</x:v>
       </x:c>
       <x:c r="E168" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers install a protective gateway-module cover free of charge under campaign 90V2. If multiple warnings or reduced power occur after a spill, move out of traffic safely and arrange dealer inspection.</x:v>
+        <x:v>Same diagnostic and repair approach as SQ7 (shared 4M platform). Isolate the failed component: air springs ($800-$1,500 per corner), compressor ($1,200-$2,500), valve block ($500-$1,000), or height sensor ($200-$400). Always check for air leaks before replacing the compressor. Aftermarket air suspension components from Arnott/Strutmasters offer 40-50% savings over OEM. Annual inspection of air springs for cracking recommended, especially in hot climates where UV and heat accelerate rubber degradation.</x:v>
       </x:c>
       <x:c r="F168" s="9" t="n">
         <x:v>0</x:v>
@@ -13770,21 +16542,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="169" ht="528" hidden="0" customHeight="1">
+    <x:row r="169" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A169" s="40" t="n">
         <x:v>168</x:v>
       </x:c>
       <x:c r="B169" s="9" t="str">
-        <x:v>audi-s7-high-pressure-fuel-pump-failure-causing-hard-start-power-los</x:v>
+        <x:v>audi-sq8-airbag-mount-2023</x:v>
       </x:c>
       <x:c r="C169" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
+        <x:v>2023-2024 | Audi | SQ8 | 4.0T V8</x:v>
       </x:c>
       <x:c r="D169" s="9" t="str">
-        <x:v>High-Pressure Fuel Pump (HPFP) Failure Causing Hard Start and Power Loss (4.0T V8)</x:v>
+        <x:v>2023-2024 SQ8 Driver-Seat Side-Airbag Mount Recall 69GA (23V868)</x:v>
       </x:c>
       <x:c r="E169" s="9" t="str">
-        <x:v>Diagnose with live fuel-rail pressure data before condemning the pump, as a faulty low-pressure sensor or in-tank pump can set the same codes. Replace the failed high-pressure pump (the affected bank, or both as a set on high-mileage cars) together with the cam follower and seals. Verify low-pressure (in-tank) supply is within spec.</x:v>
+        <x:v>Check the VIN for open Audi recall 69GA and have an authorized dealer inspect the driver-seat side-airbag installation. If needed, the dealer will reinstall the airbag correctly; the recall filing says no parts are replaced. A clock spring or generic airbag part is not the recall remedy.</x:v>
       </x:c>
       <x:c r="F169" s="9" t="n">
         <x:v>0</x:v>
@@ -13793,44 +16565,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="170" ht="660" hidden="0" customHeight="1">
+    <x:row r="170" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A170" s="40" t="n">
         <x:v>169</x:v>
       </x:c>
       <x:c r="B170" s="9" t="str">
-        <x:v>audi-s7-ignition-coil-pack-failure-causing-misfires</x:v>
+        <x:v>audi-sq8-mmi-mib3-freeze-2020</x:v>
       </x:c>
       <x:c r="C170" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+        <x:v>2020-2026 | Audi | SQ8 | 4.0T V8</x:v>
       </x:c>
       <x:c r="D170" s="9" t="str">
-        <x:v>Ignition Coil Pack Failure Causing Misfires (4.0T V8)</x:v>
+        <x:v>2020-2026 SQ8 Rearview Camera Software Recall 90TV (25V900)</x:v>
       </x:c>
       <x:c r="E170" s="9" t="str">
-        <x:v>Confirm the failing cylinder, then swap the suspect coil to another cylinder to verify the fault follows the coil. Replace the failed coil; best practice on the 4.0T is to replace all eight coils and the spark plugs as a set since the access labor is shared and mixed-age coils tend to fail in sequence. Use OE or quality OE-equivalent coils (the 4.0T uses the 079905110-series coil). Inspect spark plugs for fouling/oil that could indicate a secondary issue.</x:v>
+        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install more robust driver-assistance software free of charge. Until repaired, use extra caution when reversing and do not treat a restart, bus sleep or temporary image recovery as completion of the recall. A generic scan tool or head-unit replacement is not the recall remedy.</x:v>
       </x:c>
       <x:c r="F170" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G170" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="171" ht="237.60000610351562" hidden="0" customHeight="1">
+    <x:row r="171" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A171" s="40" t="n">
         <x:v>170</x:v>
       </x:c>
       <x:c r="B171" s="9" t="str">
-        <x:v>audi-s7-motor-mount-failure-2012</x:v>
+        <x:v>audi-sq8-turbo-coolant-2020</x:v>
       </x:c>
       <x:c r="C171" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7</x:v>
+        <x:v>2020-2021 | Audi | SQ8 | 4.0T V8</x:v>
       </x:c>
       <x:c r="D171" s="9" t="str">
-        <x:v>Passenger Occupant Detection Mat Can Disable the Airbag (Recall 18V370 / 74D5)</x:v>
+        <x:v>2020-Early 2021 SQ8 Red Coolant Warning - Check G407 per TSB 2062951/4</x:v>
       </x:c>
       <x:c r="E171" s="9" t="str">
-        <x:v>Check VIN eligibility because seat equipment affects scope. Audi dealers install the occupant-detection repair kit free of charge under campaign 74D5.</x:v>
+        <x:v>Have the vehicle checked with Audi Guided Fault Finding and inspect G407 and its O-ring. Replace G407 only if the O-ring is damaged or pinched and the diagnosis matches the bulletin; follow the related Audi diagnostic path if additional listed faults are stored. Do not replace turbo coolant hoses, pumps or other cooling parts from this card alone.</x:v>
       </x:c>
       <x:c r="F171" s="9" t="n">
         <x:v>0</x:v>
@@ -13839,21 +16611,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="172" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="172" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A172" s="40" t="n">
         <x:v>171</x:v>
       </x:c>
       <x:c r="B172" s="9" t="str">
-        <x:v>audi-s7-pcv-oil-separator-failure-causing-oil-consumption-whistling</x:v>
+        <x:v>audi-tt-absesp-control-module-failure-2000</x:v>
       </x:c>
       <x:c r="C172" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
+        <x:v>2000-2001 | Audi | TT</x:v>
       </x:c>
       <x:c r="D172" s="9" t="str">
-        <x:v>PCV / Oil Separator (Ölabscheider) Failure Causing Oil Consumption and Whistling (4.0T V8)</x:v>
+        <x:v>Driver Airbag Inflator May Deploy Improperly (Recall 21V470 / 69CJ)</x:v>
       </x:c>
       <x:c r="E172" s="9" t="str">
-        <x:v>Replace the failed oil separator / PCV assembly and the associated breather hose with the latest revised part. An ECM update may accompany the new part on some VINs. Confirm with a smoke test for intake-side vacuum leaks; inspect the rear main seal if oil consumption is severe, as a failed PCV is a common cause of rear main seal damage on these engines.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the driver frontal-airbag inflator with an alternative inflator free of charge under campaign 69CJ.</x:v>
       </x:c>
       <x:c r="F172" s="9" t="n">
         <x:v>0</x:v>
@@ -13862,21 +16634,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="173" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="173" ht="277.20001220703125" hidden="0" customHeight="1">
       <x:c r="A173" s="40" t="n">
         <x:v>172</x:v>
       </x:c>
       <x:c r="B173" s="9" t="str">
-        <x:v>audi-s7-power-liftgate-motor-gas-strut-failure</x:v>
+        <x:v>audi-tt-cam-follower-2008</x:v>
       </x:c>
       <x:c r="C173" s="9" t="str">
-        <x:v>2013-2022 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824), 2.9T TFSI Biturbo V6 (EA839)</x:v>
+        <x:v>2000-2000 | Audi | TT</x:v>
       </x:c>
       <x:c r="D173" s="9" t="str">
-        <x:v>Power Liftgate Motor and Gas Strut Failure (Sportback Tailgate)</x:v>
+        <x:v>Fuel-Line Assembly Can Leak (Recall 99V222)</x:v>
       </x:c>
       <x:c r="E173" s="9" t="str">
-        <x:v>Diagnose whether the fault is the gas struts (won't stay up / weak lift), the spindle lift motors (slow or struggling travel), or the latch/cinching motor (won't release or won't pull closed — see TSB 2072431/1). Replace worn gas struts in pairs; replace failed lift or cinching motors as needed. After repair, perform the power-liftgate relearn/reset procedure so travel limits recalibrate.</x:v>
+        <x:v>Check VIN eligibility and campaign completion. Audi dealers replace the fuel-line assembly free of charge under recall 99V222. Stop driving if fuel odor or leakage is present.</x:v>
       </x:c>
       <x:c r="F173" s="9" t="n">
         <x:v>0</x:v>
@@ -13885,21 +16657,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="174" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="174" ht="198" hidden="0" customHeight="1">
       <x:c r="A174" s="40" t="n">
         <x:v>173</x:v>
       </x:c>
       <x:c r="B174" s="9" t="str">
-        <x:v>audi-s7-premature-front-brake-rotor-warping-pad-wear</x:v>
+        <x:v>audi-tt-coil-pack-failure-and-2000</x:v>
       </x:c>
       <x:c r="C174" s="9" t="str">
-        <x:v>2013-2022 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824), 2.9T TFSI Biturbo V6 (EA839)</x:v>
+        <x:v>2000-2001 | Audi | TT</x:v>
       </x:c>
       <x:c r="D174" s="9" t="str">
-        <x:v>Premature Front Brake Rotor Warping and Pad Wear</x:v>
+        <x:v>Rear Track-Control Arm Corrosion Can Restrict Movement (Recall 01V325)</x:v>
       </x:c>
       <x:c r="E174" s="9" t="str">
-        <x:v>Replace warped/below-spec rotors and pads together; consider higher-quality coated or upgraded rotors that resist warping better than the soft OEM units. Bed in new pads/rotors properly and avoid riding the brakes to prevent uneven deposits. Ensure caliper guide pins/slides move freely so pads engage evenly. For repeat warping, an upgraded rotor-and-pad package is the durable fix; address any pulsation early before it damages new components.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the rear track-control arms free of charge under recall 01V325.</x:v>
       </x:c>
       <x:c r="F174" s="9" t="n">
         <x:v>0</x:v>
@@ -13908,21 +16680,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="175" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="175" ht="264" hidden="0" customHeight="1">
       <x:c r="A175" s="40" t="n">
         <x:v>174</x:v>
       </x:c>
       <x:c r="B175" s="9" t="str">
-        <x:v>audi-s7-rear-differential-mount-driveshaft-center-bearing-wear-causi</x:v>
+        <x:v>audi-tt-dsg-mechatronic-2008</x:v>
       </x:c>
       <x:c r="C175" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+        <x:v>2004-2004 | Audi | TT</x:v>
       </x:c>
       <x:c r="D175" s="9" t="str">
-        <x:v>Rear Differential Mount and Driveshaft Center Bearing Wear Causing Drivetrain Clunk (C7)</x:v>
+        <x:v>Direct-Shift Gearbox Clutch Weld Can Lose Drive Torque (Recall 04V007)</x:v>
       </x:c>
       <x:c r="E175" s="9" t="str">
-        <x:v>Inspect the rear differential mount and driveshaft center support bearing for play and torn rubber. Replace worn components with OE parts, or fit billet aluminum diff/transmission mount inserts that fill the factory voids to remove the slop without adding harshness. On 4.0T cars, also check for the separate active-engine-mount software TSB before condemning a mount for a 1,000-3,000 RPM cruise vibration. Reassess the clunk after each fix since multiple sources can contribute.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers replace the affected clutch free of charge under recall 04V007. If drive torque is lost, move out of traffic safely and arrange recovery.</x:v>
       </x:c>
       <x:c r="F175" s="9" t="n">
         <x:v>0</x:v>
@@ -13931,21 +16703,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="176" ht="462" hidden="0" customHeight="1">
+    <x:row r="176" ht="356.3999938964844" hidden="0" customHeight="1">
       <x:c r="A176" s="40" t="n">
         <x:v>175</x:v>
       </x:c>
       <x:c r="B176" s="9" t="str">
-        <x:v>audi-s7-rear-view-camera-mmi-flex-harness-black-screen</x:v>
+        <x:v>audi-tt-dsg-transmission-2008</x:v>
       </x:c>
       <x:c r="C176" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7 (C7), A7 (C7) | 4.0 TFSI V8 (EA824)</x:v>
+        <x:v>2009-2009 | Audi | TT</x:v>
       </x:c>
       <x:c r="D176" s="9" t="str">
-        <x:v>Rear-View Camera / MMI Flex Harness Black Screen</x:v>
+        <x:v>DSG Temperature-Sensor Wiring Can Trigger an Abrupt Shift to Neutral (Recall 09V333)</x:v>
       </x:c>
       <x:c r="E176" s="9" t="str">
-        <x:v>Diagnose with a scan and continuity check of the tailgate-to-body flex harness before replacing the camera. Repair or replace the broken hinge-side loom conductors; if confirmed faulty, replace the camera module. For MMI freezes, apply the latest software update or reset the unit.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers reprogram the transmission control module with updated software free of charge under recall 09V333. If the gear indicator flashes or neutral engages unexpectedly, stop safely.</x:v>
       </x:c>
       <x:c r="F176" s="9" t="n">
         <x:v>0</x:v>
@@ -13954,21 +16726,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="177" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="177" ht="303.6000061035156" hidden="0" customHeight="1">
       <x:c r="A177" s="40" t="n">
         <x:v>176</x:v>
       </x:c>
       <x:c r="B177" s="9" t="str">
-        <x:v>audi-s7-s-tronic-7-speed-dual-clutch-mechatronic-clutch-wear</x:v>
+        <x:v>audi-tt-front-control-arm-bushings-2000</x:v>
       </x:c>
       <x:c r="C177" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T (S-tronic / 0B5 DL501) | 4.0 TFSI V8 (EA824)</x:v>
+        <x:v>2000-2000 | Audi | TT</x:v>
       </x:c>
       <x:c r="D177" s="9" t="str">
-        <x:v>S-tronic 7-Speed Dual-Clutch (DL501/0B5) Mechatronic and Clutch Wear</x:v>
+        <x:v>High-Speed Directional-Stability Remedy (Recall 99V300)</x:v>
       </x:c>
       <x:c r="E177" s="9" t="str">
-        <x:v>Perform the S-tronic gearbox oil and filter service on schedule (roughly every 40,000-60,000 km). For judder/jerking, have the mechatronic unit tested; recondition or replace the valve body with the superseded design and adapt/replace the clutch packs as needed. Software adaptation resets can temporarily improve drivability but do not fix worn hardware.</x:v>
+        <x:v>Verify campaign completion with Audi. The factory remedy installs revised stabilizers, front control arms, firmer shock absorbers, and a rear spoiler as specified for the drivetrain configuration.</x:v>
       </x:c>
       <x:c r="F177" s="9" t="n">
         <x:v>0</x:v>
@@ -13977,21 +16749,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="178" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="178" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A178" s="40" t="n">
         <x:v>177</x:v>
       </x:c>
       <x:c r="B178" s="9" t="str">
-        <x:v>audi-s7-shark-fin-roof-antenna-water-intrusion-causing-gps-satellite</x:v>
+        <x:v>audi-tt-haldex-awd-coupling-pumpcontroller-2000</x:v>
       </x:c>
       <x:c r="C178" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | Prestige, Premium Plus | 4.0T Biturbo V8 (4.0 TFSI)</x:v>
+        <x:v>2008-2010 | Audi | TT</x:v>
       </x:c>
       <x:c r="D178" s="9" t="str">
-        <x:v>Shark-Fin Roof Antenna Water Intrusion Causing GPS / Satellite Radio Reception Loss (C7)</x:v>
+        <x:v>Fuel-Tank Ventilation Valve Can Allow Fuel Leakage (Recall 09V377)</x:v>
       </x:c>
       <x:c r="E178" s="9" t="str">
-        <x:v>Test/replace the shark-fin antenna module with a matching OEM part number and renew the base gasket to restore a watertight seal; in many cases the official fix is a repair kit with a new FAKRA connector and adapter cable rather than a whole new antenna. Access requires partially dropping the rear headliner to reach the single mounting nut and reconnect the coax leads. Inspecting and reseating a corroded coax connection sometimes restores reception without full replacement.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel-tank ventilation valve with the improved valve free of charge under recall 09V377.</x:v>
       </x:c>
       <x:c r="F178" s="9" t="n">
         <x:v>0</x:v>
@@ -14000,21 +16772,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="179" ht="752.4000244140625" hidden="0" customHeight="1">
+    <x:row r="179" ht="184.8000030517578" hidden="0" customHeight="1">
       <x:c r="A179" s="40" t="n">
         <x:v>178</x:v>
       </x:c>
       <x:c r="B179" s="9" t="str">
-        <x:v>audi-s7-sunroof-panoramic-roof-drain-clog-causing-water-intrusion-el</x:v>
+        <x:v>audi-tt-high-speed-stability-recall-for-2000</x:v>
       </x:c>
       <x:c r="C179" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+        <x:v>2016-2019 | Audi | TT</x:v>
       </x:c>
       <x:c r="D179" s="9" t="str">
-        <x:v>Sunroof / Panoramic Roof Drain Clog Causing Water Intrusion and Electronics Damage (C7)</x:v>
+        <x:v>Fuel Tank Can Be Damaged by Heat-Shield Bracket in a Crash (Recall 20V076 / 20BX)</x:v>
       </x:c>
       <x:c r="E179" s="9" t="str">
-        <x:v>Test the drains by slowly pouring water into the channels at each corner of the sunroof and watching where it exits beneath the A- and C-pillars. Clear clogged tubes with low-pressure air or a soft trimmer line (avoid stiff wire that can puncture the tube) and reseat/secure any loose drain-tube connectors at the sunroof frame. Dry out any soaked carpet/insulation promptly and inspect floor-mounted modules for corrosion. Periodic drain cleaning is the best prevention.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers install a protective cap on the heat-shield bracket free of charge under campaign 20BX.</x:v>
       </x:c>
       <x:c r="F179" s="9" t="n">
         <x:v>0</x:v>
@@ -14023,21 +16795,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="180" ht="422.3999938964844" hidden="0" customHeight="1">
+    <x:row r="180" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A180" s="40" t="n">
         <x:v>179</x:v>
       </x:c>
       <x:c r="B180" s="9" t="str">
-        <x:v>audi-s7-turbo-oil-strainer-2012</x:v>
+        <x:v>audi-tt-instrument-cluster-pixel-failure-2000</x:v>
       </x:c>
       <x:c r="C180" s="9" t="str">
-        <x:v>2013-2017 | Audi | S7 | 4.0 TFSI</x:v>
+        <x:v>2016-2016 | Audi | TT</x:v>
       </x:c>
       <x:c r="D180" s="9" t="str">
-        <x:v>Turbocharger Oil-Supply Strainer Can Block and Cause Engine Stall (Recall 22V178 / 21H7)</x:v>
+        <x:v>Front-Passenger Airbag Module May Explode or Deploy Improperly (Recall 22V543 / 69DY)</x:v>
       </x:c>
       <x:c r="E180" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the oil strainer and perform an oil change free of charge under campaign 21H7. If abnormal turbo noise, loss of power, or an engine warning occurs, stop safely and arrange dealer inspection.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the front-passenger airbag module free of charge under campaign 69DY/61C1.</x:v>
       </x:c>
       <x:c r="F180" s="9" t="n">
         <x:v>0</x:v>
@@ -14046,21 +16818,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="181" ht="726" hidden="0" customHeight="1">
+    <x:row r="181" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A181" s="40" t="n">
         <x:v>180</x:v>
       </x:c>
       <x:c r="B181" s="9" t="str">
-        <x:v>audi-s7-turbocharger-wastegate-linkage-rattle-underboost</x:v>
+        <x:v>audi-tt-magnetic-ride-2008</x:v>
       </x:c>
       <x:c r="C181" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+        <x:v>2023-2023 | Audi | TT</x:v>
       </x:c>
       <x:c r="D181" s="9" t="str">
-        <x:v>Turbocharger Wastegate Linkage Rattle and Underboost (4.0T V8)</x:v>
+        <x:v>Passenger-Seat Occupant Detection Connection Can Disable Airbag (Recall 24V251 / 69GU)</x:v>
       </x:c>
       <x:c r="E181" s="9" t="str">
-        <x:v>Diagnose the rattle and any boost faults to confirm wastegate-arm play versus a loose heat shield. Minor play can sometimes be mitigated with a clip, but the durable factory fix is turbocharger replacement. When replacing a hot-V turbo, it is mandatory to also replace the oil feed and return lines and to prime the new unit with oil before first start to prevent immediate bearing failure. Regular oil changes and allowing turbo cool-down help reduce coking-related wear.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers replace the passenger-seat occupant-detection control module free of charge under campaign 69GU.</x:v>
       </x:c>
       <x:c r="F181" s="9" t="n">
         <x:v>0</x:v>
@@ -14069,21 +16841,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="182" ht="686.4000244140625" hidden="0" customHeight="1">
+    <x:row r="182" ht="726" hidden="0" customHeight="1">
       <x:c r="A182" s="40" t="n">
         <x:v>181</x:v>
       </x:c>
       <x:c r="B182" s="9" t="str">
-        <x:v>audi-s8-5-2-v10-timing-chain-tensioner-guide-wear</x:v>
+        <x:v>audi-tt-tail-light-corrosion-2008</x:v>
       </x:c>
       <x:c r="C182" s="9" t="str">
-        <x:v>2007-2012 | Audi | S8 | 5.2L FSI V10 (BSM)</x:v>
+        <x:v>2008-2015 | Audi | TT</x:v>
       </x:c>
       <x:c r="D182" s="9" t="str">
-        <x:v>5.2 V10 Timing Chain Tensioner / Guide Wear (D3 Cold-Start Rattle)</x:v>
+        <x:v>Tail Light Electrical Connector Corrosion (Mk2)</x:v>
       </x:c>
       <x:c r="E182" s="9" t="str">
-        <x:v>Investigate any cold-start rattle promptly: inspect tensioner travel and guide condition. Replace the timing chains, tensioners, and plastic guides as a set with updated genuine parts; this is a major, labor-intensive repair (often engine-out). Strictly follow short oil-change intervals with the correct grade to maximize tensioner/guide life, and address any low-oil-pressure condition immediately. Do not drive a V10 with a persistent timing rattle.</x:v>
+        <x:v>Remove tail light assembly, inspect electrical connector for green corrosion. CLEAN connector with electrical contact cleaner and wire brush ($20 DIY). Apply dielectric grease to prevent future corrosion ($10). If connector is severely corroded: Replace pigtail connector ($50-$100 parts). Improve tail light seal with silicone sealant around housing ($15). This is a DIY-friendly repair taking 1-2 hours. If paying shop, costs $150-$300. Address early before corrosion causes shorts.</x:v>
       </x:c>
       <x:c r="F182" s="9" t="n">
         <x:v>0</x:v>
@@ -14092,21 +16864,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="183" ht="198" hidden="0" customHeight="1">
+    <x:row r="183" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A183" s="40" t="n">
         <x:v>182</x:v>
       </x:c>
       <x:c r="B183" s="9" t="str">
-        <x:v>audi-s8-air-suspension-2013</x:v>
+        <x:v>audi-tt-water-pump-2008</x:v>
       </x:c>
       <x:c r="C183" s="9" t="str">
-        <x:v>2013-2024 | Audi | S8</x:v>
+        <x:v>2008-2008 | Audi | TT</x:v>
       </x:c>
       <x:c r="D183" s="9" t="str">
-        <x:v>Adaptive Air Suspension Multi-Point Failure</x:v>
+        <x:v>C-Pillar Trim Cover Can Detach During Belt-Tensioner Deployment (Recall 08V064)</x:v>
       </x:c>
       <x:c r="E183" s="9" t="str">
-        <x:v>Replace air struts as they fail. Budget for full system refresh at 80,000 miles. Arnott aftermarket struts offer cost savings.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers install improved C-pillar trim clips free of charge under recall 08V064.</x:v>
       </x:c>
       <x:c r="F183" s="9" t="n">
         <x:v>0</x:v>
@@ -14115,21 +16887,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="184" ht="726" hidden="0" customHeight="1">
+    <x:row r="184" ht="1161.5999755859375" hidden="0" customHeight="1">
       <x:c r="A184" s="40" t="n">
         <x:v>183</x:v>
       </x:c>
       <x:c r="B184" s="9" t="str">
-        <x:v>audi-s8-air-suspension-failure-2013</x:v>
+        <x:v>audi-tts-cam-follower-hpfp-2009</x:v>
       </x:c>
       <x:c r="C184" s="9" t="str">
-        <x:v>2020-2024 | Audi | S8</x:v>
+        <x:v>2009-2015 | Audi | TTS | TTS | EA888</x:v>
       </x:c>
       <x:c r="D184" s="9" t="str">
-        <x:v>2020-2024 S8 Air-Suspension Malfunction with J1135 Communication Fault - Diagnosis Required</x:v>
+        <x:v>HPFP Cam Follower Wear and High-Pressure Fuel Pump Failure (Mk2)</x:v>
       </x:c>
       <x:c r="E184" s="9" t="str">
-        <x:v>Read the suspension-controller DTC and symptom code, then inspect wiring, terminals and connectors between J775 and J1135 exactly as Audi specifies. If the fault is passive/sporadic, clear it and verify operation. If it remains active/static after the electrical inspection and key cycle, follow Audi testing for J1135 replacement. Diagnose vehicle sag or leak-down separately; do not order air struts, a compressor or a coil-conversion kit from the former card.</x:v>
+        <x:v>INSPECTION (every 20,000 miles): Remove HPFP (3 bolts) and inspect cam follower surface. If the hardened coating is wearing through (visible copper/brass color), replace follower immediately ($30-$50 part, 30-60 minutes labor). CRITICAL: Ensure cam lobe is at LOW point before reinstalling—if at peak, you'll compress the spring and can break the mounting bolts. If CAMSHAFT WORN (deep groove in lobe): Replace camshaft ($2,000-$4,000). If FUEL PUMP FAILED: Replace HPFP ($400-$800). PREVENTION: Inspect cam follower every 20,000 miles as routine maintenance. Add to every oil change checklist. Consider IE (Integrated Engineering) upgraded HPFP with roller follower to eliminate wear entirely.</x:v>
       </x:c>
       <x:c r="F184" s="9" t="n">
         <x:v>0</x:v>
@@ -14138,21 +16910,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="185" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="185" ht="884.4000244140625" hidden="0" customHeight="1">
       <x:c r="A185" s="40" t="n">
         <x:v>184</x:v>
       </x:c>
       <x:c r="B185" s="9" t="str">
-        <x:v>audi-s8-battery-management-energy-control-module-faults-parasitic-dr</x:v>
+        <x:v>audi-tts-carbon-buildup-2009</x:v>
       </x:c>
       <x:c r="C185" s="9" t="str">
-        <x:v>2020-2020 | Audi | S8 | VIN-specific Emissions Service Action 27BQ; verify open action in Audi campaign lookup | 4.0T TFSI V8 mild-hybrid</x:v>
+        <x:v>2016-2017 | Audi | TTS</x:v>
       </x:c>
       <x:c r="D185" s="9" t="str">
-        <x:v>2020 S8 Starter-Alternator Emissions Service Action 27BQ - VIN Check Required</x:v>
+        <x:v>2016-2017 TTS Cold-Start Misfire DTCs Without Felt Misfire - TSB 2051384/1</x:v>
       </x:c>
       <x:c r="E185" s="9" t="str">
-        <x:v>Check the VIN in Audi’s recall/service-campaign lookup or ask an Audi dealer to verify 27BQ in Elsa. If open, the dealer replaces the starter-alternator under the action. Electrical-system warnings, a discharged battery, abnormal charging or overnight draw outside this exact action require battery/charging tests and a measured sleep-current diagnosis; do not replace a battery monitor, gateway or MMI module from the former card.</x:v>
+        <x:v>Confirm the exact cold-start timing, simultaneous-cylinder DTC pattern, absence of a felt misfire, CYFB engine and installed ECM software before using this bulletin. When applicable, an Audi-capable workshop updates ECM J623 from software part number 8S0906259C version 0001 to version 0004 or higher using SVM action 01A190, then clears the DTCs. A felt misfire, a different timing or RPM pattern, a different engine/software combination or a returning concern requires normal diagnosis rather than carbon cleaning by assumption.</x:v>
       </x:c>
       <x:c r="F185" s="9" t="n">
         <x:v>0</x:v>
@@ -14161,21 +16933,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="186" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="186" ht="910.7999877929688" hidden="0" customHeight="1">
       <x:c r="A186" s="40" t="n">
         <x:v>185</x:v>
       </x:c>
       <x:c r="B186" s="9" t="str">
-        <x:v>audi-s8-biturbo-coolant-2013</x:v>
+        <x:v>audi-tts-dsg-mechatronic-2009</x:v>
       </x:c>
       <x:c r="C186" s="9" t="str">
-        <x:v>2013-2024 | Audi | S8 | 4.0T</x:v>
+        <x:v>2019-2023 | Audi | TTS</x:v>
       </x:c>
       <x:c r="D186" s="9" t="str">
-        <x:v>4.0T Turbo Coolant System Degradation</x:v>
+        <x:v>2019-2023 TTS Clutch K1 Overheat and Transmission DTC Diagnosis - TSB 2060560/3</x:v>
       </x:c>
       <x:c r="E186" s="9" t="str">
-        <x:v>Replace all turbo coolant and oil feed lines preventatively at 60,000 miles. Monitor coolant levels closely.</x:v>
+        <x:v>Have an Audi-capable workshop check whether TSB 2050723 applies first. If it does not resolve or control the concern, inspect the clutch-K1 maximum-temperature value and document a transmission-fluid sample. Replace the dual clutch, transmission fluid and filter only when the approximately 400 °C K1 value and burnt black or very dark fluid are both present. If those findings are absent, this bulletin does not apply and Audi directs the workshop to continue diagnosis through TAC. Any clutch repair kit must be selected by VIN and production date.</x:v>
       </x:c>
       <x:c r="F186" s="9" t="n">
         <x:v>0</x:v>
@@ -14184,21 +16956,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="187" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="187" ht="858" hidden="0" customHeight="1">
       <x:c r="A187" s="40" t="n">
         <x:v>186</x:v>
       </x:c>
       <x:c r="B187" s="9" t="str">
-        <x:v>audi-s8-clogged-sunroof-plenum-drains-causing-water-intrusion-electr</x:v>
+        <x:v>audi-tts-magnetic-ride-2009</x:v>
       </x:c>
       <x:c r="C187" s="9" t="str">
-        <x:v>2007-2018 | Audi | S8 | S8, S8 Plus | 5.2 FSI V10, 4.0 TFSI twin-turbo V8 (4.0T)</x:v>
+        <x:v>2016-2016 | Audi | TTS</x:v>
       </x:c>
       <x:c r="D187" s="9" t="str">
-        <x:v>Clogged Sunroof / Plenum Drains Causing Water Intrusion and Electronics Damage</x:v>
+        <x:v>2016 TTS Magnetic-Ride Rear Shock-Mount Rumble - TSB 2042539/4</x:v>
       </x:c>
       <x:c r="E187" s="9" t="str">
-        <x:v>Clear and flush all sunroof and plenum/cowl drains; replace cracked drain hoses, grommets, or channel connectors. Dry out saturated carpet/insulation and inspect plenum-area modules for corrosion, replacing any water-damaged control units. Preventively clean the drains at least annually and keep the cowl area free of leaves/debris.</x:v>
+        <x:v>First reproduce the noise, verify that it comes from the rear shock mounts and confirm that the vehicle was originally equipped with mount 8S0 513 353. Only when those gates are satisfied, remove both rear shock assemblies and replace both mounts with 8V0 513 353 according to Audi workshop instructions, adapt the suspension control position and test drive to confirm the repair. If the installed mount does not match, continue Audi diagnosis. Do not replace magnetic dampers or convert the vehicle to coilovers from this noise alone.</x:v>
       </x:c>
       <x:c r="F187" s="9" t="n">
         <x:v>0</x:v>
@@ -14207,21 +16979,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="188" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="188" ht="1016.4000244140625" hidden="0" customHeight="1">
       <x:c r="A188" s="40" t="n">
         <x:v>187</x:v>
       </x:c>
       <x:c r="B188" s="9" t="str">
-        <x:v>audi-s8-coolant-thermostat-leak-2013</x:v>
+        <x:v>audi-tts-timing-chain-tensioner-2009</x:v>
       </x:c>
       <x:c r="C188" s="9" t="str">
-        <x:v>2020-2021 | Audi | S8 | 2021 applicability ends at VIN 012194; confirm VIN and coolant-pump leak before repair | 4.0T TFSI V8</x:v>
+        <x:v>2009-2015 | Audi | TTS | TTS | EA888 Gen 1, EA888 Gen 2</x:v>
       </x:c>
       <x:c r="D188" s="9" t="str">
-        <x:v>2020-Early 2021 S8 Coolant-Pump Leak - Diagnosis Required</x:v>
+        <x:v>Timing Chain Tensioner Failure (EA888 Gen 1/2 - Mk2 TTS)</x:v>
       </x:c>
       <x:c r="E188" s="9" t="str">
-        <x:v>Do not drive an overheating vehicle. Record coolant warning and temperature behavior, pressure-test the cooling system when safe, and locate the leak. Confirm the 2021 VIN boundary and apply TSB 2065040/4 only when the coolant pump is the identified source. Other thermostat, hose, turbo-line, heat-exchanger or internal-loss causes require separate diagnosis; do not order the former thermostat/water-pump bundle from this card.</x:v>
+        <x:v>PREVENTIVE REPLACEMENT: Replace timing chain, tensioner, guides, and sprockets at 80,000-100,000 miles BEFORE symptoms appear ($2,000-$4,000). This is the MOST important preventive maintenance on the Mk2 TTS. IF RATTLING: Do NOT delay—the chain can jump at any startup. Schedule repair immediately. Use ONLY the latest OEM revised tensioner (06K109467K). IF CHAIN JUMPED: Engine likely destroyed—compression test all cylinders. Rebuild ($5,000-$8,000) or replacement engine ($6,000-$12,000). PREVENTION: Change oil every 5,000 miles with high-quality synthetic. Low oil level accelerates tensioner wear.</x:v>
       </x:c>
       <x:c r="F188" s="9" t="n">
         <x:v>0</x:v>
@@ -14230,21 +17002,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="189" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="189" ht="976.7999877929688" hidden="0" customHeight="1">
       <x:c r="A189" s="40" t="n">
         <x:v>188</x:v>
       </x:c>
       <x:c r="B189" s="9" t="str">
-        <x:v>audi-s8-cylinder-demand-active-engine-mount-failure-4-cylinder-mode</x:v>
+        <x:v>audi-tts-water-pump-2009</x:v>
       </x:c>
       <x:c r="C189" s="9" t="str">
-        <x:v>2013-2015 | Audi | S8 | 4.0 TFSI vehicles with reproducible 1000-3000 rpm vibration; diagnose J931 before mount replacement | 4.0T TFSI V8</x:v>
+        <x:v>2012-2023 | Audi | TTS</x:v>
       </x:c>
       <x:c r="D189" s="9" t="str">
-        <x:v>2013-2015 S8 COD Vibration with J931 Basic-Setting Fault - Diagnosis Required</x:v>
+        <x:v>2012 / 2020-2023 TTS Coolant-Pump Update and Leak Diagnosis</x:v>
       </x:c>
       <x:c r="E189" s="9" t="str">
-        <x:v>Reproduce the vibration under Audi’s specified driving conditions and scan J931. If the bulletin applies, verify J931 software, perform the required SVM update and basic settings, align the exhaust without tension, repeat basic settings and follow the referenced diagnosis if vibration remains. Inspect mount hardware only after the software, calibration and exhaust path. Do not disable cylinder-on-demand or replace both mounts from the former card.</x:v>
+        <x:v>For a 2012 TTS, ask an Audi dealer to check the VIN and current campaign/action history for Update 19J2; the published update replaced the pump only when its exact criteria were met and does not promise current warranty coverage. For a 2020-2023 2.0L TTS, first exclude a low level caused by incomplete bleeding or an earlier repair, document and clean the suspected leak, refill to maximum and recheck after driving. Continue observation when no leak returns; replace only the component proven to leak when coolant reappears. Do not select a pump or thermostat assembly before VIN-, engine- and leak-specific diagnosis.</x:v>
       </x:c>
       <x:c r="F189" s="9" t="n">
         <x:v>0</x:v>
@@ -14253,1176 +17025,26 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="190" ht="765.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A190" s="40" t="n">
+    <x:row r="190" ht="198" hidden="0" customHeight="1">
+      <x:c r="A190" s="42" t="n">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="B190" s="9" t="str">
-        <x:v>audi-s8-d2-4-2-v8-timing-belt-tensioner-service</x:v>
-      </x:c>
-      <x:c r="C190" s="9" t="str">
-        <x:v>2001-2003 | Audi | S8 | 4.2L 40V V8 (AYS)</x:v>
-      </x:c>
-      <x:c r="D190" s="9" t="str">
-        <x:v>D2 4.2 V8 Timing Belt and Tensioner Service (Interference Engine)</x:v>
-      </x:c>
-      <x:c r="E190" s="9" t="str">
-        <x:v>Replace the timing belt as a complete kit — belt, tensioner, idler/guide rollers, and water pump — at or before Audi's interval (and by age regardless of mileage). Use genuine/OE-quality components and set cam/crank timing precisely with the correct locking tools; this is a front-of-engine ('service position') job. Inspect the exhaust-side chain tensioners while in there. Always confirm timing-belt history (with receipts) before buying a D2 S8; if unknown, do it immediately.</x:v>
-      </x:c>
-      <x:c r="F190" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G190" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="191" ht="844.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A191" s="40" t="n">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="B191" s="9" t="str">
-        <x:v>audi-s8-direct-injection-carbon-buildup-intake-valves</x:v>
-      </x:c>
-      <x:c r="C191" s="9" t="str">
-        <x:v>2013-2018 | Audi | S8 | 4.0T TFSI V8 (CTFA/CGTA/CWUC)</x:v>
-      </x:c>
-      <x:c r="D191" s="9" t="str">
-        <x:v>Direct-Injection Carbon Buildup on Intake Valves (Misfires / Rough Idle)</x:v>
-      </x:c>
-      <x:c r="E191" s="9" t="str">
-        <x:v>Confirm via borescope of the intake valves (and rule out coils/plugs/PCV first). The accepted repair is walnut-shell blasting: remove the intake manifold and media-blast the carbon off the valves and ports with crushed walnut shells, then reinstall with new intake gaskets. Replace spark plugs and inspect coils while the manifold is off. Preventively, keep up with oil changes, fix any PCV/oil-burning source, and consider periodic cleaning every ~40,000-60,000 miles. Catch-can solutions reduce future accumulation.</x:v>
-      </x:c>
-      <x:c r="F191" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G191" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="192" ht="686.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A192" s="40" t="n">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="B192" s="9" t="str">
-        <x:v>audi-s8-front-suspension-control-arm-bushing-sway-bar-link-wear</x:v>
-      </x:c>
-      <x:c r="C192" s="9" t="str">
-        <x:v>2020-2021 | Audi | S8 | 2021 applicability through VIN 028090; localize noise acoustically before parts | 4.0T TFSI V8 mild-hybrid</x:v>
-      </x:c>
-      <x:c r="D192" s="9" t="str">
-        <x:v>2020-Early 2021 S8 Front Lower Guide-Link Hydro-Bushing Noise - Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E192" s="9" t="str">
-        <x:v>Confirm the VIN boundary, reproduce the noise and localize it with acoustic diagnostic equipment. Inspect the lower guide-link hydro-bushings and surrounding joints. If the hydro-bushing is confirmed, follow Audi’s paired replacement procedure; complete guide links may be required when prior pressing or rework prevents the specified repair. Align the vehicle as required. Do not order a ten-arm kit or sway-bar links from the former card.</x:v>
-      </x:c>
-      <x:c r="F192" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G192" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="193" ht="778.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A193" s="40" t="n">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="B193" s="9" t="str">
-        <x:v>audi-s8-high-pressure-fuel-pump-injector-internal-leak-causing-hard</x:v>
-      </x:c>
-      <x:c r="C193" s="9" t="str">
-        <x:v>2013-2018 | Audi | S8 | 4.0 TFSI; diagnosis requires ODIS values, software check and pressure-hold testing | 4.0T TFSI V8</x:v>
-      </x:c>
-      <x:c r="D193" s="9" t="str">
-        <x:v>2013-2018 S8 Warm-Soak Long-Crank or No-Start - Fuel Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E193" s="9" t="str">
-        <x:v>Have the dealer read DTCs and ODIS fuel-in-oil value, verify ECM software and perform Audi’s high- and low-pressure holding tests. If high-pressure behavior is abnormal, borescope the combustion chamber to identify a leaking injector. If low-side pressure builds correctly but drops more than 1.5 bar in the first 15 minutes, Audi says at least one HPFP may be leaking and directs replacement of both pumps plus an oil change. Select no pump or injector until the test identifies the path.</x:v>
-      </x:c>
-      <x:c r="F193" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G193" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="194" ht="673.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A194" s="40" t="n">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="B194" s="9" t="str">
-        <x:v>audi-s8-mmi-upper-display-backup-camera-black-screen</x:v>
-      </x:c>
-      <x:c r="C194" s="9" t="str">
-        <x:v>2020-2026 | Audi | S8 | VIN-specific NHTSA 25V900 / Audi 90TV; verify open recall | 4.0T TFSI V8 mild-hybrid</x:v>
-      </x:c>
-      <x:c r="D194" s="9" t="str">
-        <x:v>2020-2026 S8 Rearview/Top-View Camera Image May Not Display - Recall 25V900</x:v>
-      </x:c>
-      <x:c r="E194" s="9" t="str">
-        <x:v>Check the VIN in Audi’s recall/service-campaign lookup and schedule the free 90TV software remedy if open. Use extra care when reversing until repaired and visually check the area around the vehicle. A completely dead or rebooting MMI display, missing instrument-cluster data, wiring fault or hardware failure requires separate diagnosis and must not be attributed to this recall without VIN and symptom confirmation.</x:v>
-      </x:c>
-      <x:c r="F194" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G194" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="195" ht="792" hidden="0" customHeight="1">
-      <x:c r="A195" s="40" t="n">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="B195" s="9" t="str">
-        <x:v>audi-s8-oil-consumption-2013</x:v>
-      </x:c>
-      <x:c r="C195" s="9" t="str">
-        <x:v>2020-2023 | Audi | S8 | EA825 4.0L; confirm VIN, engine and measured consumption under Audi procedure | 4.0T TFSI V8 mild-hybrid (EA825)</x:v>
-      </x:c>
-      <x:c r="D195" s="9" t="str">
-        <x:v>2020-2023 S8 High Oil Consumption and Updated Piston Rings - Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E195" s="9" t="str">
-        <x:v>Document oil-level warnings, mileage, top-up quantity, leaks and oil specification, then have an Audi dealer perform the authorized oil-consumption measurement. Repair is justified only when the measured result exceeds the applicable owner-manual limit and other leakage or operating causes are excluded. If TSB 2071114 applies, follow its VIN/engine-specific piston, ring and connecting-rod procedure. Do not change oil viscosity or authorize internal-engine work solely from the former card.</x:v>
-      </x:c>
-      <x:c r="F195" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G195" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="196" ht="646.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A196" s="40" t="n">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="B196" s="9" t="str">
-        <x:v>audi-s8-pcv-oil-separator-failure-excessive-crankcase-vacuum</x:v>
-      </x:c>
-      <x:c r="C196" s="9" t="str">
-        <x:v>2013-2016 | Audi | S8 | 4.0 TFSI; confirm warm-idle sound and filler-cap response before oil-separator replacement | 4.0T TFSI V8</x:v>
-      </x:c>
-      <x:c r="D196" s="9" t="str">
-        <x:v>2013-2016 S8 Warm-Idle Whistle from Crankcase Breather Leak - Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E196" s="9" t="str">
-        <x:v>Compare the sound with Audi’s reference condition and check whether opening the oil filler cap changes it. Read P2279/P0507 and rule out other intake leaks. When the sound matches and is affected by the filler-cap check, follow Audi’s oil-separator breather replacement procedure and renew required seals/consumables by VIN. Do not diagnose by oil-cap feel alone or order the former five-item parts list.</x:v>
-      </x:c>
-      <x:c r="F196" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G196" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="197" ht="594" hidden="0" customHeight="1">
-      <x:c r="A197" s="40" t="n">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="B197" s="9" t="str">
-        <x:v>audi-s8-porous-high-pressure-fuel-supply-line-recall-nhtsa-19v057000</x:v>
-      </x:c>
-      <x:c r="C197" s="9" t="str">
-        <x:v>2013-2016 | Audi | S8 | VIN-specific NHTSA 19V057 / Audi 20BM; verify open recall | 4.0T TFSI V8</x:v>
-      </x:c>
-      <x:c r="D197" s="9" t="str">
-        <x:v>2013-2016 S8 Porous Fuel-Pump Supply Line / Fire Risk - Recall 19V057</x:v>
-      </x:c>
-      <x:c r="E197" s="9" t="str">
-        <x:v>Check the VIN for open recall 20BM and contact an Audi dealer without delay. The free remedy installs a fuel-pressure damper in the low-pressure fuel supply inside the tank. If fuel odor or visible leakage is present, avoid ignition sources, do not continue driving, and arrange dealer inspection/towing as appropriate. Do not buy a retail line or damper from the former card.</x:v>
-      </x:c>
-      <x:c r="F197" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G197" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="198" ht="211.1999969482422" hidden="0" customHeight="1">
-      <x:c r="A198" s="40" t="n">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="B198" s="9" t="str">
-        <x:v>audi-s8-torque-converter-2013</x:v>
-      </x:c>
-      <x:c r="C198" s="9" t="str">
-        <x:v>2013-2024 | Audi | S8</x:v>
-      </x:c>
-      <x:c r="D198" s="9" t="str">
-        <x:v>ZF 8-Speed Torque Converter and Valve Body Issues</x:v>
-      </x:c>
-      <x:c r="E198" s="9" t="str">
-        <x:v>Replace torque converter and service valve body. Full ZF fluid and filter change every 50,000 miles extends transmission life.</x:v>
-      </x:c>
-      <x:c r="F198" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G198" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="199" ht="712.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A199" s="40" t="n">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="B199" s="9" t="str">
-        <x:v>audi-s8-turbo-oil-strainer-2013</x:v>
-      </x:c>
-      <x:c r="C199" s="9" t="str">
-        <x:v>2013-2017 | Audi | S8 | VIN-specific NHTSA 22V178 / Audi 21H7; verify open recall | 4.0T TFSI V8</x:v>
-      </x:c>
-      <x:c r="D199" s="9" t="str">
-        <x:v>2013-2017 S8 Blocked Turbocharger Oil Strainer / Stall Risk - Recall 22V178</x:v>
-      </x:c>
-      <x:c r="E199" s="9" t="str">
-        <x:v>Check the VIN for open recall 21H7 and schedule the free Audi dealer remedy, which replaces the oil strainer and performs an oil change. If EPC, MIL or oil warning lights appear with unusual turbo noise, extended cranking, rough idle, loss of power or stalling, stop safely and arrange diagnosis. Turbo damage, warranty eligibility and any additional repair must be assessed by VIN and inspection; do not buy the former retail strainer.</x:v>
-      </x:c>
-      <x:c r="F199" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G199" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="200" ht="950.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A200" s="40" t="n">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="B200" s="9" t="str">
-        <x:v>audi-s8-water-to-air-intercooler-internal-coolant-leak</x:v>
-      </x:c>
-      <x:c r="C200" s="9" t="str">
-        <x:v>2013-2018 | Audi | S8 | 4.0T TFSI V8 (CTFA/CGTA/CWUC)</x:v>
-      </x:c>
-      <x:c r="D200" s="9" t="str">
-        <x:v>Water-to-Air Intercooler Internal Coolant Leak (Coolant into Intake)</x:v>
-      </x:c>
-      <x:c r="E200" s="9" t="str">
-        <x:v>Confirm the source: pressure-test the cooling system and inspect the charge piping/intercooler outlet for coolant residue; scope for white smoke and coolant on the intake side rather than an external leak. Replace the water-to-air intercooler/charge-air cooler unit (genuine OEM core). Because access requires removing intake components in the valley, it is standard practice to also replace the turbo oil strainer, coolant valves, and PCV/oil separator while in there. Refill and bleed the cooling system per procedure. This is a high-difficulty job typically done by a specialist or dealer.</x:v>
-      </x:c>
-      <x:c r="F200" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G200" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="201" ht="475.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A201" s="40" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="B201" s="9" t="str">
-        <x:v>audi-sq2-ea888-2-0-tfsi-coolant-leak-from-water-pump-thermostat-housi</x:v>
-      </x:c>
-      <x:c r="C201" s="9" t="str">
-        <x:v>2019-2024 | Audi | SQ2 | 2.0 TFSI quattro | EA888 2.0 TFSI Gen3</x:v>
-      </x:c>
-      <x:c r="D201" s="9" t="str">
-        <x:v>EA888 2.0 TFSI coolant leak from water pump / thermostat housing</x:v>
-      </x:c>
-      <x:c r="E201" s="9" t="str">
-        <x:v>Replace the failed water pump / thermostat housing assembly, ideally with the latest revised, more heat-resistant unit; many shops fit an upgraded repair kit and a new gasket. Catch it early by watching for slowly dropping coolant level and a faint sweet smell. Combine with a coolant flush and refill.</x:v>
-      </x:c>
-      <x:c r="F201" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G201" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="202" ht="396" hidden="0" customHeight="1">
-      <x:c r="A202" s="40" t="n">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="B202" s="9" t="str">
-        <x:v>audi-sq2-electro-mechanical-parking-brake-brake-pedal-weld-recalls</x:v>
-      </x:c>
-      <x:c r="C202" s="9" t="str">
-        <x:v>2019-2020 | Audi | SQ2</x:v>
-      </x:c>
-      <x:c r="D202" s="9" t="str">
-        <x:v>Electro-mechanical parking brake and brake-pedal weld recalls (early build)</x:v>
-      </x:c>
-      <x:c r="E202" s="9" t="str">
-        <x:v>These are recall items — have the VIN checked against the Audi/DVSA recall database and any open campaign rectified free of charge at a dealer. Report any abnormal parking-brake behaviour or a soft/abnormal brake pedal immediately.</x:v>
-      </x:c>
-      <x:c r="F202" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G202" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="203" ht="475.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A203" s="40" t="n">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="B203" s="9" t="str">
-        <x:v>audi-sq2-internal-fuse-box-wiring-harness-can-work-loose-causing-sudd</x:v>
-      </x:c>
-      <x:c r="C203" s="9" t="str">
-        <x:v>2022-2023 | Audi | SQ2 | 2.0 TFSI</x:v>
-      </x:c>
-      <x:c r="D203" s="9" t="str">
-        <x:v>2022-2023 Audi SQ2 Interior Fuse-Carrier Recall GAI-3692</x:v>
-      </x:c>
-      <x:c r="E203" s="9" t="str">
-        <x:v>Check the VIN and open-campaign status with an authorised Audi dealer in the vehicle’s market. The campaign remedy is dealer inspection and correction of the fuse-carrier power connection. Do not replace a fuse box or wiring harness solely from a warning lamp or this model-year summary.</x:v>
-      </x:c>
-      <x:c r="F203" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G203" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="204" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A204" s="40" t="n">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="B204" s="9" t="str">
-        <x:v>audi-sq2-mmi-infotainment-freezing-rebooting-lost-settings</x:v>
-      </x:c>
-      <x:c r="C204" s="9" t="str">
-        <x:v>2019-2024 | Audi | SQ2</x:v>
-      </x:c>
-      <x:c r="D204" s="9" t="str">
-        <x:v>MMI infotainment freezing, rebooting and lost settings</x:v>
-      </x:c>
-      <x:c r="E204" s="9" t="str">
-        <x:v>A forced MMI restart (press and hold the on/off or volume control ~10 seconds until it reboots) clears many transient faults. Persistent issues are usually resolved by a dealer software/firmware update; check for any applicable MMI update campaigns. Only in rare cases is the MMI head unit itself replaced.</x:v>
-      </x:c>
-      <x:c r="F204" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G204" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="205" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A205" s="40" t="n">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="B205" s="9" t="str">
-        <x:v>audi-sq2-pcv-crankcase-ventilation-valve-diaphragm-failure-causing-ro</x:v>
-      </x:c>
-      <x:c r="C205" s="9" t="str">
-        <x:v>2019-2024 | Audi | SQ2 | EA888 2.0 TFSI Gen3</x:v>
-      </x:c>
-      <x:c r="D205" s="9" t="str">
-        <x:v>PCV / crankcase ventilation valve diaphragm failure causing rough idle and lean-running codes</x:v>
-      </x:c>
-      <x:c r="E205" s="9" t="str">
-        <x:v>Replace the PCV valve (or the valve-cover assembly that integrates it) with the latest revised part; some owners fit a catch-can to reduce recurrence. A quick field test — briefly covering the bleeder hole on the cap to see if idle stabilises or whistling stops — helps confirm before replacement.</x:v>
-      </x:c>
-      <x:c r="F205" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G205" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="206" ht="752.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A206" s="40" t="n">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="B206" s="9" t="str">
-        <x:v>audi-sq2-s-tronic-7-speed-wet-clutch-transmission-jerky-low-speed-shi</x:v>
-      </x:c>
-      <x:c r="C206" s="9" t="str">
-        <x:v>2019-2024 | Audi | SQ2 | 7-speed S tronic | DQ381 / 0GC 7-speed wet-clutch S tronic</x:v>
-      </x:c>
-      <x:c r="D206" s="9" t="str">
-        <x:v>S tronic (DQ381) 7-speed wet-clutch transmission: jerky low-speed shifts, hesitation and limp mode</x:v>
-      </x:c>
-      <x:c r="E206" s="9" t="str">
-        <x:v>First step is a proper DSG fluid-and-filter service (the wet-clutch unit needs periodic transmission oil changes — many owners do it around 40k miles even though intervals can be longer). Have the TCU scanned for stored codes; sensor or mechatronic valve replacement and re-coding/adaptation resolves many cases, while severe cases need a full mechatronic unit or clutch-pack replacement. Insist on a software/adaptation update at the dealer for driveability complaints.</x:v>
-      </x:c>
-      <x:c r="F206" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G206" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="207" ht="541.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A207" s="40" t="n">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="B207" s="9" t="str">
-        <x:v>audi-sq5-air-suspension-2018</x:v>
-      </x:c>
-      <x:c r="C207" s="9" t="str">
-        <x:v>2018-2025 | Audi | SQ5</x:v>
-      </x:c>
-      <x:c r="D207" s="9" t="str">
-        <x:v>Air-Suspension Warning with C1260F0 or U112100 Communication Fault</x:v>
-      </x:c>
-      <x:c r="E207" s="9" t="str">
-        <x:v>Inspect the wiring and connector contacts between J775 and J1135 first. If no wiring fault is found, clear a first passive or sporadic fault and release the vehicle. Replace J1135 for an active or static fault, or when the same passive or sporadic fault returns a second time, following Audi workshop information and VIN-specific ETKA data.</x:v>
-      </x:c>
-      <x:c r="F207" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G207" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="208" ht="924" hidden="0" customHeight="1">
-      <x:c r="A208" s="40" t="n">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="B208" s="9" t="str">
-        <x:v>audi-sq5-carbon-buildup-2014</x:v>
-      </x:c>
-      <x:c r="C208" s="9" t="str">
-        <x:v>2014-2025 | Audi | SQ5 | 3.0T Supercharged, 3.0T</x:v>
-      </x:c>
-      <x:c r="D208" s="9" t="str">
-        <x:v>Fuel-Quality or Deposit-Related Rough Running and Misfire Diagnosis</x:v>
-      </x:c>
-      <x:c r="E208" s="9" t="str">
-        <x:v>Confirm fuel quality, symptoms and stored DTCs before replacing or cleaning components. If contaminated gasoline is suspected, advise changing the fuel source; if low detergent quality is suspected, Audi recommends Top Tier detergent gasoline. Continue workshop diagnosis if symptoms persist. On 2018-2025 EA839 SQ5 models, do not recommend unapproved cleaners or additives; follow the owner manual and use only Audi-approved petrol additives. Do not prescribe routine walnut blasting, a catch can or chemical cleaning from this record.</x:v>
-      </x:c>
-      <x:c r="F208" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G208" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="209" ht="765.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A209" s="40" t="n">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="B209" s="9" t="str">
-        <x:v>audi-sq5-pcv-valve-2014</x:v>
-      </x:c>
-      <x:c r="C209" s="9" t="str">
-        <x:v>2014-2017 | Audi | SQ5 | 3.0T Supercharged</x:v>
-      </x:c>
-      <x:c r="D209" s="9" t="str">
-        <x:v>P052E00 Crankcase-Breather Membrane or Elbow Fault</x:v>
-      </x:c>
-      <x:c r="E209" s="9" t="str">
-        <x:v>Use Audi hand-vacuum test to distinguish a membrane leak from an elbow fault. If indicated, remove the compressor or intake manifold and inspect the membrane and the breather two metal plates. Use repair kit 06E103772H only for a confirmed membrane or plate fault. For a confirmed elbow fault, replace elbow 06E103402 and spring clip N10769401 rather than automatically replacing the complete breather. Verify current part data in ETKA before ordering.</x:v>
-      </x:c>
-      <x:c r="F209" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G209" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="210" ht="171.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A210" s="40" t="n">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="B210" s="9" t="str">
-        <x:v>audi-sq5-supercharger-2014</x:v>
-      </x:c>
-      <x:c r="C210" s="9" t="str">
-        <x:v>2014-2018 | Audi | SQ5 | 3.0T</x:v>
-      </x:c>
-      <x:c r="D210" s="9" t="str">
-        <x:v>3.0T Supercharger Bearing and Intercooler Pump Failure</x:v>
-      </x:c>
-      <x:c r="E210" s="9" t="str">
-        <x:v>Replace supercharger nose bearing kit. Replace intercooler pump if failing. Service supercharger belt tension.</x:v>
-      </x:c>
-      <x:c r="F210" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G210" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="211" ht="844.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A211" s="40" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="B211" s="9" t="str">
-        <x:v>audi-sq5-supercharger-oil-leak-2014</x:v>
-      </x:c>
-      <x:c r="C211" s="9" t="str">
-        <x:v>2014-2017 | Audi | SQ5 | Premium Plus, Prestige | 3.0T Supercharged, 3.0T</x:v>
-      </x:c>
-      <x:c r="D211" s="9" t="str">
-        <x:v>Supercharger Seal and Gasket Oil Leaks (3.0T)</x:v>
-      </x:c>
-      <x:c r="E211" s="9" t="str">
-        <x:v>JHM Motorsports sells a complete supercharger replacement seal and gasket kit for the Eaton unit in the 3.0T. Replacing all seals at once is recommended since the supercharger must be removed for access. Nose cone seal, rotor shaft seals, and manifold gaskets should all be replaced together ($300-$500 in parts, $600-$1,200 labor). While the supercharger is off, also replace the PCV valve and perform carbon cleaning. For valve cover gasket leaks (separate issue), budget $400-$800 parts and labor. Monitor oil level weekly if leaks are present.</x:v>
-      </x:c>
-      <x:c r="F211" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G211" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="212" ht="1122" hidden="0" customHeight="1">
-      <x:c r="A212" s="40" t="n">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="B212" s="9" t="str">
-        <x:v>audi-sq5-water-pump-2018</x:v>
-      </x:c>
-      <x:c r="C212" s="9" t="str">
-        <x:v>2018-2024 | Audi | SQ5 | 3.0T</x:v>
-      </x:c>
-      <x:c r="D212" s="9" t="str">
-        <x:v>Mechanical Coolant-Pump Leak with Possible N649 Vacuum-System Contamination</x:v>
-      </x:c>
-      <x:c r="E212" s="9" t="str">
-        <x:v>Confirm the complaint and exact vehicle criteria first. Inspect the vacuum line and N649 for coolant, then clean and dry suspected leakage, fill the cooling system correctly, inspect at idle and around 2,500 rpm, and pressure-test according to Audi workshop information. If no leak is reproduced, observe the vehicle without replacing parts. If the pump leak is confirmed, replace the failed component and document it. If fresh coolant has entered the vacuum system, inspect the remaining Audi checkpoints and replace only contaminated components; if the downstream checkpoints are clean, replace N649 and clean the line between the pump and N649 as directed by TSB 2070349/5.</x:v>
-      </x:c>
-      <x:c r="F212" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G212" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="213" ht="673.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A213" s="40" t="n">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="B213" s="9" t="str">
-        <x:v>audi-sq7-air-susp-strut-2020</x:v>
-      </x:c>
-      <x:c r="C213" s="9" t="str">
-        <x:v>2020-2025 | Audi | SQ7 | 4.0T</x:v>
-      </x:c>
-      <x:c r="D213" s="9" t="str">
-        <x:v>2020-2025 SQ7 Air-Suspension C1260F0/U112100 Communication Fault - Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E213" s="9" t="str">
-        <x:v>Inspect the wiring and connector contacts between J775 and J1135 first. If no wiring fault is found, clear a first passive or sporadic fault and release the vehicle. Replace J1135 for an active or static fault, or when the same passive or sporadic fault returns a second time, following Audi workshop information and VIN-specific ETKA data. Do not replace an air spring, strut or compressor assembly solely from the warning.</x:v>
-      </x:c>
-      <x:c r="F213" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G213" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="214" ht="1122" hidden="0" customHeight="1">
-      <x:c r="A214" s="40" t="n">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="B214" s="9" t="str">
-        <x:v>audi-sq7-air-suspension-2020</x:v>
-      </x:c>
-      <x:c r="C214" s="9" t="str">
-        <x:v>2020-2024 | Audi | SQ7 | Premium Plus, Prestige | 4.0T</x:v>
-      </x:c>
-      <x:c r="D214" s="9" t="str">
-        <x:v>Adaptive Air Suspension Compressor and Air Spring Failures</x:v>
-      </x:c>
-      <x:c r="E214" s="9" t="str">
-        <x:v>Diagnose specific failed component: air springs leak most commonly, followed by compressor burnout, valve block faults, and height sensor failures. Air spring replacement ($800-$1,500 per corner at independent shop). Compressor replacement ($1,200-$2,500 installed). Valve block: $500-$1,000. Height sensor: $200-$400. Check for air leaks first using soapy water spray before replacing the compressor - a $200 air spring seal may be causing a $2,000 compressor to overwork and fail. Aftermarket solutions from Arnott offer cost savings. Converting to conventional springs ($1,500-$2,500) eliminates future air suspension costs but sacrifices ride height adjustment.</x:v>
-      </x:c>
-      <x:c r="F214" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G214" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="215" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A215" s="40" t="n">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="B215" s="9" t="str">
-        <x:v>audi-sq7-mmi-mib3-freeze-2020</x:v>
-      </x:c>
-      <x:c r="C215" s="9" t="str">
-        <x:v>2020-2026 | Audi | SQ7</x:v>
-      </x:c>
-      <x:c r="D215" s="9" t="str">
-        <x:v>2020-2026 Audi SQ7 Rearview Camera Software Recall 25V900 / 90TV</x:v>
-      </x:c>
-      <x:c r="E215" s="9" t="str">
-        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install the more robust driver-assistance software update free of charge. Until repaired, use extra caution when reversing and do not treat a restart, bus sleep or temporary image recovery as completion of the recall.</x:v>
-      </x:c>
-      <x:c r="F215" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G215" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="216" ht="990" hidden="0" customHeight="1">
-      <x:c r="A216" s="40" t="n">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="B216" s="9" t="str">
-        <x:v>audi-sq7-valve-cover-oil-leak-2020</x:v>
-      </x:c>
-      <x:c r="C216" s="9" t="str">
-        <x:v>2020-2024 | Audi | SQ7 | 4.0T</x:v>
-      </x:c>
-      <x:c r="D216" s="9" t="str">
-        <x:v>2020-2024 SQ7 4.0L High Oil Consumption and Piston-Ring Diagnosis - TSB 2071114/5</x:v>
-      </x:c>
-      <x:c r="E216" s="9" t="str">
-        <x:v>First inspect for visible engine-oil traces or leaks. Have an Audi dealer perform the authorized ODIS oil-consumption measurement, preserve and upload both test logs, and document the requested driving-profile data. Internal-engine repair is justified only when measured consumption exceeds the applicable limit and no other cause is found. If every TSB gate is met, follow Audi's VIN-, engine-code- and power-class-specific procedure for replacement of all eight pistons and piston rings, using current ETKA and ELSA information. Do not diagnose valve-cover gaskets or turbocharger seals from oil consumption alone.</x:v>
-      </x:c>
-      <x:c r="F216" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G216" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="217" ht="686.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A217" s="40" t="n">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="B217" s="9" t="str">
-        <x:v>audi-sq8-air-susp-compressor-2020</x:v>
-      </x:c>
-      <x:c r="C217" s="9" t="str">
-        <x:v>2020-2025 | Audi | SQ8</x:v>
-      </x:c>
-      <x:c r="D217" s="9" t="str">
-        <x:v>2020-2025 SQ8 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
-      </x:c>
-      <x:c r="E217" s="9" t="str">
-        <x:v>Inspect the wiring and connector contacts between J775 and J1135 before replacing a component. For a first passive or sporadic occurrence, clear the fault and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after wiring inspection, Audi directs replacement of J1135 under current repair and parts information. Do not buy struts, springs or a compressor solely from this warning.</x:v>
-      </x:c>
-      <x:c r="F217" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G217" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="218" ht="831.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A218" s="40" t="n">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="B218" s="9" t="str">
-        <x:v>audi-sq8-air-suspension-2020</x:v>
-      </x:c>
-      <x:c r="C218" s="9" t="str">
-        <x:v>2020-2024 | Audi | SQ8 | Premium Plus, Prestige | 4.0T</x:v>
-      </x:c>
-      <x:c r="D218" s="9" t="str">
-        <x:v>Adaptive Air Suspension Compressor and Air Spring Failures</x:v>
-      </x:c>
-      <x:c r="E218" s="9" t="str">
-        <x:v>Same diagnostic and repair approach as SQ7 (shared 4M platform). Isolate the failed component: air springs ($800-$1,500 per corner), compressor ($1,200-$2,500), valve block ($500-$1,000), or height sensor ($200-$400). Always check for air leaks before replacing the compressor. Aftermarket air suspension components from Arnott/Strutmasters offer 40-50% savings over OEM. Annual inspection of air springs for cracking recommended, especially in hot climates where UV and heat accelerate rubber degradation.</x:v>
-      </x:c>
-      <x:c r="F218" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G218" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="219" ht="448.79998779296875" hidden="0" customHeight="1">
-      <x:c r="A219" s="40" t="n">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="B219" s="9" t="str">
-        <x:v>audi-sq8-airbag-mount-2023</x:v>
-      </x:c>
-      <x:c r="C219" s="9" t="str">
-        <x:v>2023-2024 | Audi | SQ8 | 4.0T V8</x:v>
-      </x:c>
-      <x:c r="D219" s="9" t="str">
-        <x:v>2023-2024 SQ8 Driver-Seat Side-Airbag Mount Recall 69GA (23V868)</x:v>
-      </x:c>
-      <x:c r="E219" s="9" t="str">
-        <x:v>Check the VIN for open Audi recall 69GA and have an authorized dealer inspect the driver-seat side-airbag installation. If needed, the dealer will reinstall the airbag correctly; the recall filing says no parts are replaced. A clock spring or generic airbag part is not the recall remedy.</x:v>
-      </x:c>
-      <x:c r="F219" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G219" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="220" ht="580.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A220" s="40" t="n">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="B220" s="9" t="str">
-        <x:v>audi-sq8-mmi-mib3-freeze-2020</x:v>
-      </x:c>
-      <x:c r="C220" s="9" t="str">
-        <x:v>2020-2026 | Audi | SQ8 | 4.0T V8</x:v>
-      </x:c>
-      <x:c r="D220" s="9" t="str">
-        <x:v>2020-2026 SQ8 Rearview Camera Software Recall 90TV (25V900)</x:v>
-      </x:c>
-      <x:c r="E220" s="9" t="str">
-        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install more robust driver-assistance software free of charge. Until repaired, use extra caution when reversing and do not treat a restart, bus sleep or temporary image recovery as completion of the recall. A generic scan tool or head-unit replacement is not the recall remedy.</x:v>
-      </x:c>
-      <x:c r="F220" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G220" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="221" ht="567.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A221" s="40" t="n">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="B221" s="9" t="str">
-        <x:v>audi-sq8-turbo-coolant-2020</x:v>
-      </x:c>
-      <x:c r="C221" s="9" t="str">
-        <x:v>2020-2021 | Audi | SQ8 | 4.0T V8</x:v>
-      </x:c>
-      <x:c r="D221" s="9" t="str">
-        <x:v>2020-Early 2021 SQ8 Red Coolant Warning - Check G407 per TSB 2062951/4</x:v>
-      </x:c>
-      <x:c r="E221" s="9" t="str">
-        <x:v>Have the vehicle checked with Audi Guided Fault Finding and inspect G407 and its O-ring. Replace G407 only if the O-ring is damaged or pinched and the diagnosis matches the bulletin; follow the related Audi diagnostic path if additional listed faults are stored. Do not replace turbo coolant hoses, pumps or other cooling parts from this card alone.</x:v>
-      </x:c>
-      <x:c r="F221" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G221" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="222" ht="250.8000030517578" hidden="0" customHeight="1">
-      <x:c r="A222" s="40" t="n">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="B222" s="9" t="str">
-        <x:v>audi-tt-absesp-control-module-failure-2000</x:v>
-      </x:c>
-      <x:c r="C222" s="9" t="str">
-        <x:v>2000-2001 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D222" s="9" t="str">
-        <x:v>Driver Airbag Inflator May Deploy Improperly (Recall 21V470 / 69CJ)</x:v>
-      </x:c>
-      <x:c r="E222" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the driver frontal-airbag inflator with an alternative inflator free of charge under campaign 69CJ.</x:v>
-      </x:c>
-      <x:c r="F222" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G222" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="223" ht="277.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A223" s="40" t="n">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="B223" s="9" t="str">
-        <x:v>audi-tt-cam-follower-2008</x:v>
-      </x:c>
-      <x:c r="C223" s="9" t="str">
-        <x:v>2000-2000 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D223" s="9" t="str">
-        <x:v>Fuel-Line Assembly Can Leak (Recall 99V222)</x:v>
-      </x:c>
-      <x:c r="E223" s="9" t="str">
-        <x:v>Check VIN eligibility and campaign completion. Audi dealers replace the fuel-line assembly free of charge under recall 99V222. Stop driving if fuel odor or leakage is present.</x:v>
-      </x:c>
-      <x:c r="F223" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G223" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="224" ht="198" hidden="0" customHeight="1">
-      <x:c r="A224" s="40" t="n">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="B224" s="9" t="str">
-        <x:v>audi-tt-coil-pack-failure-and-2000</x:v>
-      </x:c>
-      <x:c r="C224" s="9" t="str">
-        <x:v>2000-2001 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D224" s="9" t="str">
-        <x:v>Rear Track-Control Arm Corrosion Can Restrict Movement (Recall 01V325)</x:v>
-      </x:c>
-      <x:c r="E224" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the rear track-control arms free of charge under recall 01V325.</x:v>
-      </x:c>
-      <x:c r="F224" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G224" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="225" ht="264" hidden="0" customHeight="1">
-      <x:c r="A225" s="40" t="n">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="B225" s="9" t="str">
-        <x:v>audi-tt-dsg-mechatronic-2008</x:v>
-      </x:c>
-      <x:c r="C225" s="9" t="str">
-        <x:v>2004-2004 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D225" s="9" t="str">
-        <x:v>Direct-Shift Gearbox Clutch Weld Can Lose Drive Torque (Recall 04V007)</x:v>
-      </x:c>
-      <x:c r="E225" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers replace the affected clutch free of charge under recall 04V007. If drive torque is lost, move out of traffic safely and arrange recovery.</x:v>
-      </x:c>
-      <x:c r="F225" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G225" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="226" ht="356.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A226" s="40" t="n">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="B226" s="9" t="str">
-        <x:v>audi-tt-dsg-transmission-2008</x:v>
-      </x:c>
-      <x:c r="C226" s="9" t="str">
-        <x:v>2009-2009 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D226" s="9" t="str">
-        <x:v>DSG Temperature-Sensor Wiring Can Trigger an Abrupt Shift to Neutral (Recall 09V333)</x:v>
-      </x:c>
-      <x:c r="E226" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers reprogram the transmission control module with updated software free of charge under recall 09V333. If the gear indicator flashes or neutral engages unexpectedly, stop safely.</x:v>
-      </x:c>
-      <x:c r="F226" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G226" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="227" ht="303.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A227" s="40" t="n">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="B227" s="9" t="str">
-        <x:v>audi-tt-front-control-arm-bushings-2000</x:v>
-      </x:c>
-      <x:c r="C227" s="9" t="str">
-        <x:v>2000-2000 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D227" s="9" t="str">
-        <x:v>High-Speed Directional-Stability Remedy (Recall 99V300)</x:v>
-      </x:c>
-      <x:c r="E227" s="9" t="str">
-        <x:v>Verify campaign completion with Audi. The factory remedy installs revised stabilizers, front control arms, firmer shock absorbers, and a rear spoiler as specified for the drivetrain configuration.</x:v>
-      </x:c>
-      <x:c r="F227" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G227" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="228" ht="237.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A228" s="40" t="n">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="B228" s="9" t="str">
-        <x:v>audi-tt-haldex-awd-coupling-pumpcontroller-2000</x:v>
-      </x:c>
-      <x:c r="C228" s="9" t="str">
-        <x:v>2008-2010 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D228" s="9" t="str">
-        <x:v>Fuel-Tank Ventilation Valve Can Allow Fuel Leakage (Recall 09V377)</x:v>
-      </x:c>
-      <x:c r="E228" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel-tank ventilation valve with the improved valve free of charge under recall 09V377.</x:v>
-      </x:c>
-      <x:c r="F228" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G228" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="229" ht="184.8000030517578" hidden="0" customHeight="1">
-      <x:c r="A229" s="40" t="n">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="B229" s="9" t="str">
-        <x:v>audi-tt-high-speed-stability-recall-for-2000</x:v>
-      </x:c>
-      <x:c r="C229" s="9" t="str">
-        <x:v>2016-2019 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D229" s="9" t="str">
-        <x:v>Fuel Tank Can Be Damaged by Heat-Shield Bracket in a Crash (Recall 20V076 / 20BX)</x:v>
-      </x:c>
-      <x:c r="E229" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers install a protective cap on the heat-shield bracket free of charge under campaign 20BX.</x:v>
-      </x:c>
-      <x:c r="F229" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G229" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="230" ht="237.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A230" s="40" t="n">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="B230" s="9" t="str">
-        <x:v>audi-tt-instrument-cluster-pixel-failure-2000</x:v>
-      </x:c>
-      <x:c r="C230" s="9" t="str">
-        <x:v>2016-2016 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D230" s="9" t="str">
-        <x:v>Front-Passenger Airbag Module May Explode or Deploy Improperly (Recall 22V543 / 69DY)</x:v>
-      </x:c>
-      <x:c r="E230" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the front-passenger airbag module free of charge under campaign 69DY/61C1.</x:v>
-      </x:c>
-      <x:c r="F230" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G230" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="231" ht="224.39999389648438" hidden="0" customHeight="1">
-      <x:c r="A231" s="40" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="B231" s="9" t="str">
-        <x:v>audi-tt-magnetic-ride-2008</x:v>
-      </x:c>
-      <x:c r="C231" s="9" t="str">
-        <x:v>2023-2023 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D231" s="9" t="str">
-        <x:v>Passenger-Seat Occupant Detection Connection Can Disable Airbag (Recall 24V251 / 69GU)</x:v>
-      </x:c>
-      <x:c r="E231" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers replace the passenger-seat occupant-detection control module free of charge under campaign 69GU.</x:v>
-      </x:c>
-      <x:c r="F231" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G231" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="232" ht="726" hidden="0" customHeight="1">
-      <x:c r="A232" s="40" t="n">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="B232" s="9" t="str">
-        <x:v>audi-tt-tail-light-corrosion-2008</x:v>
-      </x:c>
-      <x:c r="C232" s="9" t="str">
-        <x:v>2008-2015 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D232" s="9" t="str">
-        <x:v>Tail Light Electrical Connector Corrosion (Mk2)</x:v>
-      </x:c>
-      <x:c r="E232" s="9" t="str">
-        <x:v>Remove tail light assembly, inspect electrical connector for green corrosion. CLEAN connector with electrical contact cleaner and wire brush ($20 DIY). Apply dielectric grease to prevent future corrosion ($10). If connector is severely corroded: Replace pigtail connector ($50-$100 parts). Improve tail light seal with silicone sealant around housing ($15). This is a DIY-friendly repair taking 1-2 hours. If paying shop, costs $150-$300. Address early before corrosion causes shorts.</x:v>
-      </x:c>
-      <x:c r="F232" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G232" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="233" ht="171.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A233" s="40" t="n">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="B233" s="9" t="str">
-        <x:v>audi-tt-water-pump-2008</x:v>
-      </x:c>
-      <x:c r="C233" s="9" t="str">
-        <x:v>2008-2008 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D233" s="9" t="str">
-        <x:v>C-Pillar Trim Cover Can Detach During Belt-Tensioner Deployment (Recall 08V064)</x:v>
-      </x:c>
-      <x:c r="E233" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers install improved C-pillar trim clips free of charge under recall 08V064.</x:v>
-      </x:c>
-      <x:c r="F233" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G233" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="234" ht="1161.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A234" s="40" t="n">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="B234" s="9" t="str">
-        <x:v>audi-tts-cam-follower-hpfp-2009</x:v>
-      </x:c>
-      <x:c r="C234" s="9" t="str">
-        <x:v>2009-2015 | Audi | TTS | TTS | EA888</x:v>
-      </x:c>
-      <x:c r="D234" s="9" t="str">
-        <x:v>HPFP Cam Follower Wear and High-Pressure Fuel Pump Failure (Mk2)</x:v>
-      </x:c>
-      <x:c r="E234" s="9" t="str">
-        <x:v>INSPECTION (every 20,000 miles): Remove HPFP (3 bolts) and inspect cam follower surface. If the hardened coating is wearing through (visible copper/brass color), replace follower immediately ($30-$50 part, 30-60 minutes labor). CRITICAL: Ensure cam lobe is at LOW point before reinstalling—if at peak, you'll compress the spring and can break the mounting bolts. If CAMSHAFT WORN (deep groove in lobe): Replace camshaft ($2,000-$4,000). If FUEL PUMP FAILED: Replace HPFP ($400-$800). PREVENTION: Inspect cam follower every 20,000 miles as routine maintenance. Add to every oil change checklist. Consider IE (Integrated Engineering) upgraded HPFP with roller follower to eliminate wear entirely.</x:v>
-      </x:c>
-      <x:c r="F234" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G234" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="235" ht="884.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A235" s="40" t="n">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="B235" s="9" t="str">
-        <x:v>audi-tts-carbon-buildup-2009</x:v>
-      </x:c>
-      <x:c r="C235" s="9" t="str">
-        <x:v>2016-2017 | Audi | TTS</x:v>
-      </x:c>
-      <x:c r="D235" s="9" t="str">
-        <x:v>2016-2017 TTS Cold-Start Misfire DTCs Without Felt Misfire - TSB 2051384/1</x:v>
-      </x:c>
-      <x:c r="E235" s="9" t="str">
-        <x:v>Confirm the exact cold-start timing, simultaneous-cylinder DTC pattern, absence of a felt misfire, CYFB engine and installed ECM software before using this bulletin. When applicable, an Audi-capable workshop updates ECM J623 from software part number 8S0906259C version 0001 to version 0004 or higher using SVM action 01A190, then clears the DTCs. A felt misfire, a different timing or RPM pattern, a different engine/software combination or a returning concern requires normal diagnosis rather than carbon cleaning by assumption.</x:v>
-      </x:c>
-      <x:c r="F235" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G235" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="236" ht="910.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A236" s="40" t="n">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="B236" s="9" t="str">
-        <x:v>audi-tts-dsg-mechatronic-2009</x:v>
-      </x:c>
-      <x:c r="C236" s="9" t="str">
-        <x:v>2019-2023 | Audi | TTS</x:v>
-      </x:c>
-      <x:c r="D236" s="9" t="str">
-        <x:v>2019-2023 TTS Clutch K1 Overheat and Transmission DTC Diagnosis - TSB 2060560/3</x:v>
-      </x:c>
-      <x:c r="E236" s="9" t="str">
-        <x:v>Have an Audi-capable workshop check whether TSB 2050723 applies first. If it does not resolve or control the concern, inspect the clutch-K1 maximum-temperature value and document a transmission-fluid sample. Replace the dual clutch, transmission fluid and filter only when the approximately 400 °C K1 value and burnt black or very dark fluid are both present. If those findings are absent, this bulletin does not apply and Audi directs the workshop to continue diagnosis through TAC. Any clutch repair kit must be selected by VIN and production date.</x:v>
-      </x:c>
-      <x:c r="F236" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G236" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="237" ht="858" hidden="0" customHeight="1">
-      <x:c r="A237" s="40" t="n">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="B237" s="9" t="str">
-        <x:v>audi-tts-magnetic-ride-2009</x:v>
-      </x:c>
-      <x:c r="C237" s="9" t="str">
-        <x:v>2016-2016 | Audi | TTS</x:v>
-      </x:c>
-      <x:c r="D237" s="9" t="str">
-        <x:v>2016 TTS Magnetic-Ride Rear Shock-Mount Rumble - TSB 2042539/4</x:v>
-      </x:c>
-      <x:c r="E237" s="9" t="str">
-        <x:v>First reproduce the noise, verify that it comes from the rear shock mounts and confirm that the vehicle was originally equipped with mount 8S0 513 353. Only when those gates are satisfied, remove both rear shock assemblies and replace both mounts with 8V0 513 353 according to Audi workshop instructions, adapt the suspension control position and test drive to confirm the repair. If the installed mount does not match, continue Audi diagnosis. Do not replace magnetic dampers or convert the vehicle to coilovers from this noise alone.</x:v>
-      </x:c>
-      <x:c r="F237" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G237" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="238" ht="1016.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A238" s="40" t="n">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="B238" s="9" t="str">
-        <x:v>audi-tts-timing-chain-tensioner-2009</x:v>
-      </x:c>
-      <x:c r="C238" s="9" t="str">
-        <x:v>2009-2015 | Audi | TTS | TTS | EA888 Gen 1, EA888 Gen 2</x:v>
-      </x:c>
-      <x:c r="D238" s="9" t="str">
-        <x:v>Timing Chain Tensioner Failure (EA888 Gen 1/2 - Mk2 TTS)</x:v>
-      </x:c>
-      <x:c r="E238" s="9" t="str">
-        <x:v>PREVENTIVE REPLACEMENT: Replace timing chain, tensioner, guides, and sprockets at 80,000-100,000 miles BEFORE symptoms appear ($2,000-$4,000). This is the MOST important preventive maintenance on the Mk2 TTS. IF RATTLING: Do NOT delay—the chain can jump at any startup. Schedule repair immediately. Use ONLY the latest OEM revised tensioner (06K109467K). IF CHAIN JUMPED: Engine likely destroyed—compression test all cylinders. Rebuild ($5,000-$8,000) or replacement engine ($6,000-$12,000). PREVENTION: Change oil every 5,000 miles with high-quality synthetic. Low oil level accelerates tensioner wear.</x:v>
-      </x:c>
-      <x:c r="F238" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G238" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="239" ht="976.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A239" s="40" t="n">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="B239" s="9" t="str">
-        <x:v>audi-tts-water-pump-2009</x:v>
-      </x:c>
-      <x:c r="C239" s="9" t="str">
-        <x:v>2012-2023 | Audi | TTS</x:v>
-      </x:c>
-      <x:c r="D239" s="9" t="str">
-        <x:v>2012 / 2020-2023 TTS Coolant-Pump Update and Leak Diagnosis</x:v>
-      </x:c>
-      <x:c r="E239" s="9" t="str">
-        <x:v>For a 2012 TTS, ask an Audi dealer to check the VIN and current campaign/action history for Update 19J2; the published update replaced the pump only when its exact criteria were met and does not promise current warranty coverage. For a 2020-2023 2.0L TTS, first exclude a low level caused by incomplete bleeding or an earlier repair, document and clean the suspected leak, refill to maximum and recheck after driving. Continue observation when no leak returns; replace only the component proven to leak when coolant reappears. Do not select a pump or thermostat assembly before VIN-, engine- and leak-specific diagnosis.</x:v>
-      </x:c>
-      <x:c r="F239" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G239" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="240" ht="198" hidden="0" customHeight="1">
-      <x:c r="A240" s="42" t="n">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="B240" s="43" t="str">
+      <x:c r="B190" s="43" t="str">
         <x:v>audi-tts-waterpump-housing-2009</x:v>
       </x:c>
-      <x:c r="C240" s="43" t="str">
+      <x:c r="C190" s="43" t="str">
         <x:v>2009-2024 | Audi | TTS | EA888</x:v>
       </x:c>
-      <x:c r="D240" s="43" t="str">
+      <x:c r="D190" s="43" t="str">
         <x:v>Water Pump and Thermostat Housing Failure</x:v>
       </x:c>
-      <x:c r="E240" s="43" t="str">
+      <x:c r="E190" s="43" t="str">
         <x:v>Replace water pump, thermostat, and housing as a complete assembly. Use metal-impeller aftermarket pump if available.</x:v>
       </x:c>
-      <x:c r="F240" s="43" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G240" s="44" t="str">
+      <x:c r="F190" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G190" s="44" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>

--- a/outputs/audi-repair-first-review/Audi-repair-first-fitment-review.xlsx
+++ b/outputs/audi-repair-first-review/Audi-repair-first-fitment-review.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R418bf19a57044f3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audi Review" sheetId="2" r:id="Re4cbc34205a440a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Queue" sheetId="3" r:id="Rd9126246985f4582"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" r:id="Re82e4b5bb1414dea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rbfc4caea0ca249d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audi Review" sheetId="2" r:id="Rbd35e80b5fdf4e3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Queue" sheetId="3" r:id="Rcfbb0f41b79b4721"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" r:id="Reccd3ecfa5934e37"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -484,7 +484,7 @@
         <x:v>Reviewed in this batch</x:v>
       </x:c>
       <x:c r="B5" s="13" t="n">
-        <x:v>200</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C5" s="11"/>
       <x:c r="D5" s="11"/>
@@ -498,7 +498,7 @@
         <x:v>Remaining queue</x:v>
       </x:c>
       <x:c r="B6" s="13" t="n">
-        <x:v>189</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C6" s="11"/>
       <x:c r="D6" s="11"/>
@@ -512,7 +512,7 @@
         <x:v>Issues with destinations</x:v>
       </x:c>
       <x:c r="B7" s="13" t="n">
-        <x:v>196</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C7" s="11"/>
       <x:c r="D7" s="11"/>
@@ -526,7 +526,7 @@
         <x:v>Destination entries</x:v>
       </x:c>
       <x:c r="B8" s="13" t="n">
-        <x:v>344</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="C8" s="11"/>
       <x:c r="D8" s="11"/>
@@ -540,7 +540,7 @@
         <x:v>Distinct URLs</x:v>
       </x:c>
       <x:c r="B9" s="13" t="n">
-        <x:v>67</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C9" s="11"/>
       <x:c r="D9" s="11"/>
@@ -12641,28 +12641,3016 @@
       </x:c>
     </x:row>
     <x:row r="349" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A349" s="42" t="str"/>
-      <x:c r="B349" s="43" t="str"/>
-      <x:c r="C349" s="43" t="str"/>
-      <x:c r="D349" s="43" t="str"/>
-      <x:c r="E349" s="43" t="str"/>
-      <x:c r="F349" s="43" t="str"/>
-      <x:c r="G349" s="43" t="str"/>
-      <x:c r="H349" s="43" t="str">
+      <x:c r="A349" s="40" t="str"/>
+      <x:c r="B349" s="9" t="str"/>
+      <x:c r="C349" s="9" t="str"/>
+      <x:c r="D349" s="9" t="str"/>
+      <x:c r="E349" s="9" t="str"/>
+      <x:c r="F349" s="9" t="str"/>
+      <x:c r="G349" s="9" t="str"/>
+      <x:c r="H349" s="9" t="str">
         <x:v>Audi specialist locator</x:v>
       </x:c>
-      <x:c r="I349" s="43" t="str">
+      <x:c r="I349" s="9" t="str">
         <x:v>https://www.audishops.com/</x:v>
       </x:c>
-      <x:c r="J349" s="43" t="str">
+      <x:c r="J349" s="9" t="str">
         <x:v>trained VAG SAI diagnosis</x:v>
       </x:c>
-      <x:c r="K349" s="43" t="str">
+      <x:c r="K349" s="9" t="str">
         <x:v>specialist emissions service</x:v>
       </x:c>
-      <x:c r="L349" s="43" t="str"/>
-      <x:c r="M349" s="43" t="str"/>
-      <x:c r="N349" s="44" t="str"/>
+      <x:c r="L349" s="9" t="str"/>
+      <x:c r="M349" s="9" t="str"/>
+      <x:c r="N349" s="41" t="str"/>
+    </x:row>
+    <x:row r="350" ht="712.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A350" s="40" t="n">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B350" s="9" t="str">
+        <x:v>audi-q7-supercharger-failure-2011</x:v>
+      </x:c>
+      <x:c r="C350" s="9" t="str">
+        <x:v>2011-2015 | Audi | Q7 | Premium, Premium Plus, Prestige, S line, SQ7 | 3.0T</x:v>
+      </x:c>
+      <x:c r="D350" s="9" t="str">
+        <x:v>Supercharger Bearing Failure and Boost Leaks (3.0T)</x:v>
+      </x:c>
+      <x:c r="E350" s="9" t="str">
+        <x:v>Worn bearings: Supercharger rebuild with new bearings ($1,500-2,500) or replacement supercharger ($3,000-5,000). Bypass valve: Replace supercharger bypass valve ($300-600). Boost leaks: Inspect all boost hoses/clamps, replace cracked hoses ($150-400). Use OEM Audi or quality aftermarket (INA) supercharger bearings. AudiWorld recommends catch can installation ($300-500) to reduce oil vapor damage to supercharger.</x:v>
+      </x:c>
+      <x:c r="F350" s="9" t="str">
+        <x:v>3.0T boost/smoke/leak test; distinguish hose/clamp, bypass valve, pulley/bearing and complete supercharger; exact failed component/VIN</x:v>
+      </x:c>
+      <x:c r="G350" s="9" t="str">
+        <x:v>COMPONENT / BOOST-DIAGNOSIS GATE</x:v>
+      </x:c>
+      <x:c r="H350" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I350" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J350" s="9" t="str">
+        <x:v>2011-2015 Q7 3.0T boost and supercharger diagnosis</x:v>
+      </x:c>
+      <x:c r="K350" s="9" t="str">
+        <x:v>specialist engine service</x:v>
+      </x:c>
+      <x:c r="L350" s="9" t="str"/>
+      <x:c r="M350" s="9" t="str">
+        <x:v>Bearing, bypass and external boost leaks require different repairs.</x:v>
+      </x:c>
+      <x:c r="N350" s="41" t="str">
+        <x:v>Trim list wrongly includes SQ7; no catch-can or generic bearing link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351" ht="66" hidden="0" customHeight="1">
+      <x:c r="A351" s="40" t="str"/>
+      <x:c r="B351" s="9" t="str"/>
+      <x:c r="C351" s="9" t="str"/>
+      <x:c r="D351" s="9" t="str"/>
+      <x:c r="E351" s="9" t="str"/>
+      <x:c r="F351" s="9" t="str"/>
+      <x:c r="G351" s="9" t="str"/>
+      <x:c r="H351" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I351" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J351" s="9" t="str">
+        <x:v>VIN component/supersession</x:v>
+      </x:c>
+      <x:c r="K351" s="9" t="str">
+        <x:v>manufacturer parts route</x:v>
+      </x:c>
+      <x:c r="L351" s="9" t="str"/>
+      <x:c r="M351" s="9" t="str"/>
+      <x:c r="N351" s="41" t="str"/>
+    </x:row>
+    <x:row r="352" ht="646.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A352" s="40" t="n">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="B352" s="9" t="str">
+        <x:v>audi-q7-tdi-emissions-scandal-2009</x:v>
+      </x:c>
+      <x:c r="C352" s="9" t="str">
+        <x:v>2009-2015 | Audi | Q7 | 3.0 TDI</x:v>
+      </x:c>
+      <x:c r="D352" s="9" t="str">
+        <x:v>2009-2015 Q7 3.0 TDI Emissions Settlement and Modification History</x:v>
+      </x:c>
+      <x:c r="E352" s="9" t="str">
+        <x:v>Check the VIN and service history with an authorized Audi dealer and use current EPA or Audi settlement information to determine whether an emissions modification was completed and what extended emissions warranty, if any, applies to that vehicle. Diagnose any present warning or drivability concern separately. Do not buy a scan tool or generic repair manual as a settlement remedy.</x:v>
+      </x:c>
+      <x:c r="F352" s="9" t="str">
+        <x:v>VIN modification/settlement history and current extended-emissions coverage; separate present-fault diagnosis</x:v>
+      </x:c>
+      <x:c r="G352" s="9" t="str">
+        <x:v>VIN / COVERAGE ROUTE ONLY</x:v>
+      </x:c>
+      <x:c r="H352" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I352" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J352" s="9" t="str">
+        <x:v>2009-2015 Q7 3.0 TDI modification/coverage history</x:v>
+      </x:c>
+      <x:c r="K352" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L352" s="9" t="str"/>
+      <x:c r="M352" s="9" t="str">
+        <x:v>Settlement status is VIN-specific and not a retail repair.</x:v>
+      </x:c>
+      <x:c r="N352" s="41" t="str">
+        <x:v>No scanner/manual link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A353" s="40" t="str"/>
+      <x:c r="B353" s="9" t="str"/>
+      <x:c r="C353" s="9" t="str"/>
+      <x:c r="D353" s="9" t="str"/>
+      <x:c r="E353" s="9" t="str"/>
+      <x:c r="F353" s="9" t="str"/>
+      <x:c r="G353" s="9" t="str"/>
+      <x:c r="H353" s="9" t="str">
+        <x:v>EPA Volkswagen diesel information</x:v>
+      </x:c>
+      <x:c r="I353" s="9" t="str">
+        <x:v>https://www.epa.gov/vw</x:v>
+      </x:c>
+      <x:c r="J353" s="9" t="str">
+        <x:v>current official settlement/emissions information</x:v>
+      </x:c>
+      <x:c r="K353" s="9" t="str">
+        <x:v>government information</x:v>
+      </x:c>
+      <x:c r="L353" s="9" t="str"/>
+      <x:c r="M353" s="9" t="str"/>
+      <x:c r="N353" s="41" t="str"/>
+    </x:row>
+    <x:row r="354" ht="594" hidden="0" customHeight="1">
+      <x:c r="A354" s="40" t="n">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="B354" s="9" t="str">
+        <x:v>audi-q7-tdi-oil-cooler-leak-2013</x:v>
+      </x:c>
+      <x:c r="C354" s="9" t="str">
+        <x:v>2013-2013 | Audi | Q7 | 3.0 TDI</x:v>
+      </x:c>
+      <x:c r="D354" s="9" t="str">
+        <x:v>2013 Q7 TDI Brake-Booster Vacuum-Line Recall 47L8 (14V516)</x:v>
+      </x:c>
+      <x:c r="E354" s="9" t="str">
+        <x:v>Check the VIN for open recall 47L8 with Audi. The dealer remedy replaces the specified vacuum line and inspects the vacuum line and brake booster for oil contamination. Additional vacuum-line or brake-booster components are replaced when contamination is found. The recall repair is dealer work and is not a reason to buy an oil cooler, scan tool or manual.</x:v>
+      </x:c>
+      <x:c r="F354" s="9" t="str">
+        <x:v>VIN/47L8/14V516 check; dealer vacuum-line replacement plus contamination inspection and conditional booster/line parts</x:v>
+      </x:c>
+      <x:c r="G354" s="9" t="str">
+        <x:v>SOURCE-ID MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H354" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I354" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J354" s="9" t="str">
+        <x:v>2013 Q7 TDI 47L8</x:v>
+      </x:c>
+      <x:c r="K354" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L354" s="9" t="str"/>
+      <x:c r="M354" s="9" t="str">
+        <x:v>Repair is brake-booster vacuum-line recall, not oil cooler.</x:v>
+      </x:c>
+      <x:c r="N354" s="41" t="str">
+        <x:v>Rename/re-key; no oil-cooler/scanner/manual link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A355" s="40" t="str"/>
+      <x:c r="B355" s="9" t="str"/>
+      <x:c r="C355" s="9" t="str"/>
+      <x:c r="D355" s="9" t="str"/>
+      <x:c r="E355" s="9" t="str"/>
+      <x:c r="F355" s="9" t="str"/>
+      <x:c r="G355" s="9" t="str"/>
+      <x:c r="H355" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I355" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J355" s="9" t="str">
+        <x:v>14V516 VIN history</x:v>
+      </x:c>
+      <x:c r="K355" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L355" s="9" t="str"/>
+      <x:c r="M355" s="9" t="str"/>
+      <x:c r="N355" s="41" t="str"/>
+    </x:row>
+    <x:row r="356" ht="488.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A356" s="40" t="n">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B356" s="9" t="str">
+        <x:v>audi-q7-timing-chain-tensioner-2007</x:v>
+      </x:c>
+      <x:c r="C356" s="9" t="str">
+        <x:v>2011-2015 | Audi | Q7 | 3.0 TFSI</x:v>
+      </x:c>
+      <x:c r="D356" s="9" t="str">
+        <x:v>2011-2015 Q7 3.0 TFSI Brief Cold-Start Timing-Chain Rattle - TSB 2039995/2</x:v>
+      </x:c>
+      <x:c r="E356" s="9" t="str">
+        <x:v>Confirm that the concern is the bulletin-defined one-to-three-second first-start rattle and have an Audi technician follow TSB 2039995/2 and current repair information. A longer, persistent or different noise, warning light or drivability concern requires separate diagnosis. Do not order a timing kit from this card.</x:v>
+      </x:c>
+      <x:c r="F356" s="9" t="str">
+        <x:v>Confirm 2011-2015 3.0 TFSI exact 1-3 second first-start rattle; TSB upper tensioners; separate other noise/fault diagnosis</x:v>
+      </x:c>
+      <x:c r="G356" s="9" t="str">
+        <x:v>SOURCE-YEAR MISMATCH / TSB SERVICE</x:v>
+      </x:c>
+      <x:c r="H356" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I356" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J356" s="9" t="str">
+        <x:v>Q7 TSB 2039995/2</x:v>
+      </x:c>
+      <x:c r="K356" s="9" t="str">
+        <x:v>manufacturer timing service</x:v>
+      </x:c>
+      <x:c r="L356" s="9" t="str"/>
+      <x:c r="M356" s="9" t="str">
+        <x:v>Only exact bulletin condition follows this repair.</x:v>
+      </x:c>
+      <x:c r="N356" s="41" t="str">
+        <x:v>Identifier says 2007; no complete timing-kit link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="357" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A357" s="40" t="str"/>
+      <x:c r="B357" s="9" t="str"/>
+      <x:c r="C357" s="9" t="str"/>
+      <x:c r="D357" s="9" t="str"/>
+      <x:c r="E357" s="9" t="str"/>
+      <x:c r="F357" s="9" t="str"/>
+      <x:c r="G357" s="9" t="str"/>
+      <x:c r="H357" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I357" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J357" s="9" t="str">
+        <x:v>cold-start timing diagnosis</x:v>
+      </x:c>
+      <x:c r="K357" s="9" t="str">
+        <x:v>specialist engine service</x:v>
+      </x:c>
+      <x:c r="L357" s="9" t="str"/>
+      <x:c r="M357" s="9" t="str"/>
+      <x:c r="N357" s="41" t="str"/>
+    </x:row>
+    <x:row r="358" ht="435.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A358" s="40" t="n">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="B358" s="9" t="str">
+        <x:v>audi-q7-transfer-case-2007</x:v>
+      </x:c>
+      <x:c r="C358" s="9" t="str">
+        <x:v>2007-2019 | Audi | Q7 | Premium, Premium Plus, Prestige | 3.0T, 3.6L, 4.2L, 3.0 TDI</x:v>
+      </x:c>
+      <x:c r="D358" s="9" t="str">
+        <x:v>Transfer Case Fluid Leak and Failure</x:v>
+      </x:c>
+      <x:c r="E358" s="9" t="str">
+        <x:v>Replace leaking seals and refill with correct fluid (75W-90 GL-5 or Audi specification). If grinding is present, the transfer case may need rebuild or replacement. Regular fluid changes every 60,000 miles can prevent internal damage. Check for leaks at every oil change.</x:v>
+      </x:c>
+      <x:c r="F358" s="9" t="str">
+        <x:v>Identify transfer-case/final-drive code and exact leak source; VIN/position seals; manufacturer-specified fluid; rebuild/replacement only after internal diagnosis</x:v>
+      </x:c>
+      <x:c r="G358" s="9" t="str">
+        <x:v>DRIVELINE-CODE / LEAK-SOURCE GATE</x:v>
+      </x:c>
+      <x:c r="H358" s="9" t="str">
+        <x:v>Audi Q7 transfer-case fluid catalog</x:v>
+      </x:c>
+      <x:c r="I358" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/Q7/Transfer-Case-Fluid/</x:v>
+      </x:c>
+      <x:c r="J358" s="9" t="str">
+        <x:v>2007-2019 Q7; verify transfer-case code and exact Audi fluid before purchase</x:v>
+      </x:c>
+      <x:c r="K358" s="9" t="str">
+        <x:v>conditional fluid catalog</x:v>
+      </x:c>
+      <x:c r="L358" s="9" t="str"/>
+      <x:c r="M358" s="9" t="str">
+        <x:v>The live catalog does not prove generic 75W-90 for every case.</x:v>
+      </x:c>
+      <x:c r="N358" s="41" t="str">
+        <x:v>No universal 60k interval or transfer-case replacement from grinding alone.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359" ht="66" hidden="0" customHeight="1">
+      <x:c r="A359" s="40" t="str"/>
+      <x:c r="B359" s="9" t="str"/>
+      <x:c r="C359" s="9" t="str"/>
+      <x:c r="D359" s="9" t="str"/>
+      <x:c r="E359" s="9" t="str"/>
+      <x:c r="F359" s="9" t="str"/>
+      <x:c r="G359" s="9" t="str"/>
+      <x:c r="H359" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I359" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J359" s="9" t="str">
+        <x:v>seal, bearing/grinding and fluid diagnosis</x:v>
+      </x:c>
+      <x:c r="K359" s="9" t="str">
+        <x:v>specialist driveline service</x:v>
+      </x:c>
+      <x:c r="L359" s="9" t="str"/>
+      <x:c r="M359" s="9" t="str"/>
+      <x:c r="N359" s="41" t="str"/>
+    </x:row>
+    <x:row r="360" ht="673.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A360" s="40" t="n">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="B360" s="9" t="str">
+        <x:v>audi-q7-water-pump-failure-2007</x:v>
+      </x:c>
+      <x:c r="C360" s="9" t="str">
+        <x:v>2007-2015 | Audi | Q7</x:v>
+      </x:c>
+      <x:c r="D360" s="9" t="str">
+        <x:v>Water Pump and Thermostat Failure (Overheating)</x:v>
+      </x:c>
+      <x:c r="E360" s="9" t="str">
+        <x:v>IMMEDIATE if overheating: Pull over, turn off engine, DO NOT continue - engine damage occurs in minutes. Preventive: Replace water pump/thermostat assembly at 60k-80k miles ($800-1,500) to avoid catastrophic failure. Failed pump: Replace water pump/thermostat ($800-1,500). If overheated: Cylinder head inspection, possible head gasket replacement ($2,500-5,000). Use OEM Audi or premium Geba/Meyle parts.</x:v>
+      </x:c>
+      <x:c r="F360" s="9" t="str">
+        <x:v>Stop for overheating; split engines and pressure-test pump/thermostat/leak source; exact component and coolant; overheat damage test</x:v>
+      </x:c>
+      <x:c r="G360" s="9" t="str">
+        <x:v>MULTI-ENGINE / LEAK-SOURCE GATE</x:v>
+      </x:c>
+      <x:c r="H360" s="9" t="str">
+        <x:v>Audi Q7 water-pump catalog</x:v>
+      </x:c>
+      <x:c r="I360" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/Q7/Water-Pump/</x:v>
+      </x:c>
+      <x:c r="J360" s="9" t="str">
+        <x:v>2007-2015 Q7; exact engine/VIN and confirmed failed component</x:v>
+      </x:c>
+      <x:c r="K360" s="9" t="str">
+        <x:v>vehicle-specific pump catalog</x:v>
+      </x:c>
+      <x:c r="L360" s="9" t="str"/>
+      <x:c r="M360" s="9" t="str">
+        <x:v>The range includes multiple unrelated pumps/thermostats.</x:v>
+      </x:c>
+      <x:c r="N360" s="41" t="str">
+        <x:v>No universal preventive 60k-80k assembly replacement or brand claim.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361" ht="66" hidden="0" customHeight="1">
+      <x:c r="A361" s="40" t="str"/>
+      <x:c r="B361" s="9" t="str"/>
+      <x:c r="C361" s="9" t="str"/>
+      <x:c r="D361" s="9" t="str"/>
+      <x:c r="E361" s="9" t="str"/>
+      <x:c r="F361" s="9" t="str"/>
+      <x:c r="G361" s="9" t="str"/>
+      <x:c r="H361" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I361" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J361" s="9" t="str">
+        <x:v>pressure test and overheat-damage diagnosis</x:v>
+      </x:c>
+      <x:c r="K361" s="9" t="str">
+        <x:v>specialist cooling service</x:v>
+      </x:c>
+      <x:c r="L361" s="9" t="str"/>
+      <x:c r="M361" s="9" t="str"/>
+      <x:c r="N361" s="41" t="str"/>
+    </x:row>
+    <x:row r="362" ht="633.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A362" s="40" t="n">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="B362" s="9" t="str">
+        <x:v>audi-q8-48v-system-2019</x:v>
+      </x:c>
+      <x:c r="C362" s="9" t="str">
+        <x:v>2019-2024 | Audi | Q8</x:v>
+      </x:c>
+      <x:c r="D362" s="9" t="str">
+        <x:v>2019-2024 Q8 Starter-Alternator Service Action 27BQ - Check VIN</x:v>
+      </x:c>
+      <x:c r="E362" s="9" t="str">
+        <x:v>Check the VIN and current campaign status with an Audi dealer. If 27BQ is open, the dealer follows the campaign procedure and replaces the starter-alternator at no cost when directed. If the action is not open, use Audi guided diagnostics: current bulletins distinguish a replacement result from sensor and CAN faults that replacement will not fix. Do not buy a 12V battery, charger or starter from this card.</x:v>
+      </x:c>
+      <x:c r="F362" s="9" t="str">
+        <x:v>VIN/open 27BQ check; campaign starter-alternator; outside campaign guided tests distinguishing replacement from sensor/CAN faults</x:v>
+      </x:c>
+      <x:c r="G362" s="9" t="str">
+        <x:v>48V CAMPAIGN / GUIDED SERVICE</x:v>
+      </x:c>
+      <x:c r="H362" s="9" t="str">
+        <x:v>Audi recall and campaign lookup</x:v>
+      </x:c>
+      <x:c r="I362" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J362" s="9" t="str">
+        <x:v>2019-2024 Q8 27BQ</x:v>
+      </x:c>
+      <x:c r="K362" s="9" t="str">
+        <x:v>manufacturer campaign lookup</x:v>
+      </x:c>
+      <x:c r="L362" s="9" t="str"/>
+      <x:c r="M362" s="9" t="str">
+        <x:v>Replacement depends on VIN/test result.</x:v>
+      </x:c>
+      <x:c r="N362" s="41" t="str">
+        <x:v>No 12V battery, charger or starter link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="363" ht="66" hidden="0" customHeight="1">
+      <x:c r="A363" s="40" t="str"/>
+      <x:c r="B363" s="9" t="str"/>
+      <x:c r="C363" s="9" t="str"/>
+      <x:c r="D363" s="9" t="str"/>
+      <x:c r="E363" s="9" t="str"/>
+      <x:c r="F363" s="9" t="str"/>
+      <x:c r="G363" s="9" t="str"/>
+      <x:c r="H363" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I363" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J363" s="9" t="str">
+        <x:v>48V guided diagnosis/remedy</x:v>
+      </x:c>
+      <x:c r="K363" s="9" t="str">
+        <x:v>authorized high-voltage service</x:v>
+      </x:c>
+      <x:c r="L363" s="9" t="str"/>
+      <x:c r="M363" s="9" t="str"/>
+      <x:c r="N363" s="41" t="str"/>
+    </x:row>
+    <x:row r="364" ht="422.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A364" s="40" t="n">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="B364" s="9" t="str">
+        <x:v>audi-q8-8-speed-tiptronic-harsh-shifting-jolt-delayed-engagement</x:v>
+      </x:c>
+      <x:c r="C364" s="9" t="str">
+        <x:v>2019-2023 | Audi | Q8 | Q8 55 TFSI, SQ8, RS Q8, 50 TDI</x:v>
+      </x:c>
+      <x:c r="D364" s="9" t="str">
+        <x:v>8-Speed Tiptronic Harsh Shifting, Jolt and Delayed Engagement</x:v>
+      </x:c>
+      <x:c r="E364" s="9" t="str">
+        <x:v>Perform a full ZF 8HP transmission fluid and filter (pan) service with the correct Audi-spec fluid, then run the gearbox adaptation/relearn procedure. Update the transmission control module software if a TSB applies. Inspect transmission and engine mounts and replace if collapsed.</x:v>
+      </x:c>
+      <x:c r="F364" s="9" t="str">
+        <x:v>Identify exact ZF 8HP code/application; faults, fluid/debris, adaptation/software and mount diagnosis; exact pan/filter/fluid only when service branch applies</x:v>
+      </x:c>
+      <x:c r="G364" s="9" t="str">
+        <x:v>TRANSMISSION-CODE / DIAGNOSTIC GATE</x:v>
+      </x:c>
+      <x:c r="H364" s="9" t="str">
+        <x:v>Audi Q8 transmission-service catalog</x:v>
+      </x:c>
+      <x:c r="I364" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/Q8/Automatic-Transmission-Service/</x:v>
+      </x:c>
+      <x:c r="J364" s="9" t="str">
+        <x:v>2019-2023 Q8/SQ8/RS Q8; exact transmission code and fluid spec</x:v>
+      </x:c>
+      <x:c r="K364" s="9" t="str">
+        <x:v>vehicle-specific transmission catalog</x:v>
+      </x:c>
+      <x:c r="L364" s="9" t="str"/>
+      <x:c r="M364" s="9" t="str">
+        <x:v>Variants do not share one fluid/service path.</x:v>
+      </x:c>
+      <x:c r="N364" s="41" t="str">
+        <x:v>Do not service or reset adaptations before code/fault diagnosis.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="365" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A365" s="40" t="str"/>
+      <x:c r="B365" s="9" t="str"/>
+      <x:c r="C365" s="9" t="str"/>
+      <x:c r="D365" s="9" t="str"/>
+      <x:c r="E365" s="9" t="str"/>
+      <x:c r="F365" s="9" t="str"/>
+      <x:c r="G365" s="9" t="str"/>
+      <x:c r="H365" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I365" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J365" s="9" t="str">
+        <x:v>shift/adaptation/mount diagnosis</x:v>
+      </x:c>
+      <x:c r="K365" s="9" t="str">
+        <x:v>specialist transmission service</x:v>
+      </x:c>
+      <x:c r="L365" s="9" t="str"/>
+      <x:c r="M365" s="9" t="str"/>
+      <x:c r="N365" s="41" t="str"/>
+    </x:row>
+    <x:row r="366" ht="699.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A366" s="40" t="n">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B366" s="9" t="str">
+        <x:v>audi-q8-air-suspension-2019</x:v>
+      </x:c>
+      <x:c r="C366" s="9" t="str">
+        <x:v>2019-2025 | Audi | Q8</x:v>
+      </x:c>
+      <x:c r="D366" s="9" t="str">
+        <x:v>2019-2025 Q8 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
+      </x:c>
+      <x:c r="E366" s="9" t="str">
+        <x:v>Inspect the wiring and connector contacts between J775 and J1135 before replacing a component. For a first passive or sporadic occurrence, clear the fault and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after wiring inspection, Audi directs replacement of J1135 under current repair and parts information. Do not buy struts, springs, a compressor or a conversion kit solely from this warning.</x:v>
+      </x:c>
+      <x:c r="F366" s="9" t="str">
+        <x:v>J775-J1135 wiring/contact inspection; clear first passive event; conditional J1135 after active/static or second return</x:v>
+      </x:c>
+      <x:c r="G366" s="9" t="str">
+        <x:v>TSB CONDITIONAL MODULE / WIRING-FIRST</x:v>
+      </x:c>
+      <x:c r="H366" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I366" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J366" s="9" t="str">
+        <x:v>2019-2025 Q8 TSB 2059363/6</x:v>
+      </x:c>
+      <x:c r="K366" s="9" t="str">
+        <x:v>manufacturer suspension service</x:v>
+      </x:c>
+      <x:c r="L366" s="9" t="str"/>
+      <x:c r="M366" s="9" t="str">
+        <x:v>Bulletin has explicit occurrence/status branches.</x:v>
+      </x:c>
+      <x:c r="N366" s="41" t="str">
+        <x:v>No strut, spring, compressor or conversion link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="367" ht="607.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A367" s="40" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="B367" s="9" t="str">
+        <x:v>audi-q8-carbon-buildup-2019</x:v>
+      </x:c>
+      <x:c r="C367" s="9" t="str">
+        <x:v>2019-2023 | Audi | Q8</x:v>
+      </x:c>
+      <x:c r="D367" s="9" t="str">
+        <x:v>Severe Carbon Buildup on Intake Valves (3.0T)</x:v>
+      </x:c>
+      <x:c r="E367" s="9" t="str">
+        <x:v>WALNUT BLASTING: Remove intake manifold and blast walnut shells through intake ports ($900-$1,500). Requires specialized equipment. Repeat every 60,000 miles as PREVENTIVE maintenance. PREVENTION: Install catch can ($400-$600) to filter PCV vapors—extends interval to 100k+ miles. Add Liqui Moly Intake Valve Cleaner to every oil change. Change oil every 5,000 miles.</x:v>
+      </x:c>
+      <x:c r="F367" s="9" t="str">
+        <x:v>Confirm 3.0T deposits after ignition/fuel/air/compression diagnosis and intake inspection; engine-specific cleaning</x:v>
+      </x:c>
+      <x:c r="G367" s="9" t="str">
+        <x:v>CONFIRMED-DEPOSIT SERVICE</x:v>
+      </x:c>
+      <x:c r="H367" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I367" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J367" s="9" t="str">
+        <x:v>2019-2023 Q8 3.0T intake diagnosis/cleaning</x:v>
+      </x:c>
+      <x:c r="K367" s="9" t="str">
+        <x:v>specialist intake service</x:v>
+      </x:c>
+      <x:c r="L367" s="9" t="str"/>
+      <x:c r="M367" s="9" t="str">
+        <x:v>Mileage/symptoms do not prove deposits.</x:v>
+      </x:c>
+      <x:c r="N367" s="41" t="str">
+        <x:v>No universal interval, catch can, cleaner or oil schedule.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="368" ht="554.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A368" s="40" t="n">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="B368" s="9" t="str">
+        <x:v>audi-q8-e-tron-brake-pedal-to-booster-pushrod-screw-joint-detachment</x:v>
+      </x:c>
+      <x:c r="C368" s="9" t="str">
+        <x:v>2023-2024 | Audi | Q8 e-tron</x:v>
+      </x:c>
+      <x:c r="D368" s="9" t="str">
+        <x:v>2023-2024 Audi Q8 e-tron Brake-Pedal Recall 46P7 / NHTSA 26V240</x:v>
+      </x:c>
+      <x:c r="E368" s="9" t="str">
+        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. Dealers inspect and tighten the brake-booster pushrod screw joint as necessary at no charge. If the brake pedal makes an unusual noise, fails to return or feels abnormal, do not continue driving; contact Audi for recovery and follow the owner’s manual emergency-braking instructions.</x:v>
+      </x:c>
+      <x:c r="F368" s="9" t="str">
+        <x:v>VIN/46P7/26V240 check; dealer pushrod screw inspection/torque; recovery for abnormal pedal</x:v>
+      </x:c>
+      <x:c r="G368" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H368" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I368" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J368" s="9" t="str">
+        <x:v>2023-2024 Q8 e-tron 46P7</x:v>
+      </x:c>
+      <x:c r="K368" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L368" s="9" t="str"/>
+      <x:c r="M368" s="9" t="str">
+        <x:v>Campaign controls inspection/remedy.</x:v>
+      </x:c>
+      <x:c r="N368" s="41" t="str">
+        <x:v>No brake-pedal/booster product link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="369" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A369" s="40" t="str"/>
+      <x:c r="B369" s="9" t="str"/>
+      <x:c r="C369" s="9" t="str"/>
+      <x:c r="D369" s="9" t="str"/>
+      <x:c r="E369" s="9" t="str"/>
+      <x:c r="F369" s="9" t="str"/>
+      <x:c r="G369" s="9" t="str"/>
+      <x:c r="H369" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I369" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J369" s="9" t="str">
+        <x:v>26V240 VIN history</x:v>
+      </x:c>
+      <x:c r="K369" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L369" s="9" t="str"/>
+      <x:c r="M369" s="9" t="str"/>
+      <x:c r="N369" s="41" t="str"/>
+    </x:row>
+    <x:row r="370" ht="594" hidden="0" customHeight="1">
+      <x:c r="A370" s="40" t="n">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="B370" s="9" t="str">
+        <x:v>audi-q8-e-tron-dc-fast-charging-handshake-timeout-failure-to-initiate-sessi</x:v>
+      </x:c>
+      <x:c r="C370" s="9" t="str">
+        <x:v>2023-2024 | Audi | Q8 e-tron</x:v>
+      </x:c>
+      <x:c r="D370" s="9" t="str">
+        <x:v>2023-2024 Audi Q8 e-tron Plug &amp; Charge TSB 2071345/1</x:v>
+      </x:c>
+      <x:c r="E370" s="9" t="str">
+        <x:v>Confirm that the failure repeats at the same station, AC charging works and U15AF00 symptom 2097297 is present. Temporarily disable Plug &amp; Charge in the MMI or use another compatible charging station. Do not replace vehicle charging hardware solely from this symptom; follow current Audi guidance if the failure also occurs with Plug &amp; Charge disabled or at multiple stations.</x:v>
+      </x:c>
+      <x:c r="F370" s="9" t="str">
+        <x:v>Confirm same-station repetition, AC works and exact U15AF00 symptom; disable Plug &amp; Charge/use other station; guided diagnosis if broader</x:v>
+      </x:c>
+      <x:c r="G370" s="9" t="str">
+        <x:v>STATION/SOFTWARE CONDITION / NO HARDWARE LINK</x:v>
+      </x:c>
+      <x:c r="H370" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I370" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J370" s="9" t="str">
+        <x:v>2023-2024 Q8 e-tron TSB 2071345/1</x:v>
+      </x:c>
+      <x:c r="K370" s="9" t="str">
+        <x:v>manufacturer EV service</x:v>
+      </x:c>
+      <x:c r="L370" s="9" t="str"/>
+      <x:c r="M370" s="9" t="str">
+        <x:v>Defined Plug &amp; Charge condition does not prove vehicle hardware failure.</x:v>
+      </x:c>
+      <x:c r="N370" s="41" t="str">
+        <x:v>No charger/inlet/module link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="371" ht="488.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A371" s="40" t="n">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="B371" s="9" t="str">
+        <x:v>audi-q8-e-tron-front-passenger-occupant-detection-system-deactivates-airbag</x:v>
+      </x:c>
+      <x:c r="C371" s="9" t="str">
+        <x:v>2024-2024 | Audi | Q8 e-tron</x:v>
+      </x:c>
+      <x:c r="D371" s="9" t="str">
+        <x:v>2024 Audi Q8 e-tron Passenger-Airbag Recall 69GU / NHTSA 24V251</x:v>
+      </x:c>
+      <x:c r="E371" s="9" t="str">
+        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. The free remedy replaces the passenger-seat occupant-detection control module. If the passenger-airbag warning or AIRBAG OFF indicator behaves unexpectedly, avoid using that seat until Audi inspects it. Do not buy an ODS module from this summary.</x:v>
+      </x:c>
+      <x:c r="F371" s="9" t="str">
+        <x:v>VIN/69GU/24V251 check; dealer passenger ODS module; avoid seat if indicators abnormal</x:v>
+      </x:c>
+      <x:c r="G371" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H371" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I371" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J371" s="9" t="str">
+        <x:v>2024 Q8 e-tron 69GU</x:v>
+      </x:c>
+      <x:c r="K371" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L371" s="9" t="str"/>
+      <x:c r="M371" s="9" t="str">
+        <x:v>Module replacement is campaign-controlled.</x:v>
+      </x:c>
+      <x:c r="N371" s="41" t="str">
+        <x:v>No retail ODS module.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="372" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A372" s="40" t="str"/>
+      <x:c r="B372" s="9" t="str"/>
+      <x:c r="C372" s="9" t="str"/>
+      <x:c r="D372" s="9" t="str"/>
+      <x:c r="E372" s="9" t="str"/>
+      <x:c r="F372" s="9" t="str"/>
+      <x:c r="G372" s="9" t="str"/>
+      <x:c r="H372" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I372" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J372" s="9" t="str">
+        <x:v>24V251 VIN history</x:v>
+      </x:c>
+      <x:c r="K372" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L372" s="9" t="str"/>
+      <x:c r="M372" s="9" t="str"/>
+      <x:c r="N372" s="41" t="str"/>
+    </x:row>
+    <x:row r="373" ht="409.20001220703125" hidden="0" customHeight="1">
+      <x:c r="A373" s="40" t="n">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="B373" s="9" t="str">
+        <x:v>audi-q8-e-tron-over-torqued-brake-pressure-line-failure-fluid-leak</x:v>
+      </x:c>
+      <x:c r="C373" s="9" t="str">
+        <x:v>2024-2024 | Audi | Q8 e-tron</x:v>
+      </x:c>
+      <x:c r="D373" s="9" t="str">
+        <x:v>2024 Audi Q8 e-tron Brake-Line Recall 47DE / NHTSA 24V428</x:v>
+      </x:c>
+      <x:c r="E373" s="9" t="str">
+        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. Dealers inspect and replace the brake-pressure line when necessary at no charge. If the brake warning appears, pedal travel increases or fluid is visible, stop driving and arrange recovery.</x:v>
+      </x:c>
+      <x:c r="F373" s="9" t="str">
+        <x:v>VIN/47DE/24V428 check; dealer line inspection/conditional replacement; recovery for warning/leak/pedal travel</x:v>
+      </x:c>
+      <x:c r="G373" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H373" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I373" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J373" s="9" t="str">
+        <x:v>2024 Q8 e-tron 47DE</x:v>
+      </x:c>
+      <x:c r="K373" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L373" s="9" t="str"/>
+      <x:c r="M373" s="9" t="str">
+        <x:v>Recall determines affected line/remedy.</x:v>
+      </x:c>
+      <x:c r="N373" s="41" t="str">
+        <x:v>No generic brake line.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="374" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A374" s="40" t="str"/>
+      <x:c r="B374" s="9" t="str"/>
+      <x:c r="C374" s="9" t="str"/>
+      <x:c r="D374" s="9" t="str"/>
+      <x:c r="E374" s="9" t="str"/>
+      <x:c r="F374" s="9" t="str"/>
+      <x:c r="G374" s="9" t="str"/>
+      <x:c r="H374" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I374" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J374" s="9" t="str">
+        <x:v>24V428 VIN history</x:v>
+      </x:c>
+      <x:c r="K374" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L374" s="9" t="str"/>
+      <x:c r="M374" s="9" t="str"/>
+      <x:c r="N374" s="41" t="str"/>
+    </x:row>
+    <x:row r="375" ht="699.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A375" s="40" t="n">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B375" s="9" t="str">
+        <x:v>audi-q8-e-tron-panoramic-glass-roof-water-leak-into-cabin</x:v>
+      </x:c>
+      <x:c r="C375" s="9" t="str">
+        <x:v>2023-2024 | Audi | Q8 e-tron | Q8 e-tron (panoramic roof equipped), Q8 Sportback e-tron</x:v>
+      </x:c>
+      <x:c r="D375" s="9" t="str">
+        <x:v>Panoramic Glass Roof Water Leak into Cabin (TSB MC-10182485-0001)</x:v>
+      </x:c>
+      <x:c r="E375" s="9" t="str">
+        <x:v>Have the dealer diagnose per the panoramic roof TSB. Repair depends on the root cause: clear or re-route clogged/pinched drain tubes, correct a pinched-shut rear drain, or replace/reseal the cracked plastic water channel. Dry out and inspect saturated carpet/underlay to prevent mold and electrical corrosion. Audi performs the repair reactively (only after water ingress is confirmed); some owners report the factory fix failing and needing a second visit.</x:v>
+      </x:c>
+      <x:c r="F375" s="9" t="str">
+        <x:v>TSB root-cause test; clear/reroute pinched drains or replace/reseal cracked channel; dry carpet/electronics</x:v>
+      </x:c>
+      <x:c r="G375" s="9" t="str">
+        <x:v>LEAK-SOURCE BODY SERVICE</x:v>
+      </x:c>
+      <x:c r="H375" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I375" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J375" s="9" t="str">
+        <x:v>2023-2024 Q8 e-tron panoramic-roof TSB diagnosis</x:v>
+      </x:c>
+      <x:c r="K375" s="9" t="str">
+        <x:v>manufacturer body service</x:v>
+      </x:c>
+      <x:c r="L375" s="9" t="str"/>
+      <x:c r="M375" s="9" t="str">
+        <x:v>Drain and cracked-channel branches differ.</x:v>
+      </x:c>
+      <x:c r="N375" s="41" t="str">
+        <x:v>Do not generalize owner reports or link sealant/drain parts before diagnosis.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="376" ht="673.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A376" s="40" t="n">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="B376" s="9" t="str">
+        <x:v>audi-q8-e-tron-premature-brake-pad-rotor-wear-brake-vibration-pulsation</x:v>
+      </x:c>
+      <x:c r="C376" s="9" t="str">
+        <x:v>2023-2024 | Audi | Q8 e-tron | Q8 e-tron, Q8 Sportback e-tron, SQ8 e-tron</x:v>
+      </x:c>
+      <x:c r="D376" s="9" t="str">
+        <x:v>Premature Brake Pad/Rotor Wear and Brake Vibration/Pulsation</x:v>
+      </x:c>
+      <x:c r="E376" s="9" t="str">
+        <x:v>Have a dealer or independent measure rotor runout/thickness variation and machine or replace rotors with correct torque and bedding-in. Verify pad hardware and caliper slides. Using a stronger regenerative-braking setting reduces friction-brake duty and corrosion. If vibration returns shortly after a full brake job, escalate for a deeper inspection of hubs/wheel bearings and calibration.</x:v>
+      </x:c>
+      <x:c r="F376" s="9" t="str">
+        <x:v>Measure pad/rotor thickness/runout and hub/bearing/caliper causes; exact PR-code friction parts if failed; correct torque/bedding</x:v>
+      </x:c>
+      <x:c r="G376" s="9" t="str">
+        <x:v>BRAKE MEASUREMENT / PR-CODE GATE</x:v>
+      </x:c>
+      <x:c r="H376" s="9" t="str">
+        <x:v>Audi Q8 e-tron brake catalog</x:v>
+      </x:c>
+      <x:c r="I376" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/Q8-e-tron/Brakes/</x:v>
+      </x:c>
+      <x:c r="J376" s="9" t="str">
+        <x:v>2023-2024 exact VIN/brake PR code/axle after measurements</x:v>
+      </x:c>
+      <x:c r="K376" s="9" t="str">
+        <x:v>vehicle-specific brake catalog</x:v>
+      </x:c>
+      <x:c r="L376" s="9" t="str"/>
+      <x:c r="M376" s="9" t="str">
+        <x:v>Wear, corrosion and hub runout require different repairs.</x:v>
+      </x:c>
+      <x:c r="N376" s="41" t="str">
+        <x:v>Do not claim regen setting prevents corrosion or machine rotors without limits.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="377" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A377" s="40" t="str"/>
+      <x:c r="B377" s="9" t="str"/>
+      <x:c r="C377" s="9" t="str"/>
+      <x:c r="D377" s="9" t="str"/>
+      <x:c r="E377" s="9" t="str"/>
+      <x:c r="F377" s="9" t="str"/>
+      <x:c r="G377" s="9" t="str"/>
+      <x:c r="H377" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I377" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J377" s="9" t="str">
+        <x:v>runout/hub/caliper diagnosis</x:v>
+      </x:c>
+      <x:c r="K377" s="9" t="str">
+        <x:v>specialist brake service</x:v>
+      </x:c>
+      <x:c r="L377" s="9" t="str"/>
+      <x:c r="M377" s="9" t="str"/>
+      <x:c r="N377" s="41" t="str"/>
+    </x:row>
+    <x:row r="378" ht="303.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A378" s="40" t="n">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="B378" s="9" t="str">
+        <x:v>audi-q8-e-tron-rearview-camera-image-fails-is-delayed-when-shifting-to-reve</x:v>
+      </x:c>
+      <x:c r="C378" s="9" t="str">
+        <x:v>2023-2024 | Audi | Q8 e-tron</x:v>
+      </x:c>
+      <x:c r="D378" s="9" t="str">
+        <x:v>2023-2024 Audi Q8 e-tron Camera Recall 90TV / NHTSA 25V900</x:v>
+      </x:c>
+      <x:c r="E378" s="9" t="str">
+        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. Dealers update the software at no charge. Until completed, use mirrors and direct observation with extra care while reversing.</x:v>
+      </x:c>
+      <x:c r="F378" s="9" t="str">
+        <x:v>VIN/90TV/25V900 check; dealer software; direct observation until complete</x:v>
+      </x:c>
+      <x:c r="G378" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H378" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I378" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J378" s="9" t="str">
+        <x:v>2023-2024 Q8 e-tron 90TV</x:v>
+      </x:c>
+      <x:c r="K378" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L378" s="9" t="str"/>
+      <x:c r="M378" s="9" t="str">
+        <x:v>Software is free remedy.</x:v>
+      </x:c>
+      <x:c r="N378" s="41" t="str">
+        <x:v>No camera/module link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="379" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A379" s="40" t="str"/>
+      <x:c r="B379" s="9" t="str"/>
+      <x:c r="C379" s="9" t="str"/>
+      <x:c r="D379" s="9" t="str"/>
+      <x:c r="E379" s="9" t="str"/>
+      <x:c r="F379" s="9" t="str"/>
+      <x:c r="G379" s="9" t="str"/>
+      <x:c r="H379" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I379" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J379" s="9" t="str">
+        <x:v>25V900 VIN history</x:v>
+      </x:c>
+      <x:c r="K379" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L379" s="9" t="str"/>
+      <x:c r="M379" s="9" t="str"/>
+      <x:c r="N379" s="41" t="str"/>
+    </x:row>
+    <x:row r="380" ht="699.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A380" s="40" t="n">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="B380" s="9" t="str">
+        <x:v>audi-q8-e-tron-severe-cold-weather-range-loss-reduced-dc-charge-speed</x:v>
+      </x:c>
+      <x:c r="C380" s="9" t="str">
+        <x:v>2023-2024 | Audi | Q8 e-tron | Q8 e-tron, Q8 Sportback e-tron, SQ8 e-tron</x:v>
+      </x:c>
+      <x:c r="D380" s="9" t="str">
+        <x:v>Severe Cold-Weather Range Loss and Reduced DC Charge Speed (Cold Battery)</x:v>
+      </x:c>
+      <x:c r="E380" s="9" t="str">
+        <x:v>Use route-based battery preconditioning: enter the DC fast charger as a navigation destination so the car warms the pack en route, restoring charge speed. Precondition the cabin while still plugged in at home, use seat/steering heaters over cabin heat, and rely on Level 2 home charging (40-60A) to absorb seasonal losses overnight. No repair is needed unless range/charge limits persist in mild weather, which warrants a dealer battery-health check.</x:v>
+      </x:c>
+      <x:c r="F380" s="9" t="str">
+        <x:v>Owner-manual route-based battery preconditioning and plugged-in cabin preconditioning; mild-weather persistence triggers dealer battery/thermal diagnosis</x:v>
+      </x:c>
+      <x:c r="G380" s="9" t="str">
+        <x:v>OPERATING GUIDANCE / CONDITIONAL EV SERVICE</x:v>
+      </x:c>
+      <x:c r="H380" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I380" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J380" s="9" t="str">
+        <x:v>2023-2024 Q8 e-tron persistent mild-weather range/charge diagnosis</x:v>
+      </x:c>
+      <x:c r="K380" s="9" t="str">
+        <x:v>manufacturer EV service</x:v>
+      </x:c>
+      <x:c r="L380" s="9" t="str"/>
+      <x:c r="M380" s="9" t="str">
+        <x:v>Normal cold-battery behavior is not a failed part.</x:v>
+      </x:c>
+      <x:c r="N380" s="41" t="str">
+        <x:v>Do not prescribe charger amperage or hardware from this card.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="381" ht="660" hidden="0" customHeight="1">
+      <x:c r="A381" s="40" t="n">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="B381" s="9" t="str">
+        <x:v>audi-q8-ea839-3-0t-water-pump-internal-leak-coolant-loss</x:v>
+      </x:c>
+      <x:c r="C381" s="9" t="str">
+        <x:v>2019-2024 | Audi | Q8 | V6 TFSI</x:v>
+      </x:c>
+      <x:c r="D381" s="9" t="str">
+        <x:v>2019-2024 Q8 V6 Coolant-Pump Leak Diagnosis - TSB 2070349/4</x:v>
+      </x:c>
+      <x:c r="E381" s="9" t="str">
+        <x:v>Have the suspected area cleaned and dried, fill the cooling system correctly, inspect at idle and up to about 2,500 rpm, and pressure-test it per Audi repair information. If no leak returns, continue to observe without replacing parts. Replace only the component proven to leak and inspect the vacuum path and N649 when P0299 is present. Do not order a pump from this card without confirmation.</x:v>
+      </x:c>
+      <x:c r="F381" s="9" t="str">
+        <x:v>Clean/dry/fill, idle/2500-rpm inspect and pressure-test; exact proven leak component; P0299 vacuum/N649 branch</x:v>
+      </x:c>
+      <x:c r="G381" s="9" t="str">
+        <x:v>TSB LEAK-CONFIRMATION GATE</x:v>
+      </x:c>
+      <x:c r="H381" s="9" t="str">
+        <x:v>Audi Q8 water-pump catalog</x:v>
+      </x:c>
+      <x:c r="I381" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/Q8/Water-Pump/</x:v>
+      </x:c>
+      <x:c r="J381" s="9" t="str">
+        <x:v>2019-2024 Q8 V6 TFSI after confirmed pump source/VIN</x:v>
+      </x:c>
+      <x:c r="K381" s="9" t="str">
+        <x:v>conditional pump catalog</x:v>
+      </x:c>
+      <x:c r="L381" s="9" t="str"/>
+      <x:c r="M381" s="9" t="str">
+        <x:v>No returned leak means observation; P0299 may be vacuum control.</x:v>
+      </x:c>
+      <x:c r="N381" s="41" t="str">
+        <x:v>No pump link without confirmation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="382" ht="66" hidden="0" customHeight="1">
+      <x:c r="A382" s="40" t="str"/>
+      <x:c r="B382" s="9" t="str"/>
+      <x:c r="C382" s="9" t="str"/>
+      <x:c r="D382" s="9" t="str"/>
+      <x:c r="E382" s="9" t="str"/>
+      <x:c r="F382" s="9" t="str"/>
+      <x:c r="G382" s="9" t="str"/>
+      <x:c r="H382" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I382" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J382" s="9" t="str">
+        <x:v>TSB 2070349/4</x:v>
+      </x:c>
+      <x:c r="K382" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L382" s="9" t="str"/>
+      <x:c r="M382" s="9" t="str"/>
+      <x:c r="N382" s="41" t="str"/>
+    </x:row>
+    <x:row r="383" ht="382.79998779296875" hidden="0" customHeight="1">
+      <x:c r="A383" s="40" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B383" s="9" t="str">
+        <x:v>audi-q8-etron-12v-battery-drain-2023</x:v>
+      </x:c>
+      <x:c r="C383" s="9" t="str">
+        <x:v>2023-2025 | Audi | Q8 e-tron</x:v>
+      </x:c>
+      <x:c r="D383" s="9" t="str">
+        <x:v>12V Auxiliary Battery Excessive Drain</x:v>
+      </x:c>
+      <x:c r="E383" s="9" t="str">
+        <x:v>Update vehicle software to latest version via dealer. If drain persists, have dealer perform parasitic draw test to identify module staying awake. 12V battery replacement with AGM type may be needed if battery was deeply discharged.</x:v>
+      </x:c>
+      <x:c r="F383" s="9" t="str">
+        <x:v>Software/version check; sleep-current/parasitic-draw isolation; exact AGM battery only if failed; registration/coding</x:v>
+      </x:c>
+      <x:c r="G383" s="9" t="str">
+        <x:v>PARASITIC-DRAW / BATTERY-SPEC GATE</x:v>
+      </x:c>
+      <x:c r="H383" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I383" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J383" s="9" t="str">
+        <x:v>2023-2025 Q8 e-tron software/draw/battery diagnosis</x:v>
+      </x:c>
+      <x:c r="K383" s="9" t="str">
+        <x:v>manufacturer EV electrical service</x:v>
+      </x:c>
+      <x:c r="L383" s="9" t="str"/>
+      <x:c r="M383" s="9" t="str">
+        <x:v>Battery may be victim of module wake-up.</x:v>
+      </x:c>
+      <x:c r="N383" s="41" t="str">
+        <x:v>No AGM product until group/capacity/VIN confirmed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A384" s="40" t="str"/>
+      <x:c r="B384" s="9" t="str"/>
+      <x:c r="C384" s="9" t="str"/>
+      <x:c r="D384" s="9" t="str"/>
+      <x:c r="E384" s="9" t="str"/>
+      <x:c r="F384" s="9" t="str"/>
+      <x:c r="G384" s="9" t="str"/>
+      <x:c r="H384" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I384" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J384" s="9" t="str">
+        <x:v>exact AGM and registration after failure test</x:v>
+      </x:c>
+      <x:c r="K384" s="9" t="str">
+        <x:v>specialist electrical service</x:v>
+      </x:c>
+      <x:c r="L384" s="9" t="str"/>
+      <x:c r="M384" s="9" t="str"/>
+      <x:c r="N384" s="41" t="str"/>
+    </x:row>
+    <x:row r="385" ht="501.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A385" s="40" t="n">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="B385" s="9" t="str">
+        <x:v>audi-q8-etron-12v-battery-drain-2024</x:v>
+      </x:c>
+      <x:c r="C385" s="9" t="str">
+        <x:v>2024-2026 | Audi | Q8 e-tron | Premium, Premium Plus, Prestige, Sportback Premium, Sportback Premium Plus, Sportback Prestige | Electric</x:v>
+      </x:c>
+      <x:c r="D385" s="9" t="str">
+        <x:v>12V Auxiliary Battery Parasitic Drain</x:v>
+      </x:c>
+      <x:c r="E385" s="9" t="str">
+        <x:v>Update the vehicle software to the latest version which includes revised module sleep timing. If the 12V battery has been deeply discharged multiple times, it may need replacement as lead-acid batteries are damaged by deep discharge cycles. Connect a 12V trickle charger if the vehicle will sit for more than a week.</x:v>
+      </x:c>
+      <x:c r="F385" s="9" t="str">
+        <x:v>Software/sleep-timing check; parasitic draw and battery SOH; exact battery if failed; storage charging only per manual-approved equipment</x:v>
+      </x:c>
+      <x:c r="G385" s="9" t="str">
+        <x:v>PARASITIC-DRAW / BATTERY-SPEC GATE</x:v>
+      </x:c>
+      <x:c r="H385" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I385" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J385" s="9" t="str">
+        <x:v>2024-2026 Q8 e-tron software/draw/battery diagnosis</x:v>
+      </x:c>
+      <x:c r="K385" s="9" t="str">
+        <x:v>manufacturer EV electrical service</x:v>
+      </x:c>
+      <x:c r="L385" s="9" t="str"/>
+      <x:c r="M385" s="9" t="str">
+        <x:v>Deep discharge does not identify module or exact replacement battery.</x:v>
+      </x:c>
+      <x:c r="N385" s="41" t="str">
+        <x:v>No universal trickle charger or battery link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="386" ht="462" hidden="0" customHeight="1">
+      <x:c r="A386" s="40" t="n">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="B386" s="9" t="str">
+        <x:v>audi-q8-etron-charge-port-actuator-2024</x:v>
+      </x:c>
+      <x:c r="C386" s="9" t="str">
+        <x:v>2024-2026 | Audi | Q8 e-tron | Premium, Premium Plus, Prestige, Sportback Premium, Sportback Premium Plus, Sportback Prestige | Electric</x:v>
+      </x:c>
+      <x:c r="D386" s="9" t="str">
+        <x:v>Charge Port Door Actuator and Locking Mechanism Failure</x:v>
+      </x:c>
+      <x:c r="E386" s="9" t="str">
+        <x:v>Replace the charge port door actuator and/or latch mechanism. In an emergency, there is a manual cable release in the cargo area to free a stuck charging cable. The actuator replacement is a straightforward repair that can be done by an independent shop if comfortable with the charge port housing.</x:v>
+      </x:c>
+      <x:c r="F386" s="9" t="str">
+        <x:v>Manual release per manual; debris/ice, latch/actuator/wiring/software diagnosis; exact door/latch only after proof</x:v>
+      </x:c>
+      <x:c r="G386" s="9" t="str">
+        <x:v>EV CHARGE-DOOR COMPONENT GATE</x:v>
+      </x:c>
+      <x:c r="H386" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I386" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J386" s="9" t="str">
+        <x:v>2024-2026 Q8 e-tron charge-door VIN/component diagnosis</x:v>
+      </x:c>
+      <x:c r="K386" s="9" t="str">
+        <x:v>authorized EV service</x:v>
+      </x:c>
+      <x:c r="L386" s="9" t="str"/>
+      <x:c r="M386" s="9" t="str">
+        <x:v>Actuator, latch, obstruction and controls differ.</x:v>
+      </x:c>
+      <x:c r="N386" s="41" t="str">
+        <x:v>Do not describe independent repair as straightforward near charge hardware.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="387" ht="316.79998779296875" hidden="0" customHeight="1">
+      <x:c r="A387" s="40" t="n">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="B387" s="9" t="str">
+        <x:v>audi-q8-etron-charge-port-lid-2023</x:v>
+      </x:c>
+      <x:c r="C387" s="9" t="str">
+        <x:v>2023-2025 | Audi | Q8 e-tron</x:v>
+      </x:c>
+      <x:c r="D387" s="9" t="str">
+        <x:v>Charge Port Door Actuator Failure</x:v>
+      </x:c>
+      <x:c r="E387" s="9" t="str">
+        <x:v>Replace charge port door actuator assembly. Check for debris or ice in the mechanism. Software update may improve actuator control logic. Manual release is accessible from inside the cargo area.</x:v>
+      </x:c>
+      <x:c r="F387" s="9" t="str">
+        <x:v>Manual release per manual; inspect ice/debris; actuator/latch/wiring/software diagnosis; exact assembly only if failed</x:v>
+      </x:c>
+      <x:c r="G387" s="9" t="str">
+        <x:v>EV CHARGE-DOOR COMPONENT GATE</x:v>
+      </x:c>
+      <x:c r="H387" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I387" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J387" s="9" t="str">
+        <x:v>2023-2025 Q8 e-tron charge-door diagnosis</x:v>
+      </x:c>
+      <x:c r="K387" s="9" t="str">
+        <x:v>authorized EV service</x:v>
+      </x:c>
+      <x:c r="L387" s="9" t="str"/>
+      <x:c r="M387" s="9" t="str">
+        <x:v>Symptoms do not prove actuator assembly.</x:v>
+      </x:c>
+      <x:c r="N387" s="41" t="str">
+        <x:v>No actuator link before VIN/DTC/component proof.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="388" ht="646.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A388" s="40" t="n">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="B388" s="9" t="str">
+        <x:v>audi-q8-etron-hvac-compressor-2024</x:v>
+      </x:c>
+      <x:c r="C388" s="9" t="str">
+        <x:v>2024-2024 | Audi | Q8 e-tron</x:v>
+      </x:c>
+      <x:c r="D388" s="9" t="str">
+        <x:v>2024 Audi Q8 e-tron A/C Compressor-Area Noise TSB 2063467/6</x:v>
+      </x:c>
+      <x:c r="E388" s="9" t="str">
+        <x:v>Reproduce the exact noise with the A/C compressor active and confirm that it stops when A/C is switched off. Inspect the bulletin’s refrigerant-line contact points and hood-release cable clip and perform only the branch that matches the confirmed contact. Diagnose non-reproducible noise or loss of heating/cooling separately; do not buy a battery, maintainer or portable EVSE from this card.</x:v>
+      </x:c>
+      <x:c r="F388" s="9" t="str">
+        <x:v>Reproduce A/C-on noise; confirm off when disabled; inspect refrigerant-line contact and hood-release clip; matching contact branch only</x:v>
+      </x:c>
+      <x:c r="G388" s="9" t="str">
+        <x:v>TSB CONTACT-NOISE SERVICE</x:v>
+      </x:c>
+      <x:c r="H388" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I388" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J388" s="9" t="str">
+        <x:v>2024 Q8 e-tron TSB 2063467/6</x:v>
+      </x:c>
+      <x:c r="K388" s="9" t="str">
+        <x:v>manufacturer EV HVAC service</x:v>
+      </x:c>
+      <x:c r="L388" s="9" t="str"/>
+      <x:c r="M388" s="9" t="str">
+        <x:v>Bulletin does not prove compressor failure.</x:v>
+      </x:c>
+      <x:c r="N388" s="41" t="str">
+        <x:v>No compressor, battery, maintainer or EVSE link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="389" ht="435.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A389" s="40" t="n">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="B389" s="9" t="str">
+        <x:v>audi-q8-front-brake-rotor-corrosion-premature-pad-rotor-wear</x:v>
+      </x:c>
+      <x:c r="C389" s="9" t="str">
+        <x:v>2019-2024 | Audi | Q8</x:v>
+      </x:c>
+      <x:c r="D389" s="9" t="str">
+        <x:v>Front Brake Rotor Corrosion and Premature Pad/Rotor Wear</x:v>
+      </x:c>
+      <x:c r="E389" s="9" t="str">
+        <x:v>For light surface rust, normal braking usually clears it; for noise, refinish or replace rotors and fit OEM-spec pads with proper bedding-in. Apply high-temp anti-seize/lubricant on contact points and ensure caliper slides move freely. Replace warped or deeply corroded rotors in axle sets.</x:v>
+      </x:c>
+      <x:c r="F389" s="9" t="str">
+        <x:v>Classify surface rust versus deep corrosion/warp; measure thickness/runout; exact PR-code axle pads/rotors if limits require; slides/hardware/bedding</x:v>
+      </x:c>
+      <x:c r="G389" s="9" t="str">
+        <x:v>BRAKE MEASUREMENT / PR-CODE GATE</x:v>
+      </x:c>
+      <x:c r="H389" s="9" t="str">
+        <x:v>Audi Q8 brake catalog</x:v>
+      </x:c>
+      <x:c r="I389" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/Q8/Brakes/</x:v>
+      </x:c>
+      <x:c r="J389" s="9" t="str">
+        <x:v>2019-2024 exact VIN/brake PR code/axle</x:v>
+      </x:c>
+      <x:c r="K389" s="9" t="str">
+        <x:v>vehicle-specific brake catalog</x:v>
+      </x:c>
+      <x:c r="L389" s="9" t="str"/>
+      <x:c r="M389" s="9" t="str">
+        <x:v>Light rust and failed friction parts are different conditions.</x:v>
+      </x:c>
+      <x:c r="N389" s="41" t="str">
+        <x:v>No anti-seize on unspecified friction/brake contact points; follow approved lubricant locations.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A390" s="40" t="str"/>
+      <x:c r="B390" s="9" t="str"/>
+      <x:c r="C390" s="9" t="str"/>
+      <x:c r="D390" s="9" t="str"/>
+      <x:c r="E390" s="9" t="str"/>
+      <x:c r="F390" s="9" t="str"/>
+      <x:c r="G390" s="9" t="str"/>
+      <x:c r="H390" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I390" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J390" s="9" t="str">
+        <x:v>runout/corrosion/caliper diagnosis</x:v>
+      </x:c>
+      <x:c r="K390" s="9" t="str">
+        <x:v>specialist brake service</x:v>
+      </x:c>
+      <x:c r="L390" s="9" t="str"/>
+      <x:c r="M390" s="9" t="str"/>
+      <x:c r="N390" s="41" t="str"/>
+    </x:row>
+    <x:row r="391" ht="422.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A391" s="40" t="n">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="B391" s="9" t="str">
+        <x:v>audi-q8-front-shock-absorber-fork-cracking</x:v>
+      </x:c>
+      <x:c r="C391" s="9" t="str">
+        <x:v>2019-2019 | Audi | Q8</x:v>
+      </x:c>
+      <x:c r="D391" s="9" t="str">
+        <x:v>2019 Q8 Front Shock-Absorber Fork Recall 40O4 (19V114) - Check VIN</x:v>
+      </x:c>
+      <x:c r="E391" s="9" t="str">
+        <x:v>Check the VIN for open recall 40O4 with Audi or NHTSA and contact an authorized Audi dealer. The dealer replaces the affected front shock-absorber fork free of charge. Do not buy a fork from this card or assume a generic suspension noise proves the recall condition.</x:v>
+      </x:c>
+      <x:c r="F391" s="9" t="str">
+        <x:v>VIN/40O4/19V114 check; free dealer affected fork replacement; separate generic suspension-noise diagnosis</x:v>
+      </x:c>
+      <x:c r="G391" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H391" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I391" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J391" s="9" t="str">
+        <x:v>2019 Q8 40O4</x:v>
+      </x:c>
+      <x:c r="K391" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L391" s="9" t="str"/>
+      <x:c r="M391" s="9" t="str">
+        <x:v>Recall condition/part is VIN-controlled.</x:v>
+      </x:c>
+      <x:c r="N391" s="41" t="str">
+        <x:v>No retail fork link or noise inference.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A392" s="40" t="str"/>
+      <x:c r="B392" s="9" t="str"/>
+      <x:c r="C392" s="9" t="str"/>
+      <x:c r="D392" s="9" t="str"/>
+      <x:c r="E392" s="9" t="str"/>
+      <x:c r="F392" s="9" t="str"/>
+      <x:c r="G392" s="9" t="str"/>
+      <x:c r="H392" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I392" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J392" s="9" t="str">
+        <x:v>19V114 VIN history</x:v>
+      </x:c>
+      <x:c r="K392" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L392" s="9" t="str"/>
+      <x:c r="M392" s="9" t="str"/>
+      <x:c r="N392" s="41" t="str"/>
+    </x:row>
+    <x:row r="393" ht="422.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A393" s="40" t="n">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="B393" s="9" t="str">
+        <x:v>audi-q8-fuel-pump-internal-failure-causing-engine-stall</x:v>
+      </x:c>
+      <x:c r="C393" s="9" t="str">
+        <x:v>2019-2021 | Audi | Q8 | V6</x:v>
+      </x:c>
+      <x:c r="D393" s="9" t="str">
+        <x:v>2019-2021 Q8 V6 Fuel-Delivery-Module Recall 20DR (22V516)</x:v>
+      </x:c>
+      <x:c r="E393" s="9" t="str">
+        <x:v>Check the VIN for open recall 20DR and contact an authorized Audi dealer. The recall remedy replaces the fuel-delivery module with the improved version. Do not purchase the old or improved module from this card or attempt an in-tank repair based only on the model year.</x:v>
+      </x:c>
+      <x:c r="F393" s="9" t="str">
+        <x:v>VIN/20DR/22V516 check; free improved fuel-delivery module; recovery for stall risk</x:v>
+      </x:c>
+      <x:c r="G393" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H393" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I393" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J393" s="9" t="str">
+        <x:v>2019-2021 Q8 V6 20DR</x:v>
+      </x:c>
+      <x:c r="K393" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L393" s="9" t="str"/>
+      <x:c r="M393" s="9" t="str">
+        <x:v>In-tank module replacement is recall work.</x:v>
+      </x:c>
+      <x:c r="N393" s="41" t="str">
+        <x:v>No old/improved retail module link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="394" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A394" s="40" t="str"/>
+      <x:c r="B394" s="9" t="str"/>
+      <x:c r="C394" s="9" t="str"/>
+      <x:c r="D394" s="9" t="str"/>
+      <x:c r="E394" s="9" t="str"/>
+      <x:c r="F394" s="9" t="str"/>
+      <x:c r="G394" s="9" t="str"/>
+      <x:c r="H394" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I394" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J394" s="9" t="str">
+        <x:v>22V516 VIN history</x:v>
+      </x:c>
+      <x:c r="K394" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L394" s="9" t="str"/>
+      <x:c r="M394" s="9" t="str"/>
+      <x:c r="N394" s="41" t="str"/>
+    </x:row>
+    <x:row r="395" ht="356.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A395" s="40" t="n">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="B395" s="9" t="str">
+        <x:v>audi-q8-mmi-electrical-2019</x:v>
+      </x:c>
+      <x:c r="C395" s="9" t="str">
+        <x:v>2019-2023 | Audi | Q8</x:v>
+      </x:c>
+      <x:c r="D395" s="9" t="str">
+        <x:v>MMI Infotainment and Electrical Issues</x:v>
+      </x:c>
+      <x:c r="E395" s="9" t="str">
+        <x:v>MMI hard reset (hold power + volume up 10 seconds). If persistent, dealer software update ($150-$300). For severe cases: MMI replacement ($2,000-$3,500). Most covered under 4-year/50k warranty.</x:v>
+      </x:c>
+      <x:c r="F395" s="9" t="str">
+        <x:v>Document exact MMI/electrical symptom, DTC and software; safe reset only per manual; VIN update or module branch after diagnosis</x:v>
+      </x:c>
+      <x:c r="G395" s="9" t="str">
+        <x:v>OVERBROAD SOFTWARE/ELECTRICAL SERVICE</x:v>
+      </x:c>
+      <x:c r="H395" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I395" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J395" s="9" t="str">
+        <x:v>2019-2023 Q8 MMI software/module diagnosis</x:v>
+      </x:c>
+      <x:c r="K395" s="9" t="str">
+        <x:v>manufacturer electronics service</x:v>
+      </x:c>
+      <x:c r="L395" s="9" t="str"/>
+      <x:c r="M395" s="9" t="str">
+        <x:v>Generic glitches do not prove MMI replacement.</x:v>
+      </x:c>
+      <x:c r="N395" s="41" t="str">
+        <x:v>No universal reset, price or warranty promise.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A396" s="40" t="str"/>
+      <x:c r="B396" s="9" t="str"/>
+      <x:c r="C396" s="9" t="str"/>
+      <x:c r="D396" s="9" t="str"/>
+      <x:c r="E396" s="9" t="str"/>
+      <x:c r="F396" s="9" t="str"/>
+      <x:c r="G396" s="9" t="str"/>
+      <x:c r="H396" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I396" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J396" s="9" t="str">
+        <x:v>system-specific electrical diagnosis</x:v>
+      </x:c>
+      <x:c r="K396" s="9" t="str">
+        <x:v>specialist service</x:v>
+      </x:c>
+      <x:c r="L396" s="9" t="str"/>
+      <x:c r="M396" s="9" t="str"/>
+      <x:c r="N396" s="41" t="str"/>
+    </x:row>
+    <x:row r="397" ht="488.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A397" s="40" t="n">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="B397" s="9" t="str">
+        <x:v>audi-q8-mmi-infotainment-2019</x:v>
+      </x:c>
+      <x:c r="C397" s="9" t="str">
+        <x:v>2019-2026 | Audi | Q8</x:v>
+      </x:c>
+      <x:c r="D397" s="9" t="str">
+        <x:v>2019-2026 Q8 Rearview-Camera Software Recall 90TV (25V900)</x:v>
+      </x:c>
+      <x:c r="E397" s="9" t="str">
+        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers install more robust driver-assistance software free of charge. Until repaired, use extra caution when reversing. A hard reset, scan tool, relay, multimeter or temporary image recovery is not completion of the recall.</x:v>
+      </x:c>
+      <x:c r="F397" s="9" t="str">
+        <x:v>VIN/90TV/25V900 check; free driver-assistance software; direct reverse observation</x:v>
+      </x:c>
+      <x:c r="G397" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H397" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I397" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J397" s="9" t="str">
+        <x:v>2019-2026 Q8 90TV</x:v>
+      </x:c>
+      <x:c r="K397" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L397" s="9" t="str"/>
+      <x:c r="M397" s="9" t="str">
+        <x:v>Reset/tool recovery does not complete recall.</x:v>
+      </x:c>
+      <x:c r="N397" s="41" t="str">
+        <x:v>No scanner, relay, meter or MMI part link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A398" s="40" t="str"/>
+      <x:c r="B398" s="9" t="str"/>
+      <x:c r="C398" s="9" t="str"/>
+      <x:c r="D398" s="9" t="str"/>
+      <x:c r="E398" s="9" t="str"/>
+      <x:c r="F398" s="9" t="str"/>
+      <x:c r="G398" s="9" t="str"/>
+      <x:c r="H398" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I398" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J398" s="9" t="str">
+        <x:v>25V900 VIN history</x:v>
+      </x:c>
+      <x:c r="K398" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L398" s="9" t="str"/>
+      <x:c r="M398" s="9" t="str"/>
+      <x:c r="N398" s="41" t="str"/>
+    </x:row>
+    <x:row r="399" ht="382.79998779296875" hidden="0" customHeight="1">
+      <x:c r="A399" s="40" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="B399" s="9" t="str">
+        <x:v>audi-q8-oil-separator-pcv-valve-failure-elevated-oil-consumption</x:v>
+      </x:c>
+      <x:c r="C399" s="9" t="str">
+        <x:v>2019-2023 | Audi | Q8 | 3.0L V6 TFSI (EA839)</x:v>
+      </x:c>
+      <x:c r="D399" s="9" t="str">
+        <x:v>Oil Separator / PCV Valve Failure and Elevated Oil Consumption (3.0T)</x:v>
+      </x:c>
+      <x:c r="E399" s="9" t="str">
+        <x:v>Replace the cracked oil separator / PCV valve assembly with the updated part, inspect the intake and spark plugs for oil fouling, and reseal the intake manifold. Monitor oil level between services; perform a consumption test if usage exceeds Audi's threshold.</x:v>
+      </x:c>
+      <x:c r="F399" s="9" t="str">
+        <x:v>Measure crankcase pressure/consumption and inspect leaks/intake/plugs; exact EA839 VIN oil separator only if failed; intake seals required by procedure</x:v>
+      </x:c>
+      <x:c r="G399" s="9" t="str">
+        <x:v>DIAGNOSIS / ENGINE-VIN PCV GATE</x:v>
+      </x:c>
+      <x:c r="H399" s="9" t="str">
+        <x:v>Audi Q8 PCV catalog</x:v>
+      </x:c>
+      <x:c r="I399" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/Q8/PCV/</x:v>
+      </x:c>
+      <x:c r="J399" s="9" t="str">
+        <x:v>2019-2023 Q8 3.0T EA839; exact VIN/current separator after diagnosis</x:v>
+      </x:c>
+      <x:c r="K399" s="9" t="str">
+        <x:v>conditional engine catalog</x:v>
+      </x:c>
+      <x:c r="L399" s="9" t="str"/>
+      <x:c r="M399" s="9" t="str">
+        <x:v>Consumption and oil fouling do not alone prove cracked separator.</x:v>
+      </x:c>
+      <x:c r="N399" s="41" t="str">
+        <x:v>Do not automatically reseal intake or replace plugs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="400" ht="66" hidden="0" customHeight="1">
+      <x:c r="A400" s="40" t="str"/>
+      <x:c r="B400" s="9" t="str"/>
+      <x:c r="C400" s="9" t="str"/>
+      <x:c r="D400" s="9" t="str"/>
+      <x:c r="E400" s="9" t="str"/>
+      <x:c r="F400" s="9" t="str"/>
+      <x:c r="G400" s="9" t="str"/>
+      <x:c r="H400" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I400" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J400" s="9" t="str">
+        <x:v>crankcase pressure/consumption diagnosis</x:v>
+      </x:c>
+      <x:c r="K400" s="9" t="str">
+        <x:v>specialist engine service</x:v>
+      </x:c>
+      <x:c r="L400" s="9" t="str"/>
+      <x:c r="M400" s="9" t="str"/>
+      <x:c r="N400" s="41" t="str"/>
+    </x:row>
+    <x:row r="401" ht="607.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A401" s="40" t="n">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="B401" s="9" t="str">
+        <x:v>audi-q8-panoramic-sunroof-water-leak-into-cabin</x:v>
+      </x:c>
+      <x:c r="C401" s="9" t="str">
+        <x:v>2019-2021 | Audi | Q8</x:v>
+      </x:c>
+      <x:c r="D401" s="9" t="str">
+        <x:v>2019-2021 Q8 Water Entry from Sunroof Area - TSB 2056944/10</x:v>
+      </x:c>
+      <x:c r="E401" s="9" t="str">
+        <x:v>Have all four bulletin branches inspected and water-flow tested. Clear a drain obstruction or replace a damaged hose or valve, replace a damaged opening seal, correct glass adjustment, and perform the specified wind-deflector and channel modifications when applicable. Replace the sunroof frame only when actual structural damage is found. Do not order a frame from this card.</x:v>
+      </x:c>
+      <x:c r="F401" s="9" t="str">
+        <x:v>Inspect/water-test four TSB branches; exact drain/hose/valve/seal/adjustment/deflector repair; frame only if structurally damaged</x:v>
+      </x:c>
+      <x:c r="G401" s="9" t="str">
+        <x:v>TSB LEAK-SOURCE SERVICE</x:v>
+      </x:c>
+      <x:c r="H401" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I401" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J401" s="9" t="str">
+        <x:v>2019-2021 Q8 TSB 2056944/10</x:v>
+      </x:c>
+      <x:c r="K401" s="9" t="str">
+        <x:v>manufacturer body service</x:v>
+      </x:c>
+      <x:c r="L401" s="9" t="str"/>
+      <x:c r="M401" s="9" t="str">
+        <x:v>Multiple branches require evidence.</x:v>
+      </x:c>
+      <x:c r="N401" s="41" t="str">
+        <x:v>No sunroof-frame link from water entry alone.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402" ht="752.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A402" s="40" t="n">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B402" s="9" t="str">
+        <x:v>audi-r8-5-2-v10-excessive-oil-consumption</x:v>
+      </x:c>
+      <x:c r="C402" s="9" t="str">
+        <x:v>2009-2023 | Audi | R8 | 5.2L V10 FSI</x:v>
+      </x:c>
+      <x:c r="D402" s="9" t="str">
+        <x:v>5.2 V10 Excessive Oil Consumption</x:v>
+      </x:c>
+      <x:c r="E402" s="9" t="str">
+        <x:v>Establish a documented consumption baseline (measured quarts over measured miles) and inspect the plugs/exhaust for oil fouling. Use a manufacturer-approved oil of the correct viscosity (owners report fewer issues with a quality 502/505-approved synthetic); some go to a heavier grade only with caution. Truly excessive consumption with smoke requires teardown for rings/valve seals, an engine-out job. Keep the oil topped between changes to protect the engine.</x:v>
+      </x:c>
+      <x:c r="F402" s="9" t="str">
+        <x:v>Measured consumption baseline; external leak/PCV/turbo? and plug/exhaust inspection; exact approved oil; rings/valve seals only after mechanical teardown diagnosis</x:v>
+      </x:c>
+      <x:c r="G402" s="9" t="str">
+        <x:v>MEASURED-CONSUMPTION / ENGINE GATE</x:v>
+      </x:c>
+      <x:c r="H402" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I402" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J402" s="9" t="str">
+        <x:v>2009-2023 R8 V10 oil-consumption diagnosis</x:v>
+      </x:c>
+      <x:c r="K402" s="9" t="str">
+        <x:v>specialist engine service</x:v>
+      </x:c>
+      <x:c r="L402" s="9" t="str"/>
+      <x:c r="M402" s="9" t="str">
+        <x:v>Consumption has several causes; heavier oil is not universal remedy.</x:v>
+      </x:c>
+      <x:c r="N402" s="41" t="str">
+        <x:v>Do not prescribe 502/505/heavier oil without exact model-year approval.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403" ht="66" hidden="0" customHeight="1">
+      <x:c r="A403" s="40" t="str"/>
+      <x:c r="B403" s="9" t="str"/>
+      <x:c r="C403" s="9" t="str"/>
+      <x:c r="D403" s="9" t="str"/>
+      <x:c r="E403" s="9" t="str"/>
+      <x:c r="F403" s="9" t="str"/>
+      <x:c r="G403" s="9" t="str"/>
+      <x:c r="H403" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I403" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J403" s="9" t="str">
+        <x:v>VIN-approved oil and threshold</x:v>
+      </x:c>
+      <x:c r="K403" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L403" s="9" t="str"/>
+      <x:c r="M403" s="9" t="str"/>
+      <x:c r="N403" s="41" t="str"/>
+    </x:row>
+    <x:row r="404" ht="726" hidden="0" customHeight="1">
+      <x:c r="A404" s="40" t="n">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="B404" s="9" t="str">
+        <x:v>audi-r8-5-2-v10-oil-pump-driveshaft-seal-timing-case-oil-leak</x:v>
+      </x:c>
+      <x:c r="C404" s="9" t="str">
+        <x:v>2009-2023 | Audi | R8 | R8 V10, R8 V10 Plus, R8 V10 Performance, R8 V10 Spyder | 5.2L V10 FSI</x:v>
+      </x:c>
+      <x:c r="D404" s="9" t="str">
+        <x:v>5.2 V10 Oil Pump Driveshaft Seal Timing-Case Oil Leak</x:v>
+      </x:c>
+      <x:c r="E404" s="9" t="str">
+        <x:v>Confirm the source (timing-case oil-pump driveshaft seal, not valve covers or oil cooler). Repair involves removing the oil pump and renewing the oil-pump drive-shaft seal and associated O-rings/gaskets; a full reseal kit (e.g. RKX/Steso) is commonly used. It is mostly a labor and gasket/seal job rather than replacing the pump, though the pump can be replaced if worn. Fresh oil and coolant and a proper fill/bleed are required because both systems are opened.</x:v>
+      </x:c>
+      <x:c r="F404" s="9" t="str">
+        <x:v>Clean/trace exact oil source; confirm pump driveshaft seal versus covers/cooler; VIN/engine seal/O-ring/gasket scope; pump only if worn; exact fluids/fill</x:v>
+      </x:c>
+      <x:c r="G404" s="9" t="str">
+        <x:v>LEAK-SOURCE / ENGINE-VIN GATE</x:v>
+      </x:c>
+      <x:c r="H404" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I404" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J404" s="9" t="str">
+        <x:v>2009-2023 R8 V10 engine-out/access leak diagnosis and reseal</x:v>
+      </x:c>
+      <x:c r="K404" s="9" t="str">
+        <x:v>specialist R8 engine service</x:v>
+      </x:c>
+      <x:c r="L404" s="9" t="str"/>
+      <x:c r="M404" s="9" t="str">
+        <x:v>Aftermarket reseal kit fitment was not proven for all generations.</x:v>
+      </x:c>
+      <x:c r="N404" s="41" t="str">
+        <x:v>Hold RKX/Steso link until live page proves engine/year/contents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405" ht="66" hidden="0" customHeight="1">
+      <x:c r="A405" s="40" t="str"/>
+      <x:c r="B405" s="9" t="str"/>
+      <x:c r="C405" s="9" t="str"/>
+      <x:c r="D405" s="9" t="str"/>
+      <x:c r="E405" s="9" t="str"/>
+      <x:c r="F405" s="9" t="str"/>
+      <x:c r="G405" s="9" t="str"/>
+      <x:c r="H405" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I405" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J405" s="9" t="str">
+        <x:v>VIN seal diagrams/parts</x:v>
+      </x:c>
+      <x:c r="K405" s="9" t="str">
+        <x:v>manufacturer parts route</x:v>
+      </x:c>
+      <x:c r="L405" s="9" t="str"/>
+      <x:c r="M405" s="9" t="str"/>
+      <x:c r="N405" s="41" t="str"/>
+    </x:row>
+    <x:row r="406" ht="1042.800048828125" hidden="0" customHeight="1">
+      <x:c r="A406" s="40" t="n">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="B406" s="9" t="str">
+        <x:v>audi-r8-ac-compressor-v8-2008</x:v>
+      </x:c>
+      <x:c r="C406" s="9" t="str">
+        <x:v>2008-2012 | Audi | R8 | 4.2 | 4.2 V8</x:v>
+      </x:c>
+      <x:c r="D406" s="9" t="str">
+        <x:v>A/C Compressor Failure Requiring Engine-Out Repair (4.2 V8)</x:v>
+      </x:c>
+      <x:c r="E406" s="9" t="str">
+        <x:v>A/C COMPRESSOR REPLACEMENT: Requires ENGINE REMOVAL on the V8 model. Total repair cost $5,000-$8,000 ($1,000-$1,500 for parts, $4,000-$6,500 for labor). When the engine is out, strongly recommended to also address: motor mounts, clutch inspection, and any other components that benefit from engine-out access. ALTERNATIVE: Some specialty R8 shops have developed methods to access the compressor with partial disassembly (removing subframe) rather than full engine removal, potentially reducing labor to $3,000-$4,000. PREVENTION: Run the A/C regularly (even in winter for 5-10 minutes monthly) to keep compressor seals lubricated.</x:v>
+      </x:c>
+      <x:c r="F406" s="9" t="str">
+        <x:v>Confirm 4.2 V8 refrigerant/compressor fault; VIN compressor and required dryer/seals/oil; current R8 removal procedure; condition-only overlapping engine-out work</x:v>
+      </x:c>
+      <x:c r="G406" s="9" t="str">
+        <x:v>ENGINE / HVAC-DIAGNOSIS SERVICE</x:v>
+      </x:c>
+      <x:c r="H406" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I406" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J406" s="9" t="str">
+        <x:v>2008-2012 R8 4.2 compressor diagnosis and current access procedure</x:v>
+      </x:c>
+      <x:c r="K406" s="9" t="str">
+        <x:v>specialist R8 HVAC service</x:v>
+      </x:c>
+      <x:c r="L406" s="9" t="str"/>
+      <x:c r="M406" s="9" t="str">
+        <x:v>Compressor failure and engine-removal requirement must be verified before parts.</x:v>
+      </x:c>
+      <x:c r="N406" s="41" t="str">
+        <x:v>Do not bundle mounts/clutch or promise alternate labor path; no monthly-run prevention claim.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407" ht="66" hidden="0" customHeight="1">
+      <x:c r="A407" s="40" t="str"/>
+      <x:c r="B407" s="9" t="str"/>
+      <x:c r="C407" s="9" t="str"/>
+      <x:c r="D407" s="9" t="str"/>
+      <x:c r="E407" s="9" t="str"/>
+      <x:c r="F407" s="9" t="str"/>
+      <x:c r="G407" s="9" t="str"/>
+      <x:c r="H407" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I407" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J407" s="9" t="str">
+        <x:v>VIN compressor/procedure</x:v>
+      </x:c>
+      <x:c r="K407" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L407" s="9" t="str"/>
+      <x:c r="M407" s="9" t="str"/>
+      <x:c r="N407" s="41" t="str"/>
+    </x:row>
+    <x:row r="408" ht="976.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A408" s="40" t="n">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="B408" s="9" t="str">
+        <x:v>audi-r8-carbon-buildup-2008</x:v>
+      </x:c>
+      <x:c r="C408" s="9" t="str">
+        <x:v>2008-2015 | Audi | R8 | 4.2, 5.2 | 4.2 FSI V8, 5.2 FSI V10</x:v>
+      </x:c>
+      <x:c r="D408" s="9" t="str">
+        <x:v>Carbon Buildup on Intake Valves (4.2 V8 FSI and 5.2 V10 FSI)</x:v>
+      </x:c>
+      <x:c r="E408" s="9" t="str">
+        <x:v>WALNUT BLASTING: Remove intake manifolds and blast all intake ports with walnut shells. V8 (4.2L): $800-$1,200. V10 (5.2L): $1,200-$2,000 due to 10 cylinders. Perform a leak-down test BEFORE walnut blasting to ensure intake valves seat properly. Repeat every 50,000-70,000 miles. CHEMICAL CLEANING: Less effective than walnut blasting but some owners use intake valve cleaners (BG Products, CRC) as interim maintenance. DRIVING HABITS: Regular high-RPM driving (the R8's natural habitat) helps slow carbon accumulation. PREVENTION: Use quality fuel (91+ octane) and change oil every 5,000 miles.</x:v>
+      </x:c>
+      <x:c r="F408" s="9" t="str">
+        <x:v>Split V8/V10; leak-down and ignition/fuel/air diagnosis; confirm deposits; engine-specific intake-valve cleaning and seals</x:v>
+      </x:c>
+      <x:c r="G408" s="9" t="str">
+        <x:v>ENGINE / CONFIRMED-DEPOSIT SERVICE</x:v>
+      </x:c>
+      <x:c r="H408" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I408" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J408" s="9" t="str">
+        <x:v>2008-2015 R8 V8/V10 leak-down, intake inspection and cleaning</x:v>
+      </x:c>
+      <x:c r="K408" s="9" t="str">
+        <x:v>specialist R8 intake service</x:v>
+      </x:c>
+      <x:c r="L408" s="9" t="str"/>
+      <x:c r="M408" s="9" t="str">
+        <x:v>V8/V10 scope differs and deposits require confirmation.</x:v>
+      </x:c>
+      <x:c r="N408" s="41" t="str">
+        <x:v>Remove fixed interval, chemical, high-RPM, octane and oil-schedule claims.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409" ht="554.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A409" s="40" t="n">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="B409" s="9" t="str">
+        <x:v>audi-r8-carbon-fiber-sideblade-trim-clear-coat-peeling</x:v>
+      </x:c>
+      <x:c r="C409" s="9" t="str">
+        <x:v>2008-2015 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+      </x:c>
+      <x:c r="D409" s="9" t="str">
+        <x:v>Carbon Fiber Sideblade and Trim Clear-Coat Peeling</x:v>
+      </x:c>
+      <x:c r="E409" s="9" t="str">
+        <x:v>Refinish the affected panel: carefully sand back the failed lacquer without cutting into the carbon weave, then re-clear with a UV-stabilized automotive clear coat (best done by a shop experienced with carbon). To prevent recurrence, protect the finish with paint-protection film (clear wrap) or a ceramic coating, which also guards against stone chips.</x:v>
+      </x:c>
+      <x:c r="F409" s="9" t="str">
+        <x:v>Inspect clear-coat versus fiber damage; carbon-experienced refinish with UV-stable system; optional PPF after cured refinish</x:v>
+      </x:c>
+      <x:c r="G409" s="9" t="str">
+        <x:v>CONDITION-BASED BODY SERVICE</x:v>
+      </x:c>
+      <x:c r="H409" s="9" t="str">
+        <x:v>XPEL installer locator</x:v>
+      </x:c>
+      <x:c r="I409" s="9" t="str">
+        <x:v>https://www.xpel.com/installer-locator</x:v>
+      </x:c>
+      <x:c r="J409" s="9" t="str">
+        <x:v>PPF only after 2008-2015 R8 carbon panel finish is sound/cured</x:v>
+      </x:c>
+      <x:c r="K409" s="9" t="str">
+        <x:v>conditional protection service</x:v>
+      </x:c>
+      <x:c r="L409" s="9" t="str"/>
+      <x:c r="M409" s="9" t="str">
+        <x:v>Peeling clear requires refinishing skill; coating does not repair failed finish.</x:v>
+      </x:c>
+      <x:c r="N409" s="41" t="str">
+        <x:v>No DIY abrasive/coating product without weave/finish assessment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410" ht="66" hidden="0" customHeight="1">
+      <x:c r="A410" s="40" t="str"/>
+      <x:c r="B410" s="9" t="str"/>
+      <x:c r="C410" s="9" t="str"/>
+      <x:c r="D410" s="9" t="str"/>
+      <x:c r="E410" s="9" t="str"/>
+      <x:c r="F410" s="9" t="str"/>
+      <x:c r="G410" s="9" t="str"/>
+      <x:c r="H410" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I410" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J410" s="9" t="str">
+        <x:v>panel identity/replacement options</x:v>
+      </x:c>
+      <x:c r="K410" s="9" t="str">
+        <x:v>manufacturer body route</x:v>
+      </x:c>
+      <x:c r="L410" s="9" t="str"/>
+      <x:c r="M410" s="9" t="str"/>
+      <x:c r="N410" s="41" t="str"/>
+    </x:row>
+    <x:row r="411" ht="567.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A411" s="40" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="B411" s="9" t="str">
+        <x:v>audi-r8-catalytic-converter-failure-requiring-engine-out-replacement</x:v>
+      </x:c>
+      <x:c r="C411" s="9" t="str">
+        <x:v>2008-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+      </x:c>
+      <x:c r="D411" s="9" t="str">
+        <x:v>Catalytic Converter Failure Requiring Engine-Out Replacement</x:v>
+      </x:c>
+      <x:c r="E411" s="9" t="str">
+        <x:v>Confirm the failed bank with O2/catalyst-efficiency data and a back-pressure check before condemning. OEM repair means replacing the catalytic-converter-with-integrated-manifold assembly (engine-out labor); many owners opt for high-flow aftermarket or de-catted manifolds where legal. Verify no upstream misfire/oil-consumption issue is destroying the new cats.</x:v>
+      </x:c>
+      <x:c r="F411" s="9" t="str">
+        <x:v>Confirm bank with O2 efficiency and backpressure; correct upstream misfire/oil cause; engine/generation/side-specific converter-manifold; legal emissions compliance</x:v>
+      </x:c>
+      <x:c r="G411" s="9" t="str">
+        <x:v>BANK / ENGINE / EMISSIONS-COMPLIANCE GATE</x:v>
+      </x:c>
+      <x:c r="H411" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I411" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J411" s="9" t="str">
+        <x:v>2008-2023 R8 VIN/bank converter-manifold</x:v>
+      </x:c>
+      <x:c r="K411" s="9" t="str">
+        <x:v>manufacturer emissions parts/service</x:v>
+      </x:c>
+      <x:c r="L411" s="9" t="str"/>
+      <x:c r="M411" s="9" t="str">
+        <x:v>Bank/engine and root cause must be known.</x:v>
+      </x:c>
+      <x:c r="N411" s="41" t="str">
+        <x:v>Do not recommend de-catted manifolds; high-flow legality must be verified for jurisdiction.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A412" s="40" t="str"/>
+      <x:c r="B412" s="9" t="str"/>
+      <x:c r="C412" s="9" t="str"/>
+      <x:c r="D412" s="9" t="str"/>
+      <x:c r="E412" s="9" t="str"/>
+      <x:c r="F412" s="9" t="str"/>
+      <x:c r="G412" s="9" t="str"/>
+      <x:c r="H412" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I412" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J412" s="9" t="str">
+        <x:v>backpressure/root-cause diagnosis</x:v>
+      </x:c>
+      <x:c r="K412" s="9" t="str">
+        <x:v>specialist R8 emissions service</x:v>
+      </x:c>
+      <x:c r="L412" s="9" t="str"/>
+      <x:c r="M412" s="9" t="str"/>
+      <x:c r="N412" s="41" t="str"/>
+    </x:row>
+    <x:row r="413" ht="422.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A413" s="40" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="B413" s="9" t="str">
+        <x:v>audi-r8-clutch-pack-2008</x:v>
+      </x:c>
+      <x:c r="C413" s="9" t="str">
+        <x:v>2021-2022 | Audi | R8</x:v>
+      </x:c>
+      <x:c r="D413" s="9" t="str">
+        <x:v>Gearbox Underfilled: Clutch Slippage or Transmission-Oil Leak (Recall 22V225 / 37O1)</x:v>
+      </x:c>
+      <x:c r="E413" s="9" t="str">
+        <x:v>Check the VIN and campaign history with Audi or NHTSA. Under campaign 37O1, an Audi dealer inspects and corrects the transmission-oil level free of charge. If drive power drops, a clutch slips, or oil/smoke is noticed, stop safely and arrange dealer inspection.</x:v>
+      </x:c>
+      <x:c r="F413" s="9" t="str">
+        <x:v>VIN/37O1/22V225 check; dealer transmission-oil level inspection/correction; recovery for slip/leak/smoke</x:v>
+      </x:c>
+      <x:c r="G413" s="9" t="str">
+        <x:v>SOURCE-YEAR MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H413" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I413" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J413" s="9" t="str">
+        <x:v>2021-2022 R8 37O1</x:v>
+      </x:c>
+      <x:c r="K413" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L413" s="9" t="str"/>
+      <x:c r="M413" s="9" t="str">
+        <x:v>This is oil-level recall, not 2008 clutch pack.</x:v>
+      </x:c>
+      <x:c r="N413" s="41" t="str">
+        <x:v>Rename/re-key; no clutch/fluid commerce link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A414" s="40" t="str"/>
+      <x:c r="B414" s="9" t="str"/>
+      <x:c r="C414" s="9" t="str"/>
+      <x:c r="D414" s="9" t="str"/>
+      <x:c r="E414" s="9" t="str"/>
+      <x:c r="F414" s="9" t="str"/>
+      <x:c r="G414" s="9" t="str"/>
+      <x:c r="H414" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I414" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J414" s="9" t="str">
+        <x:v>22V225 VIN history</x:v>
+      </x:c>
+      <x:c r="K414" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L414" s="9" t="str"/>
+      <x:c r="M414" s="9" t="str"/>
+      <x:c r="N414" s="41" t="str"/>
+    </x:row>
+    <x:row r="415" ht="1042.800048828125" hidden="0" customHeight="1">
+      <x:c r="A415" s="40" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="B415" s="9" t="str">
+        <x:v>audi-r8-clutch-wear-2008</x:v>
+      </x:c>
+      <x:c r="C415" s="9" t="str">
+        <x:v>2008-2015 | Audi | R8 | 4.2, 5.2</x:v>
+      </x:c>
+      <x:c r="D415" s="9" t="str">
+        <x:v>R-Tronic Clutch Premature Wear and Expensive Replacement</x:v>
+      </x:c>
+      <x:c r="E415" s="9" t="str">
+        <x:v>CLUTCH REPLACEMENT: Replace clutch disc, pressure plate, throwout bearing, and resurface/replace flywheel ($5,500-$9,000 at dealer, $4,000-$6,000 at independent specialist). The mid-engine layout requires dropping the transmission—8-12 hours of labor. DRIVING TECHNIQUE: Minimize R-Tronic slip by avoiding creeping in traffic (use brake hold instead). Use manual mode in stop-and-go traffic. Avoid reverse on steep inclines. For TRACK USE: Budget for clutch replacement every 10,000-20,000 miles—R-Tronic track driving is hard on clutches. ALTERNATIVE: S-Tronic (Gen 2 R8) wet dual-clutch is significantly more durable for daily driving.</x:v>
+      </x:c>
+      <x:c r="F415" s="9" t="str">
+        <x:v>Confirm R tronic versus manual/S tronic and measured clutch wear/adaptation; exact clutch/pressure plate/release bearing/flywheel branch; transmission removal procedure</x:v>
+      </x:c>
+      <x:c r="G415" s="9" t="str">
+        <x:v>TRANSMISSION / CLUTCH-WEAR GATE</x:v>
+      </x:c>
+      <x:c r="H415" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I415" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J415" s="9" t="str">
+        <x:v>2008-2015 R8 transmission-specific clutch wear/adaptation diagnosis</x:v>
+      </x:c>
+      <x:c r="K415" s="9" t="str">
+        <x:v>specialist R8 transmission service</x:v>
+      </x:c>
+      <x:c r="L415" s="9" t="str"/>
+      <x:c r="M415" s="9" t="str">
+        <x:v>The listed years include different transmissions and not all need every part.</x:v>
+      </x:c>
+      <x:c r="N415" s="41" t="str">
+        <x:v>Remove driving/track-life and S-tronic comparison claims from fitment guidance.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416" ht="66" hidden="0" customHeight="1">
+      <x:c r="A416" s="40" t="str"/>
+      <x:c r="B416" s="9" t="str"/>
+      <x:c r="C416" s="9" t="str"/>
+      <x:c r="D416" s="9" t="str"/>
+      <x:c r="E416" s="9" t="str"/>
+      <x:c r="F416" s="9" t="str"/>
+      <x:c r="G416" s="9" t="str"/>
+      <x:c r="H416" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I416" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J416" s="9" t="str">
+        <x:v>VIN clutch components</x:v>
+      </x:c>
+      <x:c r="K416" s="9" t="str">
+        <x:v>manufacturer parts route</x:v>
+      </x:c>
+      <x:c r="L416" s="9" t="str"/>
+      <x:c r="M416" s="9" t="str"/>
+      <x:c r="N416" s="41" t="str"/>
+    </x:row>
+    <x:row r="417" ht="554.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A417" s="40" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="B417" s="9" t="str">
+        <x:v>audi-r8-coolant-expansion-tank-cracking-cooling-system-leaks</x:v>
+      </x:c>
+      <x:c r="C417" s="9" t="str">
+        <x:v>2008-2015 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+      </x:c>
+      <x:c r="D417" s="9" t="str">
+        <x:v>Coolant Expansion Tank Cracking and Cooling System Leaks</x:v>
+      </x:c>
+      <x:c r="E417" s="9" t="str">
+        <x:v>Pressure-test the cooling system to pinpoint the leak. Replace the cracked expansion/overflow tank with the updated design and renew brittle hose clamps/connections; inspect the radiator and cap. Refill with the correct Audi G13/G12 coolant specification and bleed the system fully. Address any weeping hose fittings at the same time.</x:v>
+      </x:c>
+      <x:c r="F417" s="9" t="str">
+        <x:v>Pressure-test exact leak; VIN/current expansion tank 420121403 when fitted and cracked; cap/hoses/radiator by condition; current coolant/bleed</x:v>
+      </x:c>
+      <x:c r="G417" s="9" t="str">
+        <x:v>LEAK-SOURCE / EXACT CONDITIONAL TANK</x:v>
+      </x:c>
+      <x:c r="H417" s="9" t="str">
+        <x:v>Genuine Audi R8 expansion tank 420121403</x:v>
+      </x:c>
+      <x:c r="I417" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/R8/Coolant-Expansion-Tank/</x:v>
+      </x:c>
+      <x:c r="J417" s="9" t="str">
+        <x:v>FCP lists R8 and current availability; verify 2008-2015 VIN and installed tank</x:v>
+      </x:c>
+      <x:c r="K417" s="9" t="str">
+        <x:v>exact conditional expansion tank</x:v>
+      </x:c>
+      <x:c r="L417" s="9" t="str"/>
+      <x:c r="M417" s="9" t="str">
+        <x:v>Live catalog proves R8 tank but leak source/VIN still required.</x:v>
+      </x:c>
+      <x:c r="N417" s="41" t="str">
+        <x:v>Do not prescribe G13/G12 universally or replace all fittings.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A418" s="40" t="str"/>
+      <x:c r="B418" s="9" t="str"/>
+      <x:c r="C418" s="9" t="str"/>
+      <x:c r="D418" s="9" t="str"/>
+      <x:c r="E418" s="9" t="str"/>
+      <x:c r="F418" s="9" t="str"/>
+      <x:c r="G418" s="9" t="str"/>
+      <x:c r="H418" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I418" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J418" s="9" t="str">
+        <x:v>pressure test and bleed</x:v>
+      </x:c>
+      <x:c r="K418" s="9" t="str">
+        <x:v>specialist cooling service</x:v>
+      </x:c>
+      <x:c r="L418" s="9" t="str"/>
+      <x:c r="M418" s="9" t="str"/>
+      <x:c r="N418" s="41" t="str"/>
+    </x:row>
+    <x:row r="419" ht="646.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A419" s="40" t="n">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="B419" s="9" t="str">
+        <x:v>audi-r8-direct-injection-fuel-injector-failure</x:v>
+      </x:c>
+      <x:c r="C419" s="9" t="str">
+        <x:v>2008-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+      </x:c>
+      <x:c r="D419" s="9" t="str">
+        <x:v>Direct-Injection Fuel Injector Failure</x:v>
+      </x:c>
+      <x:c r="E419" s="9" t="str">
+        <x:v>Confirm the failing cylinder with misfire and fuel-trim data and, where possible, injector-specific fault codes rather than replacing coils blindly. Replace the failed injector(s) with OEM FSI units; many owners replace as a bank or full set given shared age and mileage, and clean or address intake-valve carbon at the same service. Expect roughly $2,900 for a multi-injector job including labor per owner reports.</x:v>
+      </x:c>
+      <x:c r="F419" s="9" t="str">
+        <x:v>Cylinder-specific misfire/fuel-trim/injector diagnosis; engine/generation/VIN exact injector and seals; bank/set only when strategy/condition supports; carbon service separately confirmed</x:v>
+      </x:c>
+      <x:c r="G419" s="9" t="str">
+        <x:v>CYLINDER / ENGINE / INJECTOR GATE</x:v>
+      </x:c>
+      <x:c r="H419" s="9" t="str">
+        <x:v>Audi R8 fuel-injector catalog</x:v>
+      </x:c>
+      <x:c r="I419" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/R8/Fuel-Injector/</x:v>
+      </x:c>
+      <x:c r="J419" s="9" t="str">
+        <x:v>2008-2023 R8; exact V8/V10 generation, VIN and injector revision</x:v>
+      </x:c>
+      <x:c r="K419" s="9" t="str">
+        <x:v>vehicle-specific injector catalog</x:v>
+      </x:c>
+      <x:c r="L419" s="9" t="str"/>
+      <x:c r="M419" s="9" t="str">
+        <x:v>Full set/bank replacement and carbon cleaning are conditional.</x:v>
+      </x:c>
+      <x:c r="N419" s="41" t="str">
+        <x:v>Do not replace coils or injectors from misfire alone; remove owner-price claim.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A420" s="40" t="str"/>
+      <x:c r="B420" s="9" t="str"/>
+      <x:c r="C420" s="9" t="str"/>
+      <x:c r="D420" s="9" t="str"/>
+      <x:c r="E420" s="9" t="str"/>
+      <x:c r="F420" s="9" t="str"/>
+      <x:c r="G420" s="9" t="str"/>
+      <x:c r="H420" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I420" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J420" s="9" t="str">
+        <x:v>injector-specific diagnosis</x:v>
+      </x:c>
+      <x:c r="K420" s="9" t="str">
+        <x:v>specialist R8 fuel service</x:v>
+      </x:c>
+      <x:c r="L420" s="9" t="str"/>
+      <x:c r="M420" s="9" t="str"/>
+      <x:c r="N420" s="41" t="str"/>
+    </x:row>
+    <x:row r="421" ht="528" hidden="0" customHeight="1">
+      <x:c r="A421" s="40" t="n">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="B421" s="9" t="str">
+        <x:v>audi-r8-front-axle-hydraulic-lift-system-pump-failure</x:v>
+      </x:c>
+      <x:c r="C421" s="9" t="str">
+        <x:v>2017-2023 | Audi | R8 | 5.2L V10 FSI</x:v>
+      </x:c>
+      <x:c r="D421" s="9" t="str">
+        <x:v>Front Axle Hydraulic Lift System Pump Failure</x:v>
+      </x:c>
+      <x:c r="E421" s="9" t="str">
+        <x:v>Diagnose the lift pump/hydraulic circuit; a failed pump is the usual culprit. A new dealer pump assembly runs over $3,000, so many owners fit a good used OEM pump or an independent rebuild as a cost-effective alternative. Until repaired, approach inclines and speed bumps at an angle and very slowly to avoid front-end damage.</x:v>
+      </x:c>
+      <x:c r="F421" s="9" t="str">
+        <x:v>Lift circuit pressure/leak, pump power/ground, valve and hydraulic diagnosis; exact VIN pump or original rebuild only after failure</x:v>
+      </x:c>
+      <x:c r="G421" s="9" t="str">
+        <x:v>HYDRAULIC-CIRCUIT / PUMP GATE</x:v>
+      </x:c>
+      <x:c r="H421" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I421" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J421" s="9" t="str">
+        <x:v>2017-2023 R8 front-lift hydraulic diagnosis</x:v>
+      </x:c>
+      <x:c r="K421" s="9" t="str">
+        <x:v>specialist R8 suspension service</x:v>
+      </x:c>
+      <x:c r="L421" s="9" t="str"/>
+      <x:c r="M421" s="9" t="str">
+        <x:v>Pump is not established as usual cause without tests.</x:v>
+      </x:c>
+      <x:c r="N421" s="41" t="str">
+        <x:v>No used/rebuild pump link without exact identity, condition, warranty and service proof.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422" ht="66" hidden="0" customHeight="1">
+      <x:c r="A422" s="40" t="str"/>
+      <x:c r="B422" s="9" t="str"/>
+      <x:c r="C422" s="9" t="str"/>
+      <x:c r="D422" s="9" t="str"/>
+      <x:c r="E422" s="9" t="str"/>
+      <x:c r="F422" s="9" t="str"/>
+      <x:c r="G422" s="9" t="str"/>
+      <x:c r="H422" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I422" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J422" s="9" t="str">
+        <x:v>VIN pump/parts</x:v>
+      </x:c>
+      <x:c r="K422" s="9" t="str">
+        <x:v>manufacturer parts route</x:v>
+      </x:c>
+      <x:c r="L422" s="9" t="str"/>
+      <x:c r="M422" s="9" t="str"/>
+      <x:c r="N422" s="41" t="str"/>
+    </x:row>
+    <x:row r="423" ht="316.79998779296875" hidden="0" customHeight="1">
+      <x:c r="A423" s="40" t="n">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="B423" s="9" t="str">
+        <x:v>audi-r8-front-passenger-airbag-inflator-rupture</x:v>
+      </x:c>
+      <x:c r="C423" s="9" t="str">
+        <x:v>2016-2016 | Audi | R8</x:v>
+      </x:c>
+      <x:c r="D423" s="9" t="str">
+        <x:v>Front-Passenger Airbag Module May Explode or Deploy Improperly (Recall 22V543 / 69DY)</x:v>
+      </x:c>
+      <x:c r="E423" s="9" t="str">
+        <x:v>Check the VIN with Audi or NHTSA. Audi dealers replace the front-passenger airbag module free of charge under campaign 69DY/61C1. Do not source a used airbag module from this summary.</x:v>
+      </x:c>
+      <x:c r="F423" s="9" t="str">
+        <x:v>VIN/69DY/61C1/22V543 check; free passenger airbag module</x:v>
+      </x:c>
+      <x:c r="G423" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H423" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I423" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J423" s="9" t="str">
+        <x:v>2016 R8 airbag recall</x:v>
+      </x:c>
+      <x:c r="K423" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L423" s="9" t="str"/>
+      <x:c r="M423" s="9" t="str">
+        <x:v>Pyrotechnic module remedy is campaign-controlled.</x:v>
+      </x:c>
+      <x:c r="N423" s="41" t="str">
+        <x:v>No used airbag link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A424" s="40" t="str"/>
+      <x:c r="B424" s="9" t="str"/>
+      <x:c r="C424" s="9" t="str"/>
+      <x:c r="D424" s="9" t="str"/>
+      <x:c r="E424" s="9" t="str"/>
+      <x:c r="F424" s="9" t="str"/>
+      <x:c r="G424" s="9" t="str"/>
+      <x:c r="H424" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I424" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J424" s="9" t="str">
+        <x:v>22V543 VIN history</x:v>
+      </x:c>
+      <x:c r="K424" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L424" s="9" t="str"/>
+      <x:c r="M424" s="9" t="str"/>
+      <x:c r="N424" s="41" t="str"/>
+    </x:row>
+    <x:row r="425" ht="409.20001220703125" hidden="0" customHeight="1">
+      <x:c r="A425" s="40" t="n">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="B425" s="9" t="str">
+        <x:v>audi-r8-fuel-supply-line-chafing-heat-shield</x:v>
+      </x:c>
+      <x:c r="C425" s="9" t="str">
+        <x:v>2011-2012 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+      </x:c>
+      <x:c r="D425" s="9" t="str">
+        <x:v>R8 Spyder Fuel Supply Line Can Chafe on Heat Shield (Recall 11V390 / 20Q8)</x:v>
+      </x:c>
+      <x:c r="E425" s="9" t="str">
+        <x:v>Check the VIN and recall status. Audi dealers inspect the line, replace it if damaged, and adjust the fuel line and heat shield for proper clearance free of charge. If fuel odor or leakage is present, stop driving and arrange immediate inspection.</x:v>
+      </x:c>
+      <x:c r="F425" s="9" t="str">
+        <x:v>VIN/20Q8/11V390 check; dealer line inspection/conditional replacement and heat-shield clearance; stop for fuel odor/leak</x:v>
+      </x:c>
+      <x:c r="G425" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H425" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I425" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J425" s="9" t="str">
+        <x:v>2011-2012 R8 Spyder 20Q8</x:v>
+      </x:c>
+      <x:c r="K425" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L425" s="9" t="str"/>
+      <x:c r="M425" s="9" t="str">
+        <x:v>Line/clearance remedy is recall work.</x:v>
+      </x:c>
+      <x:c r="N425" s="41" t="str">
+        <x:v>No fuel-line product link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A426" s="40" t="str"/>
+      <x:c r="B426" s="9" t="str"/>
+      <x:c r="C426" s="9" t="str"/>
+      <x:c r="D426" s="9" t="str"/>
+      <x:c r="E426" s="9" t="str"/>
+      <x:c r="F426" s="9" t="str"/>
+      <x:c r="G426" s="9" t="str"/>
+      <x:c r="H426" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I426" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J426" s="9" t="str">
+        <x:v>11V390 VIN history</x:v>
+      </x:c>
+      <x:c r="K426" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L426" s="9" t="str"/>
+      <x:c r="M426" s="9" t="str"/>
+      <x:c r="N426" s="41" t="str"/>
+    </x:row>
+    <x:row r="427" ht="792" hidden="0" customHeight="1">
+      <x:c r="A427" s="40" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="B427" s="9" t="str">
+        <x:v>audi-r8-ignition-coil-pack-failure-causing-misfires</x:v>
+      </x:c>
+      <x:c r="C427" s="9" t="str">
+        <x:v>2008-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+      </x:c>
+      <x:c r="D427" s="9" t="str">
+        <x:v>Ignition Coil Pack Failure Causing Misfires</x:v>
+      </x:c>
+      <x:c r="E427" s="9" t="str">
+        <x:v>Diagnose the misfiring cylinder(s) via the stored misfire counters, then replace the failed coil(s) along with spark plugs; most specialists replace the full set of 8 (V8) or 10 (V10) plus plugs to avoid repeat visits. The canonical 4.2 V8 coil is the revision-'T' red coil, Audi/VW PN 077905115T (superseded family, aftermarket cross-reference 06E905115E). The Gen-2 5.2 V10 uses Audi PN 07L905115B. Address any valve-cover or plug-tube oil leak at the same time so new coils are not contaminated.</x:v>
+      </x:c>
+      <x:c r="F427" s="9" t="str">
+        <x:v>Misfire counters/cylinder swap and plug/oil-leak inspection; exact engine/generation coil; plugs/full set only by condition/strategy</x:v>
+      </x:c>
+      <x:c r="G427" s="9" t="str">
+        <x:v>ENGINE-GENERATION / CYLINDER GATE</x:v>
+      </x:c>
+      <x:c r="H427" s="9" t="str">
+        <x:v>Genuine R8 V10 coil 07L905115B</x:v>
+      </x:c>
+      <x:c r="I427" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/products/audi-direct-ignition-coil-genuine-audi-07l905115b</x:v>
+      </x:c>
+      <x:c r="J427" s="9" t="str">
+        <x:v>live page lists R8; verify Gen-2 5.2 V10 VIN before purchase</x:v>
+      </x:c>
+      <x:c r="K427" s="9" t="str">
+        <x:v>exact conditional V10 coil</x:v>
+      </x:c>
+      <x:c r="L427" s="9" t="str"/>
+      <x:c r="M427" s="9" t="str">
+        <x:v>07L905115B is live and R8-listed; the claimed 077905115T family was not verified across the V8 population.</x:v>
+      </x:c>
+      <x:c r="N427" s="41" t="str">
+        <x:v>Do not replace full set/plugs or use cross-reference 06E905115E without VIN/engine proof.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A428" s="40" t="str"/>
+      <x:c r="B428" s="9" t="str"/>
+      <x:c r="C428" s="9" t="str"/>
+      <x:c r="D428" s="9" t="str"/>
+      <x:c r="E428" s="9" t="str"/>
+      <x:c r="F428" s="9" t="str"/>
+      <x:c r="G428" s="9" t="str"/>
+      <x:c r="H428" s="9" t="str">
+        <x:v>Audi R8 ignition-coil catalog</x:v>
+      </x:c>
+      <x:c r="I428" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/R8/Ignition-Coil/</x:v>
+      </x:c>
+      <x:c r="J428" s="9" t="str">
+        <x:v>select exact V8/V10 generation and current revision</x:v>
+      </x:c>
+      <x:c r="K428" s="9" t="str">
+        <x:v>vehicle-specific coil catalog</x:v>
+      </x:c>
+      <x:c r="L428" s="9" t="str"/>
+      <x:c r="M428" s="9" t="str"/>
+      <x:c r="N428" s="41" t="str"/>
+    </x:row>
+    <x:row r="429" ht="673.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A429" s="40" t="n">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="B429" s="9" t="str">
+        <x:v>audi-r8-led-headlight-drl-module-failure-flickering</x:v>
+      </x:c>
+      <x:c r="C429" s="9" t="str">
+        <x:v>2014-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+      </x:c>
+      <x:c r="D429" s="9" t="str">
+        <x:v>LED Headlight / DRL Module Failure and Flickering</x:v>
+      </x:c>
+      <x:c r="E429" s="9" t="str">
+        <x:v>Inspect the headlight for moisture and corroded connectors; a failed LED driver module usually requires replacing the headlight assembly (used units run roughly £1,600-1,800, new from Audi around £2,800), followed by headlight aiming/auto-leveling calibration with a diagnostic tool. Reseal or replace cracked housings to stop repeat water damage. Some independent specialists can repair the driver board at lower cost.</x:v>
+      </x:c>
+      <x:c r="F429" s="9" t="str">
+        <x:v>Split generations/options/side; moisture/connector/driver diagnosis; exact module or assembly; reseal source; aim/level calibration</x:v>
+      </x:c>
+      <x:c r="G429" s="9" t="str">
+        <x:v>HEADLAMP-OPTION / SIDE / DIAGNOSIS GATE</x:v>
+      </x:c>
+      <x:c r="H429" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I429" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J429" s="9" t="str">
+        <x:v>2014-2023 R8 VIN/side/headlamp-option parts and calibration</x:v>
+      </x:c>
+      <x:c r="K429" s="9" t="str">
+        <x:v>manufacturer lighting service</x:v>
+      </x:c>
+      <x:c r="L429" s="9" t="str"/>
+      <x:c r="M429" s="9" t="str">
+        <x:v>Driver may be repairable and full assembly/side/options vary.</x:v>
+      </x:c>
+      <x:c r="N429" s="41" t="str">
+        <x:v>Remove UK price claims and no generic diagnostic-tool link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A430" s="40" t="str"/>
+      <x:c r="B430" s="9" t="str"/>
+      <x:c r="C430" s="9" t="str"/>
+      <x:c r="D430" s="9" t="str"/>
+      <x:c r="E430" s="9" t="str"/>
+      <x:c r="F430" s="9" t="str"/>
+      <x:c r="G430" s="9" t="str"/>
+      <x:c r="H430" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I430" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J430" s="9" t="str">
+        <x:v>moisture/driver diagnosis and repair</x:v>
+      </x:c>
+      <x:c r="K430" s="9" t="str">
+        <x:v>specialist lighting service</x:v>
+      </x:c>
+      <x:c r="L430" s="9" t="str"/>
+      <x:c r="M430" s="9" t="str"/>
+      <x:c r="N430" s="41" t="str"/>
+    </x:row>
+    <x:row r="431" ht="264" hidden="0" customHeight="1">
+      <x:c r="A431" s="40" t="n">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="B431" s="9" t="str">
+        <x:v>audi-r8-magnetic-ride-2008</x:v>
+      </x:c>
+      <x:c r="C431" s="9" t="str">
+        <x:v>2008-2024 | Audi | R8</x:v>
+      </x:c>
+      <x:c r="D431" s="9" t="str">
+        <x:v>Magnetic Ride Damper Fluid Leaks</x:v>
+      </x:c>
+      <x:c r="E431" s="9" t="str">
+        <x:v>Replace magnetic ride dampers. OEM replacements are very expensive. KW or Bilstein aftermarket coilovers are popular track-oriented alternatives.</x:v>
+      </x:c>
+      <x:c r="F431" s="9" t="str">
+        <x:v>Per-corner leak/damping/electrical diagnosis; exact generation/PR-code damper; matched axle/set as required; calibrated OEM repair or engineered conversion plan</x:v>
+      </x:c>
+      <x:c r="G431" s="9" t="str">
+        <x:v>GENERATION / PR-CODE SUSPENSION GATE</x:v>
+      </x:c>
+      <x:c r="H431" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I431" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J431" s="9" t="str">
+        <x:v>2008-2024 R8 magnetic-ride diagnosis and conversion implications</x:v>
+      </x:c>
+      <x:c r="K431" s="9" t="str">
+        <x:v>specialist R8 suspension service</x:v>
+      </x:c>
+      <x:c r="L431" s="9" t="str"/>
+      <x:c r="M431" s="9" t="str">
+        <x:v>Seventeen years span different generations and options.</x:v>
+      </x:c>
+      <x:c r="N431" s="41" t="str">
+        <x:v>No KW/Bilstein link before exact kit fitment, cancellation hardware, alignment and ride-control tradeoffs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432" ht="1227.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A432" s="40" t="n">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="B432" s="9" t="str">
+        <x:v>audi-r8-magnetic-ride-leak-2008</x:v>
+      </x:c>
+      <x:c r="C432" s="9" t="str">
+        <x:v>2008-2015 | Audi | R8 | 4.2, 5.2</x:v>
+      </x:c>
+      <x:c r="D432" s="9" t="str">
+        <x:v>Magnetic Ride Suspension Damper Leak and Premature Failure</x:v>
+      </x:c>
+      <x:c r="E432" s="9" t="str">
+        <x:v>OEM REPLACEMENT: Replace leaking magnetic ride shocks ($1,800 each, $5,100-$8,000+ for full set installed). OEM replacements use the same technology and will eventually fail again. REFURBISHED OPTION: Refurbished magnetic ride dampers from specialty rebuilders (approximately $1,000-$1,400 each). PASSIVE CONVERSION: Convert to R8 Plus passive shocks ($3,000-$4,000 for set—less than 2 OEM magnetic ride shocks) or aftermarket coilovers ($2,500-$5,000 for quality kit like KW, JRZ, or Ohlins). Passive conversion eliminates the failure mode permanently but removes adaptive ride control. PREVENTION: Limited—magnetic fluid degradation is inherent to the technology. Budget for replacement every 30,000-50,000 miles if keeping magnetic ride.</x:v>
+      </x:c>
+      <x:c r="F432" s="9" t="str">
+        <x:v>Confirm leaking corner and electronic function; exact first-gen damper or verified original rebuild; engineered passive conversion only with complete hardware/coding/alignment plan</x:v>
+      </x:c>
+      <x:c r="G432" s="9" t="str">
+        <x:v>CORNER / OPTION / CONVERSION GATE</x:v>
+      </x:c>
+      <x:c r="H432" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I432" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J432" s="9" t="str">
+        <x:v>2008-2015 R8 magnetic-ride diagnosis/rebuild/conversion planning</x:v>
+      </x:c>
+      <x:c r="K432" s="9" t="str">
+        <x:v>specialist R8 suspension service</x:v>
+      </x:c>
+      <x:c r="L432" s="9" t="str"/>
+      <x:c r="M432" s="9" t="str">
+        <x:v>OEM, rebuild and passive conversion are distinct choices.</x:v>
+      </x:c>
+      <x:c r="N432" s="41" t="str">
+        <x:v>No 30k-50k life claim or named kit link without live exact fitment evidence.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433" ht="1003.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A433" s="40" t="n">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="B433" s="9" t="str">
+        <x:v>audi-r8-r-tronic-hydraulic-pump-pressure-accumulator-failure</x:v>
+      </x:c>
+      <x:c r="C433" s="9" t="str">
+        <x:v>2008-2015 | Audi | R8 | R8 4.2 R tronic, R8 V10 R tronic, R8 V10 Plus R tronic | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+      </x:c>
+      <x:c r="D433" s="9" t="str">
+        <x:v>R tronic Hydraulic Pump and Pressure Accumulator Failure</x:v>
+      </x:c>
+      <x:c r="E433" s="9" t="str">
+        <x:v>Diagnose with a scan tool: a failing accumulator/pump typically stores P17BF (hydraulic pump play protection) and/or P0944 (loss of hydraulic pressure). Standard repair order is to renew the relatively inexpensive pressure accumulator first; if pressure loss persists, replace the hydraulic pump (and its relay/fuse), and only then suspect the hydraulic clutch/gear actuator or the solenoid-valve O-rings. Fresh, correct-spec hydraulic fluid and a proper bleed with a diagnostic tool are required. Owners are advised not to drive the car (except directly to a shop) once the pump is heard running continuously or shifting becomes intermittent.</x:v>
+      </x:c>
+      <x:c r="F433" s="9" t="str">
+        <x:v>Explicit manufacturer-capable scan for P17BF/P0944 plus pressure/run-time; accumulator first only if diagnosis supports; pump/relay/fuse then actuator/O-rings; exact fluid and guided bleed</x:v>
+      </x:c>
+      <x:c r="G433" s="9" t="str">
+        <x:v>EXPLICIT SCANNER/DIAGNOSTIC TOOL APPROVAL — R TRONIC GUIDED SERVICE</x:v>
+      </x:c>
+      <x:c r="H433" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I433" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J433" s="9" t="str">
+        <x:v>2008-2015 R8 R tronic pressure diagnosis and guided bleed</x:v>
+      </x:c>
+      <x:c r="K433" s="9" t="str">
+        <x:v>specialist diagnostic service</x:v>
+      </x:c>
+      <x:c r="L433" s="9" t="str"/>
+      <x:c r="M433" s="9" t="str">
+        <x:v>How to Fix explicitly needs a scan/guided bleed, but specialized R-tronic service is safer than a generic OBD link.</x:v>
+      </x:c>
+      <x:c r="N433" s="41" t="str">
+        <x:v>No accumulator/pump until pressure diagnosis; verify trim incorrectly listing V10 Plus R tronic.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434" ht="66" hidden="0" customHeight="1">
+      <x:c r="A434" s="40" t="str"/>
+      <x:c r="B434" s="9" t="str"/>
+      <x:c r="C434" s="9" t="str"/>
+      <x:c r="D434" s="9" t="str"/>
+      <x:c r="E434" s="9" t="str"/>
+      <x:c r="F434" s="9" t="str"/>
+      <x:c r="G434" s="9" t="str"/>
+      <x:c r="H434" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I434" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J434" s="9" t="str">
+        <x:v>VIN hydraulic components/fluid/procedure</x:v>
+      </x:c>
+      <x:c r="K434" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L434" s="9" t="str"/>
+      <x:c r="M434" s="9" t="str"/>
+      <x:c r="N434" s="41" t="str"/>
+    </x:row>
+    <x:row r="435" ht="237.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A435" s="40" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="B435" s="9" t="str">
+        <x:v>audi-r8-s-tronic-actuator-2008</x:v>
+      </x:c>
+      <x:c r="C435" s="9" t="str">
+        <x:v>2008-2024 | Audi | R8</x:v>
+      </x:c>
+      <x:c r="D435" s="9" t="str">
+        <x:v>S-tronic Transmission Actuator Failure</x:v>
+      </x:c>
+      <x:c r="E435" s="9" t="str">
+        <x:v>Replace S-tronic actuators. Full transmission service with correct S-tronic fluid is critical. Dealer or specialist only repair.</x:v>
+      </x:c>
+      <x:c r="F435" s="9" t="str">
+        <x:v>Correct model-year/transmission population; exact S tronic code; faults/pressure/adaptation/fluid and actuator diagnosis; component only after proof</x:v>
+      </x:c>
+      <x:c r="G435" s="9" t="str">
+        <x:v>SOURCE RANGE ERROR / TRANSMISSION-CODE GATE</x:v>
+      </x:c>
+      <x:c r="H435" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I435" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J435" s="9" t="str">
+        <x:v>R8 S tronic transmission-code and actuator diagnosis</x:v>
+      </x:c>
+      <x:c r="K435" s="9" t="str">
+        <x:v>specialist R8 transmission service</x:v>
+      </x:c>
+      <x:c r="L435" s="9" t="str"/>
+      <x:c r="M435" s="9" t="str">
+        <x:v>2008-2012 first-gen R8 did not uniformly use S tronic and the range spans different units.</x:v>
+      </x:c>
+      <x:c r="N435" s="41" t="str">
+        <x:v>Correct years/transmission before any actuator/fluid link; no blanket replacement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="436" ht="66" hidden="0" customHeight="1">
+      <x:c r="A436" s="42" t="str"/>
+      <x:c r="B436" s="43" t="str"/>
+      <x:c r="C436" s="43" t="str"/>
+      <x:c r="D436" s="43" t="str"/>
+      <x:c r="E436" s="43" t="str"/>
+      <x:c r="F436" s="43" t="str"/>
+      <x:c r="G436" s="43" t="str"/>
+      <x:c r="H436" s="43" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I436" s="43" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J436" s="43" t="str">
+        <x:v>VIN transmission/actuator/fluid</x:v>
+      </x:c>
+      <x:c r="K436" s="43" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L436" s="43" t="str"/>
+      <x:c r="M436" s="43" t="str"/>
+      <x:c r="N436" s="44" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12705,21 +15693,21 @@
         <x:v>Queue status</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="712.7999877929688" hidden="0" customHeight="1">
+    <x:row r="2" ht="330" hidden="0" customHeight="1">
       <x:c r="A2" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="9" t="str">
-        <x:v>audi-q7-supercharger-failure-2011</x:v>
+        <x:v>audi-r8-s-tronic-gearbox-ventilation-hose-transmission-fluid-leak</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
-        <x:v>2011-2015 | Audi | Q7 | Premium, Premium Plus, Prestige, S line, SQ7 | 3.0T</x:v>
+        <x:v>2017-2018 | Audi | R8 | 5.2L V10 FSI</x:v>
       </x:c>
       <x:c r="D2" s="9" t="str">
-        <x:v>Supercharger Bearing Failure and Boost Leaks (3.0T)</x:v>
+        <x:v>Gearbox Ventilation Hose Can Leak Fluid Near Hot Engine Parts (Recall 18V639 / 34J1)</x:v>
       </x:c>
       <x:c r="E2" s="9" t="str">
-        <x:v>Worn bearings: Supercharger rebuild with new bearings ($1,500-2,500) or replacement supercharger ($3,000-5,000). Bypass valve: Replace supercharger bypass valve ($300-600). Boost leaks: Inspect all boost hoses/clamps, replace cracked hoses ($150-400). Use OEM Audi or quality aftermarket (INA) supercharger bearings. AudiWorld recommends catch can installation ($300-500) to reduce oil vapor damage to supercharger.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the single gearbox ventilation hose with the higher-volume double hose free of charge under campaign 34J1. Stop driving if hot-oil odor or smoke appears.</x:v>
       </x:c>
       <x:c r="F2" s="9" t="n">
         <x:v>0</x:v>
@@ -12728,21 +15716,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="3" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A3" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
-        <x:v>audi-q7-tdi-emissions-scandal-2009</x:v>
+        <x:v>audi-r8-spyder-convertible-top-hydraulic-pump-failure</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
-        <x:v>2009-2015 | Audi | Q7 | 3.0 TDI</x:v>
+        <x:v>2011-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
       </x:c>
       <x:c r="D3" s="9" t="str">
-        <x:v>2009-2015 Q7 3.0 TDI Emissions Settlement and Modification History</x:v>
+        <x:v>Spyder Convertible Top Hydraulic Pump Failure</x:v>
       </x:c>
       <x:c r="E3" s="9" t="str">
-        <x:v>Check the VIN and service history with an authorized Audi dealer and use current EPA or Audi settlement information to determine whether an emissions modification was completed and what extended emissions warranty, if any, applies to that vehicle. Diagnose any present warning or drivability concern separately. Do not buy a scan tool or generic repair manual as a settlement remedy.</x:v>
+        <x:v>Scan for the specific fault (pump vs. sensor vs. latch) before parting; a mis-reading position sensor can mimic a dead pump. Replace the hydraulic pump/motor assembly (Audi R8 Spyder convertible-top hydraulic pump PN 427871791 for 2010-2016 cars) and top up/refill the correct hydraulic fluid, or replace the failed cylinder/sensor. Leaking lines and worn seals should be renewed together. Independent hydraulic rebuild services exist as a lower-cost alternative to a full dealer pump.</x:v>
       </x:c>
       <x:c r="F3" s="9" t="n">
         <x:v>0</x:v>
@@ -12751,21 +15739,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="594" hidden="0" customHeight="1">
+    <x:row r="4" ht="1122" hidden="0" customHeight="1">
       <x:c r="A4" s="40" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>audi-q7-tdi-oil-cooler-leak-2013</x:v>
+        <x:v>audi-r8-v8-engine-bearing-2008</x:v>
       </x:c>
       <x:c r="C4" s="9" t="str">
-        <x:v>2013-2013 | Audi | Q7 | 3.0 TDI</x:v>
+        <x:v>2008-2015 | Audi | R8 | 4.2 | 4.2 FSI</x:v>
       </x:c>
       <x:c r="D4" s="9" t="str">
-        <x:v>2013 Q7 TDI Brake-Booster Vacuum-Line Recall 47L8 (14V516)</x:v>
+        <x:v>Rod Bearing Wear and Engine Failure Risk (4.2 V8 FSI)</x:v>
       </x:c>
       <x:c r="E4" s="9" t="str">
-        <x:v>Check the VIN for open recall 47L8 with Audi. The dealer remedy replaces the specified vacuum line and inspects the vacuum line and brake booster for oil contamination. Additional vacuum-line or brake-booster components are replaced when contamination is found. The recall repair is dealer work and is not a reason to buy an oil cooler, scan tool or manual.</x:v>
+        <x:v>EARLY DETECTION (knocking noise only): Rod bearing replacement ($2,000-$5,000). Must be caught EARLY before bearing material migrates through oil system. Cut open every oil filter at oil change to inspect for metallic debris. CATASTROPHIC FAILURE: Engine replacement ($13,000+ Audi exchange, $8,000-$15,000 rebuilt from AMTuned or specialist rebuilder). ARP 2000 reinforced connecting rod bolts are available as a preventive upgrade during any engine-out service. PREVENTION: Use ONLY premium 5W-40 synthetic oil. Change oil every 5,000 miles maximum. NEVER exceed oil change intervals—the high-revving V8 is extremely sensitive to oil condition. For track use, change oil after every 2-3 track days.</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
         <x:v>0</x:v>
@@ -12774,21 +15762,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="488.3999938964844" hidden="0" customHeight="1">
+    <x:row r="5" ht="924" hidden="0" customHeight="1">
       <x:c r="A5" s="40" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>audi-q7-timing-chain-tensioner-2007</x:v>
+        <x:v>audi-rs-etron-gt-battery-short-2022</x:v>
       </x:c>
       <x:c r="C5" s="9" t="str">
-        <x:v>2011-2015 | Audi | Q7 | 3.0 TFSI</x:v>
+        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
       </x:c>
       <x:c r="D5" s="9" t="str">
-        <x:v>2011-2015 Q7 3.0 TFSI Brief Cold-Start Timing-Chain Rattle - TSB 2039995/2</x:v>
+        <x:v>2022-2024 RS e-tron GT High-Voltage Battery Recall 931A/931B (24V726)</x:v>
       </x:c>
       <x:c r="E5" s="9" t="str">
-        <x:v>Confirm that the concern is the bulletin-defined one-to-three-second first-start rattle and have an Audi technician follow TSB 2039995/2 and current repair information. A longer, persistent or different noise, warning light or drivability concern requires separate diagnosis. Do not order a timing kit from this card.</x:v>
+        <x:v>Check the VIN for open Audi campaign 931A or 931B and complete the authorized dealer remedy. Under 931A, enrolled vehicles can be monitored through online battery data; Audi contacts owners if a module appears critical. Under 931B, the dealer performs diagnostic procedures until the final monitoring software is installed. Audi installs the onboard diagnostic software and replaces affected battery modules at no cost when anomalies are identified. Follow any vehicle- or dealer-specific 80-percent charging instruction; the filing does not direct every 931A vehicle to use that limit.</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
         <x:v>0</x:v>
@@ -12797,21 +15785,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="6" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A6" s="40" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>audi-q7-transfer-case-2007</x:v>
+        <x:v>audi-rs-etron-gt-brake-hose-2022</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
-        <x:v>2007-2019 | Audi | Q7 | Premium, Premium Plus, Prestige | 3.0T, 3.6L, 4.2L, 3.0 TDI</x:v>
+        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
-        <x:v>Transfer Case Fluid Leak and Failure</x:v>
+        <x:v>2022-2024 RS e-tron GT Front Brake-Hose Recall 47UP (24V465)</x:v>
       </x:c>
       <x:c r="E6" s="9" t="str">
-        <x:v>Replace leaking seals and refill with correct fluid (75W-90 GL-5 or Audi specification). If grinding is present, the transfer case may need rebuild or replacement. Regular fluid changes every 60,000 miles can prevent internal damage. Check for leaks at every oil change.</x:v>
+        <x:v>Check the VIN for an open 47UP action and have an authorized Audi dealer replace both front brake hoses and holders free of charge. If pedal travel increases or the vehicle displays a warning related to reduced brake fluid, contact an Audi dealer for diagnosis without delay. Do not buy a single hose or substitute generic brake lines from the prior links; the campaign controls the complete criteria-specific repair.</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
         <x:v>0</x:v>
@@ -12820,21 +15808,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="7" ht="726" hidden="0" customHeight="1">
       <x:c r="A7" s="40" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>audi-q7-water-pump-failure-2007</x:v>
+        <x:v>audi-rs-etron-gt-charging-port-2022</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
-        <x:v>2007-2015 | Audi | Q7</x:v>
+        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
-        <x:v>Water Pump and Thermostat Failure (Overheating)</x:v>
+        <x:v>2022-2024 RS e-tron GT Red Charging LED or Fast-Charging Abort - Audi 91VT</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
-        <x:v>IMMEDIATE if overheating: Pull over, turn off engine, DO NOT continue - engine damage occurs in minutes. Preventive: Replace water pump/thermostat assembly at 60k-80k miles ($800-1,500) to avoid catastrophic failure. Failed pump: Replace water pump/thermostat ($800-1,500). If overheated: Cylinder head inspection, possible head gasket replacement ($2,500-5,000). Use OEM Audi or premium Geba/Meyle parts.</x:v>
+        <x:v>Have an Audi dealer check the VIN and assigned 91VT criterion in the campaign/action system. For the charging-related criteria, the authorized remedy updates the high-voltage battery control-module software, with the convenience-system control module also updated where the assigned criterion requires it. Diagnose charging failures outside that exact campaign branch rather than replacing the charging socket or module from symptoms alone.</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
         <x:v>0</x:v>
@@ -12843,21 +15831,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="8" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A8" s="40" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>audi-q8-48v-system-2019</x:v>
+        <x:v>audi-rs-etron-gt-software-2022</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
-        <x:v>2019-2024 | Audi | Q8</x:v>
+        <x:v>2022-2022 | Audi | RS e-tron GT</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>2019-2024 Q8 Starter-Alternator Service Action 27BQ - Check VIN</x:v>
+        <x:v>2022 RS e-tron GT Audi connect Inoperative after 91DZ - TSB 2068824/2</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
-        <x:v>Check the VIN and current campaign status with an Audi dealer. If 27BQ is open, the dealer follows the campaign procedure and replaces the starter-alternator at no cost when directed. If the action is not open, use Audi guided diagnostics: current bulletins distinguish a replacement result from sensor and CAN faults that replacement will not fix. Do not buy a 12V battery, charger or starter from this card.</x:v>
+        <x:v>Confirm that the failure began after 91DZ and matches the Audi connect/SOS-LED condition. An Audi technician should use ODIS Guided Fault Finding and run SVM Check Module Configuration for diagnostic address 0019, J533. Manual coding is no longer required. Escalate a continuing Audi connect failure through Audi support after the guided coding procedure rather than buying hardware or a retail software service.</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
         <x:v>0</x:v>
@@ -12866,21 +15854,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="422.3999938964844" hidden="0" customHeight="1">
+    <x:row r="9" ht="937.2000122070312" hidden="0" customHeight="1">
       <x:c r="A9" s="40" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>audi-q8-8-speed-tiptronic-harsh-shifting-jolt-delayed-engagement</x:v>
+        <x:v>audi-rs-etron-gt-tire-wear-2022</x:v>
       </x:c>
       <x:c r="C9" s="9" t="str">
-        <x:v>2019-2023 | Audi | Q8 | Q8 55 TFSI, SQ8, RS Q8, 50 TDI</x:v>
+        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
       </x:c>
       <x:c r="D9" s="9" t="str">
-        <x:v>8-Speed Tiptronic Harsh Shifting, Jolt and Delayed Engagement</x:v>
+        <x:v>Accelerated Tire Wear and Alignment Sensitivity</x:v>
       </x:c>
       <x:c r="E9" s="9" t="str">
-        <x:v>Perform a full ZF 8HP transmission fluid and filter (pan) service with the correct Audi-spec fluid, then run the gearbox adaptation/relearn procedure. Update the transmission control module software if a TSB applies. Inspect transmission and engine mounts and replace if collapsed.</x:v>
+        <x:v>Rotate front-to-back every 3,000-5,000 miles (only possible if sizes permit, which staggered setups often do not). Check alignment every 5,000 miles or after any pothole impact - even 0.1 degree of toe deviation causes rapid edge wear on these wide tires. Consider switching to Michelin Pilot Sport 4S or Pirelli P Zero PZ4 for improved tread life over the OE Continental SportContact 6. Budget $1,400-$2,000 for a set of four replacement tires. Aggressive driving with launch control dramatically reduces tire life. For better longevity, use Comfort mode instead of Dynamic for daily driving.</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
         <x:v>0</x:v>
@@ -12894,13 +15882,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>audi-q8-air-suspension-2019</x:v>
+        <x:v>audi-rs-q8-air-suspension-2020</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
-        <x:v>2019-2025 | Audi | Q8</x:v>
+        <x:v>2020-2025 | Audi | RS Q8</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>2019-2025 Q8 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
+        <x:v>2020-2025 RS Q8 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
         <x:v>Inspect the wiring and connector contacts between J775 and J1135 before replacing a component. For a first passive or sporadic occurrence, clear the fault and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after wiring inspection, Audi directs replacement of J1135 under current repair and parts information. Do not buy struts, springs, a compressor or a conversion kit solely from this warning.</x:v>
@@ -12912,21 +15900,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="607.2000122070312" hidden="0" customHeight="1">
+    <x:row r="11" ht="184.8000030517578" hidden="0" customHeight="1">
       <x:c r="A11" s="40" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>audi-q8-carbon-buildup-2019</x:v>
+        <x:v>audi-rs3-carbon-buildup-2017</x:v>
       </x:c>
       <x:c r="C11" s="9" t="str">
-        <x:v>2019-2023 | Audi | Q8</x:v>
+        <x:v>2017-2025 | Audi | RS3 | 2.5T</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>Severe Carbon Buildup on Intake Valves (3.0T)</x:v>
+        <x:v>2.5T Five-Cylinder Carbon Buildup</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
-        <x:v>WALNUT BLASTING: Remove intake manifold and blast walnut shells through intake ports ($900-$1,500). Requires specialized equipment. Repeat every 60,000 miles as PREVENTIVE maintenance. PREVENTION: Install catch can ($400-$600) to filter PCV vapors—extends interval to 100k+ miles. Add Liqui Moly Intake Valve Cleaner to every oil change. Change oil every 5,000 miles.</x:v>
+        <x:v>Walnut blast intake valves every 30,000-40,000 miles. Install catch can immediately on new vehicles.</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
         <x:v>0</x:v>
@@ -12935,21 +15923,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="12" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A12" s="40" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="9" t="str">
-        <x:v>audi-q8-e-tron-brake-pedal-to-booster-pushrod-screw-joint-detachment</x:v>
+        <x:v>audi-rs3-dsg-transmission-2015</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
-        <x:v>2023-2024 | Audi | Q8 e-tron</x:v>
+        <x:v>2023-2023 | Audi | RS3</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>2023-2024 Audi Q8 e-tron Brake-Pedal Recall 46P7 / NHTSA 26V240</x:v>
+        <x:v>2023 RS3 TCM Software Emissions Recall 37P3 - VIN Check Required</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. Dealers inspect and tighten the brake-booster pushrod screw joint as necessary at no charge. If the brake pedal makes an unusual noise, fails to return or feels abnormal, do not continue driving; contact Audi for recovery and follow the owner’s manual emergency-braking instructions.</x:v>
+        <x:v>Ask an Audi dealer to check whether Emissions Recall 37P3 is currently open for the VIN in Elsa. When open, the dealer updates the transmission-control-module software under the campaign; the published remedy requires no parts. Diagnose and repair the underlying fault separately before expecting its stored entry or MIL to clear. Do not buy a mechatronic unit, clutch pack, filter or upgraded DQ500 part for this software campaign.</x:v>
       </x:c>
       <x:c r="F12" s="9" t="n">
         <x:v>0</x:v>
@@ -12958,21 +15946,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="594" hidden="0" customHeight="1">
+    <x:row r="13" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A13" s="40" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="9" t="str">
-        <x:v>audi-q8-e-tron-dc-fast-charging-handshake-timeout-failure-to-initiate-sessi</x:v>
+        <x:v>audi-rs3-hpfp-2017</x:v>
       </x:c>
       <x:c r="C13" s="9" t="str">
-        <x:v>2023-2024 | Audi | Q8 e-tron</x:v>
+        <x:v>2017-2023 | Audi | RS3</x:v>
       </x:c>
       <x:c r="D13" s="9" t="str">
-        <x:v>2023-2024 Audi Q8 e-tron Plug &amp; Charge TSB 2071345/1</x:v>
+        <x:v>2017-2020 / 2022-2023 RS3 Drive-System Warning or No-Start Diagnosis - TSB 2067757/3</x:v>
       </x:c>
       <x:c r="E13" s="9" t="str">
-        <x:v>Confirm that the failure repeats at the same station, AC charging works and U15AF00 symptom 2097297 is present. Temporarily disable Plug &amp; Charge in the MMI or use another compatible charging station. Do not replace vehicle charging hardware solely from this symptom; follow current Audi guidance if the failure also occurs with Plug &amp; Charge disabled or at multiple stations.</x:v>
+        <x:v>Reproduce and document the complaint, scan the vehicle with current ODIS and complete Guided Fault Finding. When one of the listed DTC/symptom combinations is stored but GFF produces no result, manually add and complete the G265 intermediate-shaft-speed-sensor test plan. Repair only the component identified by that diagnosis. Do not replace or upgrade the high-pressure fuel pump from this warning or DTC set alone.</x:v>
       </x:c>
       <x:c r="F13" s="9" t="n">
         <x:v>0</x:v>
@@ -12981,21 +15969,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="488.3999938964844" hidden="0" customHeight="1">
+    <x:row r="14" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A14" s="40" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="9" t="str">
-        <x:v>audi-q8-e-tron-front-passenger-occupant-detection-system-deactivates-airbag</x:v>
+        <x:v>audi-rs3-magnetic-ride-2017</x:v>
       </x:c>
       <x:c r="C14" s="9" t="str">
-        <x:v>2024-2024 | Audi | Q8 e-tron</x:v>
+        <x:v>2015-2019 | Audi | RS3</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
-        <x:v>2024 Audi Q8 e-tron Passenger-Airbag Recall 69GU / NHTSA 24V251</x:v>
+        <x:v>2015-2018 / Certain 2019 RS3 Magnetic-Ride Rear Shock Noise - TSB 2059240/1</x:v>
       </x:c>
       <x:c r="E14" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. The free remedy replaces the passenger-seat occupant-detection control module. If the passenger-airbag warning or AIRBAG OFF indicator behaves unexpectedly, avoid using that seat until Audi inspects it. Do not buy an ODS module from this summary.</x:v>
+        <x:v>Confirm magnetic-ride equipment, the exact model-year/VIN boundary and that the noise originates at the rear shock absorbers. When every bulletin criterion matches, replace both rear shock absorbers according to Audi workshop instructions and order the correct units by VIN. Do not replace dampers or convert the suspension from visible residue, ride feel or noise alone without this diagnosis.</x:v>
       </x:c>
       <x:c r="F14" s="9" t="n">
         <x:v>0</x:v>
@@ -13004,21 +15992,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="15" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A15" s="40" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="9" t="str">
-        <x:v>audi-q8-e-tron-over-torqued-brake-pressure-line-failure-fluid-leak</x:v>
+        <x:v>audi-rs3-ttrs-carbon-buildup-2015</x:v>
       </x:c>
       <x:c r="C15" s="9" t="str">
-        <x:v>2024-2024 | Audi | Q8 e-tron</x:v>
+        <x:v>2015-2023 | Audi | RS3 | 2.5T EA855</x:v>
       </x:c>
       <x:c r="D15" s="9" t="str">
-        <x:v>2024 Audi Q8 e-tron Brake-Line Recall 47DE / NHTSA 24V428</x:v>
+        <x:v>Severe Carbon Buildup on Intake Valves (2.5T 5-Cylinder)</x:v>
       </x:c>
       <x:c r="E15" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. Dealers inspect and replace the brake-pressure line when necessary at no charge. If the brake warning appears, pedal travel increases or fluid is visible, stop driving and arrange recovery.</x:v>
+        <x:v>WALNUT BLASTING: Remove intake manifold and blast walnut shells through intake ports ($800-$1,500). Repeat every 30,000-40,000 miles—MORE frequent than base models due to high performance. PREVENTION: Install catch can ($400-$700) to filter PCV vapors. Add Liqui Moly Intake Valve Cleaner to every oil change. Change oil every 5,000 miles. Drive car hard regularly—Audi's own recommendation to burn off carbon.</x:v>
       </x:c>
       <x:c r="F15" s="9" t="n">
         <x:v>0</x:v>
@@ -13027,21 +16015,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="16" ht="792" hidden="0" customHeight="1">
       <x:c r="A16" s="40" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="9" t="str">
-        <x:v>audi-q8-e-tron-panoramic-glass-roof-water-leak-into-cabin</x:v>
+        <x:v>audi-rs3-ttrs-injector-failure-2015</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
-        <x:v>2023-2024 | Audi | Q8 e-tron | Q8 e-tron (panoramic roof equipped), Q8 Sportback e-tron</x:v>
+        <x:v>2015-2023 | Audi | RS3 | EA855</x:v>
       </x:c>
       <x:c r="D16" s="9" t="str">
-        <x:v>Panoramic Glass Roof Water Leak into Cabin (TSB MC-10182485-0001)</x:v>
+        <x:v>Fuel Injector Failure and "Torch Effect" (2.5T)</x:v>
       </x:c>
       <x:c r="E16" s="9" t="str">
-        <x:v>Have the dealer diagnose per the panoramic roof TSB. Repair depends on the root cause: clear or re-route clogged/pinched drain tubes, correct a pinched-shut rear drain, or replace/reseal the cracked plastic water channel. Dry out and inspect saturated carpet/underlay to prevent mold and electrical corrosion. Audi performs the repair reactively (only after water ingress is confirmed); some owners report the factory fix failing and needing a second visit.</x:v>
+        <x:v>PREVENTIVE REPLACEMENT: Replace all fuel injectors every 60,000 km (37,000 miles) with OEM Audi injectors ($1,500-$2,500 installed). If engine misfires or runs rough: Inspect injectors IMMEDIATELY—do NOT continue driving. Failed injector can destroy engine in minutes. If piston is melted: Engine replacement required ($15,000-$25,000). Consider extended warranty or aftermarket warranty for out-of-warranty RS3/TT RS. This is the most serious reliability issue with the 2.5T engine.</x:v>
       </x:c>
       <x:c r="F16" s="9" t="n">
         <x:v>0</x:v>
@@ -13050,21 +16038,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="17" ht="937.2000122070312" hidden="0" customHeight="1">
       <x:c r="A17" s="40" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="9" t="str">
-        <x:v>audi-q8-e-tron-premature-brake-pad-rotor-wear-brake-vibration-pulsation</x:v>
+        <x:v>audi-rs4-b7-carbon-buildup-2007</x:v>
       </x:c>
       <x:c r="C17" s="9" t="str">
-        <x:v>2023-2024 | Audi | Q8 e-tron | Q8 e-tron, Q8 Sportback e-tron, SQ8 e-tron</x:v>
+        <x:v>2007-2008 | Audi | RS4 | 4.2L FSI V8</x:v>
       </x:c>
       <x:c r="D17" s="9" t="str">
-        <x:v>Premature Brake Pad/Rotor Wear and Brake Vibration/Pulsation</x:v>
+        <x:v>2007-2008 RS4 Deposit-Related Cold-Start Misfire - Diagnose Before Cleaning</x:v>
       </x:c>
       <x:c r="E17" s="9" t="str">
-        <x:v>Have a dealer or independent measure rotor runout/thickness variation and machine or replace rotors with correct torque and bedding-in. Verify pad hardware and caliper slides. Using a stronger regenerative-braking setting reduces friction-brake duty and corrosion. If vibration returns shortly after a full brake job, escalate for a deeper inspection of hubs/wheel bearings and calibration.</x:v>
+        <x:v>Have the cold-start event and stored faults diagnosed before authorizing intake cleaning. The B7 RS4 bulletin first checks whether its fuel-additive and follow-up procedure resolves injector-deposit misfires. Current TSB 2014753/13 warns that gasoline additive can clean FSI injectors and combustion chambers but not FSI intake valves. If the misfire remains, the shop should continue guided diagnosis and confirm inlet-valve deposits before using the applicable mechanical-cleaning procedure. Do not buy a scanner, oil bundle or cleaning service solely from this card.</x:v>
       </x:c>
       <x:c r="F17" s="9" t="n">
         <x:v>0</x:v>
@@ -13073,21 +16061,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="303.6000061035156" hidden="0" customHeight="1">
+    <x:row r="18" ht="963.5999755859375" hidden="0" customHeight="1">
       <x:c r="A18" s="40" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="9" t="str">
-        <x:v>audi-q8-e-tron-rearview-camera-image-fails-is-delayed-when-shifting-to-reve</x:v>
+        <x:v>audi-rs4-rs5-carbon-buildup-2018</x:v>
       </x:c>
       <x:c r="C18" s="9" t="str">
-        <x:v>2023-2024 | Audi | Q8 e-tron</x:v>
+        <x:v>2018-2023 | Audi | RS4 | 2.9T</x:v>
       </x:c>
       <x:c r="D18" s="9" t="str">
-        <x:v>2023-2024 Audi Q8 e-tron Camera Recall 90TV / NHTSA 25V900</x:v>
+        <x:v>2018-2023 RS4 2.9T Cold-Start Misfire from Confirmed Inlet Deposits</x:v>
       </x:c>
       <x:c r="E18" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history with Audi or NHTSA. Dealers update the software at no charge. Until completed, use mirrors and direct observation with extra care while reversing.</x:v>
+        <x:v>Confirm the cold-start complaint, review the engine-control-unit event memory and verify inlet-port or inlet-valve deposits before cleaning. When that condition is confirmed, Audi TSB 2075530/1 directs the shop to remove the intake manifold or compressor and clean the inlet valves and ports by walnut blasting; the cylinder head remains installed. The cited Audi guidance does not support a mandatory 60,000-mile interval, a fixed price, dual catch cans, additive at every oil change, a 5,000-mile oil interval or a drive-hard prescription. Do not buy a catch can or cleaning product solely from this card.</x:v>
       </x:c>
       <x:c r="F18" s="9" t="n">
         <x:v>0</x:v>
@@ -13096,21 +16084,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="19" ht="1227.5999755859375" hidden="0" customHeight="1">
       <x:c r="A19" s="40" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="9" t="str">
-        <x:v>audi-q8-e-tron-severe-cold-weather-range-loss-reduced-dc-charge-speed</x:v>
+        <x:v>audi-rs5-b8-carbon-buildup-2013</x:v>
       </x:c>
       <x:c r="C19" s="9" t="str">
-        <x:v>2023-2024 | Audi | Q8 e-tron | Q8 e-tron, Q8 Sportback e-tron, SQ8 e-tron</x:v>
+        <x:v>2013-2015 | Audi | RS5 | 4.2L V8</x:v>
       </x:c>
       <x:c r="D19" s="9" t="str">
-        <x:v>Severe Cold-Weather Range Loss and Reduced DC Charge Speed (Cold Battery)</x:v>
+        <x:v>4.2L V8 Carbon Buildup and High-Rev Issues</x:v>
       </x:c>
       <x:c r="E19" s="9" t="str">
-        <x:v>Use route-based battery preconditioning: enter the DC fast charger as a navigation destination so the car warms the pack en route, restoring charge speed. Precondition the cabin while still plugged in at home, use seat/steering heaters over cabin heat, and rely on Level 2 home charging (40-60A) to absorb seasonal losses overnight. No repair is needed unless range/charge limits persist in mild weather, which warrants a dealer battery-health check.</x:v>
+        <x:v>Confirm carbon buildup by scanning for misfire/fuel-trim faults, reviewing live data, and inspecting the intake valves with a borescope after removing the intake manifold. The proper repair is an intake-valve carbon cleaning service—typically walnut-shell blasting or manual chemical cleaning—while replacing the intake manifold gaskets, injector seals/O-rings, and PCV-related breather components if leaking or contributing to oil vapor. After reassembly, clear adaptations, perform a throttle-body/basic setting relearn, and road test to verify restored high-RPM pull and smooth idle. Independent shops typically charge about $800-$1,500 for a carbon clean on the 4.2 FSI V8, while dealer pricing can run roughly $1,500-$2,500 depending on how many seals and ancillary parts are replaced.</x:v>
       </x:c>
       <x:c r="F19" s="9" t="n">
         <x:v>0</x:v>
@@ -13119,21 +16107,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="660" hidden="0" customHeight="1">
+    <x:row r="20" ht="1122" hidden="0" customHeight="1">
       <x:c r="A20" s="40" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="9" t="str">
-        <x:v>audi-q8-ea839-3-0t-water-pump-internal-leak-coolant-loss</x:v>
+        <x:v>audi-rs5-carbon-buildup-2018</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>2019-2024 | Audi | Q8 | V6 TFSI</x:v>
+        <x:v>2018-2026 | Audi | RS5</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>2019-2024 Q8 V6 Coolant-Pump Leak Diagnosis - TSB 2070349/4</x:v>
+        <x:v>Direct Injection Carbon Buildup on Intake Valves</x:v>
       </x:c>
       <x:c r="E20" s="9" t="str">
-        <x:v>Have the suspected area cleaned and dried, fill the cooling system correctly, inspect at idle and up to about 2,500 rpm, and pressure-test it per Audi repair information. If no leak returns, continue to observe without replacing parts. Replace only the component proven to leak and inspect the vacuum path and N649 when P0299 is present. Do not order a pump from this card without confirmation.</x:v>
+        <x:v>Confirm intake-valve carbon buildup by scanning for misfire faults, reviewing fuel trims, and inspecting the intake valves with a borescope through the intake ports after removing the intake manifold. The proper repair is an intake-valve cleaning service, typically walnut-shell blasting each intake port with the valves closed, then replacing the intake manifold gaskets and any disturbed PCV or breather seals before clearing adaptations and road-testing. If misfires persist, inspect and replace worn spark plugs or ignition coils as needed, since heavy deposits can foul plugs and mimic ignition faults. Typical cost is about $800-$1,500 depending on labor rates and how much disassembly is required.</x:v>
       </x:c>
       <x:c r="F20" s="9" t="n">
         <x:v>0</x:v>
@@ -13142,21 +16130,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="382.79998779296875" hidden="0" customHeight="1">
+    <x:row r="21" ht="1003.2000122070312" hidden="0" customHeight="1">
       <x:c r="A21" s="40" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="9" t="str">
-        <x:v>audi-q8-etron-12v-battery-drain-2023</x:v>
+        <x:v>audi-rs5-turbo-coolant-2018</x:v>
       </x:c>
       <x:c r="C21" s="9" t="str">
-        <x:v>2023-2025 | Audi | Q8 e-tron</x:v>
+        <x:v>2021-2024 | Audi | RS5 | 2.9L V6 TFSI</x:v>
       </x:c>
       <x:c r="D21" s="9" t="str">
-        <x:v>12V Auxiliary Battery Excessive Drain</x:v>
+        <x:v>2021-2024 RS5 V6 Coolant-Pump Leak Diagnosis - TSB 2070349/4</x:v>
       </x:c>
       <x:c r="E21" s="9" t="str">
-        <x:v>Update vehicle software to latest version via dealer. If drain persists, have dealer perform parasitic draw test to identify module staying awake. 12V battery replacement with AGM type may be needed if battery was deeply discharged.</x:v>
+        <x:v>Locate the leak before replacing parts. Clean and dry the area, fill the cooling system to maximum, inspect at idle and at engine speeds up to about 2,500 rpm, and perform the Workshop Manual cooling-system leak test. If no further leak is detected, continue observation without replacing parts. If a leak recurs, replace only the component or components causing the leak and document the finding with clear photos or video; a pump-leak repair also requires a photo of the pump production date. Inspect the vacuum circuit and N649 when contamination or P0299 is present, following current Audi workshop and parts information.</x:v>
       </x:c>
       <x:c r="F21" s="9" t="n">
         <x:v>0</x:v>
@@ -13165,21 +16153,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="501.6000061035156" hidden="0" customHeight="1">
+    <x:row r="22" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A22" s="40" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="9" t="str">
-        <x:v>audi-q8-etron-12v-battery-drain-2024</x:v>
+        <x:v>audi-rs6-air-suspension-2020</x:v>
       </x:c>
       <x:c r="C22" s="9" t="str">
-        <x:v>2024-2026 | Audi | Q8 e-tron | Premium, Premium Plus, Prestige, Sportback Premium, Sportback Premium Plus, Sportback Prestige | Electric</x:v>
+        <x:v>2021-2024 | Audi | RS6</x:v>
       </x:c>
       <x:c r="D22" s="9" t="str">
-        <x:v>12V Auxiliary Battery Parasitic Drain</x:v>
+        <x:v>2021-2024 RS6 Air-Suspension Warning - Check C1260F0 or U112100</x:v>
       </x:c>
       <x:c r="E22" s="9" t="str">
-        <x:v>Update the vehicle software to the latest version which includes revised module sleep timing. If the 12V battery has been deeply discharged multiple times, it may need replacement as lead-acid batteries are damaged by deep discharge cycles. Connect a 12V trickle charger if the vehicle will sit for more than a week.</x:v>
+        <x:v>Have the wiring and connector contacts between suspension controller J775 and compressor controller J1135 inspected first. Audi says to clear a first passive or sporadic occurrence and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after the wiring check, the bulletin directs replacement of J1135 under the applicable service procedure. Do not replace air struts, a compressor or an unverified aftermarket assembly solely from this warning card.</x:v>
       </x:c>
       <x:c r="F22" s="9" t="n">
         <x:v>0</x:v>
@@ -13188,21 +16176,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="462" hidden="0" customHeight="1">
+    <x:row r="23" ht="831.5999755859375" hidden="0" customHeight="1">
       <x:c r="A23" s="40" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="9" t="str">
-        <x:v>audi-q8-etron-charge-port-actuator-2024</x:v>
+        <x:v>audi-rs6-carbon-buildup-2020</x:v>
       </x:c>
       <x:c r="C23" s="9" t="str">
-        <x:v>2024-2026 | Audi | Q8 e-tron | Premium, Premium Plus, Prestige, Sportback Premium, Sportback Premium Plus, Sportback Prestige | Electric</x:v>
+        <x:v>2021-2024 | Audi | RS6 | 4.0T V8</x:v>
       </x:c>
       <x:c r="D23" s="9" t="str">
-        <x:v>Charge Port Door Actuator and Locking Mechanism Failure</x:v>
+        <x:v>2021-2024 RS6 4.0T Cold-Start Misfire from Confirmed Inlet Deposits</x:v>
       </x:c>
       <x:c r="E23" s="9" t="str">
-        <x:v>Replace the charge port door actuator and/or latch mechanism. In an emergency, there is a manual cable release in the cargo area to free a stuck charging cable. The actuator replacement is a straightforward repair that can be done by an independent shop if comfortable with the charge port housing.</x:v>
+        <x:v>Confirm the cold-start complaint, review the engine-control-unit event memory and verify inlet-port or inlet-valve deposits before cleaning. When that condition is confirmed, Audi TSB 2075530/1 directs the shop to remove the intake manifold or compressor and clean the inlet valves and ports by walnut blasting; the cylinder head remains installed. The cited Audi guidance does not specify a 30,000-40,000-mile interval, a fixed price or a mandatory catch can. Do not buy a catch can or cleaning product solely from this card.</x:v>
       </x:c>
       <x:c r="F23" s="9" t="n">
         <x:v>0</x:v>
@@ -13211,21 +16199,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="316.79998779296875" hidden="0" customHeight="1">
+    <x:row r="24" ht="528" hidden="0" customHeight="1">
       <x:c r="A24" s="40" t="n">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="9" t="str">
-        <x:v>audi-q8-etron-charge-port-lid-2023</x:v>
+        <x:v>audi-rs6-rs7-carbon-buildup-2013</x:v>
       </x:c>
       <x:c r="C24" s="9" t="str">
-        <x:v>2023-2025 | Audi | Q8 e-tron</x:v>
+        <x:v>2013-2023 | Audi | RS6 | 4.0T V8</x:v>
       </x:c>
       <x:c r="D24" s="9" t="str">
-        <x:v>Charge Port Door Actuator Failure</x:v>
+        <x:v>Severe Carbon Buildup on Intake Valves (4.0T V8)</x:v>
       </x:c>
       <x:c r="E24" s="9" t="str">
-        <x:v>Replace charge port door actuator assembly. Check for debris or ice in the mechanism. Software update may improve actuator control logic. Manual release is accessible from inside the cargo area.</x:v>
+        <x:v>WALNUT BLASTING: Remove both intake manifolds and blast walnut shells through all intake ports ($1,200-$2,000 for V8). Repeat every 60,000 miles. PREVENTION: Install catch can ($500-$800 for twin-turbo setup). Add Liqui Moly Intake Valve Cleaner to every oil change. Change oil every 5,000 miles. Drive car hard regularly.</x:v>
       </x:c>
       <x:c r="F24" s="9" t="n">
         <x:v>0</x:v>
@@ -13239,16 +16227,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="9" t="str">
-        <x:v>audi-q8-etron-hvac-compressor-2024</x:v>
+        <x:v>audi-rs6-rs7-motor-mounts-2013</x:v>
       </x:c>
       <x:c r="C25" s="9" t="str">
-        <x:v>2024-2024 | Audi | Q8 e-tron</x:v>
+        <x:v>2013-2023 | Audi | RS6 | 4.0T V8</x:v>
       </x:c>
       <x:c r="D25" s="9" t="str">
-        <x:v>2024 Audi Q8 e-tron A/C Compressor-Area Noise TSB 2063467/6</x:v>
+        <x:v>Premature Motor Mount Failure (4.0T V8)</x:v>
       </x:c>
       <x:c r="E25" s="9" t="str">
-        <x:v>Reproduce the exact noise with the A/C compressor active and confirm that it stops when A/C is switched off. Inspect the bulletin’s refrigerant-line contact points and hood-release cable clip and perform only the branch that matches the confirmed contact. Diagnose non-reproducible noise or loss of heating/cooling separately; do not buy a battery, maintainer or portable EVSE from this card.</x:v>
+        <x:v>Replace failed motor mounts with OEM or upgraded mounts ($800-$1,500 for all mounts). Upgraded aftermarket mounts (034 Motorsport, ECS) offer better durability for high-torque engines ($400-$600 per mount). If you drive aggressively or track the car, consider upgrading to performance mounts preventively. Monitor for vibrations and clunking—early replacement prevents driveline damage.</x:v>
       </x:c>
       <x:c r="F25" s="9" t="n">
         <x:v>0</x:v>
@@ -13257,21 +16245,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="26" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A26" s="40" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="9" t="str">
-        <x:v>audi-q8-front-brake-rotor-corrosion-premature-pad-rotor-wear</x:v>
+        <x:v>audi-rs7-air-suspension-2014</x:v>
       </x:c>
       <x:c r="C26" s="9" t="str">
-        <x:v>2019-2024 | Audi | Q8</x:v>
+        <x:v>2021-2025 | Audi | RS7</x:v>
       </x:c>
       <x:c r="D26" s="9" t="str">
-        <x:v>Front Brake Rotor Corrosion and Premature Pad/Rotor Wear</x:v>
+        <x:v>2021-2025 RS7 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
       </x:c>
       <x:c r="E26" s="9" t="str">
-        <x:v>For light surface rust, normal braking usually clears it; for noise, refinish or replace rotors and fit OEM-spec pads with proper bedding-in. Apply high-temp anti-seize/lubricant on contact points and ensure caliper slides move freely. Replace warped or deeply corroded rotors in axle sets.</x:v>
+        <x:v>Inspect the wiring and connectors between J775 and J1135 before replacing a component. For a first passive/sporadic occurrence, clear the fault and release the vehicle. If the fault is active/static after wiring and connector inspection, or the same passive/sporadic fault returns a second time, replace J1135 using current Audi repair and parts information. Audi notes that improved J1135 software remains under development.</x:v>
       </x:c>
       <x:c r="F26" s="9" t="n">
         <x:v>0</x:v>
@@ -13280,21 +16268,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="422.3999938964844" hidden="0" customHeight="1">
+    <x:row r="27" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A27" s="40" t="n">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="9" t="str">
-        <x:v>audi-q8-front-shock-absorber-fork-cracking</x:v>
+        <x:v>audi-rs7-carbon-buildup-2014</x:v>
       </x:c>
       <x:c r="C27" s="9" t="str">
-        <x:v>2019-2019 | Audi | Q8</x:v>
+        <x:v>2014-2026 | Audi | RS7 | 4.0T</x:v>
       </x:c>
       <x:c r="D27" s="9" t="str">
-        <x:v>2019 Q8 Front Shock-Absorber Fork Recall 40O4 (19V114) - Check VIN</x:v>
+        <x:v>4.0T Carbon Deposit Accumulation</x:v>
       </x:c>
       <x:c r="E27" s="9" t="str">
-        <x:v>Check the VIN for open recall 40O4 with Audi or NHTSA and contact an authorized Audi dealer. The dealer replaces the affected front shock-absorber fork free of charge. Do not buy a fork from this card or assume a generic suspension noise proves the recall condition.</x:v>
+        <x:v>Walnut blast every 30,000-40,000 miles. Install dual catch can setup for both turbo sides.</x:v>
       </x:c>
       <x:c r="F27" s="9" t="n">
         <x:v>0</x:v>
@@ -13303,21 +16291,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="422.3999938964844" hidden="0" customHeight="1">
+    <x:row r="28" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A28" s="40" t="n">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="9" t="str">
-        <x:v>audi-q8-fuel-pump-internal-failure-causing-engine-stall</x:v>
+        <x:v>audi-rs7-turbo-coolant-2014</x:v>
       </x:c>
       <x:c r="C28" s="9" t="str">
-        <x:v>2019-2021 | Audi | Q8 | V6</x:v>
+        <x:v>2014-2026 | Audi | RS7 | 4.0T</x:v>
       </x:c>
       <x:c r="D28" s="9" t="str">
-        <x:v>2019-2021 Q8 V6 Fuel-Delivery-Module Recall 20DR (22V516)</x:v>
+        <x:v>4.0T Twin-Turbo Coolant System Degradation</x:v>
       </x:c>
       <x:c r="E28" s="9" t="str">
-        <x:v>Check the VIN for open recall 20DR and contact an authorized Audi dealer. The recall remedy replaces the fuel-delivery module with the improved version. Do not purchase the old or improved module from this card or attempt an in-tank repair based only on the model year.</x:v>
+        <x:v>Replace turbo coolant lines proactively at 50,000 miles. Upgrade to silicone lines where possible.</x:v>
       </x:c>
       <x:c r="F28" s="9" t="n">
         <x:v>0</x:v>
@@ -13326,21 +16314,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="356.3999938964844" hidden="0" customHeight="1">
+    <x:row r="29" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A29" s="40" t="n">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="9" t="str">
-        <x:v>audi-q8-mmi-electrical-2019</x:v>
+        <x:v>audi-rs7-turbo-wastegate-2014</x:v>
       </x:c>
       <x:c r="C29" s="9" t="str">
-        <x:v>2019-2023 | Audi | Q8</x:v>
+        <x:v>2014-2017 | Audi | RS7 | 4.0L TFSI twin-turbo V8</x:v>
       </x:c>
       <x:c r="D29" s="9" t="str">
-        <x:v>MMI Infotainment and Electrical Issues</x:v>
+        <x:v>2014-2017 RS7 Turbocharger Oil-Strainer Safety Recall 21H7 / 22V178 - Check VIN</x:v>
       </x:c>
       <x:c r="E29" s="9" t="str">
-        <x:v>MMI hard reset (hold power + volume up 10 seconds). If persistent, dealer software update ($150-$300). For severe cases: MMI replacement ($2,000-$3,500). Most covered under 4-year/50k warranty.</x:v>
+        <x:v>Check the VIN for open Audi campaign 21H7 in Elsa or the NHTSA recall lookup. The authorized dealer replaces the turbocharger oil strainer, changes the engine oil and filter, and performs the campaign scan-tool turbo/boost-system check at no charge. Follow the campaign procedure for any damage found; do not buy a turbocharger, actuator or gasket kit from this card.</x:v>
       </x:c>
       <x:c r="F29" s="9" t="n">
         <x:v>0</x:v>
@@ -13349,21 +16337,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="488.3999938964844" hidden="0" customHeight="1">
+    <x:row r="30" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A30" s="40" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="9" t="str">
-        <x:v>audi-q8-mmi-infotainment-2019</x:v>
+        <x:v>audi-rsq8-4.0t-coolant-2020</x:v>
       </x:c>
       <x:c r="C30" s="9" t="str">
-        <x:v>2019-2026 | Audi | Q8</x:v>
+        <x:v>2020-2021 | Audi | RS Q8 | 4.0T V8</x:v>
       </x:c>
       <x:c r="D30" s="9" t="str">
-        <x:v>2019-2026 Q8 Rearview-Camera Software Recall 90TV (25V900)</x:v>
+        <x:v>2020-Early 2021 RS Q8 Red Coolant Warning - Check G407 per TSB 2062951/4</x:v>
       </x:c>
       <x:c r="E30" s="9" t="str">
-        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers install more robust driver-assistance software free of charge. Until repaired, use extra caution when reversing. A hard reset, scan tool, relay, multimeter or temporary image recovery is not completion of the recall.</x:v>
+        <x:v>Have the vehicle checked with Audi Guided Fault Finding and inspect G407 and its O-ring. Replace G407 only if the O-ring is damaged or pinched and the diagnosis matches the bulletin; follow the related Audi diagnostic path if additional listed faults are stored. Do not replace turbo coolant hoses, pumps or other cooling parts from this card alone.</x:v>
       </x:c>
       <x:c r="F30" s="9" t="n">
         <x:v>0</x:v>
@@ -13372,21 +16360,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="382.79998779296875" hidden="0" customHeight="1">
+    <x:row r="31" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A31" s="40" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="9" t="str">
-        <x:v>audi-q8-oil-separator-pcv-valve-failure-elevated-oil-consumption</x:v>
+        <x:v>audi-rsq8-air-suspension-2020</x:v>
       </x:c>
       <x:c r="C31" s="9" t="str">
-        <x:v>2019-2023 | Audi | Q8 | 3.0L V6 TFSI (EA839)</x:v>
+        <x:v>2020-2026 | Audi | RS Q8</x:v>
       </x:c>
       <x:c r="D31" s="9" t="str">
-        <x:v>Oil Separator / PCV Valve Failure and Elevated Oil Consumption (3.0T)</x:v>
+        <x:v>Adaptive Air Suspension Failure Under SUV Weight</x:v>
       </x:c>
       <x:c r="E31" s="9" t="str">
-        <x:v>Replace the cracked oil separator / PCV valve assembly with the updated part, inspect the intake and spark plugs for oil fouling, and reseal the intake manifold. Monitor oil level between services; perform a consumption test if usage exceeds Audi's threshold.</x:v>
+        <x:v>Replace air struts as they fail. Budget for compressor replacement. Consider heavy-duty aftermarket options designed for the RS Q8 weight.</x:v>
       </x:c>
       <x:c r="F31" s="9" t="n">
         <x:v>0</x:v>
@@ -13395,22 +16383,20 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="607.2000122070312" hidden="0" customHeight="1">
+    <x:row r="32" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A32" s="40" t="n">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="9" t="str">
-        <x:v>audi-q8-panoramic-sunroof-water-leak-into-cabin</x:v>
+        <x:v>audi-rsq8-air-suspension-leak-2020</x:v>
       </x:c>
       <x:c r="C32" s="9" t="str">
-        <x:v>2019-2021 | Audi | Q8</x:v>
+        <x:v>2020-2026 | Audi | RS Q8</x:v>
       </x:c>
       <x:c r="D32" s="9" t="str">
-        <x:v>2019-2021 Q8 Water Entry from Sunroof Area - TSB 2056944/10</x:v>
-      </x:c>
-      <x:c r="E32" s="9" t="str">
-        <x:v>Have all four bulletin branches inspected and water-flow tested. Clear a drain obstruction or replace a damaged hose or valve, replace a damaged opening seal, correct glass adjustment, and perform the specified wind-deflector and channel modifications when applicable. Replace the sunroof frame only when actual structural damage is found. Do not order a frame from this card.</x:v>
-      </x:c>
+        <x:v>Adaptive Air Suspension Air Spring Leaks</x:v>
+      </x:c>
+      <x:c r="E32" s="9" t="str"/>
       <x:c r="F32" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -13418,21 +16404,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="752.4000244140625" hidden="0" customHeight="1">
+    <x:row r="33" ht="607.2000122070312" hidden="0" customHeight="1">
       <x:c r="A33" s="40" t="n">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="9" t="str">
-        <x:v>audi-r8-5-2-v10-excessive-oil-consumption</x:v>
+        <x:v>audi-rsq8-brake-wear-2020</x:v>
       </x:c>
       <x:c r="C33" s="9" t="str">
-        <x:v>2009-2023 | Audi | R8 | 5.2L V10 FSI</x:v>
+        <x:v>2020-2021 | Audi | RS Q8</x:v>
       </x:c>
       <x:c r="D33" s="9" t="str">
-        <x:v>5.2 V10 Excessive Oil Consumption</x:v>
+        <x:v>2020-2021 RS Q8 Front Steel-Brake Squeal - TSB 2062052/1</x:v>
       </x:c>
       <x:c r="E33" s="9" t="str">
-        <x:v>Establish a documented consumption baseline (measured quarts over measured miles) and inspect the plugs/exhaust for oil fouling. Use a manufacturer-approved oil of the correct viscosity (owners report fewer issues with a quality 502/505-approved synthetic); some go to a heavier grade only with caution. Truly excessive consumption with smoke requires teardown for rings/valve seals, an engine-out job. Keep the oil topped between changes to protect the engine.</x:v>
+        <x:v>Confirm the frequency and operating conditions and inspect the discs for corrosion, grooves or glazing. When the bulletin applies, Audi directs replacement of the front pad set using current parts information followed by the specified bedding procedure. Do not perform ABS stops for bedding, and do not replace rotors or buy aftermarket pads solely from the prior wear narrative.</x:v>
       </x:c>
       <x:c r="F33" s="9" t="n">
         <x:v>0</x:v>
@@ -13441,21 +16427,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="726" hidden="0" customHeight="1">
+    <x:row r="34" ht="897.5999755859375" hidden="0" customHeight="1">
       <x:c r="A34" s="40" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="9" t="str">
-        <x:v>audi-r8-5-2-v10-oil-pump-driveshaft-seal-timing-case-oil-leak</x:v>
+        <x:v>audi-s3-carbon-buildup-2015</x:v>
       </x:c>
       <x:c r="C34" s="9" t="str">
-        <x:v>2009-2023 | Audi | R8 | R8 V10, R8 V10 Plus, R8 V10 Performance, R8 V10 Spyder | 5.2L V10 FSI</x:v>
+        <x:v>2015-2019 | Audi | S3 | S3 | EA888 Gen 3</x:v>
       </x:c>
       <x:c r="D34" s="9" t="str">
-        <x:v>5.2 V10 Oil Pump Driveshaft Seal Timing-Case Oil Leak</x:v>
+        <x:v>Carbon Buildup on Intake Valves (Pre-Dual Injection EA888 Gen 3)</x:v>
       </x:c>
       <x:c r="E34" s="9" t="str">
-        <x:v>Confirm the source (timing-case oil-pump driveshaft seal, not valve covers or oil cooler). Repair involves removing the oil pump and renewing the oil-pump drive-shaft seal and associated O-rings/gaskets; a full reseal kit (e.g. RKX/Steso) is commonly used. It is mostly a labor and gasket/seal job rather than replacing the pump, though the pump can be replaced if worn. Fresh oil and coolant and a proper fill/bleed are required because both systems are opened.</x:v>
+        <x:v>WALNUT BLASTING: Remove intake manifold and blast intake valve ports with crushed walnut shells ($500-$1,000). Repeat every 40,000-60,000 miles. CATCH CAN: Install an oil catch can ($200-$400) to capture PCV vapors before they reach intake valves—significantly slows carbon buildup. OIL CHANGES: Use high-quality synthetic oil and change every 5,000 miles. DRIVING HABITS: Regular spirited driving helps burn off some deposits. NOTE: 2020+ S3 models with EA888 Gen 3B dual injection are largely immune to this issue.</x:v>
       </x:c>
       <x:c r="F34" s="9" t="n">
         <x:v>0</x:v>
@@ -13464,44 +16450,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="1042.800048828125" hidden="0" customHeight="1">
+    <x:row r="35" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A35" s="40" t="n">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="9" t="str">
-        <x:v>audi-r8-ac-compressor-v8-2008</x:v>
+        <x:v>audi-s3-dq250-mechatronic-2015</x:v>
       </x:c>
       <x:c r="C35" s="9" t="str">
-        <x:v>2008-2012 | Audi | R8 | 4.2 | 4.2 V8</x:v>
+        <x:v>2015-2024 | Audi | S3</x:v>
       </x:c>
       <x:c r="D35" s="9" t="str">
-        <x:v>A/C Compressor Failure Requiring Engine-Out Repair (4.2 V8)</x:v>
+        <x:v>DQ250 DSG Mechatronic Unit Failure</x:v>
       </x:c>
       <x:c r="E35" s="9" t="str">
-        <x:v>A/C COMPRESSOR REPLACEMENT: Requires ENGINE REMOVAL on the V8 model. Total repair cost $5,000-$8,000 ($1,000-$1,500 for parts, $4,000-$6,500 for labor). When the engine is out, strongly recommended to also address: motor mounts, clutch inspection, and any other components that benefit from engine-out access. ALTERNATIVE: Some specialty R8 shops have developed methods to access the compressor with partial disassembly (removing subframe) rather than full engine removal, potentially reducing labor to $3,000-$4,000. PREVENTION: Run the A/C regularly (even in winter for 5-10 minutes monthly) to keep compressor seals lubricated.</x:v>
+        <x:v>Replace or rebuild mechatronic unit. Regular DSG fluid changes every 40,000 miles help prevent premature failure.</x:v>
       </x:c>
       <x:c r="F35" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G35" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="976.7999877929688" hidden="0" customHeight="1">
+    <x:row r="36" ht="897.5999755859375" hidden="0" customHeight="1">
       <x:c r="A36" s="40" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="9" t="str">
-        <x:v>audi-r8-carbon-buildup-2008</x:v>
+        <x:v>audi-s3-dsg-mechatronic-2015</x:v>
       </x:c>
       <x:c r="C36" s="9" t="str">
-        <x:v>2008-2015 | Audi | R8 | 4.2, 5.2 | 4.2 FSI V8, 5.2 FSI V10</x:v>
+        <x:v>2015-2024 | Audi | S3 | S3</x:v>
       </x:c>
       <x:c r="D36" s="9" t="str">
-        <x:v>Carbon Buildup on Intake Valves (4.2 V8 FSI and 5.2 V10 FSI)</x:v>
+        <x:v>DQ381 S-Tronic Mechatronic Unit Failure</x:v>
       </x:c>
       <x:c r="E36" s="9" t="str">
-        <x:v>WALNUT BLASTING: Remove intake manifolds and blast all intake ports with walnut shells. V8 (4.2L): $800-$1,200. V10 (5.2L): $1,200-$2,000 due to 10 cylinders. Perform a leak-down test BEFORE walnut blasting to ensure intake valves seat properly. Repeat every 50,000-70,000 miles. CHEMICAL CLEANING: Less effective than walnut blasting but some owners use intake valve cleaners (BG Products, CRC) as interim maintenance. DRIVING HABITS: Regular high-RPM driving (the R8's natural habitat) helps slow carbon accumulation. PREVENTION: Use quality fuel (91+ octane) and change oil every 5,000 miles.</x:v>
+        <x:v>EARLY SYMPTOMS (jerky shifts): DSG fluid and filter service ($500-$700) plus dealer software update. This may resolve early-stage issues. MECHATRONIC FAILURE: Replace mechatronic unit ($2,000-$4,000 installed) plus TCU coding. Remanufactured units available for $1,500-$2,500. CLUTCH PACK FAILURE: Replace dual clutch pack ($3,000-$5,000). PREVENTION: Service DSG fluid every 40,000 miles—ignore Audi's 'lifetime fill' claim. Use ONLY OEM Audi DSG fluid (G 052 182 A2) or approved Pentosin FFL-2. Avoid aggressive launches and excessive clutch slip in traffic.</x:v>
       </x:c>
       <x:c r="F36" s="9" t="n">
         <x:v>0</x:v>
@@ -13510,21 +16496,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="37" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A37" s="40" t="n">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="9" t="str">
-        <x:v>audi-r8-carbon-fiber-sideblade-trim-clear-coat-peeling</x:v>
+        <x:v>audi-s3-ea888-carbon-2015</x:v>
       </x:c>
       <x:c r="C37" s="9" t="str">
-        <x:v>2008-2015 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+        <x:v>2015-2024 | Audi | S3 | EA888</x:v>
       </x:c>
       <x:c r="D37" s="9" t="str">
-        <x:v>Carbon Fiber Sideblade and Trim Clear-Coat Peeling</x:v>
+        <x:v>EA888 Carbon Buildup on Intake Valves</x:v>
       </x:c>
       <x:c r="E37" s="9" t="str">
-        <x:v>Refinish the affected panel: carefully sand back the failed lacquer without cutting into the carbon weave, then re-clear with a UV-stabilized automotive clear coat (best done by a shop experienced with carbon). To prevent recurrence, protect the finish with paint-protection film (clear wrap) or a ceramic coating, which also guards against stone chips.</x:v>
+        <x:v>Walnut blast intake valves every 40,000-60,000 miles or install a catch can to reduce buildup rate.</x:v>
       </x:c>
       <x:c r="F37" s="9" t="n">
         <x:v>0</x:v>
@@ -13533,21 +16519,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="38" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A38" s="40" t="n">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="9" t="str">
-        <x:v>audi-r8-catalytic-converter-failure-requiring-engine-out-replacement</x:v>
+        <x:v>audi-s3-hpfp-2015</x:v>
       </x:c>
       <x:c r="C38" s="9" t="str">
-        <x:v>2008-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+        <x:v>2015-2024 | Audi | S3 | EA888</x:v>
       </x:c>
       <x:c r="D38" s="9" t="str">
-        <x:v>Catalytic Converter Failure Requiring Engine-Out Replacement</x:v>
+        <x:v>High-Pressure Fuel Pump (HPFP) Failure</x:v>
       </x:c>
       <x:c r="E38" s="9" t="str">
-        <x:v>Confirm the failed bank with O2/catalyst-efficiency data and a back-pressure check before condemning. OEM repair means replacing the catalytic-converter-with-integrated-manifold assembly (engine-out labor); many owners opt for high-flow aftermarket or de-catted manifolds where legal. Verify no upstream misfire/oil-consumption issue is destroying the new cats.</x:v>
+        <x:v>Replace HPFP with updated revision. Check cam follower for wear during replacement.</x:v>
       </x:c>
       <x:c r="F38" s="9" t="n">
         <x:v>0</x:v>
@@ -13556,21 +16542,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="422.3999938964844" hidden="0" customHeight="1">
+    <x:row r="39" ht="1122" hidden="0" customHeight="1">
       <x:c r="A39" s="40" t="n">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="9" t="str">
-        <x:v>audi-r8-clutch-pack-2008</x:v>
+        <x:v>audi-s3-turbo-wastegate-rattle-2015</x:v>
       </x:c>
       <x:c r="C39" s="9" t="str">
-        <x:v>2021-2022 | Audi | R8</x:v>
+        <x:v>2015-2020 | Audi | S3 | S3</x:v>
       </x:c>
       <x:c r="D39" s="9" t="str">
-        <x:v>Gearbox Underfilled: Clutch Slippage or Transmission-Oil Leak (Recall 22V225 / 37O1)</x:v>
+        <x:v>IS20 Turbocharger Wastegate Rattle and Actuator Failure</x:v>
       </x:c>
       <x:c r="E39" s="9" t="str">
-        <x:v>Check the VIN and campaign history with Audi or NHTSA. Under campaign 37O1, an Audi dealer inspects and corrects the transmission-oil level free of charge. If drive power drops, a clutch slips, or oil/smoke is noticed, stop safely and arrange dealer inspection.</x:v>
+        <x:v>EARLY STAGE (rattle only, no power loss): Audi TSB 2027585/3 prescribes installation of a metal retaining clip (part 06J145220A) to tighten wastegate arm play ($200-$400 if under warranty, $500-$800 out of pocket). UPGRADED DIVERTER VALVE: Replace with revision 'D' diverter valve to improve boost control. SEVERE (actuator failure or power loss): Replace complete IS20 turbocharger ($2,500-$4,000 installed). The IS20 actuator is integrated and not serviceable separately. Upgraded IS38 turbo swap ($3,500-$5,000) from Golf R is a popular option if replacing turbo anyway. PREVENTION: Avoid short trips that don't fully heat the turbo. Change oil every 5,000 miles with high-quality synthetic.</x:v>
       </x:c>
       <x:c r="F39" s="9" t="n">
         <x:v>0</x:v>
@@ -13579,21 +16565,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="1042.800048828125" hidden="0" customHeight="1">
+    <x:row r="40" ht="594" hidden="0" customHeight="1">
       <x:c r="A40" s="40" t="n">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="9" t="str">
-        <x:v>audi-r8-clutch-wear-2008</x:v>
+        <x:v>audi-s3-water-pump-thermostat-2015</x:v>
       </x:c>
       <x:c r="C40" s="9" t="str">
-        <x:v>2008-2015 | Audi | R8 | 4.2, 5.2</x:v>
+        <x:v>2020-2024 | Audi | S3 | 2.0L TFSI</x:v>
       </x:c>
       <x:c r="D40" s="9" t="str">
-        <x:v>R-Tronic Clutch Premature Wear and Expensive Replacement</x:v>
+        <x:v>2020/2022-2024 Audi S3 2.0 TFSI Coolant-Pump Leak Diagnosis</x:v>
       </x:c>
       <x:c r="E40" s="9" t="str">
-        <x:v>CLUTCH REPLACEMENT: Replace clutch disc, pressure plate, throwout bearing, and resurface/replace flywheel ($5,500-$9,000 at dealer, $4,000-$6,000 at independent specialist). The mid-engine layout requires dropping the transmission—8-12 hours of labor. DRIVING TECHNIQUE: Minimize R-Tronic slip by avoiding creeping in traffic (use brake hold instead). Use manual mode in stop-and-go traffic. Avoid reverse on steep inclines. For TRACK USE: Budget for clutch replacement every 10,000-20,000 miles—R-Tronic track driving is hard on clutches. ALTERNATIVE: S-Tronic (Gen 2 R8) wet dual-clutch is significantly more durable for daily driving.</x:v>
+        <x:v>Document the suspected leak, clean and dry all traces, fill the cooling system to the correct level and reassess after driving a few miles. If no fresh leak appears, continue observing without replacing parts. If leakage recurs, replace only the component causing the damage under the exact VIN, engine and part criteria. Outside applicable warranty, Audi states the bulletin is informational.</x:v>
       </x:c>
       <x:c r="F40" s="9" t="n">
         <x:v>0</x:v>
@@ -13602,21 +16588,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="41" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A41" s="40" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="9" t="str">
-        <x:v>audi-r8-coolant-expansion-tank-cracking-cooling-system-leaks</x:v>
+        <x:v>audi-s4-b5-timing-chain-2000</x:v>
       </x:c>
       <x:c r="C41" s="9" t="str">
-        <x:v>2008-2015 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+        <x:v>2000-2002 | Audi | S4</x:v>
       </x:c>
       <x:c r="D41" s="9" t="str">
-        <x:v>Coolant Expansion Tank Cracking and Cooling System Leaks</x:v>
+        <x:v>Driver Airbag Inflator May Deploy Improperly (Recall 21V470 / 69CJ)</x:v>
       </x:c>
       <x:c r="E41" s="9" t="str">
-        <x:v>Pressure-test the cooling system to pinpoint the leak. Replace the cracked expansion/overflow tank with the updated design and renew brittle hose clamps/connections; inspect the radiator and cap. Refill with the correct Audi G13/G12 coolant specification and bleed the system fully. Address any weeping hose fittings at the same time.</x:v>
+        <x:v>Check the VIN with Audi or NHTSA. Audi dealers replace the driver frontal-airbag inflator with an alternative inflator free of charge under campaign 69CJ.</x:v>
       </x:c>
       <x:c r="F41" s="9" t="n">
         <x:v>0</x:v>
@@ -13625,21 +16611,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="42" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A42" s="40" t="n">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="9" t="str">
-        <x:v>audi-r8-direct-injection-fuel-injector-failure</x:v>
+        <x:v>audi-s4-b5-turbo-failure-2000</x:v>
       </x:c>
       <x:c r="C42" s="9" t="str">
-        <x:v>2008-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+        <x:v>2003-2004 | Audi | S4</x:v>
       </x:c>
       <x:c r="D42" s="9" t="str">
-        <x:v>Direct-Injection Fuel Injector Failure</x:v>
+        <x:v>Xenon Headlamp Reflector Coating Can Reduce Light Output (Recall 05V096)</x:v>
       </x:c>
       <x:c r="E42" s="9" t="str">
-        <x:v>Confirm the failing cylinder with misfire and fuel-trim data and, where possible, injector-specific fault codes rather than replacing coils blindly. Replace the failed injector(s) with OEM FSI units; many owners replace as a bank or full set given shared age and mileage, and clean or address intake-valve carbon at the same service. Expect roughly $2,900 for a multi-injector job including labor per owner reports.</x:v>
+        <x:v>Verify VIN eligibility and campaign completion with Audi. Dealers replace both xenon headlamp reflectors free of charge under recall 05V096.</x:v>
       </x:c>
       <x:c r="F42" s="9" t="n">
         <x:v>0</x:v>
@@ -13648,21 +16634,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="528" hidden="0" customHeight="1">
+    <x:row r="43" ht="303.6000061035156" hidden="0" customHeight="1">
       <x:c r="A43" s="40" t="n">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="9" t="str">
-        <x:v>audi-r8-front-axle-hydraulic-lift-system-pump-failure</x:v>
+        <x:v>audi-s4-b6-timing-chain-2004</x:v>
       </x:c>
       <x:c r="C43" s="9" t="str">
-        <x:v>2017-2023 | Audi | R8 | 5.2L V10 FSI</x:v>
+        <x:v>2005-2009 | Audi | S4</x:v>
       </x:c>
       <x:c r="D43" s="9" t="str">
-        <x:v>Front Axle Hydraulic Lift System Pump Failure</x:v>
+        <x:v>Passenger Airbag Inflator Can Rupture (Recall 18V427 / 69R7)</x:v>
       </x:c>
       <x:c r="E43" s="9" t="str">
-        <x:v>Diagnose the lift pump/hydraulic circuit; a failed pump is the usual culprit. A new dealer pump assembly runs over $3,000, so many owners fit a good used OEM pump or an independent rebuild as a cost-effective alternative. Until repaired, approach inclines and speed bumps at an angle and very slowly to avoid front-end damage.</x:v>
+        <x:v>Check VIN eligibility because body style and original registration history affect scope. Audi dealers replace the passenger frontal-airbag remedy part free of charge under campaign 69R7.</x:v>
       </x:c>
       <x:c r="F43" s="9" t="n">
         <x:v>0</x:v>
@@ -13671,21 +16657,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="316.79998779296875" hidden="0" customHeight="1">
+    <x:row r="44" ht="356.3999938964844" hidden="0" customHeight="1">
       <x:c r="A44" s="40" t="n">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="9" t="str">
-        <x:v>audi-r8-front-passenger-airbag-inflator-rupture</x:v>
+        <x:v>audi-s4-carbon-buildup-2010</x:v>
       </x:c>
       <x:c r="C44" s="9" t="str">
-        <x:v>2016-2016 | Audi | R8</x:v>
+        <x:v>2011-2012 | Audi | S4 | 3.0 TFSI</x:v>
       </x:c>
       <x:c r="D44" s="9" t="str">
-        <x:v>Front-Passenger Airbag Module May Explode or Deploy Improperly (Recall 22V543 / 69DY)</x:v>
+        <x:v>Fuel Rail or Seal Leak Creates Fire Risk (Recall 15V019 / 24AP)</x:v>
       </x:c>
       <x:c r="E44" s="9" t="str">
-        <x:v>Check the VIN with Audi or NHTSA. Audi dealers replace the front-passenger airbag module free of charge under campaign 69DY/61C1. Do not source a used airbag module from this summary.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel rails and corresponding seals free of charge under campaign 24AP. If fuel odor or leakage is present, stop driving and arrange immediate inspection.</x:v>
       </x:c>
       <x:c r="F44" s="9" t="n">
         <x:v>0</x:v>
@@ -13694,21 +16680,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="45" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A45" s="40" t="n">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="9" t="str">
-        <x:v>audi-r8-fuel-supply-line-chafing-heat-shield</x:v>
+        <x:v>audi-s4-supercharger-nose-2010</x:v>
       </x:c>
       <x:c r="C45" s="9" t="str">
-        <x:v>2011-2012 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+        <x:v>2013-2015 | Audi | S4</x:v>
       </x:c>
       <x:c r="D45" s="9" t="str">
-        <x:v>R8 Spyder Fuel Supply Line Can Chafe on Heat Shield (Recall 11V390 / 20Q8)</x:v>
+        <x:v>Airbag-Control Software May Miss Front-Airbag Deployment After a Second Impact (Recall 14V667 / 69K5)</x:v>
       </x:c>
       <x:c r="E45" s="9" t="str">
-        <x:v>Check the VIN and recall status. Audi dealers inspect the line, replace it if damaged, and adjust the fuel line and heat shield for proper clearance free of charge. If fuel odor or leakage is present, stop driving and arrange immediate inspection.</x:v>
+        <x:v>Check VIN eligibility and completion history. Audi dealers update the airbag control-unit software free of charge under campaign 69K5.</x:v>
       </x:c>
       <x:c r="F45" s="9" t="n">
         <x:v>0</x:v>
@@ -13717,21 +16703,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="792" hidden="0" customHeight="1">
+    <x:row r="46" ht="198" hidden="0" customHeight="1">
       <x:c r="A46" s="40" t="n">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="9" t="str">
-        <x:v>audi-r8-ignition-coil-pack-failure-causing-misfires</x:v>
+        <x:v>audi-s4-thermostat-2010</x:v>
       </x:c>
       <x:c r="C46" s="9" t="str">
-        <x:v>2008-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+        <x:v>2010-2025 | Audi | S4 | 3.0T</x:v>
       </x:c>
       <x:c r="D46" s="9" t="str">
-        <x:v>Ignition Coil Pack Failure Causing Misfires</x:v>
+        <x:v>Thermostat Housing Failure and Coolant Leak</x:v>
       </x:c>
       <x:c r="E46" s="9" t="str">
-        <x:v>Diagnose the misfiring cylinder(s) via the stored misfire counters, then replace the failed coil(s) along with spark plugs; most specialists replace the full set of 8 (V8) or 10 (V10) plus plugs to avoid repeat visits. The canonical 4.2 V8 coil is the revision-'T' red coil, Audi/VW PN 077905115T (superseded family, aftermarket cross-reference 06E905115E). The Gen-2 5.2 V10 uses Audi PN 07L905115B. Address any valve-cover or plug-tube oil leak at the same time so new coils are not contaminated.</x:v>
+        <x:v>Replace thermostat housing assembly with updated part. Use OEM or quality aftermarket housing with metal reinforcement.</x:v>
       </x:c>
       <x:c r="F46" s="9" t="n">
         <x:v>1</x:v>
@@ -13740,21 +16726,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="47" ht="963.5999755859375" hidden="0" customHeight="1">
       <x:c r="A47" s="40" t="n">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="9" t="str">
-        <x:v>audi-r8-led-headlight-drl-module-failure-flickering</x:v>
+        <x:v>audi-s5-b9-water-pump-2018</x:v>
       </x:c>
       <x:c r="C47" s="9" t="str">
-        <x:v>2014-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+        <x:v>2018-2018 | Audi | S5 | 3.0L V6 TFSI EA839</x:v>
       </x:c>
       <x:c r="D47" s="9" t="str">
-        <x:v>LED Headlight / DRL Module Failure and Flickering</x:v>
+        <x:v>2018 S5 3.0L Mechanical Coolant-Pump Fault P000000/33688 - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E47" s="9" t="str">
-        <x:v>Inspect the headlight for moisture and corroded connectors; a failed LED driver module usually requires replacing the headlight assembly (used units run roughly £1,600-1,800, new from Audi around £2,800), followed by headlight aiming/auto-leveling calibration with a diagnostic tool. Reseal or replace cracked housings to stop repeat water damage. Some independent specialists can repair the driver board at lower cost.</x:v>
+        <x:v>Follow the bulletin in order. Verify coolant level; if low, inspect the cooling system for a leak and repair only the identified source or top up per Audi instructions when no leak is found. Check the ECM software level and apply the specified SVM update only when required. If the concern returns or software is current, test vacuum at N649 and inspect the solenoid and hoses. If the vacuum system works, apply vacuum to the pump hose and verify that the pump sleeve clicks; replace the mechanical coolant pump only when the sleeve does not operate. Use current Audi workshop and parts information.</x:v>
       </x:c>
       <x:c r="F47" s="9" t="n">
         <x:v>0</x:v>
@@ -13763,21 +16749,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="264" hidden="0" customHeight="1">
+    <x:row r="48" ht="184.8000030517578" hidden="0" customHeight="1">
       <x:c r="A48" s="40" t="n">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="9" t="str">
-        <x:v>audi-r8-magnetic-ride-2008</x:v>
+        <x:v>audi-s5-carbon-buildup-2008</x:v>
       </x:c>
       <x:c r="C48" s="9" t="str">
-        <x:v>2008-2024 | Audi | R8</x:v>
+        <x:v>2008-2025 | Audi | S5</x:v>
       </x:c>
       <x:c r="D48" s="9" t="str">
-        <x:v>Magnetic Ride Damper Fluid Leaks</x:v>
+        <x:v>Direct Injection Carbon Buildup</x:v>
       </x:c>
       <x:c r="E48" s="9" t="str">
-        <x:v>Replace magnetic ride dampers. OEM replacements are very expensive. KW or Bilstein aftermarket coilovers are popular track-oriented alternatives.</x:v>
+        <x:v>Walnut blast intake valves every 40,000-60,000 miles. Install oil catch can to reduce oil vapor reaching valves.</x:v>
       </x:c>
       <x:c r="F48" s="9" t="n">
         <x:v>0</x:v>
@@ -13786,44 +16772,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="1227.5999755859375" hidden="0" customHeight="1">
+    <x:row r="49" ht="937.2000122070312" hidden="0" customHeight="1">
       <x:c r="A49" s="40" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" s="9" t="str">
-        <x:v>audi-r8-magnetic-ride-leak-2008</x:v>
+        <x:v>audi-s5-crankshaft-pulley-2010</x:v>
       </x:c>
       <x:c r="C49" s="9" t="str">
-        <x:v>2008-2015 | Audi | R8 | 4.2, 5.2</x:v>
+        <x:v>2010-2017 | Audi | S5 | Premium Plus, Prestige | 3.0T</x:v>
       </x:c>
       <x:c r="D49" s="9" t="str">
-        <x:v>Magnetic Ride Suspension Damper Leak and Premature Failure</x:v>
+        <x:v>Crankshaft Pulley (Harmonic Balancer) Failure (3.0T)</x:v>
       </x:c>
       <x:c r="E49" s="9" t="str">
-        <x:v>OEM REPLACEMENT: Replace leaking magnetic ride shocks ($1,800 each, $5,100-$8,000+ for full set installed). OEM replacements use the same technology and will eventually fail again. REFURBISHED OPTION: Refurbished magnetic ride dampers from specialty rebuilders (approximately $1,000-$1,400 each). PASSIVE CONVERSION: Convert to R8 Plus passive shocks ($3,000-$4,000 for set—less than 2 OEM magnetic ride shocks) or aftermarket coilovers ($2,500-$5,000 for quality kit like KW, JRZ, or Ohlins). Passive conversion eliminates the failure mode permanently but removes adaptive ride control. PREVENTION: Limited—magnetic fluid degradation is inherent to the technology. Budget for replacement every 30,000-50,000 miles if keeping magnetic ride.</x:v>
+        <x:v>Replace crankshaft pulley/harmonic balancer with LATEST REVISION (revision F or later) part ($300-$600 for part, $800-$1,700 with labor). This is NOT a DIY-friendly repair—requires specialized holding tools and precise torque. If belts are damaged, replace serpentine belt and tensioner ($200-$400 additional). INSPECT: Check for collateral damage to supercharger snout, idler pulleys, and timing. If timing was affected, expect $3,000-$5,000 additional repair. PREVENTIVE: Inspect pulley for wobble at every oil change. Consider preemptive replacement at 80,000 miles on 2010-2013 models.</x:v>
       </x:c>
       <x:c r="F49" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G49" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="1003.2000122070312" hidden="0" customHeight="1">
+    <x:row r="50" ht="844.7999877929688" hidden="0" customHeight="1">
       <x:c r="A50" s="40" t="n">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B50" s="9" t="str">
-        <x:v>audi-r8-r-tronic-hydraulic-pump-pressure-accumulator-failure</x:v>
+        <x:v>audi-s5-pcv-valve-failure-2010</x:v>
       </x:c>
       <x:c r="C50" s="9" t="str">
-        <x:v>2008-2015 | Audi | R8 | R8 4.2 R tronic, R8 V10 R tronic, R8 V10 Plus R tronic | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+        <x:v>2010-2017 | Audi | S5 | 3.0L supercharged V6</x:v>
       </x:c>
       <x:c r="D50" s="9" t="str">
-        <x:v>R tronic Hydraulic Pump and Pressure Accumulator Failure</x:v>
+        <x:v>2010-2017 S5 3.0L Crankcase-Breather P052E00 - Body/Year Diagnosis</x:v>
       </x:c>
       <x:c r="E50" s="9" t="str">
-        <x:v>Diagnose with a scan tool: a failing accumulator/pump typically stores P17BF (hydraulic pump play protection) and/or P0944 (loss of hydraulic pressure). Standard repair order is to renew the relatively inexpensive pressure accumulator first; if pressure loss persists, replace the hydraulic pump (and its relay/fuse), and only then suspect the hydraulic clutch/gear actuator or the solenoid-valve O-rings. Fresh, correct-spec hydraulic fluid and a proper bleed with a diagnostic tool are required. Owners are advised not to drive the car (except directly to a shop) once the pump is heard running continuously or shifting becomes intermittent.</x:v>
+        <x:v>Verify the body style, model year and P052E00 condition first. For the applicable membrane branch, use the specified hand-vacuum test, then inspect the membrane and metal plates after compressor/intake-manifold removal; replace only the faulted membrane/plate repair kit or crankcase breather per current Audi instructions. If testing identifies the elbow branch, replace the elbow and hose clip as directed by TSB 2060259/1. Do not assume that both branches or unrelated cooling parts require replacement.</x:v>
       </x:c>
       <x:c r="F50" s="9" t="n">
         <x:v>0</x:v>
@@ -13832,21 +16818,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="198" hidden="0" customHeight="1">
+    <x:row r="51" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A51" s="40" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B51" s="9" t="str">
-        <x:v>audi-r8-s-tronic-actuator-2008</x:v>
+        <x:v>audi-s5-supercharger-2008</x:v>
       </x:c>
       <x:c r="C51" s="9" t="str">
-        <x:v>2008-2024 | Audi | R8</x:v>
+        <x:v>2008-2025 | Audi | S5 | 3.0T</x:v>
       </x:c>
       <x:c r="D51" s="9" t="str">
-        <x:v>S-tronic Transmission Actuator Failure</x:v>
+        <x:v>3.0T Supercharger Intercooler Pump Failure</x:v>
       </x:c>
       <x:c r="E51" s="9" t="str">
-        <x:v>Replace S-tronic actuators. Full transmission service with correct S-tronic fluid is critical. Dealer or specialist only repair.</x:v>
+        <x:v>Replace intercooler coolant pump. Check intercooler lines for leaks and flush the circuit during replacement.</x:v>
       </x:c>
       <x:c r="F51" s="9" t="n">
         <x:v>0</x:v>
@@ -13855,21 +16841,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="330" hidden="0" customHeight="1">
+    <x:row r="52" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A52" s="40" t="n">
         <x:v>51</x:v>
       </x:c>
       <x:c r="B52" s="9" t="str">
-        <x:v>audi-r8-s-tronic-gearbox-ventilation-hose-transmission-fluid-leak</x:v>
+        <x:v>audi-s5-thermostat-2008</x:v>
       </x:c>
       <x:c r="C52" s="9" t="str">
-        <x:v>2017-2018 | Audi | R8 | 5.2L V10 FSI</x:v>
+        <x:v>2008-2025 | Audi | S5 | 3.0T</x:v>
       </x:c>
       <x:c r="D52" s="9" t="str">
-        <x:v>Gearbox Ventilation Hose Can Leak Fluid Near Hot Engine Parts (Recall 18V639 / 34J1)</x:v>
+        <x:v>Thermostat and Water Pump Assembly Failure</x:v>
       </x:c>
       <x:c r="E52" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the single gearbox ventilation hose with the higher-volume double hose free of charge under campaign 34J1. Stop driving if hot-oil odor or smoke appears.</x:v>
+        <x:v>Replace thermostat/water pump assembly. Upgrade to revised housing if available.</x:v>
       </x:c>
       <x:c r="F52" s="9" t="n">
         <x:v>0</x:v>
@@ -13878,21 +16864,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="53" ht="818.4000244140625" hidden="0" customHeight="1">
       <x:c r="A53" s="40" t="n">
         <x:v>52</x:v>
       </x:c>
       <x:c r="B53" s="9" t="str">
-        <x:v>audi-r8-spyder-convertible-top-hydraulic-pump-failure</x:v>
+        <x:v>audi-s6-air-suspension-2013</x:v>
       </x:c>
       <x:c r="C53" s="9" t="str">
-        <x:v>2011-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+        <x:v>2013-2013 | Audi | S6 | 4.0T</x:v>
       </x:c>
       <x:c r="D53" s="9" t="str">
-        <x:v>Spyder Convertible Top Hydraulic Pump Failure</x:v>
+        <x:v>2013 Audi S6 Air-Suspension Compressor or Relay Fault - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E53" s="9" t="str">
-        <x:v>Scan for the specific fault (pump vs. sensor vs. latch) before parting; a mis-reading position sensor can mimic a dead pump. Replace the hydraulic pump/motor assembly (Audi R8 Spyder convertible-top hydraulic pump PN 427871791 for 2010-2016 cars) and top up/refill the correct hydraulic fluid, or replace the failed cylinder/sensor. Leaking lines and worn seals should be renewed together. Independent hydraulic rebuild services exist as a lower-cost alternative to a full dealer pump.</x:v>
+        <x:v>Have an Audi-qualified technician test the air-suspension compressor and inspect relay J403. Audi directs replacement of both the compressor and relay when the relay has severe contact erosion or an overheated strand; when the compressor sounds normal and the relay has only minor contact marks, replace the relay only. A sagging corner or leak-down condition requires separate leak localization before any strut is replaced. Do not order the former strut or compressor recommendations from this card.</x:v>
       </x:c>
       <x:c r="F53" s="9" t="n">
         <x:v>0</x:v>
@@ -13901,21 +16887,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="1122" hidden="0" customHeight="1">
+    <x:row r="54" ht="1359.5999755859375" hidden="0" customHeight="1">
       <x:c r="A54" s="40" t="n">
         <x:v>53</x:v>
       </x:c>
       <x:c r="B54" s="9" t="str">
-        <x:v>audi-r8-v8-engine-bearing-2008</x:v>
+        <x:v>audi-s6-c7-carbon-buildup-2013</x:v>
       </x:c>
       <x:c r="C54" s="9" t="str">
-        <x:v>2008-2015 | Audi | R8 | 4.2 | 4.2 FSI</x:v>
+        <x:v>2013-2018 | Audi | S6 | 4.0T</x:v>
       </x:c>
       <x:c r="D54" s="9" t="str">
-        <x:v>Rod Bearing Wear and Engine Failure Risk (4.2 V8 FSI)</x:v>
+        <x:v>4.0T Carbon Buildup on Intake Valves</x:v>
       </x:c>
       <x:c r="E54" s="9" t="str">
-        <x:v>EARLY DETECTION (knocking noise only): Rod bearing replacement ($2,000-$5,000). Must be caught EARLY before bearing material migrates through oil system. Cut open every oil filter at oil change to inspect for metallic debris. CATASTROPHIC FAILURE: Engine replacement ($13,000+ Audi exchange, $8,000-$15,000 rebuilt from AMTuned or specialist rebuilder). ARP 2000 reinforced connecting rod bolts are available as a preventive upgrade during any engine-out service. PREVENTION: Use ONLY premium 5W-40 synthetic oil. Change oil every 5,000 miles maximum. NEVER exceed oil change intervals—the high-revving V8 is extremely sensitive to oil condition. For track use, change oil after every 2-3 track days.</x:v>
+        <x:v>Confirm carbon buildup by scanning for misfire faults (commonly random/multiple or cylinder-specific misfires), reviewing fuel trims, and inspecting the intake valves with a borescope after removing the intake manifold or accessing the ports. The proper repair is an intake valve carbon cleaning, typically walnut shell blasting each intake port with the valves closed, then replacing intake manifold gaskets, injector seals/O-rings or any disturbed PCV-related seals as needed and clearing/adapting the ECU afterward. If buildup is severe or returns quickly, inspect the PCV/oil separator system and crankcase ventilation hoses for excessive oil carryover. Independent shops typically charge about $800-$1,500 for a full walnut blast service on the 4.0T, while dealer pricing can run roughly $1,500-$2,500 depending on labor and gasket/seal replacement.</x:v>
       </x:c>
       <x:c r="F54" s="9" t="n">
         <x:v>0</x:v>
@@ -13924,21 +16910,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="924" hidden="0" customHeight="1">
+    <x:row r="55" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A55" s="40" t="n">
         <x:v>54</x:v>
       </x:c>
       <x:c r="B55" s="9" t="str">
-        <x:v>audi-rs-etron-gt-battery-short-2022</x:v>
+        <x:v>audi-s6-carbon-buildup-2013</x:v>
       </x:c>
       <x:c r="C55" s="9" t="str">
-        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
+        <x:v>2013-2024 | Audi | S6 | 4.0T</x:v>
       </x:c>
       <x:c r="D55" s="9" t="str">
-        <x:v>2022-2024 RS e-tron GT High-Voltage Battery Recall 931A/931B (24V726)</x:v>
+        <x:v>4.0T Direct Injection Carbon Buildup</x:v>
       </x:c>
       <x:c r="E55" s="9" t="str">
-        <x:v>Check the VIN for open Audi campaign 931A or 931B and complete the authorized dealer remedy. Under 931A, enrolled vehicles can be monitored through online battery data; Audi contacts owners if a module appears critical. Under 931B, the dealer performs diagnostic procedures until the final monitoring software is installed. Audi installs the onboard diagnostic software and replaces affected battery modules at no cost when anomalies are identified. Follow any vehicle- or dealer-specific 80-percent charging instruction; the filing does not direct every 931A vehicle to use that limit.</x:v>
+        <x:v>Walnut blast all eight intake runners. Dual-injection models (2019+) are less affected.</x:v>
       </x:c>
       <x:c r="F55" s="9" t="n">
         <x:v>0</x:v>
@@ -13947,21 +16933,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="56" ht="462" hidden="0" customHeight="1">
       <x:c r="A56" s="40" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="B56" s="9" t="str">
-        <x:v>audi-rs-etron-gt-brake-hose-2022</x:v>
+        <x:v>audi-s6-rearview-camera-image-failure-from-software-error</x:v>
       </x:c>
       <x:c r="C56" s="9" t="str">
-        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
+        <x:v>2020-2025 | Audi | S6</x:v>
       </x:c>
       <x:c r="D56" s="9" t="str">
-        <x:v>2022-2024 RS e-tron GT Front Brake-Hose Recall 47UP (24V465)</x:v>
+        <x:v>2020-2025 Audi S6 Rearview Camera Software Recall 25V900 / 90TV</x:v>
       </x:c>
       <x:c r="E56" s="9" t="str">
-        <x:v>Check the VIN for an open 47UP action and have an authorized Audi dealer replace both front brake hoses and holders free of charge. If pedal travel increases or the vehicle displays a warning related to reduced brake fluid, contact an Audi dealer for diagnosis without delay. Do not buy a single hose or substitute generic brake lines from the prior links; the campaign controls the complete criteria-specific repair.</x:v>
+        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install the more robust driver-assistance software update free of charge. Until repaired, use extra caution when reversing and do not treat a restart or temporary image recovery as completion of the recall.</x:v>
       </x:c>
       <x:c r="F56" s="9" t="n">
         <x:v>0</x:v>
@@ -13970,21 +16956,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="726" hidden="0" customHeight="1">
+    <x:row r="57" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A57" s="40" t="n">
         <x:v>56</x:v>
       </x:c>
       <x:c r="B57" s="9" t="str">
-        <x:v>audi-rs-etron-gt-charging-port-2022</x:v>
+        <x:v>audi-s6-takata-passenger-airbag-inflator-recall</x:v>
       </x:c>
       <x:c r="C57" s="9" t="str">
-        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
+        <x:v>2007-2011 | Audi | S6</x:v>
       </x:c>
       <x:c r="D57" s="9" t="str">
-        <x:v>2022-2024 RS e-tron GT Red Charging LED or Fast-Charging Abort - Audi 91VT</x:v>
+        <x:v>2007-2011 Audi S6 Takata Passenger-Airbag Recall 18V427 / 69R7</x:v>
       </x:c>
       <x:c r="E57" s="9" t="str">
-        <x:v>Have an Audi dealer check the VIN and assigned 91VT criterion in the campaign/action system. For the charging-related criteria, the authorized remedy updates the high-voltage battery control-module software, with the convenience-system control module also updated where the assigned criterion requires it. Diagnose charging failures outside that exact campaign branch rather than replacing the charging socket or module from symptoms alone.</x:v>
+        <x:v>Check the VIN for recall 18V427/69R7 and arrange the free final passenger-frontal-airbag replacement with an Audi dealer. Do not use an airbag warning light to determine recall eligibility; Audi states that the warning light is unrelated to this inflator defect.</x:v>
       </x:c>
       <x:c r="F57" s="9" t="n">
         <x:v>0</x:v>
@@ -13993,22 +16979,20 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="58" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A58" s="40" t="n">
         <x:v>57</x:v>
       </x:c>
       <x:c r="B58" s="9" t="str">
-        <x:v>audi-rs-etron-gt-software-2022</x:v>
+        <x:v>audi-s6-transmission-valve-body-2002</x:v>
       </x:c>
       <x:c r="C58" s="9" t="str">
-        <x:v>2022-2022 | Audi | RS e-tron GT</x:v>
+        <x:v>2002-2004 | Audi | S6</x:v>
       </x:c>
       <x:c r="D58" s="9" t="str">
-        <x:v>2022 RS e-tron GT Audi connect Inoperative after 91DZ - TSB 2068824/2</x:v>
-      </x:c>
-      <x:c r="E58" s="9" t="str">
-        <x:v>Confirm that the failure began after 91DZ and matches the Audi connect/SOS-LED condition. An Audi technician should use ODIS Guided Fault Finding and run SVM Check Module Configuration for diagnostic address 0019, J533. Manual coding is no longer required. Escalate a continuing Audi connect failure through Audi support after the guided coding procedure rather than buying hardware or a retail software service.</x:v>
-      </x:c>
+        <x:v>ZF 5HP24 Tiptronic Transmission Valve Body Failure</x:v>
+      </x:c>
+      <x:c r="E58" s="9" t="str"/>
       <x:c r="F58" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -14016,21 +17000,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="59" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A59" s="40" t="n">
         <x:v>58</x:v>
       </x:c>
       <x:c r="B59" s="9" t="str">
-        <x:v>audi-rs-etron-gt-tire-wear-2022</x:v>
+        <x:v>audi-s6-turbo-coolant-2013</x:v>
       </x:c>
       <x:c r="C59" s="9" t="str">
-        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
+        <x:v>2013-2013 | Audi | S6 | 4.0T</x:v>
       </x:c>
       <x:c r="D59" s="9" t="str">
-        <x:v>Accelerated Tire Wear and Alignment Sensitivity</x:v>
+        <x:v>2013 Audi S6 Turbocharger Coolant-Pipe Seepage - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E59" s="9" t="str">
-        <x:v>Rotate front-to-back every 3,000-5,000 miles (only possible if sizes permit, which staggered setups often do not). Check alignment every 5,000 miles or after any pothole impact - even 0.1 degree of toe deviation causes rapid edge wear on these wide tires. Consider switching to Michelin Pilot Sport 4S or Pirelli P Zero PZ4 for improved tread life over the OE Continental SportContact 6. Budget $1,400-$2,000 for a set of four replacement tires. Aggressive driving with launch control dramatically reduces tire life. For better longevity, use Comfort mode instead of Dynamic for daily driving.</x:v>
+        <x:v>Confirm the leak source and VIN applicability before ordering parts. For the TSB condition, Audi specifies replacing the coolant feed and return pipes on both cylinder banks, replacing the disturbed oil-feed-pipe O-rings, then refilling and bleeding the cooling system. Service Action 21F7 was VIN-specific and expired in 2019, so current coverage must not be assumed. Do not order the former single pipe or alleged silicone-line kit from this card.</x:v>
       </x:c>
       <x:c r="F59" s="9" t="n">
         <x:v>0</x:v>
@@ -14039,21 +17023,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="60" ht="290.3999938964844" hidden="0" customHeight="1">
       <x:c r="A60" s="40" t="n">
         <x:v>59</x:v>
       </x:c>
       <x:c r="B60" s="9" t="str">
-        <x:v>audi-rs-q8-air-suspension-2020</x:v>
+        <x:v>audi-s7-air-suspension-2012</x:v>
       </x:c>
       <x:c r="C60" s="9" t="str">
-        <x:v>2020-2025 | Audi | RS Q8</x:v>
+        <x:v>2020-2021 | Audi | S7</x:v>
       </x:c>
       <x:c r="D60" s="9" t="str">
-        <x:v>2020-2025 RS Q8 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
+        <x:v>Rear-Axle Lock Nut and Alignment Recall Follow-Up (21V295 / 22V034)</x:v>
       </x:c>
       <x:c r="E60" s="9" t="str">
-        <x:v>Inspect the wiring and connector contacts between J775 and J1135 before replacing a component. For a first passive or sporadic occurrence, clear the fault and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after wiring inspection, Audi directs replacement of J1135 under current repair and parts information. Do not buy struts, springs, a compressor or a conversion kit solely from this warning.</x:v>
+        <x:v>Check the VIN for both campaigns 42L1 and 42L5. Audi dealers replace affected nuts and bolts, inspect and adjust rear alignment, and replace qualifying unevenly worn tires free of charge.</x:v>
       </x:c>
       <x:c r="F60" s="9" t="n">
         <x:v>0</x:v>
@@ -14062,21 +17046,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="184.8000030517578" hidden="0" customHeight="1">
+    <x:row r="61" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A61" s="40" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="B61" s="9" t="str">
-        <x:v>audi-rs3-carbon-buildup-2017</x:v>
+        <x:v>audi-s7-biturbo-coolant-2012</x:v>
       </x:c>
       <x:c r="C61" s="9" t="str">
-        <x:v>2017-2025 | Audi | RS3 | 2.5T</x:v>
+        <x:v>2013-2014 | Audi | S7 | 4.0 TFSI</x:v>
       </x:c>
       <x:c r="D61" s="9" t="str">
-        <x:v>2.5T Five-Cylinder Carbon Buildup</x:v>
+        <x:v>4.0L Fuel Line Can Leak and Create a Fire Risk (Recall 13V450 / 20U6)</x:v>
       </x:c>
       <x:c r="E61" s="9" t="str">
-        <x:v>Walnut blast intake valves every 30,000-40,000 miles. Install catch can immediately on new vehicles.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel line free of charge under campaign 20U6/L8. Stop driving if fuel odor or leakage is present.</x:v>
       </x:c>
       <x:c r="F61" s="9" t="n">
         <x:v>0</x:v>
@@ -14085,21 +17069,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" ht="686.4000244140625" hidden="0" customHeight="1">
+    <x:row r="62" ht="264" hidden="0" customHeight="1">
       <x:c r="A62" s="40" t="n">
         <x:v>61</x:v>
       </x:c>
       <x:c r="B62" s="9" t="str">
-        <x:v>audi-rs3-dsg-transmission-2015</x:v>
+        <x:v>audi-s7-carbon-buildup-4.0t-2012</x:v>
       </x:c>
       <x:c r="C62" s="9" t="str">
-        <x:v>2023-2023 | Audi | RS3</x:v>
+        <x:v>2021-2021 | Audi | S7</x:v>
       </x:c>
       <x:c r="D62" s="9" t="str">
-        <x:v>2023 RS3 TCM Software Emissions Recall 37P3 - VIN Check Required</x:v>
+        <x:v>Rear Seat-Belt Retractor Can Release a Child Restraint Early (Recall 21V606 / 69CS)</x:v>
       </x:c>
       <x:c r="E62" s="9" t="str">
-        <x:v>Ask an Audi dealer to check whether Emissions Recall 37P3 is currently open for the VIN in Elsa. When open, the dealer updates the transmission-control-module software under the campaign; the published remedy requires no parts. Diagnose and repair the underlying fault separately before expecting its stored entry or MIL to clear. Do not buy a mechatronic unit, clutch pack, filter or upgraded DQ500 part for this software campaign.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers inspect and replace the affected middle-rear seat-belt assembly as necessary free of charge under campaign 69CS.</x:v>
       </x:c>
       <x:c r="F62" s="9" t="n">
         <x:v>0</x:v>
@@ -14108,21 +17092,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" ht="686.4000244140625" hidden="0" customHeight="1">
+    <x:row r="63" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A63" s="40" t="n">
         <x:v>62</x:v>
       </x:c>
       <x:c r="B63" s="9" t="str">
-        <x:v>audi-rs3-hpfp-2017</x:v>
+        <x:v>audi-s7-cylinder-demand-rough-running-hesitation</x:v>
       </x:c>
       <x:c r="C63" s="9" t="str">
-        <x:v>2017-2023 | Audi | RS3</x:v>
+        <x:v>2021-2021 | Audi | S7</x:v>
       </x:c>
       <x:c r="D63" s="9" t="str">
-        <x:v>2017-2020 / 2022-2023 RS3 Drive-System Warning or No-Start Diagnosis - TSB 2067757/3</x:v>
+        <x:v>Instrument Panel May Fail to Display Critical Safety Information (Recall 25V201 / 90VC)</x:v>
       </x:c>
       <x:c r="E63" s="9" t="str">
-        <x:v>Reproduce and document the complaint, scan the vehicle with current ODIS and complete Guided Fault Finding. When one of the listed DTC/symptom combinations is stored but GFF produces no result, manually add and complete the G265 intermediate-shaft-speed-sensor test plan. Repair only the component identified by that diagnosis. Do not replace or upgrade the high-pressure fuel pump from this warning or DTC set alone.</x:v>
+        <x:v>Check the VIN and campaign-completion history. Audi dealers update the instrument-panel module software free of charge under campaign 90VC.</x:v>
       </x:c>
       <x:c r="F63" s="9" t="n">
         <x:v>0</x:v>
@@ -14131,21 +17115,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="64" ht="316.79998779296875" hidden="0" customHeight="1">
       <x:c r="A64" s="40" t="n">
         <x:v>63</x:v>
       </x:c>
       <x:c r="B64" s="9" t="str">
-        <x:v>audi-rs3-magnetic-ride-2017</x:v>
+        <x:v>audi-s7-ea839-2-9t-v6-water-pump-internal-leak-overheating</x:v>
       </x:c>
       <x:c r="C64" s="9" t="str">
-        <x:v>2015-2019 | Audi | RS3</x:v>
+        <x:v>2020-2024 | Audi | S7</x:v>
       </x:c>
       <x:c r="D64" s="9" t="str">
-        <x:v>2015-2018 / Certain 2019 RS3 Magnetic-Ride Rear Shock Noise - TSB 2059240/1</x:v>
+        <x:v>Rearview Camera Image May Not Display (Recall 25V900 / 90TV)</x:v>
       </x:c>
       <x:c r="E64" s="9" t="str">
-        <x:v>Confirm magnetic-ride equipment, the exact model-year/VIN boundary and that the noise originates at the rear shock absorbers. When every bulletin criterion matches, replace both rear shock absorbers according to Audi workshop instructions and order the correct units by VIN. Do not replace dampers or convert the suspension from visible residue, ride feel or noise alone without this diagnosis.</x:v>
+        <x:v>Check the VIN and campaign-completion history. Audi dealers update the relevant software free of charge under campaign 90TV. Continue direct visual checks when reversing until repaired.</x:v>
       </x:c>
       <x:c r="F64" s="9" t="n">
         <x:v>0</x:v>
@@ -14154,21 +17138,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="65" ht="343.20001220703125" hidden="0" customHeight="1">
       <x:c r="A65" s="40" t="n">
         <x:v>64</x:v>
       </x:c>
       <x:c r="B65" s="9" t="str">
-        <x:v>audi-rs3-ttrs-carbon-buildup-2015</x:v>
+        <x:v>audi-s7-electromechanical-steering-rack-torque-sensor-failure-causin</x:v>
       </x:c>
       <x:c r="C65" s="9" t="str">
-        <x:v>2015-2023 | Audi | RS3 | 2.5T EA855</x:v>
+        <x:v>2021-2021 | Audi | S7</x:v>
       </x:c>
       <x:c r="D65" s="9" t="str">
-        <x:v>Severe Carbon Buildup on Intake Valves (2.5T 5-Cylinder)</x:v>
+        <x:v>Incorrect Brake-Fluid Reservoir Cap Label (Recall 23V601 / 47T9)</x:v>
       </x:c>
       <x:c r="E65" s="9" t="str">
-        <x:v>WALNUT BLASTING: Remove intake manifold and blast walnut shells through intake ports ($800-$1,500). Repeat every 30,000-40,000 miles—MORE frequent than base models due to high performance. PREVENTION: Install catch can ($400-$700) to filter PCV vapors. Add Liqui Moly Intake Valve Cleaner to every oil change. Change oil every 5,000 miles. Drive car hard regularly—Audi's own recommendation to burn off carbon.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers inspect the reservoir cap and replace it when necessary free of charge under campaign 47T9. Use only the brake-fluid specification in the owner and service information.</x:v>
       </x:c>
       <x:c r="F65" s="9" t="n">
         <x:v>0</x:v>
@@ -14177,44 +17161,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" ht="792" hidden="0" customHeight="1">
+    <x:row r="66" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A66" s="40" t="n">
         <x:v>65</x:v>
       </x:c>
       <x:c r="B66" s="9" t="str">
-        <x:v>audi-rs3-ttrs-injector-failure-2015</x:v>
+        <x:v>audi-s7-front-control-arm-bushing-ball-joint-failure</x:v>
       </x:c>
       <x:c r="C66" s="9" t="str">
-        <x:v>2015-2023 | Audi | RS3 | EA855</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
       </x:c>
       <x:c r="D66" s="9" t="str">
-        <x:v>Fuel Injector Failure and "Torch Effect" (2.5T)</x:v>
+        <x:v>Front Control Arm Bushing and Ball Joint Failure (C7 Suspension)</x:v>
       </x:c>
       <x:c r="E66" s="9" t="str">
-        <x:v>PREVENTIVE REPLACEMENT: Replace all fuel injectors every 60,000 km (37,000 miles) with OEM Audi injectors ($1,500-$2,500 installed). If engine misfires or runs rough: Inspect injectors IMMEDIATELY—do NOT continue driving. Failed injector can destroy engine in minutes. If piston is melted: Engine replacement required ($15,000-$25,000). Consider extended warranty or aftermarket warranty for out-of-warranty RS3/TT RS. This is the most serious reliability issue with the 2.5T engine.</x:v>
+        <x:v>Inspect all front control arms for play in the bushings and ball joints. Replace worn arms — many owners do the full front control-arm set (commonly a 16-piece kit covering both sides) to avoid repeat visits since the labor overlaps. Critical install notes: torque the bushing bolts at ride height (not with the suspension hanging) to avoid pre-loading and destroying the new bushings, and perform a four-wheel alignment afterward.</x:v>
       </x:c>
       <x:c r="F66" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G66" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="67" ht="396" hidden="0" customHeight="1">
       <x:c r="A67" s="40" t="n">
         <x:v>66</x:v>
       </x:c>
       <x:c r="B67" s="9" t="str">
-        <x:v>audi-rs4-b7-carbon-buildup-2007</x:v>
+        <x:v>audi-s7-fuel-injector-deposits-failure-causing-misfire-rough-running</x:v>
       </x:c>
       <x:c r="C67" s="9" t="str">
-        <x:v>2007-2008 | Audi | RS4 | 4.2L FSI V8</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
       </x:c>
       <x:c r="D67" s="9" t="str">
-        <x:v>2007-2008 RS4 Deposit-Related Cold-Start Misfire - Diagnose Before Cleaning</x:v>
+        <x:v>Fuel Injector Deposits / Failure Causing Misfire and Rough Running (4.0T V8)</x:v>
       </x:c>
       <x:c r="E67" s="9" t="str">
-        <x:v>Have the cold-start event and stored faults diagnosed before authorizing intake cleaning. The B7 RS4 bulletin first checks whether its fuel-additive and follow-up procedure resolves injector-deposit misfires. Current TSB 2014753/13 warns that gasoline additive can clean FSI injectors and combustion chambers but not FSI intake valves. If the misfire remains, the shop should continue guided diagnosis and confirm inlet-valve deposits before using the applicable mechanical-cleaning procedure. Do not buy a scanner, oil bundle or cleaning service solely from this card.</x:v>
+        <x:v>Pull misfire counts per cylinder to localize the fault. Inspect/replace failed or leaking injectors and renew injector seals; replace spark plugs and any weak coils as a set. Confirm fuel trims return to normal and clear codes; address intake carbon if present.</x:v>
       </x:c>
       <x:c r="F67" s="9" t="n">
         <x:v>0</x:v>
@@ -14223,21 +17207,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" ht="963.5999755859375" hidden="0" customHeight="1">
+    <x:row r="68" ht="396" hidden="0" customHeight="1">
       <x:c r="A68" s="40" t="n">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B68" s="9" t="str">
-        <x:v>audi-rs4-rs5-carbon-buildup-2018</x:v>
+        <x:v>audi-s7-gateway-control-module-shutdown-from-rear-seat-liquid-spill</x:v>
       </x:c>
       <x:c r="C68" s="9" t="str">
-        <x:v>2018-2023 | Audi | RS4 | 2.9T</x:v>
+        <x:v>2020-2022 | Audi | S7 | 2.9 TFSI</x:v>
       </x:c>
       <x:c r="D68" s="9" t="str">
-        <x:v>2018-2023 RS4 2.9T Cold-Start Misfire from Confirmed Inlet Deposits</x:v>
+        <x:v>Rear-Seat Liquid Spill Can Shut Down Gateway Module (Recall 22V861 / 90V2)</x:v>
       </x:c>
       <x:c r="E68" s="9" t="str">
-        <x:v>Confirm the cold-start complaint, review the engine-control-unit event memory and verify inlet-port or inlet-valve deposits before cleaning. When that condition is confirmed, Audi TSB 2075530/1 directs the shop to remove the intake manifold or compressor and clean the inlet valves and ports by walnut blasting; the cylinder head remains installed. The cited Audi guidance does not support a mandatory 60,000-mile interval, a fixed price, dual catch cans, additive at every oil change, a 5,000-mile oil interval or a drive-hard prescription. Do not buy a catch can or cleaning product solely from this card.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers install a protective gateway-module cover free of charge under campaign 90V2. If multiple warnings or reduced power occur after a spill, move out of traffic safely and arrange dealer inspection.</x:v>
       </x:c>
       <x:c r="F68" s="9" t="n">
         <x:v>0</x:v>
@@ -14246,21 +17230,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" ht="1227.5999755859375" hidden="0" customHeight="1">
+    <x:row r="69" ht="528" hidden="0" customHeight="1">
       <x:c r="A69" s="40" t="n">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B69" s="9" t="str">
-        <x:v>audi-rs5-b8-carbon-buildup-2013</x:v>
+        <x:v>audi-s7-high-pressure-fuel-pump-failure-causing-hard-start-power-los</x:v>
       </x:c>
       <x:c r="C69" s="9" t="str">
-        <x:v>2013-2015 | Audi | RS5 | 4.2L V8</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
       </x:c>
       <x:c r="D69" s="9" t="str">
-        <x:v>4.2L V8 Carbon Buildup and High-Rev Issues</x:v>
+        <x:v>High-Pressure Fuel Pump (HPFP) Failure Causing Hard Start and Power Loss (4.0T V8)</x:v>
       </x:c>
       <x:c r="E69" s="9" t="str">
-        <x:v>Confirm carbon buildup by scanning for misfire/fuel-trim faults, reviewing live data, and inspecting the intake valves with a borescope after removing the intake manifold. The proper repair is an intake-valve carbon cleaning service—typically walnut-shell blasting or manual chemical cleaning—while replacing the intake manifold gaskets, injector seals/O-rings, and PCV-related breather components if leaking or contributing to oil vapor. After reassembly, clear adaptations, perform a throttle-body/basic setting relearn, and road test to verify restored high-RPM pull and smooth idle. Independent shops typically charge about $800-$1,500 for a carbon clean on the 4.2 FSI V8, while dealer pricing can run roughly $1,500-$2,500 depending on how many seals and ancillary parts are replaced.</x:v>
+        <x:v>Diagnose with live fuel-rail pressure data before condemning the pump, as a faulty low-pressure sensor or in-tank pump can set the same codes. Replace the failed high-pressure pump (the affected bank, or both as a set on high-mileage cars) together with the cam follower and seals. Verify low-pressure (in-tank) supply is within spec.</x:v>
       </x:c>
       <x:c r="F69" s="9" t="n">
         <x:v>0</x:v>
@@ -14269,44 +17253,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" ht="1122" hidden="0" customHeight="1">
+    <x:row r="70" ht="660" hidden="0" customHeight="1">
       <x:c r="A70" s="40" t="n">
         <x:v>69</x:v>
       </x:c>
       <x:c r="B70" s="9" t="str">
-        <x:v>audi-rs5-carbon-buildup-2018</x:v>
+        <x:v>audi-s7-ignition-coil-pack-failure-causing-misfires</x:v>
       </x:c>
       <x:c r="C70" s="9" t="str">
-        <x:v>2018-2026 | Audi | RS5</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
       </x:c>
       <x:c r="D70" s="9" t="str">
-        <x:v>Direct Injection Carbon Buildup on Intake Valves</x:v>
+        <x:v>Ignition Coil Pack Failure Causing Misfires (4.0T V8)</x:v>
       </x:c>
       <x:c r="E70" s="9" t="str">
-        <x:v>Confirm intake-valve carbon buildup by scanning for misfire faults, reviewing fuel trims, and inspecting the intake valves with a borescope through the intake ports after removing the intake manifold. The proper repair is an intake-valve cleaning service, typically walnut-shell blasting each intake port with the valves closed, then replacing the intake manifold gaskets and any disturbed PCV or breather seals before clearing adaptations and road-testing. If misfires persist, inspect and replace worn spark plugs or ignition coils as needed, since heavy deposits can foul plugs and mimic ignition faults. Typical cost is about $800-$1,500 depending on labor rates and how much disassembly is required.</x:v>
+        <x:v>Confirm the failing cylinder, then swap the suspect coil to another cylinder to verify the fault follows the coil. Replace the failed coil; best practice on the 4.0T is to replace all eight coils and the spark plugs as a set since the access labor is shared and mixed-age coils tend to fail in sequence. Use OE or quality OE-equivalent coils (the 4.0T uses the 079905110-series coil). Inspect spark plugs for fouling/oil that could indicate a secondary issue.</x:v>
       </x:c>
       <x:c r="F70" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G70" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="1003.2000122070312" hidden="0" customHeight="1">
+    <x:row r="71" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A71" s="40" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="B71" s="9" t="str">
-        <x:v>audi-rs5-turbo-coolant-2018</x:v>
+        <x:v>audi-s7-motor-mount-failure-2012</x:v>
       </x:c>
       <x:c r="C71" s="9" t="str">
-        <x:v>2021-2024 | Audi | RS5 | 2.9L V6 TFSI</x:v>
+        <x:v>2013-2018 | Audi | S7</x:v>
       </x:c>
       <x:c r="D71" s="9" t="str">
-        <x:v>2021-2024 RS5 V6 Coolant-Pump Leak Diagnosis - TSB 2070349/4</x:v>
+        <x:v>Passenger Occupant Detection Mat Can Disable the Airbag (Recall 18V370 / 74D5)</x:v>
       </x:c>
       <x:c r="E71" s="9" t="str">
-        <x:v>Locate the leak before replacing parts. Clean and dry the area, fill the cooling system to maximum, inspect at idle and at engine speeds up to about 2,500 rpm, and perform the Workshop Manual cooling-system leak test. If no further leak is detected, continue observation without replacing parts. If a leak recurs, replace only the component or components causing the leak and document the finding with clear photos or video; a pump-leak repair also requires a photo of the pump production date. Inspect the vacuum circuit and N649 when contamination or P0299 is present, following current Audi workshop and parts information.</x:v>
+        <x:v>Check VIN eligibility because seat equipment affects scope. Audi dealers install the occupant-detection repair kit free of charge under campaign 74D5.</x:v>
       </x:c>
       <x:c r="F71" s="9" t="n">
         <x:v>0</x:v>
@@ -14315,21 +17299,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="72" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A72" s="40" t="n">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B72" s="9" t="str">
-        <x:v>audi-rs6-air-suspension-2020</x:v>
+        <x:v>audi-s7-pcv-oil-separator-failure-causing-oil-consumption-whistling</x:v>
       </x:c>
       <x:c r="C72" s="9" t="str">
-        <x:v>2021-2024 | Audi | RS6</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
       </x:c>
       <x:c r="D72" s="9" t="str">
-        <x:v>2021-2024 RS6 Air-Suspension Warning - Check C1260F0 or U112100</x:v>
+        <x:v>PCV / Oil Separator (Ölabscheider) Failure Causing Oil Consumption and Whistling (4.0T V8)</x:v>
       </x:c>
       <x:c r="E72" s="9" t="str">
-        <x:v>Have the wiring and connector contacts between suspension controller J775 and compressor controller J1135 inspected first. Audi says to clear a first passive or sporadic occurrence and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after the wiring check, the bulletin directs replacement of J1135 under the applicable service procedure. Do not replace air struts, a compressor or an unverified aftermarket assembly solely from this warning card.</x:v>
+        <x:v>Replace the failed oil separator / PCV assembly and the associated breather hose with the latest revised part. An ECM update may accompany the new part on some VINs. Confirm with a smoke test for intake-side vacuum leaks; inspect the rear main seal if oil consumption is severe, as a failed PCV is a common cause of rear main seal damage on these engines.</x:v>
       </x:c>
       <x:c r="F72" s="9" t="n">
         <x:v>0</x:v>
@@ -14338,21 +17322,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" ht="831.5999755859375" hidden="0" customHeight="1">
+    <x:row r="73" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A73" s="40" t="n">
         <x:v>72</x:v>
       </x:c>
       <x:c r="B73" s="9" t="str">
-        <x:v>audi-rs6-carbon-buildup-2020</x:v>
+        <x:v>audi-s7-power-liftgate-motor-gas-strut-failure</x:v>
       </x:c>
       <x:c r="C73" s="9" t="str">
-        <x:v>2021-2024 | Audi | RS6 | 4.0T V8</x:v>
+        <x:v>2013-2022 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824), 2.9T TFSI Biturbo V6 (EA839)</x:v>
       </x:c>
       <x:c r="D73" s="9" t="str">
-        <x:v>2021-2024 RS6 4.0T Cold-Start Misfire from Confirmed Inlet Deposits</x:v>
+        <x:v>Power Liftgate Motor and Gas Strut Failure (Sportback Tailgate)</x:v>
       </x:c>
       <x:c r="E73" s="9" t="str">
-        <x:v>Confirm the cold-start complaint, review the engine-control-unit event memory and verify inlet-port or inlet-valve deposits before cleaning. When that condition is confirmed, Audi TSB 2075530/1 directs the shop to remove the intake manifold or compressor and clean the inlet valves and ports by walnut blasting; the cylinder head remains installed. The cited Audi guidance does not specify a 30,000-40,000-mile interval, a fixed price or a mandatory catch can. Do not buy a catch can or cleaning product solely from this card.</x:v>
+        <x:v>Diagnose whether the fault is the gas struts (won't stay up / weak lift), the spindle lift motors (slow or struggling travel), or the latch/cinching motor (won't release or won't pull closed — see TSB 2072431/1). Replace worn gas struts in pairs; replace failed lift or cinching motors as needed. After repair, perform the power-liftgate relearn/reset procedure so travel limits recalibrate.</x:v>
       </x:c>
       <x:c r="F73" s="9" t="n">
         <x:v>0</x:v>
@@ -14361,21 +17345,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="528" hidden="0" customHeight="1">
+    <x:row r="74" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A74" s="40" t="n">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B74" s="9" t="str">
-        <x:v>audi-rs6-rs7-carbon-buildup-2013</x:v>
+        <x:v>audi-s7-premature-front-brake-rotor-warping-pad-wear</x:v>
       </x:c>
       <x:c r="C74" s="9" t="str">
-        <x:v>2013-2023 | Audi | RS6 | 4.0T V8</x:v>
+        <x:v>2013-2022 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824), 2.9T TFSI Biturbo V6 (EA839)</x:v>
       </x:c>
       <x:c r="D74" s="9" t="str">
-        <x:v>Severe Carbon Buildup on Intake Valves (4.0T V8)</x:v>
+        <x:v>Premature Front Brake Rotor Warping and Pad Wear</x:v>
       </x:c>
       <x:c r="E74" s="9" t="str">
-        <x:v>WALNUT BLASTING: Remove both intake manifolds and blast walnut shells through all intake ports ($1,200-$2,000 for V8). Repeat every 60,000 miles. PREVENTION: Install catch can ($500-$800 for twin-turbo setup). Add Liqui Moly Intake Valve Cleaner to every oil change. Change oil every 5,000 miles. Drive car hard regularly.</x:v>
+        <x:v>Replace warped/below-spec rotors and pads together; consider higher-quality coated or upgraded rotors that resist warping better than the soft OEM units. Bed in new pads/rotors properly and avoid riding the brakes to prevent uneven deposits. Ensure caliper guide pins/slides move freely so pads engage evenly. For repeat warping, an upgraded rotor-and-pad package is the durable fix; address any pulsation early before it damages new components.</x:v>
       </x:c>
       <x:c r="F74" s="9" t="n">
         <x:v>0</x:v>
@@ -14384,21 +17368,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="75" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A75" s="40" t="n">
         <x:v>74</x:v>
       </x:c>
       <x:c r="B75" s="9" t="str">
-        <x:v>audi-rs6-rs7-motor-mounts-2013</x:v>
+        <x:v>audi-s7-rear-differential-mount-driveshaft-center-bearing-wear-causi</x:v>
       </x:c>
       <x:c r="C75" s="9" t="str">
-        <x:v>2013-2023 | Audi | RS6 | 4.0T V8</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
       </x:c>
       <x:c r="D75" s="9" t="str">
-        <x:v>Premature Motor Mount Failure (4.0T V8)</x:v>
+        <x:v>Rear Differential Mount and Driveshaft Center Bearing Wear Causing Drivetrain Clunk (C7)</x:v>
       </x:c>
       <x:c r="E75" s="9" t="str">
-        <x:v>Replace failed motor mounts with OEM or upgraded mounts ($800-$1,500 for all mounts). Upgraded aftermarket mounts (034 Motorsport, ECS) offer better durability for high-torque engines ($400-$600 per mount). If you drive aggressively or track the car, consider upgrading to performance mounts preventively. Monitor for vibrations and clunking—early replacement prevents driveline damage.</x:v>
+        <x:v>Inspect the rear differential mount and driveshaft center support bearing for play and torn rubber. Replace worn components with OE parts, or fit billet aluminum diff/transmission mount inserts that fill the factory voids to remove the slop without adding harshness. On 4.0T cars, also check for the separate active-engine-mount software TSB before condemning a mount for a 1,000-3,000 RPM cruise vibration. Reassess the clunk after each fix since multiple sources can contribute.</x:v>
       </x:c>
       <x:c r="F75" s="9" t="n">
         <x:v>0</x:v>
@@ -14407,21 +17391,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="76" ht="462" hidden="0" customHeight="1">
       <x:c r="A76" s="40" t="n">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B76" s="9" t="str">
-        <x:v>audi-rs7-air-suspension-2014</x:v>
+        <x:v>audi-s7-rear-view-camera-mmi-flex-harness-black-screen</x:v>
       </x:c>
       <x:c r="C76" s="9" t="str">
-        <x:v>2021-2025 | Audi | RS7</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7 (C7), A7 (C7) | 4.0 TFSI V8 (EA824)</x:v>
       </x:c>
       <x:c r="D76" s="9" t="str">
-        <x:v>2021-2025 RS7 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
+        <x:v>Rear-View Camera / MMI Flex Harness Black Screen</x:v>
       </x:c>
       <x:c r="E76" s="9" t="str">
-        <x:v>Inspect the wiring and connectors between J775 and J1135 before replacing a component. For a first passive/sporadic occurrence, clear the fault and release the vehicle. If the fault is active/static after wiring and connector inspection, or the same passive/sporadic fault returns a second time, replace J1135 using current Audi repair and parts information. Audi notes that improved J1135 software remains under development.</x:v>
+        <x:v>Diagnose with a scan and continuity check of the tailgate-to-body flex harness before replacing the camera. Repair or replace the broken hinge-side loom conductors; if confirmed faulty, replace the camera module. For MMI freezes, apply the latest software update or reset the unit.</x:v>
       </x:c>
       <x:c r="F76" s="9" t="n">
         <x:v>0</x:v>
@@ -14430,21 +17414,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" ht="158.39999389648438" hidden="0" customHeight="1">
+    <x:row r="77" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A77" s="40" t="n">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B77" s="9" t="str">
-        <x:v>audi-rs7-carbon-buildup-2014</x:v>
+        <x:v>audi-s7-s-tronic-7-speed-dual-clutch-mechatronic-clutch-wear</x:v>
       </x:c>
       <x:c r="C77" s="9" t="str">
-        <x:v>2014-2026 | Audi | RS7 | 4.0T</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T (S-tronic / 0B5 DL501) | 4.0 TFSI V8 (EA824)</x:v>
       </x:c>
       <x:c r="D77" s="9" t="str">
-        <x:v>4.0T Carbon Deposit Accumulation</x:v>
+        <x:v>S-tronic 7-Speed Dual-Clutch (DL501/0B5) Mechatronic and Clutch Wear</x:v>
       </x:c>
       <x:c r="E77" s="9" t="str">
-        <x:v>Walnut blast every 30,000-40,000 miles. Install dual catch can setup for both turbo sides.</x:v>
+        <x:v>Perform the S-tronic gearbox oil and filter service on schedule (roughly every 40,000-60,000 km). For judder/jerking, have the mechatronic unit tested; recondition or replace the valve body with the superseded design and adapt/replace the clutch packs as needed. Software adaptation resets can temporarily improve drivability but do not fix worn hardware.</x:v>
       </x:c>
       <x:c r="F77" s="9" t="n">
         <x:v>0</x:v>
@@ -14453,21 +17437,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="78" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A78" s="40" t="n">
         <x:v>77</x:v>
       </x:c>
       <x:c r="B78" s="9" t="str">
-        <x:v>audi-rs7-turbo-coolant-2014</x:v>
+        <x:v>audi-s7-shark-fin-roof-antenna-water-intrusion-causing-gps-satellite</x:v>
       </x:c>
       <x:c r="C78" s="9" t="str">
-        <x:v>2014-2026 | Audi | RS7 | 4.0T</x:v>
+        <x:v>2013-2018 | Audi | S7 | Prestige, Premium Plus | 4.0T Biturbo V8 (4.0 TFSI)</x:v>
       </x:c>
       <x:c r="D78" s="9" t="str">
-        <x:v>4.0T Twin-Turbo Coolant System Degradation</x:v>
+        <x:v>Shark-Fin Roof Antenna Water Intrusion Causing GPS / Satellite Radio Reception Loss (C7)</x:v>
       </x:c>
       <x:c r="E78" s="9" t="str">
-        <x:v>Replace turbo coolant lines proactively at 50,000 miles. Upgrade to silicone lines where possible.</x:v>
+        <x:v>Test/replace the shark-fin antenna module with a matching OEM part number and renew the base gasket to restore a watertight seal; in many cases the official fix is a repair kit with a new FAKRA connector and adapter cable rather than a whole new antenna. Access requires partially dropping the rear headliner to reach the single mounting nut and reconnect the coax leads. Inspecting and reseating a corroded coax connection sometimes restores reception without full replacement.</x:v>
       </x:c>
       <x:c r="F78" s="9" t="n">
         <x:v>0</x:v>
@@ -14476,21 +17460,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="79" ht="752.4000244140625" hidden="0" customHeight="1">
       <x:c r="A79" s="40" t="n">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B79" s="9" t="str">
-        <x:v>audi-rs7-turbo-wastegate-2014</x:v>
+        <x:v>audi-s7-sunroof-panoramic-roof-drain-clog-causing-water-intrusion-el</x:v>
       </x:c>
       <x:c r="C79" s="9" t="str">
-        <x:v>2014-2017 | Audi | RS7 | 4.0L TFSI twin-turbo V8</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
       </x:c>
       <x:c r="D79" s="9" t="str">
-        <x:v>2014-2017 RS7 Turbocharger Oil-Strainer Safety Recall 21H7 / 22V178 - Check VIN</x:v>
+        <x:v>Sunroof / Panoramic Roof Drain Clog Causing Water Intrusion and Electronics Damage (C7)</x:v>
       </x:c>
       <x:c r="E79" s="9" t="str">
-        <x:v>Check the VIN for open Audi campaign 21H7 in Elsa or the NHTSA recall lookup. The authorized dealer replaces the turbocharger oil strainer, changes the engine oil and filter, and performs the campaign scan-tool turbo/boost-system check at no charge. Follow the campaign procedure for any damage found; do not buy a turbocharger, actuator or gasket kit from this card.</x:v>
+        <x:v>Test the drains by slowly pouring water into the channels at each corner of the sunroof and watching where it exits beneath the A- and C-pillars. Clear clogged tubes with low-pressure air or a soft trimmer line (avoid stiff wire that can puncture the tube) and reseat/secure any loose drain-tube connectors at the sunroof frame. Dry out any soaked carpet/insulation promptly and inspect floor-mounted modules for corrosion. Periodic drain cleaning is the best prevention.</x:v>
       </x:c>
       <x:c r="F79" s="9" t="n">
         <x:v>0</x:v>
@@ -14499,21 +17483,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="80" ht="422.3999938964844" hidden="0" customHeight="1">
       <x:c r="A80" s="40" t="n">
         <x:v>79</x:v>
       </x:c>
       <x:c r="B80" s="9" t="str">
-        <x:v>audi-rsq8-4.0t-coolant-2020</x:v>
+        <x:v>audi-s7-turbo-oil-strainer-2012</x:v>
       </x:c>
       <x:c r="C80" s="9" t="str">
-        <x:v>2020-2021 | Audi | RS Q8 | 4.0T V8</x:v>
+        <x:v>2013-2017 | Audi | S7 | 4.0 TFSI</x:v>
       </x:c>
       <x:c r="D80" s="9" t="str">
-        <x:v>2020-Early 2021 RS Q8 Red Coolant Warning - Check G407 per TSB 2062951/4</x:v>
+        <x:v>Turbocharger Oil-Supply Strainer Can Block and Cause Engine Stall (Recall 22V178 / 21H7)</x:v>
       </x:c>
       <x:c r="E80" s="9" t="str">
-        <x:v>Have the vehicle checked with Audi Guided Fault Finding and inspect G407 and its O-ring. Replace G407 only if the O-ring is damaged or pinched and the diagnosis matches the bulletin; follow the related Audi diagnostic path if additional listed faults are stored. Do not replace turbo coolant hoses, pumps or other cooling parts from this card alone.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the oil strainer and perform an oil change free of charge under campaign 21H7. If abnormal turbo noise, loss of power, or an engine warning occurs, stop safely and arrange dealer inspection.</x:v>
       </x:c>
       <x:c r="F80" s="9" t="n">
         <x:v>0</x:v>
@@ -14522,21 +17506,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="237.60000610351562" hidden="0" customHeight="1">
+    <x:row r="81" ht="726" hidden="0" customHeight="1">
       <x:c r="A81" s="40" t="n">
         <x:v>80</x:v>
       </x:c>
       <x:c r="B81" s="9" t="str">
-        <x:v>audi-rsq8-air-suspension-2020</x:v>
+        <x:v>audi-s7-turbocharger-wastegate-linkage-rattle-underboost</x:v>
       </x:c>
       <x:c r="C81" s="9" t="str">
-        <x:v>2020-2026 | Audi | RS Q8</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
       </x:c>
       <x:c r="D81" s="9" t="str">
-        <x:v>Adaptive Air Suspension Failure Under SUV Weight</x:v>
+        <x:v>Turbocharger Wastegate Linkage Rattle and Underboost (4.0T V8)</x:v>
       </x:c>
       <x:c r="E81" s="9" t="str">
-        <x:v>Replace air struts as they fail. Budget for compressor replacement. Consider heavy-duty aftermarket options designed for the RS Q8 weight.</x:v>
+        <x:v>Diagnose the rattle and any boost faults to confirm wastegate-arm play versus a loose heat shield. Minor play can sometimes be mitigated with a clip, but the durable factory fix is turbocharger replacement. When replacing a hot-V turbo, it is mandatory to also replace the oil feed and return lines and to prime the new unit with oil before first start to prevent immediate bearing failure. Regular oil changes and allowing turbo cool-down help reduce coking-related wear.</x:v>
       </x:c>
       <x:c r="F81" s="9" t="n">
         <x:v>0</x:v>
@@ -14545,20 +17529,22 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="82" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A82" s="40" t="n">
         <x:v>81</x:v>
       </x:c>
       <x:c r="B82" s="9" t="str">
-        <x:v>audi-rsq8-air-suspension-leak-2020</x:v>
+        <x:v>audi-s8-5-2-v10-timing-chain-tensioner-guide-wear</x:v>
       </x:c>
       <x:c r="C82" s="9" t="str">
-        <x:v>2020-2026 | Audi | RS Q8</x:v>
+        <x:v>2007-2012 | Audi | S8 | 5.2L FSI V10 (BSM)</x:v>
       </x:c>
       <x:c r="D82" s="9" t="str">
-        <x:v>Adaptive Air Suspension Air Spring Leaks</x:v>
-      </x:c>
-      <x:c r="E82" s="9" t="str"/>
+        <x:v>5.2 V10 Timing Chain Tensioner / Guide Wear (D3 Cold-Start Rattle)</x:v>
+      </x:c>
+      <x:c r="E82" s="9" t="str">
+        <x:v>Investigate any cold-start rattle promptly: inspect tensioner travel and guide condition. Replace the timing chains, tensioners, and plastic guides as a set with updated genuine parts; this is a major, labor-intensive repair (often engine-out). Strictly follow short oil-change intervals with the correct grade to maximize tensioner/guide life, and address any low-oil-pressure condition immediately. Do not drive a V10 with a persistent timing rattle.</x:v>
+      </x:c>
       <x:c r="F82" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -14566,21 +17552,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="607.2000122070312" hidden="0" customHeight="1">
+    <x:row r="83" ht="198" hidden="0" customHeight="1">
       <x:c r="A83" s="40" t="n">
         <x:v>82</x:v>
       </x:c>
       <x:c r="B83" s="9" t="str">
-        <x:v>audi-rsq8-brake-wear-2020</x:v>
+        <x:v>audi-s8-air-suspension-2013</x:v>
       </x:c>
       <x:c r="C83" s="9" t="str">
-        <x:v>2020-2021 | Audi | RS Q8</x:v>
+        <x:v>2013-2024 | Audi | S8</x:v>
       </x:c>
       <x:c r="D83" s="9" t="str">
-        <x:v>2020-2021 RS Q8 Front Steel-Brake Squeal - TSB 2062052/1</x:v>
+        <x:v>Adaptive Air Suspension Multi-Point Failure</x:v>
       </x:c>
       <x:c r="E83" s="9" t="str">
-        <x:v>Confirm the frequency and operating conditions and inspect the discs for corrosion, grooves or glazing. When the bulletin applies, Audi directs replacement of the front pad set using current parts information followed by the specified bedding procedure. Do not perform ABS stops for bedding, and do not replace rotors or buy aftermarket pads solely from the prior wear narrative.</x:v>
+        <x:v>Replace air struts as they fail. Budget for full system refresh at 80,000 miles. Arnott aftermarket struts offer cost savings.</x:v>
       </x:c>
       <x:c r="F83" s="9" t="n">
         <x:v>0</x:v>
@@ -14589,21 +17575,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="84" ht="726" hidden="0" customHeight="1">
       <x:c r="A84" s="40" t="n">
         <x:v>83</x:v>
       </x:c>
       <x:c r="B84" s="9" t="str">
-        <x:v>audi-s3-carbon-buildup-2015</x:v>
+        <x:v>audi-s8-air-suspension-failure-2013</x:v>
       </x:c>
       <x:c r="C84" s="9" t="str">
-        <x:v>2015-2019 | Audi | S3 | S3 | EA888 Gen 3</x:v>
+        <x:v>2020-2024 | Audi | S8</x:v>
       </x:c>
       <x:c r="D84" s="9" t="str">
-        <x:v>Carbon Buildup on Intake Valves (Pre-Dual Injection EA888 Gen 3)</x:v>
+        <x:v>2020-2024 S8 Air-Suspension Malfunction with J1135 Communication Fault - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E84" s="9" t="str">
-        <x:v>WALNUT BLASTING: Remove intake manifold and blast intake valve ports with crushed walnut shells ($500-$1,000). Repeat every 40,000-60,000 miles. CATCH CAN: Install an oil catch can ($200-$400) to capture PCV vapors before they reach intake valves—significantly slows carbon buildup. OIL CHANGES: Use high-quality synthetic oil and change every 5,000 miles. DRIVING HABITS: Regular spirited driving helps burn off some deposits. NOTE: 2020+ S3 models with EA888 Gen 3B dual injection are largely immune to this issue.</x:v>
+        <x:v>Read the suspension-controller DTC and symptom code, then inspect wiring, terminals and connectors between J775 and J1135 exactly as Audi specifies. If the fault is passive/sporadic, clear it and verify operation. If it remains active/static after the electrical inspection and key cycle, follow Audi testing for J1135 replacement. Diagnose vehicle sag or leak-down separately; do not order air struts, a compressor or a coil-conversion kit from the former card.</x:v>
       </x:c>
       <x:c r="F84" s="9" t="n">
         <x:v>0</x:v>
@@ -14612,21 +17598,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="85" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A85" s="40" t="n">
         <x:v>84</x:v>
       </x:c>
       <x:c r="B85" s="9" t="str">
-        <x:v>audi-s3-dq250-mechatronic-2015</x:v>
+        <x:v>audi-s8-battery-management-energy-control-module-faults-parasitic-dr</x:v>
       </x:c>
       <x:c r="C85" s="9" t="str">
-        <x:v>2015-2024 | Audi | S3</x:v>
+        <x:v>2020-2020 | Audi | S8 | VIN-specific Emissions Service Action 27BQ; verify open action in Audi campaign lookup | 4.0T TFSI V8 mild-hybrid</x:v>
       </x:c>
       <x:c r="D85" s="9" t="str">
-        <x:v>DQ250 DSG Mechatronic Unit Failure</x:v>
+        <x:v>2020 S8 Starter-Alternator Emissions Service Action 27BQ - VIN Check Required</x:v>
       </x:c>
       <x:c r="E85" s="9" t="str">
-        <x:v>Replace or rebuild mechatronic unit. Regular DSG fluid changes every 40,000 miles help prevent premature failure.</x:v>
+        <x:v>Check the VIN in Audi’s recall/service-campaign lookup or ask an Audi dealer to verify 27BQ in Elsa. If open, the dealer replaces the starter-alternator under the action. Electrical-system warnings, a discharged battery, abnormal charging or overnight draw outside this exact action require battery/charging tests and a measured sleep-current diagnosis; do not replace a battery monitor, gateway or MMI module from the former card.</x:v>
       </x:c>
       <x:c r="F85" s="9" t="n">
         <x:v>0</x:v>
@@ -14635,21 +17621,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="86" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A86" s="40" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="B86" s="9" t="str">
-        <x:v>audi-s3-dsg-mechatronic-2015</x:v>
+        <x:v>audi-s8-biturbo-coolant-2013</x:v>
       </x:c>
       <x:c r="C86" s="9" t="str">
-        <x:v>2015-2024 | Audi | S3 | S3</x:v>
+        <x:v>2013-2024 | Audi | S8 | 4.0T</x:v>
       </x:c>
       <x:c r="D86" s="9" t="str">
-        <x:v>DQ381 S-Tronic Mechatronic Unit Failure</x:v>
+        <x:v>4.0T Turbo Coolant System Degradation</x:v>
       </x:c>
       <x:c r="E86" s="9" t="str">
-        <x:v>EARLY SYMPTOMS (jerky shifts): DSG fluid and filter service ($500-$700) plus dealer software update. This may resolve early-stage issues. MECHATRONIC FAILURE: Replace mechatronic unit ($2,000-$4,000 installed) plus TCU coding. Remanufactured units available for $1,500-$2,500. CLUTCH PACK FAILURE: Replace dual clutch pack ($3,000-$5,000). PREVENTION: Service DSG fluid every 40,000 miles—ignore Audi's 'lifetime fill' claim. Use ONLY OEM Audi DSG fluid (G 052 182 A2) or approved Pentosin FFL-2. Avoid aggressive launches and excessive clutch slip in traffic.</x:v>
+        <x:v>Replace all turbo coolant and oil feed lines preventatively at 60,000 miles. Monitor coolant levels closely.</x:v>
       </x:c>
       <x:c r="F86" s="9" t="n">
         <x:v>0</x:v>
@@ -14658,21 +17644,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="158.39999389648438" hidden="0" customHeight="1">
+    <x:row r="87" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A87" s="40" t="n">
         <x:v>86</x:v>
       </x:c>
       <x:c r="B87" s="9" t="str">
-        <x:v>audi-s3-ea888-carbon-2015</x:v>
+        <x:v>audi-s8-clogged-sunroof-plenum-drains-causing-water-intrusion-electr</x:v>
       </x:c>
       <x:c r="C87" s="9" t="str">
-        <x:v>2015-2024 | Audi | S3 | EA888</x:v>
+        <x:v>2007-2018 | Audi | S8 | S8, S8 Plus | 5.2 FSI V10, 4.0 TFSI twin-turbo V8 (4.0T)</x:v>
       </x:c>
       <x:c r="D87" s="9" t="str">
-        <x:v>EA888 Carbon Buildup on Intake Valves</x:v>
+        <x:v>Clogged Sunroof / Plenum Drains Causing Water Intrusion and Electronics Damage</x:v>
       </x:c>
       <x:c r="E87" s="9" t="str">
-        <x:v>Walnut blast intake valves every 40,000-60,000 miles or install a catch can to reduce buildup rate.</x:v>
+        <x:v>Clear and flush all sunroof and plenum/cowl drains; replace cracked drain hoses, grommets, or channel connectors. Dry out saturated carpet/insulation and inspect plenum-area modules for corrosion, replacing any water-damaged control units. Preventively clean the drains at least annually and keep the cowl area free of leaves/debris.</x:v>
       </x:c>
       <x:c r="F87" s="9" t="n">
         <x:v>0</x:v>
@@ -14681,21 +17667,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="88" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A88" s="40" t="n">
         <x:v>87</x:v>
       </x:c>
       <x:c r="B88" s="9" t="str">
-        <x:v>audi-s3-hpfp-2015</x:v>
+        <x:v>audi-s8-coolant-thermostat-leak-2013</x:v>
       </x:c>
       <x:c r="C88" s="9" t="str">
-        <x:v>2015-2024 | Audi | S3 | EA888</x:v>
+        <x:v>2020-2021 | Audi | S8 | 2021 applicability ends at VIN 012194; confirm VIN and coolant-pump leak before repair | 4.0T TFSI V8</x:v>
       </x:c>
       <x:c r="D88" s="9" t="str">
-        <x:v>High-Pressure Fuel Pump (HPFP) Failure</x:v>
+        <x:v>2020-Early 2021 S8 Coolant-Pump Leak - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E88" s="9" t="str">
-        <x:v>Replace HPFP with updated revision. Check cam follower for wear during replacement.</x:v>
+        <x:v>Do not drive an overheating vehicle. Record coolant warning and temperature behavior, pressure-test the cooling system when safe, and locate the leak. Confirm the 2021 VIN boundary and apply TSB 2065040/4 only when the coolant pump is the identified source. Other thermostat, hose, turbo-line, heat-exchanger or internal-loss causes require separate diagnosis; do not order the former thermostat/water-pump bundle from this card.</x:v>
       </x:c>
       <x:c r="F88" s="9" t="n">
         <x:v>0</x:v>
@@ -14704,21 +17690,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="1122" hidden="0" customHeight="1">
+    <x:row r="89" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A89" s="40" t="n">
         <x:v>88</x:v>
       </x:c>
       <x:c r="B89" s="9" t="str">
-        <x:v>audi-s3-turbo-wastegate-rattle-2015</x:v>
+        <x:v>audi-s8-cylinder-demand-active-engine-mount-failure-4-cylinder-mode</x:v>
       </x:c>
       <x:c r="C89" s="9" t="str">
-        <x:v>2015-2020 | Audi | S3 | S3</x:v>
+        <x:v>2013-2015 | Audi | S8 | 4.0 TFSI vehicles with reproducible 1000-3000 rpm vibration; diagnose J931 before mount replacement | 4.0T TFSI V8</x:v>
       </x:c>
       <x:c r="D89" s="9" t="str">
-        <x:v>IS20 Turbocharger Wastegate Rattle and Actuator Failure</x:v>
+        <x:v>2013-2015 S8 COD Vibration with J931 Basic-Setting Fault - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E89" s="9" t="str">
-        <x:v>EARLY STAGE (rattle only, no power loss): Audi TSB 2027585/3 prescribes installation of a metal retaining clip (part 06J145220A) to tighten wastegate arm play ($200-$400 if under warranty, $500-$800 out of pocket). UPGRADED DIVERTER VALVE: Replace with revision 'D' diverter valve to improve boost control. SEVERE (actuator failure or power loss): Replace complete IS20 turbocharger ($2,500-$4,000 installed). The IS20 actuator is integrated and not serviceable separately. Upgraded IS38 turbo swap ($3,500-$5,000) from Golf R is a popular option if replacing turbo anyway. PREVENTION: Avoid short trips that don't fully heat the turbo. Change oil every 5,000 miles with high-quality synthetic.</x:v>
+        <x:v>Reproduce the vibration under Audi’s specified driving conditions and scan J931. If the bulletin applies, verify J931 software, perform the required SVM update and basic settings, align the exhaust without tension, repeat basic settings and follow the referenced diagnosis if vibration remains. Inspect mount hardware only after the software, calibration and exhaust path. Do not disable cylinder-on-demand or replace both mounts from the former card.</x:v>
       </x:c>
       <x:c r="F89" s="9" t="n">
         <x:v>0</x:v>
@@ -14727,44 +17713,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" ht="594" hidden="0" customHeight="1">
+    <x:row r="90" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A90" s="40" t="n">
         <x:v>89</x:v>
       </x:c>
       <x:c r="B90" s="9" t="str">
-        <x:v>audi-s3-water-pump-thermostat-2015</x:v>
+        <x:v>audi-s8-d2-4-2-v8-timing-belt-tensioner-service</x:v>
       </x:c>
       <x:c r="C90" s="9" t="str">
-        <x:v>2020-2024 | Audi | S3 | 2.0L TFSI</x:v>
+        <x:v>2001-2003 | Audi | S8 | 4.2L 40V V8 (AYS)</x:v>
       </x:c>
       <x:c r="D90" s="9" t="str">
-        <x:v>2020/2022-2024 Audi S3 2.0 TFSI Coolant-Pump Leak Diagnosis</x:v>
+        <x:v>D2 4.2 V8 Timing Belt and Tensioner Service (Interference Engine)</x:v>
       </x:c>
       <x:c r="E90" s="9" t="str">
-        <x:v>Document the suspected leak, clean and dry all traces, fill the cooling system to the correct level and reassess after driving a few miles. If no fresh leak appears, continue observing without replacing parts. If leakage recurs, replace only the component causing the damage under the exact VIN, engine and part criteria. Outside applicable warranty, Audi states the bulletin is informational.</x:v>
+        <x:v>Replace the timing belt as a complete kit — belt, tensioner, idler/guide rollers, and water pump — at or before Audi's interval (and by age regardless of mileage). Use genuine/OE-quality components and set cam/crank timing precisely with the correct locking tools; this is a front-of-engine ('service position') job. Inspect the exhaust-side chain tensioners while in there. Always confirm timing-belt history (with receipts) before buying a D2 S8; if unknown, do it immediately.</x:v>
       </x:c>
       <x:c r="F90" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G90" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="250.8000030517578" hidden="0" customHeight="1">
+    <x:row r="91" ht="844.7999877929688" hidden="0" customHeight="1">
       <x:c r="A91" s="40" t="n">
         <x:v>90</x:v>
       </x:c>
       <x:c r="B91" s="9" t="str">
-        <x:v>audi-s4-b5-timing-chain-2000</x:v>
+        <x:v>audi-s8-direct-injection-carbon-buildup-intake-valves</x:v>
       </x:c>
       <x:c r="C91" s="9" t="str">
-        <x:v>2000-2002 | Audi | S4</x:v>
+        <x:v>2013-2018 | Audi | S8 | 4.0T TFSI V8 (CTFA/CGTA/CWUC)</x:v>
       </x:c>
       <x:c r="D91" s="9" t="str">
-        <x:v>Driver Airbag Inflator May Deploy Improperly (Recall 21V470 / 69CJ)</x:v>
+        <x:v>Direct-Injection Carbon Buildup on Intake Valves (Misfires / Rough Idle)</x:v>
       </x:c>
       <x:c r="E91" s="9" t="str">
-        <x:v>Check the VIN with Audi or NHTSA. Audi dealers replace the driver frontal-airbag inflator with an alternative inflator free of charge under campaign 69CJ.</x:v>
+        <x:v>Confirm via borescope of the intake valves (and rule out coils/plugs/PCV first). The accepted repair is walnut-shell blasting: remove the intake manifold and media-blast the carbon off the valves and ports with crushed walnut shells, then reinstall with new intake gaskets. Replace spark plugs and inspect coils while the manifold is off. Preventively, keep up with oil changes, fix any PCV/oil-burning source, and consider periodic cleaning every ~40,000-60,000 miles. Catch-can solutions reduce future accumulation.</x:v>
       </x:c>
       <x:c r="F91" s="9" t="n">
         <x:v>0</x:v>
@@ -14773,21 +17759,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="237.60000610351562" hidden="0" customHeight="1">
+    <x:row r="92" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A92" s="40" t="n">
         <x:v>91</x:v>
       </x:c>
       <x:c r="B92" s="9" t="str">
-        <x:v>audi-s4-b5-turbo-failure-2000</x:v>
+        <x:v>audi-s8-front-suspension-control-arm-bushing-sway-bar-link-wear</x:v>
       </x:c>
       <x:c r="C92" s="9" t="str">
-        <x:v>2003-2004 | Audi | S4</x:v>
+        <x:v>2020-2021 | Audi | S8 | 2021 applicability through VIN 028090; localize noise acoustically before parts | 4.0T TFSI V8 mild-hybrid</x:v>
       </x:c>
       <x:c r="D92" s="9" t="str">
-        <x:v>Xenon Headlamp Reflector Coating Can Reduce Light Output (Recall 05V096)</x:v>
+        <x:v>2020-Early 2021 S8 Front Lower Guide-Link Hydro-Bushing Noise - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E92" s="9" t="str">
-        <x:v>Verify VIN eligibility and campaign completion with Audi. Dealers replace both xenon headlamp reflectors free of charge under recall 05V096.</x:v>
+        <x:v>Confirm the VIN boundary, reproduce the noise and localize it with acoustic diagnostic equipment. Inspect the lower guide-link hydro-bushings and surrounding joints. If the hydro-bushing is confirmed, follow Audi’s paired replacement procedure; complete guide links may be required when prior pressing or rework prevents the specified repair. Align the vehicle as required. Do not order a ten-arm kit or sway-bar links from the former card.</x:v>
       </x:c>
       <x:c r="F92" s="9" t="n">
         <x:v>0</x:v>
@@ -14796,21 +17782,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="303.6000061035156" hidden="0" customHeight="1">
+    <x:row r="93" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A93" s="40" t="n">
         <x:v>92</x:v>
       </x:c>
       <x:c r="B93" s="9" t="str">
-        <x:v>audi-s4-b6-timing-chain-2004</x:v>
+        <x:v>audi-s8-high-pressure-fuel-pump-injector-internal-leak-causing-hard</x:v>
       </x:c>
       <x:c r="C93" s="9" t="str">
-        <x:v>2005-2009 | Audi | S4</x:v>
+        <x:v>2013-2018 | Audi | S8 | 4.0 TFSI; diagnosis requires ODIS values, software check and pressure-hold testing | 4.0T TFSI V8</x:v>
       </x:c>
       <x:c r="D93" s="9" t="str">
-        <x:v>Passenger Airbag Inflator Can Rupture (Recall 18V427 / 69R7)</x:v>
+        <x:v>2013-2018 S8 Warm-Soak Long-Crank or No-Start - Fuel Diagnosis Required</x:v>
       </x:c>
       <x:c r="E93" s="9" t="str">
-        <x:v>Check VIN eligibility because body style and original registration history affect scope. Audi dealers replace the passenger frontal-airbag remedy part free of charge under campaign 69R7.</x:v>
+        <x:v>Have the dealer read DTCs and ODIS fuel-in-oil value, verify ECM software and perform Audi’s high- and low-pressure holding tests. If high-pressure behavior is abnormal, borescope the combustion chamber to identify a leaking injector. If low-side pressure builds correctly but drops more than 1.5 bar in the first 15 minutes, Audi says at least one HPFP may be leaking and directs replacement of both pumps plus an oil change. Select no pump or injector until the test identifies the path.</x:v>
       </x:c>
       <x:c r="F93" s="9" t="n">
         <x:v>0</x:v>
@@ -14819,21 +17805,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="356.3999938964844" hidden="0" customHeight="1">
+    <x:row r="94" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A94" s="40" t="n">
         <x:v>93</x:v>
       </x:c>
       <x:c r="B94" s="9" t="str">
-        <x:v>audi-s4-carbon-buildup-2010</x:v>
+        <x:v>audi-s8-mmi-upper-display-backup-camera-black-screen</x:v>
       </x:c>
       <x:c r="C94" s="9" t="str">
-        <x:v>2011-2012 | Audi | S4 | 3.0 TFSI</x:v>
+        <x:v>2020-2026 | Audi | S8 | VIN-specific NHTSA 25V900 / Audi 90TV; verify open recall | 4.0T TFSI V8 mild-hybrid</x:v>
       </x:c>
       <x:c r="D94" s="9" t="str">
-        <x:v>Fuel Rail or Seal Leak Creates Fire Risk (Recall 15V019 / 24AP)</x:v>
+        <x:v>2020-2026 S8 Rearview/Top-View Camera Image May Not Display - Recall 25V900</x:v>
       </x:c>
       <x:c r="E94" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel rails and corresponding seals free of charge under campaign 24AP. If fuel odor or leakage is present, stop driving and arrange immediate inspection.</x:v>
+        <x:v>Check the VIN in Audi’s recall/service-campaign lookup and schedule the free 90TV software remedy if open. Use extra care when reversing until repaired and visually check the area around the vehicle. A completely dead or rebooting MMI display, missing instrument-cluster data, wiring fault or hardware failure requires separate diagnosis and must not be attributed to this recall without VIN and symptom confirmation.</x:v>
       </x:c>
       <x:c r="F94" s="9" t="n">
         <x:v>0</x:v>
@@ -14842,21 +17828,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="224.39999389648438" hidden="0" customHeight="1">
+    <x:row r="95" ht="792" hidden="0" customHeight="1">
       <x:c r="A95" s="40" t="n">
         <x:v>94</x:v>
       </x:c>
       <x:c r="B95" s="9" t="str">
-        <x:v>audi-s4-supercharger-nose-2010</x:v>
+        <x:v>audi-s8-oil-consumption-2013</x:v>
       </x:c>
       <x:c r="C95" s="9" t="str">
-        <x:v>2013-2015 | Audi | S4</x:v>
+        <x:v>2020-2023 | Audi | S8 | EA825 4.0L; confirm VIN, engine and measured consumption under Audi procedure | 4.0T TFSI V8 mild-hybrid (EA825)</x:v>
       </x:c>
       <x:c r="D95" s="9" t="str">
-        <x:v>Airbag-Control Software May Miss Front-Airbag Deployment After a Second Impact (Recall 14V667 / 69K5)</x:v>
+        <x:v>2020-2023 S8 High Oil Consumption and Updated Piston Rings - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E95" s="9" t="str">
-        <x:v>Check VIN eligibility and completion history. Audi dealers update the airbag control-unit software free of charge under campaign 69K5.</x:v>
+        <x:v>Document oil-level warnings, mileage, top-up quantity, leaks and oil specification, then have an Audi dealer perform the authorized oil-consumption measurement. Repair is justified only when the measured result exceeds the applicable owner-manual limit and other leakage or operating causes are excluded. If TSB 2071114 applies, follow its VIN/engine-specific piston, ring and connecting-rod procedure. Do not change oil viscosity or authorize internal-engine work solely from the former card.</x:v>
       </x:c>
       <x:c r="F95" s="9" t="n">
         <x:v>0</x:v>
@@ -14865,44 +17851,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" ht="198" hidden="0" customHeight="1">
+    <x:row r="96" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A96" s="40" t="n">
         <x:v>95</x:v>
       </x:c>
       <x:c r="B96" s="9" t="str">
-        <x:v>audi-s4-thermostat-2010</x:v>
+        <x:v>audi-s8-pcv-oil-separator-failure-excessive-crankcase-vacuum</x:v>
       </x:c>
       <x:c r="C96" s="9" t="str">
-        <x:v>2010-2025 | Audi | S4 | 3.0T</x:v>
+        <x:v>2013-2016 | Audi | S8 | 4.0 TFSI; confirm warm-idle sound and filler-cap response before oil-separator replacement | 4.0T TFSI V8</x:v>
       </x:c>
       <x:c r="D96" s="9" t="str">
-        <x:v>Thermostat Housing Failure and Coolant Leak</x:v>
+        <x:v>2013-2016 S8 Warm-Idle Whistle from Crankcase Breather Leak - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E96" s="9" t="str">
-        <x:v>Replace thermostat housing assembly with updated part. Use OEM or quality aftermarket housing with metal reinforcement.</x:v>
+        <x:v>Compare the sound with Audi’s reference condition and check whether opening the oil filler cap changes it. Read P2279/P0507 and rule out other intake leaks. When the sound matches and is affected by the filler-cap check, follow Audi’s oil-separator breather replacement procedure and renew required seals/consumables by VIN. Do not diagnose by oil-cap feel alone or order the former five-item parts list.</x:v>
       </x:c>
       <x:c r="F96" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G96" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" ht="963.5999755859375" hidden="0" customHeight="1">
+    <x:row r="97" ht="594" hidden="0" customHeight="1">
       <x:c r="A97" s="40" t="n">
         <x:v>96</x:v>
       </x:c>
       <x:c r="B97" s="9" t="str">
-        <x:v>audi-s5-b9-water-pump-2018</x:v>
+        <x:v>audi-s8-porous-high-pressure-fuel-supply-line-recall-nhtsa-19v057000</x:v>
       </x:c>
       <x:c r="C97" s="9" t="str">
-        <x:v>2018-2018 | Audi | S5 | 3.0L V6 TFSI EA839</x:v>
+        <x:v>2013-2016 | Audi | S8 | VIN-specific NHTSA 19V057 / Audi 20BM; verify open recall | 4.0T TFSI V8</x:v>
       </x:c>
       <x:c r="D97" s="9" t="str">
-        <x:v>2018 S5 3.0L Mechanical Coolant-Pump Fault P000000/33688 - Diagnosis Required</x:v>
+        <x:v>2013-2016 S8 Porous Fuel-Pump Supply Line / Fire Risk - Recall 19V057</x:v>
       </x:c>
       <x:c r="E97" s="9" t="str">
-        <x:v>Follow the bulletin in order. Verify coolant level; if low, inspect the cooling system for a leak and repair only the identified source or top up per Audi instructions when no leak is found. Check the ECM software level and apply the specified SVM update only when required. If the concern returns or software is current, test vacuum at N649 and inspect the solenoid and hoses. If the vacuum system works, apply vacuum to the pump hose and verify that the pump sleeve clicks; replace the mechanical coolant pump only when the sleeve does not operate. Use current Audi workshop and parts information.</x:v>
+        <x:v>Check the VIN for open recall 20BM and contact an Audi dealer without delay. The free remedy installs a fuel-pressure damper in the low-pressure fuel supply inside the tank. If fuel odor or visible leakage is present, avoid ignition sources, do not continue driving, and arrange dealer inspection/towing as appropriate. Do not buy a retail line or damper from the former card.</x:v>
       </x:c>
       <x:c r="F97" s="9" t="n">
         <x:v>0</x:v>
@@ -14911,21 +17897,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" ht="184.8000030517578" hidden="0" customHeight="1">
+    <x:row r="98" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A98" s="40" t="n">
         <x:v>97</x:v>
       </x:c>
       <x:c r="B98" s="9" t="str">
-        <x:v>audi-s5-carbon-buildup-2008</x:v>
+        <x:v>audi-s8-torque-converter-2013</x:v>
       </x:c>
       <x:c r="C98" s="9" t="str">
-        <x:v>2008-2025 | Audi | S5</x:v>
+        <x:v>2013-2024 | Audi | S8</x:v>
       </x:c>
       <x:c r="D98" s="9" t="str">
-        <x:v>Direct Injection Carbon Buildup</x:v>
+        <x:v>ZF 8-Speed Torque Converter and Valve Body Issues</x:v>
       </x:c>
       <x:c r="E98" s="9" t="str">
-        <x:v>Walnut blast intake valves every 40,000-60,000 miles. Install oil catch can to reduce oil vapor reaching valves.</x:v>
+        <x:v>Replace torque converter and service valve body. Full ZF fluid and filter change every 50,000 miles extends transmission life.</x:v>
       </x:c>
       <x:c r="F98" s="9" t="n">
         <x:v>0</x:v>
@@ -14934,44 +17920,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="99" ht="712.7999877929688" hidden="0" customHeight="1">
       <x:c r="A99" s="40" t="n">
         <x:v>98</x:v>
       </x:c>
       <x:c r="B99" s="9" t="str">
-        <x:v>audi-s5-crankshaft-pulley-2010</x:v>
+        <x:v>audi-s8-turbo-oil-strainer-2013</x:v>
       </x:c>
       <x:c r="C99" s="9" t="str">
-        <x:v>2010-2017 | Audi | S5 | Premium Plus, Prestige | 3.0T</x:v>
+        <x:v>2013-2017 | Audi | S8 | VIN-specific NHTSA 22V178 / Audi 21H7; verify open recall | 4.0T TFSI V8</x:v>
       </x:c>
       <x:c r="D99" s="9" t="str">
-        <x:v>Crankshaft Pulley (Harmonic Balancer) Failure (3.0T)</x:v>
+        <x:v>2013-2017 S8 Blocked Turbocharger Oil Strainer / Stall Risk - Recall 22V178</x:v>
       </x:c>
       <x:c r="E99" s="9" t="str">
-        <x:v>Replace crankshaft pulley/harmonic balancer with LATEST REVISION (revision F or later) part ($300-$600 for part, $800-$1,700 with labor). This is NOT a DIY-friendly repair—requires specialized holding tools and precise torque. If belts are damaged, replace serpentine belt and tensioner ($200-$400 additional). INSPECT: Check for collateral damage to supercharger snout, idler pulleys, and timing. If timing was affected, expect $3,000-$5,000 additional repair. PREVENTIVE: Inspect pulley for wobble at every oil change. Consider preemptive replacement at 80,000 miles on 2010-2013 models.</x:v>
+        <x:v>Check the VIN for open recall 21H7 and schedule the free Audi dealer remedy, which replaces the oil strainer and performs an oil change. If EPC, MIL or oil warning lights appear with unusual turbo noise, extended cranking, rough idle, loss of power or stalling, stop safely and arrange diagnosis. Turbo damage, warranty eligibility and any additional repair must be assessed by VIN and inspection; do not buy the former retail strainer.</x:v>
       </x:c>
       <x:c r="F99" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G99" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="844.7999877929688" hidden="0" customHeight="1">
+    <x:row r="100" ht="950.4000244140625" hidden="0" customHeight="1">
       <x:c r="A100" s="40" t="n">
         <x:v>99</x:v>
       </x:c>
       <x:c r="B100" s="9" t="str">
-        <x:v>audi-s5-pcv-valve-failure-2010</x:v>
+        <x:v>audi-s8-water-to-air-intercooler-internal-coolant-leak</x:v>
       </x:c>
       <x:c r="C100" s="9" t="str">
-        <x:v>2010-2017 | Audi | S5 | 3.0L supercharged V6</x:v>
+        <x:v>2013-2018 | Audi | S8 | 4.0T TFSI V8 (CTFA/CGTA/CWUC)</x:v>
       </x:c>
       <x:c r="D100" s="9" t="str">
-        <x:v>2010-2017 S5 3.0L Crankcase-Breather P052E00 - Body/Year Diagnosis</x:v>
+        <x:v>Water-to-Air Intercooler Internal Coolant Leak (Coolant into Intake)</x:v>
       </x:c>
       <x:c r="E100" s="9" t="str">
-        <x:v>Verify the body style, model year and P052E00 condition first. For the applicable membrane branch, use the specified hand-vacuum test, then inspect the membrane and metal plates after compressor/intake-manifold removal; replace only the faulted membrane/plate repair kit or crankcase breather per current Audi instructions. If testing identifies the elbow branch, replace the elbow and hose clip as directed by TSB 2060259/1. Do not assume that both branches or unrelated cooling parts require replacement.</x:v>
+        <x:v>Confirm the source: pressure-test the cooling system and inspect the charge piping/intercooler outlet for coolant residue; scope for white smoke and coolant on the intake side rather than an external leak. Replace the water-to-air intercooler/charge-air cooler unit (genuine OEM core). Because access requires removing intake components in the valley, it is standard practice to also replace the turbo oil strainer, coolant valves, and PCV/oil separator while in there. Refill and bleed the cooling system per procedure. This is a high-difficulty job typically done by a specialist or dealer.</x:v>
       </x:c>
       <x:c r="F100" s="9" t="n">
         <x:v>0</x:v>
@@ -14980,21 +17966,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="101" ht="475.20001220703125" hidden="0" customHeight="1">
       <x:c r="A101" s="40" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="B101" s="9" t="str">
-        <x:v>audi-s5-supercharger-2008</x:v>
+        <x:v>audi-sq2-ea888-2-0-tfsi-coolant-leak-from-water-pump-thermostat-housi</x:v>
       </x:c>
       <x:c r="C101" s="9" t="str">
-        <x:v>2008-2025 | Audi | S5 | 3.0T</x:v>
+        <x:v>2019-2024 | Audi | SQ2 | 2.0 TFSI quattro | EA888 2.0 TFSI Gen3</x:v>
       </x:c>
       <x:c r="D101" s="9" t="str">
-        <x:v>3.0T Supercharger Intercooler Pump Failure</x:v>
+        <x:v>EA888 2.0 TFSI coolant leak from water pump / thermostat housing</x:v>
       </x:c>
       <x:c r="E101" s="9" t="str">
-        <x:v>Replace intercooler coolant pump. Check intercooler lines for leaks and flush the circuit during replacement.</x:v>
+        <x:v>Replace the failed water pump / thermostat housing assembly, ideally with the latest revised, more heat-resistant unit; many shops fit an upgraded repair kit and a new gasket. Catch it early by watching for slowly dropping coolant level and a faint sweet smell. Combine with a coolant flush and refill.</x:v>
       </x:c>
       <x:c r="F101" s="9" t="n">
         <x:v>0</x:v>
@@ -15003,21 +17989,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="102" ht="396" hidden="0" customHeight="1">
       <x:c r="A102" s="40" t="n">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B102" s="9" t="str">
-        <x:v>audi-s5-thermostat-2008</x:v>
+        <x:v>audi-sq2-electro-mechanical-parking-brake-brake-pedal-weld-recalls</x:v>
       </x:c>
       <x:c r="C102" s="9" t="str">
-        <x:v>2008-2025 | Audi | S5 | 3.0T</x:v>
+        <x:v>2019-2020 | Audi | SQ2</x:v>
       </x:c>
       <x:c r="D102" s="9" t="str">
-        <x:v>Thermostat and Water Pump Assembly Failure</x:v>
+        <x:v>Electro-mechanical parking brake and brake-pedal weld recalls (early build)</x:v>
       </x:c>
       <x:c r="E102" s="9" t="str">
-        <x:v>Replace thermostat/water pump assembly. Upgrade to revised housing if available.</x:v>
+        <x:v>These are recall items — have the VIN checked against the Audi/DVSA recall database and any open campaign rectified free of charge at a dealer. Report any abnormal parking-brake behaviour or a soft/abnormal brake pedal immediately.</x:v>
       </x:c>
       <x:c r="F102" s="9" t="n">
         <x:v>0</x:v>
@@ -15026,21 +18012,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="103" ht="475.20001220703125" hidden="0" customHeight="1">
       <x:c r="A103" s="40" t="n">
         <x:v>102</x:v>
       </x:c>
       <x:c r="B103" s="9" t="str">
-        <x:v>audi-s6-air-suspension-2013</x:v>
+        <x:v>audi-sq2-internal-fuse-box-wiring-harness-can-work-loose-causing-sudd</x:v>
       </x:c>
       <x:c r="C103" s="9" t="str">
-        <x:v>2013-2013 | Audi | S6 | 4.0T</x:v>
+        <x:v>2022-2023 | Audi | SQ2 | 2.0 TFSI</x:v>
       </x:c>
       <x:c r="D103" s="9" t="str">
-        <x:v>2013 Audi S6 Air-Suspension Compressor or Relay Fault - Diagnosis Required</x:v>
+        <x:v>2022-2023 Audi SQ2 Interior Fuse-Carrier Recall GAI-3692</x:v>
       </x:c>
       <x:c r="E103" s="9" t="str">
-        <x:v>Have an Audi-qualified technician test the air-suspension compressor and inspect relay J403. Audi directs replacement of both the compressor and relay when the relay has severe contact erosion or an overheated strand; when the compressor sounds normal and the relay has only minor contact marks, replace the relay only. A sagging corner or leak-down condition requires separate leak localization before any strut is replaced. Do not order the former strut or compressor recommendations from this card.</x:v>
+        <x:v>Check the VIN and open-campaign status with an authorised Audi dealer in the vehicle’s market. The campaign remedy is dealer inspection and correction of the fuse-carrier power connection. Do not replace a fuse box or wiring harness solely from a warning lamp or this model-year summary.</x:v>
       </x:c>
       <x:c r="F103" s="9" t="n">
         <x:v>0</x:v>
@@ -15049,21 +18035,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="1359.5999755859375" hidden="0" customHeight="1">
+    <x:row r="104" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A104" s="40" t="n">
         <x:v>103</x:v>
       </x:c>
       <x:c r="B104" s="9" t="str">
-        <x:v>audi-s6-c7-carbon-buildup-2013</x:v>
+        <x:v>audi-sq2-mmi-infotainment-freezing-rebooting-lost-settings</x:v>
       </x:c>
       <x:c r="C104" s="9" t="str">
-        <x:v>2013-2018 | Audi | S6 | 4.0T</x:v>
+        <x:v>2019-2024 | Audi | SQ2</x:v>
       </x:c>
       <x:c r="D104" s="9" t="str">
-        <x:v>4.0T Carbon Buildup on Intake Valves</x:v>
+        <x:v>MMI infotainment freezing, rebooting and lost settings</x:v>
       </x:c>
       <x:c r="E104" s="9" t="str">
-        <x:v>Confirm carbon buildup by scanning for misfire faults (commonly random/multiple or cylinder-specific misfires), reviewing fuel trims, and inspecting the intake valves with a borescope after removing the intake manifold or accessing the ports. The proper repair is an intake valve carbon cleaning, typically walnut shell blasting each intake port with the valves closed, then replacing intake manifold gaskets, injector seals/O-rings or any disturbed PCV-related seals as needed and clearing/adapting the ECU afterward. If buildup is severe or returns quickly, inspect the PCV/oil separator system and crankcase ventilation hoses for excessive oil carryover. Independent shops typically charge about $800-$1,500 for a full walnut blast service on the 4.0T, while dealer pricing can run roughly $1,500-$2,500 depending on labor and gasket/seal replacement.</x:v>
+        <x:v>A forced MMI restart (press and hold the on/off or volume control ~10 seconds until it reboots) clears many transient faults. Persistent issues are usually resolved by a dealer software/firmware update; check for any applicable MMI update campaigns. Only in rare cases is the MMI head unit itself replaced.</x:v>
       </x:c>
       <x:c r="F104" s="9" t="n">
         <x:v>0</x:v>
@@ -15072,21 +18058,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="105" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A105" s="40" t="n">
         <x:v>104</x:v>
       </x:c>
       <x:c r="B105" s="9" t="str">
-        <x:v>audi-s6-carbon-buildup-2013</x:v>
+        <x:v>audi-sq2-pcv-crankcase-ventilation-valve-diaphragm-failure-causing-ro</x:v>
       </x:c>
       <x:c r="C105" s="9" t="str">
-        <x:v>2013-2024 | Audi | S6 | 4.0T</x:v>
+        <x:v>2019-2024 | Audi | SQ2 | EA888 2.0 TFSI Gen3</x:v>
       </x:c>
       <x:c r="D105" s="9" t="str">
-        <x:v>4.0T Direct Injection Carbon Buildup</x:v>
+        <x:v>PCV / crankcase ventilation valve diaphragm failure causing rough idle and lean-running codes</x:v>
       </x:c>
       <x:c r="E105" s="9" t="str">
-        <x:v>Walnut blast all eight intake runners. Dual-injection models (2019+) are less affected.</x:v>
+        <x:v>Replace the PCV valve (or the valve-cover assembly that integrates it) with the latest revised part; some owners fit a catch-can to reduce recurrence. A quick field test — briefly covering the bleeder hole on the cap to see if idle stabilises or whistling stops — helps confirm before replacement.</x:v>
       </x:c>
       <x:c r="F105" s="9" t="n">
         <x:v>0</x:v>
@@ -15095,21 +18081,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" ht="462" hidden="0" customHeight="1">
+    <x:row r="106" ht="752.4000244140625" hidden="0" customHeight="1">
       <x:c r="A106" s="40" t="n">
         <x:v>105</x:v>
       </x:c>
       <x:c r="B106" s="9" t="str">
-        <x:v>audi-s6-rearview-camera-image-failure-from-software-error</x:v>
+        <x:v>audi-sq2-s-tronic-7-speed-wet-clutch-transmission-jerky-low-speed-shi</x:v>
       </x:c>
       <x:c r="C106" s="9" t="str">
-        <x:v>2020-2025 | Audi | S6</x:v>
+        <x:v>2019-2024 | Audi | SQ2 | 7-speed S tronic | DQ381 / 0GC 7-speed wet-clutch S tronic</x:v>
       </x:c>
       <x:c r="D106" s="9" t="str">
-        <x:v>2020-2025 Audi S6 Rearview Camera Software Recall 25V900 / 90TV</x:v>
+        <x:v>S tronic (DQ381) 7-speed wet-clutch transmission: jerky low-speed shifts, hesitation and limp mode</x:v>
       </x:c>
       <x:c r="E106" s="9" t="str">
-        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install the more robust driver-assistance software update free of charge. Until repaired, use extra caution when reversing and do not treat a restart or temporary image recovery as completion of the recall.</x:v>
+        <x:v>First step is a proper DSG fluid-and-filter service (the wet-clutch unit needs periodic transmission oil changes — many owners do it around 40k miles even though intervals can be longer). Have the TCU scanned for stored codes; sensor or mechatronic valve replacement and re-coding/adaptation resolves many cases, while severe cases need a full mechatronic unit or clutch-pack replacement. Insist on a software/adaptation update at the dealer for driveability complaints.</x:v>
       </x:c>
       <x:c r="F106" s="9" t="n">
         <x:v>0</x:v>
@@ -15118,21 +18104,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="107" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A107" s="40" t="n">
         <x:v>106</x:v>
       </x:c>
       <x:c r="B107" s="9" t="str">
-        <x:v>audi-s6-takata-passenger-airbag-inflator-recall</x:v>
+        <x:v>audi-sq5-air-suspension-2018</x:v>
       </x:c>
       <x:c r="C107" s="9" t="str">
-        <x:v>2007-2011 | Audi | S6</x:v>
+        <x:v>2018-2025 | Audi | SQ5</x:v>
       </x:c>
       <x:c r="D107" s="9" t="str">
-        <x:v>2007-2011 Audi S6 Takata Passenger-Airbag Recall 18V427 / 69R7</x:v>
+        <x:v>Air-Suspension Warning with C1260F0 or U112100 Communication Fault</x:v>
       </x:c>
       <x:c r="E107" s="9" t="str">
-        <x:v>Check the VIN for recall 18V427/69R7 and arrange the free final passenger-frontal-airbag replacement with an Audi dealer. Do not use an airbag warning light to determine recall eligibility; Audi states that the warning light is unrelated to this inflator defect.</x:v>
+        <x:v>Inspect the wiring and connector contacts between J775 and J1135 first. If no wiring fault is found, clear a first passive or sporadic fault and release the vehicle. Replace J1135 for an active or static fault, or when the same passive or sporadic fault returns a second time, following Audi workshop information and VIN-specific ETKA data.</x:v>
       </x:c>
       <x:c r="F107" s="9" t="n">
         <x:v>0</x:v>
@@ -15141,20 +18127,22 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="108" ht="924" hidden="0" customHeight="1">
       <x:c r="A108" s="40" t="n">
         <x:v>107</x:v>
       </x:c>
       <x:c r="B108" s="9" t="str">
-        <x:v>audi-s6-transmission-valve-body-2002</x:v>
+        <x:v>audi-sq5-carbon-buildup-2014</x:v>
       </x:c>
       <x:c r="C108" s="9" t="str">
-        <x:v>2002-2004 | Audi | S6</x:v>
+        <x:v>2014-2025 | Audi | SQ5 | 3.0T Supercharged, 3.0T</x:v>
       </x:c>
       <x:c r="D108" s="9" t="str">
-        <x:v>ZF 5HP24 Tiptronic Transmission Valve Body Failure</x:v>
-      </x:c>
-      <x:c r="E108" s="9" t="str"/>
+        <x:v>Fuel-Quality or Deposit-Related Rough Running and Misfire Diagnosis</x:v>
+      </x:c>
+      <x:c r="E108" s="9" t="str">
+        <x:v>Confirm fuel quality, symptoms and stored DTCs before replacing or cleaning components. If contaminated gasoline is suspected, advise changing the fuel source; if low detergent quality is suspected, Audi recommends Top Tier detergent gasoline. Continue workshop diagnosis if symptoms persist. On 2018-2025 EA839 SQ5 models, do not recommend unapproved cleaners or additives; follow the owner manual and use only Audi-approved petrol additives. Do not prescribe routine walnut blasting, a catch can or chemical cleaning from this record.</x:v>
+      </x:c>
       <x:c r="F108" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -15162,21 +18150,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="109" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A109" s="40" t="n">
         <x:v>108</x:v>
       </x:c>
       <x:c r="B109" s="9" t="str">
-        <x:v>audi-s6-turbo-coolant-2013</x:v>
+        <x:v>audi-sq5-pcv-valve-2014</x:v>
       </x:c>
       <x:c r="C109" s="9" t="str">
-        <x:v>2013-2013 | Audi | S6 | 4.0T</x:v>
+        <x:v>2014-2017 | Audi | SQ5 | 3.0T Supercharged</x:v>
       </x:c>
       <x:c r="D109" s="9" t="str">
-        <x:v>2013 Audi S6 Turbocharger Coolant-Pipe Seepage - Diagnosis Required</x:v>
+        <x:v>P052E00 Crankcase-Breather Membrane or Elbow Fault</x:v>
       </x:c>
       <x:c r="E109" s="9" t="str">
-        <x:v>Confirm the leak source and VIN applicability before ordering parts. For the TSB condition, Audi specifies replacing the coolant feed and return pipes on both cylinder banks, replacing the disturbed oil-feed-pipe O-rings, then refilling and bleeding the cooling system. Service Action 21F7 was VIN-specific and expired in 2019, so current coverage must not be assumed. Do not order the former single pipe or alleged silicone-line kit from this card.</x:v>
+        <x:v>Use Audi hand-vacuum test to distinguish a membrane leak from an elbow fault. If indicated, remove the compressor or intake manifold and inspect the membrane and the breather two metal plates. Use repair kit 06E103772H only for a confirmed membrane or plate fault. For a confirmed elbow fault, replace elbow 06E103402 and spring clip N10769401 rather than automatically replacing the complete breather. Verify current part data in ETKA before ordering.</x:v>
       </x:c>
       <x:c r="F109" s="9" t="n">
         <x:v>0</x:v>
@@ -15185,21 +18173,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" ht="290.3999938964844" hidden="0" customHeight="1">
+    <x:row r="110" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A110" s="40" t="n">
         <x:v>109</x:v>
       </x:c>
       <x:c r="B110" s="9" t="str">
-        <x:v>audi-s7-air-suspension-2012</x:v>
+        <x:v>audi-sq5-supercharger-2014</x:v>
       </x:c>
       <x:c r="C110" s="9" t="str">
-        <x:v>2020-2021 | Audi | S7</x:v>
+        <x:v>2014-2018 | Audi | SQ5 | 3.0T</x:v>
       </x:c>
       <x:c r="D110" s="9" t="str">
-        <x:v>Rear-Axle Lock Nut and Alignment Recall Follow-Up (21V295 / 22V034)</x:v>
+        <x:v>3.0T Supercharger Bearing and Intercooler Pump Failure</x:v>
       </x:c>
       <x:c r="E110" s="9" t="str">
-        <x:v>Check the VIN for both campaigns 42L1 and 42L5. Audi dealers replace affected nuts and bolts, inspect and adjust rear alignment, and replace qualifying unevenly worn tires free of charge.</x:v>
+        <x:v>Replace supercharger nose bearing kit. Replace intercooler pump if failing. Service supercharger belt tension.</x:v>
       </x:c>
       <x:c r="F110" s="9" t="n">
         <x:v>0</x:v>
@@ -15208,21 +18196,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" ht="237.60000610351562" hidden="0" customHeight="1">
+    <x:row r="111" ht="844.7999877929688" hidden="0" customHeight="1">
       <x:c r="A111" s="40" t="n">
         <x:v>110</x:v>
       </x:c>
       <x:c r="B111" s="9" t="str">
-        <x:v>audi-s7-biturbo-coolant-2012</x:v>
+        <x:v>audi-sq5-supercharger-oil-leak-2014</x:v>
       </x:c>
       <x:c r="C111" s="9" t="str">
-        <x:v>2013-2014 | Audi | S7 | 4.0 TFSI</x:v>
+        <x:v>2014-2017 | Audi | SQ5 | Premium Plus, Prestige | 3.0T Supercharged, 3.0T</x:v>
       </x:c>
       <x:c r="D111" s="9" t="str">
-        <x:v>4.0L Fuel Line Can Leak and Create a Fire Risk (Recall 13V450 / 20U6)</x:v>
+        <x:v>Supercharger Seal and Gasket Oil Leaks (3.0T)</x:v>
       </x:c>
       <x:c r="E111" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel line free of charge under campaign 20U6/L8. Stop driving if fuel odor or leakage is present.</x:v>
+        <x:v>JHM Motorsports sells a complete supercharger replacement seal and gasket kit for the Eaton unit in the 3.0T. Replacing all seals at once is recommended since the supercharger must be removed for access. Nose cone seal, rotor shaft seals, and manifold gaskets should all be replaced together ($300-$500 in parts, $600-$1,200 labor). While the supercharger is off, also replace the PCV valve and perform carbon cleaning. For valve cover gasket leaks (separate issue), budget $400-$800 parts and labor. Monitor oil level weekly if leaks are present.</x:v>
       </x:c>
       <x:c r="F111" s="9" t="n">
         <x:v>0</x:v>
@@ -15231,21 +18219,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" ht="264" hidden="0" customHeight="1">
+    <x:row r="112" ht="1122" hidden="0" customHeight="1">
       <x:c r="A112" s="40" t="n">
         <x:v>111</x:v>
       </x:c>
       <x:c r="B112" s="9" t="str">
-        <x:v>audi-s7-carbon-buildup-4.0t-2012</x:v>
+        <x:v>audi-sq5-water-pump-2018</x:v>
       </x:c>
       <x:c r="C112" s="9" t="str">
-        <x:v>2021-2021 | Audi | S7</x:v>
+        <x:v>2018-2024 | Audi | SQ5 | 3.0T</x:v>
       </x:c>
       <x:c r="D112" s="9" t="str">
-        <x:v>Rear Seat-Belt Retractor Can Release a Child Restraint Early (Recall 21V606 / 69CS)</x:v>
+        <x:v>Mechanical Coolant-Pump Leak with Possible N649 Vacuum-System Contamination</x:v>
       </x:c>
       <x:c r="E112" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers inspect and replace the affected middle-rear seat-belt assembly as necessary free of charge under campaign 69CS.</x:v>
+        <x:v>Confirm the complaint and exact vehicle criteria first. Inspect the vacuum line and N649 for coolant, then clean and dry suspected leakage, fill the cooling system correctly, inspect at idle and around 2,500 rpm, and pressure-test according to Audi workshop information. If no leak is reproduced, observe the vehicle without replacing parts. If the pump leak is confirmed, replace the failed component and document it. If fresh coolant has entered the vacuum system, inspect the remaining Audi checkpoints and replace only contaminated components; if the downstream checkpoints are clean, replace N649 and clean the line between the pump and N649 as directed by TSB 2070349/5.</x:v>
       </x:c>
       <x:c r="F112" s="9" t="n">
         <x:v>0</x:v>
@@ -15254,21 +18242,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="113" ht="237.60000610351562" hidden="0" customHeight="1">
+    <x:row r="113" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A113" s="40" t="n">
         <x:v>112</x:v>
       </x:c>
       <x:c r="B113" s="9" t="str">
-        <x:v>audi-s7-cylinder-demand-rough-running-hesitation</x:v>
+        <x:v>audi-sq7-air-susp-strut-2020</x:v>
       </x:c>
       <x:c r="C113" s="9" t="str">
-        <x:v>2021-2021 | Audi | S7</x:v>
+        <x:v>2020-2025 | Audi | SQ7 | 4.0T</x:v>
       </x:c>
       <x:c r="D113" s="9" t="str">
-        <x:v>Instrument Panel May Fail to Display Critical Safety Information (Recall 25V201 / 90VC)</x:v>
+        <x:v>2020-2025 SQ7 Air-Suspension C1260F0/U112100 Communication Fault - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E113" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history. Audi dealers update the instrument-panel module software free of charge under campaign 90VC.</x:v>
+        <x:v>Inspect the wiring and connector contacts between J775 and J1135 first. If no wiring fault is found, clear a first passive or sporadic fault and release the vehicle. Replace J1135 for an active or static fault, or when the same passive or sporadic fault returns a second time, following Audi workshop information and VIN-specific ETKA data. Do not replace an air spring, strut or compressor assembly solely from the warning.</x:v>
       </x:c>
       <x:c r="F113" s="9" t="n">
         <x:v>0</x:v>
@@ -15277,21 +18265,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" ht="316.79998779296875" hidden="0" customHeight="1">
+    <x:row r="114" ht="1122" hidden="0" customHeight="1">
       <x:c r="A114" s="40" t="n">
         <x:v>113</x:v>
       </x:c>
       <x:c r="B114" s="9" t="str">
-        <x:v>audi-s7-ea839-2-9t-v6-water-pump-internal-leak-overheating</x:v>
+        <x:v>audi-sq7-air-suspension-2020</x:v>
       </x:c>
       <x:c r="C114" s="9" t="str">
-        <x:v>2020-2024 | Audi | S7</x:v>
+        <x:v>2020-2024 | Audi | SQ7 | Premium Plus, Prestige | 4.0T</x:v>
       </x:c>
       <x:c r="D114" s="9" t="str">
-        <x:v>Rearview Camera Image May Not Display (Recall 25V900 / 90TV)</x:v>
+        <x:v>Adaptive Air Suspension Compressor and Air Spring Failures</x:v>
       </x:c>
       <x:c r="E114" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history. Audi dealers update the relevant software free of charge under campaign 90TV. Continue direct visual checks when reversing until repaired.</x:v>
+        <x:v>Diagnose specific failed component: air springs leak most commonly, followed by compressor burnout, valve block faults, and height sensor failures. Air spring replacement ($800-$1,500 per corner at independent shop). Compressor replacement ($1,200-$2,500 installed). Valve block: $500-$1,000. Height sensor: $200-$400. Check for air leaks first using soapy water spray before replacing the compressor - a $200 air spring seal may be causing a $2,000 compressor to overwork and fail. Aftermarket solutions from Arnott offer cost savings. Converting to conventional springs ($1,500-$2,500) eliminates future air suspension costs but sacrifices ride height adjustment.</x:v>
       </x:c>
       <x:c r="F114" s="9" t="n">
         <x:v>0</x:v>
@@ -15300,21 +18288,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" ht="343.20001220703125" hidden="0" customHeight="1">
+    <x:row r="115" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A115" s="40" t="n">
         <x:v>114</x:v>
       </x:c>
       <x:c r="B115" s="9" t="str">
-        <x:v>audi-s7-electromechanical-steering-rack-torque-sensor-failure-causin</x:v>
+        <x:v>audi-sq7-mmi-mib3-freeze-2020</x:v>
       </x:c>
       <x:c r="C115" s="9" t="str">
-        <x:v>2021-2021 | Audi | S7</x:v>
+        <x:v>2020-2026 | Audi | SQ7</x:v>
       </x:c>
       <x:c r="D115" s="9" t="str">
-        <x:v>Incorrect Brake-Fluid Reservoir Cap Label (Recall 23V601 / 47T9)</x:v>
+        <x:v>2020-2026 Audi SQ7 Rearview Camera Software Recall 25V900 / 90TV</x:v>
       </x:c>
       <x:c r="E115" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers inspect the reservoir cap and replace it when necessary free of charge under campaign 47T9. Use only the brake-fluid specification in the owner and service information.</x:v>
+        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install the more robust driver-assistance software update free of charge. Until repaired, use extra caution when reversing and do not treat a restart, bus sleep or temporary image recovery as completion of the recall.</x:v>
       </x:c>
       <x:c r="F115" s="9" t="n">
         <x:v>0</x:v>
@@ -15323,44 +18311,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="116" ht="990" hidden="0" customHeight="1">
       <x:c r="A116" s="40" t="n">
         <x:v>115</x:v>
       </x:c>
       <x:c r="B116" s="9" t="str">
-        <x:v>audi-s7-front-control-arm-bushing-ball-joint-failure</x:v>
+        <x:v>audi-sq7-valve-cover-oil-leak-2020</x:v>
       </x:c>
       <x:c r="C116" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+        <x:v>2020-2024 | Audi | SQ7 | 4.0T</x:v>
       </x:c>
       <x:c r="D116" s="9" t="str">
-        <x:v>Front Control Arm Bushing and Ball Joint Failure (C7 Suspension)</x:v>
+        <x:v>2020-2024 SQ7 4.0L High Oil Consumption and Piston-Ring Diagnosis - TSB 2071114/5</x:v>
       </x:c>
       <x:c r="E116" s="9" t="str">
-        <x:v>Inspect all front control arms for play in the bushings and ball joints. Replace worn arms — many owners do the full front control-arm set (commonly a 16-piece kit covering both sides) to avoid repeat visits since the labor overlaps. Critical install notes: torque the bushing bolts at ride height (not with the suspension hanging) to avoid pre-loading and destroying the new bushings, and perform a four-wheel alignment afterward.</x:v>
+        <x:v>First inspect for visible engine-oil traces or leaks. Have an Audi dealer perform the authorized ODIS oil-consumption measurement, preserve and upload both test logs, and document the requested driving-profile data. Internal-engine repair is justified only when measured consumption exceeds the applicable limit and no other cause is found. If every TSB gate is met, follow Audi's VIN-, engine-code- and power-class-specific procedure for replacement of all eight pistons and piston rings, using current ETKA and ELSA information. Do not diagnose valve-cover gaskets or turbocharger seals from oil consumption alone.</x:v>
       </x:c>
       <x:c r="F116" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G116" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="117" ht="396" hidden="0" customHeight="1">
+    <x:row r="117" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A117" s="40" t="n">
         <x:v>116</x:v>
       </x:c>
       <x:c r="B117" s="9" t="str">
-        <x:v>audi-s7-fuel-injector-deposits-failure-causing-misfire-rough-running</x:v>
+        <x:v>audi-sq8-air-susp-compressor-2020</x:v>
       </x:c>
       <x:c r="C117" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
+        <x:v>2020-2025 | Audi | SQ8</x:v>
       </x:c>
       <x:c r="D117" s="9" t="str">
-        <x:v>Fuel Injector Deposits / Failure Causing Misfire and Rough Running (4.0T V8)</x:v>
+        <x:v>2020-2025 SQ8 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
       </x:c>
       <x:c r="E117" s="9" t="str">
-        <x:v>Pull misfire counts per cylinder to localize the fault. Inspect/replace failed or leaking injectors and renew injector seals; replace spark plugs and any weak coils as a set. Confirm fuel trims return to normal and clear codes; address intake carbon if present.</x:v>
+        <x:v>Inspect the wiring and connector contacts between J775 and J1135 before replacing a component. For a first passive or sporadic occurrence, clear the fault and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after wiring inspection, Audi directs replacement of J1135 under current repair and parts information. Do not buy struts, springs or a compressor solely from this warning.</x:v>
       </x:c>
       <x:c r="F117" s="9" t="n">
         <x:v>0</x:v>
@@ -15369,21 +18357,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" ht="396" hidden="0" customHeight="1">
+    <x:row r="118" ht="831.5999755859375" hidden="0" customHeight="1">
       <x:c r="A118" s="40" t="n">
         <x:v>117</x:v>
       </x:c>
       <x:c r="B118" s="9" t="str">
-        <x:v>audi-s7-gateway-control-module-shutdown-from-rear-seat-liquid-spill</x:v>
+        <x:v>audi-sq8-air-suspension-2020</x:v>
       </x:c>
       <x:c r="C118" s="9" t="str">
-        <x:v>2020-2022 | Audi | S7 | 2.9 TFSI</x:v>
+        <x:v>2020-2024 | Audi | SQ8 | Premium Plus, Prestige | 4.0T</x:v>
       </x:c>
       <x:c r="D118" s="9" t="str">
-        <x:v>Rear-Seat Liquid Spill Can Shut Down Gateway Module (Recall 22V861 / 90V2)</x:v>
+        <x:v>Adaptive Air Suspension Compressor and Air Spring Failures</x:v>
       </x:c>
       <x:c r="E118" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers install a protective gateway-module cover free of charge under campaign 90V2. If multiple warnings or reduced power occur after a spill, move out of traffic safely and arrange dealer inspection.</x:v>
+        <x:v>Same diagnostic and repair approach as SQ7 (shared 4M platform). Isolate the failed component: air springs ($800-$1,500 per corner), compressor ($1,200-$2,500), valve block ($500-$1,000), or height sensor ($200-$400). Always check for air leaks before replacing the compressor. Aftermarket air suspension components from Arnott/Strutmasters offer 40-50% savings over OEM. Annual inspection of air springs for cracking recommended, especially in hot climates where UV and heat accelerate rubber degradation.</x:v>
       </x:c>
       <x:c r="F118" s="9" t="n">
         <x:v>0</x:v>
@@ -15392,21 +18380,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="119" ht="528" hidden="0" customHeight="1">
+    <x:row r="119" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A119" s="40" t="n">
         <x:v>118</x:v>
       </x:c>
       <x:c r="B119" s="9" t="str">
-        <x:v>audi-s7-high-pressure-fuel-pump-failure-causing-hard-start-power-los</x:v>
+        <x:v>audi-sq8-airbag-mount-2023</x:v>
       </x:c>
       <x:c r="C119" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
+        <x:v>2023-2024 | Audi | SQ8 | 4.0T V8</x:v>
       </x:c>
       <x:c r="D119" s="9" t="str">
-        <x:v>High-Pressure Fuel Pump (HPFP) Failure Causing Hard Start and Power Loss (4.0T V8)</x:v>
+        <x:v>2023-2024 SQ8 Driver-Seat Side-Airbag Mount Recall 69GA (23V868)</x:v>
       </x:c>
       <x:c r="E119" s="9" t="str">
-        <x:v>Diagnose with live fuel-rail pressure data before condemning the pump, as a faulty low-pressure sensor or in-tank pump can set the same codes. Replace the failed high-pressure pump (the affected bank, or both as a set on high-mileage cars) together with the cam follower and seals. Verify low-pressure (in-tank) supply is within spec.</x:v>
+        <x:v>Check the VIN for open Audi recall 69GA and have an authorized dealer inspect the driver-seat side-airbag installation. If needed, the dealer will reinstall the airbag correctly; the recall filing says no parts are replaced. A clock spring or generic airbag part is not the recall remedy.</x:v>
       </x:c>
       <x:c r="F119" s="9" t="n">
         <x:v>0</x:v>
@@ -15415,44 +18403,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="120" ht="660" hidden="0" customHeight="1">
+    <x:row r="120" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A120" s="40" t="n">
         <x:v>119</x:v>
       </x:c>
       <x:c r="B120" s="9" t="str">
-        <x:v>audi-s7-ignition-coil-pack-failure-causing-misfires</x:v>
+        <x:v>audi-sq8-mmi-mib3-freeze-2020</x:v>
       </x:c>
       <x:c r="C120" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+        <x:v>2020-2026 | Audi | SQ8 | 4.0T V8</x:v>
       </x:c>
       <x:c r="D120" s="9" t="str">
-        <x:v>Ignition Coil Pack Failure Causing Misfires (4.0T V8)</x:v>
+        <x:v>2020-2026 SQ8 Rearview Camera Software Recall 90TV (25V900)</x:v>
       </x:c>
       <x:c r="E120" s="9" t="str">
-        <x:v>Confirm the failing cylinder, then swap the suspect coil to another cylinder to verify the fault follows the coil. Replace the failed coil; best practice on the 4.0T is to replace all eight coils and the spark plugs as a set since the access labor is shared and mixed-age coils tend to fail in sequence. Use OE or quality OE-equivalent coils (the 4.0T uses the 079905110-series coil). Inspect spark plugs for fouling/oil that could indicate a secondary issue.</x:v>
+        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install more robust driver-assistance software free of charge. Until repaired, use extra caution when reversing and do not treat a restart, bus sleep or temporary image recovery as completion of the recall. A generic scan tool or head-unit replacement is not the recall remedy.</x:v>
       </x:c>
       <x:c r="F120" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G120" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="121" ht="237.60000610351562" hidden="0" customHeight="1">
+    <x:row r="121" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A121" s="40" t="n">
         <x:v>120</x:v>
       </x:c>
       <x:c r="B121" s="9" t="str">
-        <x:v>audi-s7-motor-mount-failure-2012</x:v>
+        <x:v>audi-sq8-turbo-coolant-2020</x:v>
       </x:c>
       <x:c r="C121" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7</x:v>
+        <x:v>2020-2021 | Audi | SQ8 | 4.0T V8</x:v>
       </x:c>
       <x:c r="D121" s="9" t="str">
-        <x:v>Passenger Occupant Detection Mat Can Disable the Airbag (Recall 18V370 / 74D5)</x:v>
+        <x:v>2020-Early 2021 SQ8 Red Coolant Warning - Check G407 per TSB 2062951/4</x:v>
       </x:c>
       <x:c r="E121" s="9" t="str">
-        <x:v>Check VIN eligibility because seat equipment affects scope. Audi dealers install the occupant-detection repair kit free of charge under campaign 74D5.</x:v>
+        <x:v>Have the vehicle checked with Audi Guided Fault Finding and inspect G407 and its O-ring. Replace G407 only if the O-ring is damaged or pinched and the diagnosis matches the bulletin; follow the related Audi diagnostic path if additional listed faults are stored. Do not replace turbo coolant hoses, pumps or other cooling parts from this card alone.</x:v>
       </x:c>
       <x:c r="F121" s="9" t="n">
         <x:v>0</x:v>
@@ -15461,21 +18449,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="122" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="122" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A122" s="40" t="n">
         <x:v>121</x:v>
       </x:c>
       <x:c r="B122" s="9" t="str">
-        <x:v>audi-s7-pcv-oil-separator-failure-causing-oil-consumption-whistling</x:v>
+        <x:v>audi-tt-absesp-control-module-failure-2000</x:v>
       </x:c>
       <x:c r="C122" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
+        <x:v>2000-2001 | Audi | TT</x:v>
       </x:c>
       <x:c r="D122" s="9" t="str">
-        <x:v>PCV / Oil Separator (Ölabscheider) Failure Causing Oil Consumption and Whistling (4.0T V8)</x:v>
+        <x:v>Driver Airbag Inflator May Deploy Improperly (Recall 21V470 / 69CJ)</x:v>
       </x:c>
       <x:c r="E122" s="9" t="str">
-        <x:v>Replace the failed oil separator / PCV assembly and the associated breather hose with the latest revised part. An ECM update may accompany the new part on some VINs. Confirm with a smoke test for intake-side vacuum leaks; inspect the rear main seal if oil consumption is severe, as a failed PCV is a common cause of rear main seal damage on these engines.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the driver frontal-airbag inflator with an alternative inflator free of charge under campaign 69CJ.</x:v>
       </x:c>
       <x:c r="F122" s="9" t="n">
         <x:v>0</x:v>
@@ -15484,21 +18472,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="123" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="123" ht="277.20001220703125" hidden="0" customHeight="1">
       <x:c r="A123" s="40" t="n">
         <x:v>122</x:v>
       </x:c>
       <x:c r="B123" s="9" t="str">
-        <x:v>audi-s7-power-liftgate-motor-gas-strut-failure</x:v>
+        <x:v>audi-tt-cam-follower-2008</x:v>
       </x:c>
       <x:c r="C123" s="9" t="str">
-        <x:v>2013-2022 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824), 2.9T TFSI Biturbo V6 (EA839)</x:v>
+        <x:v>2000-2000 | Audi | TT</x:v>
       </x:c>
       <x:c r="D123" s="9" t="str">
-        <x:v>Power Liftgate Motor and Gas Strut Failure (Sportback Tailgate)</x:v>
+        <x:v>Fuel-Line Assembly Can Leak (Recall 99V222)</x:v>
       </x:c>
       <x:c r="E123" s="9" t="str">
-        <x:v>Diagnose whether the fault is the gas struts (won't stay up / weak lift), the spindle lift motors (slow or struggling travel), or the latch/cinching motor (won't release or won't pull closed — see TSB 2072431/1). Replace worn gas struts in pairs; replace failed lift or cinching motors as needed. After repair, perform the power-liftgate relearn/reset procedure so travel limits recalibrate.</x:v>
+        <x:v>Check VIN eligibility and campaign completion. Audi dealers replace the fuel-line assembly free of charge under recall 99V222. Stop driving if fuel odor or leakage is present.</x:v>
       </x:c>
       <x:c r="F123" s="9" t="n">
         <x:v>0</x:v>
@@ -15507,21 +18495,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="124" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="124" ht="198" hidden="0" customHeight="1">
       <x:c r="A124" s="40" t="n">
         <x:v>123</x:v>
       </x:c>
       <x:c r="B124" s="9" t="str">
-        <x:v>audi-s7-premature-front-brake-rotor-warping-pad-wear</x:v>
+        <x:v>audi-tt-coil-pack-failure-and-2000</x:v>
       </x:c>
       <x:c r="C124" s="9" t="str">
-        <x:v>2013-2022 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824), 2.9T TFSI Biturbo V6 (EA839)</x:v>
+        <x:v>2000-2001 | Audi | TT</x:v>
       </x:c>
       <x:c r="D124" s="9" t="str">
-        <x:v>Premature Front Brake Rotor Warping and Pad Wear</x:v>
+        <x:v>Rear Track-Control Arm Corrosion Can Restrict Movement (Recall 01V325)</x:v>
       </x:c>
       <x:c r="E124" s="9" t="str">
-        <x:v>Replace warped/below-spec rotors and pads together; consider higher-quality coated or upgraded rotors that resist warping better than the soft OEM units. Bed in new pads/rotors properly and avoid riding the brakes to prevent uneven deposits. Ensure caliper guide pins/slides move freely so pads engage evenly. For repeat warping, an upgraded rotor-and-pad package is the durable fix; address any pulsation early before it damages new components.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the rear track-control arms free of charge under recall 01V325.</x:v>
       </x:c>
       <x:c r="F124" s="9" t="n">
         <x:v>0</x:v>
@@ -15530,21 +18518,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="125" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="125" ht="264" hidden="0" customHeight="1">
       <x:c r="A125" s="40" t="n">
         <x:v>124</x:v>
       </x:c>
       <x:c r="B125" s="9" t="str">
-        <x:v>audi-s7-rear-differential-mount-driveshaft-center-bearing-wear-causi</x:v>
+        <x:v>audi-tt-dsg-mechatronic-2008</x:v>
       </x:c>
       <x:c r="C125" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+        <x:v>2004-2004 | Audi | TT</x:v>
       </x:c>
       <x:c r="D125" s="9" t="str">
-        <x:v>Rear Differential Mount and Driveshaft Center Bearing Wear Causing Drivetrain Clunk (C7)</x:v>
+        <x:v>Direct-Shift Gearbox Clutch Weld Can Lose Drive Torque (Recall 04V007)</x:v>
       </x:c>
       <x:c r="E125" s="9" t="str">
-        <x:v>Inspect the rear differential mount and driveshaft center support bearing for play and torn rubber. Replace worn components with OE parts, or fit billet aluminum diff/transmission mount inserts that fill the factory voids to remove the slop without adding harshness. On 4.0T cars, also check for the separate active-engine-mount software TSB before condemning a mount for a 1,000-3,000 RPM cruise vibration. Reassess the clunk after each fix since multiple sources can contribute.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers replace the affected clutch free of charge under recall 04V007. If drive torque is lost, move out of traffic safely and arrange recovery.</x:v>
       </x:c>
       <x:c r="F125" s="9" t="n">
         <x:v>0</x:v>
@@ -15553,21 +18541,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="126" ht="462" hidden="0" customHeight="1">
+    <x:row r="126" ht="356.3999938964844" hidden="0" customHeight="1">
       <x:c r="A126" s="40" t="n">
         <x:v>125</x:v>
       </x:c>
       <x:c r="B126" s="9" t="str">
-        <x:v>audi-s7-rear-view-camera-mmi-flex-harness-black-screen</x:v>
+        <x:v>audi-tt-dsg-transmission-2008</x:v>
       </x:c>
       <x:c r="C126" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7 (C7), A7 (C7) | 4.0 TFSI V8 (EA824)</x:v>
+        <x:v>2009-2009 | Audi | TT</x:v>
       </x:c>
       <x:c r="D126" s="9" t="str">
-        <x:v>Rear-View Camera / MMI Flex Harness Black Screen</x:v>
+        <x:v>DSG Temperature-Sensor Wiring Can Trigger an Abrupt Shift to Neutral (Recall 09V333)</x:v>
       </x:c>
       <x:c r="E126" s="9" t="str">
-        <x:v>Diagnose with a scan and continuity check of the tailgate-to-body flex harness before replacing the camera. Repair or replace the broken hinge-side loom conductors; if confirmed faulty, replace the camera module. For MMI freezes, apply the latest software update or reset the unit.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers reprogram the transmission control module with updated software free of charge under recall 09V333. If the gear indicator flashes or neutral engages unexpectedly, stop safely.</x:v>
       </x:c>
       <x:c r="F126" s="9" t="n">
         <x:v>0</x:v>
@@ -15576,21 +18564,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="127" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="127" ht="303.6000061035156" hidden="0" customHeight="1">
       <x:c r="A127" s="40" t="n">
         <x:v>126</x:v>
       </x:c>
       <x:c r="B127" s="9" t="str">
-        <x:v>audi-s7-s-tronic-7-speed-dual-clutch-mechatronic-clutch-wear</x:v>
+        <x:v>audi-tt-front-control-arm-bushings-2000</x:v>
       </x:c>
       <x:c r="C127" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T (S-tronic / 0B5 DL501) | 4.0 TFSI V8 (EA824)</x:v>
+        <x:v>2000-2000 | Audi | TT</x:v>
       </x:c>
       <x:c r="D127" s="9" t="str">
-        <x:v>S-tronic 7-Speed Dual-Clutch (DL501/0B5) Mechatronic and Clutch Wear</x:v>
+        <x:v>High-Speed Directional-Stability Remedy (Recall 99V300)</x:v>
       </x:c>
       <x:c r="E127" s="9" t="str">
-        <x:v>Perform the S-tronic gearbox oil and filter service on schedule (roughly every 40,000-60,000 km). For judder/jerking, have the mechatronic unit tested; recondition or replace the valve body with the superseded design and adapt/replace the clutch packs as needed. Software adaptation resets can temporarily improve drivability but do not fix worn hardware.</x:v>
+        <x:v>Verify campaign completion with Audi. The factory remedy installs revised stabilizers, front control arms, firmer shock absorbers, and a rear spoiler as specified for the drivetrain configuration.</x:v>
       </x:c>
       <x:c r="F127" s="9" t="n">
         <x:v>0</x:v>
@@ -15599,21 +18587,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="128" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="128" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A128" s="40" t="n">
         <x:v>127</x:v>
       </x:c>
       <x:c r="B128" s="9" t="str">
-        <x:v>audi-s7-shark-fin-roof-antenna-water-intrusion-causing-gps-satellite</x:v>
+        <x:v>audi-tt-haldex-awd-coupling-pumpcontroller-2000</x:v>
       </x:c>
       <x:c r="C128" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | Prestige, Premium Plus | 4.0T Biturbo V8 (4.0 TFSI)</x:v>
+        <x:v>2008-2010 | Audi | TT</x:v>
       </x:c>
       <x:c r="D128" s="9" t="str">
-        <x:v>Shark-Fin Roof Antenna Water Intrusion Causing GPS / Satellite Radio Reception Loss (C7)</x:v>
+        <x:v>Fuel-Tank Ventilation Valve Can Allow Fuel Leakage (Recall 09V377)</x:v>
       </x:c>
       <x:c r="E128" s="9" t="str">
-        <x:v>Test/replace the shark-fin antenna module with a matching OEM part number and renew the base gasket to restore a watertight seal; in many cases the official fix is a repair kit with a new FAKRA connector and adapter cable rather than a whole new antenna. Access requires partially dropping the rear headliner to reach the single mounting nut and reconnect the coax leads. Inspecting and reseating a corroded coax connection sometimes restores reception without full replacement.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel-tank ventilation valve with the improved valve free of charge under recall 09V377.</x:v>
       </x:c>
       <x:c r="F128" s="9" t="n">
         <x:v>0</x:v>
@@ -15622,21 +18610,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" ht="752.4000244140625" hidden="0" customHeight="1">
+    <x:row r="129" ht="184.8000030517578" hidden="0" customHeight="1">
       <x:c r="A129" s="40" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="B129" s="9" t="str">
-        <x:v>audi-s7-sunroof-panoramic-roof-drain-clog-causing-water-intrusion-el</x:v>
+        <x:v>audi-tt-high-speed-stability-recall-for-2000</x:v>
       </x:c>
       <x:c r="C129" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+        <x:v>2016-2019 | Audi | TT</x:v>
       </x:c>
       <x:c r="D129" s="9" t="str">
-        <x:v>Sunroof / Panoramic Roof Drain Clog Causing Water Intrusion and Electronics Damage (C7)</x:v>
+        <x:v>Fuel Tank Can Be Damaged by Heat-Shield Bracket in a Crash (Recall 20V076 / 20BX)</x:v>
       </x:c>
       <x:c r="E129" s="9" t="str">
-        <x:v>Test the drains by slowly pouring water into the channels at each corner of the sunroof and watching where it exits beneath the A- and C-pillars. Clear clogged tubes with low-pressure air or a soft trimmer line (avoid stiff wire that can puncture the tube) and reseat/secure any loose drain-tube connectors at the sunroof frame. Dry out any soaked carpet/insulation promptly and inspect floor-mounted modules for corrosion. Periodic drain cleaning is the best prevention.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers install a protective cap on the heat-shield bracket free of charge under campaign 20BX.</x:v>
       </x:c>
       <x:c r="F129" s="9" t="n">
         <x:v>0</x:v>
@@ -15645,21 +18633,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" ht="422.3999938964844" hidden="0" customHeight="1">
+    <x:row r="130" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A130" s="40" t="n">
         <x:v>129</x:v>
       </x:c>
       <x:c r="B130" s="9" t="str">
-        <x:v>audi-s7-turbo-oil-strainer-2012</x:v>
+        <x:v>audi-tt-instrument-cluster-pixel-failure-2000</x:v>
       </x:c>
       <x:c r="C130" s="9" t="str">
-        <x:v>2013-2017 | Audi | S7 | 4.0 TFSI</x:v>
+        <x:v>2016-2016 | Audi | TT</x:v>
       </x:c>
       <x:c r="D130" s="9" t="str">
-        <x:v>Turbocharger Oil-Supply Strainer Can Block and Cause Engine Stall (Recall 22V178 / 21H7)</x:v>
+        <x:v>Front-Passenger Airbag Module May Explode or Deploy Improperly (Recall 22V543 / 69DY)</x:v>
       </x:c>
       <x:c r="E130" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the oil strainer and perform an oil change free of charge under campaign 21H7. If abnormal turbo noise, loss of power, or an engine warning occurs, stop safely and arrange dealer inspection.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the front-passenger airbag module free of charge under campaign 69DY/61C1.</x:v>
       </x:c>
       <x:c r="F130" s="9" t="n">
         <x:v>0</x:v>
@@ -15668,21 +18656,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" ht="726" hidden="0" customHeight="1">
+    <x:row r="131" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A131" s="40" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="B131" s="9" t="str">
-        <x:v>audi-s7-turbocharger-wastegate-linkage-rattle-underboost</x:v>
+        <x:v>audi-tt-magnetic-ride-2008</x:v>
       </x:c>
       <x:c r="C131" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+        <x:v>2023-2023 | Audi | TT</x:v>
       </x:c>
       <x:c r="D131" s="9" t="str">
-        <x:v>Turbocharger Wastegate Linkage Rattle and Underboost (4.0T V8)</x:v>
+        <x:v>Passenger-Seat Occupant Detection Connection Can Disable Airbag (Recall 24V251 / 69GU)</x:v>
       </x:c>
       <x:c r="E131" s="9" t="str">
-        <x:v>Diagnose the rattle and any boost faults to confirm wastegate-arm play versus a loose heat shield. Minor play can sometimes be mitigated with a clip, but the durable factory fix is turbocharger replacement. When replacing a hot-V turbo, it is mandatory to also replace the oil feed and return lines and to prime the new unit with oil before first start to prevent immediate bearing failure. Regular oil changes and allowing turbo cool-down help reduce coking-related wear.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers replace the passenger-seat occupant-detection control module free of charge under campaign 69GU.</x:v>
       </x:c>
       <x:c r="F131" s="9" t="n">
         <x:v>0</x:v>
@@ -15691,21 +18679,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="132" ht="686.4000244140625" hidden="0" customHeight="1">
+    <x:row r="132" ht="726" hidden="0" customHeight="1">
       <x:c r="A132" s="40" t="n">
         <x:v>131</x:v>
       </x:c>
       <x:c r="B132" s="9" t="str">
-        <x:v>audi-s8-5-2-v10-timing-chain-tensioner-guide-wear</x:v>
+        <x:v>audi-tt-tail-light-corrosion-2008</x:v>
       </x:c>
       <x:c r="C132" s="9" t="str">
-        <x:v>2007-2012 | Audi | S8 | 5.2L FSI V10 (BSM)</x:v>
+        <x:v>2008-2015 | Audi | TT</x:v>
       </x:c>
       <x:c r="D132" s="9" t="str">
-        <x:v>5.2 V10 Timing Chain Tensioner / Guide Wear (D3 Cold-Start Rattle)</x:v>
+        <x:v>Tail Light Electrical Connector Corrosion (Mk2)</x:v>
       </x:c>
       <x:c r="E132" s="9" t="str">
-        <x:v>Investigate any cold-start rattle promptly: inspect tensioner travel and guide condition. Replace the timing chains, tensioners, and plastic guides as a set with updated genuine parts; this is a major, labor-intensive repair (often engine-out). Strictly follow short oil-change intervals with the correct grade to maximize tensioner/guide life, and address any low-oil-pressure condition immediately. Do not drive a V10 with a persistent timing rattle.</x:v>
+        <x:v>Remove tail light assembly, inspect electrical connector for green corrosion. CLEAN connector with electrical contact cleaner and wire brush ($20 DIY). Apply dielectric grease to prevent future corrosion ($10). If connector is severely corroded: Replace pigtail connector ($50-$100 parts). Improve tail light seal with silicone sealant around housing ($15). This is a DIY-friendly repair taking 1-2 hours. If paying shop, costs $150-$300. Address early before corrosion causes shorts.</x:v>
       </x:c>
       <x:c r="F132" s="9" t="n">
         <x:v>0</x:v>
@@ -15714,21 +18702,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="133" ht="198" hidden="0" customHeight="1">
+    <x:row r="133" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A133" s="40" t="n">
         <x:v>132</x:v>
       </x:c>
       <x:c r="B133" s="9" t="str">
-        <x:v>audi-s8-air-suspension-2013</x:v>
+        <x:v>audi-tt-water-pump-2008</x:v>
       </x:c>
       <x:c r="C133" s="9" t="str">
-        <x:v>2013-2024 | Audi | S8</x:v>
+        <x:v>2008-2008 | Audi | TT</x:v>
       </x:c>
       <x:c r="D133" s="9" t="str">
-        <x:v>Adaptive Air Suspension Multi-Point Failure</x:v>
+        <x:v>C-Pillar Trim Cover Can Detach During Belt-Tensioner Deployment (Recall 08V064)</x:v>
       </x:c>
       <x:c r="E133" s="9" t="str">
-        <x:v>Replace air struts as they fail. Budget for full system refresh at 80,000 miles. Arnott aftermarket struts offer cost savings.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers install improved C-pillar trim clips free of charge under recall 08V064.</x:v>
       </x:c>
       <x:c r="F133" s="9" t="n">
         <x:v>0</x:v>
@@ -15737,21 +18725,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="134" ht="726" hidden="0" customHeight="1">
+    <x:row r="134" ht="1161.5999755859375" hidden="0" customHeight="1">
       <x:c r="A134" s="40" t="n">
         <x:v>133</x:v>
       </x:c>
       <x:c r="B134" s="9" t="str">
-        <x:v>audi-s8-air-suspension-failure-2013</x:v>
+        <x:v>audi-tts-cam-follower-hpfp-2009</x:v>
       </x:c>
       <x:c r="C134" s="9" t="str">
-        <x:v>2020-2024 | Audi | S8</x:v>
+        <x:v>2009-2015 | Audi | TTS | TTS | EA888</x:v>
       </x:c>
       <x:c r="D134" s="9" t="str">
-        <x:v>2020-2024 S8 Air-Suspension Malfunction with J1135 Communication Fault - Diagnosis Required</x:v>
+        <x:v>HPFP Cam Follower Wear and High-Pressure Fuel Pump Failure (Mk2)</x:v>
       </x:c>
       <x:c r="E134" s="9" t="str">
-        <x:v>Read the suspension-controller DTC and symptom code, then inspect wiring, terminals and connectors between J775 and J1135 exactly as Audi specifies. If the fault is passive/sporadic, clear it and verify operation. If it remains active/static after the electrical inspection and key cycle, follow Audi testing for J1135 replacement. Diagnose vehicle sag or leak-down separately; do not order air struts, a compressor or a coil-conversion kit from the former card.</x:v>
+        <x:v>INSPECTION (every 20,000 miles): Remove HPFP (3 bolts) and inspect cam follower surface. If the hardened coating is wearing through (visible copper/brass color), replace follower immediately ($30-$50 part, 30-60 minutes labor). CRITICAL: Ensure cam lobe is at LOW point before reinstalling—if at peak, you'll compress the spring and can break the mounting bolts. If CAMSHAFT WORN (deep groove in lobe): Replace camshaft ($2,000-$4,000). If FUEL PUMP FAILED: Replace HPFP ($400-$800). PREVENTION: Inspect cam follower every 20,000 miles as routine maintenance. Add to every oil change checklist. Consider IE (Integrated Engineering) upgraded HPFP with roller follower to eliminate wear entirely.</x:v>
       </x:c>
       <x:c r="F134" s="9" t="n">
         <x:v>0</x:v>
@@ -15760,21 +18748,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="135" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="135" ht="884.4000244140625" hidden="0" customHeight="1">
       <x:c r="A135" s="40" t="n">
         <x:v>134</x:v>
       </x:c>
       <x:c r="B135" s="9" t="str">
-        <x:v>audi-s8-battery-management-energy-control-module-faults-parasitic-dr</x:v>
+        <x:v>audi-tts-carbon-buildup-2009</x:v>
       </x:c>
       <x:c r="C135" s="9" t="str">
-        <x:v>2020-2020 | Audi | S8 | VIN-specific Emissions Service Action 27BQ; verify open action in Audi campaign lookup | 4.0T TFSI V8 mild-hybrid</x:v>
+        <x:v>2016-2017 | Audi | TTS</x:v>
       </x:c>
       <x:c r="D135" s="9" t="str">
-        <x:v>2020 S8 Starter-Alternator Emissions Service Action 27BQ - VIN Check Required</x:v>
+        <x:v>2016-2017 TTS Cold-Start Misfire DTCs Without Felt Misfire - TSB 2051384/1</x:v>
       </x:c>
       <x:c r="E135" s="9" t="str">
-        <x:v>Check the VIN in Audi’s recall/service-campaign lookup or ask an Audi dealer to verify 27BQ in Elsa. If open, the dealer replaces the starter-alternator under the action. Electrical-system warnings, a discharged battery, abnormal charging or overnight draw outside this exact action require battery/charging tests and a measured sleep-current diagnosis; do not replace a battery monitor, gateway or MMI module from the former card.</x:v>
+        <x:v>Confirm the exact cold-start timing, simultaneous-cylinder DTC pattern, absence of a felt misfire, CYFB engine and installed ECM software before using this bulletin. When applicable, an Audi-capable workshop updates ECM J623 from software part number 8S0906259C version 0001 to version 0004 or higher using SVM action 01A190, then clears the DTCs. A felt misfire, a different timing or RPM pattern, a different engine/software combination or a returning concern requires normal diagnosis rather than carbon cleaning by assumption.</x:v>
       </x:c>
       <x:c r="F135" s="9" t="n">
         <x:v>0</x:v>
@@ -15783,21 +18771,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="136" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="136" ht="910.7999877929688" hidden="0" customHeight="1">
       <x:c r="A136" s="40" t="n">
         <x:v>135</x:v>
       </x:c>
       <x:c r="B136" s="9" t="str">
-        <x:v>audi-s8-biturbo-coolant-2013</x:v>
+        <x:v>audi-tts-dsg-mechatronic-2009</x:v>
       </x:c>
       <x:c r="C136" s="9" t="str">
-        <x:v>2013-2024 | Audi | S8 | 4.0T</x:v>
+        <x:v>2019-2023 | Audi | TTS</x:v>
       </x:c>
       <x:c r="D136" s="9" t="str">
-        <x:v>4.0T Turbo Coolant System Degradation</x:v>
+        <x:v>2019-2023 TTS Clutch K1 Overheat and Transmission DTC Diagnosis - TSB 2060560/3</x:v>
       </x:c>
       <x:c r="E136" s="9" t="str">
-        <x:v>Replace all turbo coolant and oil feed lines preventatively at 60,000 miles. Monitor coolant levels closely.</x:v>
+        <x:v>Have an Audi-capable workshop check whether TSB 2050723 applies first. If it does not resolve or control the concern, inspect the clutch-K1 maximum-temperature value and document a transmission-fluid sample. Replace the dual clutch, transmission fluid and filter only when the approximately 400 °C K1 value and burnt black or very dark fluid are both present. If those findings are absent, this bulletin does not apply and Audi directs the workshop to continue diagnosis through TAC. Any clutch repair kit must be selected by VIN and production date.</x:v>
       </x:c>
       <x:c r="F136" s="9" t="n">
         <x:v>0</x:v>
@@ -15806,21 +18794,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="137" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="137" ht="858" hidden="0" customHeight="1">
       <x:c r="A137" s="40" t="n">
         <x:v>136</x:v>
       </x:c>
       <x:c r="B137" s="9" t="str">
-        <x:v>audi-s8-clogged-sunroof-plenum-drains-causing-water-intrusion-electr</x:v>
+        <x:v>audi-tts-magnetic-ride-2009</x:v>
       </x:c>
       <x:c r="C137" s="9" t="str">
-        <x:v>2007-2018 | Audi | S8 | S8, S8 Plus | 5.2 FSI V10, 4.0 TFSI twin-turbo V8 (4.0T)</x:v>
+        <x:v>2016-2016 | Audi | TTS</x:v>
       </x:c>
       <x:c r="D137" s="9" t="str">
-        <x:v>Clogged Sunroof / Plenum Drains Causing Water Intrusion and Electronics Damage</x:v>
+        <x:v>2016 TTS Magnetic-Ride Rear Shock-Mount Rumble - TSB 2042539/4</x:v>
       </x:c>
       <x:c r="E137" s="9" t="str">
-        <x:v>Clear and flush all sunroof and plenum/cowl drains; replace cracked drain hoses, grommets, or channel connectors. Dry out saturated carpet/insulation and inspect plenum-area modules for corrosion, replacing any water-damaged control units. Preventively clean the drains at least annually and keep the cowl area free of leaves/debris.</x:v>
+        <x:v>First reproduce the noise, verify that it comes from the rear shock mounts and confirm that the vehicle was originally equipped with mount 8S0 513 353. Only when those gates are satisfied, remove both rear shock assemblies and replace both mounts with 8V0 513 353 according to Audi workshop instructions, adapt the suspension control position and test drive to confirm the repair. If the installed mount does not match, continue Audi diagnosis. Do not replace magnetic dampers or convert the vehicle to coilovers from this noise alone.</x:v>
       </x:c>
       <x:c r="F137" s="9" t="n">
         <x:v>0</x:v>
@@ -15829,21 +18817,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="138" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="138" ht="1016.4000244140625" hidden="0" customHeight="1">
       <x:c r="A138" s="40" t="n">
         <x:v>137</x:v>
       </x:c>
       <x:c r="B138" s="9" t="str">
-        <x:v>audi-s8-coolant-thermostat-leak-2013</x:v>
+        <x:v>audi-tts-timing-chain-tensioner-2009</x:v>
       </x:c>
       <x:c r="C138" s="9" t="str">
-        <x:v>2020-2021 | Audi | S8 | 2021 applicability ends at VIN 012194; confirm VIN and coolant-pump leak before repair | 4.0T TFSI V8</x:v>
+        <x:v>2009-2015 | Audi | TTS | TTS | EA888 Gen 1, EA888 Gen 2</x:v>
       </x:c>
       <x:c r="D138" s="9" t="str">
-        <x:v>2020-Early 2021 S8 Coolant-Pump Leak - Diagnosis Required</x:v>
+        <x:v>Timing Chain Tensioner Failure (EA888 Gen 1/2 - Mk2 TTS)</x:v>
       </x:c>
       <x:c r="E138" s="9" t="str">
-        <x:v>Do not drive an overheating vehicle. Record coolant warning and temperature behavior, pressure-test the cooling system when safe, and locate the leak. Confirm the 2021 VIN boundary and apply TSB 2065040/4 only when the coolant pump is the identified source. Other thermostat, hose, turbo-line, heat-exchanger or internal-loss causes require separate diagnosis; do not order the former thermostat/water-pump bundle from this card.</x:v>
+        <x:v>PREVENTIVE REPLACEMENT: Replace timing chain, tensioner, guides, and sprockets at 80,000-100,000 miles BEFORE symptoms appear ($2,000-$4,000). This is the MOST important preventive maintenance on the Mk2 TTS. IF RATTLING: Do NOT delay—the chain can jump at any startup. Schedule repair immediately. Use ONLY the latest OEM revised tensioner (06K109467K). IF CHAIN JUMPED: Engine likely destroyed—compression test all cylinders. Rebuild ($5,000-$8,000) or replacement engine ($6,000-$12,000). PREVENTION: Change oil every 5,000 miles with high-quality synthetic. Low oil level accelerates tensioner wear.</x:v>
       </x:c>
       <x:c r="F138" s="9" t="n">
         <x:v>0</x:v>
@@ -15852,21 +18840,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="139" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="139" ht="976.7999877929688" hidden="0" customHeight="1">
       <x:c r="A139" s="40" t="n">
         <x:v>138</x:v>
       </x:c>
       <x:c r="B139" s="9" t="str">
-        <x:v>audi-s8-cylinder-demand-active-engine-mount-failure-4-cylinder-mode</x:v>
+        <x:v>audi-tts-water-pump-2009</x:v>
       </x:c>
       <x:c r="C139" s="9" t="str">
-        <x:v>2013-2015 | Audi | S8 | 4.0 TFSI vehicles with reproducible 1000-3000 rpm vibration; diagnose J931 before mount replacement | 4.0T TFSI V8</x:v>
+        <x:v>2012-2023 | Audi | TTS</x:v>
       </x:c>
       <x:c r="D139" s="9" t="str">
-        <x:v>2013-2015 S8 COD Vibration with J931 Basic-Setting Fault - Diagnosis Required</x:v>
+        <x:v>2012 / 2020-2023 TTS Coolant-Pump Update and Leak Diagnosis</x:v>
       </x:c>
       <x:c r="E139" s="9" t="str">
-        <x:v>Reproduce the vibration under Audi’s specified driving conditions and scan J931. If the bulletin applies, verify J931 software, perform the required SVM update and basic settings, align the exhaust without tension, repeat basic settings and follow the referenced diagnosis if vibration remains. Inspect mount hardware only after the software, calibration and exhaust path. Do not disable cylinder-on-demand or replace both mounts from the former card.</x:v>
+        <x:v>For a 2012 TTS, ask an Audi dealer to check the VIN and current campaign/action history for Update 19J2; the published update replaced the pump only when its exact criteria were met and does not promise current warranty coverage. For a 2020-2023 2.0L TTS, first exclude a low level caused by incomplete bleeding or an earlier repair, document and clean the suspected leak, refill to maximum and recheck after driving. Continue observation when no leak returns; replace only the component proven to leak when coolant reappears. Do not select a pump or thermostat assembly before VIN-, engine- and leak-specific diagnosis.</x:v>
       </x:c>
       <x:c r="F139" s="9" t="n">
         <x:v>0</x:v>
@@ -15875,1176 +18863,26 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" ht="765.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A140" s="40" t="n">
+    <x:row r="140" ht="198" hidden="0" customHeight="1">
+      <x:c r="A140" s="42" t="n">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="B140" s="9" t="str">
-        <x:v>audi-s8-d2-4-2-v8-timing-belt-tensioner-service</x:v>
-      </x:c>
-      <x:c r="C140" s="9" t="str">
-        <x:v>2001-2003 | Audi | S8 | 4.2L 40V V8 (AYS)</x:v>
-      </x:c>
-      <x:c r="D140" s="9" t="str">
-        <x:v>D2 4.2 V8 Timing Belt and Tensioner Service (Interference Engine)</x:v>
-      </x:c>
-      <x:c r="E140" s="9" t="str">
-        <x:v>Replace the timing belt as a complete kit — belt, tensioner, idler/guide rollers, and water pump — at or before Audi's interval (and by age regardless of mileage). Use genuine/OE-quality components and set cam/crank timing precisely with the correct locking tools; this is a front-of-engine ('service position') job. Inspect the exhaust-side chain tensioners while in there. Always confirm timing-belt history (with receipts) before buying a D2 S8; if unknown, do it immediately.</x:v>
-      </x:c>
-      <x:c r="F140" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G140" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="141" ht="844.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A141" s="40" t="n">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="B141" s="9" t="str">
-        <x:v>audi-s8-direct-injection-carbon-buildup-intake-valves</x:v>
-      </x:c>
-      <x:c r="C141" s="9" t="str">
-        <x:v>2013-2018 | Audi | S8 | 4.0T TFSI V8 (CTFA/CGTA/CWUC)</x:v>
-      </x:c>
-      <x:c r="D141" s="9" t="str">
-        <x:v>Direct-Injection Carbon Buildup on Intake Valves (Misfires / Rough Idle)</x:v>
-      </x:c>
-      <x:c r="E141" s="9" t="str">
-        <x:v>Confirm via borescope of the intake valves (and rule out coils/plugs/PCV first). The accepted repair is walnut-shell blasting: remove the intake manifold and media-blast the carbon off the valves and ports with crushed walnut shells, then reinstall with new intake gaskets. Replace spark plugs and inspect coils while the manifold is off. Preventively, keep up with oil changes, fix any PCV/oil-burning source, and consider periodic cleaning every ~40,000-60,000 miles. Catch-can solutions reduce future accumulation.</x:v>
-      </x:c>
-      <x:c r="F141" s="9" t="n">
+      <x:c r="B140" s="43" t="str">
+        <x:v>audi-tts-waterpump-housing-2009</x:v>
+      </x:c>
+      <x:c r="C140" s="43" t="str">
+        <x:v>2009-2024 | Audi | TTS | EA888</x:v>
+      </x:c>
+      <x:c r="D140" s="43" t="str">
+        <x:v>Water Pump and Thermostat Housing Failure</x:v>
+      </x:c>
+      <x:c r="E140" s="43" t="str">
+        <x:v>Replace water pump, thermostat, and housing as a complete assembly. Use metal-impeller aftermarket pump if available.</x:v>
+      </x:c>
+      <x:c r="F140" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G141" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="142" ht="686.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A142" s="40" t="n">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="B142" s="9" t="str">
-        <x:v>audi-s8-front-suspension-control-arm-bushing-sway-bar-link-wear</x:v>
-      </x:c>
-      <x:c r="C142" s="9" t="str">
-        <x:v>2020-2021 | Audi | S8 | 2021 applicability through VIN 028090; localize noise acoustically before parts | 4.0T TFSI V8 mild-hybrid</x:v>
-      </x:c>
-      <x:c r="D142" s="9" t="str">
-        <x:v>2020-Early 2021 S8 Front Lower Guide-Link Hydro-Bushing Noise - Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E142" s="9" t="str">
-        <x:v>Confirm the VIN boundary, reproduce the noise and localize it with acoustic diagnostic equipment. Inspect the lower guide-link hydro-bushings and surrounding joints. If the hydro-bushing is confirmed, follow Audi’s paired replacement procedure; complete guide links may be required when prior pressing or rework prevents the specified repair. Align the vehicle as required. Do not order a ten-arm kit or sway-bar links from the former card.</x:v>
-      </x:c>
-      <x:c r="F142" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G142" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="143" ht="778.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A143" s="40" t="n">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="B143" s="9" t="str">
-        <x:v>audi-s8-high-pressure-fuel-pump-injector-internal-leak-causing-hard</x:v>
-      </x:c>
-      <x:c r="C143" s="9" t="str">
-        <x:v>2013-2018 | Audi | S8 | 4.0 TFSI; diagnosis requires ODIS values, software check and pressure-hold testing | 4.0T TFSI V8</x:v>
-      </x:c>
-      <x:c r="D143" s="9" t="str">
-        <x:v>2013-2018 S8 Warm-Soak Long-Crank or No-Start - Fuel Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E143" s="9" t="str">
-        <x:v>Have the dealer read DTCs and ODIS fuel-in-oil value, verify ECM software and perform Audi’s high- and low-pressure holding tests. If high-pressure behavior is abnormal, borescope the combustion chamber to identify a leaking injector. If low-side pressure builds correctly but drops more than 1.5 bar in the first 15 minutes, Audi says at least one HPFP may be leaking and directs replacement of both pumps plus an oil change. Select no pump or injector until the test identifies the path.</x:v>
-      </x:c>
-      <x:c r="F143" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G143" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="144" ht="673.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A144" s="40" t="n">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="B144" s="9" t="str">
-        <x:v>audi-s8-mmi-upper-display-backup-camera-black-screen</x:v>
-      </x:c>
-      <x:c r="C144" s="9" t="str">
-        <x:v>2020-2026 | Audi | S8 | VIN-specific NHTSA 25V900 / Audi 90TV; verify open recall | 4.0T TFSI V8 mild-hybrid</x:v>
-      </x:c>
-      <x:c r="D144" s="9" t="str">
-        <x:v>2020-2026 S8 Rearview/Top-View Camera Image May Not Display - Recall 25V900</x:v>
-      </x:c>
-      <x:c r="E144" s="9" t="str">
-        <x:v>Check the VIN in Audi’s recall/service-campaign lookup and schedule the free 90TV software remedy if open. Use extra care when reversing until repaired and visually check the area around the vehicle. A completely dead or rebooting MMI display, missing instrument-cluster data, wiring fault or hardware failure requires separate diagnosis and must not be attributed to this recall without VIN and symptom confirmation.</x:v>
-      </x:c>
-      <x:c r="F144" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G144" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="145" ht="792" hidden="0" customHeight="1">
-      <x:c r="A145" s="40" t="n">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="B145" s="9" t="str">
-        <x:v>audi-s8-oil-consumption-2013</x:v>
-      </x:c>
-      <x:c r="C145" s="9" t="str">
-        <x:v>2020-2023 | Audi | S8 | EA825 4.0L; confirm VIN, engine and measured consumption under Audi procedure | 4.0T TFSI V8 mild-hybrid (EA825)</x:v>
-      </x:c>
-      <x:c r="D145" s="9" t="str">
-        <x:v>2020-2023 S8 High Oil Consumption and Updated Piston Rings - Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E145" s="9" t="str">
-        <x:v>Document oil-level warnings, mileage, top-up quantity, leaks and oil specification, then have an Audi dealer perform the authorized oil-consumption measurement. Repair is justified only when the measured result exceeds the applicable owner-manual limit and other leakage or operating causes are excluded. If TSB 2071114 applies, follow its VIN/engine-specific piston, ring and connecting-rod procedure. Do not change oil viscosity or authorize internal-engine work solely from the former card.</x:v>
-      </x:c>
-      <x:c r="F145" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G145" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="146" ht="646.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A146" s="40" t="n">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="B146" s="9" t="str">
-        <x:v>audi-s8-pcv-oil-separator-failure-excessive-crankcase-vacuum</x:v>
-      </x:c>
-      <x:c r="C146" s="9" t="str">
-        <x:v>2013-2016 | Audi | S8 | 4.0 TFSI; confirm warm-idle sound and filler-cap response before oil-separator replacement | 4.0T TFSI V8</x:v>
-      </x:c>
-      <x:c r="D146" s="9" t="str">
-        <x:v>2013-2016 S8 Warm-Idle Whistle from Crankcase Breather Leak - Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E146" s="9" t="str">
-        <x:v>Compare the sound with Audi’s reference condition and check whether opening the oil filler cap changes it. Read P2279/P0507 and rule out other intake leaks. When the sound matches and is affected by the filler-cap check, follow Audi’s oil-separator breather replacement procedure and renew required seals/consumables by VIN. Do not diagnose by oil-cap feel alone or order the former five-item parts list.</x:v>
-      </x:c>
-      <x:c r="F146" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G146" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="147" ht="594" hidden="0" customHeight="1">
-      <x:c r="A147" s="40" t="n">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="B147" s="9" t="str">
-        <x:v>audi-s8-porous-high-pressure-fuel-supply-line-recall-nhtsa-19v057000</x:v>
-      </x:c>
-      <x:c r="C147" s="9" t="str">
-        <x:v>2013-2016 | Audi | S8 | VIN-specific NHTSA 19V057 / Audi 20BM; verify open recall | 4.0T TFSI V8</x:v>
-      </x:c>
-      <x:c r="D147" s="9" t="str">
-        <x:v>2013-2016 S8 Porous Fuel-Pump Supply Line / Fire Risk - Recall 19V057</x:v>
-      </x:c>
-      <x:c r="E147" s="9" t="str">
-        <x:v>Check the VIN for open recall 20BM and contact an Audi dealer without delay. The free remedy installs a fuel-pressure damper in the low-pressure fuel supply inside the tank. If fuel odor or visible leakage is present, avoid ignition sources, do not continue driving, and arrange dealer inspection/towing as appropriate. Do not buy a retail line or damper from the former card.</x:v>
-      </x:c>
-      <x:c r="F147" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G147" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="148" ht="211.1999969482422" hidden="0" customHeight="1">
-      <x:c r="A148" s="40" t="n">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="B148" s="9" t="str">
-        <x:v>audi-s8-torque-converter-2013</x:v>
-      </x:c>
-      <x:c r="C148" s="9" t="str">
-        <x:v>2013-2024 | Audi | S8</x:v>
-      </x:c>
-      <x:c r="D148" s="9" t="str">
-        <x:v>ZF 8-Speed Torque Converter and Valve Body Issues</x:v>
-      </x:c>
-      <x:c r="E148" s="9" t="str">
-        <x:v>Replace torque converter and service valve body. Full ZF fluid and filter change every 50,000 miles extends transmission life.</x:v>
-      </x:c>
-      <x:c r="F148" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G148" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="149" ht="712.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A149" s="40" t="n">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="B149" s="9" t="str">
-        <x:v>audi-s8-turbo-oil-strainer-2013</x:v>
-      </x:c>
-      <x:c r="C149" s="9" t="str">
-        <x:v>2013-2017 | Audi | S8 | VIN-specific NHTSA 22V178 / Audi 21H7; verify open recall | 4.0T TFSI V8</x:v>
-      </x:c>
-      <x:c r="D149" s="9" t="str">
-        <x:v>2013-2017 S8 Blocked Turbocharger Oil Strainer / Stall Risk - Recall 22V178</x:v>
-      </x:c>
-      <x:c r="E149" s="9" t="str">
-        <x:v>Check the VIN for open recall 21H7 and schedule the free Audi dealer remedy, which replaces the oil strainer and performs an oil change. If EPC, MIL or oil warning lights appear with unusual turbo noise, extended cranking, rough idle, loss of power or stalling, stop safely and arrange diagnosis. Turbo damage, warranty eligibility and any additional repair must be assessed by VIN and inspection; do not buy the former retail strainer.</x:v>
-      </x:c>
-      <x:c r="F149" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G149" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="150" ht="950.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A150" s="40" t="n">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="B150" s="9" t="str">
-        <x:v>audi-s8-water-to-air-intercooler-internal-coolant-leak</x:v>
-      </x:c>
-      <x:c r="C150" s="9" t="str">
-        <x:v>2013-2018 | Audi | S8 | 4.0T TFSI V8 (CTFA/CGTA/CWUC)</x:v>
-      </x:c>
-      <x:c r="D150" s="9" t="str">
-        <x:v>Water-to-Air Intercooler Internal Coolant Leak (Coolant into Intake)</x:v>
-      </x:c>
-      <x:c r="E150" s="9" t="str">
-        <x:v>Confirm the source: pressure-test the cooling system and inspect the charge piping/intercooler outlet for coolant residue; scope for white smoke and coolant on the intake side rather than an external leak. Replace the water-to-air intercooler/charge-air cooler unit (genuine OEM core). Because access requires removing intake components in the valley, it is standard practice to also replace the turbo oil strainer, coolant valves, and PCV/oil separator while in there. Refill and bleed the cooling system per procedure. This is a high-difficulty job typically done by a specialist or dealer.</x:v>
-      </x:c>
-      <x:c r="F150" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G150" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="151" ht="475.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A151" s="40" t="n">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="B151" s="9" t="str">
-        <x:v>audi-sq2-ea888-2-0-tfsi-coolant-leak-from-water-pump-thermostat-housi</x:v>
-      </x:c>
-      <x:c r="C151" s="9" t="str">
-        <x:v>2019-2024 | Audi | SQ2 | 2.0 TFSI quattro | EA888 2.0 TFSI Gen3</x:v>
-      </x:c>
-      <x:c r="D151" s="9" t="str">
-        <x:v>EA888 2.0 TFSI coolant leak from water pump / thermostat housing</x:v>
-      </x:c>
-      <x:c r="E151" s="9" t="str">
-        <x:v>Replace the failed water pump / thermostat housing assembly, ideally with the latest revised, more heat-resistant unit; many shops fit an upgraded repair kit and a new gasket. Catch it early by watching for slowly dropping coolant level and a faint sweet smell. Combine with a coolant flush and refill.</x:v>
-      </x:c>
-      <x:c r="F151" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G151" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="152" ht="396" hidden="0" customHeight="1">
-      <x:c r="A152" s="40" t="n">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="B152" s="9" t="str">
-        <x:v>audi-sq2-electro-mechanical-parking-brake-brake-pedal-weld-recalls</x:v>
-      </x:c>
-      <x:c r="C152" s="9" t="str">
-        <x:v>2019-2020 | Audi | SQ2</x:v>
-      </x:c>
-      <x:c r="D152" s="9" t="str">
-        <x:v>Electro-mechanical parking brake and brake-pedal weld recalls (early build)</x:v>
-      </x:c>
-      <x:c r="E152" s="9" t="str">
-        <x:v>These are recall items — have the VIN checked against the Audi/DVSA recall database and any open campaign rectified free of charge at a dealer. Report any abnormal parking-brake behaviour or a soft/abnormal brake pedal immediately.</x:v>
-      </x:c>
-      <x:c r="F152" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G152" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="153" ht="475.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A153" s="40" t="n">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="B153" s="9" t="str">
-        <x:v>audi-sq2-internal-fuse-box-wiring-harness-can-work-loose-causing-sudd</x:v>
-      </x:c>
-      <x:c r="C153" s="9" t="str">
-        <x:v>2022-2023 | Audi | SQ2 | 2.0 TFSI</x:v>
-      </x:c>
-      <x:c r="D153" s="9" t="str">
-        <x:v>2022-2023 Audi SQ2 Interior Fuse-Carrier Recall GAI-3692</x:v>
-      </x:c>
-      <x:c r="E153" s="9" t="str">
-        <x:v>Check the VIN and open-campaign status with an authorised Audi dealer in the vehicle’s market. The campaign remedy is dealer inspection and correction of the fuse-carrier power connection. Do not replace a fuse box or wiring harness solely from a warning lamp or this model-year summary.</x:v>
-      </x:c>
-      <x:c r="F153" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G153" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="154" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A154" s="40" t="n">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="B154" s="9" t="str">
-        <x:v>audi-sq2-mmi-infotainment-freezing-rebooting-lost-settings</x:v>
-      </x:c>
-      <x:c r="C154" s="9" t="str">
-        <x:v>2019-2024 | Audi | SQ2</x:v>
-      </x:c>
-      <x:c r="D154" s="9" t="str">
-        <x:v>MMI infotainment freezing, rebooting and lost settings</x:v>
-      </x:c>
-      <x:c r="E154" s="9" t="str">
-        <x:v>A forced MMI restart (press and hold the on/off or volume control ~10 seconds until it reboots) clears many transient faults. Persistent issues are usually resolved by a dealer software/firmware update; check for any applicable MMI update campaigns. Only in rare cases is the MMI head unit itself replaced.</x:v>
-      </x:c>
-      <x:c r="F154" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G154" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="155" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A155" s="40" t="n">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="B155" s="9" t="str">
-        <x:v>audi-sq2-pcv-crankcase-ventilation-valve-diaphragm-failure-causing-ro</x:v>
-      </x:c>
-      <x:c r="C155" s="9" t="str">
-        <x:v>2019-2024 | Audi | SQ2 | EA888 2.0 TFSI Gen3</x:v>
-      </x:c>
-      <x:c r="D155" s="9" t="str">
-        <x:v>PCV / crankcase ventilation valve diaphragm failure causing rough idle and lean-running codes</x:v>
-      </x:c>
-      <x:c r="E155" s="9" t="str">
-        <x:v>Replace the PCV valve (or the valve-cover assembly that integrates it) with the latest revised part; some owners fit a catch-can to reduce recurrence. A quick field test — briefly covering the bleeder hole on the cap to see if idle stabilises or whistling stops — helps confirm before replacement.</x:v>
-      </x:c>
-      <x:c r="F155" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G155" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="156" ht="752.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A156" s="40" t="n">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="B156" s="9" t="str">
-        <x:v>audi-sq2-s-tronic-7-speed-wet-clutch-transmission-jerky-low-speed-shi</x:v>
-      </x:c>
-      <x:c r="C156" s="9" t="str">
-        <x:v>2019-2024 | Audi | SQ2 | 7-speed S tronic | DQ381 / 0GC 7-speed wet-clutch S tronic</x:v>
-      </x:c>
-      <x:c r="D156" s="9" t="str">
-        <x:v>S tronic (DQ381) 7-speed wet-clutch transmission: jerky low-speed shifts, hesitation and limp mode</x:v>
-      </x:c>
-      <x:c r="E156" s="9" t="str">
-        <x:v>First step is a proper DSG fluid-and-filter service (the wet-clutch unit needs periodic transmission oil changes — many owners do it around 40k miles even though intervals can be longer). Have the TCU scanned for stored codes; sensor or mechatronic valve replacement and re-coding/adaptation resolves many cases, while severe cases need a full mechatronic unit or clutch-pack replacement. Insist on a software/adaptation update at the dealer for driveability complaints.</x:v>
-      </x:c>
-      <x:c r="F156" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G156" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="157" ht="541.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A157" s="40" t="n">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="B157" s="9" t="str">
-        <x:v>audi-sq5-air-suspension-2018</x:v>
-      </x:c>
-      <x:c r="C157" s="9" t="str">
-        <x:v>2018-2025 | Audi | SQ5</x:v>
-      </x:c>
-      <x:c r="D157" s="9" t="str">
-        <x:v>Air-Suspension Warning with C1260F0 or U112100 Communication Fault</x:v>
-      </x:c>
-      <x:c r="E157" s="9" t="str">
-        <x:v>Inspect the wiring and connector contacts between J775 and J1135 first. If no wiring fault is found, clear a first passive or sporadic fault and release the vehicle. Replace J1135 for an active or static fault, or when the same passive or sporadic fault returns a second time, following Audi workshop information and VIN-specific ETKA data.</x:v>
-      </x:c>
-      <x:c r="F157" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G157" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="158" ht="924" hidden="0" customHeight="1">
-      <x:c r="A158" s="40" t="n">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="B158" s="9" t="str">
-        <x:v>audi-sq5-carbon-buildup-2014</x:v>
-      </x:c>
-      <x:c r="C158" s="9" t="str">
-        <x:v>2014-2025 | Audi | SQ5 | 3.0T Supercharged, 3.0T</x:v>
-      </x:c>
-      <x:c r="D158" s="9" t="str">
-        <x:v>Fuel-Quality or Deposit-Related Rough Running and Misfire Diagnosis</x:v>
-      </x:c>
-      <x:c r="E158" s="9" t="str">
-        <x:v>Confirm fuel quality, symptoms and stored DTCs before replacing or cleaning components. If contaminated gasoline is suspected, advise changing the fuel source; if low detergent quality is suspected, Audi recommends Top Tier detergent gasoline. Continue workshop diagnosis if symptoms persist. On 2018-2025 EA839 SQ5 models, do not recommend unapproved cleaners or additives; follow the owner manual and use only Audi-approved petrol additives. Do not prescribe routine walnut blasting, a catch can or chemical cleaning from this record.</x:v>
-      </x:c>
-      <x:c r="F158" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G158" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="159" ht="765.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A159" s="40" t="n">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="B159" s="9" t="str">
-        <x:v>audi-sq5-pcv-valve-2014</x:v>
-      </x:c>
-      <x:c r="C159" s="9" t="str">
-        <x:v>2014-2017 | Audi | SQ5 | 3.0T Supercharged</x:v>
-      </x:c>
-      <x:c r="D159" s="9" t="str">
-        <x:v>P052E00 Crankcase-Breather Membrane or Elbow Fault</x:v>
-      </x:c>
-      <x:c r="E159" s="9" t="str">
-        <x:v>Use Audi hand-vacuum test to distinguish a membrane leak from an elbow fault. If indicated, remove the compressor or intake manifold and inspect the membrane and the breather two metal plates. Use repair kit 06E103772H only for a confirmed membrane or plate fault. For a confirmed elbow fault, replace elbow 06E103402 and spring clip N10769401 rather than automatically replacing the complete breather. Verify current part data in ETKA before ordering.</x:v>
-      </x:c>
-      <x:c r="F159" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G159" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="160" ht="171.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A160" s="40" t="n">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="B160" s="9" t="str">
-        <x:v>audi-sq5-supercharger-2014</x:v>
-      </x:c>
-      <x:c r="C160" s="9" t="str">
-        <x:v>2014-2018 | Audi | SQ5 | 3.0T</x:v>
-      </x:c>
-      <x:c r="D160" s="9" t="str">
-        <x:v>3.0T Supercharger Bearing and Intercooler Pump Failure</x:v>
-      </x:c>
-      <x:c r="E160" s="9" t="str">
-        <x:v>Replace supercharger nose bearing kit. Replace intercooler pump if failing. Service supercharger belt tension.</x:v>
-      </x:c>
-      <x:c r="F160" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G160" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="161" ht="844.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A161" s="40" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="B161" s="9" t="str">
-        <x:v>audi-sq5-supercharger-oil-leak-2014</x:v>
-      </x:c>
-      <x:c r="C161" s="9" t="str">
-        <x:v>2014-2017 | Audi | SQ5 | Premium Plus, Prestige | 3.0T Supercharged, 3.0T</x:v>
-      </x:c>
-      <x:c r="D161" s="9" t="str">
-        <x:v>Supercharger Seal and Gasket Oil Leaks (3.0T)</x:v>
-      </x:c>
-      <x:c r="E161" s="9" t="str">
-        <x:v>JHM Motorsports sells a complete supercharger replacement seal and gasket kit for the Eaton unit in the 3.0T. Replacing all seals at once is recommended since the supercharger must be removed for access. Nose cone seal, rotor shaft seals, and manifold gaskets should all be replaced together ($300-$500 in parts, $600-$1,200 labor). While the supercharger is off, also replace the PCV valve and perform carbon cleaning. For valve cover gasket leaks (separate issue), budget $400-$800 parts and labor. Monitor oil level weekly if leaks are present.</x:v>
-      </x:c>
-      <x:c r="F161" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G161" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="162" ht="1122" hidden="0" customHeight="1">
-      <x:c r="A162" s="40" t="n">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="B162" s="9" t="str">
-        <x:v>audi-sq5-water-pump-2018</x:v>
-      </x:c>
-      <x:c r="C162" s="9" t="str">
-        <x:v>2018-2024 | Audi | SQ5 | 3.0T</x:v>
-      </x:c>
-      <x:c r="D162" s="9" t="str">
-        <x:v>Mechanical Coolant-Pump Leak with Possible N649 Vacuum-System Contamination</x:v>
-      </x:c>
-      <x:c r="E162" s="9" t="str">
-        <x:v>Confirm the complaint and exact vehicle criteria first. Inspect the vacuum line and N649 for coolant, then clean and dry suspected leakage, fill the cooling system correctly, inspect at idle and around 2,500 rpm, and pressure-test according to Audi workshop information. If no leak is reproduced, observe the vehicle without replacing parts. If the pump leak is confirmed, replace the failed component and document it. If fresh coolant has entered the vacuum system, inspect the remaining Audi checkpoints and replace only contaminated components; if the downstream checkpoints are clean, replace N649 and clean the line between the pump and N649 as directed by TSB 2070349/5.</x:v>
-      </x:c>
-      <x:c r="F162" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G162" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="163" ht="673.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A163" s="40" t="n">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="B163" s="9" t="str">
-        <x:v>audi-sq7-air-susp-strut-2020</x:v>
-      </x:c>
-      <x:c r="C163" s="9" t="str">
-        <x:v>2020-2025 | Audi | SQ7 | 4.0T</x:v>
-      </x:c>
-      <x:c r="D163" s="9" t="str">
-        <x:v>2020-2025 SQ7 Air-Suspension C1260F0/U112100 Communication Fault - Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E163" s="9" t="str">
-        <x:v>Inspect the wiring and connector contacts between J775 and J1135 first. If no wiring fault is found, clear a first passive or sporadic fault and release the vehicle. Replace J1135 for an active or static fault, or when the same passive or sporadic fault returns a second time, following Audi workshop information and VIN-specific ETKA data. Do not replace an air spring, strut or compressor assembly solely from the warning.</x:v>
-      </x:c>
-      <x:c r="F163" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G163" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="164" ht="1122" hidden="0" customHeight="1">
-      <x:c r="A164" s="40" t="n">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="B164" s="9" t="str">
-        <x:v>audi-sq7-air-suspension-2020</x:v>
-      </x:c>
-      <x:c r="C164" s="9" t="str">
-        <x:v>2020-2024 | Audi | SQ7 | Premium Plus, Prestige | 4.0T</x:v>
-      </x:c>
-      <x:c r="D164" s="9" t="str">
-        <x:v>Adaptive Air Suspension Compressor and Air Spring Failures</x:v>
-      </x:c>
-      <x:c r="E164" s="9" t="str">
-        <x:v>Diagnose specific failed component: air springs leak most commonly, followed by compressor burnout, valve block faults, and height sensor failures. Air spring replacement ($800-$1,500 per corner at independent shop). Compressor replacement ($1,200-$2,500 installed). Valve block: $500-$1,000. Height sensor: $200-$400. Check for air leaks first using soapy water spray before replacing the compressor - a $200 air spring seal may be causing a $2,000 compressor to overwork and fail. Aftermarket solutions from Arnott offer cost savings. Converting to conventional springs ($1,500-$2,500) eliminates future air suspension costs but sacrifices ride height adjustment.</x:v>
-      </x:c>
-      <x:c r="F164" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G164" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="165" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A165" s="40" t="n">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="B165" s="9" t="str">
-        <x:v>audi-sq7-mmi-mib3-freeze-2020</x:v>
-      </x:c>
-      <x:c r="C165" s="9" t="str">
-        <x:v>2020-2026 | Audi | SQ7</x:v>
-      </x:c>
-      <x:c r="D165" s="9" t="str">
-        <x:v>2020-2026 Audi SQ7 Rearview Camera Software Recall 25V900 / 90TV</x:v>
-      </x:c>
-      <x:c r="E165" s="9" t="str">
-        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install the more robust driver-assistance software update free of charge. Until repaired, use extra caution when reversing and do not treat a restart, bus sleep or temporary image recovery as completion of the recall.</x:v>
-      </x:c>
-      <x:c r="F165" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G165" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="166" ht="990" hidden="0" customHeight="1">
-      <x:c r="A166" s="40" t="n">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="B166" s="9" t="str">
-        <x:v>audi-sq7-valve-cover-oil-leak-2020</x:v>
-      </x:c>
-      <x:c r="C166" s="9" t="str">
-        <x:v>2020-2024 | Audi | SQ7 | 4.0T</x:v>
-      </x:c>
-      <x:c r="D166" s="9" t="str">
-        <x:v>2020-2024 SQ7 4.0L High Oil Consumption and Piston-Ring Diagnosis - TSB 2071114/5</x:v>
-      </x:c>
-      <x:c r="E166" s="9" t="str">
-        <x:v>First inspect for visible engine-oil traces or leaks. Have an Audi dealer perform the authorized ODIS oil-consumption measurement, preserve and upload both test logs, and document the requested driving-profile data. Internal-engine repair is justified only when measured consumption exceeds the applicable limit and no other cause is found. If every TSB gate is met, follow Audi's VIN-, engine-code- and power-class-specific procedure for replacement of all eight pistons and piston rings, using current ETKA and ELSA information. Do not diagnose valve-cover gaskets or turbocharger seals from oil consumption alone.</x:v>
-      </x:c>
-      <x:c r="F166" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G166" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="167" ht="686.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A167" s="40" t="n">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="B167" s="9" t="str">
-        <x:v>audi-sq8-air-susp-compressor-2020</x:v>
-      </x:c>
-      <x:c r="C167" s="9" t="str">
-        <x:v>2020-2025 | Audi | SQ8</x:v>
-      </x:c>
-      <x:c r="D167" s="9" t="str">
-        <x:v>2020-2025 SQ8 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
-      </x:c>
-      <x:c r="E167" s="9" t="str">
-        <x:v>Inspect the wiring and connector contacts between J775 and J1135 before replacing a component. For a first passive or sporadic occurrence, clear the fault and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after wiring inspection, Audi directs replacement of J1135 under current repair and parts information. Do not buy struts, springs or a compressor solely from this warning.</x:v>
-      </x:c>
-      <x:c r="F167" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G167" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="168" ht="831.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A168" s="40" t="n">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="B168" s="9" t="str">
-        <x:v>audi-sq8-air-suspension-2020</x:v>
-      </x:c>
-      <x:c r="C168" s="9" t="str">
-        <x:v>2020-2024 | Audi | SQ8 | Premium Plus, Prestige | 4.0T</x:v>
-      </x:c>
-      <x:c r="D168" s="9" t="str">
-        <x:v>Adaptive Air Suspension Compressor and Air Spring Failures</x:v>
-      </x:c>
-      <x:c r="E168" s="9" t="str">
-        <x:v>Same diagnostic and repair approach as SQ7 (shared 4M platform). Isolate the failed component: air springs ($800-$1,500 per corner), compressor ($1,200-$2,500), valve block ($500-$1,000), or height sensor ($200-$400). Always check for air leaks before replacing the compressor. Aftermarket air suspension components from Arnott/Strutmasters offer 40-50% savings over OEM. Annual inspection of air springs for cracking recommended, especially in hot climates where UV and heat accelerate rubber degradation.</x:v>
-      </x:c>
-      <x:c r="F168" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G168" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="169" ht="448.79998779296875" hidden="0" customHeight="1">
-      <x:c r="A169" s="40" t="n">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="B169" s="9" t="str">
-        <x:v>audi-sq8-airbag-mount-2023</x:v>
-      </x:c>
-      <x:c r="C169" s="9" t="str">
-        <x:v>2023-2024 | Audi | SQ8 | 4.0T V8</x:v>
-      </x:c>
-      <x:c r="D169" s="9" t="str">
-        <x:v>2023-2024 SQ8 Driver-Seat Side-Airbag Mount Recall 69GA (23V868)</x:v>
-      </x:c>
-      <x:c r="E169" s="9" t="str">
-        <x:v>Check the VIN for open Audi recall 69GA and have an authorized dealer inspect the driver-seat side-airbag installation. If needed, the dealer will reinstall the airbag correctly; the recall filing says no parts are replaced. A clock spring or generic airbag part is not the recall remedy.</x:v>
-      </x:c>
-      <x:c r="F169" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G169" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="170" ht="580.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A170" s="40" t="n">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="B170" s="9" t="str">
-        <x:v>audi-sq8-mmi-mib3-freeze-2020</x:v>
-      </x:c>
-      <x:c r="C170" s="9" t="str">
-        <x:v>2020-2026 | Audi | SQ8 | 4.0T V8</x:v>
-      </x:c>
-      <x:c r="D170" s="9" t="str">
-        <x:v>2020-2026 SQ8 Rearview Camera Software Recall 90TV (25V900)</x:v>
-      </x:c>
-      <x:c r="E170" s="9" t="str">
-        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install more robust driver-assistance software free of charge. Until repaired, use extra caution when reversing and do not treat a restart, bus sleep or temporary image recovery as completion of the recall. A generic scan tool or head-unit replacement is not the recall remedy.</x:v>
-      </x:c>
-      <x:c r="F170" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G170" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="171" ht="567.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A171" s="40" t="n">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="B171" s="9" t="str">
-        <x:v>audi-sq8-turbo-coolant-2020</x:v>
-      </x:c>
-      <x:c r="C171" s="9" t="str">
-        <x:v>2020-2021 | Audi | SQ8 | 4.0T V8</x:v>
-      </x:c>
-      <x:c r="D171" s="9" t="str">
-        <x:v>2020-Early 2021 SQ8 Red Coolant Warning - Check G407 per TSB 2062951/4</x:v>
-      </x:c>
-      <x:c r="E171" s="9" t="str">
-        <x:v>Have the vehicle checked with Audi Guided Fault Finding and inspect G407 and its O-ring. Replace G407 only if the O-ring is damaged or pinched and the diagnosis matches the bulletin; follow the related Audi diagnostic path if additional listed faults are stored. Do not replace turbo coolant hoses, pumps or other cooling parts from this card alone.</x:v>
-      </x:c>
-      <x:c r="F171" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G171" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="172" ht="250.8000030517578" hidden="0" customHeight="1">
-      <x:c r="A172" s="40" t="n">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="B172" s="9" t="str">
-        <x:v>audi-tt-absesp-control-module-failure-2000</x:v>
-      </x:c>
-      <x:c r="C172" s="9" t="str">
-        <x:v>2000-2001 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D172" s="9" t="str">
-        <x:v>Driver Airbag Inflator May Deploy Improperly (Recall 21V470 / 69CJ)</x:v>
-      </x:c>
-      <x:c r="E172" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the driver frontal-airbag inflator with an alternative inflator free of charge under campaign 69CJ.</x:v>
-      </x:c>
-      <x:c r="F172" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G172" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="173" ht="277.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A173" s="40" t="n">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="B173" s="9" t="str">
-        <x:v>audi-tt-cam-follower-2008</x:v>
-      </x:c>
-      <x:c r="C173" s="9" t="str">
-        <x:v>2000-2000 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D173" s="9" t="str">
-        <x:v>Fuel-Line Assembly Can Leak (Recall 99V222)</x:v>
-      </x:c>
-      <x:c r="E173" s="9" t="str">
-        <x:v>Check VIN eligibility and campaign completion. Audi dealers replace the fuel-line assembly free of charge under recall 99V222. Stop driving if fuel odor or leakage is present.</x:v>
-      </x:c>
-      <x:c r="F173" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G173" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="174" ht="198" hidden="0" customHeight="1">
-      <x:c r="A174" s="40" t="n">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="B174" s="9" t="str">
-        <x:v>audi-tt-coil-pack-failure-and-2000</x:v>
-      </x:c>
-      <x:c r="C174" s="9" t="str">
-        <x:v>2000-2001 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D174" s="9" t="str">
-        <x:v>Rear Track-Control Arm Corrosion Can Restrict Movement (Recall 01V325)</x:v>
-      </x:c>
-      <x:c r="E174" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the rear track-control arms free of charge under recall 01V325.</x:v>
-      </x:c>
-      <x:c r="F174" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G174" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="175" ht="264" hidden="0" customHeight="1">
-      <x:c r="A175" s="40" t="n">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="B175" s="9" t="str">
-        <x:v>audi-tt-dsg-mechatronic-2008</x:v>
-      </x:c>
-      <x:c r="C175" s="9" t="str">
-        <x:v>2004-2004 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D175" s="9" t="str">
-        <x:v>Direct-Shift Gearbox Clutch Weld Can Lose Drive Torque (Recall 04V007)</x:v>
-      </x:c>
-      <x:c r="E175" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers replace the affected clutch free of charge under recall 04V007. If drive torque is lost, move out of traffic safely and arrange recovery.</x:v>
-      </x:c>
-      <x:c r="F175" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G175" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="176" ht="356.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A176" s="40" t="n">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="B176" s="9" t="str">
-        <x:v>audi-tt-dsg-transmission-2008</x:v>
-      </x:c>
-      <x:c r="C176" s="9" t="str">
-        <x:v>2009-2009 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D176" s="9" t="str">
-        <x:v>DSG Temperature-Sensor Wiring Can Trigger an Abrupt Shift to Neutral (Recall 09V333)</x:v>
-      </x:c>
-      <x:c r="E176" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers reprogram the transmission control module with updated software free of charge under recall 09V333. If the gear indicator flashes or neutral engages unexpectedly, stop safely.</x:v>
-      </x:c>
-      <x:c r="F176" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G176" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="177" ht="303.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A177" s="40" t="n">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="B177" s="9" t="str">
-        <x:v>audi-tt-front-control-arm-bushings-2000</x:v>
-      </x:c>
-      <x:c r="C177" s="9" t="str">
-        <x:v>2000-2000 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D177" s="9" t="str">
-        <x:v>High-Speed Directional-Stability Remedy (Recall 99V300)</x:v>
-      </x:c>
-      <x:c r="E177" s="9" t="str">
-        <x:v>Verify campaign completion with Audi. The factory remedy installs revised stabilizers, front control arms, firmer shock absorbers, and a rear spoiler as specified for the drivetrain configuration.</x:v>
-      </x:c>
-      <x:c r="F177" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G177" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="178" ht="237.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A178" s="40" t="n">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="B178" s="9" t="str">
-        <x:v>audi-tt-haldex-awd-coupling-pumpcontroller-2000</x:v>
-      </x:c>
-      <x:c r="C178" s="9" t="str">
-        <x:v>2008-2010 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D178" s="9" t="str">
-        <x:v>Fuel-Tank Ventilation Valve Can Allow Fuel Leakage (Recall 09V377)</x:v>
-      </x:c>
-      <x:c r="E178" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel-tank ventilation valve with the improved valve free of charge under recall 09V377.</x:v>
-      </x:c>
-      <x:c r="F178" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G178" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="179" ht="184.8000030517578" hidden="0" customHeight="1">
-      <x:c r="A179" s="40" t="n">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="B179" s="9" t="str">
-        <x:v>audi-tt-high-speed-stability-recall-for-2000</x:v>
-      </x:c>
-      <x:c r="C179" s="9" t="str">
-        <x:v>2016-2019 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D179" s="9" t="str">
-        <x:v>Fuel Tank Can Be Damaged by Heat-Shield Bracket in a Crash (Recall 20V076 / 20BX)</x:v>
-      </x:c>
-      <x:c r="E179" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers install a protective cap on the heat-shield bracket free of charge under campaign 20BX.</x:v>
-      </x:c>
-      <x:c r="F179" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G179" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="180" ht="237.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A180" s="40" t="n">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="B180" s="9" t="str">
-        <x:v>audi-tt-instrument-cluster-pixel-failure-2000</x:v>
-      </x:c>
-      <x:c r="C180" s="9" t="str">
-        <x:v>2016-2016 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D180" s="9" t="str">
-        <x:v>Front-Passenger Airbag Module May Explode or Deploy Improperly (Recall 22V543 / 69DY)</x:v>
-      </x:c>
-      <x:c r="E180" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the front-passenger airbag module free of charge under campaign 69DY/61C1.</x:v>
-      </x:c>
-      <x:c r="F180" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G180" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="181" ht="224.39999389648438" hidden="0" customHeight="1">
-      <x:c r="A181" s="40" t="n">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="B181" s="9" t="str">
-        <x:v>audi-tt-magnetic-ride-2008</x:v>
-      </x:c>
-      <x:c r="C181" s="9" t="str">
-        <x:v>2023-2023 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D181" s="9" t="str">
-        <x:v>Passenger-Seat Occupant Detection Connection Can Disable Airbag (Recall 24V251 / 69GU)</x:v>
-      </x:c>
-      <x:c r="E181" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers replace the passenger-seat occupant-detection control module free of charge under campaign 69GU.</x:v>
-      </x:c>
-      <x:c r="F181" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G181" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="182" ht="726" hidden="0" customHeight="1">
-      <x:c r="A182" s="40" t="n">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="B182" s="9" t="str">
-        <x:v>audi-tt-tail-light-corrosion-2008</x:v>
-      </x:c>
-      <x:c r="C182" s="9" t="str">
-        <x:v>2008-2015 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D182" s="9" t="str">
-        <x:v>Tail Light Electrical Connector Corrosion (Mk2)</x:v>
-      </x:c>
-      <x:c r="E182" s="9" t="str">
-        <x:v>Remove tail light assembly, inspect electrical connector for green corrosion. CLEAN connector with electrical contact cleaner and wire brush ($20 DIY). Apply dielectric grease to prevent future corrosion ($10). If connector is severely corroded: Replace pigtail connector ($50-$100 parts). Improve tail light seal with silicone sealant around housing ($15). This is a DIY-friendly repair taking 1-2 hours. If paying shop, costs $150-$300. Address early before corrosion causes shorts.</x:v>
-      </x:c>
-      <x:c r="F182" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G182" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="183" ht="171.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A183" s="40" t="n">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="B183" s="9" t="str">
-        <x:v>audi-tt-water-pump-2008</x:v>
-      </x:c>
-      <x:c r="C183" s="9" t="str">
-        <x:v>2008-2008 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D183" s="9" t="str">
-        <x:v>C-Pillar Trim Cover Can Detach During Belt-Tensioner Deployment (Recall 08V064)</x:v>
-      </x:c>
-      <x:c r="E183" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers install improved C-pillar trim clips free of charge under recall 08V064.</x:v>
-      </x:c>
-      <x:c r="F183" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G183" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="184" ht="1161.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A184" s="40" t="n">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="B184" s="9" t="str">
-        <x:v>audi-tts-cam-follower-hpfp-2009</x:v>
-      </x:c>
-      <x:c r="C184" s="9" t="str">
-        <x:v>2009-2015 | Audi | TTS | TTS | EA888</x:v>
-      </x:c>
-      <x:c r="D184" s="9" t="str">
-        <x:v>HPFP Cam Follower Wear and High-Pressure Fuel Pump Failure (Mk2)</x:v>
-      </x:c>
-      <x:c r="E184" s="9" t="str">
-        <x:v>INSPECTION (every 20,000 miles): Remove HPFP (3 bolts) and inspect cam follower surface. If the hardened coating is wearing through (visible copper/brass color), replace follower immediately ($30-$50 part, 30-60 minutes labor). CRITICAL: Ensure cam lobe is at LOW point before reinstalling—if at peak, you'll compress the spring and can break the mounting bolts. If CAMSHAFT WORN (deep groove in lobe): Replace camshaft ($2,000-$4,000). If FUEL PUMP FAILED: Replace HPFP ($400-$800). PREVENTION: Inspect cam follower every 20,000 miles as routine maintenance. Add to every oil change checklist. Consider IE (Integrated Engineering) upgraded HPFP with roller follower to eliminate wear entirely.</x:v>
-      </x:c>
-      <x:c r="F184" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G184" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="185" ht="884.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A185" s="40" t="n">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="B185" s="9" t="str">
-        <x:v>audi-tts-carbon-buildup-2009</x:v>
-      </x:c>
-      <x:c r="C185" s="9" t="str">
-        <x:v>2016-2017 | Audi | TTS</x:v>
-      </x:c>
-      <x:c r="D185" s="9" t="str">
-        <x:v>2016-2017 TTS Cold-Start Misfire DTCs Without Felt Misfire - TSB 2051384/1</x:v>
-      </x:c>
-      <x:c r="E185" s="9" t="str">
-        <x:v>Confirm the exact cold-start timing, simultaneous-cylinder DTC pattern, absence of a felt misfire, CYFB engine and installed ECM software before using this bulletin. When applicable, an Audi-capable workshop updates ECM J623 from software part number 8S0906259C version 0001 to version 0004 or higher using SVM action 01A190, then clears the DTCs. A felt misfire, a different timing or RPM pattern, a different engine/software combination or a returning concern requires normal diagnosis rather than carbon cleaning by assumption.</x:v>
-      </x:c>
-      <x:c r="F185" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G185" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="186" ht="910.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A186" s="40" t="n">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="B186" s="9" t="str">
-        <x:v>audi-tts-dsg-mechatronic-2009</x:v>
-      </x:c>
-      <x:c r="C186" s="9" t="str">
-        <x:v>2019-2023 | Audi | TTS</x:v>
-      </x:c>
-      <x:c r="D186" s="9" t="str">
-        <x:v>2019-2023 TTS Clutch K1 Overheat and Transmission DTC Diagnosis - TSB 2060560/3</x:v>
-      </x:c>
-      <x:c r="E186" s="9" t="str">
-        <x:v>Have an Audi-capable workshop check whether TSB 2050723 applies first. If it does not resolve or control the concern, inspect the clutch-K1 maximum-temperature value and document a transmission-fluid sample. Replace the dual clutch, transmission fluid and filter only when the approximately 400 °C K1 value and burnt black or very dark fluid are both present. If those findings are absent, this bulletin does not apply and Audi directs the workshop to continue diagnosis through TAC. Any clutch repair kit must be selected by VIN and production date.</x:v>
-      </x:c>
-      <x:c r="F186" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G186" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="187" ht="858" hidden="0" customHeight="1">
-      <x:c r="A187" s="40" t="n">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="B187" s="9" t="str">
-        <x:v>audi-tts-magnetic-ride-2009</x:v>
-      </x:c>
-      <x:c r="C187" s="9" t="str">
-        <x:v>2016-2016 | Audi | TTS</x:v>
-      </x:c>
-      <x:c r="D187" s="9" t="str">
-        <x:v>2016 TTS Magnetic-Ride Rear Shock-Mount Rumble - TSB 2042539/4</x:v>
-      </x:c>
-      <x:c r="E187" s="9" t="str">
-        <x:v>First reproduce the noise, verify that it comes from the rear shock mounts and confirm that the vehicle was originally equipped with mount 8S0 513 353. Only when those gates are satisfied, remove both rear shock assemblies and replace both mounts with 8V0 513 353 according to Audi workshop instructions, adapt the suspension control position and test drive to confirm the repair. If the installed mount does not match, continue Audi diagnosis. Do not replace magnetic dampers or convert the vehicle to coilovers from this noise alone.</x:v>
-      </x:c>
-      <x:c r="F187" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G187" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="188" ht="1016.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A188" s="40" t="n">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="B188" s="9" t="str">
-        <x:v>audi-tts-timing-chain-tensioner-2009</x:v>
-      </x:c>
-      <x:c r="C188" s="9" t="str">
-        <x:v>2009-2015 | Audi | TTS | TTS | EA888 Gen 1, EA888 Gen 2</x:v>
-      </x:c>
-      <x:c r="D188" s="9" t="str">
-        <x:v>Timing Chain Tensioner Failure (EA888 Gen 1/2 - Mk2 TTS)</x:v>
-      </x:c>
-      <x:c r="E188" s="9" t="str">
-        <x:v>PREVENTIVE REPLACEMENT: Replace timing chain, tensioner, guides, and sprockets at 80,000-100,000 miles BEFORE symptoms appear ($2,000-$4,000). This is the MOST important preventive maintenance on the Mk2 TTS. IF RATTLING: Do NOT delay—the chain can jump at any startup. Schedule repair immediately. Use ONLY the latest OEM revised tensioner (06K109467K). IF CHAIN JUMPED: Engine likely destroyed—compression test all cylinders. Rebuild ($5,000-$8,000) or replacement engine ($6,000-$12,000). PREVENTION: Change oil every 5,000 miles with high-quality synthetic. Low oil level accelerates tensioner wear.</x:v>
-      </x:c>
-      <x:c r="F188" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G188" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="189" ht="976.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A189" s="40" t="n">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="B189" s="9" t="str">
-        <x:v>audi-tts-water-pump-2009</x:v>
-      </x:c>
-      <x:c r="C189" s="9" t="str">
-        <x:v>2012-2023 | Audi | TTS</x:v>
-      </x:c>
-      <x:c r="D189" s="9" t="str">
-        <x:v>2012 / 2020-2023 TTS Coolant-Pump Update and Leak Diagnosis</x:v>
-      </x:c>
-      <x:c r="E189" s="9" t="str">
-        <x:v>For a 2012 TTS, ask an Audi dealer to check the VIN and current campaign/action history for Update 19J2; the published update replaced the pump only when its exact criteria were met and does not promise current warranty coverage. For a 2020-2023 2.0L TTS, first exclude a low level caused by incomplete bleeding or an earlier repair, document and clean the suspected leak, refill to maximum and recheck after driving. Continue observation when no leak returns; replace only the component proven to leak when coolant reappears. Do not select a pump or thermostat assembly before VIN-, engine- and leak-specific diagnosis.</x:v>
-      </x:c>
-      <x:c r="F189" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G189" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="190" ht="198" hidden="0" customHeight="1">
-      <x:c r="A190" s="42" t="n">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="B190" s="43" t="str">
-        <x:v>audi-tts-waterpump-housing-2009</x:v>
-      </x:c>
-      <x:c r="C190" s="43" t="str">
-        <x:v>2009-2024 | Audi | TTS | EA888</x:v>
-      </x:c>
-      <x:c r="D190" s="43" t="str">
-        <x:v>Water Pump and Thermostat Housing Failure</x:v>
-      </x:c>
-      <x:c r="E190" s="43" t="str">
-        <x:v>Replace water pump, thermostat, and housing as a complete assembly. Use metal-impeller aftermarket pump if available.</x:v>
-      </x:c>
-      <x:c r="F190" s="43" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G190" s="44" t="str">
+      <x:c r="G140" s="44" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>

--- a/outputs/audi-repair-first-review/Audi-repair-first-fitment-review.xlsx
+++ b/outputs/audi-repair-first-review/Audi-repair-first-fitment-review.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rbfc4caea0ca249d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audi Review" sheetId="2" r:id="Rbd35e80b5fdf4e3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Queue" sheetId="3" r:id="Rcfbb0f41b79b4721"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" r:id="Reccd3ecfa5934e37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R49941522a7274700"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audi Review" sheetId="2" r:id="Rad259c8fcd504851"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Queue" sheetId="3" r:id="Rf8c63222b675417b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" r:id="Rc5230f09ee654b3a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -484,7 +484,7 @@
         <x:v>Reviewed in this batch</x:v>
       </x:c>
       <x:c r="B5" s="13" t="n">
-        <x:v>250</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C5" s="11"/>
       <x:c r="D5" s="11"/>
@@ -498,7 +498,7 @@
         <x:v>Remaining queue</x:v>
       </x:c>
       <x:c r="B6" s="13" t="n">
-        <x:v>139</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C6" s="11"/>
       <x:c r="D6" s="11"/>
@@ -512,7 +512,7 @@
         <x:v>Issues with destinations</x:v>
       </x:c>
       <x:c r="B7" s="13" t="n">
-        <x:v>246</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="C7" s="11"/>
       <x:c r="D7" s="11"/>
@@ -526,7 +526,7 @@
         <x:v>Destination entries</x:v>
       </x:c>
       <x:c r="B8" s="13" t="n">
-        <x:v>431</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="C8" s="11"/>
       <x:c r="D8" s="11"/>
@@ -540,7 +540,7 @@
         <x:v>Distinct URLs</x:v>
       </x:c>
       <x:c r="B9" s="13" t="n">
-        <x:v>80</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C9" s="11"/>
       <x:c r="D9" s="11"/>
@@ -568,7 +568,7 @@
         <x:v>Missing How to Fix</x:v>
       </x:c>
       <x:c r="B11" s="13" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C11" s="11"/>
       <x:c r="D11" s="11"/>
@@ -15629,28 +15629,2908 @@
       </x:c>
     </x:row>
     <x:row r="436" ht="66" hidden="0" customHeight="1">
-      <x:c r="A436" s="42" t="str"/>
-      <x:c r="B436" s="43" t="str"/>
-      <x:c r="C436" s="43" t="str"/>
-      <x:c r="D436" s="43" t="str"/>
-      <x:c r="E436" s="43" t="str"/>
-      <x:c r="F436" s="43" t="str"/>
-      <x:c r="G436" s="43" t="str"/>
-      <x:c r="H436" s="43" t="str">
+      <x:c r="A436" s="40" t="str"/>
+      <x:c r="B436" s="9" t="str"/>
+      <x:c r="C436" s="9" t="str"/>
+      <x:c r="D436" s="9" t="str"/>
+      <x:c r="E436" s="9" t="str"/>
+      <x:c r="F436" s="9" t="str"/>
+      <x:c r="G436" s="9" t="str"/>
+      <x:c r="H436" s="9" t="str">
         <x:v>Audi dealer locator</x:v>
       </x:c>
-      <x:c r="I436" s="43" t="str">
+      <x:c r="I436" s="9" t="str">
         <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
       </x:c>
-      <x:c r="J436" s="43" t="str">
+      <x:c r="J436" s="9" t="str">
         <x:v>VIN transmission/actuator/fluid</x:v>
       </x:c>
-      <x:c r="K436" s="43" t="str">
+      <x:c r="K436" s="9" t="str">
         <x:v>manufacturer service</x:v>
       </x:c>
-      <x:c r="L436" s="43" t="str"/>
-      <x:c r="M436" s="43" t="str"/>
-      <x:c r="N436" s="44" t="str"/>
+      <x:c r="L436" s="9" t="str"/>
+      <x:c r="M436" s="9" t="str"/>
+      <x:c r="N436" s="41" t="str"/>
+    </x:row>
+    <x:row r="437" ht="330" hidden="0" customHeight="1">
+      <x:c r="A437" s="40" t="n">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="B437" s="9" t="str">
+        <x:v>audi-r8-s-tronic-gearbox-ventilation-hose-transmission-fluid-leak</x:v>
+      </x:c>
+      <x:c r="C437" s="9" t="str">
+        <x:v>2017-2018 | Audi | R8 | 5.2L V10 FSI</x:v>
+      </x:c>
+      <x:c r="D437" s="9" t="str">
+        <x:v>Gearbox Ventilation Hose Can Leak Fluid Near Hot Engine Parts (Recall 18V639 / 34J1)</x:v>
+      </x:c>
+      <x:c r="E437" s="9" t="str">
+        <x:v>Check the VIN and campaign history. Audi dealers replace the single gearbox ventilation hose with the higher-volume double hose free of charge under campaign 34J1. Stop driving if hot-oil odor or smoke appears.</x:v>
+      </x:c>
+      <x:c r="F437" s="9" t="str">
+        <x:v>VIN/34J1/18V639 check; free higher-volume double ventilation hose; stop for hot-oil odor/smoke</x:v>
+      </x:c>
+      <x:c r="G437" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H437" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I437" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J437" s="9" t="str">
+        <x:v>2017-2018 R8 34J1</x:v>
+      </x:c>
+      <x:c r="K437" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L437" s="9" t="str"/>
+      <x:c r="M437" s="9" t="str">
+        <x:v>Campaign specifies hose remedy.</x:v>
+      </x:c>
+      <x:c r="N437" s="41" t="str">
+        <x:v>No gearbox hose product link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="438" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A438" s="40" t="str"/>
+      <x:c r="B438" s="9" t="str"/>
+      <x:c r="C438" s="9" t="str"/>
+      <x:c r="D438" s="9" t="str"/>
+      <x:c r="E438" s="9" t="str"/>
+      <x:c r="F438" s="9" t="str"/>
+      <x:c r="G438" s="9" t="str"/>
+      <x:c r="H438" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I438" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J438" s="9" t="str">
+        <x:v>18V639 VIN history</x:v>
+      </x:c>
+      <x:c r="K438" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L438" s="9" t="str"/>
+      <x:c r="M438" s="9" t="str"/>
+      <x:c r="N438" s="41" t="str"/>
+    </x:row>
+    <x:row r="439" ht="765.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A439" s="40" t="n">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="B439" s="9" t="str">
+        <x:v>audi-r8-spyder-convertible-top-hydraulic-pump-failure</x:v>
+      </x:c>
+      <x:c r="C439" s="9" t="str">
+        <x:v>2011-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+      </x:c>
+      <x:c r="D439" s="9" t="str">
+        <x:v>Spyder Convertible Top Hydraulic Pump Failure</x:v>
+      </x:c>
+      <x:c r="E439" s="9" t="str">
+        <x:v>Scan for the specific fault (pump vs. sensor vs. latch) before parting; a mis-reading position sensor can mimic a dead pump. Replace the hydraulic pump/motor assembly (Audi R8 Spyder convertible-top hydraulic pump PN 427871791 for 2010-2016 cars) and top up/refill the correct hydraulic fluid, or replace the failed cylinder/sensor. Leaking lines and worn seals should be renewed together. Independent hydraulic rebuild services exist as a lower-cost alternative to a full dealer pump.</x:v>
+      </x:c>
+      <x:c r="F439" s="9" t="str">
+        <x:v>Explicit VAG scan to split pump, sensor, latch; generation/VIN pump 427871791 only where proven; exact fluid, cylinder/line/seal branch and bleed</x:v>
+      </x:c>
+      <x:c r="G439" s="9" t="str">
+        <x:v>EXPLICIT SCANNER/DIAGNOSTIC TOOL APPROVAL — TOP SYSTEM DIAGNOSIS</x:v>
+      </x:c>
+      <x:c r="H439" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I439" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J439" s="9" t="str">
+        <x:v>2011-2023 R8 Spyder generation-specific top scan/hydraulic diagnosis</x:v>
+      </x:c>
+      <x:c r="K439" s="9" t="str">
+        <x:v>specialist diagnostic service</x:v>
+      </x:c>
+      <x:c r="L439" s="9" t="str"/>
+      <x:c r="M439" s="9" t="str">
+        <x:v>Position sensor/latch can mimic pump failure and generations differ.</x:v>
+      </x:c>
+      <x:c r="N439" s="41" t="str">
+        <x:v>No generic scanner/pump/rebuild link until exact fault and provider terms are verified.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="440" ht="66" hidden="0" customHeight="1">
+      <x:c r="A440" s="40" t="str"/>
+      <x:c r="B440" s="9" t="str"/>
+      <x:c r="C440" s="9" t="str"/>
+      <x:c r="D440" s="9" t="str"/>
+      <x:c r="E440" s="9" t="str"/>
+      <x:c r="F440" s="9" t="str"/>
+      <x:c r="G440" s="9" t="str"/>
+      <x:c r="H440" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I440" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J440" s="9" t="str">
+        <x:v>VIN pump/fluid/parts</x:v>
+      </x:c>
+      <x:c r="K440" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L440" s="9" t="str"/>
+      <x:c r="M440" s="9" t="str"/>
+      <x:c r="N440" s="41" t="str"/>
+    </x:row>
+    <x:row r="441" ht="1122" hidden="0" customHeight="1">
+      <x:c r="A441" s="40" t="n">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B441" s="9" t="str">
+        <x:v>audi-r8-v8-engine-bearing-2008</x:v>
+      </x:c>
+      <x:c r="C441" s="9" t="str">
+        <x:v>2008-2015 | Audi | R8 | 4.2 | 4.2 FSI</x:v>
+      </x:c>
+      <x:c r="D441" s="9" t="str">
+        <x:v>Rod Bearing Wear and Engine Failure Risk (4.2 V8 FSI)</x:v>
+      </x:c>
+      <x:c r="E441" s="9" t="str">
+        <x:v>EARLY DETECTION (knocking noise only): Rod bearing replacement ($2,000-$5,000). Must be caught EARLY before bearing material migrates through oil system. Cut open every oil filter at oil change to inspect for metallic debris. CATASTROPHIC FAILURE: Engine replacement ($13,000+ Audi exchange, $8,000-$15,000 rebuilt from AMTuned or specialist rebuilder). ARP 2000 reinforced connecting rod bolts are available as a preventive upgrade during any engine-out service. PREVENTION: Use ONLY premium 5W-40 synthetic oil. Change oil every 5,000 miles maximum. NEVER exceed oil change intervals—the high-revving V8 is extremely sensitive to oil condition. For track use, change oil after every 2-3 track days.</x:v>
+      </x:c>
+      <x:c r="F441" s="9" t="str">
+        <x:v>Oil-pressure/noise/filter-debris and engine-condition diagnosis; engine-code bearings/bolts/clearances only after teardown; oil spec by VIN/use</x:v>
+      </x:c>
+      <x:c r="G441" s="9" t="str">
+        <x:v>ENGINE-CONDITION / TEARDOWN GATE</x:v>
+      </x:c>
+      <x:c r="H441" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I441" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J441" s="9" t="str">
+        <x:v>2008-2015 R8 4.2 bearing/oil-system diagnosis</x:v>
+      </x:c>
+      <x:c r="K441" s="9" t="str">
+        <x:v>specialist R8 engine service</x:v>
+      </x:c>
+      <x:c r="L441" s="9" t="str"/>
+      <x:c r="M441" s="9" t="str">
+        <x:v>Knock/debris does not prove repairable rod bearings and engine replacement is conditional.</x:v>
+      </x:c>
+      <x:c r="N441" s="41" t="str">
+        <x:v>No ARP bolt/preventive oil-interval/track schedule claim without engine-builder and manufacturer evidence.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="442" ht="66" hidden="0" customHeight="1">
+      <x:c r="A442" s="40" t="str"/>
+      <x:c r="B442" s="9" t="str"/>
+      <x:c r="C442" s="9" t="str"/>
+      <x:c r="D442" s="9" t="str"/>
+      <x:c r="E442" s="9" t="str"/>
+      <x:c r="F442" s="9" t="str"/>
+      <x:c r="G442" s="9" t="str"/>
+      <x:c r="H442" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I442" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J442" s="9" t="str">
+        <x:v>VIN oil spec/internal parts</x:v>
+      </x:c>
+      <x:c r="K442" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L442" s="9" t="str"/>
+      <x:c r="M442" s="9" t="str"/>
+      <x:c r="N442" s="41" t="str"/>
+    </x:row>
+    <x:row r="443" ht="924" hidden="0" customHeight="1">
+      <x:c r="A443" s="40" t="n">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="B443" s="9" t="str">
+        <x:v>audi-rs-etron-gt-battery-short-2022</x:v>
+      </x:c>
+      <x:c r="C443" s="9" t="str">
+        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
+      </x:c>
+      <x:c r="D443" s="9" t="str">
+        <x:v>2022-2024 RS e-tron GT High-Voltage Battery Recall 931A/931B (24V726)</x:v>
+      </x:c>
+      <x:c r="E443" s="9" t="str">
+        <x:v>Check the VIN for open Audi campaign 931A or 931B and complete the authorized dealer remedy. Under 931A, enrolled vehicles can be monitored through online battery data; Audi contacts owners if a module appears critical. Under 931B, the dealer performs diagnostic procedures until the final monitoring software is installed. Audi installs the onboard diagnostic software and replaces affected battery modules at no cost when anomalies are identified. Follow any vehicle- or dealer-specific 80-percent charging instruction; the filing does not direct every 931A vehicle to use that limit.</x:v>
+      </x:c>
+      <x:c r="F443" s="9" t="str">
+        <x:v>VIN/931A/931B/24V726 check; dealer monitoring software and conditional HV module remedy; vehicle-specific charge limit</x:v>
+      </x:c>
+      <x:c r="G443" s="9" t="str">
+        <x:v>HIGH-VOLTAGE RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H443" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I443" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J443" s="9" t="str">
+        <x:v>2022-2024 RS e-tron GT 931A/931B</x:v>
+      </x:c>
+      <x:c r="K443" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L443" s="9" t="str"/>
+      <x:c r="M443" s="9" t="str">
+        <x:v>HV remedy/limit is VIN-specific.</x:v>
+      </x:c>
+      <x:c r="N443" s="41" t="str">
+        <x:v>No battery product link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="444" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A444" s="40" t="str"/>
+      <x:c r="B444" s="9" t="str"/>
+      <x:c r="C444" s="9" t="str"/>
+      <x:c r="D444" s="9" t="str"/>
+      <x:c r="E444" s="9" t="str"/>
+      <x:c r="F444" s="9" t="str"/>
+      <x:c r="G444" s="9" t="str"/>
+      <x:c r="H444" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I444" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J444" s="9" t="str">
+        <x:v>24V726 VIN history</x:v>
+      </x:c>
+      <x:c r="K444" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L444" s="9" t="str"/>
+      <x:c r="M444" s="9" t="str"/>
+      <x:c r="N444" s="41" t="str"/>
+    </x:row>
+    <x:row r="445" ht="646.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A445" s="40" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B445" s="9" t="str">
+        <x:v>audi-rs-etron-gt-brake-hose-2022</x:v>
+      </x:c>
+      <x:c r="C445" s="9" t="str">
+        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
+      </x:c>
+      <x:c r="D445" s="9" t="str">
+        <x:v>2022-2024 RS e-tron GT Front Brake-Hose Recall 47UP (24V465)</x:v>
+      </x:c>
+      <x:c r="E445" s="9" t="str">
+        <x:v>Check the VIN for an open 47UP action and have an authorized Audi dealer replace both front brake hoses and holders free of charge. If pedal travel increases or the vehicle displays a warning related to reduced brake fluid, contact an Audi dealer for diagnosis without delay. Do not buy a single hose or substitute generic brake lines from the prior links; the campaign controls the complete criteria-specific repair.</x:v>
+      </x:c>
+      <x:c r="F445" s="9" t="str">
+        <x:v>VIN/47UP/24V465 check; both front hoses/holders; urgent warning/pedal diagnosis</x:v>
+      </x:c>
+      <x:c r="G445" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H445" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I445" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J445" s="9" t="str">
+        <x:v>2022-2024 RS e-tron GT 47UP</x:v>
+      </x:c>
+      <x:c r="K445" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L445" s="9" t="str"/>
+      <x:c r="M445" s="9" t="str">
+        <x:v>Complete paired repair is campaign-controlled.</x:v>
+      </x:c>
+      <x:c r="N445" s="41" t="str">
+        <x:v>No single/generic hose link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="446" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A446" s="40" t="str"/>
+      <x:c r="B446" s="9" t="str"/>
+      <x:c r="C446" s="9" t="str"/>
+      <x:c r="D446" s="9" t="str"/>
+      <x:c r="E446" s="9" t="str"/>
+      <x:c r="F446" s="9" t="str"/>
+      <x:c r="G446" s="9" t="str"/>
+      <x:c r="H446" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I446" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J446" s="9" t="str">
+        <x:v>24V465 VIN history</x:v>
+      </x:c>
+      <x:c r="K446" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L446" s="9" t="str"/>
+      <x:c r="M446" s="9" t="str"/>
+      <x:c r="N446" s="41" t="str"/>
+    </x:row>
+    <x:row r="447" ht="726" hidden="0" customHeight="1">
+      <x:c r="A447" s="40" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="B447" s="9" t="str">
+        <x:v>audi-rs-etron-gt-charging-port-2022</x:v>
+      </x:c>
+      <x:c r="C447" s="9" t="str">
+        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
+      </x:c>
+      <x:c r="D447" s="9" t="str">
+        <x:v>2022-2024 RS e-tron GT Red Charging LED or Fast-Charging Abort - Audi 91VT</x:v>
+      </x:c>
+      <x:c r="E447" s="9" t="str">
+        <x:v>Have an Audi dealer check the VIN and assigned 91VT criterion in the campaign/action system. For the charging-related criteria, the authorized remedy updates the high-voltage battery control-module software, with the convenience-system control module also updated where the assigned criterion requires it. Diagnose charging failures outside that exact campaign branch rather than replacing the charging socket or module from symptoms alone.</x:v>
+      </x:c>
+      <x:c r="F447" s="9" t="str">
+        <x:v>VIN/91VT criterion; HV battery-control and conditional convenience-module software; separate other charging diagnosis</x:v>
+      </x:c>
+      <x:c r="G447" s="9" t="str">
+        <x:v>SOFTWARE ACTION ROUTE</x:v>
+      </x:c>
+      <x:c r="H447" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I447" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J447" s="9" t="str">
+        <x:v>2022-2024 RS e-tron GT 91VT</x:v>
+      </x:c>
+      <x:c r="K447" s="9" t="str">
+        <x:v>authorized EV software service</x:v>
+      </x:c>
+      <x:c r="L447" s="9" t="str"/>
+      <x:c r="M447" s="9" t="str">
+        <x:v>Campaign branch is software.</x:v>
+      </x:c>
+      <x:c r="N447" s="41" t="str">
+        <x:v>No socket/module link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="448" ht="673.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A448" s="40" t="n">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="B448" s="9" t="str">
+        <x:v>audi-rs-etron-gt-software-2022</x:v>
+      </x:c>
+      <x:c r="C448" s="9" t="str">
+        <x:v>2022-2022 | Audi | RS e-tron GT</x:v>
+      </x:c>
+      <x:c r="D448" s="9" t="str">
+        <x:v>2022 RS e-tron GT Audi connect Inoperative after 91DZ - TSB 2068824/2</x:v>
+      </x:c>
+      <x:c r="E448" s="9" t="str">
+        <x:v>Confirm that the failure began after 91DZ and matches the Audi connect/SOS-LED condition. An Audi technician should use ODIS Guided Fault Finding and run SVM Check Module Configuration for diagnostic address 0019, J533. Manual coding is no longer required. Escalate a continuing Audi connect failure through Audi support after the guided coding procedure rather than buying hardware or a retail software service.</x:v>
+      </x:c>
+      <x:c r="F448" s="9" t="str">
+        <x:v>Confirm post-91DZ Audi connect/SOS; ODIS GFF and J533 SVM configuration; Audi escalation if persistent</x:v>
+      </x:c>
+      <x:c r="G448" s="9" t="str">
+        <x:v>GUIDED SOFTWARE SERVICE</x:v>
+      </x:c>
+      <x:c r="H448" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I448" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J448" s="9" t="str">
+        <x:v>2022 RS e-tron GT TSB 2068824/2</x:v>
+      </x:c>
+      <x:c r="K448" s="9" t="str">
+        <x:v>manufacturer software service</x:v>
+      </x:c>
+      <x:c r="L448" s="9" t="str"/>
+      <x:c r="M448" s="9" t="str">
+        <x:v>No hardware/manual coding remedy.</x:v>
+      </x:c>
+      <x:c r="N448" s="41" t="str">
+        <x:v>No module or retail coding link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="449" ht="937.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A449" s="40" t="n">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="B449" s="9" t="str">
+        <x:v>audi-rs-etron-gt-tire-wear-2022</x:v>
+      </x:c>
+      <x:c r="C449" s="9" t="str">
+        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
+      </x:c>
+      <x:c r="D449" s="9" t="str">
+        <x:v>Accelerated Tire Wear and Alignment Sensitivity</x:v>
+      </x:c>
+      <x:c r="E449" s="9" t="str">
+        <x:v>Rotate front-to-back every 3,000-5,000 miles (only possible if sizes permit, which staggered setups often do not). Check alignment every 5,000 miles or after any pothole impact - even 0.1 degree of toe deviation causes rapid edge wear on these wide tires. Consider switching to Michelin Pilot Sport 4S or Pirelli P Zero PZ4 for improved tread life over the OE Continental SportContact 6. Budget $1,400-$2,000 for a set of four replacement tires. Aggressive driving with launch control dramatically reduces tire life. For better longevity, use Comfort mode instead of Dynamic for daily driving.</x:v>
+      </x:c>
+      <x:c r="F449" s="9" t="str">
+        <x:v>Record exact tire sizes/load/speed rating and stagger; pressure/alignment/tread-depth/wear diagnosis; rotation only if sizes permit; exact replacement tire by axle</x:v>
+      </x:c>
+      <x:c r="G449" s="9" t="str">
+        <x:v>TIRE-SIZE / AXLE / ALIGNMENT GATE</x:v>
+      </x:c>
+      <x:c r="H449" s="9" t="str">
+        <x:v>Tire Rack Audi RS e-tron GT tires</x:v>
+      </x:c>
+      <x:c r="I449" s="9" t="str">
+        <x:v>https://www.tirerack.com/tires/TireSearchResults.jsp?autoMake=Audi&amp;autoModel=RS+e-tron+GT</x:v>
+      </x:c>
+      <x:c r="J449" s="9" t="str">
+        <x:v>2022-2024; select exact wheel size, axle, load/speed rating and OE marking</x:v>
+      </x:c>
+      <x:c r="K449" s="9" t="str">
+        <x:v>vehicle-specific tire catalog</x:v>
+      </x:c>
+      <x:c r="L449" s="9" t="str"/>
+      <x:c r="M449" s="9" t="str">
+        <x:v>Staggered setups often cannot rotate and model has multiple wheel sizes.</x:v>
+      </x:c>
+      <x:c r="N449" s="41" t="str">
+        <x:v>Remove fixed alignment interval, 0.1-degree claim, brand-life promise and driving-mode claim.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="450" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A450" s="40" t="str"/>
+      <x:c r="B450" s="9" t="str"/>
+      <x:c r="C450" s="9" t="str"/>
+      <x:c r="D450" s="9" t="str"/>
+      <x:c r="E450" s="9" t="str"/>
+      <x:c r="F450" s="9" t="str"/>
+      <x:c r="G450" s="9" t="str"/>
+      <x:c r="H450" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I450" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J450" s="9" t="str">
+        <x:v>VIN alignment specs and stagger confirmation</x:v>
+      </x:c>
+      <x:c r="K450" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L450" s="9" t="str"/>
+      <x:c r="M450" s="9" t="str"/>
+      <x:c r="N450" s="41" t="str"/>
+    </x:row>
+    <x:row r="451" ht="699.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A451" s="40" t="n">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="B451" s="9" t="str">
+        <x:v>audi-rs-q8-air-suspension-2020</x:v>
+      </x:c>
+      <x:c r="C451" s="9" t="str">
+        <x:v>2020-2025 | Audi | RS Q8</x:v>
+      </x:c>
+      <x:c r="D451" s="9" t="str">
+        <x:v>2020-2025 RS Q8 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
+      </x:c>
+      <x:c r="E451" s="9" t="str">
+        <x:v>Inspect the wiring and connector contacts between J775 and J1135 before replacing a component. For a first passive or sporadic occurrence, clear the fault and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after wiring inspection, Audi directs replacement of J1135 under current repair and parts information. Do not buy struts, springs, a compressor or a conversion kit solely from this warning.</x:v>
+      </x:c>
+      <x:c r="F451" s="9" t="str">
+        <x:v>J775-J1135 wiring/contact inspection; first passive clear; conditional J1135 after active/static or second return</x:v>
+      </x:c>
+      <x:c r="G451" s="9" t="str">
+        <x:v>TSB WIRING-FIRST / CONDITIONAL MODULE</x:v>
+      </x:c>
+      <x:c r="H451" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I451" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J451" s="9" t="str">
+        <x:v>2020-2025 RS Q8 TSB 2059363/6</x:v>
+      </x:c>
+      <x:c r="K451" s="9" t="str">
+        <x:v>manufacturer suspension service</x:v>
+      </x:c>
+      <x:c r="L451" s="9" t="str"/>
+      <x:c r="M451" s="9" t="str">
+        <x:v>Occurrence/status controls replacement.</x:v>
+      </x:c>
+      <x:c r="N451" s="41" t="str">
+        <x:v>No strut/spring/compressor/conversion link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="452" ht="184.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A452" s="40" t="n">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="B452" s="9" t="str">
+        <x:v>audi-rs3-carbon-buildup-2017</x:v>
+      </x:c>
+      <x:c r="C452" s="9" t="str">
+        <x:v>2017-2025 | Audi | RS3 | 2.5T</x:v>
+      </x:c>
+      <x:c r="D452" s="9" t="str">
+        <x:v>2.5T Five-Cylinder Carbon Buildup</x:v>
+      </x:c>
+      <x:c r="E452" s="9" t="str">
+        <x:v>Walnut blast intake valves every 30,000-40,000 miles. Install catch can immediately on new vehicles.</x:v>
+      </x:c>
+      <x:c r="F452" s="9" t="str">
+        <x:v>Confirm 2.5T deposits after ignition/fuel/compression and intake inspection; engine-specific cleaning</x:v>
+      </x:c>
+      <x:c r="G452" s="9" t="str">
+        <x:v>CONFIRMED-DEPOSIT SERVICE</x:v>
+      </x:c>
+      <x:c r="H452" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I452" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J452" s="9" t="str">
+        <x:v>2017-2025 RS3 2.5T intake diagnosis/cleaning</x:v>
+      </x:c>
+      <x:c r="K452" s="9" t="str">
+        <x:v>specialist intake service</x:v>
+      </x:c>
+      <x:c r="L452" s="9" t="str"/>
+      <x:c r="M452" s="9" t="str">
+        <x:v>No evidence supports 30k-40k universal cleaning.</x:v>
+      </x:c>
+      <x:c r="N452" s="41" t="str">
+        <x:v>No immediate catch-can mandate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="453" ht="686.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A453" s="40" t="n">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="B453" s="9" t="str">
+        <x:v>audi-rs3-dsg-transmission-2015</x:v>
+      </x:c>
+      <x:c r="C453" s="9" t="str">
+        <x:v>2023-2023 | Audi | RS3</x:v>
+      </x:c>
+      <x:c r="D453" s="9" t="str">
+        <x:v>2023 RS3 TCM Software Emissions Recall 37P3 - VIN Check Required</x:v>
+      </x:c>
+      <x:c r="E453" s="9" t="str">
+        <x:v>Ask an Audi dealer to check whether Emissions Recall 37P3 is currently open for the VIN in Elsa. When open, the dealer updates the transmission-control-module software under the campaign; the published remedy requires no parts. Diagnose and repair the underlying fault separately before expecting its stored entry or MIL to clear. Do not buy a mechatronic unit, clutch pack, filter or upgraded DQ500 part for this software campaign.</x:v>
+      </x:c>
+      <x:c r="F453" s="9" t="str">
+        <x:v>VIN/open 37P3 check; dealer TCM emissions software; underlying fault separately diagnosed</x:v>
+      </x:c>
+      <x:c r="G453" s="9" t="str">
+        <x:v>SOURCE-ID MISMATCH / SOFTWARE CAMPAIGN</x:v>
+      </x:c>
+      <x:c r="H453" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I453" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J453" s="9" t="str">
+        <x:v>2023 RS3 37P3 Elsa check/update</x:v>
+      </x:c>
+      <x:c r="K453" s="9" t="str">
+        <x:v>manufacturer campaign service</x:v>
+      </x:c>
+      <x:c r="L453" s="9" t="str"/>
+      <x:c r="M453" s="9" t="str">
+        <x:v>No parts in remedy.</x:v>
+      </x:c>
+      <x:c r="N453" s="41" t="str">
+        <x:v>Identifier says 2015; no mechatronic/clutch/filter/DQ500 link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="454" ht="686.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A454" s="40" t="n">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="B454" s="9" t="str">
+        <x:v>audi-rs3-hpfp-2017</x:v>
+      </x:c>
+      <x:c r="C454" s="9" t="str">
+        <x:v>2017-2023 | Audi | RS3</x:v>
+      </x:c>
+      <x:c r="D454" s="9" t="str">
+        <x:v>2017-2020 / 2022-2023 RS3 Drive-System Warning or No-Start Diagnosis - TSB 2067757/3</x:v>
+      </x:c>
+      <x:c r="E454" s="9" t="str">
+        <x:v>Reproduce and document the complaint, scan the vehicle with current ODIS and complete Guided Fault Finding. When one of the listed DTC/symptom combinations is stored but GFF produces no result, manually add and complete the G265 intermediate-shaft-speed-sensor test plan. Repair only the component identified by that diagnosis. Do not replace or upgrade the high-pressure fuel pump from this warning or DTC set alone.</x:v>
+      </x:c>
+      <x:c r="F454" s="9" t="str">
+        <x:v>ODIS/GFF plus G265 intermediate-shaft-speed-sensor plan for listed no-result combinations; repair identified component only</x:v>
+      </x:c>
+      <x:c r="G454" s="9" t="str">
+        <x:v>SOURCE-ID MISMATCH / GUIDED DIAGNOSIS</x:v>
+      </x:c>
+      <x:c r="H454" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I454" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J454" s="9" t="str">
+        <x:v>2017-2020/2022-2023 RS3 TSB 2067757/3</x:v>
+      </x:c>
+      <x:c r="K454" s="9" t="str">
+        <x:v>manufacturer diagnostic service</x:v>
+      </x:c>
+      <x:c r="L454" s="9" t="str"/>
+      <x:c r="M454" s="9" t="str">
+        <x:v>TSB concerns guided G265 diagnosis, not HPFP.</x:v>
+      </x:c>
+      <x:c r="N454" s="41" t="str">
+        <x:v>Rename/re-key; no HPFP product link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="455" ht="633.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A455" s="40" t="n">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="B455" s="9" t="str">
+        <x:v>audi-rs3-magnetic-ride-2017</x:v>
+      </x:c>
+      <x:c r="C455" s="9" t="str">
+        <x:v>2015-2019 | Audi | RS3</x:v>
+      </x:c>
+      <x:c r="D455" s="9" t="str">
+        <x:v>2015-2018 / Certain 2019 RS3 Magnetic-Ride Rear Shock Noise - TSB 2059240/1</x:v>
+      </x:c>
+      <x:c r="E455" s="9" t="str">
+        <x:v>Confirm magnetic-ride equipment, the exact model-year/VIN boundary and that the noise originates at the rear shock absorbers. When every bulletin criterion matches, replace both rear shock absorbers according to Audi workshop instructions and order the correct units by VIN. Do not replace dampers or convert the suspension from visible residue, ride feel or noise alone without this diagnosis.</x:v>
+      </x:c>
+      <x:c r="F455" s="9" t="str">
+        <x:v>Confirm equipment/VIN boundary and rear-shock source; both VIN-selected rear shocks only when every TSB criterion matches</x:v>
+      </x:c>
+      <x:c r="G455" s="9" t="str">
+        <x:v>TSB / VIN CONDITIONAL PAIR</x:v>
+      </x:c>
+      <x:c r="H455" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I455" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J455" s="9" t="str">
+        <x:v>2015-2018/certain 2019 RS3 TSB 2059240/1</x:v>
+      </x:c>
+      <x:c r="K455" s="9" t="str">
+        <x:v>manufacturer suspension service</x:v>
+      </x:c>
+      <x:c r="L455" s="9" t="str"/>
+      <x:c r="M455" s="9" t="str">
+        <x:v>Residue/ride feel/noise alone do not satisfy bulletin.</x:v>
+      </x:c>
+      <x:c r="N455" s="41" t="str">
+        <x:v>No damper/conversion product before VIN diagnosis.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="456" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A456" s="40" t="str"/>
+      <x:c r="B456" s="9" t="str"/>
+      <x:c r="C456" s="9" t="str"/>
+      <x:c r="D456" s="9" t="str"/>
+      <x:c r="E456" s="9" t="str"/>
+      <x:c r="F456" s="9" t="str"/>
+      <x:c r="G456" s="9" t="str"/>
+      <x:c r="H456" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I456" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J456" s="9" t="str">
+        <x:v>rear-noise diagnosis</x:v>
+      </x:c>
+      <x:c r="K456" s="9" t="str">
+        <x:v>specialist suspension service</x:v>
+      </x:c>
+      <x:c r="L456" s="9" t="str"/>
+      <x:c r="M456" s="9" t="str"/>
+      <x:c r="N456" s="41" t="str"/>
+    </x:row>
+    <x:row r="457" ht="699.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A457" s="40" t="n">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B457" s="9" t="str">
+        <x:v>audi-rs3-ttrs-carbon-buildup-2015</x:v>
+      </x:c>
+      <x:c r="C457" s="9" t="str">
+        <x:v>2015-2023 | Audi | RS3 | 2.5T EA855</x:v>
+      </x:c>
+      <x:c r="D457" s="9" t="str">
+        <x:v>Severe Carbon Buildup on Intake Valves (2.5T 5-Cylinder)</x:v>
+      </x:c>
+      <x:c r="E457" s="9" t="str">
+        <x:v>WALNUT BLASTING: Remove intake manifold and blast walnut shells through intake ports ($800-$1,500). Repeat every 30,000-40,000 miles—MORE frequent than base models due to high performance. PREVENTION: Install catch can ($400-$700) to filter PCV vapors. Add Liqui Moly Intake Valve Cleaner to every oil change. Change oil every 5,000 miles. Drive car hard regularly—Audi's own recommendation to burn off carbon.</x:v>
+      </x:c>
+      <x:c r="F457" s="9" t="str">
+        <x:v>Confirm EA855 generation and deposits after ignition/fuel/compression and intake inspection; engine-specific cleaning</x:v>
+      </x:c>
+      <x:c r="G457" s="9" t="str">
+        <x:v>ENGINE / CONFIRMED-DEPOSIT SERVICE</x:v>
+      </x:c>
+      <x:c r="H457" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I457" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J457" s="9" t="str">
+        <x:v>2015-2023 RS3/TT RS 2.5T intake diagnosis/cleaning</x:v>
+      </x:c>
+      <x:c r="K457" s="9" t="str">
+        <x:v>specialist intake service</x:v>
+      </x:c>
+      <x:c r="L457" s="9" t="str"/>
+      <x:c r="M457" s="9" t="str">
+        <x:v>No evidence supports fixed interval or products.</x:v>
+      </x:c>
+      <x:c r="N457" s="41" t="str">
+        <x:v>Remove catch can, cleaner, oil interval and drive-hard claim.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="458" ht="792" hidden="0" customHeight="1">
+      <x:c r="A458" s="40" t="n">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="B458" s="9" t="str">
+        <x:v>audi-rs3-ttrs-injector-failure-2015</x:v>
+      </x:c>
+      <x:c r="C458" s="9" t="str">
+        <x:v>2015-2023 | Audi | RS3 | EA855</x:v>
+      </x:c>
+      <x:c r="D458" s="9" t="str">
+        <x:v>Fuel Injector Failure and "Torch Effect" (2.5T)</x:v>
+      </x:c>
+      <x:c r="E458" s="9" t="str">
+        <x:v>PREVENTIVE REPLACEMENT: Replace all fuel injectors every 60,000 km (37,000 miles) with OEM Audi injectors ($1,500-$2,500 installed). If engine misfires or runs rough: Inspect injectors IMMEDIATELY—do NOT continue driving. Failed injector can destroy engine in minutes. If piston is melted: Engine replacement required ($15,000-$25,000). Consider extended warranty or aftermarket warranty for out-of-warranty RS3/TT RS. This is the most serious reliability issue with the 2.5T engine.</x:v>
+      </x:c>
+      <x:c r="F458" s="9" t="str">
+        <x:v>Cylinder-specific misfire, fuel pressure/balance/leak and borescope/compression diagnosis; engine-generation/VIN injector and seals; set only by strategy</x:v>
+      </x:c>
+      <x:c r="G458" s="9" t="str">
+        <x:v>ENGINE-GENERATION / INJECTOR-DIAGNOSIS GATE</x:v>
+      </x:c>
+      <x:c r="H458" s="9" t="str">
+        <x:v>Audi RS3 fuel-injector catalog</x:v>
+      </x:c>
+      <x:c r="I458" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/RS3/Fuel-Injector/</x:v>
+      </x:c>
+      <x:c r="J458" s="9" t="str">
+        <x:v>2015-2023; exact engine generation/VIN and injector revision</x:v>
+      </x:c>
+      <x:c r="K458" s="9" t="str">
+        <x:v>vehicle-specific injector catalog</x:v>
+      </x:c>
+      <x:c r="L458" s="9" t="str"/>
+      <x:c r="M458" s="9" t="str">
+        <x:v>Preventive full-set replacement every 60k km is unsupported.</x:v>
+      </x:c>
+      <x:c r="N458" s="41" t="str">
+        <x:v>Remove torch-effect catastrophe, fixed interval/cost and warranty claims without authoritative evidence.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="459" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A459" s="40" t="str"/>
+      <x:c r="B459" s="9" t="str"/>
+      <x:c r="C459" s="9" t="str"/>
+      <x:c r="D459" s="9" t="str"/>
+      <x:c r="E459" s="9" t="str"/>
+      <x:c r="F459" s="9" t="str"/>
+      <x:c r="G459" s="9" t="str"/>
+      <x:c r="H459" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I459" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J459" s="9" t="str">
+        <x:v>2.5T injector/engine diagnosis</x:v>
+      </x:c>
+      <x:c r="K459" s="9" t="str">
+        <x:v>specialist service</x:v>
+      </x:c>
+      <x:c r="L459" s="9" t="str"/>
+      <x:c r="M459" s="9" t="str"/>
+      <x:c r="N459" s="41" t="str"/>
+    </x:row>
+    <x:row r="460" ht="937.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A460" s="40" t="n">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="B460" s="9" t="str">
+        <x:v>audi-rs4-b7-carbon-buildup-2007</x:v>
+      </x:c>
+      <x:c r="C460" s="9" t="str">
+        <x:v>2007-2008 | Audi | RS4 | 4.2L FSI V8</x:v>
+      </x:c>
+      <x:c r="D460" s="9" t="str">
+        <x:v>2007-2008 RS4 Deposit-Related Cold-Start Misfire - Diagnose Before Cleaning</x:v>
+      </x:c>
+      <x:c r="E460" s="9" t="str">
+        <x:v>Have the cold-start event and stored faults diagnosed before authorizing intake cleaning. The B7 RS4 bulletin first checks whether its fuel-additive and follow-up procedure resolves injector-deposit misfires. Current TSB 2014753/13 warns that gasoline additive can clean FSI injectors and combustion chambers but not FSI intake valves. If the misfire remains, the shop should continue guided diagnosis and confirm inlet-valve deposits before using the applicable mechanical-cleaning procedure. Do not buy a scanner, oil bundle or cleaning service solely from this card.</x:v>
+      </x:c>
+      <x:c r="F460" s="9" t="str">
+        <x:v>Cold-start/DTC diagnosis; bulletin additive/follow-up for injector/combustion deposits; confirm intake-valve deposits before mechanical clean</x:v>
+      </x:c>
+      <x:c r="G460" s="9" t="str">
+        <x:v>TSB DIAGNOSTIC SEQUENCE / NO PRODUCT LINK</x:v>
+      </x:c>
+      <x:c r="H460" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I460" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J460" s="9" t="str">
+        <x:v>2007-2008 RS4 guided deposit diagnosis</x:v>
+      </x:c>
+      <x:c r="K460" s="9" t="str">
+        <x:v>specialist service</x:v>
+      </x:c>
+      <x:c r="L460" s="9" t="str"/>
+      <x:c r="M460" s="9" t="str">
+        <x:v>Additive cannot clean FSI intake valves and cleaning is conditional.</x:v>
+      </x:c>
+      <x:c r="N460" s="41" t="str">
+        <x:v>No scanner, oil bundle or cleaning-service purchase from card alone.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="461" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A461" s="40" t="str"/>
+      <x:c r="B461" s="9" t="str"/>
+      <x:c r="C461" s="9" t="str"/>
+      <x:c r="D461" s="9" t="str"/>
+      <x:c r="E461" s="9" t="str"/>
+      <x:c r="F461" s="9" t="str"/>
+      <x:c r="G461" s="9" t="str"/>
+      <x:c r="H461" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I461" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J461" s="9" t="str">
+        <x:v>current TSB 2014753/13 procedure/additive</x:v>
+      </x:c>
+      <x:c r="K461" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L461" s="9" t="str"/>
+      <x:c r="M461" s="9" t="str"/>
+      <x:c r="N461" s="41" t="str"/>
+    </x:row>
+    <x:row r="462" ht="963.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A462" s="40" t="n">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="B462" s="9" t="str">
+        <x:v>audi-rs4-rs5-carbon-buildup-2018</x:v>
+      </x:c>
+      <x:c r="C462" s="9" t="str">
+        <x:v>2018-2023 | Audi | RS4 | 2.9T</x:v>
+      </x:c>
+      <x:c r="D462" s="9" t="str">
+        <x:v>2018-2023 RS4 2.9T Cold-Start Misfire from Confirmed Inlet Deposits</x:v>
+      </x:c>
+      <x:c r="E462" s="9" t="str">
+        <x:v>Confirm the cold-start complaint, review the engine-control-unit event memory and verify inlet-port or inlet-valve deposits before cleaning. When that condition is confirmed, Audi TSB 2075530/1 directs the shop to remove the intake manifold or compressor and clean the inlet valves and ports by walnut blasting; the cylinder head remains installed. The cited Audi guidance does not support a mandatory 60,000-mile interval, a fixed price, dual catch cans, additive at every oil change, a 5,000-mile oil interval or a drive-hard prescription. Do not buy a catch can or cleaning product solely from this card.</x:v>
+      </x:c>
+      <x:c r="F462" s="9" t="str">
+        <x:v>Confirm cold-start event/event memory and inlet deposits; TSB manifold/compressor removal and walnut cleaning with head installed</x:v>
+      </x:c>
+      <x:c r="G462" s="9" t="str">
+        <x:v>TSB CONFIRMED-DEPOSIT SERVICE</x:v>
+      </x:c>
+      <x:c r="H462" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I462" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J462" s="9" t="str">
+        <x:v>2018-2023 RS4 2.9T TSB 2075530/1 confirmed cleaning</x:v>
+      </x:c>
+      <x:c r="K462" s="9" t="str">
+        <x:v>specialist intake service</x:v>
+      </x:c>
+      <x:c r="L462" s="9" t="str"/>
+      <x:c r="M462" s="9" t="str">
+        <x:v>Cleaning is valid only after deposit confirmation.</x:v>
+      </x:c>
+      <x:c r="N462" s="41" t="str">
+        <x:v>No interval, price, catch can, additive, oil schedule or drive-hard claim.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="463" ht="66" hidden="0" customHeight="1">
+      <x:c r="A463" s="40" t="str"/>
+      <x:c r="B463" s="9" t="str"/>
+      <x:c r="C463" s="9" t="str"/>
+      <x:c r="D463" s="9" t="str"/>
+      <x:c r="E463" s="9" t="str"/>
+      <x:c r="F463" s="9" t="str"/>
+      <x:c r="G463" s="9" t="str"/>
+      <x:c r="H463" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I463" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J463" s="9" t="str">
+        <x:v>TSB procedure/VIN</x:v>
+      </x:c>
+      <x:c r="K463" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L463" s="9" t="str"/>
+      <x:c r="M463" s="9" t="str"/>
+      <x:c r="N463" s="41" t="str"/>
+    </x:row>
+    <x:row r="464" ht="1227.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A464" s="40" t="n">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="B464" s="9" t="str">
+        <x:v>audi-rs5-b8-carbon-buildup-2013</x:v>
+      </x:c>
+      <x:c r="C464" s="9" t="str">
+        <x:v>2013-2015 | Audi | RS5 | 4.2L V8</x:v>
+      </x:c>
+      <x:c r="D464" s="9" t="str">
+        <x:v>4.2L V8 Carbon Buildup and High-Rev Issues</x:v>
+      </x:c>
+      <x:c r="E464" s="9" t="str">
+        <x:v>Confirm carbon buildup by scanning for misfire/fuel-trim faults, reviewing live data, and inspecting the intake valves with a borescope after removing the intake manifold. The proper repair is an intake-valve carbon cleaning service—typically walnut-shell blasting or manual chemical cleaning—while replacing the intake manifold gaskets, injector seals/O-rings, and PCV-related breather components if leaking or contributing to oil vapor. After reassembly, clear adaptations, perform a throttle-body/basic setting relearn, and road test to verify restored high-RPM pull and smooth idle. Independent shops typically charge about $800-$1,500 for a carbon clean on the 4.2 FSI V8, while dealer pricing can run roughly $1,500-$2,500 depending on how many seals and ancillary parts are replaced.</x:v>
+      </x:c>
+      <x:c r="F464" s="9" t="str">
+        <x:v>Misfire/fuel-trim/live-data and borescope confirmation; 4.2 FSI intake cleaning; manifold gaskets/injector seals and PCV parts only as disturbed/failed; adaptations</x:v>
+      </x:c>
+      <x:c r="G464" s="9" t="str">
+        <x:v>CONFIRMED-DEPOSIT / SERVICE-CONSUMABLE GATE</x:v>
+      </x:c>
+      <x:c r="H464" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I464" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J464" s="9" t="str">
+        <x:v>2013-2015 RS5 4.2 FSI intake diagnosis/cleaning</x:v>
+      </x:c>
+      <x:c r="K464" s="9" t="str">
+        <x:v>specialist intake service</x:v>
+      </x:c>
+      <x:c r="L464" s="9" t="str"/>
+      <x:c r="M464" s="9" t="str">
+        <x:v>Cleaning is repair role; seals/PCV are conditional.</x:v>
+      </x:c>
+      <x:c r="N464" s="41" t="str">
+        <x:v>Remove price claims and do not replace PCV unless leaking/failed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="465" ht="66" hidden="0" customHeight="1">
+      <x:c r="A465" s="40" t="str"/>
+      <x:c r="B465" s="9" t="str"/>
+      <x:c r="C465" s="9" t="str"/>
+      <x:c r="D465" s="9" t="str"/>
+      <x:c r="E465" s="9" t="str"/>
+      <x:c r="F465" s="9" t="str"/>
+      <x:c r="G465" s="9" t="str"/>
+      <x:c r="H465" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I465" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J465" s="9" t="str">
+        <x:v>VIN seals/procedure</x:v>
+      </x:c>
+      <x:c r="K465" s="9" t="str">
+        <x:v>manufacturer parts route</x:v>
+      </x:c>
+      <x:c r="L465" s="9" t="str"/>
+      <x:c r="M465" s="9" t="str"/>
+      <x:c r="N465" s="41" t="str"/>
+    </x:row>
+    <x:row r="466" ht="1122" hidden="0" customHeight="1">
+      <x:c r="A466" s="40" t="n">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="B466" s="9" t="str">
+        <x:v>audi-rs5-carbon-buildup-2018</x:v>
+      </x:c>
+      <x:c r="C466" s="9" t="str">
+        <x:v>2018-2026 | Audi | RS5</x:v>
+      </x:c>
+      <x:c r="D466" s="9" t="str">
+        <x:v>Direct Injection Carbon Buildup on Intake Valves</x:v>
+      </x:c>
+      <x:c r="E466" s="9" t="str">
+        <x:v>Confirm intake-valve carbon buildup by scanning for misfire faults, reviewing fuel trims, and inspecting the intake valves with a borescope through the intake ports after removing the intake manifold. The proper repair is an intake-valve cleaning service, typically walnut-shell blasting each intake port with the valves closed, then replacing the intake manifold gaskets and any disturbed PCV or breather seals before clearing adaptations and road-testing. If misfires persist, inspect and replace worn spark plugs or ignition coils as needed, since heavy deposits can foul plugs and mimic ignition faults. Typical cost is about $800-$1,500 depending on labor rates and how much disassembly is required.</x:v>
+      </x:c>
+      <x:c r="F466" s="9" t="str">
+        <x:v>Confirm exact engine and deposits via misfire/fuel trims/borescope; engine-specific cleaning and disturbed seals; ignition only if separately failed</x:v>
+      </x:c>
+      <x:c r="G466" s="9" t="str">
+        <x:v>ENGINE / CONFIRMED-DEPOSIT SERVICE</x:v>
+      </x:c>
+      <x:c r="H466" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I466" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J466" s="9" t="str">
+        <x:v>2018-2026 RS5 intake diagnosis/cleaning</x:v>
+      </x:c>
+      <x:c r="K466" s="9" t="str">
+        <x:v>specialist intake service</x:v>
+      </x:c>
+      <x:c r="L466" s="9" t="str"/>
+      <x:c r="M466" s="9" t="str">
+        <x:v>Range needs engine/VIN procedure and misfires may be ignition.</x:v>
+      </x:c>
+      <x:c r="N466" s="41" t="str">
+        <x:v>No fixed price or plugs/coils without testing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="467" ht="1003.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A467" s="40" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="B467" s="9" t="str">
+        <x:v>audi-rs5-turbo-coolant-2018</x:v>
+      </x:c>
+      <x:c r="C467" s="9" t="str">
+        <x:v>2021-2024 | Audi | RS5 | 2.9L V6 TFSI</x:v>
+      </x:c>
+      <x:c r="D467" s="9" t="str">
+        <x:v>2021-2024 RS5 V6 Coolant-Pump Leak Diagnosis - TSB 2070349/4</x:v>
+      </x:c>
+      <x:c r="E467" s="9" t="str">
+        <x:v>Locate the leak before replacing parts. Clean and dry the area, fill the cooling system to maximum, inspect at idle and at engine speeds up to about 2,500 rpm, and perform the Workshop Manual cooling-system leak test. If no further leak is detected, continue observation without replacing parts. If a leak recurs, replace only the component or components causing the leak and document the finding with clear photos or video; a pump-leak repair also requires a photo of the pump production date. Inspect the vacuum circuit and N649 when contamination or P0299 is present, following current Audi workshop and parts information.</x:v>
+      </x:c>
+      <x:c r="F467" s="9" t="str">
+        <x:v>Clean/dry/fill/idle-to-2500/pressure-test; exact recurring leak component; pump-date evidence; P0299 vacuum/N649 branch</x:v>
+      </x:c>
+      <x:c r="G467" s="9" t="str">
+        <x:v>SOURCE-YEAR MISMATCH / TSB LEAK-CONFIRMATION</x:v>
+      </x:c>
+      <x:c r="H467" s="9" t="str">
+        <x:v>Audi RS5 water-pump catalog</x:v>
+      </x:c>
+      <x:c r="I467" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/RS5/Water-Pump/</x:v>
+      </x:c>
+      <x:c r="J467" s="9" t="str">
+        <x:v>2021-2024 RS5 2.9T after confirmed pump leak/VIN</x:v>
+      </x:c>
+      <x:c r="K467" s="9" t="str">
+        <x:v>conditional pump catalog</x:v>
+      </x:c>
+      <x:c r="L467" s="9" t="str"/>
+      <x:c r="M467" s="9" t="str">
+        <x:v>No returned leak means observation and P0299 may be vacuum path.</x:v>
+      </x:c>
+      <x:c r="N467" s="41" t="str">
+        <x:v>Identifier says 2018; no turbo-coolant line inference.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="468" ht="66" hidden="0" customHeight="1">
+      <x:c r="A468" s="40" t="str"/>
+      <x:c r="B468" s="9" t="str"/>
+      <x:c r="C468" s="9" t="str"/>
+      <x:c r="D468" s="9" t="str"/>
+      <x:c r="E468" s="9" t="str"/>
+      <x:c r="F468" s="9" t="str"/>
+      <x:c r="G468" s="9" t="str"/>
+      <x:c r="H468" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I468" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J468" s="9" t="str">
+        <x:v>TSB 2070349/4</x:v>
+      </x:c>
+      <x:c r="K468" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L468" s="9" t="str"/>
+      <x:c r="M468" s="9" t="str"/>
+      <x:c r="N468" s="41" t="str"/>
+    </x:row>
+    <x:row r="469" ht="765.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A469" s="40" t="n">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="B469" s="9" t="str">
+        <x:v>audi-rs6-air-suspension-2020</x:v>
+      </x:c>
+      <x:c r="C469" s="9" t="str">
+        <x:v>2021-2024 | Audi | RS6</x:v>
+      </x:c>
+      <x:c r="D469" s="9" t="str">
+        <x:v>2021-2024 RS6 Air-Suspension Warning - Check C1260F0 or U112100</x:v>
+      </x:c>
+      <x:c r="E469" s="9" t="str">
+        <x:v>Have the wiring and connector contacts between suspension controller J775 and compressor controller J1135 inspected first. Audi says to clear a first passive or sporadic occurrence and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after the wiring check, the bulletin directs replacement of J1135 under the applicable service procedure. Do not replace air struts, a compressor or an unverified aftermarket assembly solely from this warning card.</x:v>
+      </x:c>
+      <x:c r="F469" s="9" t="str">
+        <x:v>J775-J1135 wiring/contact first; clear first passive; conditional J1135 after active/static or second return</x:v>
+      </x:c>
+      <x:c r="G469" s="9" t="str">
+        <x:v>SOURCE-YEAR MISMATCH / TSB CONDITIONAL MODULE</x:v>
+      </x:c>
+      <x:c r="H469" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I469" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J469" s="9" t="str">
+        <x:v>2021-2024 RS6 suspension bulletin</x:v>
+      </x:c>
+      <x:c r="K469" s="9" t="str">
+        <x:v>manufacturer suspension service</x:v>
+      </x:c>
+      <x:c r="L469" s="9" t="str"/>
+      <x:c r="M469" s="9" t="str">
+        <x:v>Fault status/occurrence controls replacement.</x:v>
+      </x:c>
+      <x:c r="N469" s="41" t="str">
+        <x:v>Identifier says 2020; no strut/compressor link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="470" ht="831.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A470" s="40" t="n">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="B470" s="9" t="str">
+        <x:v>audi-rs6-carbon-buildup-2020</x:v>
+      </x:c>
+      <x:c r="C470" s="9" t="str">
+        <x:v>2021-2024 | Audi | RS6 | 4.0T V8</x:v>
+      </x:c>
+      <x:c r="D470" s="9" t="str">
+        <x:v>2021-2024 RS6 4.0T Cold-Start Misfire from Confirmed Inlet Deposits</x:v>
+      </x:c>
+      <x:c r="E470" s="9" t="str">
+        <x:v>Confirm the cold-start complaint, review the engine-control-unit event memory and verify inlet-port or inlet-valve deposits before cleaning. When that condition is confirmed, Audi TSB 2075530/1 directs the shop to remove the intake manifold or compressor and clean the inlet valves and ports by walnut blasting; the cylinder head remains installed. The cited Audi guidance does not specify a 30,000-40,000-mile interval, a fixed price or a mandatory catch can. Do not buy a catch can or cleaning product solely from this card.</x:v>
+      </x:c>
+      <x:c r="F470" s="9" t="str">
+        <x:v>Confirm 2021-2024 cold-start event/event memory/inlet deposits; TSB walnut clean with head installed</x:v>
+      </x:c>
+      <x:c r="G470" s="9" t="str">
+        <x:v>SOURCE-YEAR MISMATCH / TSB CONFIRMED CLEANING</x:v>
+      </x:c>
+      <x:c r="H470" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I470" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J470" s="9" t="str">
+        <x:v>2021-2024 RS6 4.0T TSB cleaning</x:v>
+      </x:c>
+      <x:c r="K470" s="9" t="str">
+        <x:v>specialist intake service</x:v>
+      </x:c>
+      <x:c r="L470" s="9" t="str"/>
+      <x:c r="M470" s="9" t="str">
+        <x:v>Cleaning is conditional on confirmed inlet deposits.</x:v>
+      </x:c>
+      <x:c r="N470" s="41" t="str">
+        <x:v>No interval/price/catch-can claim.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="471" ht="66" hidden="0" customHeight="1">
+      <x:c r="A471" s="40" t="str"/>
+      <x:c r="B471" s="9" t="str"/>
+      <x:c r="C471" s="9" t="str"/>
+      <x:c r="D471" s="9" t="str"/>
+      <x:c r="E471" s="9" t="str"/>
+      <x:c r="F471" s="9" t="str"/>
+      <x:c r="G471" s="9" t="str"/>
+      <x:c r="H471" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I471" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J471" s="9" t="str">
+        <x:v>TSB 2075530/1</x:v>
+      </x:c>
+      <x:c r="K471" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L471" s="9" t="str"/>
+      <x:c r="M471" s="9" t="str"/>
+      <x:c r="N471" s="41" t="str"/>
+    </x:row>
+    <x:row r="472" ht="528" hidden="0" customHeight="1">
+      <x:c r="A472" s="40" t="n">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="B472" s="9" t="str">
+        <x:v>audi-rs6-rs7-carbon-buildup-2013</x:v>
+      </x:c>
+      <x:c r="C472" s="9" t="str">
+        <x:v>2013-2023 | Audi | RS6 | 4.0T V8</x:v>
+      </x:c>
+      <x:c r="D472" s="9" t="str">
+        <x:v>Severe Carbon Buildup on Intake Valves (4.0T V8)</x:v>
+      </x:c>
+      <x:c r="E472" s="9" t="str">
+        <x:v>WALNUT BLASTING: Remove both intake manifolds and blast walnut shells through all intake ports ($1,200-$2,000 for V8). Repeat every 60,000 miles. PREVENTION: Install catch can ($500-$800 for twin-turbo setup). Add Liqui Moly Intake Valve Cleaner to every oil change. Change oil every 5,000 miles. Drive car hard regularly.</x:v>
+      </x:c>
+      <x:c r="F472" s="9" t="str">
+        <x:v>Split generations and confirm inlet deposits after misfire/fuel/air/compression diagnosis; generation-specific cleaning</x:v>
+      </x:c>
+      <x:c r="G472" s="9" t="str">
+        <x:v>MULTI-GENERATION / CONFIRMED-DEPOSIT SERVICE</x:v>
+      </x:c>
+      <x:c r="H472" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I472" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J472" s="9" t="str">
+        <x:v>2013-2023 RS6/RS7 4.0T generation-specific diagnosis/cleaning</x:v>
+      </x:c>
+      <x:c r="K472" s="9" t="str">
+        <x:v>specialist intake service</x:v>
+      </x:c>
+      <x:c r="L472" s="9" t="str"/>
+      <x:c r="M472" s="9" t="str">
+        <x:v>Eleven-year range and two generations cannot use one interval/procedure.</x:v>
+      </x:c>
+      <x:c r="N472" s="41" t="str">
+        <x:v>Remove fixed interval, catch can, chemical, oil and drive-hard claims.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="473" ht="646.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A473" s="40" t="n">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="B473" s="9" t="str">
+        <x:v>audi-rs6-rs7-motor-mounts-2013</x:v>
+      </x:c>
+      <x:c r="C473" s="9" t="str">
+        <x:v>2013-2023 | Audi | RS6 | 4.0T V8</x:v>
+      </x:c>
+      <x:c r="D473" s="9" t="str">
+        <x:v>Premature Motor Mount Failure (4.0T V8)</x:v>
+      </x:c>
+      <x:c r="E473" s="9" t="str">
+        <x:v>Replace failed motor mounts with OEM or upgraded mounts ($800-$1,500 for all mounts). Upgraded aftermarket mounts (034 Motorsport, ECS) offer better durability for high-torque engines ($400-$600 per mount). If you drive aggressively or track the car, consider upgrading to performance mounts preventively. Monitor for vibrations and clunking—early replacement prevents driveline damage.</x:v>
+      </x:c>
+      <x:c r="F473" s="9" t="str">
+        <x:v>Confirm failed side/mount through loaded test and scan if active mounts; generation/VIN exact OEM or verified upgrade; pair only if strategy requires; alignment/support procedure</x:v>
+      </x:c>
+      <x:c r="G473" s="9" t="str">
+        <x:v>GENERATION / ACTIVE-MOUNT / SIDE GATE</x:v>
+      </x:c>
+      <x:c r="H473" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I473" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J473" s="9" t="str">
+        <x:v>2013-2023 RS6/RS7 active/passive mount diagnosis</x:v>
+      </x:c>
+      <x:c r="K473" s="9" t="str">
+        <x:v>specialist driveline service</x:v>
+      </x:c>
+      <x:c r="L473" s="9" t="str"/>
+      <x:c r="M473" s="9" t="str">
+        <x:v>Generations and active mount systems differ.</x:v>
+      </x:c>
+      <x:c r="N473" s="41" t="str">
+        <x:v>No preventive performance-mount recommendation or all-mount bundle without live exact fitment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="474" ht="66" hidden="0" customHeight="1">
+      <x:c r="A474" s="40" t="str"/>
+      <x:c r="B474" s="9" t="str"/>
+      <x:c r="C474" s="9" t="str"/>
+      <x:c r="D474" s="9" t="str"/>
+      <x:c r="E474" s="9" t="str"/>
+      <x:c r="F474" s="9" t="str"/>
+      <x:c r="G474" s="9" t="str"/>
+      <x:c r="H474" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I474" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J474" s="9" t="str">
+        <x:v>VIN mount/side/active-system parts</x:v>
+      </x:c>
+      <x:c r="K474" s="9" t="str">
+        <x:v>manufacturer parts route</x:v>
+      </x:c>
+      <x:c r="L474" s="9" t="str"/>
+      <x:c r="M474" s="9" t="str"/>
+      <x:c r="N474" s="41" t="str"/>
+    </x:row>
+    <x:row r="475" ht="699.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A475" s="40" t="n">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="B475" s="9" t="str">
+        <x:v>audi-rs7-air-suspension-2014</x:v>
+      </x:c>
+      <x:c r="C475" s="9" t="str">
+        <x:v>2021-2025 | Audi | RS7</x:v>
+      </x:c>
+      <x:c r="D475" s="9" t="str">
+        <x:v>2021-2025 RS7 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
+      </x:c>
+      <x:c r="E475" s="9" t="str">
+        <x:v>Inspect the wiring and connectors between J775 and J1135 before replacing a component. For a first passive/sporadic occurrence, clear the fault and release the vehicle. If the fault is active/static after wiring and connector inspection, or the same passive/sporadic fault returns a second time, replace J1135 using current Audi repair and parts information. Audi notes that improved J1135 software remains under development.</x:v>
+      </x:c>
+      <x:c r="F475" s="9" t="str">
+        <x:v>J775-J1135 wiring/connectors; first passive clear; conditional J1135 after active/static or second return</x:v>
+      </x:c>
+      <x:c r="G475" s="9" t="str">
+        <x:v>SOURCE-YEAR MISMATCH / TSB CONDITIONAL MODULE</x:v>
+      </x:c>
+      <x:c r="H475" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I475" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J475" s="9" t="str">
+        <x:v>2021-2025 RS7 TSB 2059363/6</x:v>
+      </x:c>
+      <x:c r="K475" s="9" t="str">
+        <x:v>manufacturer suspension service</x:v>
+      </x:c>
+      <x:c r="L475" s="9" t="str"/>
+      <x:c r="M475" s="9" t="str">
+        <x:v>Module replacement is conditional.</x:v>
+      </x:c>
+      <x:c r="N475" s="41" t="str">
+        <x:v>Identifier says 2014; no suspension hardware link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="476" ht="211.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A476" s="40" t="n">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="B476" s="9" t="str">
+        <x:v>audi-rs7-carbon-buildup-2014</x:v>
+      </x:c>
+      <x:c r="C476" s="9" t="str">
+        <x:v>2014-2026 | Audi | RS7 | 4.0T</x:v>
+      </x:c>
+      <x:c r="D476" s="9" t="str">
+        <x:v>4.0T Carbon Deposit Accumulation</x:v>
+      </x:c>
+      <x:c r="E476" s="9" t="str">
+        <x:v>Walnut blast every 30,000-40,000 miles. Install dual catch can setup for both turbo sides.</x:v>
+      </x:c>
+      <x:c r="F476" s="9" t="str">
+        <x:v>Split 4.0T generations; confirm deposits via event/misfire/air/fuel/compression and intake inspection; generation-specific cleaning</x:v>
+      </x:c>
+      <x:c r="G476" s="9" t="str">
+        <x:v>MULTI-GENERATION / CONFIRMED-DEPOSIT SERVICE</x:v>
+      </x:c>
+      <x:c r="H476" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I476" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J476" s="9" t="str">
+        <x:v>2014-2026 RS7 4.0T diagnosis/cleaning</x:v>
+      </x:c>
+      <x:c r="K476" s="9" t="str">
+        <x:v>specialist intake service</x:v>
+      </x:c>
+      <x:c r="L476" s="9" t="str"/>
+      <x:c r="M476" s="9" t="str">
+        <x:v>No evidence supports one 30k-40k schedule.</x:v>
+      </x:c>
+      <x:c r="N476" s="41" t="str">
+        <x:v>No dual catch-can mandate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="477" ht="198" hidden="0" customHeight="1">
+      <x:c r="A477" s="40" t="n">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="B477" s="9" t="str">
+        <x:v>audi-rs7-turbo-coolant-2014</x:v>
+      </x:c>
+      <x:c r="C477" s="9" t="str">
+        <x:v>2014-2026 | Audi | RS7 | 4.0T</x:v>
+      </x:c>
+      <x:c r="D477" s="9" t="str">
+        <x:v>4.0T Twin-Turbo Coolant System Degradation</x:v>
+      </x:c>
+      <x:c r="E477" s="9" t="str">
+        <x:v>Replace turbo coolant lines proactively at 50,000 miles. Upgrade to silicone lines where possible.</x:v>
+      </x:c>
+      <x:c r="F477" s="9" t="str">
+        <x:v>Pressure-test and identify exact turbo/coolant leak source; generation/VIN/side hose or line only if failed; current coolant/bleed</x:v>
+      </x:c>
+      <x:c r="G477" s="9" t="str">
+        <x:v>LEAK-SOURCE / GENERATION / SIDE GATE</x:v>
+      </x:c>
+      <x:c r="H477" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I477" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J477" s="9" t="str">
+        <x:v>2014-2026 RS7 turbo cooling leak diagnosis</x:v>
+      </x:c>
+      <x:c r="K477" s="9" t="str">
+        <x:v>specialist cooling service</x:v>
+      </x:c>
+      <x:c r="L477" s="9" t="str"/>
+      <x:c r="M477" s="9" t="str">
+        <x:v>No basis for proactive 50k replacement across generations.</x:v>
+      </x:c>
+      <x:c r="N477" s="41" t="str">
+        <x:v>No silicone upgrade without verified temperature/pressure/interfaces and exact live fitment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="478" ht="66" hidden="0" customHeight="1">
+      <x:c r="A478" s="40" t="str"/>
+      <x:c r="B478" s="9" t="str"/>
+      <x:c r="C478" s="9" t="str"/>
+      <x:c r="D478" s="9" t="str"/>
+      <x:c r="E478" s="9" t="str"/>
+      <x:c r="F478" s="9" t="str"/>
+      <x:c r="G478" s="9" t="str"/>
+      <x:c r="H478" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I478" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J478" s="9" t="str">
+        <x:v>VIN/side line parts</x:v>
+      </x:c>
+      <x:c r="K478" s="9" t="str">
+        <x:v>manufacturer parts route</x:v>
+      </x:c>
+      <x:c r="L478" s="9" t="str"/>
+      <x:c r="M478" s="9" t="str"/>
+      <x:c r="N478" s="41" t="str"/>
+    </x:row>
+    <x:row r="479" ht="567.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A479" s="40" t="n">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="B479" s="9" t="str">
+        <x:v>audi-rs7-turbo-wastegate-2014</x:v>
+      </x:c>
+      <x:c r="C479" s="9" t="str">
+        <x:v>2014-2017 | Audi | RS7 | 4.0L TFSI twin-turbo V8</x:v>
+      </x:c>
+      <x:c r="D479" s="9" t="str">
+        <x:v>2014-2017 RS7 Turbocharger Oil-Strainer Safety Recall 21H7 / 22V178 - Check VIN</x:v>
+      </x:c>
+      <x:c r="E479" s="9" t="str">
+        <x:v>Check the VIN for open Audi campaign 21H7 in Elsa or the NHTSA recall lookup. The authorized dealer replaces the turbocharger oil strainer, changes the engine oil and filter, and performs the campaign scan-tool turbo/boost-system check at no charge. Follow the campaign procedure for any damage found; do not buy a turbocharger, actuator or gasket kit from this card.</x:v>
+      </x:c>
+      <x:c r="F479" s="9" t="str">
+        <x:v>VIN/21H7/22V178 check; dealer oil strainer, oil/filter and campaign turbo/boost check; damage branch per campaign</x:v>
+      </x:c>
+      <x:c r="G479" s="9" t="str">
+        <x:v>SOURCE-ID MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H479" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I479" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J479" s="9" t="str">
+        <x:v>2014-2017 RS7 21H7</x:v>
+      </x:c>
+      <x:c r="K479" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L479" s="9" t="str"/>
+      <x:c r="M479" s="9" t="str">
+        <x:v>Recall is oil-strainer safety work, not wastegate.</x:v>
+      </x:c>
+      <x:c r="N479" s="41" t="str">
+        <x:v>Rename/re-key; no turbo/actuator/gasket link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="480" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A480" s="40" t="str"/>
+      <x:c r="B480" s="9" t="str"/>
+      <x:c r="C480" s="9" t="str"/>
+      <x:c r="D480" s="9" t="str"/>
+      <x:c r="E480" s="9" t="str"/>
+      <x:c r="F480" s="9" t="str"/>
+      <x:c r="G480" s="9" t="str"/>
+      <x:c r="H480" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I480" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J480" s="9" t="str">
+        <x:v>22V178 VIN history</x:v>
+      </x:c>
+      <x:c r="K480" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L480" s="9" t="str"/>
+      <x:c r="M480" s="9" t="str"/>
+      <x:c r="N480" s="41" t="str"/>
+    </x:row>
+    <x:row r="481" ht="567.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A481" s="40" t="n">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="B481" s="9" t="str">
+        <x:v>audi-rsq8-4.0t-coolant-2020</x:v>
+      </x:c>
+      <x:c r="C481" s="9" t="str">
+        <x:v>2020-2021 | Audi | RS Q8 | 4.0T V8</x:v>
+      </x:c>
+      <x:c r="D481" s="9" t="str">
+        <x:v>2020-Early 2021 RS Q8 Red Coolant Warning - Check G407 per TSB 2062951/4</x:v>
+      </x:c>
+      <x:c r="E481" s="9" t="str">
+        <x:v>Have the vehicle checked with Audi Guided Fault Finding and inspect G407 and its O-ring. Replace G407 only if the O-ring is damaged or pinched and the diagnosis matches the bulletin; follow the related Audi diagnostic path if additional listed faults are stored. Do not replace turbo coolant hoses, pumps or other cooling parts from this card alone.</x:v>
+      </x:c>
+      <x:c r="F481" s="9" t="str">
+        <x:v>Guided G407/O-ring diagnosis; replace G407 only for damaged/pinched O-ring and matching TSB; related fault path separately</x:v>
+      </x:c>
+      <x:c r="G481" s="9" t="str">
+        <x:v>TSB SENSOR/O-RING CONDITIONAL SERVICE</x:v>
+      </x:c>
+      <x:c r="H481" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I481" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J481" s="9" t="str">
+        <x:v>2020-early 2021 RS Q8 TSB 2062951/4</x:v>
+      </x:c>
+      <x:c r="K481" s="9" t="str">
+        <x:v>manufacturer cooling diagnosis</x:v>
+      </x:c>
+      <x:c r="L481" s="9" t="str"/>
+      <x:c r="M481" s="9" t="str">
+        <x:v>Other cooling parts not established.</x:v>
+      </x:c>
+      <x:c r="N481" s="41" t="str">
+        <x:v>No turbo hose/pump link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="482" ht="237.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A482" s="40" t="n">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="B482" s="9" t="str">
+        <x:v>audi-rsq8-air-suspension-2020</x:v>
+      </x:c>
+      <x:c r="C482" s="9" t="str">
+        <x:v>2020-2026 | Audi | RS Q8</x:v>
+      </x:c>
+      <x:c r="D482" s="9" t="str">
+        <x:v>Adaptive Air Suspension Failure Under SUV Weight</x:v>
+      </x:c>
+      <x:c r="E482" s="9" t="str">
+        <x:v>Replace air struts as they fail. Budget for compressor replacement. Consider heavy-duty aftermarket options designed for the RS Q8 weight.</x:v>
+      </x:c>
+      <x:c r="F482" s="9" t="str">
+        <x:v>Sag/leak/runtime, compressor output, valve/J1135/wiring and height-sensor diagnosis; exact failed component and calibration</x:v>
+      </x:c>
+      <x:c r="G482" s="9" t="str">
+        <x:v>SYSTEM DIAGNOSIS GATE</x:v>
+      </x:c>
+      <x:c r="H482" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I482" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J482" s="9" t="str">
+        <x:v>2020-2026 RS Q8 air-suspension diagnosis</x:v>
+      </x:c>
+      <x:c r="K482" s="9" t="str">
+        <x:v>specialist suspension service</x:v>
+      </x:c>
+      <x:c r="L482" s="9" t="str"/>
+      <x:c r="M482" s="9" t="str">
+        <x:v>Weight alone does not identify failed strut/compressor.</x:v>
+      </x:c>
+      <x:c r="N482" s="41" t="str">
+        <x:v>No heavy-duty aftermarket option without exact live fitment and calibration plan.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="483" ht="66" hidden="0" customHeight="1">
+      <x:c r="A483" s="40" t="str"/>
+      <x:c r="B483" s="9" t="str"/>
+      <x:c r="C483" s="9" t="str"/>
+      <x:c r="D483" s="9" t="str"/>
+      <x:c r="E483" s="9" t="str"/>
+      <x:c r="F483" s="9" t="str"/>
+      <x:c r="G483" s="9" t="str"/>
+      <x:c r="H483" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I483" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J483" s="9" t="str">
+        <x:v>VIN/PR-code parts/calibration</x:v>
+      </x:c>
+      <x:c r="K483" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L483" s="9" t="str"/>
+      <x:c r="M483" s="9" t="str"/>
+      <x:c r="N483" s="41" t="str"/>
+    </x:row>
+    <x:row r="484" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A484" s="40" t="n">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="B484" s="9" t="str">
+        <x:v>audi-rsq8-air-suspension-leak-2020</x:v>
+      </x:c>
+      <x:c r="C484" s="9" t="str">
+        <x:v>2020-2026 | Audi | RS Q8</x:v>
+      </x:c>
+      <x:c r="D484" s="9" t="str">
+        <x:v>Adaptive Air Suspension Air Spring Leaks</x:v>
+      </x:c>
+      <x:c r="E484" s="9" t="str"/>
+      <x:c r="F484" s="9" t="str"/>
+      <x:c r="G484" s="9" t="str">
+        <x:v>SOURCE HOW-TO-FIX REQUIRED / NO LINK</x:v>
+      </x:c>
+      <x:c r="H484" s="9" t="str"/>
+      <x:c r="I484" s="9" t="str"/>
+      <x:c r="J484" s="9" t="str"/>
+      <x:c r="K484" s="9" t="str"/>
+      <x:c r="L484" s="9" t="str"/>
+      <x:c r="M484" s="9" t="str">
+        <x:v>The source has no How to Fix instructions.</x:v>
+      </x:c>
+      <x:c r="N484" s="41" t="str">
+        <x:v>Add per-corner leak, compressor/valve/wiring diagnosis and VIN/calibration procedure before links.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="485" ht="607.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A485" s="40" t="n">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="B485" s="9" t="str">
+        <x:v>audi-rsq8-brake-wear-2020</x:v>
+      </x:c>
+      <x:c r="C485" s="9" t="str">
+        <x:v>2020-2021 | Audi | RS Q8</x:v>
+      </x:c>
+      <x:c r="D485" s="9" t="str">
+        <x:v>2020-2021 RS Q8 Front Steel-Brake Squeal - TSB 2062052/1</x:v>
+      </x:c>
+      <x:c r="E485" s="9" t="str">
+        <x:v>Confirm the frequency and operating conditions and inspect the discs for corrosion, grooves or glazing. When the bulletin applies, Audi directs replacement of the front pad set using current parts information followed by the specified bedding procedure. Do not perform ABS stops for bedding, and do not replace rotors or buy aftermarket pads solely from the prior wear narrative.</x:v>
+      </x:c>
+      <x:c r="F485" s="9" t="str">
+        <x:v>Confirm front steel brakes, frequency/conditions and disc corrosion/grooves/glazing; bulletin front pad set and specified bedding only</x:v>
+      </x:c>
+      <x:c r="G485" s="9" t="str">
+        <x:v>TSB / BRAKE-OPTION CONDITIONAL PAD SET</x:v>
+      </x:c>
+      <x:c r="H485" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I485" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J485" s="9" t="str">
+        <x:v>2020-2021 RS Q8 TSB 2062052/1 current pad set/bedding</x:v>
+      </x:c>
+      <x:c r="K485" s="9" t="str">
+        <x:v>manufacturer brake service</x:v>
+      </x:c>
+      <x:c r="L485" s="9" t="str"/>
+      <x:c r="M485" s="9" t="str">
+        <x:v>Steel versus ceramic option and TSB conditions matter.</x:v>
+      </x:c>
+      <x:c r="N485" s="41" t="str">
+        <x:v>No aftermarket pads/rotors or ABS-stop bedding.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="486" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A486" s="40" t="str"/>
+      <x:c r="B486" s="9" t="str"/>
+      <x:c r="C486" s="9" t="str"/>
+      <x:c r="D486" s="9" t="str"/>
+      <x:c r="E486" s="9" t="str"/>
+      <x:c r="F486" s="9" t="str"/>
+      <x:c r="G486" s="9" t="str"/>
+      <x:c r="H486" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I486" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J486" s="9" t="str">
+        <x:v>steel-brake noise/rotor condition diagnosis</x:v>
+      </x:c>
+      <x:c r="K486" s="9" t="str">
+        <x:v>specialist brake service</x:v>
+      </x:c>
+      <x:c r="L486" s="9" t="str"/>
+      <x:c r="M486" s="9" t="str"/>
+      <x:c r="N486" s="41" t="str"/>
+    </x:row>
+    <x:row r="487" ht="897.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A487" s="40" t="n">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="B487" s="9" t="str">
+        <x:v>audi-s3-carbon-buildup-2015</x:v>
+      </x:c>
+      <x:c r="C487" s="9" t="str">
+        <x:v>2015-2019 | Audi | S3 | S3 | EA888 Gen 3</x:v>
+      </x:c>
+      <x:c r="D487" s="9" t="str">
+        <x:v>Carbon Buildup on Intake Valves (Pre-Dual Injection EA888 Gen 3)</x:v>
+      </x:c>
+      <x:c r="E487" s="9" t="str">
+        <x:v>WALNUT BLASTING: Remove intake manifold and blast intake valve ports with crushed walnut shells ($500-$1,000). Repeat every 40,000-60,000 miles. CATCH CAN: Install an oil catch can ($200-$400) to capture PCV vapors before they reach intake valves—significantly slows carbon buildup. OIL CHANGES: Use high-quality synthetic oil and change every 5,000 miles. DRIVING HABITS: Regular spirited driving helps burn off some deposits. NOTE: 2020+ S3 models with EA888 Gen 3B dual injection are largely immune to this issue.</x:v>
+      </x:c>
+      <x:c r="F487" s="9" t="str">
+        <x:v>Confirm engine/injection system and deposits; ignition/fuel/compression diagnosis; engine-specific cleaning</x:v>
+      </x:c>
+      <x:c r="G487" s="9" t="str">
+        <x:v>ENGINE / CONFIRMED-DEPOSIT SERVICE</x:v>
+      </x:c>
+      <x:c r="H487" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I487" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J487" s="9" t="str">
+        <x:v>2015-2019 S3 EA888 intake diagnosis/cleaning</x:v>
+      </x:c>
+      <x:c r="K487" s="9" t="str">
+        <x:v>specialist intake service</x:v>
+      </x:c>
+      <x:c r="L487" s="9" t="str"/>
+      <x:c r="M487" s="9" t="str">
+        <x:v>Source claim about 2020+ dual injection is market/configuration dependent and outside row years.</x:v>
+      </x:c>
+      <x:c r="N487" s="41" t="str">
+        <x:v>Remove interval, catch can, oil schedule and spirited-driving claims.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="488" ht="224.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A488" s="40" t="n">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="B488" s="9" t="str">
+        <x:v>audi-s3-dq250-mechatronic-2015</x:v>
+      </x:c>
+      <x:c r="C488" s="9" t="str">
+        <x:v>2015-2024 | Audi | S3</x:v>
+      </x:c>
+      <x:c r="D488" s="9" t="str">
+        <x:v>DQ250 DSG Mechatronic Unit Failure</x:v>
+      </x:c>
+      <x:c r="E488" s="9" t="str">
+        <x:v>Replace or rebuild mechatronic unit. Regular DSG fluid changes every 40,000 miles help prevent premature failure.</x:v>
+      </x:c>
+      <x:c r="F488" s="9" t="str">
+        <x:v>Confirm DQ250 code (exclude DQ381); faults/pressure/adaptation/fluid and clutch/mechanical branches; exact service/mechatronic only by diagnosis</x:v>
+      </x:c>
+      <x:c r="G488" s="9" t="str">
+        <x:v>TRANSMISSION-CODE / COMPONENT GATE</x:v>
+      </x:c>
+      <x:c r="H488" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I488" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J488" s="9" t="str">
+        <x:v>2015-2024 S3 DQ250/DQ381 identification and diagnosis</x:v>
+      </x:c>
+      <x:c r="K488" s="9" t="str">
+        <x:v>specialist transmission service</x:v>
+      </x:c>
+      <x:c r="L488" s="9" t="str"/>
+      <x:c r="M488" s="9" t="str">
+        <x:v>Not all years use DQ250.</x:v>
+      </x:c>
+      <x:c r="N488" s="41" t="str">
+        <x:v>Do not prescribe mechatronic or 40k service across wrong transmission.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="489" ht="66" hidden="0" customHeight="1">
+      <x:c r="A489" s="40" t="str"/>
+      <x:c r="B489" s="9" t="str"/>
+      <x:c r="C489" s="9" t="str"/>
+      <x:c r="D489" s="9" t="str"/>
+      <x:c r="E489" s="9" t="str"/>
+      <x:c r="F489" s="9" t="str"/>
+      <x:c r="G489" s="9" t="str"/>
+      <x:c r="H489" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I489" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J489" s="9" t="str">
+        <x:v>VIN transmission/software/parts</x:v>
+      </x:c>
+      <x:c r="K489" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L489" s="9" t="str"/>
+      <x:c r="M489" s="9" t="str"/>
+      <x:c r="N489" s="41" t="str"/>
+    </x:row>
+    <x:row r="490" ht="897.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A490" s="40" t="n">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="B490" s="9" t="str">
+        <x:v>audi-s3-dsg-mechatronic-2015</x:v>
+      </x:c>
+      <x:c r="C490" s="9" t="str">
+        <x:v>2015-2024 | Audi | S3 | S3</x:v>
+      </x:c>
+      <x:c r="D490" s="9" t="str">
+        <x:v>DQ381 S-Tronic Mechatronic Unit Failure</x:v>
+      </x:c>
+      <x:c r="E490" s="9" t="str">
+        <x:v>EARLY SYMPTOMS (jerky shifts): DSG fluid and filter service ($500-$700) plus dealer software update. This may resolve early-stage issues. MECHATRONIC FAILURE: Replace mechatronic unit ($2,000-$4,000 installed) plus TCU coding. Remanufactured units available for $1,500-$2,500. CLUTCH PACK FAILURE: Replace dual clutch pack ($3,000-$5,000). PREVENTION: Service DSG fluid every 40,000 miles—ignore Audi's 'lifetime fill' claim. Use ONLY OEM Audi DSG fluid (G 052 182 A2) or approved Pentosin FFL-2. Avoid aggressive launches and excessive clutch slip in traffic.</x:v>
+      </x:c>
+      <x:c r="F490" s="9" t="str">
+        <x:v>Confirm DQ381 versus DQ250 and code; faults/pressure/clutch/adaptation/software; exact fluid/filter and component branch</x:v>
+      </x:c>
+      <x:c r="G490" s="9" t="str">
+        <x:v>SOURCE RANGE/FLUID ERROR / TRANSMISSION GATE</x:v>
+      </x:c>
+      <x:c r="H490" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I490" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J490" s="9" t="str">
+        <x:v>2015-2024 S3 transmission-code diagnosis</x:v>
+      </x:c>
+      <x:c r="K490" s="9" t="str">
+        <x:v>specialist transmission service</x:v>
+      </x:c>
+      <x:c r="L490" s="9" t="str"/>
+      <x:c r="M490" s="9" t="str">
+        <x:v>DQ381 not across full range and G052182A2/FFL-2 are not universal.</x:v>
+      </x:c>
+      <x:c r="N490" s="41" t="str">
+        <x:v>No mechatronic/clutch/fluid link or driving-style prevention claim.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="491" ht="66" hidden="0" customHeight="1">
+      <x:c r="A491" s="40" t="str"/>
+      <x:c r="B491" s="9" t="str"/>
+      <x:c r="C491" s="9" t="str"/>
+      <x:c r="D491" s="9" t="str"/>
+      <x:c r="E491" s="9" t="str"/>
+      <x:c r="F491" s="9" t="str"/>
+      <x:c r="G491" s="9" t="str"/>
+      <x:c r="H491" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I491" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J491" s="9" t="str">
+        <x:v>VIN fluid/software/mechatronic</x:v>
+      </x:c>
+      <x:c r="K491" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L491" s="9" t="str"/>
+      <x:c r="M491" s="9" t="str"/>
+      <x:c r="N491" s="41" t="str"/>
+    </x:row>
+    <x:row r="492" ht="184.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A492" s="40" t="n">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B492" s="9" t="str">
+        <x:v>audi-s3-ea888-carbon-2015</x:v>
+      </x:c>
+      <x:c r="C492" s="9" t="str">
+        <x:v>2015-2024 | Audi | S3 | EA888</x:v>
+      </x:c>
+      <x:c r="D492" s="9" t="str">
+        <x:v>EA888 Carbon Buildup on Intake Valves</x:v>
+      </x:c>
+      <x:c r="E492" s="9" t="str">
+        <x:v>Walnut blast intake valves every 40,000-60,000 miles or install a catch can to reduce buildup rate.</x:v>
+      </x:c>
+      <x:c r="F492" s="9" t="str">
+        <x:v>Confirm engine/injection design and deposits after misfire/fuel/compression diagnosis; engine-specific cleaning</x:v>
+      </x:c>
+      <x:c r="G492" s="9" t="str">
+        <x:v>CONFIRMED-DEPOSIT SERVICE</x:v>
+      </x:c>
+      <x:c r="H492" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I492" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J492" s="9" t="str">
+        <x:v>2015-2024 S3 intake diagnosis/cleaning</x:v>
+      </x:c>
+      <x:c r="K492" s="9" t="str">
+        <x:v>specialist intake service</x:v>
+      </x:c>
+      <x:c r="L492" s="9" t="str"/>
+      <x:c r="M492" s="9" t="str">
+        <x:v>Fixed interval/catch can not established.</x:v>
+      </x:c>
+      <x:c r="N492" s="41" t="str">
+        <x:v>No walnut/catch-can link without deposit and exact engine proof.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="493" ht="303.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A493" s="40" t="n">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="B493" s="9" t="str">
+        <x:v>audi-s3-hpfp-2015</x:v>
+      </x:c>
+      <x:c r="C493" s="9" t="str">
+        <x:v>2015-2024 | Audi | S3 | EA888</x:v>
+      </x:c>
+      <x:c r="D493" s="9" t="str">
+        <x:v>High-Pressure Fuel Pump (HPFP) Failure</x:v>
+      </x:c>
+      <x:c r="E493" s="9" t="str">
+        <x:v>Replace HPFP with updated revision. Check cam follower for wear during replacement.</x:v>
+      </x:c>
+      <x:c r="F493" s="9" t="str">
+        <x:v>Fuel-pressure actual/target, low-pressure supply, wiring and cam-drive diagnosis; engine-generation/VIN HPFP only if failed; cam follower only if that engine uses a serviceable follower</x:v>
+      </x:c>
+      <x:c r="G493" s="9" t="str">
+        <x:v>ENGINE-GENERATION / FUEL-PRESSURE GATE</x:v>
+      </x:c>
+      <x:c r="H493" s="9" t="str">
+        <x:v>Audi S3 high-pressure-pump catalog</x:v>
+      </x:c>
+      <x:c r="I493" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/S3/High-Pressure-Fuel-Pump/</x:v>
+      </x:c>
+      <x:c r="J493" s="9" t="str">
+        <x:v>2015-2024 exact engine/VIN/current revision after diagnosis</x:v>
+      </x:c>
+      <x:c r="K493" s="9" t="str">
+        <x:v>vehicle-specific HPFP catalog</x:v>
+      </x:c>
+      <x:c r="L493" s="9" t="str"/>
+      <x:c r="M493" s="9" t="str">
+        <x:v>Warning/symptoms do not prove HPFP; follower design varies.</x:v>
+      </x:c>
+      <x:c r="N493" s="41" t="str">
+        <x:v>Do not automatically inspect/replace a cam follower across generations.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="494" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A494" s="40" t="str"/>
+      <x:c r="B494" s="9" t="str"/>
+      <x:c r="C494" s="9" t="str"/>
+      <x:c r="D494" s="9" t="str"/>
+      <x:c r="E494" s="9" t="str"/>
+      <x:c r="F494" s="9" t="str"/>
+      <x:c r="G494" s="9" t="str"/>
+      <x:c r="H494" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I494" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J494" s="9" t="str">
+        <x:v>fuel-pressure/root-cause diagnosis</x:v>
+      </x:c>
+      <x:c r="K494" s="9" t="str">
+        <x:v>specialist fuel service</x:v>
+      </x:c>
+      <x:c r="L494" s="9" t="str"/>
+      <x:c r="M494" s="9" t="str"/>
+      <x:c r="N494" s="41" t="str"/>
+    </x:row>
+    <x:row r="495" ht="1122" hidden="0" customHeight="1">
+      <x:c r="A495" s="40" t="n">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="B495" s="9" t="str">
+        <x:v>audi-s3-turbo-wastegate-rattle-2015</x:v>
+      </x:c>
+      <x:c r="C495" s="9" t="str">
+        <x:v>2015-2020 | Audi | S3 | S3</x:v>
+      </x:c>
+      <x:c r="D495" s="9" t="str">
+        <x:v>IS20 Turbocharger Wastegate Rattle and Actuator Failure</x:v>
+      </x:c>
+      <x:c r="E495" s="9" t="str">
+        <x:v>EARLY STAGE (rattle only, no power loss): Audi TSB 2027585/3 prescribes installation of a metal retaining clip (part 06J145220A) to tighten wastegate arm play ($200-$400 if under warranty, $500-$800 out of pocket). UPGRADED DIVERTER VALVE: Replace with revision 'D' diverter valve to improve boost control. SEVERE (actuator failure or power loss): Replace complete IS20 turbocharger ($2,500-$4,000 installed). The IS20 actuator is integrated and not serviceable separately. Upgraded IS38 turbo swap ($3,500-$5,000) from Golf R is a popular option if replacing turbo anyway. PREVENTION: Avoid short trips that don't fully heat the turbo. Change oil every 5,000 miles with high-quality synthetic.</x:v>
+      </x:c>
+      <x:c r="F495" s="9" t="str">
+        <x:v>Confirm exact turbo and rattle/no-power condition; TSB applicability; clip 06J145220A only for matching older application; severe actuator/turbo separately diagnosed</x:v>
+      </x:c>
+      <x:c r="G495" s="9" t="str">
+        <x:v>SOURCE TURBO/PART MISMATCH / HOLD S3 CLIP</x:v>
+      </x:c>
+      <x:c r="H495" s="9" t="str">
+        <x:v>Genuine wastegate clip 06J145220A</x:v>
+      </x:c>
+      <x:c r="I495" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/products/vw-wastegate-anti-rattle-clip-genuine-vw-06j145220a</x:v>
+      </x:c>
+      <x:c r="J495" s="9" t="str">
+        <x:v>live page lists older A3/VW applications but does not prove 2015-2020 S3 IS20 fitment; evidence/hold only</x:v>
+      </x:c>
+      <x:c r="K495" s="9" t="str">
+        <x:v>unapproved exact-number reference</x:v>
+      </x:c>
+      <x:c r="L495" s="9" t="str"/>
+      <x:c r="M495" s="9" t="str">
+        <x:v>Official clip TSB/product application does not establish S3 IS20 coverage; source may conflate earlier 2.0T.</x:v>
+      </x:c>
+      <x:c r="N495" s="41" t="str">
+        <x:v>Do not link clip, rev-D diverter, IS20/IS38 or oil schedule until turbo/VIN and current TSB are proven.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="496" ht="66" hidden="0" customHeight="1">
+      <x:c r="A496" s="40" t="str"/>
+      <x:c r="B496" s="9" t="str"/>
+      <x:c r="C496" s="9" t="str"/>
+      <x:c r="D496" s="9" t="str"/>
+      <x:c r="E496" s="9" t="str"/>
+      <x:c r="F496" s="9" t="str"/>
+      <x:c r="G496" s="9" t="str"/>
+      <x:c r="H496" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I496" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J496" s="9" t="str">
+        <x:v>2015-2020 S3 turbo/wastegate diagnosis</x:v>
+      </x:c>
+      <x:c r="K496" s="9" t="str">
+        <x:v>specialist turbo service</x:v>
+      </x:c>
+      <x:c r="L496" s="9" t="str"/>
+      <x:c r="M496" s="9" t="str"/>
+      <x:c r="N496" s="41" t="str"/>
+    </x:row>
+    <x:row r="497" ht="594" hidden="0" customHeight="1">
+      <x:c r="A497" s="40" t="n">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="B497" s="9" t="str">
+        <x:v>audi-s3-water-pump-thermostat-2015</x:v>
+      </x:c>
+      <x:c r="C497" s="9" t="str">
+        <x:v>2020-2024 | Audi | S3 | 2.0L TFSI</x:v>
+      </x:c>
+      <x:c r="D497" s="9" t="str">
+        <x:v>2020/2022-2024 Audi S3 2.0 TFSI Coolant-Pump Leak Diagnosis</x:v>
+      </x:c>
+      <x:c r="E497" s="9" t="str">
+        <x:v>Document the suspected leak, clean and dry all traces, fill the cooling system to the correct level and reassess after driving a few miles. If no fresh leak appears, continue observing without replacing parts. If leakage recurs, replace only the component causing the damage under the exact VIN, engine and part criteria. Outside applicable warranty, Audi states the bulletin is informational.</x:v>
+      </x:c>
+      <x:c r="F497" s="9" t="str">
+        <x:v>Clean/dry/fill/reassess; exact recurring leak source/VIN component only; coverage check</x:v>
+      </x:c>
+      <x:c r="G497" s="9" t="str">
+        <x:v>SOURCE-YEAR MISMATCH / LEAK-CONFIRMATION</x:v>
+      </x:c>
+      <x:c r="H497" s="9" t="str">
+        <x:v>Audi S3 water-pump catalog</x:v>
+      </x:c>
+      <x:c r="I497" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/S3/Water-Pump/</x:v>
+      </x:c>
+      <x:c r="J497" s="9" t="str">
+        <x:v>2020/2022-2024 S3 after fresh leak confirmation</x:v>
+      </x:c>
+      <x:c r="K497" s="9" t="str">
+        <x:v>conditional pump catalog</x:v>
+      </x:c>
+      <x:c r="L497" s="9" t="str"/>
+      <x:c r="M497" s="9" t="str">
+        <x:v>No fresh leak means observation.</x:v>
+      </x:c>
+      <x:c r="N497" s="41" t="str">
+        <x:v>Identifier says 2015; align years.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="498" ht="66" hidden="0" customHeight="1">
+      <x:c r="A498" s="40" t="str"/>
+      <x:c r="B498" s="9" t="str"/>
+      <x:c r="C498" s="9" t="str"/>
+      <x:c r="D498" s="9" t="str"/>
+      <x:c r="E498" s="9" t="str"/>
+      <x:c r="F498" s="9" t="str"/>
+      <x:c r="G498" s="9" t="str"/>
+      <x:c r="H498" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I498" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J498" s="9" t="str">
+        <x:v>current bulletin/coverage</x:v>
+      </x:c>
+      <x:c r="K498" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L498" s="9" t="str"/>
+      <x:c r="M498" s="9" t="str"/>
+      <x:c r="N498" s="41" t="str"/>
+    </x:row>
+    <x:row r="499" ht="250.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A499" s="40" t="n">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="B499" s="9" t="str">
+        <x:v>audi-s4-b5-timing-chain-2000</x:v>
+      </x:c>
+      <x:c r="C499" s="9" t="str">
+        <x:v>2000-2002 | Audi | S4</x:v>
+      </x:c>
+      <x:c r="D499" s="9" t="str">
+        <x:v>Driver Airbag Inflator May Deploy Improperly (Recall 21V470 / 69CJ)</x:v>
+      </x:c>
+      <x:c r="E499" s="9" t="str">
+        <x:v>Check the VIN with Audi or NHTSA. Audi dealers replace the driver frontal-airbag inflator with an alternative inflator free of charge under campaign 69CJ.</x:v>
+      </x:c>
+      <x:c r="F499" s="9" t="str">
+        <x:v>VIN/69CJ/21V470 check; free driver inflator replacement</x:v>
+      </x:c>
+      <x:c r="G499" s="9" t="str">
+        <x:v>SOURCE-ID MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H499" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I499" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J499" s="9" t="str">
+        <x:v>2000-2002 S4 69CJ</x:v>
+      </x:c>
+      <x:c r="K499" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L499" s="9" t="str"/>
+      <x:c r="M499" s="9" t="str">
+        <x:v>Airbag recall, not timing chain.</x:v>
+      </x:c>
+      <x:c r="N499" s="41" t="str">
+        <x:v>Rename/re-key; no timing/airbag product link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="500" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A500" s="40" t="str"/>
+      <x:c r="B500" s="9" t="str"/>
+      <x:c r="C500" s="9" t="str"/>
+      <x:c r="D500" s="9" t="str"/>
+      <x:c r="E500" s="9" t="str"/>
+      <x:c r="F500" s="9" t="str"/>
+      <x:c r="G500" s="9" t="str"/>
+      <x:c r="H500" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I500" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J500" s="9" t="str">
+        <x:v>21V470 VIN history</x:v>
+      </x:c>
+      <x:c r="K500" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L500" s="9" t="str"/>
+      <x:c r="M500" s="9" t="str"/>
+      <x:c r="N500" s="41" t="str"/>
+    </x:row>
+    <x:row r="501" ht="237.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A501" s="40" t="n">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="B501" s="9" t="str">
+        <x:v>audi-s4-b5-turbo-failure-2000</x:v>
+      </x:c>
+      <x:c r="C501" s="9" t="str">
+        <x:v>2003-2004 | Audi | S4</x:v>
+      </x:c>
+      <x:c r="D501" s="9" t="str">
+        <x:v>Xenon Headlamp Reflector Coating Can Reduce Light Output (Recall 05V096)</x:v>
+      </x:c>
+      <x:c r="E501" s="9" t="str">
+        <x:v>Verify VIN eligibility and campaign completion with Audi. Dealers replace both xenon headlamp reflectors free of charge under recall 05V096.</x:v>
+      </x:c>
+      <x:c r="F501" s="9" t="str">
+        <x:v>VIN/05V096 completion check; dealer both xenon reflectors</x:v>
+      </x:c>
+      <x:c r="G501" s="9" t="str">
+        <x:v>SOURCE-ID/YEAR MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H501" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I501" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J501" s="9" t="str">
+        <x:v>2003-2004 Audi population for 05V096; confirm model/VIN</x:v>
+      </x:c>
+      <x:c r="K501" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L501" s="9" t="str"/>
+      <x:c r="M501" s="9" t="str">
+        <x:v>Headlamp recall, not B5 turbo failure.</x:v>
+      </x:c>
+      <x:c r="N501" s="41" t="str">
+        <x:v>Rename/re-key and verify S4 model scope; no turbo/headlamp retail link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="502" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A502" s="40" t="str"/>
+      <x:c r="B502" s="9" t="str"/>
+      <x:c r="C502" s="9" t="str"/>
+      <x:c r="D502" s="9" t="str"/>
+      <x:c r="E502" s="9" t="str"/>
+      <x:c r="F502" s="9" t="str"/>
+      <x:c r="G502" s="9" t="str"/>
+      <x:c r="H502" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I502" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J502" s="9" t="str">
+        <x:v>05V096 VIN history</x:v>
+      </x:c>
+      <x:c r="K502" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L502" s="9" t="str"/>
+      <x:c r="M502" s="9" t="str"/>
+      <x:c r="N502" s="41" t="str"/>
+    </x:row>
+    <x:row r="503" ht="303.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A503" s="40" t="n">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="B503" s="9" t="str">
+        <x:v>audi-s4-b6-timing-chain-2004</x:v>
+      </x:c>
+      <x:c r="C503" s="9" t="str">
+        <x:v>2005-2009 | Audi | S4</x:v>
+      </x:c>
+      <x:c r="D503" s="9" t="str">
+        <x:v>Passenger Airbag Inflator Can Rupture (Recall 18V427 / 69R7)</x:v>
+      </x:c>
+      <x:c r="E503" s="9" t="str">
+        <x:v>Check VIN eligibility because body style and original registration history affect scope. Audi dealers replace the passenger frontal-airbag remedy part free of charge under campaign 69R7.</x:v>
+      </x:c>
+      <x:c r="F503" s="9" t="str">
+        <x:v>VIN/69R7/18V427 eligibility and passenger inflator remedy</x:v>
+      </x:c>
+      <x:c r="G503" s="9" t="str">
+        <x:v>SOURCE-ID/YEAR MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H503" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I503" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J503" s="9" t="str">
+        <x:v>2005-2009 S4 body/registration-specific 69R7</x:v>
+      </x:c>
+      <x:c r="K503" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L503" s="9" t="str"/>
+      <x:c r="M503" s="9" t="str">
+        <x:v>Airbag recall, not timing chain.</x:v>
+      </x:c>
+      <x:c r="N503" s="41" t="str">
+        <x:v>Rename/re-key; no timing/airbag commerce link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="504" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A504" s="40" t="str"/>
+      <x:c r="B504" s="9" t="str"/>
+      <x:c r="C504" s="9" t="str"/>
+      <x:c r="D504" s="9" t="str"/>
+      <x:c r="E504" s="9" t="str"/>
+      <x:c r="F504" s="9" t="str"/>
+      <x:c r="G504" s="9" t="str"/>
+      <x:c r="H504" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I504" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J504" s="9" t="str">
+        <x:v>18V427 VIN history</x:v>
+      </x:c>
+      <x:c r="K504" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L504" s="9" t="str"/>
+      <x:c r="M504" s="9" t="str"/>
+      <x:c r="N504" s="41" t="str"/>
+    </x:row>
+    <x:row r="505" ht="356.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A505" s="40" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="B505" s="9" t="str">
+        <x:v>audi-s4-carbon-buildup-2010</x:v>
+      </x:c>
+      <x:c r="C505" s="9" t="str">
+        <x:v>2011-2012 | Audi | S4 | 3.0 TFSI</x:v>
+      </x:c>
+      <x:c r="D505" s="9" t="str">
+        <x:v>Fuel Rail or Seal Leak Creates Fire Risk (Recall 15V019 / 24AP)</x:v>
+      </x:c>
+      <x:c r="E505" s="9" t="str">
+        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel rails and corresponding seals free of charge under campaign 24AP. If fuel odor or leakage is present, stop driving and arrange immediate inspection.</x:v>
+      </x:c>
+      <x:c r="F505" s="9" t="str">
+        <x:v>VIN/24AP/15V019 check; dealer fuel rails and seals; stop for odor/leak</x:v>
+      </x:c>
+      <x:c r="G505" s="9" t="str">
+        <x:v>SOURCE-ID/YEAR MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H505" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I505" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J505" s="9" t="str">
+        <x:v>2011-2012 S4 3.0T 24AP</x:v>
+      </x:c>
+      <x:c r="K505" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L505" s="9" t="str"/>
+      <x:c r="M505" s="9" t="str">
+        <x:v>Fuel leak recall, not carbon buildup.</x:v>
+      </x:c>
+      <x:c r="N505" s="41" t="str">
+        <x:v>Rename/re-key; no cleaning/fuel-rail retail link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="506" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A506" s="40" t="str"/>
+      <x:c r="B506" s="9" t="str"/>
+      <x:c r="C506" s="9" t="str"/>
+      <x:c r="D506" s="9" t="str"/>
+      <x:c r="E506" s="9" t="str"/>
+      <x:c r="F506" s="9" t="str"/>
+      <x:c r="G506" s="9" t="str"/>
+      <x:c r="H506" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I506" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J506" s="9" t="str">
+        <x:v>15V019 VIN history</x:v>
+      </x:c>
+      <x:c r="K506" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L506" s="9" t="str"/>
+      <x:c r="M506" s="9" t="str"/>
+      <x:c r="N506" s="41" t="str"/>
+    </x:row>
+    <x:row r="507" ht="224.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A507" s="40" t="n">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="B507" s="9" t="str">
+        <x:v>audi-s4-supercharger-nose-2010</x:v>
+      </x:c>
+      <x:c r="C507" s="9" t="str">
+        <x:v>2013-2015 | Audi | S4</x:v>
+      </x:c>
+      <x:c r="D507" s="9" t="str">
+        <x:v>Airbag-Control Software May Miss Front-Airbag Deployment After a Second Impact (Recall 14V667 / 69K5)</x:v>
+      </x:c>
+      <x:c r="E507" s="9" t="str">
+        <x:v>Check VIN eligibility and completion history. Audi dealers update the airbag control-unit software free of charge under campaign 69K5.</x:v>
+      </x:c>
+      <x:c r="F507" s="9" t="str">
+        <x:v>VIN/69K5/14V667 check; dealer airbag control software</x:v>
+      </x:c>
+      <x:c r="G507" s="9" t="str">
+        <x:v>SOURCE-ID/YEAR MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H507" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I507" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J507" s="9" t="str">
+        <x:v>2013-2015 S4 69K5</x:v>
+      </x:c>
+      <x:c r="K507" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L507" s="9" t="str"/>
+      <x:c r="M507" s="9" t="str">
+        <x:v>Airbag software recall, not supercharger.</x:v>
+      </x:c>
+      <x:c r="N507" s="41" t="str">
+        <x:v>Rename/re-key; no nose-cone/airbag part link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="508" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A508" s="40" t="str"/>
+      <x:c r="B508" s="9" t="str"/>
+      <x:c r="C508" s="9" t="str"/>
+      <x:c r="D508" s="9" t="str"/>
+      <x:c r="E508" s="9" t="str"/>
+      <x:c r="F508" s="9" t="str"/>
+      <x:c r="G508" s="9" t="str"/>
+      <x:c r="H508" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I508" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J508" s="9" t="str">
+        <x:v>14V667 VIN history</x:v>
+      </x:c>
+      <x:c r="K508" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L508" s="9" t="str"/>
+      <x:c r="M508" s="9" t="str"/>
+      <x:c r="N508" s="41" t="str"/>
+    </x:row>
+    <x:row r="509" ht="250.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A509" s="40" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="B509" s="9" t="str">
+        <x:v>audi-s4-thermostat-2010</x:v>
+      </x:c>
+      <x:c r="C509" s="9" t="str">
+        <x:v>2010-2025 | Audi | S4 | 3.0T</x:v>
+      </x:c>
+      <x:c r="D509" s="9" t="str">
+        <x:v>Thermostat Housing Failure and Coolant Leak</x:v>
+      </x:c>
+      <x:c r="E509" s="9" t="str">
+        <x:v>Replace thermostat housing assembly with updated part. Use OEM or quality aftermarket housing with metal reinforcement.</x:v>
+      </x:c>
+      <x:c r="F509" s="9" t="str">
+        <x:v>Split 2010-2016 supercharged and 2017-2025 turbo generations; pressure-test exact thermostat/housing/pump source; VIN component and coolant</x:v>
+      </x:c>
+      <x:c r="G509" s="9" t="str">
+        <x:v>MULTI-GENERATION / LEAK-SOURCE GATE</x:v>
+      </x:c>
+      <x:c r="H509" s="9" t="str">
+        <x:v>Audi S4 thermostat catalog</x:v>
+      </x:c>
+      <x:c r="I509" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/S4/Thermostat/</x:v>
+      </x:c>
+      <x:c r="J509" s="9" t="str">
+        <x:v>2010-2025 exact generation/engine/VIN and confirmed component</x:v>
+      </x:c>
+      <x:c r="K509" s="9" t="str">
+        <x:v>vehicle-specific thermostat catalog</x:v>
+      </x:c>
+      <x:c r="L509" s="9" t="str"/>
+      <x:c r="M509" s="9" t="str">
+        <x:v>Fifteen years do not share one housing.</x:v>
+      </x:c>
+      <x:c r="N509" s="41" t="str">
+        <x:v>Engine field says 3.0T but generation technologies differ; no universal metal-reinforced claim.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="510" ht="66" hidden="0" customHeight="1">
+      <x:c r="A510" s="40" t="str"/>
+      <x:c r="B510" s="9" t="str"/>
+      <x:c r="C510" s="9" t="str"/>
+      <x:c r="D510" s="9" t="str"/>
+      <x:c r="E510" s="9" t="str"/>
+      <x:c r="F510" s="9" t="str"/>
+      <x:c r="G510" s="9" t="str"/>
+      <x:c r="H510" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I510" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J510" s="9" t="str">
+        <x:v>pressure-test and engine-generation diagnosis</x:v>
+      </x:c>
+      <x:c r="K510" s="9" t="str">
+        <x:v>specialist cooling service</x:v>
+      </x:c>
+      <x:c r="L510" s="9" t="str"/>
+      <x:c r="M510" s="9" t="str"/>
+      <x:c r="N510" s="41" t="str"/>
+    </x:row>
+    <x:row r="511" ht="963.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A511" s="40" t="n">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="B511" s="9" t="str">
+        <x:v>audi-s5-b9-water-pump-2018</x:v>
+      </x:c>
+      <x:c r="C511" s="9" t="str">
+        <x:v>2018-2018 | Audi | S5 | 3.0L V6 TFSI EA839</x:v>
+      </x:c>
+      <x:c r="D511" s="9" t="str">
+        <x:v>2018 S5 3.0L Mechanical Coolant-Pump Fault P000000/33688 - Diagnosis Required</x:v>
+      </x:c>
+      <x:c r="E511" s="9" t="str">
+        <x:v>Follow the bulletin in order. Verify coolant level; if low, inspect the cooling system for a leak and repair only the identified source or top up per Audi instructions when no leak is found. Check the ECM software level and apply the specified SVM update only when required. If the concern returns or software is current, test vacuum at N649 and inspect the solenoid and hoses. If the vacuum system works, apply vacuum to the pump hose and verify that the pump sleeve clicks; replace the mechanical coolant pump only when the sleeve does not operate. Use current Audi workshop and parts information.</x:v>
+      </x:c>
+      <x:c r="F511" s="9" t="str">
+        <x:v>Coolant level/leak branch; ECM software update when required; N649 vacuum/hoses; pump sleeve click test; mechanical pump only if sleeve fails</x:v>
+      </x:c>
+      <x:c r="G511" s="9" t="str">
+        <x:v>TSB CONDITIONAL PUMP / SOFTWARE/VACUUM FIRST</x:v>
+      </x:c>
+      <x:c r="H511" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I511" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J511" s="9" t="str">
+        <x:v>2018 S5 EA839 bulletin guided sequence</x:v>
+      </x:c>
+      <x:c r="K511" s="9" t="str">
+        <x:v>manufacturer cooling service</x:v>
+      </x:c>
+      <x:c r="L511" s="9" t="str"/>
+      <x:c r="M511" s="9" t="str">
+        <x:v>Multiple earlier branches can avoid pump replacement.</x:v>
+      </x:c>
+      <x:c r="N511" s="41" t="str">
+        <x:v>No pump link until sleeve test fails and VIN part confirmed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="512" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A512" s="40" t="str"/>
+      <x:c r="B512" s="9" t="str"/>
+      <x:c r="C512" s="9" t="str"/>
+      <x:c r="D512" s="9" t="str"/>
+      <x:c r="E512" s="9" t="str"/>
+      <x:c r="F512" s="9" t="str"/>
+      <x:c r="G512" s="9" t="str"/>
+      <x:c r="H512" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I512" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J512" s="9" t="str">
+        <x:v>vacuum/pump sleeve diagnosis</x:v>
+      </x:c>
+      <x:c r="K512" s="9" t="str">
+        <x:v>specialist service</x:v>
+      </x:c>
+      <x:c r="L512" s="9" t="str"/>
+      <x:c r="M512" s="9" t="str"/>
+      <x:c r="N512" s="41" t="str"/>
+    </x:row>
+    <x:row r="513" ht="224.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A513" s="40" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="B513" s="9" t="str">
+        <x:v>audi-s5-carbon-buildup-2008</x:v>
+      </x:c>
+      <x:c r="C513" s="9" t="str">
+        <x:v>2008-2025 | Audi | S5</x:v>
+      </x:c>
+      <x:c r="D513" s="9" t="str">
+        <x:v>Direct Injection Carbon Buildup</x:v>
+      </x:c>
+      <x:c r="E513" s="9" t="str">
+        <x:v>Walnut blast intake valves every 40,000-60,000 miles. Install oil catch can to reduce oil vapor reaching valves.</x:v>
+      </x:c>
+      <x:c r="F513" s="9" t="str">
+        <x:v>Split V8, supercharged V6 and turbo V6 generations; confirm deposits after misfire/fuel/compression diagnosis; engine-specific cleaning</x:v>
+      </x:c>
+      <x:c r="G513" s="9" t="str">
+        <x:v>OVERBROAD MULTI-ENGINE / CONFIRMED-DEPOSIT SERVICE</x:v>
+      </x:c>
+      <x:c r="H513" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I513" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J513" s="9" t="str">
+        <x:v>2008-2025 S5 engine-specific intake diagnosis/cleaning</x:v>
+      </x:c>
+      <x:c r="K513" s="9" t="str">
+        <x:v>specialist intake service</x:v>
+      </x:c>
+      <x:c r="L513" s="9" t="str"/>
+      <x:c r="M513" s="9" t="str">
+        <x:v>Eighteen years and engines cannot use one interval.</x:v>
+      </x:c>
+      <x:c r="N513" s="41" t="str">
+        <x:v>No catch-can or fixed 40k-60k cleaning claim.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="514" ht="937.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A514" s="40" t="n">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="B514" s="9" t="str">
+        <x:v>audi-s5-crankshaft-pulley-2010</x:v>
+      </x:c>
+      <x:c r="C514" s="9" t="str">
+        <x:v>2010-2017 | Audi | S5 | Premium Plus, Prestige | 3.0T</x:v>
+      </x:c>
+      <x:c r="D514" s="9" t="str">
+        <x:v>Crankshaft Pulley (Harmonic Balancer) Failure (3.0T)</x:v>
+      </x:c>
+      <x:c r="E514" s="9" t="str">
+        <x:v>Replace crankshaft pulley/harmonic balancer with LATEST REVISION (revision F or later) part ($300-$600 for part, $800-$1,700 with labor). This is NOT a DIY-friendly repair—requires specialized holding tools and precise torque. If belts are damaged, replace serpentine belt and tensioner ($200-$400 additional). INSPECT: Check for collateral damage to supercharger snout, idler pulleys, and timing. If timing was affected, expect $3,000-$5,000 additional repair. PREVENTIVE: Inspect pulley for wobble at every oil change. Consider preemptive replacement at 80,000 miles on 2010-2013 models.</x:v>
+      </x:c>
+      <x:c r="F514" s="9" t="str">
+        <x:v>Confirm 3.0T engine and balancer separation/wobble; VIN/current pulley revision, bolt/tool/torque procedure; belts/tensioner/idlers only if damaged/worn; collateral inspection</x:v>
+      </x:c>
+      <x:c r="G514" s="9" t="str">
+        <x:v>ENGINE / PULLEY-REVISION / CONDITION GATE</x:v>
+      </x:c>
+      <x:c r="H514" s="9" t="str">
+        <x:v>Audi S5 crankshaft-pulley catalog</x:v>
+      </x:c>
+      <x:c r="I514" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/S5/Crankshaft-Pulley/</x:v>
+      </x:c>
+      <x:c r="J514" s="9" t="str">
+        <x:v>2010-2017 S5 3.0T; exact engine/VIN/current revision</x:v>
+      </x:c>
+      <x:c r="K514" s="9" t="str">
+        <x:v>vehicle-specific pulley catalog</x:v>
+      </x:c>
+      <x:c r="L514" s="9" t="str"/>
+      <x:c r="M514" s="9" t="str">
+        <x:v>Revision F and collateral parts must be verified by VIN/condition.</x:v>
+      </x:c>
+      <x:c r="N514" s="41" t="str">
+        <x:v>No universal preventive 80k replacement or price/damage claim.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="515" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A515" s="40" t="str"/>
+      <x:c r="B515" s="9" t="str"/>
+      <x:c r="C515" s="9" t="str"/>
+      <x:c r="D515" s="9" t="str"/>
+      <x:c r="E515" s="9" t="str"/>
+      <x:c r="F515" s="9" t="str"/>
+      <x:c r="G515" s="9" t="str"/>
+      <x:c r="H515" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I515" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J515" s="9" t="str">
+        <x:v>wobble/collateral/timing diagnosis</x:v>
+      </x:c>
+      <x:c r="K515" s="9" t="str">
+        <x:v>specialist engine service</x:v>
+      </x:c>
+      <x:c r="L515" s="9" t="str"/>
+      <x:c r="M515" s="9" t="str"/>
+      <x:c r="N515" s="41" t="str"/>
+    </x:row>
+    <x:row r="516" ht="844.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A516" s="40" t="n">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="B516" s="9" t="str">
+        <x:v>audi-s5-pcv-valve-failure-2010</x:v>
+      </x:c>
+      <x:c r="C516" s="9" t="str">
+        <x:v>2010-2017 | Audi | S5 | 3.0L supercharged V6</x:v>
+      </x:c>
+      <x:c r="D516" s="9" t="str">
+        <x:v>2010-2017 S5 3.0L Crankcase-Breather P052E00 - Body/Year Diagnosis</x:v>
+      </x:c>
+      <x:c r="E516" s="9" t="str">
+        <x:v>Verify the body style, model year and P052E00 condition first. For the applicable membrane branch, use the specified hand-vacuum test, then inspect the membrane and metal plates after compressor/intake-manifold removal; replace only the faulted membrane/plate repair kit or crankcase breather per current Audi instructions. If testing identifies the elbow branch, replace the elbow and hose clip as directed by TSB 2060259/1. Do not assume that both branches or unrelated cooling parts require replacement.</x:v>
+      </x:c>
+      <x:c r="F516" s="9" t="str">
+        <x:v>Body/year/P052E00 split; hand-vacuum membrane test and inspection; exact membrane/plate kit or breather; elbow/clip branch only when TSB identifies</x:v>
+      </x:c>
+      <x:c r="G516" s="9" t="str">
+        <x:v>BODY/YEAR / TEST-BRANCH GATE</x:v>
+      </x:c>
+      <x:c r="H516" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I516" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J516" s="9" t="str">
+        <x:v>2010-2017 S5 3.0 supercharged TSB 2060259/1 and VIN parts</x:v>
+      </x:c>
+      <x:c r="K516" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L516" s="9" t="str"/>
+      <x:c r="M516" s="9" t="str">
+        <x:v>Membrane and elbow are separate branches.</x:v>
+      </x:c>
+      <x:c r="N516" s="41" t="str">
+        <x:v>No universal PCV/cooling bundle.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="517" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A517" s="40" t="str"/>
+      <x:c r="B517" s="9" t="str"/>
+      <x:c r="C517" s="9" t="str"/>
+      <x:c r="D517" s="9" t="str"/>
+      <x:c r="E517" s="9" t="str"/>
+      <x:c r="F517" s="9" t="str"/>
+      <x:c r="G517" s="9" t="str"/>
+      <x:c r="H517" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I517" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J517" s="9" t="str">
+        <x:v>vacuum/breather/elbow diagnosis</x:v>
+      </x:c>
+      <x:c r="K517" s="9" t="str">
+        <x:v>specialist engine service</x:v>
+      </x:c>
+      <x:c r="L517" s="9" t="str"/>
+      <x:c r="M517" s="9" t="str"/>
+      <x:c r="N517" s="41" t="str"/>
+    </x:row>
+    <x:row r="518" ht="277.20001220703125" hidden="0" customHeight="1">
+      <x:c r="A518" s="40" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B518" s="9" t="str">
+        <x:v>audi-s5-supercharger-2008</x:v>
+      </x:c>
+      <x:c r="C518" s="9" t="str">
+        <x:v>2008-2025 | Audi | S5 | 3.0T</x:v>
+      </x:c>
+      <x:c r="D518" s="9" t="str">
+        <x:v>3.0T Supercharger Intercooler Pump Failure</x:v>
+      </x:c>
+      <x:c r="E518" s="9" t="str">
+        <x:v>Replace intercooler coolant pump. Check intercooler lines for leaks and flush the circuit during replacement.</x:v>
+      </x:c>
+      <x:c r="F518" s="9" t="str">
+        <x:v>Correct 3.0T model-year population; intercooler circuit flow/pump power/ground/command and leak diagnosis; VIN pump only if failed; exact coolant/bleed</x:v>
+      </x:c>
+      <x:c r="G518" s="9" t="str">
+        <x:v>SOURCE RANGE ERROR / COOLANT-PUMP DIAGNOSIS</x:v>
+      </x:c>
+      <x:c r="H518" s="9" t="str">
+        <x:v>Audi S5 auxiliary-pump catalog</x:v>
+      </x:c>
+      <x:c r="I518" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/S5/Auxiliary-Water-Pump/</x:v>
+      </x:c>
+      <x:c r="J518" s="9" t="str">
+        <x:v>3.0T S5 years only; exact VIN/pump role after diagnosis</x:v>
+      </x:c>
+      <x:c r="K518" s="9" t="str">
+        <x:v>conditional pump catalog</x:v>
+      </x:c>
+      <x:c r="L518" s="9" t="str"/>
+      <x:c r="M518" s="9" t="str">
+        <x:v>2008-2009 S5 was not uniformly the described 3.0T application and pump failure must be proven.</x:v>
+      </x:c>
+      <x:c r="N518" s="41" t="str">
+        <x:v>Correct years/engine before link; no blanket pump replacement/flush.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="519" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A519" s="42" t="str"/>
+      <x:c r="B519" s="43" t="str"/>
+      <x:c r="C519" s="43" t="str"/>
+      <x:c r="D519" s="43" t="str"/>
+      <x:c r="E519" s="43" t="str"/>
+      <x:c r="F519" s="43" t="str"/>
+      <x:c r="G519" s="43" t="str"/>
+      <x:c r="H519" s="43" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I519" s="43" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J519" s="43" t="str">
+        <x:v>intercooler circuit flow/leak diagnosis</x:v>
+      </x:c>
+      <x:c r="K519" s="43" t="str">
+        <x:v>specialist cooling service</x:v>
+      </x:c>
+      <x:c r="L519" s="43" t="str"/>
+      <x:c r="M519" s="43" t="str"/>
+      <x:c r="N519" s="44" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15693,21 +18573,21 @@
         <x:v>Queue status</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="330" hidden="0" customHeight="1">
+    <x:row r="2" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A2" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="9" t="str">
-        <x:v>audi-r8-s-tronic-gearbox-ventilation-hose-transmission-fluid-leak</x:v>
+        <x:v>audi-s5-thermostat-2008</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
-        <x:v>2017-2018 | Audi | R8 | 5.2L V10 FSI</x:v>
+        <x:v>2008-2025 | Audi | S5 | 3.0T</x:v>
       </x:c>
       <x:c r="D2" s="9" t="str">
-        <x:v>Gearbox Ventilation Hose Can Leak Fluid Near Hot Engine Parts (Recall 18V639 / 34J1)</x:v>
+        <x:v>Thermostat and Water Pump Assembly Failure</x:v>
       </x:c>
       <x:c r="E2" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the single gearbox ventilation hose with the higher-volume double hose free of charge under campaign 34J1. Stop driving if hot-oil odor or smoke appears.</x:v>
+        <x:v>Replace thermostat/water pump assembly. Upgrade to revised housing if available.</x:v>
       </x:c>
       <x:c r="F2" s="9" t="n">
         <x:v>0</x:v>
@@ -15716,21 +18596,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="3" ht="818.4000244140625" hidden="0" customHeight="1">
       <x:c r="A3" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
-        <x:v>audi-r8-spyder-convertible-top-hydraulic-pump-failure</x:v>
+        <x:v>audi-s6-air-suspension-2013</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
-        <x:v>2011-2023 | Audi | R8 | 4.2L V8 FSI, 5.2L V10 FSI</x:v>
+        <x:v>2013-2013 | Audi | S6 | 4.0T</x:v>
       </x:c>
       <x:c r="D3" s="9" t="str">
-        <x:v>Spyder Convertible Top Hydraulic Pump Failure</x:v>
+        <x:v>2013 Audi S6 Air-Suspension Compressor or Relay Fault - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E3" s="9" t="str">
-        <x:v>Scan for the specific fault (pump vs. sensor vs. latch) before parting; a mis-reading position sensor can mimic a dead pump. Replace the hydraulic pump/motor assembly (Audi R8 Spyder convertible-top hydraulic pump PN 427871791 for 2010-2016 cars) and top up/refill the correct hydraulic fluid, or replace the failed cylinder/sensor. Leaking lines and worn seals should be renewed together. Independent hydraulic rebuild services exist as a lower-cost alternative to a full dealer pump.</x:v>
+        <x:v>Have an Audi-qualified technician test the air-suspension compressor and inspect relay J403. Audi directs replacement of both the compressor and relay when the relay has severe contact erosion or an overheated strand; when the compressor sounds normal and the relay has only minor contact marks, replace the relay only. A sagging corner or leak-down condition requires separate leak localization before any strut is replaced. Do not order the former strut or compressor recommendations from this card.</x:v>
       </x:c>
       <x:c r="F3" s="9" t="n">
         <x:v>0</x:v>
@@ -15739,21 +18619,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="1122" hidden="0" customHeight="1">
+    <x:row r="4" ht="1359.5999755859375" hidden="0" customHeight="1">
       <x:c r="A4" s="40" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>audi-r8-v8-engine-bearing-2008</x:v>
+        <x:v>audi-s6-c7-carbon-buildup-2013</x:v>
       </x:c>
       <x:c r="C4" s="9" t="str">
-        <x:v>2008-2015 | Audi | R8 | 4.2 | 4.2 FSI</x:v>
+        <x:v>2013-2018 | Audi | S6 | 4.0T</x:v>
       </x:c>
       <x:c r="D4" s="9" t="str">
-        <x:v>Rod Bearing Wear and Engine Failure Risk (4.2 V8 FSI)</x:v>
+        <x:v>4.0T Carbon Buildup on Intake Valves</x:v>
       </x:c>
       <x:c r="E4" s="9" t="str">
-        <x:v>EARLY DETECTION (knocking noise only): Rod bearing replacement ($2,000-$5,000). Must be caught EARLY before bearing material migrates through oil system. Cut open every oil filter at oil change to inspect for metallic debris. CATASTROPHIC FAILURE: Engine replacement ($13,000+ Audi exchange, $8,000-$15,000 rebuilt from AMTuned or specialist rebuilder). ARP 2000 reinforced connecting rod bolts are available as a preventive upgrade during any engine-out service. PREVENTION: Use ONLY premium 5W-40 synthetic oil. Change oil every 5,000 miles maximum. NEVER exceed oil change intervals—the high-revving V8 is extremely sensitive to oil condition. For track use, change oil after every 2-3 track days.</x:v>
+        <x:v>Confirm carbon buildup by scanning for misfire faults (commonly random/multiple or cylinder-specific misfires), reviewing fuel trims, and inspecting the intake valves with a borescope after removing the intake manifold or accessing the ports. The proper repair is an intake valve carbon cleaning, typically walnut shell blasting each intake port with the valves closed, then replacing intake manifold gaskets, injector seals/O-rings or any disturbed PCV-related seals as needed and clearing/adapting the ECU afterward. If buildup is severe or returns quickly, inspect the PCV/oil separator system and crankcase ventilation hoses for excessive oil carryover. Independent shops typically charge about $800-$1,500 for a full walnut blast service on the 4.0T, while dealer pricing can run roughly $1,500-$2,500 depending on labor and gasket/seal replacement.</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
         <x:v>0</x:v>
@@ -15762,21 +18642,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="924" hidden="0" customHeight="1">
+    <x:row r="5" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A5" s="40" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>audi-rs-etron-gt-battery-short-2022</x:v>
+        <x:v>audi-s6-carbon-buildup-2013</x:v>
       </x:c>
       <x:c r="C5" s="9" t="str">
-        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
+        <x:v>2013-2024 | Audi | S6 | 4.0T</x:v>
       </x:c>
       <x:c r="D5" s="9" t="str">
-        <x:v>2022-2024 RS e-tron GT High-Voltage Battery Recall 931A/931B (24V726)</x:v>
+        <x:v>4.0T Direct Injection Carbon Buildup</x:v>
       </x:c>
       <x:c r="E5" s="9" t="str">
-        <x:v>Check the VIN for open Audi campaign 931A or 931B and complete the authorized dealer remedy. Under 931A, enrolled vehicles can be monitored through online battery data; Audi contacts owners if a module appears critical. Under 931B, the dealer performs diagnostic procedures until the final monitoring software is installed. Audi installs the onboard diagnostic software and replaces affected battery modules at no cost when anomalies are identified. Follow any vehicle- or dealer-specific 80-percent charging instruction; the filing does not direct every 931A vehicle to use that limit.</x:v>
+        <x:v>Walnut blast all eight intake runners. Dual-injection models (2019+) are less affected.</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
         <x:v>0</x:v>
@@ -15785,21 +18665,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="6" ht="462" hidden="0" customHeight="1">
       <x:c r="A6" s="40" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>audi-rs-etron-gt-brake-hose-2022</x:v>
+        <x:v>audi-s6-rearview-camera-image-failure-from-software-error</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
-        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
+        <x:v>2020-2025 | Audi | S6</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
-        <x:v>2022-2024 RS e-tron GT Front Brake-Hose Recall 47UP (24V465)</x:v>
+        <x:v>2020-2025 Audi S6 Rearview Camera Software Recall 25V900 / 90TV</x:v>
       </x:c>
       <x:c r="E6" s="9" t="str">
-        <x:v>Check the VIN for an open 47UP action and have an authorized Audi dealer replace both front brake hoses and holders free of charge. If pedal travel increases or the vehicle displays a warning related to reduced brake fluid, contact an Audi dealer for diagnosis without delay. Do not buy a single hose or substitute generic brake lines from the prior links; the campaign controls the complete criteria-specific repair.</x:v>
+        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install the more robust driver-assistance software update free of charge. Until repaired, use extra caution when reversing and do not treat a restart or temporary image recovery as completion of the recall.</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
         <x:v>0</x:v>
@@ -15808,21 +18688,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="726" hidden="0" customHeight="1">
+    <x:row r="7" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A7" s="40" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>audi-rs-etron-gt-charging-port-2022</x:v>
+        <x:v>audi-s6-takata-passenger-airbag-inflator-recall</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
-        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
+        <x:v>2007-2011 | Audi | S6</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
-        <x:v>2022-2024 RS e-tron GT Red Charging LED or Fast-Charging Abort - Audi 91VT</x:v>
+        <x:v>2007-2011 Audi S6 Takata Passenger-Airbag Recall 18V427 / 69R7</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
-        <x:v>Have an Audi dealer check the VIN and assigned 91VT criterion in the campaign/action system. For the charging-related criteria, the authorized remedy updates the high-voltage battery control-module software, with the convenience-system control module also updated where the assigned criterion requires it. Diagnose charging failures outside that exact campaign branch rather than replacing the charging socket or module from symptoms alone.</x:v>
+        <x:v>Check the VIN for recall 18V427/69R7 and arrange the free final passenger-frontal-airbag replacement with an Audi dealer. Do not use an airbag warning light to determine recall eligibility; Audi states that the warning light is unrelated to this inflator defect.</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
         <x:v>0</x:v>
@@ -15831,22 +18711,20 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="8" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A8" s="40" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>audi-rs-etron-gt-software-2022</x:v>
+        <x:v>audi-s6-transmission-valve-body-2002</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
-        <x:v>2022-2022 | Audi | RS e-tron GT</x:v>
+        <x:v>2002-2004 | Audi | S6</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>2022 RS e-tron GT Audi connect Inoperative after 91DZ - TSB 2068824/2</x:v>
-      </x:c>
-      <x:c r="E8" s="9" t="str">
-        <x:v>Confirm that the failure began after 91DZ and matches the Audi connect/SOS-LED condition. An Audi technician should use ODIS Guided Fault Finding and run SVM Check Module Configuration for diagnostic address 0019, J533. Manual coding is no longer required. Escalate a continuing Audi connect failure through Audi support after the guided coding procedure rather than buying hardware or a retail software service.</x:v>
-      </x:c>
+        <x:v>ZF 5HP24 Tiptronic Transmission Valve Body Failure</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="str"/>
       <x:c r="F8" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -15854,21 +18732,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="9" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A9" s="40" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>audi-rs-etron-gt-tire-wear-2022</x:v>
+        <x:v>audi-s6-turbo-coolant-2013</x:v>
       </x:c>
       <x:c r="C9" s="9" t="str">
-        <x:v>2022-2024 | Audi | RS e-tron GT</x:v>
+        <x:v>2013-2013 | Audi | S6 | 4.0T</x:v>
       </x:c>
       <x:c r="D9" s="9" t="str">
-        <x:v>Accelerated Tire Wear and Alignment Sensitivity</x:v>
+        <x:v>2013 Audi S6 Turbocharger Coolant-Pipe Seepage - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E9" s="9" t="str">
-        <x:v>Rotate front-to-back every 3,000-5,000 miles (only possible if sizes permit, which staggered setups often do not). Check alignment every 5,000 miles or after any pothole impact - even 0.1 degree of toe deviation causes rapid edge wear on these wide tires. Consider switching to Michelin Pilot Sport 4S or Pirelli P Zero PZ4 for improved tread life over the OE Continental SportContact 6. Budget $1,400-$2,000 for a set of four replacement tires. Aggressive driving with launch control dramatically reduces tire life. For better longevity, use Comfort mode instead of Dynamic for daily driving.</x:v>
+        <x:v>Confirm the leak source and VIN applicability before ordering parts. For the TSB condition, Audi specifies replacing the coolant feed and return pipes on both cylinder banks, replacing the disturbed oil-feed-pipe O-rings, then refilling and bleeding the cooling system. Service Action 21F7 was VIN-specific and expired in 2019, so current coverage must not be assumed. Do not order the former single pipe or alleged silicone-line kit from this card.</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
         <x:v>0</x:v>
@@ -15877,21 +18755,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="10" ht="290.3999938964844" hidden="0" customHeight="1">
       <x:c r="A10" s="40" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>audi-rs-q8-air-suspension-2020</x:v>
+        <x:v>audi-s7-air-suspension-2012</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
-        <x:v>2020-2025 | Audi | RS Q8</x:v>
+        <x:v>2020-2021 | Audi | S7</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>2020-2025 RS Q8 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
+        <x:v>Rear-Axle Lock Nut and Alignment Recall Follow-Up (21V295 / 22V034)</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
-        <x:v>Inspect the wiring and connector contacts between J775 and J1135 before replacing a component. For a first passive or sporadic occurrence, clear the fault and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after wiring inspection, Audi directs replacement of J1135 under current repair and parts information. Do not buy struts, springs, a compressor or a conversion kit solely from this warning.</x:v>
+        <x:v>Check the VIN for both campaigns 42L1 and 42L5. Audi dealers replace affected nuts and bolts, inspect and adjust rear alignment, and replace qualifying unevenly worn tires free of charge.</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
         <x:v>0</x:v>
@@ -15900,21 +18778,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="184.8000030517578" hidden="0" customHeight="1">
+    <x:row r="11" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A11" s="40" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>audi-rs3-carbon-buildup-2017</x:v>
+        <x:v>audi-s7-biturbo-coolant-2012</x:v>
       </x:c>
       <x:c r="C11" s="9" t="str">
-        <x:v>2017-2025 | Audi | RS3 | 2.5T</x:v>
+        <x:v>2013-2014 | Audi | S7 | 4.0 TFSI</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>2.5T Five-Cylinder Carbon Buildup</x:v>
+        <x:v>4.0L Fuel Line Can Leak and Create a Fire Risk (Recall 13V450 / 20U6)</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
-        <x:v>Walnut blast intake valves every 30,000-40,000 miles. Install catch can immediately on new vehicles.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel line free of charge under campaign 20U6/L8. Stop driving if fuel odor or leakage is present.</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
         <x:v>0</x:v>
@@ -15923,21 +18801,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="686.4000244140625" hidden="0" customHeight="1">
+    <x:row r="12" ht="264" hidden="0" customHeight="1">
       <x:c r="A12" s="40" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="9" t="str">
-        <x:v>audi-rs3-dsg-transmission-2015</x:v>
+        <x:v>audi-s7-carbon-buildup-4.0t-2012</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
-        <x:v>2023-2023 | Audi | RS3</x:v>
+        <x:v>2021-2021 | Audi | S7</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>2023 RS3 TCM Software Emissions Recall 37P3 - VIN Check Required</x:v>
+        <x:v>Rear Seat-Belt Retractor Can Release a Child Restraint Early (Recall 21V606 / 69CS)</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>Ask an Audi dealer to check whether Emissions Recall 37P3 is currently open for the VIN in Elsa. When open, the dealer updates the transmission-control-module software under the campaign; the published remedy requires no parts. Diagnose and repair the underlying fault separately before expecting its stored entry or MIL to clear. Do not buy a mechatronic unit, clutch pack, filter or upgraded DQ500 part for this software campaign.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers inspect and replace the affected middle-rear seat-belt assembly as necessary free of charge under campaign 69CS.</x:v>
       </x:c>
       <x:c r="F12" s="9" t="n">
         <x:v>0</x:v>
@@ -15946,21 +18824,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="686.4000244140625" hidden="0" customHeight="1">
+    <x:row r="13" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A13" s="40" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="9" t="str">
-        <x:v>audi-rs3-hpfp-2017</x:v>
+        <x:v>audi-s7-cylinder-demand-rough-running-hesitation</x:v>
       </x:c>
       <x:c r="C13" s="9" t="str">
-        <x:v>2017-2023 | Audi | RS3</x:v>
+        <x:v>2021-2021 | Audi | S7</x:v>
       </x:c>
       <x:c r="D13" s="9" t="str">
-        <x:v>2017-2020 / 2022-2023 RS3 Drive-System Warning or No-Start Diagnosis - TSB 2067757/3</x:v>
+        <x:v>Instrument Panel May Fail to Display Critical Safety Information (Recall 25V201 / 90VC)</x:v>
       </x:c>
       <x:c r="E13" s="9" t="str">
-        <x:v>Reproduce and document the complaint, scan the vehicle with current ODIS and complete Guided Fault Finding. When one of the listed DTC/symptom combinations is stored but GFF produces no result, manually add and complete the G265 intermediate-shaft-speed-sensor test plan. Repair only the component identified by that diagnosis. Do not replace or upgrade the high-pressure fuel pump from this warning or DTC set alone.</x:v>
+        <x:v>Check the VIN and campaign-completion history. Audi dealers update the instrument-panel module software free of charge under campaign 90VC.</x:v>
       </x:c>
       <x:c r="F13" s="9" t="n">
         <x:v>0</x:v>
@@ -15969,21 +18847,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="14" ht="316.79998779296875" hidden="0" customHeight="1">
       <x:c r="A14" s="40" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="9" t="str">
-        <x:v>audi-rs3-magnetic-ride-2017</x:v>
+        <x:v>audi-s7-ea839-2-9t-v6-water-pump-internal-leak-overheating</x:v>
       </x:c>
       <x:c r="C14" s="9" t="str">
-        <x:v>2015-2019 | Audi | RS3</x:v>
+        <x:v>2020-2024 | Audi | S7</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
-        <x:v>2015-2018 / Certain 2019 RS3 Magnetic-Ride Rear Shock Noise - TSB 2059240/1</x:v>
+        <x:v>Rearview Camera Image May Not Display (Recall 25V900 / 90TV)</x:v>
       </x:c>
       <x:c r="E14" s="9" t="str">
-        <x:v>Confirm magnetic-ride equipment, the exact model-year/VIN boundary and that the noise originates at the rear shock absorbers. When every bulletin criterion matches, replace both rear shock absorbers according to Audi workshop instructions and order the correct units by VIN. Do not replace dampers or convert the suspension from visible residue, ride feel or noise alone without this diagnosis.</x:v>
+        <x:v>Check the VIN and campaign-completion history. Audi dealers update the relevant software free of charge under campaign 90TV. Continue direct visual checks when reversing until repaired.</x:v>
       </x:c>
       <x:c r="F14" s="9" t="n">
         <x:v>0</x:v>
@@ -15992,21 +18870,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="15" ht="343.20001220703125" hidden="0" customHeight="1">
       <x:c r="A15" s="40" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="9" t="str">
-        <x:v>audi-rs3-ttrs-carbon-buildup-2015</x:v>
+        <x:v>audi-s7-electromechanical-steering-rack-torque-sensor-failure-causin</x:v>
       </x:c>
       <x:c r="C15" s="9" t="str">
-        <x:v>2015-2023 | Audi | RS3 | 2.5T EA855</x:v>
+        <x:v>2021-2021 | Audi | S7</x:v>
       </x:c>
       <x:c r="D15" s="9" t="str">
-        <x:v>Severe Carbon Buildup on Intake Valves (2.5T 5-Cylinder)</x:v>
+        <x:v>Incorrect Brake-Fluid Reservoir Cap Label (Recall 23V601 / 47T9)</x:v>
       </x:c>
       <x:c r="E15" s="9" t="str">
-        <x:v>WALNUT BLASTING: Remove intake manifold and blast walnut shells through intake ports ($800-$1,500). Repeat every 30,000-40,000 miles—MORE frequent than base models due to high performance. PREVENTION: Install catch can ($400-$700) to filter PCV vapors. Add Liqui Moly Intake Valve Cleaner to every oil change. Change oil every 5,000 miles. Drive car hard regularly—Audi's own recommendation to burn off carbon.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers inspect the reservoir cap and replace it when necessary free of charge under campaign 47T9. Use only the brake-fluid specification in the owner and service information.</x:v>
       </x:c>
       <x:c r="F15" s="9" t="n">
         <x:v>0</x:v>
@@ -16015,44 +18893,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="792" hidden="0" customHeight="1">
+    <x:row r="16" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A16" s="40" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="9" t="str">
-        <x:v>audi-rs3-ttrs-injector-failure-2015</x:v>
+        <x:v>audi-s7-front-control-arm-bushing-ball-joint-failure</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
-        <x:v>2015-2023 | Audi | RS3 | EA855</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
       </x:c>
       <x:c r="D16" s="9" t="str">
-        <x:v>Fuel Injector Failure and "Torch Effect" (2.5T)</x:v>
+        <x:v>Front Control Arm Bushing and Ball Joint Failure (C7 Suspension)</x:v>
       </x:c>
       <x:c r="E16" s="9" t="str">
-        <x:v>PREVENTIVE REPLACEMENT: Replace all fuel injectors every 60,000 km (37,000 miles) with OEM Audi injectors ($1,500-$2,500 installed). If engine misfires or runs rough: Inspect injectors IMMEDIATELY—do NOT continue driving. Failed injector can destroy engine in minutes. If piston is melted: Engine replacement required ($15,000-$25,000). Consider extended warranty or aftermarket warranty for out-of-warranty RS3/TT RS. This is the most serious reliability issue with the 2.5T engine.</x:v>
+        <x:v>Inspect all front control arms for play in the bushings and ball joints. Replace worn arms — many owners do the full front control-arm set (commonly a 16-piece kit covering both sides) to avoid repeat visits since the labor overlaps. Critical install notes: torque the bushing bolts at ride height (not with the suspension hanging) to avoid pre-loading and destroying the new bushings, and perform a four-wheel alignment afterward.</x:v>
       </x:c>
       <x:c r="F16" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G16" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="17" ht="396" hidden="0" customHeight="1">
       <x:c r="A17" s="40" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="9" t="str">
-        <x:v>audi-rs4-b7-carbon-buildup-2007</x:v>
+        <x:v>audi-s7-fuel-injector-deposits-failure-causing-misfire-rough-running</x:v>
       </x:c>
       <x:c r="C17" s="9" t="str">
-        <x:v>2007-2008 | Audi | RS4 | 4.2L FSI V8</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
       </x:c>
       <x:c r="D17" s="9" t="str">
-        <x:v>2007-2008 RS4 Deposit-Related Cold-Start Misfire - Diagnose Before Cleaning</x:v>
+        <x:v>Fuel Injector Deposits / Failure Causing Misfire and Rough Running (4.0T V8)</x:v>
       </x:c>
       <x:c r="E17" s="9" t="str">
-        <x:v>Have the cold-start event and stored faults diagnosed before authorizing intake cleaning. The B7 RS4 bulletin first checks whether its fuel-additive and follow-up procedure resolves injector-deposit misfires. Current TSB 2014753/13 warns that gasoline additive can clean FSI injectors and combustion chambers but not FSI intake valves. If the misfire remains, the shop should continue guided diagnosis and confirm inlet-valve deposits before using the applicable mechanical-cleaning procedure. Do not buy a scanner, oil bundle or cleaning service solely from this card.</x:v>
+        <x:v>Pull misfire counts per cylinder to localize the fault. Inspect/replace failed or leaking injectors and renew injector seals; replace spark plugs and any weak coils as a set. Confirm fuel trims return to normal and clear codes; address intake carbon if present.</x:v>
       </x:c>
       <x:c r="F17" s="9" t="n">
         <x:v>0</x:v>
@@ -16061,21 +18939,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="963.5999755859375" hidden="0" customHeight="1">
+    <x:row r="18" ht="396" hidden="0" customHeight="1">
       <x:c r="A18" s="40" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="9" t="str">
-        <x:v>audi-rs4-rs5-carbon-buildup-2018</x:v>
+        <x:v>audi-s7-gateway-control-module-shutdown-from-rear-seat-liquid-spill</x:v>
       </x:c>
       <x:c r="C18" s="9" t="str">
-        <x:v>2018-2023 | Audi | RS4 | 2.9T</x:v>
+        <x:v>2020-2022 | Audi | S7 | 2.9 TFSI</x:v>
       </x:c>
       <x:c r="D18" s="9" t="str">
-        <x:v>2018-2023 RS4 2.9T Cold-Start Misfire from Confirmed Inlet Deposits</x:v>
+        <x:v>Rear-Seat Liquid Spill Can Shut Down Gateway Module (Recall 22V861 / 90V2)</x:v>
       </x:c>
       <x:c r="E18" s="9" t="str">
-        <x:v>Confirm the cold-start complaint, review the engine-control-unit event memory and verify inlet-port or inlet-valve deposits before cleaning. When that condition is confirmed, Audi TSB 2075530/1 directs the shop to remove the intake manifold or compressor and clean the inlet valves and ports by walnut blasting; the cylinder head remains installed. The cited Audi guidance does not support a mandatory 60,000-mile interval, a fixed price, dual catch cans, additive at every oil change, a 5,000-mile oil interval or a drive-hard prescription. Do not buy a catch can or cleaning product solely from this card.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers install a protective gateway-module cover free of charge under campaign 90V2. If multiple warnings or reduced power occur after a spill, move out of traffic safely and arrange dealer inspection.</x:v>
       </x:c>
       <x:c r="F18" s="9" t="n">
         <x:v>0</x:v>
@@ -16084,21 +18962,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="1227.5999755859375" hidden="0" customHeight="1">
+    <x:row r="19" ht="528" hidden="0" customHeight="1">
       <x:c r="A19" s="40" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="9" t="str">
-        <x:v>audi-rs5-b8-carbon-buildup-2013</x:v>
+        <x:v>audi-s7-high-pressure-fuel-pump-failure-causing-hard-start-power-los</x:v>
       </x:c>
       <x:c r="C19" s="9" t="str">
-        <x:v>2013-2015 | Audi | RS5 | 4.2L V8</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
       </x:c>
       <x:c r="D19" s="9" t="str">
-        <x:v>4.2L V8 Carbon Buildup and High-Rev Issues</x:v>
+        <x:v>High-Pressure Fuel Pump (HPFP) Failure Causing Hard Start and Power Loss (4.0T V8)</x:v>
       </x:c>
       <x:c r="E19" s="9" t="str">
-        <x:v>Confirm carbon buildup by scanning for misfire/fuel-trim faults, reviewing live data, and inspecting the intake valves with a borescope after removing the intake manifold. The proper repair is an intake-valve carbon cleaning service—typically walnut-shell blasting or manual chemical cleaning—while replacing the intake manifold gaskets, injector seals/O-rings, and PCV-related breather components if leaking or contributing to oil vapor. After reassembly, clear adaptations, perform a throttle-body/basic setting relearn, and road test to verify restored high-RPM pull and smooth idle. Independent shops typically charge about $800-$1,500 for a carbon clean on the 4.2 FSI V8, while dealer pricing can run roughly $1,500-$2,500 depending on how many seals and ancillary parts are replaced.</x:v>
+        <x:v>Diagnose with live fuel-rail pressure data before condemning the pump, as a faulty low-pressure sensor or in-tank pump can set the same codes. Replace the failed high-pressure pump (the affected bank, or both as a set on high-mileage cars) together with the cam follower and seals. Verify low-pressure (in-tank) supply is within spec.</x:v>
       </x:c>
       <x:c r="F19" s="9" t="n">
         <x:v>0</x:v>
@@ -16107,44 +18985,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="1122" hidden="0" customHeight="1">
+    <x:row r="20" ht="660" hidden="0" customHeight="1">
       <x:c r="A20" s="40" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="9" t="str">
-        <x:v>audi-rs5-carbon-buildup-2018</x:v>
+        <x:v>audi-s7-ignition-coil-pack-failure-causing-misfires</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>2018-2026 | Audi | RS5</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>Direct Injection Carbon Buildup on Intake Valves</x:v>
+        <x:v>Ignition Coil Pack Failure Causing Misfires (4.0T V8)</x:v>
       </x:c>
       <x:c r="E20" s="9" t="str">
-        <x:v>Confirm intake-valve carbon buildup by scanning for misfire faults, reviewing fuel trims, and inspecting the intake valves with a borescope through the intake ports after removing the intake manifold. The proper repair is an intake-valve cleaning service, typically walnut-shell blasting each intake port with the valves closed, then replacing the intake manifold gaskets and any disturbed PCV or breather seals before clearing adaptations and road-testing. If misfires persist, inspect and replace worn spark plugs or ignition coils as needed, since heavy deposits can foul plugs and mimic ignition faults. Typical cost is about $800-$1,500 depending on labor rates and how much disassembly is required.</x:v>
+        <x:v>Confirm the failing cylinder, then swap the suspect coil to another cylinder to verify the fault follows the coil. Replace the failed coil; best practice on the 4.0T is to replace all eight coils and the spark plugs as a set since the access labor is shared and mixed-age coils tend to fail in sequence. Use OE or quality OE-equivalent coils (the 4.0T uses the 079905110-series coil). Inspect spark plugs for fouling/oil that could indicate a secondary issue.</x:v>
       </x:c>
       <x:c r="F20" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G20" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="1003.2000122070312" hidden="0" customHeight="1">
+    <x:row r="21" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A21" s="40" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="9" t="str">
-        <x:v>audi-rs5-turbo-coolant-2018</x:v>
+        <x:v>audi-s7-motor-mount-failure-2012</x:v>
       </x:c>
       <x:c r="C21" s="9" t="str">
-        <x:v>2021-2024 | Audi | RS5 | 2.9L V6 TFSI</x:v>
+        <x:v>2013-2018 | Audi | S7</x:v>
       </x:c>
       <x:c r="D21" s="9" t="str">
-        <x:v>2021-2024 RS5 V6 Coolant-Pump Leak Diagnosis - TSB 2070349/4</x:v>
+        <x:v>Passenger Occupant Detection Mat Can Disable the Airbag (Recall 18V370 / 74D5)</x:v>
       </x:c>
       <x:c r="E21" s="9" t="str">
-        <x:v>Locate the leak before replacing parts. Clean and dry the area, fill the cooling system to maximum, inspect at idle and at engine speeds up to about 2,500 rpm, and perform the Workshop Manual cooling-system leak test. If no further leak is detected, continue observation without replacing parts. If a leak recurs, replace only the component or components causing the leak and document the finding with clear photos or video; a pump-leak repair also requires a photo of the pump production date. Inspect the vacuum circuit and N649 when contamination or P0299 is present, following current Audi workshop and parts information.</x:v>
+        <x:v>Check VIN eligibility because seat equipment affects scope. Audi dealers install the occupant-detection repair kit free of charge under campaign 74D5.</x:v>
       </x:c>
       <x:c r="F21" s="9" t="n">
         <x:v>0</x:v>
@@ -16153,21 +19031,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="22" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A22" s="40" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="9" t="str">
-        <x:v>audi-rs6-air-suspension-2020</x:v>
+        <x:v>audi-s7-pcv-oil-separator-failure-causing-oil-consumption-whistling</x:v>
       </x:c>
       <x:c r="C22" s="9" t="str">
-        <x:v>2021-2024 | Audi | RS6</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
       </x:c>
       <x:c r="D22" s="9" t="str">
-        <x:v>2021-2024 RS6 Air-Suspension Warning - Check C1260F0 or U112100</x:v>
+        <x:v>PCV / Oil Separator (Ölabscheider) Failure Causing Oil Consumption and Whistling (4.0T V8)</x:v>
       </x:c>
       <x:c r="E22" s="9" t="str">
-        <x:v>Have the wiring and connector contacts between suspension controller J775 and compressor controller J1135 inspected first. Audi says to clear a first passive or sporadic occurrence and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after the wiring check, the bulletin directs replacement of J1135 under the applicable service procedure. Do not replace air struts, a compressor or an unverified aftermarket assembly solely from this warning card.</x:v>
+        <x:v>Replace the failed oil separator / PCV assembly and the associated breather hose with the latest revised part. An ECM update may accompany the new part on some VINs. Confirm with a smoke test for intake-side vacuum leaks; inspect the rear main seal if oil consumption is severe, as a failed PCV is a common cause of rear main seal damage on these engines.</x:v>
       </x:c>
       <x:c r="F22" s="9" t="n">
         <x:v>0</x:v>
@@ -16176,21 +19054,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="831.5999755859375" hidden="0" customHeight="1">
+    <x:row r="23" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A23" s="40" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="9" t="str">
-        <x:v>audi-rs6-carbon-buildup-2020</x:v>
+        <x:v>audi-s7-power-liftgate-motor-gas-strut-failure</x:v>
       </x:c>
       <x:c r="C23" s="9" t="str">
-        <x:v>2021-2024 | Audi | RS6 | 4.0T V8</x:v>
+        <x:v>2013-2022 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824), 2.9T TFSI Biturbo V6 (EA839)</x:v>
       </x:c>
       <x:c r="D23" s="9" t="str">
-        <x:v>2021-2024 RS6 4.0T Cold-Start Misfire from Confirmed Inlet Deposits</x:v>
+        <x:v>Power Liftgate Motor and Gas Strut Failure (Sportback Tailgate)</x:v>
       </x:c>
       <x:c r="E23" s="9" t="str">
-        <x:v>Confirm the cold-start complaint, review the engine-control-unit event memory and verify inlet-port or inlet-valve deposits before cleaning. When that condition is confirmed, Audi TSB 2075530/1 directs the shop to remove the intake manifold or compressor and clean the inlet valves and ports by walnut blasting; the cylinder head remains installed. The cited Audi guidance does not specify a 30,000-40,000-mile interval, a fixed price or a mandatory catch can. Do not buy a catch can or cleaning product solely from this card.</x:v>
+        <x:v>Diagnose whether the fault is the gas struts (won't stay up / weak lift), the spindle lift motors (slow or struggling travel), or the latch/cinching motor (won't release or won't pull closed — see TSB 2072431/1). Replace worn gas struts in pairs; replace failed lift or cinching motors as needed. After repair, perform the power-liftgate relearn/reset procedure so travel limits recalibrate.</x:v>
       </x:c>
       <x:c r="F23" s="9" t="n">
         <x:v>0</x:v>
@@ -16199,21 +19077,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="528" hidden="0" customHeight="1">
+    <x:row r="24" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A24" s="40" t="n">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="9" t="str">
-        <x:v>audi-rs6-rs7-carbon-buildup-2013</x:v>
+        <x:v>audi-s7-premature-front-brake-rotor-warping-pad-wear</x:v>
       </x:c>
       <x:c r="C24" s="9" t="str">
-        <x:v>2013-2023 | Audi | RS6 | 4.0T V8</x:v>
+        <x:v>2013-2022 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824), 2.9T TFSI Biturbo V6 (EA839)</x:v>
       </x:c>
       <x:c r="D24" s="9" t="str">
-        <x:v>Severe Carbon Buildup on Intake Valves (4.0T V8)</x:v>
+        <x:v>Premature Front Brake Rotor Warping and Pad Wear</x:v>
       </x:c>
       <x:c r="E24" s="9" t="str">
-        <x:v>WALNUT BLASTING: Remove both intake manifolds and blast walnut shells through all intake ports ($1,200-$2,000 for V8). Repeat every 60,000 miles. PREVENTION: Install catch can ($500-$800 for twin-turbo setup). Add Liqui Moly Intake Valve Cleaner to every oil change. Change oil every 5,000 miles. Drive car hard regularly.</x:v>
+        <x:v>Replace warped/below-spec rotors and pads together; consider higher-quality coated or upgraded rotors that resist warping better than the soft OEM units. Bed in new pads/rotors properly and avoid riding the brakes to prevent uneven deposits. Ensure caliper guide pins/slides move freely so pads engage evenly. For repeat warping, an upgraded rotor-and-pad package is the durable fix; address any pulsation early before it damages new components.</x:v>
       </x:c>
       <x:c r="F24" s="9" t="n">
         <x:v>0</x:v>
@@ -16222,21 +19100,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="25" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A25" s="40" t="n">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="9" t="str">
-        <x:v>audi-rs6-rs7-motor-mounts-2013</x:v>
+        <x:v>audi-s7-rear-differential-mount-driveshaft-center-bearing-wear-causi</x:v>
       </x:c>
       <x:c r="C25" s="9" t="str">
-        <x:v>2013-2023 | Audi | RS6 | 4.0T V8</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
       </x:c>
       <x:c r="D25" s="9" t="str">
-        <x:v>Premature Motor Mount Failure (4.0T V8)</x:v>
+        <x:v>Rear Differential Mount and Driveshaft Center Bearing Wear Causing Drivetrain Clunk (C7)</x:v>
       </x:c>
       <x:c r="E25" s="9" t="str">
-        <x:v>Replace failed motor mounts with OEM or upgraded mounts ($800-$1,500 for all mounts). Upgraded aftermarket mounts (034 Motorsport, ECS) offer better durability for high-torque engines ($400-$600 per mount). If you drive aggressively or track the car, consider upgrading to performance mounts preventively. Monitor for vibrations and clunking—early replacement prevents driveline damage.</x:v>
+        <x:v>Inspect the rear differential mount and driveshaft center support bearing for play and torn rubber. Replace worn components with OE parts, or fit billet aluminum diff/transmission mount inserts that fill the factory voids to remove the slop without adding harshness. On 4.0T cars, also check for the separate active-engine-mount software TSB before condemning a mount for a 1,000-3,000 RPM cruise vibration. Reassess the clunk after each fix since multiple sources can contribute.</x:v>
       </x:c>
       <x:c r="F25" s="9" t="n">
         <x:v>0</x:v>
@@ -16245,21 +19123,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="26" ht="462" hidden="0" customHeight="1">
       <x:c r="A26" s="40" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="9" t="str">
-        <x:v>audi-rs7-air-suspension-2014</x:v>
+        <x:v>audi-s7-rear-view-camera-mmi-flex-harness-black-screen</x:v>
       </x:c>
       <x:c r="C26" s="9" t="str">
-        <x:v>2021-2025 | Audi | RS7</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7 (C7), A7 (C7) | 4.0 TFSI V8 (EA824)</x:v>
       </x:c>
       <x:c r="D26" s="9" t="str">
-        <x:v>2021-2025 RS7 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
+        <x:v>Rear-View Camera / MMI Flex Harness Black Screen</x:v>
       </x:c>
       <x:c r="E26" s="9" t="str">
-        <x:v>Inspect the wiring and connectors between J775 and J1135 before replacing a component. For a first passive/sporadic occurrence, clear the fault and release the vehicle. If the fault is active/static after wiring and connector inspection, or the same passive/sporadic fault returns a second time, replace J1135 using current Audi repair and parts information. Audi notes that improved J1135 software remains under development.</x:v>
+        <x:v>Diagnose with a scan and continuity check of the tailgate-to-body flex harness before replacing the camera. Repair or replace the broken hinge-side loom conductors; if confirmed faulty, replace the camera module. For MMI freezes, apply the latest software update or reset the unit.</x:v>
       </x:c>
       <x:c r="F26" s="9" t="n">
         <x:v>0</x:v>
@@ -16268,21 +19146,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="158.39999389648438" hidden="0" customHeight="1">
+    <x:row r="27" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A27" s="40" t="n">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="9" t="str">
-        <x:v>audi-rs7-carbon-buildup-2014</x:v>
+        <x:v>audi-s7-s-tronic-7-speed-dual-clutch-mechatronic-clutch-wear</x:v>
       </x:c>
       <x:c r="C27" s="9" t="str">
-        <x:v>2014-2026 | Audi | RS7 | 4.0T</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T (S-tronic / 0B5 DL501) | 4.0 TFSI V8 (EA824)</x:v>
       </x:c>
       <x:c r="D27" s="9" t="str">
-        <x:v>4.0T Carbon Deposit Accumulation</x:v>
+        <x:v>S-tronic 7-Speed Dual-Clutch (DL501/0B5) Mechatronic and Clutch Wear</x:v>
       </x:c>
       <x:c r="E27" s="9" t="str">
-        <x:v>Walnut blast every 30,000-40,000 miles. Install dual catch can setup for both turbo sides.</x:v>
+        <x:v>Perform the S-tronic gearbox oil and filter service on schedule (roughly every 40,000-60,000 km). For judder/jerking, have the mechatronic unit tested; recondition or replace the valve body with the superseded design and adapt/replace the clutch packs as needed. Software adaptation resets can temporarily improve drivability but do not fix worn hardware.</x:v>
       </x:c>
       <x:c r="F27" s="9" t="n">
         <x:v>0</x:v>
@@ -16291,21 +19169,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="28" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A28" s="40" t="n">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="9" t="str">
-        <x:v>audi-rs7-turbo-coolant-2014</x:v>
+        <x:v>audi-s7-shark-fin-roof-antenna-water-intrusion-causing-gps-satellite</x:v>
       </x:c>
       <x:c r="C28" s="9" t="str">
-        <x:v>2014-2026 | Audi | RS7 | 4.0T</x:v>
+        <x:v>2013-2018 | Audi | S7 | Prestige, Premium Plus | 4.0T Biturbo V8 (4.0 TFSI)</x:v>
       </x:c>
       <x:c r="D28" s="9" t="str">
-        <x:v>4.0T Twin-Turbo Coolant System Degradation</x:v>
+        <x:v>Shark-Fin Roof Antenna Water Intrusion Causing GPS / Satellite Radio Reception Loss (C7)</x:v>
       </x:c>
       <x:c r="E28" s="9" t="str">
-        <x:v>Replace turbo coolant lines proactively at 50,000 miles. Upgrade to silicone lines where possible.</x:v>
+        <x:v>Test/replace the shark-fin antenna module with a matching OEM part number and renew the base gasket to restore a watertight seal; in many cases the official fix is a repair kit with a new FAKRA connector and adapter cable rather than a whole new antenna. Access requires partially dropping the rear headliner to reach the single mounting nut and reconnect the coax leads. Inspecting and reseating a corroded coax connection sometimes restores reception without full replacement.</x:v>
       </x:c>
       <x:c r="F28" s="9" t="n">
         <x:v>0</x:v>
@@ -16314,21 +19192,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="29" ht="752.4000244140625" hidden="0" customHeight="1">
       <x:c r="A29" s="40" t="n">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="9" t="str">
-        <x:v>audi-rs7-turbo-wastegate-2014</x:v>
+        <x:v>audi-s7-sunroof-panoramic-roof-drain-clog-causing-water-intrusion-el</x:v>
       </x:c>
       <x:c r="C29" s="9" t="str">
-        <x:v>2014-2017 | Audi | RS7 | 4.0L TFSI twin-turbo V8</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
       </x:c>
       <x:c r="D29" s="9" t="str">
-        <x:v>2014-2017 RS7 Turbocharger Oil-Strainer Safety Recall 21H7 / 22V178 - Check VIN</x:v>
+        <x:v>Sunroof / Panoramic Roof Drain Clog Causing Water Intrusion and Electronics Damage (C7)</x:v>
       </x:c>
       <x:c r="E29" s="9" t="str">
-        <x:v>Check the VIN for open Audi campaign 21H7 in Elsa or the NHTSA recall lookup. The authorized dealer replaces the turbocharger oil strainer, changes the engine oil and filter, and performs the campaign scan-tool turbo/boost-system check at no charge. Follow the campaign procedure for any damage found; do not buy a turbocharger, actuator or gasket kit from this card.</x:v>
+        <x:v>Test the drains by slowly pouring water into the channels at each corner of the sunroof and watching where it exits beneath the A- and C-pillars. Clear clogged tubes with low-pressure air or a soft trimmer line (avoid stiff wire that can puncture the tube) and reseat/secure any loose drain-tube connectors at the sunroof frame. Dry out any soaked carpet/insulation promptly and inspect floor-mounted modules for corrosion. Periodic drain cleaning is the best prevention.</x:v>
       </x:c>
       <x:c r="F29" s="9" t="n">
         <x:v>0</x:v>
@@ -16337,21 +19215,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="30" ht="422.3999938964844" hidden="0" customHeight="1">
       <x:c r="A30" s="40" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="9" t="str">
-        <x:v>audi-rsq8-4.0t-coolant-2020</x:v>
+        <x:v>audi-s7-turbo-oil-strainer-2012</x:v>
       </x:c>
       <x:c r="C30" s="9" t="str">
-        <x:v>2020-2021 | Audi | RS Q8 | 4.0T V8</x:v>
+        <x:v>2013-2017 | Audi | S7 | 4.0 TFSI</x:v>
       </x:c>
       <x:c r="D30" s="9" t="str">
-        <x:v>2020-Early 2021 RS Q8 Red Coolant Warning - Check G407 per TSB 2062951/4</x:v>
+        <x:v>Turbocharger Oil-Supply Strainer Can Block and Cause Engine Stall (Recall 22V178 / 21H7)</x:v>
       </x:c>
       <x:c r="E30" s="9" t="str">
-        <x:v>Have the vehicle checked with Audi Guided Fault Finding and inspect G407 and its O-ring. Replace G407 only if the O-ring is damaged or pinched and the diagnosis matches the bulletin; follow the related Audi diagnostic path if additional listed faults are stored. Do not replace turbo coolant hoses, pumps or other cooling parts from this card alone.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the oil strainer and perform an oil change free of charge under campaign 21H7. If abnormal turbo noise, loss of power, or an engine warning occurs, stop safely and arrange dealer inspection.</x:v>
       </x:c>
       <x:c r="F30" s="9" t="n">
         <x:v>0</x:v>
@@ -16360,21 +19238,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="237.60000610351562" hidden="0" customHeight="1">
+    <x:row r="31" ht="726" hidden="0" customHeight="1">
       <x:c r="A31" s="40" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="9" t="str">
-        <x:v>audi-rsq8-air-suspension-2020</x:v>
+        <x:v>audi-s7-turbocharger-wastegate-linkage-rattle-underboost</x:v>
       </x:c>
       <x:c r="C31" s="9" t="str">
-        <x:v>2020-2026 | Audi | RS Q8</x:v>
+        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
       </x:c>
       <x:c r="D31" s="9" t="str">
-        <x:v>Adaptive Air Suspension Failure Under SUV Weight</x:v>
+        <x:v>Turbocharger Wastegate Linkage Rattle and Underboost (4.0T V8)</x:v>
       </x:c>
       <x:c r="E31" s="9" t="str">
-        <x:v>Replace air struts as they fail. Budget for compressor replacement. Consider heavy-duty aftermarket options designed for the RS Q8 weight.</x:v>
+        <x:v>Diagnose the rattle and any boost faults to confirm wastegate-arm play versus a loose heat shield. Minor play can sometimes be mitigated with a clip, but the durable factory fix is turbocharger replacement. When replacing a hot-V turbo, it is mandatory to also replace the oil feed and return lines and to prime the new unit with oil before first start to prevent immediate bearing failure. Regular oil changes and allowing turbo cool-down help reduce coking-related wear.</x:v>
       </x:c>
       <x:c r="F31" s="9" t="n">
         <x:v>0</x:v>
@@ -16383,20 +19261,22 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="32" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A32" s="40" t="n">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="9" t="str">
-        <x:v>audi-rsq8-air-suspension-leak-2020</x:v>
+        <x:v>audi-s8-5-2-v10-timing-chain-tensioner-guide-wear</x:v>
       </x:c>
       <x:c r="C32" s="9" t="str">
-        <x:v>2020-2026 | Audi | RS Q8</x:v>
+        <x:v>2007-2012 | Audi | S8 | 5.2L FSI V10 (BSM)</x:v>
       </x:c>
       <x:c r="D32" s="9" t="str">
-        <x:v>Adaptive Air Suspension Air Spring Leaks</x:v>
-      </x:c>
-      <x:c r="E32" s="9" t="str"/>
+        <x:v>5.2 V10 Timing Chain Tensioner / Guide Wear (D3 Cold-Start Rattle)</x:v>
+      </x:c>
+      <x:c r="E32" s="9" t="str">
+        <x:v>Investigate any cold-start rattle promptly: inspect tensioner travel and guide condition. Replace the timing chains, tensioners, and plastic guides as a set with updated genuine parts; this is a major, labor-intensive repair (often engine-out). Strictly follow short oil-change intervals with the correct grade to maximize tensioner/guide life, and address any low-oil-pressure condition immediately. Do not drive a V10 with a persistent timing rattle.</x:v>
+      </x:c>
       <x:c r="F32" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -16404,21 +19284,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="607.2000122070312" hidden="0" customHeight="1">
+    <x:row r="33" ht="198" hidden="0" customHeight="1">
       <x:c r="A33" s="40" t="n">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="9" t="str">
-        <x:v>audi-rsq8-brake-wear-2020</x:v>
+        <x:v>audi-s8-air-suspension-2013</x:v>
       </x:c>
       <x:c r="C33" s="9" t="str">
-        <x:v>2020-2021 | Audi | RS Q8</x:v>
+        <x:v>2013-2024 | Audi | S8</x:v>
       </x:c>
       <x:c r="D33" s="9" t="str">
-        <x:v>2020-2021 RS Q8 Front Steel-Brake Squeal - TSB 2062052/1</x:v>
+        <x:v>Adaptive Air Suspension Multi-Point Failure</x:v>
       </x:c>
       <x:c r="E33" s="9" t="str">
-        <x:v>Confirm the frequency and operating conditions and inspect the discs for corrosion, grooves or glazing. When the bulletin applies, Audi directs replacement of the front pad set using current parts information followed by the specified bedding procedure. Do not perform ABS stops for bedding, and do not replace rotors or buy aftermarket pads solely from the prior wear narrative.</x:v>
+        <x:v>Replace air struts as they fail. Budget for full system refresh at 80,000 miles. Arnott aftermarket struts offer cost savings.</x:v>
       </x:c>
       <x:c r="F33" s="9" t="n">
         <x:v>0</x:v>
@@ -16427,21 +19307,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="34" ht="726" hidden="0" customHeight="1">
       <x:c r="A34" s="40" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="9" t="str">
-        <x:v>audi-s3-carbon-buildup-2015</x:v>
+        <x:v>audi-s8-air-suspension-failure-2013</x:v>
       </x:c>
       <x:c r="C34" s="9" t="str">
-        <x:v>2015-2019 | Audi | S3 | S3 | EA888 Gen 3</x:v>
+        <x:v>2020-2024 | Audi | S8</x:v>
       </x:c>
       <x:c r="D34" s="9" t="str">
-        <x:v>Carbon Buildup on Intake Valves (Pre-Dual Injection EA888 Gen 3)</x:v>
+        <x:v>2020-2024 S8 Air-Suspension Malfunction with J1135 Communication Fault - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E34" s="9" t="str">
-        <x:v>WALNUT BLASTING: Remove intake manifold and blast intake valve ports with crushed walnut shells ($500-$1,000). Repeat every 40,000-60,000 miles. CATCH CAN: Install an oil catch can ($200-$400) to capture PCV vapors before they reach intake valves—significantly slows carbon buildup. OIL CHANGES: Use high-quality synthetic oil and change every 5,000 miles. DRIVING HABITS: Regular spirited driving helps burn off some deposits. NOTE: 2020+ S3 models with EA888 Gen 3B dual injection are largely immune to this issue.</x:v>
+        <x:v>Read the suspension-controller DTC and symptom code, then inspect wiring, terminals and connectors between J775 and J1135 exactly as Audi specifies. If the fault is passive/sporadic, clear it and verify operation. If it remains active/static after the electrical inspection and key cycle, follow Audi testing for J1135 replacement. Diagnose vehicle sag or leak-down separately; do not order air struts, a compressor or a coil-conversion kit from the former card.</x:v>
       </x:c>
       <x:c r="F34" s="9" t="n">
         <x:v>0</x:v>
@@ -16450,21 +19330,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="35" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A35" s="40" t="n">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="9" t="str">
-        <x:v>audi-s3-dq250-mechatronic-2015</x:v>
+        <x:v>audi-s8-battery-management-energy-control-module-faults-parasitic-dr</x:v>
       </x:c>
       <x:c r="C35" s="9" t="str">
-        <x:v>2015-2024 | Audi | S3</x:v>
+        <x:v>2020-2020 | Audi | S8 | VIN-specific Emissions Service Action 27BQ; verify open action in Audi campaign lookup | 4.0T TFSI V8 mild-hybrid</x:v>
       </x:c>
       <x:c r="D35" s="9" t="str">
-        <x:v>DQ250 DSG Mechatronic Unit Failure</x:v>
+        <x:v>2020 S8 Starter-Alternator Emissions Service Action 27BQ - VIN Check Required</x:v>
       </x:c>
       <x:c r="E35" s="9" t="str">
-        <x:v>Replace or rebuild mechatronic unit. Regular DSG fluid changes every 40,000 miles help prevent premature failure.</x:v>
+        <x:v>Check the VIN in Audi’s recall/service-campaign lookup or ask an Audi dealer to verify 27BQ in Elsa. If open, the dealer replaces the starter-alternator under the action. Electrical-system warnings, a discharged battery, abnormal charging or overnight draw outside this exact action require battery/charging tests and a measured sleep-current diagnosis; do not replace a battery monitor, gateway or MMI module from the former card.</x:v>
       </x:c>
       <x:c r="F35" s="9" t="n">
         <x:v>0</x:v>
@@ -16473,21 +19353,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="36" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A36" s="40" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="9" t="str">
-        <x:v>audi-s3-dsg-mechatronic-2015</x:v>
+        <x:v>audi-s8-biturbo-coolant-2013</x:v>
       </x:c>
       <x:c r="C36" s="9" t="str">
-        <x:v>2015-2024 | Audi | S3 | S3</x:v>
+        <x:v>2013-2024 | Audi | S8 | 4.0T</x:v>
       </x:c>
       <x:c r="D36" s="9" t="str">
-        <x:v>DQ381 S-Tronic Mechatronic Unit Failure</x:v>
+        <x:v>4.0T Turbo Coolant System Degradation</x:v>
       </x:c>
       <x:c r="E36" s="9" t="str">
-        <x:v>EARLY SYMPTOMS (jerky shifts): DSG fluid and filter service ($500-$700) plus dealer software update. This may resolve early-stage issues. MECHATRONIC FAILURE: Replace mechatronic unit ($2,000-$4,000 installed) plus TCU coding. Remanufactured units available for $1,500-$2,500. CLUTCH PACK FAILURE: Replace dual clutch pack ($3,000-$5,000). PREVENTION: Service DSG fluid every 40,000 miles—ignore Audi's 'lifetime fill' claim. Use ONLY OEM Audi DSG fluid (G 052 182 A2) or approved Pentosin FFL-2. Avoid aggressive launches and excessive clutch slip in traffic.</x:v>
+        <x:v>Replace all turbo coolant and oil feed lines preventatively at 60,000 miles. Monitor coolant levels closely.</x:v>
       </x:c>
       <x:c r="F36" s="9" t="n">
         <x:v>0</x:v>
@@ -16496,21 +19376,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="158.39999389648438" hidden="0" customHeight="1">
+    <x:row r="37" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A37" s="40" t="n">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="9" t="str">
-        <x:v>audi-s3-ea888-carbon-2015</x:v>
+        <x:v>audi-s8-clogged-sunroof-plenum-drains-causing-water-intrusion-electr</x:v>
       </x:c>
       <x:c r="C37" s="9" t="str">
-        <x:v>2015-2024 | Audi | S3 | EA888</x:v>
+        <x:v>2007-2018 | Audi | S8 | S8, S8 Plus | 5.2 FSI V10, 4.0 TFSI twin-turbo V8 (4.0T)</x:v>
       </x:c>
       <x:c r="D37" s="9" t="str">
-        <x:v>EA888 Carbon Buildup on Intake Valves</x:v>
+        <x:v>Clogged Sunroof / Plenum Drains Causing Water Intrusion and Electronics Damage</x:v>
       </x:c>
       <x:c r="E37" s="9" t="str">
-        <x:v>Walnut blast intake valves every 40,000-60,000 miles or install a catch can to reduce buildup rate.</x:v>
+        <x:v>Clear and flush all sunroof and plenum/cowl drains; replace cracked drain hoses, grommets, or channel connectors. Dry out saturated carpet/insulation and inspect plenum-area modules for corrosion, replacing any water-damaged control units. Preventively clean the drains at least annually and keep the cowl area free of leaves/debris.</x:v>
       </x:c>
       <x:c r="F37" s="9" t="n">
         <x:v>0</x:v>
@@ -16519,21 +19399,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="38" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A38" s="40" t="n">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="9" t="str">
-        <x:v>audi-s3-hpfp-2015</x:v>
+        <x:v>audi-s8-coolant-thermostat-leak-2013</x:v>
       </x:c>
       <x:c r="C38" s="9" t="str">
-        <x:v>2015-2024 | Audi | S3 | EA888</x:v>
+        <x:v>2020-2021 | Audi | S8 | 2021 applicability ends at VIN 012194; confirm VIN and coolant-pump leak before repair | 4.0T TFSI V8</x:v>
       </x:c>
       <x:c r="D38" s="9" t="str">
-        <x:v>High-Pressure Fuel Pump (HPFP) Failure</x:v>
+        <x:v>2020-Early 2021 S8 Coolant-Pump Leak - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E38" s="9" t="str">
-        <x:v>Replace HPFP with updated revision. Check cam follower for wear during replacement.</x:v>
+        <x:v>Do not drive an overheating vehicle. Record coolant warning and temperature behavior, pressure-test the cooling system when safe, and locate the leak. Confirm the 2021 VIN boundary and apply TSB 2065040/4 only when the coolant pump is the identified source. Other thermostat, hose, turbo-line, heat-exchanger or internal-loss causes require separate diagnosis; do not order the former thermostat/water-pump bundle from this card.</x:v>
       </x:c>
       <x:c r="F38" s="9" t="n">
         <x:v>0</x:v>
@@ -16542,21 +19422,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="1122" hidden="0" customHeight="1">
+    <x:row r="39" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A39" s="40" t="n">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="9" t="str">
-        <x:v>audi-s3-turbo-wastegate-rattle-2015</x:v>
+        <x:v>audi-s8-cylinder-demand-active-engine-mount-failure-4-cylinder-mode</x:v>
       </x:c>
       <x:c r="C39" s="9" t="str">
-        <x:v>2015-2020 | Audi | S3 | S3</x:v>
+        <x:v>2013-2015 | Audi | S8 | 4.0 TFSI vehicles with reproducible 1000-3000 rpm vibration; diagnose J931 before mount replacement | 4.0T TFSI V8</x:v>
       </x:c>
       <x:c r="D39" s="9" t="str">
-        <x:v>IS20 Turbocharger Wastegate Rattle and Actuator Failure</x:v>
+        <x:v>2013-2015 S8 COD Vibration with J931 Basic-Setting Fault - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E39" s="9" t="str">
-        <x:v>EARLY STAGE (rattle only, no power loss): Audi TSB 2027585/3 prescribes installation of a metal retaining clip (part 06J145220A) to tighten wastegate arm play ($200-$400 if under warranty, $500-$800 out of pocket). UPGRADED DIVERTER VALVE: Replace with revision 'D' diverter valve to improve boost control. SEVERE (actuator failure or power loss): Replace complete IS20 turbocharger ($2,500-$4,000 installed). The IS20 actuator is integrated and not serviceable separately. Upgraded IS38 turbo swap ($3,500-$5,000) from Golf R is a popular option if replacing turbo anyway. PREVENTION: Avoid short trips that don't fully heat the turbo. Change oil every 5,000 miles with high-quality synthetic.</x:v>
+        <x:v>Reproduce the vibration under Audi’s specified driving conditions and scan J931. If the bulletin applies, verify J931 software, perform the required SVM update and basic settings, align the exhaust without tension, repeat basic settings and follow the referenced diagnosis if vibration remains. Inspect mount hardware only after the software, calibration and exhaust path. Do not disable cylinder-on-demand or replace both mounts from the former card.</x:v>
       </x:c>
       <x:c r="F39" s="9" t="n">
         <x:v>0</x:v>
@@ -16565,44 +19445,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="594" hidden="0" customHeight="1">
+    <x:row r="40" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A40" s="40" t="n">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="9" t="str">
-        <x:v>audi-s3-water-pump-thermostat-2015</x:v>
+        <x:v>audi-s8-d2-4-2-v8-timing-belt-tensioner-service</x:v>
       </x:c>
       <x:c r="C40" s="9" t="str">
-        <x:v>2020-2024 | Audi | S3 | 2.0L TFSI</x:v>
+        <x:v>2001-2003 | Audi | S8 | 4.2L 40V V8 (AYS)</x:v>
       </x:c>
       <x:c r="D40" s="9" t="str">
-        <x:v>2020/2022-2024 Audi S3 2.0 TFSI Coolant-Pump Leak Diagnosis</x:v>
+        <x:v>D2 4.2 V8 Timing Belt and Tensioner Service (Interference Engine)</x:v>
       </x:c>
       <x:c r="E40" s="9" t="str">
-        <x:v>Document the suspected leak, clean and dry all traces, fill the cooling system to the correct level and reassess after driving a few miles. If no fresh leak appears, continue observing without replacing parts. If leakage recurs, replace only the component causing the damage under the exact VIN, engine and part criteria. Outside applicable warranty, Audi states the bulletin is informational.</x:v>
+        <x:v>Replace the timing belt as a complete kit — belt, tensioner, idler/guide rollers, and water pump — at or before Audi's interval (and by age regardless of mileage). Use genuine/OE-quality components and set cam/crank timing precisely with the correct locking tools; this is a front-of-engine ('service position') job. Inspect the exhaust-side chain tensioners while in there. Always confirm timing-belt history (with receipts) before buying a D2 S8; if unknown, do it immediately.</x:v>
       </x:c>
       <x:c r="F40" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G40" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="250.8000030517578" hidden="0" customHeight="1">
+    <x:row r="41" ht="844.7999877929688" hidden="0" customHeight="1">
       <x:c r="A41" s="40" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="9" t="str">
-        <x:v>audi-s4-b5-timing-chain-2000</x:v>
+        <x:v>audi-s8-direct-injection-carbon-buildup-intake-valves</x:v>
       </x:c>
       <x:c r="C41" s="9" t="str">
-        <x:v>2000-2002 | Audi | S4</x:v>
+        <x:v>2013-2018 | Audi | S8 | 4.0T TFSI V8 (CTFA/CGTA/CWUC)</x:v>
       </x:c>
       <x:c r="D41" s="9" t="str">
-        <x:v>Driver Airbag Inflator May Deploy Improperly (Recall 21V470 / 69CJ)</x:v>
+        <x:v>Direct-Injection Carbon Buildup on Intake Valves (Misfires / Rough Idle)</x:v>
       </x:c>
       <x:c r="E41" s="9" t="str">
-        <x:v>Check the VIN with Audi or NHTSA. Audi dealers replace the driver frontal-airbag inflator with an alternative inflator free of charge under campaign 69CJ.</x:v>
+        <x:v>Confirm via borescope of the intake valves (and rule out coils/plugs/PCV first). The accepted repair is walnut-shell blasting: remove the intake manifold and media-blast the carbon off the valves and ports with crushed walnut shells, then reinstall with new intake gaskets. Replace spark plugs and inspect coils while the manifold is off. Preventively, keep up with oil changes, fix any PCV/oil-burning source, and consider periodic cleaning every ~40,000-60,000 miles. Catch-can solutions reduce future accumulation.</x:v>
       </x:c>
       <x:c r="F41" s="9" t="n">
         <x:v>0</x:v>
@@ -16611,21 +19491,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="237.60000610351562" hidden="0" customHeight="1">
+    <x:row r="42" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A42" s="40" t="n">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="9" t="str">
-        <x:v>audi-s4-b5-turbo-failure-2000</x:v>
+        <x:v>audi-s8-front-suspension-control-arm-bushing-sway-bar-link-wear</x:v>
       </x:c>
       <x:c r="C42" s="9" t="str">
-        <x:v>2003-2004 | Audi | S4</x:v>
+        <x:v>2020-2021 | Audi | S8 | 2021 applicability through VIN 028090; localize noise acoustically before parts | 4.0T TFSI V8 mild-hybrid</x:v>
       </x:c>
       <x:c r="D42" s="9" t="str">
-        <x:v>Xenon Headlamp Reflector Coating Can Reduce Light Output (Recall 05V096)</x:v>
+        <x:v>2020-Early 2021 S8 Front Lower Guide-Link Hydro-Bushing Noise - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E42" s="9" t="str">
-        <x:v>Verify VIN eligibility and campaign completion with Audi. Dealers replace both xenon headlamp reflectors free of charge under recall 05V096.</x:v>
+        <x:v>Confirm the VIN boundary, reproduce the noise and localize it with acoustic diagnostic equipment. Inspect the lower guide-link hydro-bushings and surrounding joints. If the hydro-bushing is confirmed, follow Audi’s paired replacement procedure; complete guide links may be required when prior pressing or rework prevents the specified repair. Align the vehicle as required. Do not order a ten-arm kit or sway-bar links from the former card.</x:v>
       </x:c>
       <x:c r="F42" s="9" t="n">
         <x:v>0</x:v>
@@ -16634,21 +19514,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="303.6000061035156" hidden="0" customHeight="1">
+    <x:row r="43" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A43" s="40" t="n">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="9" t="str">
-        <x:v>audi-s4-b6-timing-chain-2004</x:v>
+        <x:v>audi-s8-high-pressure-fuel-pump-injector-internal-leak-causing-hard</x:v>
       </x:c>
       <x:c r="C43" s="9" t="str">
-        <x:v>2005-2009 | Audi | S4</x:v>
+        <x:v>2013-2018 | Audi | S8 | 4.0 TFSI; diagnosis requires ODIS values, software check and pressure-hold testing | 4.0T TFSI V8</x:v>
       </x:c>
       <x:c r="D43" s="9" t="str">
-        <x:v>Passenger Airbag Inflator Can Rupture (Recall 18V427 / 69R7)</x:v>
+        <x:v>2013-2018 S8 Warm-Soak Long-Crank or No-Start - Fuel Diagnosis Required</x:v>
       </x:c>
       <x:c r="E43" s="9" t="str">
-        <x:v>Check VIN eligibility because body style and original registration history affect scope. Audi dealers replace the passenger frontal-airbag remedy part free of charge under campaign 69R7.</x:v>
+        <x:v>Have the dealer read DTCs and ODIS fuel-in-oil value, verify ECM software and perform Audi’s high- and low-pressure holding tests. If high-pressure behavior is abnormal, borescope the combustion chamber to identify a leaking injector. If low-side pressure builds correctly but drops more than 1.5 bar in the first 15 minutes, Audi says at least one HPFP may be leaking and directs replacement of both pumps plus an oil change. Select no pump or injector until the test identifies the path.</x:v>
       </x:c>
       <x:c r="F43" s="9" t="n">
         <x:v>0</x:v>
@@ -16657,21 +19537,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="356.3999938964844" hidden="0" customHeight="1">
+    <x:row r="44" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A44" s="40" t="n">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="9" t="str">
-        <x:v>audi-s4-carbon-buildup-2010</x:v>
+        <x:v>audi-s8-mmi-upper-display-backup-camera-black-screen</x:v>
       </x:c>
       <x:c r="C44" s="9" t="str">
-        <x:v>2011-2012 | Audi | S4 | 3.0 TFSI</x:v>
+        <x:v>2020-2026 | Audi | S8 | VIN-specific NHTSA 25V900 / Audi 90TV; verify open recall | 4.0T TFSI V8 mild-hybrid</x:v>
       </x:c>
       <x:c r="D44" s="9" t="str">
-        <x:v>Fuel Rail or Seal Leak Creates Fire Risk (Recall 15V019 / 24AP)</x:v>
+        <x:v>2020-2026 S8 Rearview/Top-View Camera Image May Not Display - Recall 25V900</x:v>
       </x:c>
       <x:c r="E44" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel rails and corresponding seals free of charge under campaign 24AP. If fuel odor or leakage is present, stop driving and arrange immediate inspection.</x:v>
+        <x:v>Check the VIN in Audi’s recall/service-campaign lookup and schedule the free 90TV software remedy if open. Use extra care when reversing until repaired and visually check the area around the vehicle. A completely dead or rebooting MMI display, missing instrument-cluster data, wiring fault or hardware failure requires separate diagnosis and must not be attributed to this recall without VIN and symptom confirmation.</x:v>
       </x:c>
       <x:c r="F44" s="9" t="n">
         <x:v>0</x:v>
@@ -16680,21 +19560,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="224.39999389648438" hidden="0" customHeight="1">
+    <x:row r="45" ht="792" hidden="0" customHeight="1">
       <x:c r="A45" s="40" t="n">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="9" t="str">
-        <x:v>audi-s4-supercharger-nose-2010</x:v>
+        <x:v>audi-s8-oil-consumption-2013</x:v>
       </x:c>
       <x:c r="C45" s="9" t="str">
-        <x:v>2013-2015 | Audi | S4</x:v>
+        <x:v>2020-2023 | Audi | S8 | EA825 4.0L; confirm VIN, engine and measured consumption under Audi procedure | 4.0T TFSI V8 mild-hybrid (EA825)</x:v>
       </x:c>
       <x:c r="D45" s="9" t="str">
-        <x:v>Airbag-Control Software May Miss Front-Airbag Deployment After a Second Impact (Recall 14V667 / 69K5)</x:v>
+        <x:v>2020-2023 S8 High Oil Consumption and Updated Piston Rings - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E45" s="9" t="str">
-        <x:v>Check VIN eligibility and completion history. Audi dealers update the airbag control-unit software free of charge under campaign 69K5.</x:v>
+        <x:v>Document oil-level warnings, mileage, top-up quantity, leaks and oil specification, then have an Audi dealer perform the authorized oil-consumption measurement. Repair is justified only when the measured result exceeds the applicable owner-manual limit and other leakage or operating causes are excluded. If TSB 2071114 applies, follow its VIN/engine-specific piston, ring and connecting-rod procedure. Do not change oil viscosity or authorize internal-engine work solely from the former card.</x:v>
       </x:c>
       <x:c r="F45" s="9" t="n">
         <x:v>0</x:v>
@@ -16703,44 +19583,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="198" hidden="0" customHeight="1">
+    <x:row r="46" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A46" s="40" t="n">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="9" t="str">
-        <x:v>audi-s4-thermostat-2010</x:v>
+        <x:v>audi-s8-pcv-oil-separator-failure-excessive-crankcase-vacuum</x:v>
       </x:c>
       <x:c r="C46" s="9" t="str">
-        <x:v>2010-2025 | Audi | S4 | 3.0T</x:v>
+        <x:v>2013-2016 | Audi | S8 | 4.0 TFSI; confirm warm-idle sound and filler-cap response before oil-separator replacement | 4.0T TFSI V8</x:v>
       </x:c>
       <x:c r="D46" s="9" t="str">
-        <x:v>Thermostat Housing Failure and Coolant Leak</x:v>
+        <x:v>2013-2016 S8 Warm-Idle Whistle from Crankcase Breather Leak - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E46" s="9" t="str">
-        <x:v>Replace thermostat housing assembly with updated part. Use OEM or quality aftermarket housing with metal reinforcement.</x:v>
+        <x:v>Compare the sound with Audi’s reference condition and check whether opening the oil filler cap changes it. Read P2279/P0507 and rule out other intake leaks. When the sound matches and is affected by the filler-cap check, follow Audi’s oil-separator breather replacement procedure and renew required seals/consumables by VIN. Do not diagnose by oil-cap feel alone or order the former five-item parts list.</x:v>
       </x:c>
       <x:c r="F46" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G46" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="963.5999755859375" hidden="0" customHeight="1">
+    <x:row r="47" ht="594" hidden="0" customHeight="1">
       <x:c r="A47" s="40" t="n">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="9" t="str">
-        <x:v>audi-s5-b9-water-pump-2018</x:v>
+        <x:v>audi-s8-porous-high-pressure-fuel-supply-line-recall-nhtsa-19v057000</x:v>
       </x:c>
       <x:c r="C47" s="9" t="str">
-        <x:v>2018-2018 | Audi | S5 | 3.0L V6 TFSI EA839</x:v>
+        <x:v>2013-2016 | Audi | S8 | VIN-specific NHTSA 19V057 / Audi 20BM; verify open recall | 4.0T TFSI V8</x:v>
       </x:c>
       <x:c r="D47" s="9" t="str">
-        <x:v>2018 S5 3.0L Mechanical Coolant-Pump Fault P000000/33688 - Diagnosis Required</x:v>
+        <x:v>2013-2016 S8 Porous Fuel-Pump Supply Line / Fire Risk - Recall 19V057</x:v>
       </x:c>
       <x:c r="E47" s="9" t="str">
-        <x:v>Follow the bulletin in order. Verify coolant level; if low, inspect the cooling system for a leak and repair only the identified source or top up per Audi instructions when no leak is found. Check the ECM software level and apply the specified SVM update only when required. If the concern returns or software is current, test vacuum at N649 and inspect the solenoid and hoses. If the vacuum system works, apply vacuum to the pump hose and verify that the pump sleeve clicks; replace the mechanical coolant pump only when the sleeve does not operate. Use current Audi workshop and parts information.</x:v>
+        <x:v>Check the VIN for open recall 20BM and contact an Audi dealer without delay. The free remedy installs a fuel-pressure damper in the low-pressure fuel supply inside the tank. If fuel odor or visible leakage is present, avoid ignition sources, do not continue driving, and arrange dealer inspection/towing as appropriate. Do not buy a retail line or damper from the former card.</x:v>
       </x:c>
       <x:c r="F47" s="9" t="n">
         <x:v>0</x:v>
@@ -16749,21 +19629,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="184.8000030517578" hidden="0" customHeight="1">
+    <x:row r="48" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A48" s="40" t="n">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="9" t="str">
-        <x:v>audi-s5-carbon-buildup-2008</x:v>
+        <x:v>audi-s8-torque-converter-2013</x:v>
       </x:c>
       <x:c r="C48" s="9" t="str">
-        <x:v>2008-2025 | Audi | S5</x:v>
+        <x:v>2013-2024 | Audi | S8</x:v>
       </x:c>
       <x:c r="D48" s="9" t="str">
-        <x:v>Direct Injection Carbon Buildup</x:v>
+        <x:v>ZF 8-Speed Torque Converter and Valve Body Issues</x:v>
       </x:c>
       <x:c r="E48" s="9" t="str">
-        <x:v>Walnut blast intake valves every 40,000-60,000 miles. Install oil catch can to reduce oil vapor reaching valves.</x:v>
+        <x:v>Replace torque converter and service valve body. Full ZF fluid and filter change every 50,000 miles extends transmission life.</x:v>
       </x:c>
       <x:c r="F48" s="9" t="n">
         <x:v>0</x:v>
@@ -16772,44 +19652,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="49" ht="712.7999877929688" hidden="0" customHeight="1">
       <x:c r="A49" s="40" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" s="9" t="str">
-        <x:v>audi-s5-crankshaft-pulley-2010</x:v>
+        <x:v>audi-s8-turbo-oil-strainer-2013</x:v>
       </x:c>
       <x:c r="C49" s="9" t="str">
-        <x:v>2010-2017 | Audi | S5 | Premium Plus, Prestige | 3.0T</x:v>
+        <x:v>2013-2017 | Audi | S8 | VIN-specific NHTSA 22V178 / Audi 21H7; verify open recall | 4.0T TFSI V8</x:v>
       </x:c>
       <x:c r="D49" s="9" t="str">
-        <x:v>Crankshaft Pulley (Harmonic Balancer) Failure (3.0T)</x:v>
+        <x:v>2013-2017 S8 Blocked Turbocharger Oil Strainer / Stall Risk - Recall 22V178</x:v>
       </x:c>
       <x:c r="E49" s="9" t="str">
-        <x:v>Replace crankshaft pulley/harmonic balancer with LATEST REVISION (revision F or later) part ($300-$600 for part, $800-$1,700 with labor). This is NOT a DIY-friendly repair—requires specialized holding tools and precise torque. If belts are damaged, replace serpentine belt and tensioner ($200-$400 additional). INSPECT: Check for collateral damage to supercharger snout, idler pulleys, and timing. If timing was affected, expect $3,000-$5,000 additional repair. PREVENTIVE: Inspect pulley for wobble at every oil change. Consider preemptive replacement at 80,000 miles on 2010-2013 models.</x:v>
+        <x:v>Check the VIN for open recall 21H7 and schedule the free Audi dealer remedy, which replaces the oil strainer and performs an oil change. If EPC, MIL or oil warning lights appear with unusual turbo noise, extended cranking, rough idle, loss of power or stalling, stop safely and arrange diagnosis. Turbo damage, warranty eligibility and any additional repair must be assessed by VIN and inspection; do not buy the former retail strainer.</x:v>
       </x:c>
       <x:c r="F49" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G49" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="844.7999877929688" hidden="0" customHeight="1">
+    <x:row r="50" ht="950.4000244140625" hidden="0" customHeight="1">
       <x:c r="A50" s="40" t="n">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B50" s="9" t="str">
-        <x:v>audi-s5-pcv-valve-failure-2010</x:v>
+        <x:v>audi-s8-water-to-air-intercooler-internal-coolant-leak</x:v>
       </x:c>
       <x:c r="C50" s="9" t="str">
-        <x:v>2010-2017 | Audi | S5 | 3.0L supercharged V6</x:v>
+        <x:v>2013-2018 | Audi | S8 | 4.0T TFSI V8 (CTFA/CGTA/CWUC)</x:v>
       </x:c>
       <x:c r="D50" s="9" t="str">
-        <x:v>2010-2017 S5 3.0L Crankcase-Breather P052E00 - Body/Year Diagnosis</x:v>
+        <x:v>Water-to-Air Intercooler Internal Coolant Leak (Coolant into Intake)</x:v>
       </x:c>
       <x:c r="E50" s="9" t="str">
-        <x:v>Verify the body style, model year and P052E00 condition first. For the applicable membrane branch, use the specified hand-vacuum test, then inspect the membrane and metal plates after compressor/intake-manifold removal; replace only the faulted membrane/plate repair kit or crankcase breather per current Audi instructions. If testing identifies the elbow branch, replace the elbow and hose clip as directed by TSB 2060259/1. Do not assume that both branches or unrelated cooling parts require replacement.</x:v>
+        <x:v>Confirm the source: pressure-test the cooling system and inspect the charge piping/intercooler outlet for coolant residue; scope for white smoke and coolant on the intake side rather than an external leak. Replace the water-to-air intercooler/charge-air cooler unit (genuine OEM core). Because access requires removing intake components in the valley, it is standard practice to also replace the turbo oil strainer, coolant valves, and PCV/oil separator while in there. Refill and bleed the cooling system per procedure. This is a high-difficulty job typically done by a specialist or dealer.</x:v>
       </x:c>
       <x:c r="F50" s="9" t="n">
         <x:v>0</x:v>
@@ -16818,21 +19698,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="51" ht="475.20001220703125" hidden="0" customHeight="1">
       <x:c r="A51" s="40" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B51" s="9" t="str">
-        <x:v>audi-s5-supercharger-2008</x:v>
+        <x:v>audi-sq2-ea888-2-0-tfsi-coolant-leak-from-water-pump-thermostat-housi</x:v>
       </x:c>
       <x:c r="C51" s="9" t="str">
-        <x:v>2008-2025 | Audi | S5 | 3.0T</x:v>
+        <x:v>2019-2024 | Audi | SQ2 | 2.0 TFSI quattro | EA888 2.0 TFSI Gen3</x:v>
       </x:c>
       <x:c r="D51" s="9" t="str">
-        <x:v>3.0T Supercharger Intercooler Pump Failure</x:v>
+        <x:v>EA888 2.0 TFSI coolant leak from water pump / thermostat housing</x:v>
       </x:c>
       <x:c r="E51" s="9" t="str">
-        <x:v>Replace intercooler coolant pump. Check intercooler lines for leaks and flush the circuit during replacement.</x:v>
+        <x:v>Replace the failed water pump / thermostat housing assembly, ideally with the latest revised, more heat-resistant unit; many shops fit an upgraded repair kit and a new gasket. Catch it early by watching for slowly dropping coolant level and a faint sweet smell. Combine with a coolant flush and refill.</x:v>
       </x:c>
       <x:c r="F51" s="9" t="n">
         <x:v>0</x:v>
@@ -16841,21 +19721,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="52" ht="396" hidden="0" customHeight="1">
       <x:c r="A52" s="40" t="n">
         <x:v>51</x:v>
       </x:c>
       <x:c r="B52" s="9" t="str">
-        <x:v>audi-s5-thermostat-2008</x:v>
+        <x:v>audi-sq2-electro-mechanical-parking-brake-brake-pedal-weld-recalls</x:v>
       </x:c>
       <x:c r="C52" s="9" t="str">
-        <x:v>2008-2025 | Audi | S5 | 3.0T</x:v>
+        <x:v>2019-2020 | Audi | SQ2</x:v>
       </x:c>
       <x:c r="D52" s="9" t="str">
-        <x:v>Thermostat and Water Pump Assembly Failure</x:v>
+        <x:v>Electro-mechanical parking brake and brake-pedal weld recalls (early build)</x:v>
       </x:c>
       <x:c r="E52" s="9" t="str">
-        <x:v>Replace thermostat/water pump assembly. Upgrade to revised housing if available.</x:v>
+        <x:v>These are recall items — have the VIN checked against the Audi/DVSA recall database and any open campaign rectified free of charge at a dealer. Report any abnormal parking-brake behaviour or a soft/abnormal brake pedal immediately.</x:v>
       </x:c>
       <x:c r="F52" s="9" t="n">
         <x:v>0</x:v>
@@ -16864,21 +19744,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="53" ht="475.20001220703125" hidden="0" customHeight="1">
       <x:c r="A53" s="40" t="n">
         <x:v>52</x:v>
       </x:c>
       <x:c r="B53" s="9" t="str">
-        <x:v>audi-s6-air-suspension-2013</x:v>
+        <x:v>audi-sq2-internal-fuse-box-wiring-harness-can-work-loose-causing-sudd</x:v>
       </x:c>
       <x:c r="C53" s="9" t="str">
-        <x:v>2013-2013 | Audi | S6 | 4.0T</x:v>
+        <x:v>2022-2023 | Audi | SQ2 | 2.0 TFSI</x:v>
       </x:c>
       <x:c r="D53" s="9" t="str">
-        <x:v>2013 Audi S6 Air-Suspension Compressor or Relay Fault - Diagnosis Required</x:v>
+        <x:v>2022-2023 Audi SQ2 Interior Fuse-Carrier Recall GAI-3692</x:v>
       </x:c>
       <x:c r="E53" s="9" t="str">
-        <x:v>Have an Audi-qualified technician test the air-suspension compressor and inspect relay J403. Audi directs replacement of both the compressor and relay when the relay has severe contact erosion or an overheated strand; when the compressor sounds normal and the relay has only minor contact marks, replace the relay only. A sagging corner or leak-down condition requires separate leak localization before any strut is replaced. Do not order the former strut or compressor recommendations from this card.</x:v>
+        <x:v>Check the VIN and open-campaign status with an authorised Audi dealer in the vehicle’s market. The campaign remedy is dealer inspection and correction of the fuse-carrier power connection. Do not replace a fuse box or wiring harness solely from a warning lamp or this model-year summary.</x:v>
       </x:c>
       <x:c r="F53" s="9" t="n">
         <x:v>0</x:v>
@@ -16887,21 +19767,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="1359.5999755859375" hidden="0" customHeight="1">
+    <x:row r="54" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A54" s="40" t="n">
         <x:v>53</x:v>
       </x:c>
       <x:c r="B54" s="9" t="str">
-        <x:v>audi-s6-c7-carbon-buildup-2013</x:v>
+        <x:v>audi-sq2-mmi-infotainment-freezing-rebooting-lost-settings</x:v>
       </x:c>
       <x:c r="C54" s="9" t="str">
-        <x:v>2013-2018 | Audi | S6 | 4.0T</x:v>
+        <x:v>2019-2024 | Audi | SQ2</x:v>
       </x:c>
       <x:c r="D54" s="9" t="str">
-        <x:v>4.0T Carbon Buildup on Intake Valves</x:v>
+        <x:v>MMI infotainment freezing, rebooting and lost settings</x:v>
       </x:c>
       <x:c r="E54" s="9" t="str">
-        <x:v>Confirm carbon buildup by scanning for misfire faults (commonly random/multiple or cylinder-specific misfires), reviewing fuel trims, and inspecting the intake valves with a borescope after removing the intake manifold or accessing the ports. The proper repair is an intake valve carbon cleaning, typically walnut shell blasting each intake port with the valves closed, then replacing intake manifold gaskets, injector seals/O-rings or any disturbed PCV-related seals as needed and clearing/adapting the ECU afterward. If buildup is severe or returns quickly, inspect the PCV/oil separator system and crankcase ventilation hoses for excessive oil carryover. Independent shops typically charge about $800-$1,500 for a full walnut blast service on the 4.0T, while dealer pricing can run roughly $1,500-$2,500 depending on labor and gasket/seal replacement.</x:v>
+        <x:v>A forced MMI restart (press and hold the on/off or volume control ~10 seconds until it reboots) clears many transient faults. Persistent issues are usually resolved by a dealer software/firmware update; check for any applicable MMI update campaigns. Only in rare cases is the MMI head unit itself replaced.</x:v>
       </x:c>
       <x:c r="F54" s="9" t="n">
         <x:v>0</x:v>
@@ -16910,21 +19790,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="55" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A55" s="40" t="n">
         <x:v>54</x:v>
       </x:c>
       <x:c r="B55" s="9" t="str">
-        <x:v>audi-s6-carbon-buildup-2013</x:v>
+        <x:v>audi-sq2-pcv-crankcase-ventilation-valve-diaphragm-failure-causing-ro</x:v>
       </x:c>
       <x:c r="C55" s="9" t="str">
-        <x:v>2013-2024 | Audi | S6 | 4.0T</x:v>
+        <x:v>2019-2024 | Audi | SQ2 | EA888 2.0 TFSI Gen3</x:v>
       </x:c>
       <x:c r="D55" s="9" t="str">
-        <x:v>4.0T Direct Injection Carbon Buildup</x:v>
+        <x:v>PCV / crankcase ventilation valve diaphragm failure causing rough idle and lean-running codes</x:v>
       </x:c>
       <x:c r="E55" s="9" t="str">
-        <x:v>Walnut blast all eight intake runners. Dual-injection models (2019+) are less affected.</x:v>
+        <x:v>Replace the PCV valve (or the valve-cover assembly that integrates it) with the latest revised part; some owners fit a catch-can to reduce recurrence. A quick field test — briefly covering the bleeder hole on the cap to see if idle stabilises or whistling stops — helps confirm before replacement.</x:v>
       </x:c>
       <x:c r="F55" s="9" t="n">
         <x:v>0</x:v>
@@ -16933,21 +19813,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="462" hidden="0" customHeight="1">
+    <x:row r="56" ht="752.4000244140625" hidden="0" customHeight="1">
       <x:c r="A56" s="40" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="B56" s="9" t="str">
-        <x:v>audi-s6-rearview-camera-image-failure-from-software-error</x:v>
+        <x:v>audi-sq2-s-tronic-7-speed-wet-clutch-transmission-jerky-low-speed-shi</x:v>
       </x:c>
       <x:c r="C56" s="9" t="str">
-        <x:v>2020-2025 | Audi | S6</x:v>
+        <x:v>2019-2024 | Audi | SQ2 | 7-speed S tronic | DQ381 / 0GC 7-speed wet-clutch S tronic</x:v>
       </x:c>
       <x:c r="D56" s="9" t="str">
-        <x:v>2020-2025 Audi S6 Rearview Camera Software Recall 25V900 / 90TV</x:v>
+        <x:v>S tronic (DQ381) 7-speed wet-clutch transmission: jerky low-speed shifts, hesitation and limp mode</x:v>
       </x:c>
       <x:c r="E56" s="9" t="str">
-        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install the more robust driver-assistance software update free of charge. Until repaired, use extra caution when reversing and do not treat a restart or temporary image recovery as completion of the recall.</x:v>
+        <x:v>First step is a proper DSG fluid-and-filter service (the wet-clutch unit needs periodic transmission oil changes — many owners do it around 40k miles even though intervals can be longer). Have the TCU scanned for stored codes; sensor or mechatronic valve replacement and re-coding/adaptation resolves many cases, while severe cases need a full mechatronic unit or clutch-pack replacement. Insist on a software/adaptation update at the dealer for driveability complaints.</x:v>
       </x:c>
       <x:c r="F56" s="9" t="n">
         <x:v>0</x:v>
@@ -16956,21 +19836,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="57" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A57" s="40" t="n">
         <x:v>56</x:v>
       </x:c>
       <x:c r="B57" s="9" t="str">
-        <x:v>audi-s6-takata-passenger-airbag-inflator-recall</x:v>
+        <x:v>audi-sq5-air-suspension-2018</x:v>
       </x:c>
       <x:c r="C57" s="9" t="str">
-        <x:v>2007-2011 | Audi | S6</x:v>
+        <x:v>2018-2025 | Audi | SQ5</x:v>
       </x:c>
       <x:c r="D57" s="9" t="str">
-        <x:v>2007-2011 Audi S6 Takata Passenger-Airbag Recall 18V427 / 69R7</x:v>
+        <x:v>Air-Suspension Warning with C1260F0 or U112100 Communication Fault</x:v>
       </x:c>
       <x:c r="E57" s="9" t="str">
-        <x:v>Check the VIN for recall 18V427/69R7 and arrange the free final passenger-frontal-airbag replacement with an Audi dealer. Do not use an airbag warning light to determine recall eligibility; Audi states that the warning light is unrelated to this inflator defect.</x:v>
+        <x:v>Inspect the wiring and connector contacts between J775 and J1135 first. If no wiring fault is found, clear a first passive or sporadic fault and release the vehicle. Replace J1135 for an active or static fault, or when the same passive or sporadic fault returns a second time, following Audi workshop information and VIN-specific ETKA data.</x:v>
       </x:c>
       <x:c r="F57" s="9" t="n">
         <x:v>0</x:v>
@@ -16979,20 +19859,22 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="58" ht="924" hidden="0" customHeight="1">
       <x:c r="A58" s="40" t="n">
         <x:v>57</x:v>
       </x:c>
       <x:c r="B58" s="9" t="str">
-        <x:v>audi-s6-transmission-valve-body-2002</x:v>
+        <x:v>audi-sq5-carbon-buildup-2014</x:v>
       </x:c>
       <x:c r="C58" s="9" t="str">
-        <x:v>2002-2004 | Audi | S6</x:v>
+        <x:v>2014-2025 | Audi | SQ5 | 3.0T Supercharged, 3.0T</x:v>
       </x:c>
       <x:c r="D58" s="9" t="str">
-        <x:v>ZF 5HP24 Tiptronic Transmission Valve Body Failure</x:v>
-      </x:c>
-      <x:c r="E58" s="9" t="str"/>
+        <x:v>Fuel-Quality or Deposit-Related Rough Running and Misfire Diagnosis</x:v>
+      </x:c>
+      <x:c r="E58" s="9" t="str">
+        <x:v>Confirm fuel quality, symptoms and stored DTCs before replacing or cleaning components. If contaminated gasoline is suspected, advise changing the fuel source; if low detergent quality is suspected, Audi recommends Top Tier detergent gasoline. Continue workshop diagnosis if symptoms persist. On 2018-2025 EA839 SQ5 models, do not recommend unapproved cleaners or additives; follow the owner manual and use only Audi-approved petrol additives. Do not prescribe routine walnut blasting, a catch can or chemical cleaning from this record.</x:v>
+      </x:c>
       <x:c r="F58" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -17000,21 +19882,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="59" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A59" s="40" t="n">
         <x:v>58</x:v>
       </x:c>
       <x:c r="B59" s="9" t="str">
-        <x:v>audi-s6-turbo-coolant-2013</x:v>
+        <x:v>audi-sq5-pcv-valve-2014</x:v>
       </x:c>
       <x:c r="C59" s="9" t="str">
-        <x:v>2013-2013 | Audi | S6 | 4.0T</x:v>
+        <x:v>2014-2017 | Audi | SQ5 | 3.0T Supercharged</x:v>
       </x:c>
       <x:c r="D59" s="9" t="str">
-        <x:v>2013 Audi S6 Turbocharger Coolant-Pipe Seepage - Diagnosis Required</x:v>
+        <x:v>P052E00 Crankcase-Breather Membrane or Elbow Fault</x:v>
       </x:c>
       <x:c r="E59" s="9" t="str">
-        <x:v>Confirm the leak source and VIN applicability before ordering parts. For the TSB condition, Audi specifies replacing the coolant feed and return pipes on both cylinder banks, replacing the disturbed oil-feed-pipe O-rings, then refilling and bleeding the cooling system. Service Action 21F7 was VIN-specific and expired in 2019, so current coverage must not be assumed. Do not order the former single pipe or alleged silicone-line kit from this card.</x:v>
+        <x:v>Use Audi hand-vacuum test to distinguish a membrane leak from an elbow fault. If indicated, remove the compressor or intake manifold and inspect the membrane and the breather two metal plates. Use repair kit 06E103772H only for a confirmed membrane or plate fault. For a confirmed elbow fault, replace elbow 06E103402 and spring clip N10769401 rather than automatically replacing the complete breather. Verify current part data in ETKA before ordering.</x:v>
       </x:c>
       <x:c r="F59" s="9" t="n">
         <x:v>0</x:v>
@@ -17023,21 +19905,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="290.3999938964844" hidden="0" customHeight="1">
+    <x:row r="60" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A60" s="40" t="n">
         <x:v>59</x:v>
       </x:c>
       <x:c r="B60" s="9" t="str">
-        <x:v>audi-s7-air-suspension-2012</x:v>
+        <x:v>audi-sq5-supercharger-2014</x:v>
       </x:c>
       <x:c r="C60" s="9" t="str">
-        <x:v>2020-2021 | Audi | S7</x:v>
+        <x:v>2014-2018 | Audi | SQ5 | 3.0T</x:v>
       </x:c>
       <x:c r="D60" s="9" t="str">
-        <x:v>Rear-Axle Lock Nut and Alignment Recall Follow-Up (21V295 / 22V034)</x:v>
+        <x:v>3.0T Supercharger Bearing and Intercooler Pump Failure</x:v>
       </x:c>
       <x:c r="E60" s="9" t="str">
-        <x:v>Check the VIN for both campaigns 42L1 and 42L5. Audi dealers replace affected nuts and bolts, inspect and adjust rear alignment, and replace qualifying unevenly worn tires free of charge.</x:v>
+        <x:v>Replace supercharger nose bearing kit. Replace intercooler pump if failing. Service supercharger belt tension.</x:v>
       </x:c>
       <x:c r="F60" s="9" t="n">
         <x:v>0</x:v>
@@ -17046,21 +19928,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="237.60000610351562" hidden="0" customHeight="1">
+    <x:row r="61" ht="844.7999877929688" hidden="0" customHeight="1">
       <x:c r="A61" s="40" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="B61" s="9" t="str">
-        <x:v>audi-s7-biturbo-coolant-2012</x:v>
+        <x:v>audi-sq5-supercharger-oil-leak-2014</x:v>
       </x:c>
       <x:c r="C61" s="9" t="str">
-        <x:v>2013-2014 | Audi | S7 | 4.0 TFSI</x:v>
+        <x:v>2014-2017 | Audi | SQ5 | Premium Plus, Prestige | 3.0T Supercharged, 3.0T</x:v>
       </x:c>
       <x:c r="D61" s="9" t="str">
-        <x:v>4.0L Fuel Line Can Leak and Create a Fire Risk (Recall 13V450 / 20U6)</x:v>
+        <x:v>Supercharger Seal and Gasket Oil Leaks (3.0T)</x:v>
       </x:c>
       <x:c r="E61" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel line free of charge under campaign 20U6/L8. Stop driving if fuel odor or leakage is present.</x:v>
+        <x:v>JHM Motorsports sells a complete supercharger replacement seal and gasket kit for the Eaton unit in the 3.0T. Replacing all seals at once is recommended since the supercharger must be removed for access. Nose cone seal, rotor shaft seals, and manifold gaskets should all be replaced together ($300-$500 in parts, $600-$1,200 labor). While the supercharger is off, also replace the PCV valve and perform carbon cleaning. For valve cover gasket leaks (separate issue), budget $400-$800 parts and labor. Monitor oil level weekly if leaks are present.</x:v>
       </x:c>
       <x:c r="F61" s="9" t="n">
         <x:v>0</x:v>
@@ -17069,21 +19951,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" ht="264" hidden="0" customHeight="1">
+    <x:row r="62" ht="1122" hidden="0" customHeight="1">
       <x:c r="A62" s="40" t="n">
         <x:v>61</x:v>
       </x:c>
       <x:c r="B62" s="9" t="str">
-        <x:v>audi-s7-carbon-buildup-4.0t-2012</x:v>
+        <x:v>audi-sq5-water-pump-2018</x:v>
       </x:c>
       <x:c r="C62" s="9" t="str">
-        <x:v>2021-2021 | Audi | S7</x:v>
+        <x:v>2018-2024 | Audi | SQ5 | 3.0T</x:v>
       </x:c>
       <x:c r="D62" s="9" t="str">
-        <x:v>Rear Seat-Belt Retractor Can Release a Child Restraint Early (Recall 21V606 / 69CS)</x:v>
+        <x:v>Mechanical Coolant-Pump Leak with Possible N649 Vacuum-System Contamination</x:v>
       </x:c>
       <x:c r="E62" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers inspect and replace the affected middle-rear seat-belt assembly as necessary free of charge under campaign 69CS.</x:v>
+        <x:v>Confirm the complaint and exact vehicle criteria first. Inspect the vacuum line and N649 for coolant, then clean and dry suspected leakage, fill the cooling system correctly, inspect at idle and around 2,500 rpm, and pressure-test according to Audi workshop information. If no leak is reproduced, observe the vehicle without replacing parts. If the pump leak is confirmed, replace the failed component and document it. If fresh coolant has entered the vacuum system, inspect the remaining Audi checkpoints and replace only contaminated components; if the downstream checkpoints are clean, replace N649 and clean the line between the pump and N649 as directed by TSB 2070349/5.</x:v>
       </x:c>
       <x:c r="F62" s="9" t="n">
         <x:v>0</x:v>
@@ -17092,21 +19974,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" ht="237.60000610351562" hidden="0" customHeight="1">
+    <x:row r="63" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A63" s="40" t="n">
         <x:v>62</x:v>
       </x:c>
       <x:c r="B63" s="9" t="str">
-        <x:v>audi-s7-cylinder-demand-rough-running-hesitation</x:v>
+        <x:v>audi-sq7-air-susp-strut-2020</x:v>
       </x:c>
       <x:c r="C63" s="9" t="str">
-        <x:v>2021-2021 | Audi | S7</x:v>
+        <x:v>2020-2025 | Audi | SQ7 | 4.0T</x:v>
       </x:c>
       <x:c r="D63" s="9" t="str">
-        <x:v>Instrument Panel May Fail to Display Critical Safety Information (Recall 25V201 / 90VC)</x:v>
+        <x:v>2020-2025 SQ7 Air-Suspension C1260F0/U112100 Communication Fault - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E63" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history. Audi dealers update the instrument-panel module software free of charge under campaign 90VC.</x:v>
+        <x:v>Inspect the wiring and connector contacts between J775 and J1135 first. If no wiring fault is found, clear a first passive or sporadic fault and release the vehicle. Replace J1135 for an active or static fault, or when the same passive or sporadic fault returns a second time, following Audi workshop information and VIN-specific ETKA data. Do not replace an air spring, strut or compressor assembly solely from the warning.</x:v>
       </x:c>
       <x:c r="F63" s="9" t="n">
         <x:v>0</x:v>
@@ -17115,21 +19997,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="316.79998779296875" hidden="0" customHeight="1">
+    <x:row r="64" ht="1122" hidden="0" customHeight="1">
       <x:c r="A64" s="40" t="n">
         <x:v>63</x:v>
       </x:c>
       <x:c r="B64" s="9" t="str">
-        <x:v>audi-s7-ea839-2-9t-v6-water-pump-internal-leak-overheating</x:v>
+        <x:v>audi-sq7-air-suspension-2020</x:v>
       </x:c>
       <x:c r="C64" s="9" t="str">
-        <x:v>2020-2024 | Audi | S7</x:v>
+        <x:v>2020-2024 | Audi | SQ7 | Premium Plus, Prestige | 4.0T</x:v>
       </x:c>
       <x:c r="D64" s="9" t="str">
-        <x:v>Rearview Camera Image May Not Display (Recall 25V900 / 90TV)</x:v>
+        <x:v>Adaptive Air Suspension Compressor and Air Spring Failures</x:v>
       </x:c>
       <x:c r="E64" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history. Audi dealers update the relevant software free of charge under campaign 90TV. Continue direct visual checks when reversing until repaired.</x:v>
+        <x:v>Diagnose specific failed component: air springs leak most commonly, followed by compressor burnout, valve block faults, and height sensor failures. Air spring replacement ($800-$1,500 per corner at independent shop). Compressor replacement ($1,200-$2,500 installed). Valve block: $500-$1,000. Height sensor: $200-$400. Check for air leaks first using soapy water spray before replacing the compressor - a $200 air spring seal may be causing a $2,000 compressor to overwork and fail. Aftermarket solutions from Arnott offer cost savings. Converting to conventional springs ($1,500-$2,500) eliminates future air suspension costs but sacrifices ride height adjustment.</x:v>
       </x:c>
       <x:c r="F64" s="9" t="n">
         <x:v>0</x:v>
@@ -17138,21 +20020,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="343.20001220703125" hidden="0" customHeight="1">
+    <x:row r="65" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A65" s="40" t="n">
         <x:v>64</x:v>
       </x:c>
       <x:c r="B65" s="9" t="str">
-        <x:v>audi-s7-electromechanical-steering-rack-torque-sensor-failure-causin</x:v>
+        <x:v>audi-sq7-mmi-mib3-freeze-2020</x:v>
       </x:c>
       <x:c r="C65" s="9" t="str">
-        <x:v>2021-2021 | Audi | S7</x:v>
+        <x:v>2020-2026 | Audi | SQ7</x:v>
       </x:c>
       <x:c r="D65" s="9" t="str">
-        <x:v>Incorrect Brake-Fluid Reservoir Cap Label (Recall 23V601 / 47T9)</x:v>
+        <x:v>2020-2026 Audi SQ7 Rearview Camera Software Recall 25V900 / 90TV</x:v>
       </x:c>
       <x:c r="E65" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers inspect the reservoir cap and replace it when necessary free of charge under campaign 47T9. Use only the brake-fluid specification in the owner and service information.</x:v>
+        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install the more robust driver-assistance software update free of charge. Until repaired, use extra caution when reversing and do not treat a restart, bus sleep or temporary image recovery as completion of the recall.</x:v>
       </x:c>
       <x:c r="F65" s="9" t="n">
         <x:v>0</x:v>
@@ -17161,44 +20043,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="66" ht="990" hidden="0" customHeight="1">
       <x:c r="A66" s="40" t="n">
         <x:v>65</x:v>
       </x:c>
       <x:c r="B66" s="9" t="str">
-        <x:v>audi-s7-front-control-arm-bushing-ball-joint-failure</x:v>
+        <x:v>audi-sq7-valve-cover-oil-leak-2020</x:v>
       </x:c>
       <x:c r="C66" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+        <x:v>2020-2024 | Audi | SQ7 | 4.0T</x:v>
       </x:c>
       <x:c r="D66" s="9" t="str">
-        <x:v>Front Control Arm Bushing and Ball Joint Failure (C7 Suspension)</x:v>
+        <x:v>2020-2024 SQ7 4.0L High Oil Consumption and Piston-Ring Diagnosis - TSB 2071114/5</x:v>
       </x:c>
       <x:c r="E66" s="9" t="str">
-        <x:v>Inspect all front control arms for play in the bushings and ball joints. Replace worn arms — many owners do the full front control-arm set (commonly a 16-piece kit covering both sides) to avoid repeat visits since the labor overlaps. Critical install notes: torque the bushing bolts at ride height (not with the suspension hanging) to avoid pre-loading and destroying the new bushings, and perform a four-wheel alignment afterward.</x:v>
+        <x:v>First inspect for visible engine-oil traces or leaks. Have an Audi dealer perform the authorized ODIS oil-consumption measurement, preserve and upload both test logs, and document the requested driving-profile data. Internal-engine repair is justified only when measured consumption exceeds the applicable limit and no other cause is found. If every TSB gate is met, follow Audi's VIN-, engine-code- and power-class-specific procedure for replacement of all eight pistons and piston rings, using current ETKA and ELSA information. Do not diagnose valve-cover gaskets or turbocharger seals from oil consumption alone.</x:v>
       </x:c>
       <x:c r="F66" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G66" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" ht="396" hidden="0" customHeight="1">
+    <x:row r="67" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A67" s="40" t="n">
         <x:v>66</x:v>
       </x:c>
       <x:c r="B67" s="9" t="str">
-        <x:v>audi-s7-fuel-injector-deposits-failure-causing-misfire-rough-running</x:v>
+        <x:v>audi-sq8-air-susp-compressor-2020</x:v>
       </x:c>
       <x:c r="C67" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
+        <x:v>2020-2025 | Audi | SQ8</x:v>
       </x:c>
       <x:c r="D67" s="9" t="str">
-        <x:v>Fuel Injector Deposits / Failure Causing Misfire and Rough Running (4.0T V8)</x:v>
+        <x:v>2020-2025 SQ8 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
       </x:c>
       <x:c r="E67" s="9" t="str">
-        <x:v>Pull misfire counts per cylinder to localize the fault. Inspect/replace failed or leaking injectors and renew injector seals; replace spark plugs and any weak coils as a set. Confirm fuel trims return to normal and clear codes; address intake carbon if present.</x:v>
+        <x:v>Inspect the wiring and connector contacts between J775 and J1135 before replacing a component. For a first passive or sporadic occurrence, clear the fault and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after wiring inspection, Audi directs replacement of J1135 under current repair and parts information. Do not buy struts, springs or a compressor solely from this warning.</x:v>
       </x:c>
       <x:c r="F67" s="9" t="n">
         <x:v>0</x:v>
@@ -17207,21 +20089,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" ht="396" hidden="0" customHeight="1">
+    <x:row r="68" ht="831.5999755859375" hidden="0" customHeight="1">
       <x:c r="A68" s="40" t="n">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B68" s="9" t="str">
-        <x:v>audi-s7-gateway-control-module-shutdown-from-rear-seat-liquid-spill</x:v>
+        <x:v>audi-sq8-air-suspension-2020</x:v>
       </x:c>
       <x:c r="C68" s="9" t="str">
-        <x:v>2020-2022 | Audi | S7 | 2.9 TFSI</x:v>
+        <x:v>2020-2024 | Audi | SQ8 | Premium Plus, Prestige | 4.0T</x:v>
       </x:c>
       <x:c r="D68" s="9" t="str">
-        <x:v>Rear-Seat Liquid Spill Can Shut Down Gateway Module (Recall 22V861 / 90V2)</x:v>
+        <x:v>Adaptive Air Suspension Compressor and Air Spring Failures</x:v>
       </x:c>
       <x:c r="E68" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers install a protective gateway-module cover free of charge under campaign 90V2. If multiple warnings or reduced power occur after a spill, move out of traffic safely and arrange dealer inspection.</x:v>
+        <x:v>Same diagnostic and repair approach as SQ7 (shared 4M platform). Isolate the failed component: air springs ($800-$1,500 per corner), compressor ($1,200-$2,500), valve block ($500-$1,000), or height sensor ($200-$400). Always check for air leaks before replacing the compressor. Aftermarket air suspension components from Arnott/Strutmasters offer 40-50% savings over OEM. Annual inspection of air springs for cracking recommended, especially in hot climates where UV and heat accelerate rubber degradation.</x:v>
       </x:c>
       <x:c r="F68" s="9" t="n">
         <x:v>0</x:v>
@@ -17230,21 +20112,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" ht="528" hidden="0" customHeight="1">
+    <x:row r="69" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A69" s="40" t="n">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B69" s="9" t="str">
-        <x:v>audi-s7-high-pressure-fuel-pump-failure-causing-hard-start-power-los</x:v>
+        <x:v>audi-sq8-airbag-mount-2023</x:v>
       </x:c>
       <x:c r="C69" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
+        <x:v>2023-2024 | Audi | SQ8 | 4.0T V8</x:v>
       </x:c>
       <x:c r="D69" s="9" t="str">
-        <x:v>High-Pressure Fuel Pump (HPFP) Failure Causing Hard Start and Power Loss (4.0T V8)</x:v>
+        <x:v>2023-2024 SQ8 Driver-Seat Side-Airbag Mount Recall 69GA (23V868)</x:v>
       </x:c>
       <x:c r="E69" s="9" t="str">
-        <x:v>Diagnose with live fuel-rail pressure data before condemning the pump, as a faulty low-pressure sensor or in-tank pump can set the same codes. Replace the failed high-pressure pump (the affected bank, or both as a set on high-mileage cars) together with the cam follower and seals. Verify low-pressure (in-tank) supply is within spec.</x:v>
+        <x:v>Check the VIN for open Audi recall 69GA and have an authorized dealer inspect the driver-seat side-airbag installation. If needed, the dealer will reinstall the airbag correctly; the recall filing says no parts are replaced. A clock spring or generic airbag part is not the recall remedy.</x:v>
       </x:c>
       <x:c r="F69" s="9" t="n">
         <x:v>0</x:v>
@@ -17253,44 +20135,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" ht="660" hidden="0" customHeight="1">
+    <x:row r="70" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A70" s="40" t="n">
         <x:v>69</x:v>
       </x:c>
       <x:c r="B70" s="9" t="str">
-        <x:v>audi-s7-ignition-coil-pack-failure-causing-misfires</x:v>
+        <x:v>audi-sq8-mmi-mib3-freeze-2020</x:v>
       </x:c>
       <x:c r="C70" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+        <x:v>2020-2026 | Audi | SQ8 | 4.0T V8</x:v>
       </x:c>
       <x:c r="D70" s="9" t="str">
-        <x:v>Ignition Coil Pack Failure Causing Misfires (4.0T V8)</x:v>
+        <x:v>2020-2026 SQ8 Rearview Camera Software Recall 90TV (25V900)</x:v>
       </x:c>
       <x:c r="E70" s="9" t="str">
-        <x:v>Confirm the failing cylinder, then swap the suspect coil to another cylinder to verify the fault follows the coil. Replace the failed coil; best practice on the 4.0T is to replace all eight coils and the spark plugs as a set since the access labor is shared and mixed-age coils tend to fail in sequence. Use OE or quality OE-equivalent coils (the 4.0T uses the 079905110-series coil). Inspect spark plugs for fouling/oil that could indicate a secondary issue.</x:v>
+        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install more robust driver-assistance software free of charge. Until repaired, use extra caution when reversing and do not treat a restart, bus sleep or temporary image recovery as completion of the recall. A generic scan tool or head-unit replacement is not the recall remedy.</x:v>
       </x:c>
       <x:c r="F70" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G70" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="237.60000610351562" hidden="0" customHeight="1">
+    <x:row r="71" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A71" s="40" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="B71" s="9" t="str">
-        <x:v>audi-s7-motor-mount-failure-2012</x:v>
+        <x:v>audi-sq8-turbo-coolant-2020</x:v>
       </x:c>
       <x:c r="C71" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7</x:v>
+        <x:v>2020-2021 | Audi | SQ8 | 4.0T V8</x:v>
       </x:c>
       <x:c r="D71" s="9" t="str">
-        <x:v>Passenger Occupant Detection Mat Can Disable the Airbag (Recall 18V370 / 74D5)</x:v>
+        <x:v>2020-Early 2021 SQ8 Red Coolant Warning - Check G407 per TSB 2062951/4</x:v>
       </x:c>
       <x:c r="E71" s="9" t="str">
-        <x:v>Check VIN eligibility because seat equipment affects scope. Audi dealers install the occupant-detection repair kit free of charge under campaign 74D5.</x:v>
+        <x:v>Have the vehicle checked with Audi Guided Fault Finding and inspect G407 and its O-ring. Replace G407 only if the O-ring is damaged or pinched and the diagnosis matches the bulletin; follow the related Audi diagnostic path if additional listed faults are stored. Do not replace turbo coolant hoses, pumps or other cooling parts from this card alone.</x:v>
       </x:c>
       <x:c r="F71" s="9" t="n">
         <x:v>0</x:v>
@@ -17299,21 +20181,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="72" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A72" s="40" t="n">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B72" s="9" t="str">
-        <x:v>audi-s7-pcv-oil-separator-failure-causing-oil-consumption-whistling</x:v>
+        <x:v>audi-tt-absesp-control-module-failure-2000</x:v>
       </x:c>
       <x:c r="C72" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
+        <x:v>2000-2001 | Audi | TT</x:v>
       </x:c>
       <x:c r="D72" s="9" t="str">
-        <x:v>PCV / Oil Separator (Ölabscheider) Failure Causing Oil Consumption and Whistling (4.0T V8)</x:v>
+        <x:v>Driver Airbag Inflator May Deploy Improperly (Recall 21V470 / 69CJ)</x:v>
       </x:c>
       <x:c r="E72" s="9" t="str">
-        <x:v>Replace the failed oil separator / PCV assembly and the associated breather hose with the latest revised part. An ECM update may accompany the new part on some VINs. Confirm with a smoke test for intake-side vacuum leaks; inspect the rear main seal if oil consumption is severe, as a failed PCV is a common cause of rear main seal damage on these engines.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the driver frontal-airbag inflator with an alternative inflator free of charge under campaign 69CJ.</x:v>
       </x:c>
       <x:c r="F72" s="9" t="n">
         <x:v>0</x:v>
@@ -17322,21 +20204,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="73" ht="277.20001220703125" hidden="0" customHeight="1">
       <x:c r="A73" s="40" t="n">
         <x:v>72</x:v>
       </x:c>
       <x:c r="B73" s="9" t="str">
-        <x:v>audi-s7-power-liftgate-motor-gas-strut-failure</x:v>
+        <x:v>audi-tt-cam-follower-2008</x:v>
       </x:c>
       <x:c r="C73" s="9" t="str">
-        <x:v>2013-2022 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824), 2.9T TFSI Biturbo V6 (EA839)</x:v>
+        <x:v>2000-2000 | Audi | TT</x:v>
       </x:c>
       <x:c r="D73" s="9" t="str">
-        <x:v>Power Liftgate Motor and Gas Strut Failure (Sportback Tailgate)</x:v>
+        <x:v>Fuel-Line Assembly Can Leak (Recall 99V222)</x:v>
       </x:c>
       <x:c r="E73" s="9" t="str">
-        <x:v>Diagnose whether the fault is the gas struts (won't stay up / weak lift), the spindle lift motors (slow or struggling travel), or the latch/cinching motor (won't release or won't pull closed — see TSB 2072431/1). Replace worn gas struts in pairs; replace failed lift or cinching motors as needed. After repair, perform the power-liftgate relearn/reset procedure so travel limits recalibrate.</x:v>
+        <x:v>Check VIN eligibility and campaign completion. Audi dealers replace the fuel-line assembly free of charge under recall 99V222. Stop driving if fuel odor or leakage is present.</x:v>
       </x:c>
       <x:c r="F73" s="9" t="n">
         <x:v>0</x:v>
@@ -17345,21 +20227,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="74" ht="198" hidden="0" customHeight="1">
       <x:c r="A74" s="40" t="n">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B74" s="9" t="str">
-        <x:v>audi-s7-premature-front-brake-rotor-warping-pad-wear</x:v>
+        <x:v>audi-tt-coil-pack-failure-and-2000</x:v>
       </x:c>
       <x:c r="C74" s="9" t="str">
-        <x:v>2013-2022 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824), 2.9T TFSI Biturbo V6 (EA839)</x:v>
+        <x:v>2000-2001 | Audi | TT</x:v>
       </x:c>
       <x:c r="D74" s="9" t="str">
-        <x:v>Premature Front Brake Rotor Warping and Pad Wear</x:v>
+        <x:v>Rear Track-Control Arm Corrosion Can Restrict Movement (Recall 01V325)</x:v>
       </x:c>
       <x:c r="E74" s="9" t="str">
-        <x:v>Replace warped/below-spec rotors and pads together; consider higher-quality coated or upgraded rotors that resist warping better than the soft OEM units. Bed in new pads/rotors properly and avoid riding the brakes to prevent uneven deposits. Ensure caliper guide pins/slides move freely so pads engage evenly. For repeat warping, an upgraded rotor-and-pad package is the durable fix; address any pulsation early before it damages new components.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the rear track-control arms free of charge under recall 01V325.</x:v>
       </x:c>
       <x:c r="F74" s="9" t="n">
         <x:v>0</x:v>
@@ -17368,21 +20250,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="75" ht="264" hidden="0" customHeight="1">
       <x:c r="A75" s="40" t="n">
         <x:v>74</x:v>
       </x:c>
       <x:c r="B75" s="9" t="str">
-        <x:v>audi-s7-rear-differential-mount-driveshaft-center-bearing-wear-causi</x:v>
+        <x:v>audi-tt-dsg-mechatronic-2008</x:v>
       </x:c>
       <x:c r="C75" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+        <x:v>2004-2004 | Audi | TT</x:v>
       </x:c>
       <x:c r="D75" s="9" t="str">
-        <x:v>Rear Differential Mount and Driveshaft Center Bearing Wear Causing Drivetrain Clunk (C7)</x:v>
+        <x:v>Direct-Shift Gearbox Clutch Weld Can Lose Drive Torque (Recall 04V007)</x:v>
       </x:c>
       <x:c r="E75" s="9" t="str">
-        <x:v>Inspect the rear differential mount and driveshaft center support bearing for play and torn rubber. Replace worn components with OE parts, or fit billet aluminum diff/transmission mount inserts that fill the factory voids to remove the slop without adding harshness. On 4.0T cars, also check for the separate active-engine-mount software TSB before condemning a mount for a 1,000-3,000 RPM cruise vibration. Reassess the clunk after each fix since multiple sources can contribute.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers replace the affected clutch free of charge under recall 04V007. If drive torque is lost, move out of traffic safely and arrange recovery.</x:v>
       </x:c>
       <x:c r="F75" s="9" t="n">
         <x:v>0</x:v>
@@ -17391,21 +20273,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" ht="462" hidden="0" customHeight="1">
+    <x:row r="76" ht="356.3999938964844" hidden="0" customHeight="1">
       <x:c r="A76" s="40" t="n">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B76" s="9" t="str">
-        <x:v>audi-s7-rear-view-camera-mmi-flex-harness-black-screen</x:v>
+        <x:v>audi-tt-dsg-transmission-2008</x:v>
       </x:c>
       <x:c r="C76" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7 (C7), A7 (C7) | 4.0 TFSI V8 (EA824)</x:v>
+        <x:v>2009-2009 | Audi | TT</x:v>
       </x:c>
       <x:c r="D76" s="9" t="str">
-        <x:v>Rear-View Camera / MMI Flex Harness Black Screen</x:v>
+        <x:v>DSG Temperature-Sensor Wiring Can Trigger an Abrupt Shift to Neutral (Recall 09V333)</x:v>
       </x:c>
       <x:c r="E76" s="9" t="str">
-        <x:v>Diagnose with a scan and continuity check of the tailgate-to-body flex harness before replacing the camera. Repair or replace the broken hinge-side loom conductors; if confirmed faulty, replace the camera module. For MMI freezes, apply the latest software update or reset the unit.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers reprogram the transmission control module with updated software free of charge under recall 09V333. If the gear indicator flashes or neutral engages unexpectedly, stop safely.</x:v>
       </x:c>
       <x:c r="F76" s="9" t="n">
         <x:v>0</x:v>
@@ -17414,21 +20296,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="77" ht="303.6000061035156" hidden="0" customHeight="1">
       <x:c r="A77" s="40" t="n">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B77" s="9" t="str">
-        <x:v>audi-s7-s-tronic-7-speed-dual-clutch-mechatronic-clutch-wear</x:v>
+        <x:v>audi-tt-front-control-arm-bushings-2000</x:v>
       </x:c>
       <x:c r="C77" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T (S-tronic / 0B5 DL501) | 4.0 TFSI V8 (EA824)</x:v>
+        <x:v>2000-2000 | Audi | TT</x:v>
       </x:c>
       <x:c r="D77" s="9" t="str">
-        <x:v>S-tronic 7-Speed Dual-Clutch (DL501/0B5) Mechatronic and Clutch Wear</x:v>
+        <x:v>High-Speed Directional-Stability Remedy (Recall 99V300)</x:v>
       </x:c>
       <x:c r="E77" s="9" t="str">
-        <x:v>Perform the S-tronic gearbox oil and filter service on schedule (roughly every 40,000-60,000 km). For judder/jerking, have the mechatronic unit tested; recondition or replace the valve body with the superseded design and adapt/replace the clutch packs as needed. Software adaptation resets can temporarily improve drivability but do not fix worn hardware.</x:v>
+        <x:v>Verify campaign completion with Audi. The factory remedy installs revised stabilizers, front control arms, firmer shock absorbers, and a rear spoiler as specified for the drivetrain configuration.</x:v>
       </x:c>
       <x:c r="F77" s="9" t="n">
         <x:v>0</x:v>
@@ -17437,21 +20319,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="78" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A78" s="40" t="n">
         <x:v>77</x:v>
       </x:c>
       <x:c r="B78" s="9" t="str">
-        <x:v>audi-s7-shark-fin-roof-antenna-water-intrusion-causing-gps-satellite</x:v>
+        <x:v>audi-tt-haldex-awd-coupling-pumpcontroller-2000</x:v>
       </x:c>
       <x:c r="C78" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | Prestige, Premium Plus | 4.0T Biturbo V8 (4.0 TFSI)</x:v>
+        <x:v>2008-2010 | Audi | TT</x:v>
       </x:c>
       <x:c r="D78" s="9" t="str">
-        <x:v>Shark-Fin Roof Antenna Water Intrusion Causing GPS / Satellite Radio Reception Loss (C7)</x:v>
+        <x:v>Fuel-Tank Ventilation Valve Can Allow Fuel Leakage (Recall 09V377)</x:v>
       </x:c>
       <x:c r="E78" s="9" t="str">
-        <x:v>Test/replace the shark-fin antenna module with a matching OEM part number and renew the base gasket to restore a watertight seal; in many cases the official fix is a repair kit with a new FAKRA connector and adapter cable rather than a whole new antenna. Access requires partially dropping the rear headliner to reach the single mounting nut and reconnect the coax leads. Inspecting and reseating a corroded coax connection sometimes restores reception without full replacement.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel-tank ventilation valve with the improved valve free of charge under recall 09V377.</x:v>
       </x:c>
       <x:c r="F78" s="9" t="n">
         <x:v>0</x:v>
@@ -17460,21 +20342,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" ht="752.4000244140625" hidden="0" customHeight="1">
+    <x:row r="79" ht="184.8000030517578" hidden="0" customHeight="1">
       <x:c r="A79" s="40" t="n">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B79" s="9" t="str">
-        <x:v>audi-s7-sunroof-panoramic-roof-drain-clog-causing-water-intrusion-el</x:v>
+        <x:v>audi-tt-high-speed-stability-recall-for-2000</x:v>
       </x:c>
       <x:c r="C79" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+        <x:v>2016-2019 | Audi | TT</x:v>
       </x:c>
       <x:c r="D79" s="9" t="str">
-        <x:v>Sunroof / Panoramic Roof Drain Clog Causing Water Intrusion and Electronics Damage (C7)</x:v>
+        <x:v>Fuel Tank Can Be Damaged by Heat-Shield Bracket in a Crash (Recall 20V076 / 20BX)</x:v>
       </x:c>
       <x:c r="E79" s="9" t="str">
-        <x:v>Test the drains by slowly pouring water into the channels at each corner of the sunroof and watching where it exits beneath the A- and C-pillars. Clear clogged tubes with low-pressure air or a soft trimmer line (avoid stiff wire that can puncture the tube) and reseat/secure any loose drain-tube connectors at the sunroof frame. Dry out any soaked carpet/insulation promptly and inspect floor-mounted modules for corrosion. Periodic drain cleaning is the best prevention.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers install a protective cap on the heat-shield bracket free of charge under campaign 20BX.</x:v>
       </x:c>
       <x:c r="F79" s="9" t="n">
         <x:v>0</x:v>
@@ -17483,21 +20365,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" ht="422.3999938964844" hidden="0" customHeight="1">
+    <x:row r="80" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A80" s="40" t="n">
         <x:v>79</x:v>
       </x:c>
       <x:c r="B80" s="9" t="str">
-        <x:v>audi-s7-turbo-oil-strainer-2012</x:v>
+        <x:v>audi-tt-instrument-cluster-pixel-failure-2000</x:v>
       </x:c>
       <x:c r="C80" s="9" t="str">
-        <x:v>2013-2017 | Audi | S7 | 4.0 TFSI</x:v>
+        <x:v>2016-2016 | Audi | TT</x:v>
       </x:c>
       <x:c r="D80" s="9" t="str">
-        <x:v>Turbocharger Oil-Supply Strainer Can Block and Cause Engine Stall (Recall 22V178 / 21H7)</x:v>
+        <x:v>Front-Passenger Airbag Module May Explode or Deploy Improperly (Recall 22V543 / 69DY)</x:v>
       </x:c>
       <x:c r="E80" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the oil strainer and perform an oil change free of charge under campaign 21H7. If abnormal turbo noise, loss of power, or an engine warning occurs, stop safely and arrange dealer inspection.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the front-passenger airbag module free of charge under campaign 69DY/61C1.</x:v>
       </x:c>
       <x:c r="F80" s="9" t="n">
         <x:v>0</x:v>
@@ -17506,21 +20388,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="726" hidden="0" customHeight="1">
+    <x:row r="81" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A81" s="40" t="n">
         <x:v>80</x:v>
       </x:c>
       <x:c r="B81" s="9" t="str">
-        <x:v>audi-s7-turbocharger-wastegate-linkage-rattle-underboost</x:v>
+        <x:v>audi-tt-magnetic-ride-2008</x:v>
       </x:c>
       <x:c r="C81" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+        <x:v>2023-2023 | Audi | TT</x:v>
       </x:c>
       <x:c r="D81" s="9" t="str">
-        <x:v>Turbocharger Wastegate Linkage Rattle and Underboost (4.0T V8)</x:v>
+        <x:v>Passenger-Seat Occupant Detection Connection Can Disable Airbag (Recall 24V251 / 69GU)</x:v>
       </x:c>
       <x:c r="E81" s="9" t="str">
-        <x:v>Diagnose the rattle and any boost faults to confirm wastegate-arm play versus a loose heat shield. Minor play can sometimes be mitigated with a clip, but the durable factory fix is turbocharger replacement. When replacing a hot-V turbo, it is mandatory to also replace the oil feed and return lines and to prime the new unit with oil before first start to prevent immediate bearing failure. Regular oil changes and allowing turbo cool-down help reduce coking-related wear.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers replace the passenger-seat occupant-detection control module free of charge under campaign 69GU.</x:v>
       </x:c>
       <x:c r="F81" s="9" t="n">
         <x:v>0</x:v>
@@ -17529,21 +20411,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="686.4000244140625" hidden="0" customHeight="1">
+    <x:row r="82" ht="726" hidden="0" customHeight="1">
       <x:c r="A82" s="40" t="n">
         <x:v>81</x:v>
       </x:c>
       <x:c r="B82" s="9" t="str">
-        <x:v>audi-s8-5-2-v10-timing-chain-tensioner-guide-wear</x:v>
+        <x:v>audi-tt-tail-light-corrosion-2008</x:v>
       </x:c>
       <x:c r="C82" s="9" t="str">
-        <x:v>2007-2012 | Audi | S8 | 5.2L FSI V10 (BSM)</x:v>
+        <x:v>2008-2015 | Audi | TT</x:v>
       </x:c>
       <x:c r="D82" s="9" t="str">
-        <x:v>5.2 V10 Timing Chain Tensioner / Guide Wear (D3 Cold-Start Rattle)</x:v>
+        <x:v>Tail Light Electrical Connector Corrosion (Mk2)</x:v>
       </x:c>
       <x:c r="E82" s="9" t="str">
-        <x:v>Investigate any cold-start rattle promptly: inspect tensioner travel and guide condition. Replace the timing chains, tensioners, and plastic guides as a set with updated genuine parts; this is a major, labor-intensive repair (often engine-out). Strictly follow short oil-change intervals with the correct grade to maximize tensioner/guide life, and address any low-oil-pressure condition immediately. Do not drive a V10 with a persistent timing rattle.</x:v>
+        <x:v>Remove tail light assembly, inspect electrical connector for green corrosion. CLEAN connector with electrical contact cleaner and wire brush ($20 DIY). Apply dielectric grease to prevent future corrosion ($10). If connector is severely corroded: Replace pigtail connector ($50-$100 parts). Improve tail light seal with silicone sealant around housing ($15). This is a DIY-friendly repair taking 1-2 hours. If paying shop, costs $150-$300. Address early before corrosion causes shorts.</x:v>
       </x:c>
       <x:c r="F82" s="9" t="n">
         <x:v>0</x:v>
@@ -17552,21 +20434,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="198" hidden="0" customHeight="1">
+    <x:row r="83" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A83" s="40" t="n">
         <x:v>82</x:v>
       </x:c>
       <x:c r="B83" s="9" t="str">
-        <x:v>audi-s8-air-suspension-2013</x:v>
+        <x:v>audi-tt-water-pump-2008</x:v>
       </x:c>
       <x:c r="C83" s="9" t="str">
-        <x:v>2013-2024 | Audi | S8</x:v>
+        <x:v>2008-2008 | Audi | TT</x:v>
       </x:c>
       <x:c r="D83" s="9" t="str">
-        <x:v>Adaptive Air Suspension Multi-Point Failure</x:v>
+        <x:v>C-Pillar Trim Cover Can Detach During Belt-Tensioner Deployment (Recall 08V064)</x:v>
       </x:c>
       <x:c r="E83" s="9" t="str">
-        <x:v>Replace air struts as they fail. Budget for full system refresh at 80,000 miles. Arnott aftermarket struts offer cost savings.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers install improved C-pillar trim clips free of charge under recall 08V064.</x:v>
       </x:c>
       <x:c r="F83" s="9" t="n">
         <x:v>0</x:v>
@@ -17575,21 +20457,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="726" hidden="0" customHeight="1">
+    <x:row r="84" ht="1161.5999755859375" hidden="0" customHeight="1">
       <x:c r="A84" s="40" t="n">
         <x:v>83</x:v>
       </x:c>
       <x:c r="B84" s="9" t="str">
-        <x:v>audi-s8-air-suspension-failure-2013</x:v>
+        <x:v>audi-tts-cam-follower-hpfp-2009</x:v>
       </x:c>
       <x:c r="C84" s="9" t="str">
-        <x:v>2020-2024 | Audi | S8</x:v>
+        <x:v>2009-2015 | Audi | TTS | TTS | EA888</x:v>
       </x:c>
       <x:c r="D84" s="9" t="str">
-        <x:v>2020-2024 S8 Air-Suspension Malfunction with J1135 Communication Fault - Diagnosis Required</x:v>
+        <x:v>HPFP Cam Follower Wear and High-Pressure Fuel Pump Failure (Mk2)</x:v>
       </x:c>
       <x:c r="E84" s="9" t="str">
-        <x:v>Read the suspension-controller DTC and symptom code, then inspect wiring, terminals and connectors between J775 and J1135 exactly as Audi specifies. If the fault is passive/sporadic, clear it and verify operation. If it remains active/static after the electrical inspection and key cycle, follow Audi testing for J1135 replacement. Diagnose vehicle sag or leak-down separately; do not order air struts, a compressor or a coil-conversion kit from the former card.</x:v>
+        <x:v>INSPECTION (every 20,000 miles): Remove HPFP (3 bolts) and inspect cam follower surface. If the hardened coating is wearing through (visible copper/brass color), replace follower immediately ($30-$50 part, 30-60 minutes labor). CRITICAL: Ensure cam lobe is at LOW point before reinstalling—if at peak, you'll compress the spring and can break the mounting bolts. If CAMSHAFT WORN (deep groove in lobe): Replace camshaft ($2,000-$4,000). If FUEL PUMP FAILED: Replace HPFP ($400-$800). PREVENTION: Inspect cam follower every 20,000 miles as routine maintenance. Add to every oil change checklist. Consider IE (Integrated Engineering) upgraded HPFP with roller follower to eliminate wear entirely.</x:v>
       </x:c>
       <x:c r="F84" s="9" t="n">
         <x:v>0</x:v>
@@ -17598,21 +20480,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="85" ht="884.4000244140625" hidden="0" customHeight="1">
       <x:c r="A85" s="40" t="n">
         <x:v>84</x:v>
       </x:c>
       <x:c r="B85" s="9" t="str">
-        <x:v>audi-s8-battery-management-energy-control-module-faults-parasitic-dr</x:v>
+        <x:v>audi-tts-carbon-buildup-2009</x:v>
       </x:c>
       <x:c r="C85" s="9" t="str">
-        <x:v>2020-2020 | Audi | S8 | VIN-specific Emissions Service Action 27BQ; verify open action in Audi campaign lookup | 4.0T TFSI V8 mild-hybrid</x:v>
+        <x:v>2016-2017 | Audi | TTS</x:v>
       </x:c>
       <x:c r="D85" s="9" t="str">
-        <x:v>2020 S8 Starter-Alternator Emissions Service Action 27BQ - VIN Check Required</x:v>
+        <x:v>2016-2017 TTS Cold-Start Misfire DTCs Without Felt Misfire - TSB 2051384/1</x:v>
       </x:c>
       <x:c r="E85" s="9" t="str">
-        <x:v>Check the VIN in Audi’s recall/service-campaign lookup or ask an Audi dealer to verify 27BQ in Elsa. If open, the dealer replaces the starter-alternator under the action. Electrical-system warnings, a discharged battery, abnormal charging or overnight draw outside this exact action require battery/charging tests and a measured sleep-current diagnosis; do not replace a battery monitor, gateway or MMI module from the former card.</x:v>
+        <x:v>Confirm the exact cold-start timing, simultaneous-cylinder DTC pattern, absence of a felt misfire, CYFB engine and installed ECM software before using this bulletin. When applicable, an Audi-capable workshop updates ECM J623 from software part number 8S0906259C version 0001 to version 0004 or higher using SVM action 01A190, then clears the DTCs. A felt misfire, a different timing or RPM pattern, a different engine/software combination or a returning concern requires normal diagnosis rather than carbon cleaning by assumption.</x:v>
       </x:c>
       <x:c r="F85" s="9" t="n">
         <x:v>0</x:v>
@@ -17621,21 +20503,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="86" ht="910.7999877929688" hidden="0" customHeight="1">
       <x:c r="A86" s="40" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="B86" s="9" t="str">
-        <x:v>audi-s8-biturbo-coolant-2013</x:v>
+        <x:v>audi-tts-dsg-mechatronic-2009</x:v>
       </x:c>
       <x:c r="C86" s="9" t="str">
-        <x:v>2013-2024 | Audi | S8 | 4.0T</x:v>
+        <x:v>2019-2023 | Audi | TTS</x:v>
       </x:c>
       <x:c r="D86" s="9" t="str">
-        <x:v>4.0T Turbo Coolant System Degradation</x:v>
+        <x:v>2019-2023 TTS Clutch K1 Overheat and Transmission DTC Diagnosis - TSB 2060560/3</x:v>
       </x:c>
       <x:c r="E86" s="9" t="str">
-        <x:v>Replace all turbo coolant and oil feed lines preventatively at 60,000 miles. Monitor coolant levels closely.</x:v>
+        <x:v>Have an Audi-capable workshop check whether TSB 2050723 applies first. If it does not resolve or control the concern, inspect the clutch-K1 maximum-temperature value and document a transmission-fluid sample. Replace the dual clutch, transmission fluid and filter only when the approximately 400 °C K1 value and burnt black or very dark fluid are both present. If those findings are absent, this bulletin does not apply and Audi directs the workshop to continue diagnosis through TAC. Any clutch repair kit must be selected by VIN and production date.</x:v>
       </x:c>
       <x:c r="F86" s="9" t="n">
         <x:v>0</x:v>
@@ -17644,21 +20526,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="87" ht="858" hidden="0" customHeight="1">
       <x:c r="A87" s="40" t="n">
         <x:v>86</x:v>
       </x:c>
       <x:c r="B87" s="9" t="str">
-        <x:v>audi-s8-clogged-sunroof-plenum-drains-causing-water-intrusion-electr</x:v>
+        <x:v>audi-tts-magnetic-ride-2009</x:v>
       </x:c>
       <x:c r="C87" s="9" t="str">
-        <x:v>2007-2018 | Audi | S8 | S8, S8 Plus | 5.2 FSI V10, 4.0 TFSI twin-turbo V8 (4.0T)</x:v>
+        <x:v>2016-2016 | Audi | TTS</x:v>
       </x:c>
       <x:c r="D87" s="9" t="str">
-        <x:v>Clogged Sunroof / Plenum Drains Causing Water Intrusion and Electronics Damage</x:v>
+        <x:v>2016 TTS Magnetic-Ride Rear Shock-Mount Rumble - TSB 2042539/4</x:v>
       </x:c>
       <x:c r="E87" s="9" t="str">
-        <x:v>Clear and flush all sunroof and plenum/cowl drains; replace cracked drain hoses, grommets, or channel connectors. Dry out saturated carpet/insulation and inspect plenum-area modules for corrosion, replacing any water-damaged control units. Preventively clean the drains at least annually and keep the cowl area free of leaves/debris.</x:v>
+        <x:v>First reproduce the noise, verify that it comes from the rear shock mounts and confirm that the vehicle was originally equipped with mount 8S0 513 353. Only when those gates are satisfied, remove both rear shock assemblies and replace both mounts with 8V0 513 353 according to Audi workshop instructions, adapt the suspension control position and test drive to confirm the repair. If the installed mount does not match, continue Audi diagnosis. Do not replace magnetic dampers or convert the vehicle to coilovers from this noise alone.</x:v>
       </x:c>
       <x:c r="F87" s="9" t="n">
         <x:v>0</x:v>
@@ -17667,21 +20549,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="88" ht="1016.4000244140625" hidden="0" customHeight="1">
       <x:c r="A88" s="40" t="n">
         <x:v>87</x:v>
       </x:c>
       <x:c r="B88" s="9" t="str">
-        <x:v>audi-s8-coolant-thermostat-leak-2013</x:v>
+        <x:v>audi-tts-timing-chain-tensioner-2009</x:v>
       </x:c>
       <x:c r="C88" s="9" t="str">
-        <x:v>2020-2021 | Audi | S8 | 2021 applicability ends at VIN 012194; confirm VIN and coolant-pump leak before repair | 4.0T TFSI V8</x:v>
+        <x:v>2009-2015 | Audi | TTS | TTS | EA888 Gen 1, EA888 Gen 2</x:v>
       </x:c>
       <x:c r="D88" s="9" t="str">
-        <x:v>2020-Early 2021 S8 Coolant-Pump Leak - Diagnosis Required</x:v>
+        <x:v>Timing Chain Tensioner Failure (EA888 Gen 1/2 - Mk2 TTS)</x:v>
       </x:c>
       <x:c r="E88" s="9" t="str">
-        <x:v>Do not drive an overheating vehicle. Record coolant warning and temperature behavior, pressure-test the cooling system when safe, and locate the leak. Confirm the 2021 VIN boundary and apply TSB 2065040/4 only when the coolant pump is the identified source. Other thermostat, hose, turbo-line, heat-exchanger or internal-loss causes require separate diagnosis; do not order the former thermostat/water-pump bundle from this card.</x:v>
+        <x:v>PREVENTIVE REPLACEMENT: Replace timing chain, tensioner, guides, and sprockets at 80,000-100,000 miles BEFORE symptoms appear ($2,000-$4,000). This is the MOST important preventive maintenance on the Mk2 TTS. IF RATTLING: Do NOT delay—the chain can jump at any startup. Schedule repair immediately. Use ONLY the latest OEM revised tensioner (06K109467K). IF CHAIN JUMPED: Engine likely destroyed—compression test all cylinders. Rebuild ($5,000-$8,000) or replacement engine ($6,000-$12,000). PREVENTION: Change oil every 5,000 miles with high-quality synthetic. Low oil level accelerates tensioner wear.</x:v>
       </x:c>
       <x:c r="F88" s="9" t="n">
         <x:v>0</x:v>
@@ -17690,21 +20572,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="89" ht="976.7999877929688" hidden="0" customHeight="1">
       <x:c r="A89" s="40" t="n">
         <x:v>88</x:v>
       </x:c>
       <x:c r="B89" s="9" t="str">
-        <x:v>audi-s8-cylinder-demand-active-engine-mount-failure-4-cylinder-mode</x:v>
+        <x:v>audi-tts-water-pump-2009</x:v>
       </x:c>
       <x:c r="C89" s="9" t="str">
-        <x:v>2013-2015 | Audi | S8 | 4.0 TFSI vehicles with reproducible 1000-3000 rpm vibration; diagnose J931 before mount replacement | 4.0T TFSI V8</x:v>
+        <x:v>2012-2023 | Audi | TTS</x:v>
       </x:c>
       <x:c r="D89" s="9" t="str">
-        <x:v>2013-2015 S8 COD Vibration with J931 Basic-Setting Fault - Diagnosis Required</x:v>
+        <x:v>2012 / 2020-2023 TTS Coolant-Pump Update and Leak Diagnosis</x:v>
       </x:c>
       <x:c r="E89" s="9" t="str">
-        <x:v>Reproduce the vibration under Audi’s specified driving conditions and scan J931. If the bulletin applies, verify J931 software, perform the required SVM update and basic settings, align the exhaust without tension, repeat basic settings and follow the referenced diagnosis if vibration remains. Inspect mount hardware only after the software, calibration and exhaust path. Do not disable cylinder-on-demand or replace both mounts from the former card.</x:v>
+        <x:v>For a 2012 TTS, ask an Audi dealer to check the VIN and current campaign/action history for Update 19J2; the published update replaced the pump only when its exact criteria were met and does not promise current warranty coverage. For a 2020-2023 2.0L TTS, first exclude a low level caused by incomplete bleeding or an earlier repair, document and clean the suspected leak, refill to maximum and recheck after driving. Continue observation when no leak returns; replace only the component proven to leak when coolant reappears. Do not select a pump or thermostat assembly before VIN-, engine- and leak-specific diagnosis.</x:v>
       </x:c>
       <x:c r="F89" s="9" t="n">
         <x:v>0</x:v>
@@ -17713,1176 +20595,26 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" ht="765.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A90" s="40" t="n">
+    <x:row r="90" ht="198" hidden="0" customHeight="1">
+      <x:c r="A90" s="42" t="n">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="B90" s="9" t="str">
-        <x:v>audi-s8-d2-4-2-v8-timing-belt-tensioner-service</x:v>
-      </x:c>
-      <x:c r="C90" s="9" t="str">
-        <x:v>2001-2003 | Audi | S8 | 4.2L 40V V8 (AYS)</x:v>
-      </x:c>
-      <x:c r="D90" s="9" t="str">
-        <x:v>D2 4.2 V8 Timing Belt and Tensioner Service (Interference Engine)</x:v>
-      </x:c>
-      <x:c r="E90" s="9" t="str">
-        <x:v>Replace the timing belt as a complete kit — belt, tensioner, idler/guide rollers, and water pump — at or before Audi's interval (and by age regardless of mileage). Use genuine/OE-quality components and set cam/crank timing precisely with the correct locking tools; this is a front-of-engine ('service position') job. Inspect the exhaust-side chain tensioners while in there. Always confirm timing-belt history (with receipts) before buying a D2 S8; if unknown, do it immediately.</x:v>
-      </x:c>
-      <x:c r="F90" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G90" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" ht="844.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A91" s="40" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="B91" s="9" t="str">
-        <x:v>audi-s8-direct-injection-carbon-buildup-intake-valves</x:v>
-      </x:c>
-      <x:c r="C91" s="9" t="str">
-        <x:v>2013-2018 | Audi | S8 | 4.0T TFSI V8 (CTFA/CGTA/CWUC)</x:v>
-      </x:c>
-      <x:c r="D91" s="9" t="str">
-        <x:v>Direct-Injection Carbon Buildup on Intake Valves (Misfires / Rough Idle)</x:v>
-      </x:c>
-      <x:c r="E91" s="9" t="str">
-        <x:v>Confirm via borescope of the intake valves (and rule out coils/plugs/PCV first). The accepted repair is walnut-shell blasting: remove the intake manifold and media-blast the carbon off the valves and ports with crushed walnut shells, then reinstall with new intake gaskets. Replace spark plugs and inspect coils while the manifold is off. Preventively, keep up with oil changes, fix any PCV/oil-burning source, and consider periodic cleaning every ~40,000-60,000 miles. Catch-can solutions reduce future accumulation.</x:v>
-      </x:c>
-      <x:c r="F91" s="9" t="n">
+      <x:c r="B90" s="43" t="str">
+        <x:v>audi-tts-waterpump-housing-2009</x:v>
+      </x:c>
+      <x:c r="C90" s="43" t="str">
+        <x:v>2009-2024 | Audi | TTS | EA888</x:v>
+      </x:c>
+      <x:c r="D90" s="43" t="str">
+        <x:v>Water Pump and Thermostat Housing Failure</x:v>
+      </x:c>
+      <x:c r="E90" s="43" t="str">
+        <x:v>Replace water pump, thermostat, and housing as a complete assembly. Use metal-impeller aftermarket pump if available.</x:v>
+      </x:c>
+      <x:c r="F90" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G91" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" ht="686.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A92" s="40" t="n">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B92" s="9" t="str">
-        <x:v>audi-s8-front-suspension-control-arm-bushing-sway-bar-link-wear</x:v>
-      </x:c>
-      <x:c r="C92" s="9" t="str">
-        <x:v>2020-2021 | Audi | S8 | 2021 applicability through VIN 028090; localize noise acoustically before parts | 4.0T TFSI V8 mild-hybrid</x:v>
-      </x:c>
-      <x:c r="D92" s="9" t="str">
-        <x:v>2020-Early 2021 S8 Front Lower Guide-Link Hydro-Bushing Noise - Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E92" s="9" t="str">
-        <x:v>Confirm the VIN boundary, reproduce the noise and localize it with acoustic diagnostic equipment. Inspect the lower guide-link hydro-bushings and surrounding joints. If the hydro-bushing is confirmed, follow Audi’s paired replacement procedure; complete guide links may be required when prior pressing or rework prevents the specified repair. Align the vehicle as required. Do not order a ten-arm kit or sway-bar links from the former card.</x:v>
-      </x:c>
-      <x:c r="F92" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G92" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" ht="778.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A93" s="40" t="n">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="B93" s="9" t="str">
-        <x:v>audi-s8-high-pressure-fuel-pump-injector-internal-leak-causing-hard</x:v>
-      </x:c>
-      <x:c r="C93" s="9" t="str">
-        <x:v>2013-2018 | Audi | S8 | 4.0 TFSI; diagnosis requires ODIS values, software check and pressure-hold testing | 4.0T TFSI V8</x:v>
-      </x:c>
-      <x:c r="D93" s="9" t="str">
-        <x:v>2013-2018 S8 Warm-Soak Long-Crank or No-Start - Fuel Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E93" s="9" t="str">
-        <x:v>Have the dealer read DTCs and ODIS fuel-in-oil value, verify ECM software and perform Audi’s high- and low-pressure holding tests. If high-pressure behavior is abnormal, borescope the combustion chamber to identify a leaking injector. If low-side pressure builds correctly but drops more than 1.5 bar in the first 15 minutes, Audi says at least one HPFP may be leaking and directs replacement of both pumps plus an oil change. Select no pump or injector until the test identifies the path.</x:v>
-      </x:c>
-      <x:c r="F93" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G93" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" ht="673.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A94" s="40" t="n">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B94" s="9" t="str">
-        <x:v>audi-s8-mmi-upper-display-backup-camera-black-screen</x:v>
-      </x:c>
-      <x:c r="C94" s="9" t="str">
-        <x:v>2020-2026 | Audi | S8 | VIN-specific NHTSA 25V900 / Audi 90TV; verify open recall | 4.0T TFSI V8 mild-hybrid</x:v>
-      </x:c>
-      <x:c r="D94" s="9" t="str">
-        <x:v>2020-2026 S8 Rearview/Top-View Camera Image May Not Display - Recall 25V900</x:v>
-      </x:c>
-      <x:c r="E94" s="9" t="str">
-        <x:v>Check the VIN in Audi’s recall/service-campaign lookup and schedule the free 90TV software remedy if open. Use extra care when reversing until repaired and visually check the area around the vehicle. A completely dead or rebooting MMI display, missing instrument-cluster data, wiring fault or hardware failure requires separate diagnosis and must not be attributed to this recall without VIN and symptom confirmation.</x:v>
-      </x:c>
-      <x:c r="F94" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G94" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" ht="792" hidden="0" customHeight="1">
-      <x:c r="A95" s="40" t="n">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="B95" s="9" t="str">
-        <x:v>audi-s8-oil-consumption-2013</x:v>
-      </x:c>
-      <x:c r="C95" s="9" t="str">
-        <x:v>2020-2023 | Audi | S8 | EA825 4.0L; confirm VIN, engine and measured consumption under Audi procedure | 4.0T TFSI V8 mild-hybrid (EA825)</x:v>
-      </x:c>
-      <x:c r="D95" s="9" t="str">
-        <x:v>2020-2023 S8 High Oil Consumption and Updated Piston Rings - Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E95" s="9" t="str">
-        <x:v>Document oil-level warnings, mileage, top-up quantity, leaks and oil specification, then have an Audi dealer perform the authorized oil-consumption measurement. Repair is justified only when the measured result exceeds the applicable owner-manual limit and other leakage or operating causes are excluded. If TSB 2071114 applies, follow its VIN/engine-specific piston, ring and connecting-rod procedure. Do not change oil viscosity or authorize internal-engine work solely from the former card.</x:v>
-      </x:c>
-      <x:c r="F95" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G95" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" ht="646.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A96" s="40" t="n">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="B96" s="9" t="str">
-        <x:v>audi-s8-pcv-oil-separator-failure-excessive-crankcase-vacuum</x:v>
-      </x:c>
-      <x:c r="C96" s="9" t="str">
-        <x:v>2013-2016 | Audi | S8 | 4.0 TFSI; confirm warm-idle sound and filler-cap response before oil-separator replacement | 4.0T TFSI V8</x:v>
-      </x:c>
-      <x:c r="D96" s="9" t="str">
-        <x:v>2013-2016 S8 Warm-Idle Whistle from Crankcase Breather Leak - Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E96" s="9" t="str">
-        <x:v>Compare the sound with Audi’s reference condition and check whether opening the oil filler cap changes it. Read P2279/P0507 and rule out other intake leaks. When the sound matches and is affected by the filler-cap check, follow Audi’s oil-separator breather replacement procedure and renew required seals/consumables by VIN. Do not diagnose by oil-cap feel alone or order the former five-item parts list.</x:v>
-      </x:c>
-      <x:c r="F96" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G96" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" ht="594" hidden="0" customHeight="1">
-      <x:c r="A97" s="40" t="n">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="B97" s="9" t="str">
-        <x:v>audi-s8-porous-high-pressure-fuel-supply-line-recall-nhtsa-19v057000</x:v>
-      </x:c>
-      <x:c r="C97" s="9" t="str">
-        <x:v>2013-2016 | Audi | S8 | VIN-specific NHTSA 19V057 / Audi 20BM; verify open recall | 4.0T TFSI V8</x:v>
-      </x:c>
-      <x:c r="D97" s="9" t="str">
-        <x:v>2013-2016 S8 Porous Fuel-Pump Supply Line / Fire Risk - Recall 19V057</x:v>
-      </x:c>
-      <x:c r="E97" s="9" t="str">
-        <x:v>Check the VIN for open recall 20BM and contact an Audi dealer without delay. The free remedy installs a fuel-pressure damper in the low-pressure fuel supply inside the tank. If fuel odor or visible leakage is present, avoid ignition sources, do not continue driving, and arrange dealer inspection/towing as appropriate. Do not buy a retail line or damper from the former card.</x:v>
-      </x:c>
-      <x:c r="F97" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G97" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" ht="211.1999969482422" hidden="0" customHeight="1">
-      <x:c r="A98" s="40" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="B98" s="9" t="str">
-        <x:v>audi-s8-torque-converter-2013</x:v>
-      </x:c>
-      <x:c r="C98" s="9" t="str">
-        <x:v>2013-2024 | Audi | S8</x:v>
-      </x:c>
-      <x:c r="D98" s="9" t="str">
-        <x:v>ZF 8-Speed Torque Converter and Valve Body Issues</x:v>
-      </x:c>
-      <x:c r="E98" s="9" t="str">
-        <x:v>Replace torque converter and service valve body. Full ZF fluid and filter change every 50,000 miles extends transmission life.</x:v>
-      </x:c>
-      <x:c r="F98" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G98" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" ht="712.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A99" s="40" t="n">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="B99" s="9" t="str">
-        <x:v>audi-s8-turbo-oil-strainer-2013</x:v>
-      </x:c>
-      <x:c r="C99" s="9" t="str">
-        <x:v>2013-2017 | Audi | S8 | VIN-specific NHTSA 22V178 / Audi 21H7; verify open recall | 4.0T TFSI V8</x:v>
-      </x:c>
-      <x:c r="D99" s="9" t="str">
-        <x:v>2013-2017 S8 Blocked Turbocharger Oil Strainer / Stall Risk - Recall 22V178</x:v>
-      </x:c>
-      <x:c r="E99" s="9" t="str">
-        <x:v>Check the VIN for open recall 21H7 and schedule the free Audi dealer remedy, which replaces the oil strainer and performs an oil change. If EPC, MIL or oil warning lights appear with unusual turbo noise, extended cranking, rough idle, loss of power or stalling, stop safely and arrange diagnosis. Turbo damage, warranty eligibility and any additional repair must be assessed by VIN and inspection; do not buy the former retail strainer.</x:v>
-      </x:c>
-      <x:c r="F99" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G99" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" ht="950.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A100" s="40" t="n">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="B100" s="9" t="str">
-        <x:v>audi-s8-water-to-air-intercooler-internal-coolant-leak</x:v>
-      </x:c>
-      <x:c r="C100" s="9" t="str">
-        <x:v>2013-2018 | Audi | S8 | 4.0T TFSI V8 (CTFA/CGTA/CWUC)</x:v>
-      </x:c>
-      <x:c r="D100" s="9" t="str">
-        <x:v>Water-to-Air Intercooler Internal Coolant Leak (Coolant into Intake)</x:v>
-      </x:c>
-      <x:c r="E100" s="9" t="str">
-        <x:v>Confirm the source: pressure-test the cooling system and inspect the charge piping/intercooler outlet for coolant residue; scope for white smoke and coolant on the intake side rather than an external leak. Replace the water-to-air intercooler/charge-air cooler unit (genuine OEM core). Because access requires removing intake components in the valley, it is standard practice to also replace the turbo oil strainer, coolant valves, and PCV/oil separator while in there. Refill and bleed the cooling system per procedure. This is a high-difficulty job typically done by a specialist or dealer.</x:v>
-      </x:c>
-      <x:c r="F100" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G100" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" ht="475.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A101" s="40" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="B101" s="9" t="str">
-        <x:v>audi-sq2-ea888-2-0-tfsi-coolant-leak-from-water-pump-thermostat-housi</x:v>
-      </x:c>
-      <x:c r="C101" s="9" t="str">
-        <x:v>2019-2024 | Audi | SQ2 | 2.0 TFSI quattro | EA888 2.0 TFSI Gen3</x:v>
-      </x:c>
-      <x:c r="D101" s="9" t="str">
-        <x:v>EA888 2.0 TFSI coolant leak from water pump / thermostat housing</x:v>
-      </x:c>
-      <x:c r="E101" s="9" t="str">
-        <x:v>Replace the failed water pump / thermostat housing assembly, ideally with the latest revised, more heat-resistant unit; many shops fit an upgraded repair kit and a new gasket. Catch it early by watching for slowly dropping coolant level and a faint sweet smell. Combine with a coolant flush and refill.</x:v>
-      </x:c>
-      <x:c r="F101" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G101" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" ht="396" hidden="0" customHeight="1">
-      <x:c r="A102" s="40" t="n">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="B102" s="9" t="str">
-        <x:v>audi-sq2-electro-mechanical-parking-brake-brake-pedal-weld-recalls</x:v>
-      </x:c>
-      <x:c r="C102" s="9" t="str">
-        <x:v>2019-2020 | Audi | SQ2</x:v>
-      </x:c>
-      <x:c r="D102" s="9" t="str">
-        <x:v>Electro-mechanical parking brake and brake-pedal weld recalls (early build)</x:v>
-      </x:c>
-      <x:c r="E102" s="9" t="str">
-        <x:v>These are recall items — have the VIN checked against the Audi/DVSA recall database and any open campaign rectified free of charge at a dealer. Report any abnormal parking-brake behaviour or a soft/abnormal brake pedal immediately.</x:v>
-      </x:c>
-      <x:c r="F102" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G102" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" ht="475.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A103" s="40" t="n">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="B103" s="9" t="str">
-        <x:v>audi-sq2-internal-fuse-box-wiring-harness-can-work-loose-causing-sudd</x:v>
-      </x:c>
-      <x:c r="C103" s="9" t="str">
-        <x:v>2022-2023 | Audi | SQ2 | 2.0 TFSI</x:v>
-      </x:c>
-      <x:c r="D103" s="9" t="str">
-        <x:v>2022-2023 Audi SQ2 Interior Fuse-Carrier Recall GAI-3692</x:v>
-      </x:c>
-      <x:c r="E103" s="9" t="str">
-        <x:v>Check the VIN and open-campaign status with an authorised Audi dealer in the vehicle’s market. The campaign remedy is dealer inspection and correction of the fuse-carrier power connection. Do not replace a fuse box or wiring harness solely from a warning lamp or this model-year summary.</x:v>
-      </x:c>
-      <x:c r="F103" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G103" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="104" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A104" s="40" t="n">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B104" s="9" t="str">
-        <x:v>audi-sq2-mmi-infotainment-freezing-rebooting-lost-settings</x:v>
-      </x:c>
-      <x:c r="C104" s="9" t="str">
-        <x:v>2019-2024 | Audi | SQ2</x:v>
-      </x:c>
-      <x:c r="D104" s="9" t="str">
-        <x:v>MMI infotainment freezing, rebooting and lost settings</x:v>
-      </x:c>
-      <x:c r="E104" s="9" t="str">
-        <x:v>A forced MMI restart (press and hold the on/off or volume control ~10 seconds until it reboots) clears many transient faults. Persistent issues are usually resolved by a dealer software/firmware update; check for any applicable MMI update campaigns. Only in rare cases is the MMI head unit itself replaced.</x:v>
-      </x:c>
-      <x:c r="F104" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G104" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="105" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A105" s="40" t="n">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="B105" s="9" t="str">
-        <x:v>audi-sq2-pcv-crankcase-ventilation-valve-diaphragm-failure-causing-ro</x:v>
-      </x:c>
-      <x:c r="C105" s="9" t="str">
-        <x:v>2019-2024 | Audi | SQ2 | EA888 2.0 TFSI Gen3</x:v>
-      </x:c>
-      <x:c r="D105" s="9" t="str">
-        <x:v>PCV / crankcase ventilation valve diaphragm failure causing rough idle and lean-running codes</x:v>
-      </x:c>
-      <x:c r="E105" s="9" t="str">
-        <x:v>Replace the PCV valve (or the valve-cover assembly that integrates it) with the latest revised part; some owners fit a catch-can to reduce recurrence. A quick field test — briefly covering the bleeder hole on the cap to see if idle stabilises or whistling stops — helps confirm before replacement.</x:v>
-      </x:c>
-      <x:c r="F105" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G105" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" ht="752.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A106" s="40" t="n">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="B106" s="9" t="str">
-        <x:v>audi-sq2-s-tronic-7-speed-wet-clutch-transmission-jerky-low-speed-shi</x:v>
-      </x:c>
-      <x:c r="C106" s="9" t="str">
-        <x:v>2019-2024 | Audi | SQ2 | 7-speed S tronic | DQ381 / 0GC 7-speed wet-clutch S tronic</x:v>
-      </x:c>
-      <x:c r="D106" s="9" t="str">
-        <x:v>S tronic (DQ381) 7-speed wet-clutch transmission: jerky low-speed shifts, hesitation and limp mode</x:v>
-      </x:c>
-      <x:c r="E106" s="9" t="str">
-        <x:v>First step is a proper DSG fluid-and-filter service (the wet-clutch unit needs periodic transmission oil changes — many owners do it around 40k miles even though intervals can be longer). Have the TCU scanned for stored codes; sensor or mechatronic valve replacement and re-coding/adaptation resolves many cases, while severe cases need a full mechatronic unit or clutch-pack replacement. Insist on a software/adaptation update at the dealer for driveability complaints.</x:v>
-      </x:c>
-      <x:c r="F106" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G106" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107" ht="541.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A107" s="40" t="n">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="B107" s="9" t="str">
-        <x:v>audi-sq5-air-suspension-2018</x:v>
-      </x:c>
-      <x:c r="C107" s="9" t="str">
-        <x:v>2018-2025 | Audi | SQ5</x:v>
-      </x:c>
-      <x:c r="D107" s="9" t="str">
-        <x:v>Air-Suspension Warning with C1260F0 or U112100 Communication Fault</x:v>
-      </x:c>
-      <x:c r="E107" s="9" t="str">
-        <x:v>Inspect the wiring and connector contacts between J775 and J1135 first. If no wiring fault is found, clear a first passive or sporadic fault and release the vehicle. Replace J1135 for an active or static fault, or when the same passive or sporadic fault returns a second time, following Audi workshop information and VIN-specific ETKA data.</x:v>
-      </x:c>
-      <x:c r="F107" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G107" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" ht="924" hidden="0" customHeight="1">
-      <x:c r="A108" s="40" t="n">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="B108" s="9" t="str">
-        <x:v>audi-sq5-carbon-buildup-2014</x:v>
-      </x:c>
-      <x:c r="C108" s="9" t="str">
-        <x:v>2014-2025 | Audi | SQ5 | 3.0T Supercharged, 3.0T</x:v>
-      </x:c>
-      <x:c r="D108" s="9" t="str">
-        <x:v>Fuel-Quality or Deposit-Related Rough Running and Misfire Diagnosis</x:v>
-      </x:c>
-      <x:c r="E108" s="9" t="str">
-        <x:v>Confirm fuel quality, symptoms and stored DTCs before replacing or cleaning components. If contaminated gasoline is suspected, advise changing the fuel source; if low detergent quality is suspected, Audi recommends Top Tier detergent gasoline. Continue workshop diagnosis if symptoms persist. On 2018-2025 EA839 SQ5 models, do not recommend unapproved cleaners or additives; follow the owner manual and use only Audi-approved petrol additives. Do not prescribe routine walnut blasting, a catch can or chemical cleaning from this record.</x:v>
-      </x:c>
-      <x:c r="F108" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G108" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" ht="765.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A109" s="40" t="n">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="B109" s="9" t="str">
-        <x:v>audi-sq5-pcv-valve-2014</x:v>
-      </x:c>
-      <x:c r="C109" s="9" t="str">
-        <x:v>2014-2017 | Audi | SQ5 | 3.0T Supercharged</x:v>
-      </x:c>
-      <x:c r="D109" s="9" t="str">
-        <x:v>P052E00 Crankcase-Breather Membrane or Elbow Fault</x:v>
-      </x:c>
-      <x:c r="E109" s="9" t="str">
-        <x:v>Use Audi hand-vacuum test to distinguish a membrane leak from an elbow fault. If indicated, remove the compressor or intake manifold and inspect the membrane and the breather two metal plates. Use repair kit 06E103772H only for a confirmed membrane or plate fault. For a confirmed elbow fault, replace elbow 06E103402 and spring clip N10769401 rather than automatically replacing the complete breather. Verify current part data in ETKA before ordering.</x:v>
-      </x:c>
-      <x:c r="F109" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G109" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" ht="171.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A110" s="40" t="n">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="B110" s="9" t="str">
-        <x:v>audi-sq5-supercharger-2014</x:v>
-      </x:c>
-      <x:c r="C110" s="9" t="str">
-        <x:v>2014-2018 | Audi | SQ5 | 3.0T</x:v>
-      </x:c>
-      <x:c r="D110" s="9" t="str">
-        <x:v>3.0T Supercharger Bearing and Intercooler Pump Failure</x:v>
-      </x:c>
-      <x:c r="E110" s="9" t="str">
-        <x:v>Replace supercharger nose bearing kit. Replace intercooler pump if failing. Service supercharger belt tension.</x:v>
-      </x:c>
-      <x:c r="F110" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G110" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" ht="844.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A111" s="40" t="n">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="B111" s="9" t="str">
-        <x:v>audi-sq5-supercharger-oil-leak-2014</x:v>
-      </x:c>
-      <x:c r="C111" s="9" t="str">
-        <x:v>2014-2017 | Audi | SQ5 | Premium Plus, Prestige | 3.0T Supercharged, 3.0T</x:v>
-      </x:c>
-      <x:c r="D111" s="9" t="str">
-        <x:v>Supercharger Seal and Gasket Oil Leaks (3.0T)</x:v>
-      </x:c>
-      <x:c r="E111" s="9" t="str">
-        <x:v>JHM Motorsports sells a complete supercharger replacement seal and gasket kit for the Eaton unit in the 3.0T. Replacing all seals at once is recommended since the supercharger must be removed for access. Nose cone seal, rotor shaft seals, and manifold gaskets should all be replaced together ($300-$500 in parts, $600-$1,200 labor). While the supercharger is off, also replace the PCV valve and perform carbon cleaning. For valve cover gasket leaks (separate issue), budget $400-$800 parts and labor. Monitor oil level weekly if leaks are present.</x:v>
-      </x:c>
-      <x:c r="F111" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G111" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="112" ht="1122" hidden="0" customHeight="1">
-      <x:c r="A112" s="40" t="n">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="B112" s="9" t="str">
-        <x:v>audi-sq5-water-pump-2018</x:v>
-      </x:c>
-      <x:c r="C112" s="9" t="str">
-        <x:v>2018-2024 | Audi | SQ5 | 3.0T</x:v>
-      </x:c>
-      <x:c r="D112" s="9" t="str">
-        <x:v>Mechanical Coolant-Pump Leak with Possible N649 Vacuum-System Contamination</x:v>
-      </x:c>
-      <x:c r="E112" s="9" t="str">
-        <x:v>Confirm the complaint and exact vehicle criteria first. Inspect the vacuum line and N649 for coolant, then clean and dry suspected leakage, fill the cooling system correctly, inspect at idle and around 2,500 rpm, and pressure-test according to Audi workshop information. If no leak is reproduced, observe the vehicle without replacing parts. If the pump leak is confirmed, replace the failed component and document it. If fresh coolant has entered the vacuum system, inspect the remaining Audi checkpoints and replace only contaminated components; if the downstream checkpoints are clean, replace N649 and clean the line between the pump and N649 as directed by TSB 2070349/5.</x:v>
-      </x:c>
-      <x:c r="F112" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G112" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" ht="673.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A113" s="40" t="n">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="B113" s="9" t="str">
-        <x:v>audi-sq7-air-susp-strut-2020</x:v>
-      </x:c>
-      <x:c r="C113" s="9" t="str">
-        <x:v>2020-2025 | Audi | SQ7 | 4.0T</x:v>
-      </x:c>
-      <x:c r="D113" s="9" t="str">
-        <x:v>2020-2025 SQ7 Air-Suspension C1260F0/U112100 Communication Fault - Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E113" s="9" t="str">
-        <x:v>Inspect the wiring and connector contacts between J775 and J1135 first. If no wiring fault is found, clear a first passive or sporadic fault and release the vehicle. Replace J1135 for an active or static fault, or when the same passive or sporadic fault returns a second time, following Audi workshop information and VIN-specific ETKA data. Do not replace an air spring, strut or compressor assembly solely from the warning.</x:v>
-      </x:c>
-      <x:c r="F113" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G113" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" ht="1122" hidden="0" customHeight="1">
-      <x:c r="A114" s="40" t="n">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="B114" s="9" t="str">
-        <x:v>audi-sq7-air-suspension-2020</x:v>
-      </x:c>
-      <x:c r="C114" s="9" t="str">
-        <x:v>2020-2024 | Audi | SQ7 | Premium Plus, Prestige | 4.0T</x:v>
-      </x:c>
-      <x:c r="D114" s="9" t="str">
-        <x:v>Adaptive Air Suspension Compressor and Air Spring Failures</x:v>
-      </x:c>
-      <x:c r="E114" s="9" t="str">
-        <x:v>Diagnose specific failed component: air springs leak most commonly, followed by compressor burnout, valve block faults, and height sensor failures. Air spring replacement ($800-$1,500 per corner at independent shop). Compressor replacement ($1,200-$2,500 installed). Valve block: $500-$1,000. Height sensor: $200-$400. Check for air leaks first using soapy water spray before replacing the compressor - a $200 air spring seal may be causing a $2,000 compressor to overwork and fail. Aftermarket solutions from Arnott offer cost savings. Converting to conventional springs ($1,500-$2,500) eliminates future air suspension costs but sacrifices ride height adjustment.</x:v>
-      </x:c>
-      <x:c r="F114" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G114" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A115" s="40" t="n">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="B115" s="9" t="str">
-        <x:v>audi-sq7-mmi-mib3-freeze-2020</x:v>
-      </x:c>
-      <x:c r="C115" s="9" t="str">
-        <x:v>2020-2026 | Audi | SQ7</x:v>
-      </x:c>
-      <x:c r="D115" s="9" t="str">
-        <x:v>2020-2026 Audi SQ7 Rearview Camera Software Recall 25V900 / 90TV</x:v>
-      </x:c>
-      <x:c r="E115" s="9" t="str">
-        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install the more robust driver-assistance software update free of charge. Until repaired, use extra caution when reversing and do not treat a restart, bus sleep or temporary image recovery as completion of the recall.</x:v>
-      </x:c>
-      <x:c r="F115" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G115" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116" ht="990" hidden="0" customHeight="1">
-      <x:c r="A116" s="40" t="n">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="B116" s="9" t="str">
-        <x:v>audi-sq7-valve-cover-oil-leak-2020</x:v>
-      </x:c>
-      <x:c r="C116" s="9" t="str">
-        <x:v>2020-2024 | Audi | SQ7 | 4.0T</x:v>
-      </x:c>
-      <x:c r="D116" s="9" t="str">
-        <x:v>2020-2024 SQ7 4.0L High Oil Consumption and Piston-Ring Diagnosis - TSB 2071114/5</x:v>
-      </x:c>
-      <x:c r="E116" s="9" t="str">
-        <x:v>First inspect for visible engine-oil traces or leaks. Have an Audi dealer perform the authorized ODIS oil-consumption measurement, preserve and upload both test logs, and document the requested driving-profile data. Internal-engine repair is justified only when measured consumption exceeds the applicable limit and no other cause is found. If every TSB gate is met, follow Audi's VIN-, engine-code- and power-class-specific procedure for replacement of all eight pistons and piston rings, using current ETKA and ELSA information. Do not diagnose valve-cover gaskets or turbocharger seals from oil consumption alone.</x:v>
-      </x:c>
-      <x:c r="F116" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G116" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="117" ht="686.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A117" s="40" t="n">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="B117" s="9" t="str">
-        <x:v>audi-sq8-air-susp-compressor-2020</x:v>
-      </x:c>
-      <x:c r="C117" s="9" t="str">
-        <x:v>2020-2025 | Audi | SQ8</x:v>
-      </x:c>
-      <x:c r="D117" s="9" t="str">
-        <x:v>2020-2025 SQ8 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
-      </x:c>
-      <x:c r="E117" s="9" t="str">
-        <x:v>Inspect the wiring and connector contacts between J775 and J1135 before replacing a component. For a first passive or sporadic occurrence, clear the fault and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after wiring inspection, Audi directs replacement of J1135 under current repair and parts information. Do not buy struts, springs or a compressor solely from this warning.</x:v>
-      </x:c>
-      <x:c r="F117" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G117" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="118" ht="831.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A118" s="40" t="n">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="B118" s="9" t="str">
-        <x:v>audi-sq8-air-suspension-2020</x:v>
-      </x:c>
-      <x:c r="C118" s="9" t="str">
-        <x:v>2020-2024 | Audi | SQ8 | Premium Plus, Prestige | 4.0T</x:v>
-      </x:c>
-      <x:c r="D118" s="9" t="str">
-        <x:v>Adaptive Air Suspension Compressor and Air Spring Failures</x:v>
-      </x:c>
-      <x:c r="E118" s="9" t="str">
-        <x:v>Same diagnostic and repair approach as SQ7 (shared 4M platform). Isolate the failed component: air springs ($800-$1,500 per corner), compressor ($1,200-$2,500), valve block ($500-$1,000), or height sensor ($200-$400). Always check for air leaks before replacing the compressor. Aftermarket air suspension components from Arnott/Strutmasters offer 40-50% savings over OEM. Annual inspection of air springs for cracking recommended, especially in hot climates where UV and heat accelerate rubber degradation.</x:v>
-      </x:c>
-      <x:c r="F118" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G118" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="119" ht="448.79998779296875" hidden="0" customHeight="1">
-      <x:c r="A119" s="40" t="n">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="B119" s="9" t="str">
-        <x:v>audi-sq8-airbag-mount-2023</x:v>
-      </x:c>
-      <x:c r="C119" s="9" t="str">
-        <x:v>2023-2024 | Audi | SQ8 | 4.0T V8</x:v>
-      </x:c>
-      <x:c r="D119" s="9" t="str">
-        <x:v>2023-2024 SQ8 Driver-Seat Side-Airbag Mount Recall 69GA (23V868)</x:v>
-      </x:c>
-      <x:c r="E119" s="9" t="str">
-        <x:v>Check the VIN for open Audi recall 69GA and have an authorized dealer inspect the driver-seat side-airbag installation. If needed, the dealer will reinstall the airbag correctly; the recall filing says no parts are replaced. A clock spring or generic airbag part is not the recall remedy.</x:v>
-      </x:c>
-      <x:c r="F119" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G119" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="120" ht="580.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A120" s="40" t="n">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B120" s="9" t="str">
-        <x:v>audi-sq8-mmi-mib3-freeze-2020</x:v>
-      </x:c>
-      <x:c r="C120" s="9" t="str">
-        <x:v>2020-2026 | Audi | SQ8 | 4.0T V8</x:v>
-      </x:c>
-      <x:c r="D120" s="9" t="str">
-        <x:v>2020-2026 SQ8 Rearview Camera Software Recall 90TV (25V900)</x:v>
-      </x:c>
-      <x:c r="E120" s="9" t="str">
-        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install more robust driver-assistance software free of charge. Until repaired, use extra caution when reversing and do not treat a restart, bus sleep or temporary image recovery as completion of the recall. A generic scan tool or head-unit replacement is not the recall remedy.</x:v>
-      </x:c>
-      <x:c r="F120" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G120" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="121" ht="567.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A121" s="40" t="n">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="B121" s="9" t="str">
-        <x:v>audi-sq8-turbo-coolant-2020</x:v>
-      </x:c>
-      <x:c r="C121" s="9" t="str">
-        <x:v>2020-2021 | Audi | SQ8 | 4.0T V8</x:v>
-      </x:c>
-      <x:c r="D121" s="9" t="str">
-        <x:v>2020-Early 2021 SQ8 Red Coolant Warning - Check G407 per TSB 2062951/4</x:v>
-      </x:c>
-      <x:c r="E121" s="9" t="str">
-        <x:v>Have the vehicle checked with Audi Guided Fault Finding and inspect G407 and its O-ring. Replace G407 only if the O-ring is damaged or pinched and the diagnosis matches the bulletin; follow the related Audi diagnostic path if additional listed faults are stored. Do not replace turbo coolant hoses, pumps or other cooling parts from this card alone.</x:v>
-      </x:c>
-      <x:c r="F121" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G121" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="122" ht="250.8000030517578" hidden="0" customHeight="1">
-      <x:c r="A122" s="40" t="n">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="B122" s="9" t="str">
-        <x:v>audi-tt-absesp-control-module-failure-2000</x:v>
-      </x:c>
-      <x:c r="C122" s="9" t="str">
-        <x:v>2000-2001 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D122" s="9" t="str">
-        <x:v>Driver Airbag Inflator May Deploy Improperly (Recall 21V470 / 69CJ)</x:v>
-      </x:c>
-      <x:c r="E122" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the driver frontal-airbag inflator with an alternative inflator free of charge under campaign 69CJ.</x:v>
-      </x:c>
-      <x:c r="F122" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G122" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="123" ht="277.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A123" s="40" t="n">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="B123" s="9" t="str">
-        <x:v>audi-tt-cam-follower-2008</x:v>
-      </x:c>
-      <x:c r="C123" s="9" t="str">
-        <x:v>2000-2000 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D123" s="9" t="str">
-        <x:v>Fuel-Line Assembly Can Leak (Recall 99V222)</x:v>
-      </x:c>
-      <x:c r="E123" s="9" t="str">
-        <x:v>Check VIN eligibility and campaign completion. Audi dealers replace the fuel-line assembly free of charge under recall 99V222. Stop driving if fuel odor or leakage is present.</x:v>
-      </x:c>
-      <x:c r="F123" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G123" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="124" ht="198" hidden="0" customHeight="1">
-      <x:c r="A124" s="40" t="n">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="B124" s="9" t="str">
-        <x:v>audi-tt-coil-pack-failure-and-2000</x:v>
-      </x:c>
-      <x:c r="C124" s="9" t="str">
-        <x:v>2000-2001 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D124" s="9" t="str">
-        <x:v>Rear Track-Control Arm Corrosion Can Restrict Movement (Recall 01V325)</x:v>
-      </x:c>
-      <x:c r="E124" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the rear track-control arms free of charge under recall 01V325.</x:v>
-      </x:c>
-      <x:c r="F124" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G124" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="125" ht="264" hidden="0" customHeight="1">
-      <x:c r="A125" s="40" t="n">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="B125" s="9" t="str">
-        <x:v>audi-tt-dsg-mechatronic-2008</x:v>
-      </x:c>
-      <x:c r="C125" s="9" t="str">
-        <x:v>2004-2004 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D125" s="9" t="str">
-        <x:v>Direct-Shift Gearbox Clutch Weld Can Lose Drive Torque (Recall 04V007)</x:v>
-      </x:c>
-      <x:c r="E125" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers replace the affected clutch free of charge under recall 04V007. If drive torque is lost, move out of traffic safely and arrange recovery.</x:v>
-      </x:c>
-      <x:c r="F125" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G125" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="126" ht="356.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A126" s="40" t="n">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="B126" s="9" t="str">
-        <x:v>audi-tt-dsg-transmission-2008</x:v>
-      </x:c>
-      <x:c r="C126" s="9" t="str">
-        <x:v>2009-2009 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D126" s="9" t="str">
-        <x:v>DSG Temperature-Sensor Wiring Can Trigger an Abrupt Shift to Neutral (Recall 09V333)</x:v>
-      </x:c>
-      <x:c r="E126" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers reprogram the transmission control module with updated software free of charge under recall 09V333. If the gear indicator flashes or neutral engages unexpectedly, stop safely.</x:v>
-      </x:c>
-      <x:c r="F126" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G126" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="127" ht="303.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A127" s="40" t="n">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="B127" s="9" t="str">
-        <x:v>audi-tt-front-control-arm-bushings-2000</x:v>
-      </x:c>
-      <x:c r="C127" s="9" t="str">
-        <x:v>2000-2000 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D127" s="9" t="str">
-        <x:v>High-Speed Directional-Stability Remedy (Recall 99V300)</x:v>
-      </x:c>
-      <x:c r="E127" s="9" t="str">
-        <x:v>Verify campaign completion with Audi. The factory remedy installs revised stabilizers, front control arms, firmer shock absorbers, and a rear spoiler as specified for the drivetrain configuration.</x:v>
-      </x:c>
-      <x:c r="F127" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G127" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="128" ht="237.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A128" s="40" t="n">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="B128" s="9" t="str">
-        <x:v>audi-tt-haldex-awd-coupling-pumpcontroller-2000</x:v>
-      </x:c>
-      <x:c r="C128" s="9" t="str">
-        <x:v>2008-2010 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D128" s="9" t="str">
-        <x:v>Fuel-Tank Ventilation Valve Can Allow Fuel Leakage (Recall 09V377)</x:v>
-      </x:c>
-      <x:c r="E128" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel-tank ventilation valve with the improved valve free of charge under recall 09V377.</x:v>
-      </x:c>
-      <x:c r="F128" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G128" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="129" ht="184.8000030517578" hidden="0" customHeight="1">
-      <x:c r="A129" s="40" t="n">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="B129" s="9" t="str">
-        <x:v>audi-tt-high-speed-stability-recall-for-2000</x:v>
-      </x:c>
-      <x:c r="C129" s="9" t="str">
-        <x:v>2016-2019 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D129" s="9" t="str">
-        <x:v>Fuel Tank Can Be Damaged by Heat-Shield Bracket in a Crash (Recall 20V076 / 20BX)</x:v>
-      </x:c>
-      <x:c r="E129" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers install a protective cap on the heat-shield bracket free of charge under campaign 20BX.</x:v>
-      </x:c>
-      <x:c r="F129" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G129" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="130" ht="237.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A130" s="40" t="n">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="B130" s="9" t="str">
-        <x:v>audi-tt-instrument-cluster-pixel-failure-2000</x:v>
-      </x:c>
-      <x:c r="C130" s="9" t="str">
-        <x:v>2016-2016 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D130" s="9" t="str">
-        <x:v>Front-Passenger Airbag Module May Explode or Deploy Improperly (Recall 22V543 / 69DY)</x:v>
-      </x:c>
-      <x:c r="E130" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the front-passenger airbag module free of charge under campaign 69DY/61C1.</x:v>
-      </x:c>
-      <x:c r="F130" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G130" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="131" ht="224.39999389648438" hidden="0" customHeight="1">
-      <x:c r="A131" s="40" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="B131" s="9" t="str">
-        <x:v>audi-tt-magnetic-ride-2008</x:v>
-      </x:c>
-      <x:c r="C131" s="9" t="str">
-        <x:v>2023-2023 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D131" s="9" t="str">
-        <x:v>Passenger-Seat Occupant Detection Connection Can Disable Airbag (Recall 24V251 / 69GU)</x:v>
-      </x:c>
-      <x:c r="E131" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers replace the passenger-seat occupant-detection control module free of charge under campaign 69GU.</x:v>
-      </x:c>
-      <x:c r="F131" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G131" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="132" ht="726" hidden="0" customHeight="1">
-      <x:c r="A132" s="40" t="n">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="B132" s="9" t="str">
-        <x:v>audi-tt-tail-light-corrosion-2008</x:v>
-      </x:c>
-      <x:c r="C132" s="9" t="str">
-        <x:v>2008-2015 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D132" s="9" t="str">
-        <x:v>Tail Light Electrical Connector Corrosion (Mk2)</x:v>
-      </x:c>
-      <x:c r="E132" s="9" t="str">
-        <x:v>Remove tail light assembly, inspect electrical connector for green corrosion. CLEAN connector with electrical contact cleaner and wire brush ($20 DIY). Apply dielectric grease to prevent future corrosion ($10). If connector is severely corroded: Replace pigtail connector ($50-$100 parts). Improve tail light seal with silicone sealant around housing ($15). This is a DIY-friendly repair taking 1-2 hours. If paying shop, costs $150-$300. Address early before corrosion causes shorts.</x:v>
-      </x:c>
-      <x:c r="F132" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G132" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="133" ht="171.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A133" s="40" t="n">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="B133" s="9" t="str">
-        <x:v>audi-tt-water-pump-2008</x:v>
-      </x:c>
-      <x:c r="C133" s="9" t="str">
-        <x:v>2008-2008 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D133" s="9" t="str">
-        <x:v>C-Pillar Trim Cover Can Detach During Belt-Tensioner Deployment (Recall 08V064)</x:v>
-      </x:c>
-      <x:c r="E133" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers install improved C-pillar trim clips free of charge under recall 08V064.</x:v>
-      </x:c>
-      <x:c r="F133" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G133" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="134" ht="1161.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A134" s="40" t="n">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="B134" s="9" t="str">
-        <x:v>audi-tts-cam-follower-hpfp-2009</x:v>
-      </x:c>
-      <x:c r="C134" s="9" t="str">
-        <x:v>2009-2015 | Audi | TTS | TTS | EA888</x:v>
-      </x:c>
-      <x:c r="D134" s="9" t="str">
-        <x:v>HPFP Cam Follower Wear and High-Pressure Fuel Pump Failure (Mk2)</x:v>
-      </x:c>
-      <x:c r="E134" s="9" t="str">
-        <x:v>INSPECTION (every 20,000 miles): Remove HPFP (3 bolts) and inspect cam follower surface. If the hardened coating is wearing through (visible copper/brass color), replace follower immediately ($30-$50 part, 30-60 minutes labor). CRITICAL: Ensure cam lobe is at LOW point before reinstalling—if at peak, you'll compress the spring and can break the mounting bolts. If CAMSHAFT WORN (deep groove in lobe): Replace camshaft ($2,000-$4,000). If FUEL PUMP FAILED: Replace HPFP ($400-$800). PREVENTION: Inspect cam follower every 20,000 miles as routine maintenance. Add to every oil change checklist. Consider IE (Integrated Engineering) upgraded HPFP with roller follower to eliminate wear entirely.</x:v>
-      </x:c>
-      <x:c r="F134" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G134" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="135" ht="884.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A135" s="40" t="n">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="B135" s="9" t="str">
-        <x:v>audi-tts-carbon-buildup-2009</x:v>
-      </x:c>
-      <x:c r="C135" s="9" t="str">
-        <x:v>2016-2017 | Audi | TTS</x:v>
-      </x:c>
-      <x:c r="D135" s="9" t="str">
-        <x:v>2016-2017 TTS Cold-Start Misfire DTCs Without Felt Misfire - TSB 2051384/1</x:v>
-      </x:c>
-      <x:c r="E135" s="9" t="str">
-        <x:v>Confirm the exact cold-start timing, simultaneous-cylinder DTC pattern, absence of a felt misfire, CYFB engine and installed ECM software before using this bulletin. When applicable, an Audi-capable workshop updates ECM J623 from software part number 8S0906259C version 0001 to version 0004 or higher using SVM action 01A190, then clears the DTCs. A felt misfire, a different timing or RPM pattern, a different engine/software combination or a returning concern requires normal diagnosis rather than carbon cleaning by assumption.</x:v>
-      </x:c>
-      <x:c r="F135" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G135" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="136" ht="910.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A136" s="40" t="n">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="B136" s="9" t="str">
-        <x:v>audi-tts-dsg-mechatronic-2009</x:v>
-      </x:c>
-      <x:c r="C136" s="9" t="str">
-        <x:v>2019-2023 | Audi | TTS</x:v>
-      </x:c>
-      <x:c r="D136" s="9" t="str">
-        <x:v>2019-2023 TTS Clutch K1 Overheat and Transmission DTC Diagnosis - TSB 2060560/3</x:v>
-      </x:c>
-      <x:c r="E136" s="9" t="str">
-        <x:v>Have an Audi-capable workshop check whether TSB 2050723 applies first. If it does not resolve or control the concern, inspect the clutch-K1 maximum-temperature value and document a transmission-fluid sample. Replace the dual clutch, transmission fluid and filter only when the approximately 400 °C K1 value and burnt black or very dark fluid are both present. If those findings are absent, this bulletin does not apply and Audi directs the workshop to continue diagnosis through TAC. Any clutch repair kit must be selected by VIN and production date.</x:v>
-      </x:c>
-      <x:c r="F136" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G136" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="137" ht="858" hidden="0" customHeight="1">
-      <x:c r="A137" s="40" t="n">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="B137" s="9" t="str">
-        <x:v>audi-tts-magnetic-ride-2009</x:v>
-      </x:c>
-      <x:c r="C137" s="9" t="str">
-        <x:v>2016-2016 | Audi | TTS</x:v>
-      </x:c>
-      <x:c r="D137" s="9" t="str">
-        <x:v>2016 TTS Magnetic-Ride Rear Shock-Mount Rumble - TSB 2042539/4</x:v>
-      </x:c>
-      <x:c r="E137" s="9" t="str">
-        <x:v>First reproduce the noise, verify that it comes from the rear shock mounts and confirm that the vehicle was originally equipped with mount 8S0 513 353. Only when those gates are satisfied, remove both rear shock assemblies and replace both mounts with 8V0 513 353 according to Audi workshop instructions, adapt the suspension control position and test drive to confirm the repair. If the installed mount does not match, continue Audi diagnosis. Do not replace magnetic dampers or convert the vehicle to coilovers from this noise alone.</x:v>
-      </x:c>
-      <x:c r="F137" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G137" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="138" ht="1016.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A138" s="40" t="n">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="B138" s="9" t="str">
-        <x:v>audi-tts-timing-chain-tensioner-2009</x:v>
-      </x:c>
-      <x:c r="C138" s="9" t="str">
-        <x:v>2009-2015 | Audi | TTS | TTS | EA888 Gen 1, EA888 Gen 2</x:v>
-      </x:c>
-      <x:c r="D138" s="9" t="str">
-        <x:v>Timing Chain Tensioner Failure (EA888 Gen 1/2 - Mk2 TTS)</x:v>
-      </x:c>
-      <x:c r="E138" s="9" t="str">
-        <x:v>PREVENTIVE REPLACEMENT: Replace timing chain, tensioner, guides, and sprockets at 80,000-100,000 miles BEFORE symptoms appear ($2,000-$4,000). This is the MOST important preventive maintenance on the Mk2 TTS. IF RATTLING: Do NOT delay—the chain can jump at any startup. Schedule repair immediately. Use ONLY the latest OEM revised tensioner (06K109467K). IF CHAIN JUMPED: Engine likely destroyed—compression test all cylinders. Rebuild ($5,000-$8,000) or replacement engine ($6,000-$12,000). PREVENTION: Change oil every 5,000 miles with high-quality synthetic. Low oil level accelerates tensioner wear.</x:v>
-      </x:c>
-      <x:c r="F138" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G138" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="139" ht="976.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A139" s="40" t="n">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="B139" s="9" t="str">
-        <x:v>audi-tts-water-pump-2009</x:v>
-      </x:c>
-      <x:c r="C139" s="9" t="str">
-        <x:v>2012-2023 | Audi | TTS</x:v>
-      </x:c>
-      <x:c r="D139" s="9" t="str">
-        <x:v>2012 / 2020-2023 TTS Coolant-Pump Update and Leak Diagnosis</x:v>
-      </x:c>
-      <x:c r="E139" s="9" t="str">
-        <x:v>For a 2012 TTS, ask an Audi dealer to check the VIN and current campaign/action history for Update 19J2; the published update replaced the pump only when its exact criteria were met and does not promise current warranty coverage. For a 2020-2023 2.0L TTS, first exclude a low level caused by incomplete bleeding or an earlier repair, document and clean the suspected leak, refill to maximum and recheck after driving. Continue observation when no leak returns; replace only the component proven to leak when coolant reappears. Do not select a pump or thermostat assembly before VIN-, engine- and leak-specific diagnosis.</x:v>
-      </x:c>
-      <x:c r="F139" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G139" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="140" ht="198" hidden="0" customHeight="1">
-      <x:c r="A140" s="42" t="n">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="B140" s="43" t="str">
-        <x:v>audi-tts-waterpump-housing-2009</x:v>
-      </x:c>
-      <x:c r="C140" s="43" t="str">
-        <x:v>2009-2024 | Audi | TTS | EA888</x:v>
-      </x:c>
-      <x:c r="D140" s="43" t="str">
-        <x:v>Water Pump and Thermostat Housing Failure</x:v>
-      </x:c>
-      <x:c r="E140" s="43" t="str">
-        <x:v>Replace water pump, thermostat, and housing as a complete assembly. Use metal-impeller aftermarket pump if available.</x:v>
-      </x:c>
-      <x:c r="F140" s="43" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G140" s="44" t="str">
+      <x:c r="G90" s="44" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>

--- a/outputs/audi-repair-first-review/Audi-repair-first-fitment-review.xlsx
+++ b/outputs/audi-repair-first-review/Audi-repair-first-fitment-review.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R49941522a7274700"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audi Review" sheetId="2" r:id="Rad259c8fcd504851"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Queue" sheetId="3" r:id="Rf8c63222b675417b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" r:id="Rc5230f09ee654b3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Re236912b51844fae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audi Review" sheetId="2" r:id="Re5774462ba8747fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Queue" sheetId="3" r:id="Rf8f873359b384a8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" r:id="R5e7c561b84ab4128"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -484,7 +484,7 @@
         <x:v>Reviewed in this batch</x:v>
       </x:c>
       <x:c r="B5" s="13" t="n">
-        <x:v>300</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="C5" s="11"/>
       <x:c r="D5" s="11"/>
@@ -498,7 +498,7 @@
         <x:v>Remaining queue</x:v>
       </x:c>
       <x:c r="B6" s="13" t="n">
-        <x:v>89</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C6" s="11"/>
       <x:c r="D6" s="11"/>
@@ -512,7 +512,7 @@
         <x:v>Issues with destinations</x:v>
       </x:c>
       <x:c r="B7" s="13" t="n">
-        <x:v>295</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="C7" s="11"/>
       <x:c r="D7" s="11"/>
@@ -526,7 +526,7 @@
         <x:v>Destination entries</x:v>
       </x:c>
       <x:c r="B8" s="13" t="n">
-        <x:v>513</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="C8" s="11"/>
       <x:c r="D8" s="11"/>
@@ -540,7 +540,7 @@
         <x:v>Distinct URLs</x:v>
       </x:c>
       <x:c r="B9" s="13" t="n">
-        <x:v>89</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C9" s="11"/>
       <x:c r="D9" s="11"/>
@@ -568,7 +568,7 @@
         <x:v>Missing How to Fix</x:v>
       </x:c>
       <x:c r="B11" s="13" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C11" s="11"/>
       <x:c r="D11" s="11"/>
@@ -18509,28 +18509,3100 @@
       </x:c>
     </x:row>
     <x:row r="519" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A519" s="42" t="str"/>
-      <x:c r="B519" s="43" t="str"/>
-      <x:c r="C519" s="43" t="str"/>
-      <x:c r="D519" s="43" t="str"/>
-      <x:c r="E519" s="43" t="str"/>
-      <x:c r="F519" s="43" t="str"/>
-      <x:c r="G519" s="43" t="str"/>
-      <x:c r="H519" s="43" t="str">
+      <x:c r="A519" s="40" t="str"/>
+      <x:c r="B519" s="9" t="str"/>
+      <x:c r="C519" s="9" t="str"/>
+      <x:c r="D519" s="9" t="str"/>
+      <x:c r="E519" s="9" t="str"/>
+      <x:c r="F519" s="9" t="str"/>
+      <x:c r="G519" s="9" t="str"/>
+      <x:c r="H519" s="9" t="str">
         <x:v>Audi specialist locator</x:v>
       </x:c>
-      <x:c r="I519" s="43" t="str">
+      <x:c r="I519" s="9" t="str">
         <x:v>https://www.audishops.com/</x:v>
       </x:c>
-      <x:c r="J519" s="43" t="str">
+      <x:c r="J519" s="9" t="str">
         <x:v>intercooler circuit flow/leak diagnosis</x:v>
       </x:c>
-      <x:c r="K519" s="43" t="str">
+      <x:c r="K519" s="9" t="str">
         <x:v>specialist cooling service</x:v>
       </x:c>
-      <x:c r="L519" s="43" t="str"/>
-      <x:c r="M519" s="43" t="str"/>
-      <x:c r="N519" s="44" t="str"/>
+      <x:c r="L519" s="9" t="str"/>
+      <x:c r="M519" s="9" t="str"/>
+      <x:c r="N519" s="41" t="str"/>
+    </x:row>
+    <x:row r="520" ht="211.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A520" s="40" t="n">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="B520" s="9" t="str">
+        <x:v>audi-s5-thermostat-2008</x:v>
+      </x:c>
+      <x:c r="C520" s="9" t="str">
+        <x:v>2008-2025 | Audi | S5 | 3.0T</x:v>
+      </x:c>
+      <x:c r="D520" s="9" t="str">
+        <x:v>Thermostat and Water Pump Assembly Failure</x:v>
+      </x:c>
+      <x:c r="E520" s="9" t="str">
+        <x:v>Replace thermostat/water pump assembly. Upgrade to revised housing if available.</x:v>
+      </x:c>
+      <x:c r="F520" s="9" t="str">
+        <x:v>Split V8/supercharged/turbo engines; pressure-test exact pump/thermostat/housing source; VIN component/revision and coolant</x:v>
+      </x:c>
+      <x:c r="G520" s="9" t="str">
+        <x:v>OVERBROAD MULTI-ENGINE / LEAK-SOURCE GATE</x:v>
+      </x:c>
+      <x:c r="H520" s="9" t="str">
+        <x:v>Audi S5 thermostat catalog</x:v>
+      </x:c>
+      <x:c r="I520" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/S5/Thermostat/</x:v>
+      </x:c>
+      <x:c r="J520" s="9" t="str">
+        <x:v>2008-2025 exact engine/VIN and confirmed component</x:v>
+      </x:c>
+      <x:c r="K520" s="9" t="str">
+        <x:v>vehicle-specific thermostat catalog</x:v>
+      </x:c>
+      <x:c r="L520" s="9" t="str"/>
+      <x:c r="M520" s="9" t="str">
+        <x:v>Source incorrectly labels whole range 3.0T and one assembly.</x:v>
+      </x:c>
+      <x:c r="N520" s="41" t="str">
+        <x:v>No universal revised-housing upgrade or pump/thermostat bundle.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="521" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A521" s="40" t="str"/>
+      <x:c r="B521" s="9" t="str"/>
+      <x:c r="C521" s="9" t="str"/>
+      <x:c r="D521" s="9" t="str"/>
+      <x:c r="E521" s="9" t="str"/>
+      <x:c r="F521" s="9" t="str"/>
+      <x:c r="G521" s="9" t="str"/>
+      <x:c r="H521" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I521" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J521" s="9" t="str">
+        <x:v>pressure-test/engine diagnosis</x:v>
+      </x:c>
+      <x:c r="K521" s="9" t="str">
+        <x:v>specialist cooling service</x:v>
+      </x:c>
+      <x:c r="L521" s="9" t="str"/>
+      <x:c r="M521" s="9" t="str"/>
+      <x:c r="N521" s="41" t="str"/>
+    </x:row>
+    <x:row r="522" ht="818.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A522" s="40" t="n">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="B522" s="9" t="str">
+        <x:v>audi-s6-air-suspension-2013</x:v>
+      </x:c>
+      <x:c r="C522" s="9" t="str">
+        <x:v>2013-2013 | Audi | S6 | 4.0T</x:v>
+      </x:c>
+      <x:c r="D522" s="9" t="str">
+        <x:v>2013 Audi S6 Air-Suspension Compressor or Relay Fault - Diagnosis Required</x:v>
+      </x:c>
+      <x:c r="E522" s="9" t="str">
+        <x:v>Have an Audi-qualified technician test the air-suspension compressor and inspect relay J403. Audi directs replacement of both the compressor and relay when the relay has severe contact erosion or an overheated strand; when the compressor sounds normal and the relay has only minor contact marks, replace the relay only. A sagging corner or leak-down condition requires separate leak localization before any strut is replaced. Do not order the former strut or compressor recommendations from this card.</x:v>
+      </x:c>
+      <x:c r="F522" s="9" t="str">
+        <x:v>Test compressor and J403; compressor+relay only for severe relay erosion/overheat; relay only for normal compressor/minor marks; separate sag/leak diagnosis</x:v>
+      </x:c>
+      <x:c r="G522" s="9" t="str">
+        <x:v>TSB RELAY/COMPRESSOR CONDITION GATE</x:v>
+      </x:c>
+      <x:c r="H522" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I522" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J522" s="9" t="str">
+        <x:v>2013 S6 air-suspension compressor/J403 diagnosis</x:v>
+      </x:c>
+      <x:c r="K522" s="9" t="str">
+        <x:v>manufacturer suspension service</x:v>
+      </x:c>
+      <x:c r="L522" s="9" t="str"/>
+      <x:c r="M522" s="9" t="str">
+        <x:v>Relay inspection and compressor test select branch.</x:v>
+      </x:c>
+      <x:c r="N522" s="41" t="str">
+        <x:v>No strut/compressor product from warning alone.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="523" ht="1359.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A523" s="40" t="n">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B523" s="9" t="str">
+        <x:v>audi-s6-c7-carbon-buildup-2013</x:v>
+      </x:c>
+      <x:c r="C523" s="9" t="str">
+        <x:v>2013-2018 | Audi | S6 | 4.0T</x:v>
+      </x:c>
+      <x:c r="D523" s="9" t="str">
+        <x:v>4.0T Carbon Buildup on Intake Valves</x:v>
+      </x:c>
+      <x:c r="E523" s="9" t="str">
+        <x:v>Confirm carbon buildup by scanning for misfire faults (commonly random/multiple or cylinder-specific misfires), reviewing fuel trims, and inspecting the intake valves with a borescope after removing the intake manifold or accessing the ports. The proper repair is an intake valve carbon cleaning, typically walnut shell blasting each intake port with the valves closed, then replacing intake manifold gaskets, injector seals/O-rings or any disturbed PCV-related seals as needed and clearing/adapting the ECU afterward. If buildup is severe or returns quickly, inspect the PCV/oil separator system and crankcase ventilation hoses for excessive oil carryover. Independent shops typically charge about $800-$1,500 for a full walnut blast service on the 4.0T, while dealer pricing can run roughly $1,500-$2,500 depending on labor and gasket/seal replacement.</x:v>
+      </x:c>
+      <x:c r="F523" s="9" t="str">
+        <x:v>Confirm deposits after misfire/fuel/compression and borescope; 4.0T cleaning; disturbed gaskets/seals and PCV only by condition</x:v>
+      </x:c>
+      <x:c r="G523" s="9" t="str">
+        <x:v>CONFIRMED-DEPOSIT / CONSUMABLE GATE</x:v>
+      </x:c>
+      <x:c r="H523" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I523" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J523" s="9" t="str">
+        <x:v>2013-2018 S6 4.0T intake diagnosis/cleaning</x:v>
+      </x:c>
+      <x:c r="K523" s="9" t="str">
+        <x:v>specialist intake service</x:v>
+      </x:c>
+      <x:c r="L523" s="9" t="str"/>
+      <x:c r="M523" s="9" t="str">
+        <x:v>Cleaning is valid after proof; seals/PCV conditional.</x:v>
+      </x:c>
+      <x:c r="N523" s="41" t="str">
+        <x:v>Remove prices and automatic injector/PCV parts.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="524" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A524" s="40" t="n">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="B524" s="9" t="str">
+        <x:v>audi-s6-carbon-buildup-2013</x:v>
+      </x:c>
+      <x:c r="C524" s="9" t="str">
+        <x:v>2013-2024 | Audi | S6 | 4.0T</x:v>
+      </x:c>
+      <x:c r="D524" s="9" t="str">
+        <x:v>4.0T Direct Injection Carbon Buildup</x:v>
+      </x:c>
+      <x:c r="E524" s="9" t="str">
+        <x:v>Walnut blast all eight intake runners. Dual-injection models (2019+) are less affected.</x:v>
+      </x:c>
+      <x:c r="F524" s="9" t="str">
+        <x:v>Split generations/injection systems; confirm inlet deposits before generation-specific cleaning</x:v>
+      </x:c>
+      <x:c r="G524" s="9" t="str">
+        <x:v>MULTI-GENERATION / CONFIRMED-DEPOSIT SERVICE</x:v>
+      </x:c>
+      <x:c r="H524" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I524" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J524" s="9" t="str">
+        <x:v>2013-2024 S6 4.0T intake diagnosis/cleaning</x:v>
+      </x:c>
+      <x:c r="K524" s="9" t="str">
+        <x:v>specialist intake service</x:v>
+      </x:c>
+      <x:c r="L524" s="9" t="str"/>
+      <x:c r="M524" s="9" t="str">
+        <x:v>2019+ dual-injection statement not sufficient for whole range.</x:v>
+      </x:c>
+      <x:c r="N524" s="41" t="str">
+        <x:v>No automatic eight-runner walnut service.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="525" ht="462" hidden="0" customHeight="1">
+      <x:c r="A525" s="40" t="n">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="B525" s="9" t="str">
+        <x:v>audi-s6-rearview-camera-image-failure-from-software-error</x:v>
+      </x:c>
+      <x:c r="C525" s="9" t="str">
+        <x:v>2020-2025 | Audi | S6</x:v>
+      </x:c>
+      <x:c r="D525" s="9" t="str">
+        <x:v>2020-2025 Audi S6 Rearview Camera Software Recall 25V900 / 90TV</x:v>
+      </x:c>
+      <x:c r="E525" s="9" t="str">
+        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install the more robust driver-assistance software update free of charge. Until repaired, use extra caution when reversing and do not treat a restart or temporary image recovery as completion of the recall.</x:v>
+      </x:c>
+      <x:c r="F525" s="9" t="str">
+        <x:v>VIN/90TV/25V900 check; free software; direct observation</x:v>
+      </x:c>
+      <x:c r="G525" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H525" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I525" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J525" s="9" t="str">
+        <x:v>2020-2025 S6 90TV</x:v>
+      </x:c>
+      <x:c r="K525" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L525" s="9" t="str"/>
+      <x:c r="M525" s="9" t="str">
+        <x:v>Software is recall remedy.</x:v>
+      </x:c>
+      <x:c r="N525" s="41" t="str">
+        <x:v>Restart is not completion; no camera link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="526" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A526" s="40" t="str"/>
+      <x:c r="B526" s="9" t="str"/>
+      <x:c r="C526" s="9" t="str"/>
+      <x:c r="D526" s="9" t="str"/>
+      <x:c r="E526" s="9" t="str"/>
+      <x:c r="F526" s="9" t="str"/>
+      <x:c r="G526" s="9" t="str"/>
+      <x:c r="H526" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I526" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J526" s="9" t="str">
+        <x:v>25V900 VIN history</x:v>
+      </x:c>
+      <x:c r="K526" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L526" s="9" t="str"/>
+      <x:c r="M526" s="9" t="str"/>
+      <x:c r="N526" s="41" t="str"/>
+    </x:row>
+    <x:row r="527" ht="409.20001220703125" hidden="0" customHeight="1">
+      <x:c r="A527" s="40" t="n">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="B527" s="9" t="str">
+        <x:v>audi-s6-takata-passenger-airbag-inflator-recall</x:v>
+      </x:c>
+      <x:c r="C527" s="9" t="str">
+        <x:v>2007-2011 | Audi | S6</x:v>
+      </x:c>
+      <x:c r="D527" s="9" t="str">
+        <x:v>2007-2011 Audi S6 Takata Passenger-Airbag Recall 18V427 / 69R7</x:v>
+      </x:c>
+      <x:c r="E527" s="9" t="str">
+        <x:v>Check the VIN for recall 18V427/69R7 and arrange the free final passenger-frontal-airbag replacement with an Audi dealer. Do not use an airbag warning light to determine recall eligibility; Audi states that the warning light is unrelated to this inflator defect.</x:v>
+      </x:c>
+      <x:c r="F527" s="9" t="str">
+        <x:v>VIN/69R7/18V427 check; free passenger inflator remedy</x:v>
+      </x:c>
+      <x:c r="G527" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H527" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I527" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J527" s="9" t="str">
+        <x:v>2007-2011 S6 69R7</x:v>
+      </x:c>
+      <x:c r="K527" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L527" s="9" t="str"/>
+      <x:c r="M527" s="9" t="str">
+        <x:v>Warning light does not determine eligibility.</x:v>
+      </x:c>
+      <x:c r="N527" s="41" t="str">
+        <x:v>No retail airbag link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="528" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A528" s="40" t="str"/>
+      <x:c r="B528" s="9" t="str"/>
+      <x:c r="C528" s="9" t="str"/>
+      <x:c r="D528" s="9" t="str"/>
+      <x:c r="E528" s="9" t="str"/>
+      <x:c r="F528" s="9" t="str"/>
+      <x:c r="G528" s="9" t="str"/>
+      <x:c r="H528" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I528" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J528" s="9" t="str">
+        <x:v>18V427 VIN history</x:v>
+      </x:c>
+      <x:c r="K528" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L528" s="9" t="str"/>
+      <x:c r="M528" s="9" t="str"/>
+      <x:c r="N528" s="41" t="str"/>
+    </x:row>
+    <x:row r="529" ht="184.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A529" s="40" t="n">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="B529" s="9" t="str">
+        <x:v>audi-s6-transmission-valve-body-2002</x:v>
+      </x:c>
+      <x:c r="C529" s="9" t="str">
+        <x:v>2002-2004 | Audi | S6</x:v>
+      </x:c>
+      <x:c r="D529" s="9" t="str">
+        <x:v>ZF 5HP24 Tiptronic Transmission Valve Body Failure</x:v>
+      </x:c>
+      <x:c r="E529" s="9" t="str"/>
+      <x:c r="F529" s="9" t="str"/>
+      <x:c r="G529" s="9" t="str">
+        <x:v>SOURCE HOW-TO-FIX REQUIRED / NO LINK</x:v>
+      </x:c>
+      <x:c r="H529" s="9" t="str"/>
+      <x:c r="I529" s="9" t="str"/>
+      <x:c r="J529" s="9" t="str"/>
+      <x:c r="K529" s="9" t="str"/>
+      <x:c r="L529" s="9" t="str"/>
+      <x:c r="M529" s="9" t="str">
+        <x:v>Source has no How to Fix.</x:v>
+      </x:c>
+      <x:c r="N529" s="41" t="str">
+        <x:v>Add 5HP24 code, faults, fluid/debris, valve-body/solenoid/converter/mechanical branches before links.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="530" ht="739.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A530" s="40" t="n">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="B530" s="9" t="str">
+        <x:v>audi-s6-turbo-coolant-2013</x:v>
+      </x:c>
+      <x:c r="C530" s="9" t="str">
+        <x:v>2013-2013 | Audi | S6 | 4.0T</x:v>
+      </x:c>
+      <x:c r="D530" s="9" t="str">
+        <x:v>2013 Audi S6 Turbocharger Coolant-Pipe Seepage - Diagnosis Required</x:v>
+      </x:c>
+      <x:c r="E530" s="9" t="str">
+        <x:v>Confirm the leak source and VIN applicability before ordering parts. For the TSB condition, Audi specifies replacing the coolant feed and return pipes on both cylinder banks, replacing the disturbed oil-feed-pipe O-rings, then refilling and bleeding the cooling system. Service Action 21F7 was VIN-specific and expired in 2019, so current coverage must not be assumed. Do not order the former single pipe or alleged silicone-line kit from this card.</x:v>
+      </x:c>
+      <x:c r="F530" s="9" t="str">
+        <x:v>Confirm TSB leak/VIN; both-bank feed/return pipes and disturbed oil-feed O-rings; exact coolant/bleed; coverage check</x:v>
+      </x:c>
+      <x:c r="G530" s="9" t="str">
+        <x:v>TSB / VIN CONDITIONAL BOTH-BANK SERVICE</x:v>
+      </x:c>
+      <x:c r="H530" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I530" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J530" s="9" t="str">
+        <x:v>2013 S6 4.0T coolant-pipe TSB/21F7 history</x:v>
+      </x:c>
+      <x:c r="K530" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L530" s="9" t="str"/>
+      <x:c r="M530" s="9" t="str">
+        <x:v>Expired action and both-bank procedure require VIN/current parts.</x:v>
+      </x:c>
+      <x:c r="N530" s="41" t="str">
+        <x:v>No single pipe/silicone kit link or coverage promise.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="531" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A531" s="40" t="str"/>
+      <x:c r="B531" s="9" t="str"/>
+      <x:c r="C531" s="9" t="str"/>
+      <x:c r="D531" s="9" t="str"/>
+      <x:c r="E531" s="9" t="str"/>
+      <x:c r="F531" s="9" t="str"/>
+      <x:c r="G531" s="9" t="str"/>
+      <x:c r="H531" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I531" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J531" s="9" t="str">
+        <x:v>both-bank leak diagnosis/service</x:v>
+      </x:c>
+      <x:c r="K531" s="9" t="str">
+        <x:v>specialist cooling service</x:v>
+      </x:c>
+      <x:c r="L531" s="9" t="str"/>
+      <x:c r="M531" s="9" t="str"/>
+      <x:c r="N531" s="41" t="str"/>
+    </x:row>
+    <x:row r="532" ht="290.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A532" s="40" t="n">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B532" s="9" t="str">
+        <x:v>audi-s7-air-suspension-2012</x:v>
+      </x:c>
+      <x:c r="C532" s="9" t="str">
+        <x:v>2020-2021 | Audi | S7</x:v>
+      </x:c>
+      <x:c r="D532" s="9" t="str">
+        <x:v>Rear-Axle Lock Nut and Alignment Recall Follow-Up (21V295 / 22V034)</x:v>
+      </x:c>
+      <x:c r="E532" s="9" t="str">
+        <x:v>Check the VIN for both campaigns 42L1 and 42L5. Audi dealers replace affected nuts and bolts, inspect and adjust rear alignment, and replace qualifying unevenly worn tires free of charge.</x:v>
+      </x:c>
+      <x:c r="F532" s="9" t="str">
+        <x:v>VIN/42L1/42L5/21V295/22V034 check; nuts/bolts, rear alignment and qualifying tire remedy</x:v>
+      </x:c>
+      <x:c r="G532" s="9" t="str">
+        <x:v>SOURCE-ID/YEAR MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H532" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I532" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J532" s="9" t="str">
+        <x:v>2020-2021 S7 rear-axle campaigns</x:v>
+      </x:c>
+      <x:c r="K532" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L532" s="9" t="str"/>
+      <x:c r="M532" s="9" t="str">
+        <x:v>Rear-axle recall, not 2012 air suspension.</x:v>
+      </x:c>
+      <x:c r="N532" s="41" t="str">
+        <x:v>Rename/re-key; no suspension/tire commerce link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="533" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A533" s="40" t="str"/>
+      <x:c r="B533" s="9" t="str"/>
+      <x:c r="C533" s="9" t="str"/>
+      <x:c r="D533" s="9" t="str"/>
+      <x:c r="E533" s="9" t="str"/>
+      <x:c r="F533" s="9" t="str"/>
+      <x:c r="G533" s="9" t="str"/>
+      <x:c r="H533" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I533" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J533" s="9" t="str">
+        <x:v>21V295/22V034 VIN history</x:v>
+      </x:c>
+      <x:c r="K533" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L533" s="9" t="str"/>
+      <x:c r="M533" s="9" t="str"/>
+      <x:c r="N533" s="41" t="str"/>
+    </x:row>
+    <x:row r="534" ht="237.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A534" s="40" t="n">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="B534" s="9" t="str">
+        <x:v>audi-s7-biturbo-coolant-2012</x:v>
+      </x:c>
+      <x:c r="C534" s="9" t="str">
+        <x:v>2013-2014 | Audi | S7 | 4.0 TFSI</x:v>
+      </x:c>
+      <x:c r="D534" s="9" t="str">
+        <x:v>4.0L Fuel Line Can Leak and Create a Fire Risk (Recall 13V450 / 20U6)</x:v>
+      </x:c>
+      <x:c r="E534" s="9" t="str">
+        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel line free of charge under campaign 20U6/L8. Stop driving if fuel odor or leakage is present.</x:v>
+      </x:c>
+      <x:c r="F534" s="9" t="str">
+        <x:v>VIN/20U6/13V450 check; free fuel line; stop for odor/leak</x:v>
+      </x:c>
+      <x:c r="G534" s="9" t="str">
+        <x:v>SOURCE-ID/YEAR MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H534" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I534" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J534" s="9" t="str">
+        <x:v>2013-2014 S7 20U6</x:v>
+      </x:c>
+      <x:c r="K534" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L534" s="9" t="str"/>
+      <x:c r="M534" s="9" t="str">
+        <x:v>Fuel line recall, not coolant.</x:v>
+      </x:c>
+      <x:c r="N534" s="41" t="str">
+        <x:v>Rename/re-key; no fuel/coolant line product.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="535" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A535" s="40" t="str"/>
+      <x:c r="B535" s="9" t="str"/>
+      <x:c r="C535" s="9" t="str"/>
+      <x:c r="D535" s="9" t="str"/>
+      <x:c r="E535" s="9" t="str"/>
+      <x:c r="F535" s="9" t="str"/>
+      <x:c r="G535" s="9" t="str"/>
+      <x:c r="H535" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I535" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J535" s="9" t="str">
+        <x:v>13V450 VIN history</x:v>
+      </x:c>
+      <x:c r="K535" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L535" s="9" t="str"/>
+      <x:c r="M535" s="9" t="str"/>
+      <x:c r="N535" s="41" t="str"/>
+    </x:row>
+    <x:row r="536" ht="264" hidden="0" customHeight="1">
+      <x:c r="A536" s="40" t="n">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="B536" s="9" t="str">
+        <x:v>audi-s7-carbon-buildup-4.0t-2012</x:v>
+      </x:c>
+      <x:c r="C536" s="9" t="str">
+        <x:v>2021-2021 | Audi | S7</x:v>
+      </x:c>
+      <x:c r="D536" s="9" t="str">
+        <x:v>Rear Seat-Belt Retractor Can Release a Child Restraint Early (Recall 21V606 / 69CS)</x:v>
+      </x:c>
+      <x:c r="E536" s="9" t="str">
+        <x:v>Check VIN eligibility. Audi dealers inspect and replace the affected middle-rear seat-belt assembly as necessary free of charge under campaign 69CS.</x:v>
+      </x:c>
+      <x:c r="F536" s="9" t="str">
+        <x:v>VIN/69CS/21V606 check; middle-rear belt inspection/replacement</x:v>
+      </x:c>
+      <x:c r="G536" s="9" t="str">
+        <x:v>SOURCE-ID/YEAR MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H536" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I536" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J536" s="9" t="str">
+        <x:v>2021 S7 69CS</x:v>
+      </x:c>
+      <x:c r="K536" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L536" s="9" t="str"/>
+      <x:c r="M536" s="9" t="str">
+        <x:v>Seat-belt recall, not carbon.</x:v>
+      </x:c>
+      <x:c r="N536" s="41" t="str">
+        <x:v>Rename/re-key; no cleaning/seat-belt product.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="537" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A537" s="40" t="str"/>
+      <x:c r="B537" s="9" t="str"/>
+      <x:c r="C537" s="9" t="str"/>
+      <x:c r="D537" s="9" t="str"/>
+      <x:c r="E537" s="9" t="str"/>
+      <x:c r="F537" s="9" t="str"/>
+      <x:c r="G537" s="9" t="str"/>
+      <x:c r="H537" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I537" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J537" s="9" t="str">
+        <x:v>21V606 VIN history</x:v>
+      </x:c>
+      <x:c r="K537" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L537" s="9" t="str"/>
+      <x:c r="M537" s="9" t="str"/>
+      <x:c r="N537" s="41" t="str"/>
+    </x:row>
+    <x:row r="538" ht="237.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A538" s="40" t="n">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="B538" s="9" t="str">
+        <x:v>audi-s7-cylinder-demand-rough-running-hesitation</x:v>
+      </x:c>
+      <x:c r="C538" s="9" t="str">
+        <x:v>2021-2021 | Audi | S7</x:v>
+      </x:c>
+      <x:c r="D538" s="9" t="str">
+        <x:v>Instrument Panel May Fail to Display Critical Safety Information (Recall 25V201 / 90VC)</x:v>
+      </x:c>
+      <x:c r="E538" s="9" t="str">
+        <x:v>Check the VIN and campaign-completion history. Audi dealers update the instrument-panel module software free of charge under campaign 90VC.</x:v>
+      </x:c>
+      <x:c r="F538" s="9" t="str">
+        <x:v>VIN/90VC/25V201 check; instrument-panel software</x:v>
+      </x:c>
+      <x:c r="G538" s="9" t="str">
+        <x:v>SOURCE-ID MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H538" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I538" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J538" s="9" t="str">
+        <x:v>2021 S7 90VC</x:v>
+      </x:c>
+      <x:c r="K538" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L538" s="9" t="str"/>
+      <x:c r="M538" s="9" t="str">
+        <x:v>Display recall, not cylinder demand.</x:v>
+      </x:c>
+      <x:c r="N538" s="41" t="str">
+        <x:v>Rename/re-key; no engine/display product.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="539" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A539" s="40" t="str"/>
+      <x:c r="B539" s="9" t="str"/>
+      <x:c r="C539" s="9" t="str"/>
+      <x:c r="D539" s="9" t="str"/>
+      <x:c r="E539" s="9" t="str"/>
+      <x:c r="F539" s="9" t="str"/>
+      <x:c r="G539" s="9" t="str"/>
+      <x:c r="H539" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I539" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J539" s="9" t="str">
+        <x:v>25V201 VIN history</x:v>
+      </x:c>
+      <x:c r="K539" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L539" s="9" t="str"/>
+      <x:c r="M539" s="9" t="str"/>
+      <x:c r="N539" s="41" t="str"/>
+    </x:row>
+    <x:row r="540" ht="316.79998779296875" hidden="0" customHeight="1">
+      <x:c r="A540" s="40" t="n">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="B540" s="9" t="str">
+        <x:v>audi-s7-ea839-2-9t-v6-water-pump-internal-leak-overheating</x:v>
+      </x:c>
+      <x:c r="C540" s="9" t="str">
+        <x:v>2020-2024 | Audi | S7</x:v>
+      </x:c>
+      <x:c r="D540" s="9" t="str">
+        <x:v>Rearview Camera Image May Not Display (Recall 25V900 / 90TV)</x:v>
+      </x:c>
+      <x:c r="E540" s="9" t="str">
+        <x:v>Check the VIN and campaign-completion history. Audi dealers update the relevant software free of charge under campaign 90TV. Continue direct visual checks when reversing until repaired.</x:v>
+      </x:c>
+      <x:c r="F540" s="9" t="str">
+        <x:v>VIN/90TV/25V900 check; camera software; direct reverse observation</x:v>
+      </x:c>
+      <x:c r="G540" s="9" t="str">
+        <x:v>SOURCE-ID MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H540" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I540" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J540" s="9" t="str">
+        <x:v>2020-2024 S7 90TV</x:v>
+      </x:c>
+      <x:c r="K540" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L540" s="9" t="str"/>
+      <x:c r="M540" s="9" t="str">
+        <x:v>Camera recall, not water pump.</x:v>
+      </x:c>
+      <x:c r="N540" s="41" t="str">
+        <x:v>Rename/re-key; no cooling/camera product.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="541" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A541" s="40" t="str"/>
+      <x:c r="B541" s="9" t="str"/>
+      <x:c r="C541" s="9" t="str"/>
+      <x:c r="D541" s="9" t="str"/>
+      <x:c r="E541" s="9" t="str"/>
+      <x:c r="F541" s="9" t="str"/>
+      <x:c r="G541" s="9" t="str"/>
+      <x:c r="H541" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I541" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J541" s="9" t="str">
+        <x:v>25V900 VIN history</x:v>
+      </x:c>
+      <x:c r="K541" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L541" s="9" t="str"/>
+      <x:c r="M541" s="9" t="str"/>
+      <x:c r="N541" s="41" t="str"/>
+    </x:row>
+    <x:row r="542" ht="343.20001220703125" hidden="0" customHeight="1">
+      <x:c r="A542" s="40" t="n">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="B542" s="9" t="str">
+        <x:v>audi-s7-electromechanical-steering-rack-torque-sensor-failure-causin</x:v>
+      </x:c>
+      <x:c r="C542" s="9" t="str">
+        <x:v>2021-2021 | Audi | S7</x:v>
+      </x:c>
+      <x:c r="D542" s="9" t="str">
+        <x:v>Incorrect Brake-Fluid Reservoir Cap Label (Recall 23V601 / 47T9)</x:v>
+      </x:c>
+      <x:c r="E542" s="9" t="str">
+        <x:v>Check VIN eligibility. Audi dealers inspect the reservoir cap and replace it when necessary free of charge under campaign 47T9. Use only the brake-fluid specification in the owner and service information.</x:v>
+      </x:c>
+      <x:c r="F542" s="9" t="str">
+        <x:v>VIN/47T9/23V601 check; inspect/replace brake-fluid cap; use specified fluid</x:v>
+      </x:c>
+      <x:c r="G542" s="9" t="str">
+        <x:v>SOURCE-ID MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H542" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I542" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J542" s="9" t="str">
+        <x:v>2021 S7 47T9</x:v>
+      </x:c>
+      <x:c r="K542" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L542" s="9" t="str"/>
+      <x:c r="M542" s="9" t="str">
+        <x:v>Cap-label recall, not steering rack.</x:v>
+      </x:c>
+      <x:c r="N542" s="41" t="str">
+        <x:v>Rename/re-key; no steering/cap/fluid product.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="543" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A543" s="40" t="str"/>
+      <x:c r="B543" s="9" t="str"/>
+      <x:c r="C543" s="9" t="str"/>
+      <x:c r="D543" s="9" t="str"/>
+      <x:c r="E543" s="9" t="str"/>
+      <x:c r="F543" s="9" t="str"/>
+      <x:c r="G543" s="9" t="str"/>
+      <x:c r="H543" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I543" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J543" s="9" t="str">
+        <x:v>23V601 VIN history</x:v>
+      </x:c>
+      <x:c r="K543" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L543" s="9" t="str"/>
+      <x:c r="M543" s="9" t="str"/>
+      <x:c r="N543" s="41" t="str"/>
+    </x:row>
+    <x:row r="544" ht="699.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A544" s="40" t="n">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="B544" s="9" t="str">
+        <x:v>audi-s7-front-control-arm-bushing-ball-joint-failure</x:v>
+      </x:c>
+      <x:c r="C544" s="9" t="str">
+        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+      </x:c>
+      <x:c r="D544" s="9" t="str">
+        <x:v>Front Control Arm Bushing and Ball Joint Failure (C7 Suspension)</x:v>
+      </x:c>
+      <x:c r="E544" s="9" t="str">
+        <x:v>Inspect all front control arms for play in the bushings and ball joints. Replace worn arms — many owners do the full front control-arm set (commonly a 16-piece kit covering both sides) to avoid repeat visits since the labor overlaps. Critical install notes: torque the bushing bolts at ride height (not with the suspension hanging) to avoid pre-loading and destroying the new bushings, and perform a four-wheel alignment afterward.</x:v>
+      </x:c>
+      <x:c r="F544" s="9" t="str">
+        <x:v>Loaded inspection each arm/joint; exact C7 position/VIN or complete verified kit; one-time hardware, ride-height torque and alignment</x:v>
+      </x:c>
+      <x:c r="G544" s="9" t="str">
+        <x:v>POSITION / KIT-COMPLETENESS GATE</x:v>
+      </x:c>
+      <x:c r="H544" s="9" t="str">
+        <x:v>Audi S7 control-arm catalog</x:v>
+      </x:c>
+      <x:c r="I544" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/S7/Control-Arms/</x:v>
+      </x:c>
+      <x:c r="J544" s="9" t="str">
+        <x:v>2013-2018 C7 S7 exact position/VIN/kit contents</x:v>
+      </x:c>
+      <x:c r="K544" s="9" t="str">
+        <x:v>vehicle-specific suspension catalog</x:v>
+      </x:c>
+      <x:c r="L544" s="9" t="str"/>
+      <x:c r="M544" s="9" t="str">
+        <x:v>Not every car needs a 16-piece kit.</x:v>
+      </x:c>
+      <x:c r="N544" s="41" t="str">
+        <x:v>Verify hardware/positions before full-set link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="545" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A545" s="40" t="str"/>
+      <x:c r="B545" s="9" t="str"/>
+      <x:c r="C545" s="9" t="str"/>
+      <x:c r="D545" s="9" t="str"/>
+      <x:c r="E545" s="9" t="str"/>
+      <x:c r="F545" s="9" t="str"/>
+      <x:c r="G545" s="9" t="str"/>
+      <x:c r="H545" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I545" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J545" s="9" t="str">
+        <x:v>loaded inspection/ride-height torque/alignment</x:v>
+      </x:c>
+      <x:c r="K545" s="9" t="str">
+        <x:v>specialist suspension service</x:v>
+      </x:c>
+      <x:c r="L545" s="9" t="str"/>
+      <x:c r="M545" s="9" t="str"/>
+      <x:c r="N545" s="41" t="str"/>
+    </x:row>
+    <x:row r="546" ht="396" hidden="0" customHeight="1">
+      <x:c r="A546" s="40" t="n">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="B546" s="9" t="str">
+        <x:v>audi-s7-fuel-injector-deposits-failure-causing-misfire-rough-running</x:v>
+      </x:c>
+      <x:c r="C546" s="9" t="str">
+        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
+      </x:c>
+      <x:c r="D546" s="9" t="str">
+        <x:v>Fuel Injector Deposits / Failure Causing Misfire and Rough Running (4.0T V8)</x:v>
+      </x:c>
+      <x:c r="E546" s="9" t="str">
+        <x:v>Pull misfire counts per cylinder to localize the fault. Inspect/replace failed or leaking injectors and renew injector seals; replace spark plugs and any weak coils as a set. Confirm fuel trims return to normal and clear codes; address intake carbon if present.</x:v>
+      </x:c>
+      <x:c r="F546" s="9" t="str">
+        <x:v>Cylinder-specific misfire/fuel-trim/injector leak/balance diagnosis; exact injector/seals; plugs/coils/carbon only if separately failed</x:v>
+      </x:c>
+      <x:c r="G546" s="9" t="str">
+        <x:v>CYLINDER / INJECTOR-DIAGNOSIS GATE</x:v>
+      </x:c>
+      <x:c r="H546" s="9" t="str">
+        <x:v>Audi S7 fuel-injector catalog</x:v>
+      </x:c>
+      <x:c r="I546" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/S7/Fuel-Injector/</x:v>
+      </x:c>
+      <x:c r="J546" s="9" t="str">
+        <x:v>2013-2018 S7 4.0T exact VIN/current revision</x:v>
+      </x:c>
+      <x:c r="K546" s="9" t="str">
+        <x:v>vehicle-specific injector catalog</x:v>
+      </x:c>
+      <x:c r="L546" s="9" t="str"/>
+      <x:c r="M546" s="9" t="str">
+        <x:v>Source wrongly bundles plugs/coils as a set and carbon.</x:v>
+      </x:c>
+      <x:c r="N546" s="41" t="str">
+        <x:v>Replace only confirmed injector/secondary faults.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="547" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A547" s="40" t="str"/>
+      <x:c r="B547" s="9" t="str"/>
+      <x:c r="C547" s="9" t="str"/>
+      <x:c r="D547" s="9" t="str"/>
+      <x:c r="E547" s="9" t="str"/>
+      <x:c r="F547" s="9" t="str"/>
+      <x:c r="G547" s="9" t="str"/>
+      <x:c r="H547" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I547" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J547" s="9" t="str">
+        <x:v>injector/misfire diagnosis</x:v>
+      </x:c>
+      <x:c r="K547" s="9" t="str">
+        <x:v>specialist fuel service</x:v>
+      </x:c>
+      <x:c r="L547" s="9" t="str"/>
+      <x:c r="M547" s="9" t="str"/>
+      <x:c r="N547" s="41" t="str"/>
+    </x:row>
+    <x:row r="548" ht="396" hidden="0" customHeight="1">
+      <x:c r="A548" s="40" t="n">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="B548" s="9" t="str">
+        <x:v>audi-s7-gateway-control-module-shutdown-from-rear-seat-liquid-spill</x:v>
+      </x:c>
+      <x:c r="C548" s="9" t="str">
+        <x:v>2020-2022 | Audi | S7 | 2.9 TFSI</x:v>
+      </x:c>
+      <x:c r="D548" s="9" t="str">
+        <x:v>Rear-Seat Liquid Spill Can Shut Down Gateway Module (Recall 22V861 / 90V2)</x:v>
+      </x:c>
+      <x:c r="E548" s="9" t="str">
+        <x:v>Check the VIN and campaign history. Audi dealers install a protective gateway-module cover free of charge under campaign 90V2. If multiple warnings or reduced power occur after a spill, move out of traffic safely and arrange dealer inspection.</x:v>
+      </x:c>
+      <x:c r="F548" s="9" t="str">
+        <x:v>VIN/90V2/22V861 check; gateway protective cover; safe response to warnings/reduced power</x:v>
+      </x:c>
+      <x:c r="G548" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H548" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I548" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J548" s="9" t="str">
+        <x:v>2020-2022 S7 90V2</x:v>
+      </x:c>
+      <x:c r="K548" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L548" s="9" t="str"/>
+      <x:c r="M548" s="9" t="str">
+        <x:v>Cover is free remedy.</x:v>
+      </x:c>
+      <x:c r="N548" s="41" t="str">
+        <x:v>No gateway module link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="549" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A549" s="40" t="str"/>
+      <x:c r="B549" s="9" t="str"/>
+      <x:c r="C549" s="9" t="str"/>
+      <x:c r="D549" s="9" t="str"/>
+      <x:c r="E549" s="9" t="str"/>
+      <x:c r="F549" s="9" t="str"/>
+      <x:c r="G549" s="9" t="str"/>
+      <x:c r="H549" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I549" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J549" s="9" t="str">
+        <x:v>22V861 VIN history</x:v>
+      </x:c>
+      <x:c r="K549" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L549" s="9" t="str"/>
+      <x:c r="M549" s="9" t="str"/>
+      <x:c r="N549" s="41" t="str"/>
+    </x:row>
+    <x:row r="550" ht="528" hidden="0" customHeight="1">
+      <x:c r="A550" s="40" t="n">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="B550" s="9" t="str">
+        <x:v>audi-s7-high-pressure-fuel-pump-failure-causing-hard-start-power-los</x:v>
+      </x:c>
+      <x:c r="C550" s="9" t="str">
+        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
+      </x:c>
+      <x:c r="D550" s="9" t="str">
+        <x:v>High-Pressure Fuel Pump (HPFP) Failure Causing Hard Start and Power Loss (4.0T V8)</x:v>
+      </x:c>
+      <x:c r="E550" s="9" t="str">
+        <x:v>Diagnose with live fuel-rail pressure data before condemning the pump, as a faulty low-pressure sensor or in-tank pump can set the same codes. Replace the failed high-pressure pump (the affected bank, or both as a set on high-mileage cars) together with the cam follower and seals. Verify low-pressure (in-tank) supply is within spec.</x:v>
+      </x:c>
+      <x:c r="F550" s="9" t="str">
+        <x:v>Rail actual/target, low-side supply/sensor and bank diagnosis; exact bank/VIN HPFP if failed; cam follower/seals only per engine procedure; both pumps only by strategy</x:v>
+      </x:c>
+      <x:c r="G550" s="9" t="str">
+        <x:v>BANK / FUEL-PRESSURE GATE</x:v>
+      </x:c>
+      <x:c r="H550" s="9" t="str">
+        <x:v>Audi S7 HPFP catalog</x:v>
+      </x:c>
+      <x:c r="I550" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/S7/High-Pressure-Fuel-Pump/</x:v>
+      </x:c>
+      <x:c r="J550" s="9" t="str">
+        <x:v>2013-2018 S7 4.0T exact bank/VIN after diagnosis</x:v>
+      </x:c>
+      <x:c r="K550" s="9" t="str">
+        <x:v>vehicle-specific HPFP catalog</x:v>
+      </x:c>
+      <x:c r="L550" s="9" t="str"/>
+      <x:c r="M550" s="9" t="str">
+        <x:v>Low-side/sensor faults mimic HPFP.</x:v>
+      </x:c>
+      <x:c r="N550" s="41" t="str">
+        <x:v>No both-pump/follower bundle by mileage alone.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="551" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A551" s="40" t="str"/>
+      <x:c r="B551" s="9" t="str"/>
+      <x:c r="C551" s="9" t="str"/>
+      <x:c r="D551" s="9" t="str"/>
+      <x:c r="E551" s="9" t="str"/>
+      <x:c r="F551" s="9" t="str"/>
+      <x:c r="G551" s="9" t="str"/>
+      <x:c r="H551" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I551" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J551" s="9" t="str">
+        <x:v>low/high pressure diagnosis</x:v>
+      </x:c>
+      <x:c r="K551" s="9" t="str">
+        <x:v>specialist fuel service</x:v>
+      </x:c>
+      <x:c r="L551" s="9" t="str"/>
+      <x:c r="M551" s="9" t="str"/>
+      <x:c r="N551" s="41" t="str"/>
+    </x:row>
+    <x:row r="552" ht="660" hidden="0" customHeight="1">
+      <x:c r="A552" s="40" t="n">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="B552" s="9" t="str">
+        <x:v>audi-s7-ignition-coil-pack-failure-causing-misfires</x:v>
+      </x:c>
+      <x:c r="C552" s="9" t="str">
+        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+      </x:c>
+      <x:c r="D552" s="9" t="str">
+        <x:v>Ignition Coil Pack Failure Causing Misfires (4.0T V8)</x:v>
+      </x:c>
+      <x:c r="E552" s="9" t="str">
+        <x:v>Confirm the failing cylinder, then swap the suspect coil to another cylinder to verify the fault follows the coil. Replace the failed coil; best practice on the 4.0T is to replace all eight coils and the spark plugs as a set since the access labor is shared and mixed-age coils tend to fail in sequence. Use OE or quality OE-equivalent coils (the 4.0T uses the 079905110-series coil). Inspect spark plugs for fouling/oil that could indicate a secondary issue.</x:v>
+      </x:c>
+      <x:c r="F552" s="9" t="str">
+        <x:v>Cylinder-specific swap test; exact 079905110-series current VIN coil; plugs/full set only by condition/strategy; inspect oil fouling</x:v>
+      </x:c>
+      <x:c r="G552" s="9" t="str">
+        <x:v>CYLINDER / COIL-REVISION GATE</x:v>
+      </x:c>
+      <x:c r="H552" s="9" t="str">
+        <x:v>Audi S7 ignition-coil catalog</x:v>
+      </x:c>
+      <x:c r="I552" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/S7/Ignition-Coil/</x:v>
+      </x:c>
+      <x:c r="J552" s="9" t="str">
+        <x:v>2013-2018 S7 4.0T exact VIN/current revision</x:v>
+      </x:c>
+      <x:c r="K552" s="9" t="str">
+        <x:v>vehicle-specific coil catalog</x:v>
+      </x:c>
+      <x:c r="L552" s="9" t="str"/>
+      <x:c r="M552" s="9" t="str">
+        <x:v>Swap-test supports failed coil, not automatic eight-coil/plug set.</x:v>
+      </x:c>
+      <x:c r="N552" s="41" t="str">
+        <x:v>Do not generalize mixed-age failure sequence.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="553" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A553" s="40" t="str"/>
+      <x:c r="B553" s="9" t="str"/>
+      <x:c r="C553" s="9" t="str"/>
+      <x:c r="D553" s="9" t="str"/>
+      <x:c r="E553" s="9" t="str"/>
+      <x:c r="F553" s="9" t="str"/>
+      <x:c r="G553" s="9" t="str"/>
+      <x:c r="H553" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I553" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J553" s="9" t="str">
+        <x:v>misfire/secondary-cause diagnosis</x:v>
+      </x:c>
+      <x:c r="K553" s="9" t="str">
+        <x:v>specialist ignition service</x:v>
+      </x:c>
+      <x:c r="L553" s="9" t="str"/>
+      <x:c r="M553" s="9" t="str"/>
+      <x:c r="N553" s="41" t="str"/>
+    </x:row>
+    <x:row r="554" ht="237.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A554" s="40" t="n">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="B554" s="9" t="str">
+        <x:v>audi-s7-motor-mount-failure-2012</x:v>
+      </x:c>
+      <x:c r="C554" s="9" t="str">
+        <x:v>2013-2018 | Audi | S7</x:v>
+      </x:c>
+      <x:c r="D554" s="9" t="str">
+        <x:v>Passenger Occupant Detection Mat Can Disable the Airbag (Recall 18V370 / 74D5)</x:v>
+      </x:c>
+      <x:c r="E554" s="9" t="str">
+        <x:v>Check VIN eligibility because seat equipment affects scope. Audi dealers install the occupant-detection repair kit free of charge under campaign 74D5.</x:v>
+      </x:c>
+      <x:c r="F554" s="9" t="str">
+        <x:v>VIN/74D5/18V370 check; occupant-detection repair kit</x:v>
+      </x:c>
+      <x:c r="G554" s="9" t="str">
+        <x:v>SOURCE-ID/YEAR MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H554" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I554" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J554" s="9" t="str">
+        <x:v>2013-2018 S7 74D5</x:v>
+      </x:c>
+      <x:c r="K554" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L554" s="9" t="str"/>
+      <x:c r="M554" s="9" t="str">
+        <x:v>Airbag seat-mat recall, not motor mounts.</x:v>
+      </x:c>
+      <x:c r="N554" s="41" t="str">
+        <x:v>Rename/re-key; no mount/ODS product.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="555" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A555" s="40" t="str"/>
+      <x:c r="B555" s="9" t="str"/>
+      <x:c r="C555" s="9" t="str"/>
+      <x:c r="D555" s="9" t="str"/>
+      <x:c r="E555" s="9" t="str"/>
+      <x:c r="F555" s="9" t="str"/>
+      <x:c r="G555" s="9" t="str"/>
+      <x:c r="H555" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I555" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J555" s="9" t="str">
+        <x:v>18V370 VIN history</x:v>
+      </x:c>
+      <x:c r="K555" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L555" s="9" t="str"/>
+      <x:c r="M555" s="9" t="str"/>
+      <x:c r="N555" s="41" t="str"/>
+    </x:row>
+    <x:row r="556" ht="580.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A556" s="40" t="n">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="B556" s="9" t="str">
+        <x:v>audi-s7-pcv-oil-separator-failure-causing-oil-consumption-whistling</x:v>
+      </x:c>
+      <x:c r="C556" s="9" t="str">
+        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
+      </x:c>
+      <x:c r="D556" s="9" t="str">
+        <x:v>PCV / Oil Separator (Ölabscheider) Failure Causing Oil Consumption and Whistling (4.0T V8)</x:v>
+      </x:c>
+      <x:c r="E556" s="9" t="str">
+        <x:v>Replace the failed oil separator / PCV assembly and the associated breather hose with the latest revised part. An ECM update may accompany the new part on some VINs. Confirm with a smoke test for intake-side vacuum leaks; inspect the rear main seal if oil consumption is severe, as a failed PCV is a common cause of rear main seal damage on these engines.</x:v>
+      </x:c>
+      <x:c r="F556" s="9" t="str">
+        <x:v>Smoke/crankcase-pressure/whistle and oil-consumption diagnosis; exact VIN oil separator/breather; ECM update when applicable; rear-main seal only if leaking</x:v>
+      </x:c>
+      <x:c r="G556" s="9" t="str">
+        <x:v>DIAGNOSIS / VIN PCV GATE</x:v>
+      </x:c>
+      <x:c r="H556" s="9" t="str">
+        <x:v>Audi S7 PCV catalog</x:v>
+      </x:c>
+      <x:c r="I556" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/S7/PCV/</x:v>
+      </x:c>
+      <x:c r="J556" s="9" t="str">
+        <x:v>2013-2018 S7 4.0T exact VIN/current revision after diagnosis</x:v>
+      </x:c>
+      <x:c r="K556" s="9" t="str">
+        <x:v>conditional PCV catalog</x:v>
+      </x:c>
+      <x:c r="L556" s="9" t="str"/>
+      <x:c r="M556" s="9" t="str">
+        <x:v>PCV and rear-main are separate branches.</x:v>
+      </x:c>
+      <x:c r="N556" s="41" t="str">
+        <x:v>No automatic breather hose/rear-main replacement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="557" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A557" s="40" t="str"/>
+      <x:c r="B557" s="9" t="str"/>
+      <x:c r="C557" s="9" t="str"/>
+      <x:c r="D557" s="9" t="str"/>
+      <x:c r="E557" s="9" t="str"/>
+      <x:c r="F557" s="9" t="str"/>
+      <x:c r="G557" s="9" t="str"/>
+      <x:c r="H557" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I557" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J557" s="9" t="str">
+        <x:v>smoke/crankcase/rear-main diagnosis</x:v>
+      </x:c>
+      <x:c r="K557" s="9" t="str">
+        <x:v>specialist engine service</x:v>
+      </x:c>
+      <x:c r="L557" s="9" t="str"/>
+      <x:c r="M557" s="9" t="str"/>
+      <x:c r="N557" s="41" t="str"/>
+    </x:row>
+    <x:row r="558" ht="633.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A558" s="40" t="n">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="B558" s="9" t="str">
+        <x:v>audi-s7-power-liftgate-motor-gas-strut-failure</x:v>
+      </x:c>
+      <x:c r="C558" s="9" t="str">
+        <x:v>2013-2022 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824), 2.9T TFSI Biturbo V6 (EA839)</x:v>
+      </x:c>
+      <x:c r="D558" s="9" t="str">
+        <x:v>Power Liftgate Motor and Gas Strut Failure (Sportback Tailgate)</x:v>
+      </x:c>
+      <x:c r="E558" s="9" t="str">
+        <x:v>Diagnose whether the fault is the gas struts (won't stay up / weak lift), the spindle lift motors (slow or struggling travel), or the latch/cinching motor (won't release or won't pull closed — see TSB 2072431/1). Replace worn gas struts in pairs; replace failed lift or cinching motors as needed. After repair, perform the power-liftgate relearn/reset procedure so travel limits recalibrate.</x:v>
+      </x:c>
+      <x:c r="F558" s="9" t="str">
+        <x:v>Split generations; diagnose gas struts versus spindle lift motors versus latch/cinching; position/VIN component; struts paired; relearn per procedure</x:v>
+      </x:c>
+      <x:c r="G558" s="9" t="str">
+        <x:v>GENERATION / COMPONENT GATE</x:v>
+      </x:c>
+      <x:c r="H558" s="9" t="str">
+        <x:v>Audi S7 liftgate catalog</x:v>
+      </x:c>
+      <x:c r="I558" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/S7/Liftgate-and-Parts/</x:v>
+      </x:c>
+      <x:c r="J558" s="9" t="str">
+        <x:v>2013-2022 exact generation/VIN/component</x:v>
+      </x:c>
+      <x:c r="K558" s="9" t="str">
+        <x:v>vehicle-specific liftgate catalog</x:v>
+      </x:c>
+      <x:c r="L558" s="9" t="str"/>
+      <x:c r="M558" s="9" t="str">
+        <x:v>Weak support, slow travel and latch failure differ.</x:v>
+      </x:c>
+      <x:c r="N558" s="41" t="str">
+        <x:v>Engine list/generation must be split before link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="559" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A559" s="40" t="str"/>
+      <x:c r="B559" s="9" t="str"/>
+      <x:c r="C559" s="9" t="str"/>
+      <x:c r="D559" s="9" t="str"/>
+      <x:c r="E559" s="9" t="str"/>
+      <x:c r="F559" s="9" t="str"/>
+      <x:c r="G559" s="9" t="str"/>
+      <x:c r="H559" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I559" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J559" s="9" t="str">
+        <x:v>TSB 2072431/1 latch/motor diagnosis</x:v>
+      </x:c>
+      <x:c r="K559" s="9" t="str">
+        <x:v>specialist body service</x:v>
+      </x:c>
+      <x:c r="L559" s="9" t="str"/>
+      <x:c r="M559" s="9" t="str"/>
+      <x:c r="N559" s="41" t="str"/>
+    </x:row>
+    <x:row r="560" ht="739.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A560" s="40" t="n">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="B560" s="9" t="str">
+        <x:v>audi-s7-premature-front-brake-rotor-warping-pad-wear</x:v>
+      </x:c>
+      <x:c r="C560" s="9" t="str">
+        <x:v>2013-2022 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824), 2.9T TFSI Biturbo V6 (EA839)</x:v>
+      </x:c>
+      <x:c r="D560" s="9" t="str">
+        <x:v>Premature Front Brake Rotor Warping and Pad Wear</x:v>
+      </x:c>
+      <x:c r="E560" s="9" t="str">
+        <x:v>Replace warped/below-spec rotors and pads together; consider higher-quality coated or upgraded rotors that resist warping better than the soft OEM units. Bed in new pads/rotors properly and avoid riding the brakes to prevent uneven deposits. Ensure caliper guide pins/slides move freely so pads engage evenly. For repeat warping, an upgraded rotor-and-pad package is the durable fix; address any pulsation early before it damages new components.</x:v>
+      </x:c>
+      <x:c r="F560" s="9" t="str">
+        <x:v>Split generations/brake PR codes; measure runout/thickness/pad/caliper/hub; exact axle pads/rotors only if failed; correct bedding</x:v>
+      </x:c>
+      <x:c r="G560" s="9" t="str">
+        <x:v>GENERATION / BRAKE-OPTION / MEASUREMENT GATE</x:v>
+      </x:c>
+      <x:c r="H560" s="9" t="str">
+        <x:v>Audi S7 brake catalog</x:v>
+      </x:c>
+      <x:c r="I560" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/S7/Brakes/</x:v>
+      </x:c>
+      <x:c r="J560" s="9" t="str">
+        <x:v>2013-2022 exact VIN/PR code/axle</x:v>
+      </x:c>
+      <x:c r="K560" s="9" t="str">
+        <x:v>vehicle-specific brake catalog</x:v>
+      </x:c>
+      <x:c r="L560" s="9" t="str"/>
+      <x:c r="M560" s="9" t="str">
+        <x:v>Pulsation is not necessarily rotor warping.</x:v>
+      </x:c>
+      <x:c r="N560" s="41" t="str">
+        <x:v>No upgraded package or OEM-soft claim without exact evidence.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="561" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A561" s="40" t="str"/>
+      <x:c r="B561" s="9" t="str"/>
+      <x:c r="C561" s="9" t="str"/>
+      <x:c r="D561" s="9" t="str"/>
+      <x:c r="E561" s="9" t="str"/>
+      <x:c r="F561" s="9" t="str"/>
+      <x:c r="G561" s="9" t="str"/>
+      <x:c r="H561" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I561" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J561" s="9" t="str">
+        <x:v>runout/hub/caliper diagnosis</x:v>
+      </x:c>
+      <x:c r="K561" s="9" t="str">
+        <x:v>specialist brake service</x:v>
+      </x:c>
+      <x:c r="L561" s="9" t="str"/>
+      <x:c r="M561" s="9" t="str"/>
+      <x:c r="N561" s="41" t="str"/>
+    </x:row>
+    <x:row r="562" ht="778.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A562" s="40" t="n">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="B562" s="9" t="str">
+        <x:v>audi-s7-rear-differential-mount-driveshaft-center-bearing-wear-causi</x:v>
+      </x:c>
+      <x:c r="C562" s="9" t="str">
+        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+      </x:c>
+      <x:c r="D562" s="9" t="str">
+        <x:v>Rear Differential Mount and Driveshaft Center Bearing Wear Causing Drivetrain Clunk (C7)</x:v>
+      </x:c>
+      <x:c r="E562" s="9" t="str">
+        <x:v>Inspect the rear differential mount and driveshaft center support bearing for play and torn rubber. Replace worn components with OE parts, or fit billet aluminum diff/transmission mount inserts that fill the factory voids to remove the slop without adding harshness. On 4.0T cars, also check for the separate active-engine-mount software TSB before condemning a mount for a 1,000-3,000 RPM cruise vibration. Reassess the clunk after each fix since multiple sources can contribute.</x:v>
+      </x:c>
+      <x:c r="F562" s="9" t="str">
+        <x:v>Inspect diff mount, center bearing, driveshaft joints and active-engine-mount TSB; exact failed component/VIN; insert only with verified fitment/NVH disclosure</x:v>
+      </x:c>
+      <x:c r="G562" s="9" t="str">
+        <x:v>ROOT-CAUSE / DRIVELINE-COMPONENT GATE</x:v>
+      </x:c>
+      <x:c r="H562" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I562" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J562" s="9" t="str">
+        <x:v>2013-2018 S7 clunk/vibration diagnosis</x:v>
+      </x:c>
+      <x:c r="K562" s="9" t="str">
+        <x:v>specialist driveline service</x:v>
+      </x:c>
+      <x:c r="L562" s="9" t="str"/>
+      <x:c r="M562" s="9" t="str">
+        <x:v>Multiple sources contribute and inserts change compliance/NVH.</x:v>
+      </x:c>
+      <x:c r="N562" s="41" t="str">
+        <x:v>No billet insert promise without exact live fitment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="563" ht="66" hidden="0" customHeight="1">
+      <x:c r="A563" s="40" t="str"/>
+      <x:c r="B563" s="9" t="str"/>
+      <x:c r="C563" s="9" t="str"/>
+      <x:c r="D563" s="9" t="str"/>
+      <x:c r="E563" s="9" t="str"/>
+      <x:c r="F563" s="9" t="str"/>
+      <x:c r="G563" s="9" t="str"/>
+      <x:c r="H563" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I563" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J563" s="9" t="str">
+        <x:v>VIN mount/bearing and active-mount TSB</x:v>
+      </x:c>
+      <x:c r="K563" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L563" s="9" t="str"/>
+      <x:c r="M563" s="9" t="str"/>
+      <x:c r="N563" s="41" t="str"/>
+    </x:row>
+    <x:row r="564" ht="462" hidden="0" customHeight="1">
+      <x:c r="A564" s="40" t="n">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B564" s="9" t="str">
+        <x:v>audi-s7-rear-view-camera-mmi-flex-harness-black-screen</x:v>
+      </x:c>
+      <x:c r="C564" s="9" t="str">
+        <x:v>2013-2018 | Audi | S7 | S7 (C7), A7 (C7) | 4.0 TFSI V8 (EA824)</x:v>
+      </x:c>
+      <x:c r="D564" s="9" t="str">
+        <x:v>Rear-View Camera / MMI Flex Harness Black Screen</x:v>
+      </x:c>
+      <x:c r="E564" s="9" t="str">
+        <x:v>Diagnose with a scan and continuity check of the tailgate-to-body flex harness before replacing the camera. Repair or replace the broken hinge-side loom conductors; if confirmed faulty, replace the camera module. For MMI freezes, apply the latest software update or reset the unit.</x:v>
+      </x:c>
+      <x:c r="F564" s="9" t="str">
+        <x:v>Scan plus tailgate flex-harness continuity; repair broken conductors or exact loom; camera only if failed; MMI software branch separately</x:v>
+      </x:c>
+      <x:c r="G564" s="9" t="str">
+        <x:v>HARNESS-FIRST / CAMERA-SOFTWARE SPLIT</x:v>
+      </x:c>
+      <x:c r="H564" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I564" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J564" s="9" t="str">
+        <x:v>2013-2018 S7 tailgate harness/camera/MMI diagnosis</x:v>
+      </x:c>
+      <x:c r="K564" s="9" t="str">
+        <x:v>specialist electrical service</x:v>
+      </x:c>
+      <x:c r="L564" s="9" t="str"/>
+      <x:c r="M564" s="9" t="str">
+        <x:v>Black screen does not establish camera failure.</x:v>
+      </x:c>
+      <x:c r="N564" s="41" t="str">
+        <x:v>No camera/harness link before continuity and exact break/part proof.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="565" ht="66" hidden="0" customHeight="1">
+      <x:c r="A565" s="40" t="str"/>
+      <x:c r="B565" s="9" t="str"/>
+      <x:c r="C565" s="9" t="str"/>
+      <x:c r="D565" s="9" t="str"/>
+      <x:c r="E565" s="9" t="str"/>
+      <x:c r="F565" s="9" t="str"/>
+      <x:c r="G565" s="9" t="str"/>
+      <x:c r="H565" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I565" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J565" s="9" t="str">
+        <x:v>VIN loom/camera/software</x:v>
+      </x:c>
+      <x:c r="K565" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L565" s="9" t="str"/>
+      <x:c r="M565" s="9" t="str"/>
+      <x:c r="N565" s="41" t="str"/>
+    </x:row>
+    <x:row r="566" ht="567.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A566" s="40" t="n">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="B566" s="9" t="str">
+        <x:v>audi-s7-s-tronic-7-speed-dual-clutch-mechatronic-clutch-wear</x:v>
+      </x:c>
+      <x:c r="C566" s="9" t="str">
+        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T (S-tronic / 0B5 DL501) | 4.0 TFSI V8 (EA824)</x:v>
+      </x:c>
+      <x:c r="D566" s="9" t="str">
+        <x:v>S-tronic 7-Speed Dual-Clutch (DL501/0B5) Mechatronic and Clutch Wear</x:v>
+      </x:c>
+      <x:c r="E566" s="9" t="str">
+        <x:v>Perform the S-tronic gearbox oil and filter service on schedule (roughly every 40,000-60,000 km). For judder/jerking, have the mechatronic unit tested; recondition or replace the valve body with the superseded design and adapt/replace the clutch packs as needed. Software adaptation resets can temporarily improve drivability but do not fix worn hardware.</x:v>
+      </x:c>
+      <x:c r="F566" s="9" t="str">
+        <x:v>Confirm DL501/0B5 code; faults/pressure/adaptation, clutch and mechanical diagnosis; exact gearbox fluid/filter service; valve body/clutch only by test</x:v>
+      </x:c>
+      <x:c r="G566" s="9" t="str">
+        <x:v>TRANSMISSION-CODE / COMPONENT GATE</x:v>
+      </x:c>
+      <x:c r="H566" s="9" t="str">
+        <x:v>Audi S7 transmission-service catalog</x:v>
+      </x:c>
+      <x:c r="I566" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/S7/Automatic-Transmission-Service/</x:v>
+      </x:c>
+      <x:c r="J566" s="9" t="str">
+        <x:v>2013-2018 S7 DL501 exact VIN/fluid/filter</x:v>
+      </x:c>
+      <x:c r="K566" s="9" t="str">
+        <x:v>vehicle-specific transmission catalog</x:v>
+      </x:c>
+      <x:c r="L566" s="9" t="str"/>
+      <x:c r="M566" s="9" t="str">
+        <x:v>Service, valve body and clutch are separate branches.</x:v>
+      </x:c>
+      <x:c r="N566" s="41" t="str">
+        <x:v>Verify schedule from exact US manual; reset does not fix wear.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="567" ht="66" hidden="0" customHeight="1">
+      <x:c r="A567" s="40" t="str"/>
+      <x:c r="B567" s="9" t="str"/>
+      <x:c r="C567" s="9" t="str"/>
+      <x:c r="D567" s="9" t="str"/>
+      <x:c r="E567" s="9" t="str"/>
+      <x:c r="F567" s="9" t="str"/>
+      <x:c r="G567" s="9" t="str"/>
+      <x:c r="H567" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I567" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J567" s="9" t="str">
+        <x:v>mechatronic/clutch diagnosis/adaptation</x:v>
+      </x:c>
+      <x:c r="K567" s="9" t="str">
+        <x:v>specialist transmission service</x:v>
+      </x:c>
+      <x:c r="L567" s="9" t="str"/>
+      <x:c r="M567" s="9" t="str"/>
+      <x:c r="N567" s="41" t="str"/>
+    </x:row>
+    <x:row r="568" ht="778.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A568" s="40" t="n">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B568" s="9" t="str">
+        <x:v>audi-s7-shark-fin-roof-antenna-water-intrusion-causing-gps-satellite</x:v>
+      </x:c>
+      <x:c r="C568" s="9" t="str">
+        <x:v>2013-2018 | Audi | S7 | Prestige, Premium Plus | 4.0T Biturbo V8 (4.0 TFSI)</x:v>
+      </x:c>
+      <x:c r="D568" s="9" t="str">
+        <x:v>Shark-Fin Roof Antenna Water Intrusion Causing GPS / Satellite Radio Reception Loss (C7)</x:v>
+      </x:c>
+      <x:c r="E568" s="9" t="str">
+        <x:v>Test/replace the shark-fin antenna module with a matching OEM part number and renew the base gasket to restore a watertight seal; in many cases the official fix is a repair kit with a new FAKRA connector and adapter cable rather than a whole new antenna. Access requires partially dropping the rear headliner to reach the single mounting nut and reconnect the coax leads. Inspecting and reseating a corroded coax connection sometimes restores reception without full replacement.</x:v>
+      </x:c>
+      <x:c r="F568" s="9" t="str">
+        <x:v>Water/reception/coax diagnosis; exact VIN antenna module or FAKRA repair kit/gasket; reseat/repair corrosion when possible; water test</x:v>
+      </x:c>
+      <x:c r="G568" s="9" t="str">
+        <x:v>MODULE / CONNECTOR / VIN GATE</x:v>
+      </x:c>
+      <x:c r="H568" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I568" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J568" s="9" t="str">
+        <x:v>2013-2018 S7 antenna/FAKRA kit by VIN</x:v>
+      </x:c>
+      <x:c r="K568" s="9" t="str">
+        <x:v>manufacturer parts/service</x:v>
+      </x:c>
+      <x:c r="L568" s="9" t="str"/>
+      <x:c r="M568" s="9" t="str">
+        <x:v>Connector kit may avoid antenna replacement.</x:v>
+      </x:c>
+      <x:c r="N568" s="41" t="str">
+        <x:v>No whole antenna before exact module/coax failure.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="569" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A569" s="40" t="str"/>
+      <x:c r="B569" s="9" t="str"/>
+      <x:c r="C569" s="9" t="str"/>
+      <x:c r="D569" s="9" t="str"/>
+      <x:c r="E569" s="9" t="str"/>
+      <x:c r="F569" s="9" t="str"/>
+      <x:c r="G569" s="9" t="str"/>
+      <x:c r="H569" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I569" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J569" s="9" t="str">
+        <x:v>coax/reception/water diagnosis</x:v>
+      </x:c>
+      <x:c r="K569" s="9" t="str">
+        <x:v>specialist electrical service</x:v>
+      </x:c>
+      <x:c r="L569" s="9" t="str"/>
+      <x:c r="M569" s="9" t="str"/>
+      <x:c r="N569" s="41" t="str"/>
+    </x:row>
+    <x:row r="570" ht="752.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A570" s="40" t="n">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="B570" s="9" t="str">
+        <x:v>audi-s7-sunroof-panoramic-roof-drain-clog-causing-water-intrusion-el</x:v>
+      </x:c>
+      <x:c r="C570" s="9" t="str">
+        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+      </x:c>
+      <x:c r="D570" s="9" t="str">
+        <x:v>Sunroof / Panoramic Roof Drain Clog Causing Water Intrusion and Electronics Damage (C7)</x:v>
+      </x:c>
+      <x:c r="E570" s="9" t="str">
+        <x:v>Test the drains by slowly pouring water into the channels at each corner of the sunroof and watching where it exits beneath the A- and C-pillars. Clear clogged tubes with low-pressure air or a soft trimmer line (avoid stiff wire that can puncture the tube) and reseat/secure any loose drain-tube connectors at the sunroof frame. Dry out any soaked carpet/insulation promptly and inspect floor-mounted modules for corrosion. Periodic drain cleaning is the best prevention.</x:v>
+      </x:c>
+      <x:c r="F570" s="9" t="str">
+        <x:v>Modest water-test each drain; approved flexible clearing; reseat/replace exact damaged tube; dry carpet/modules</x:v>
+      </x:c>
+      <x:c r="G570" s="9" t="str">
+        <x:v>DRAIN-POSITION / LEAK-SOURCE SERVICE</x:v>
+      </x:c>
+      <x:c r="H570" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I570" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J570" s="9" t="str">
+        <x:v>2013-2018 S7 drain tracing/drying</x:v>
+      </x:c>
+      <x:c r="K570" s="9" t="str">
+        <x:v>specialist water-leak service</x:v>
+      </x:c>
+      <x:c r="L570" s="9" t="str"/>
+      <x:c r="M570" s="9" t="str">
+        <x:v>Blocked/disconnected/damaged drains differ.</x:v>
+      </x:c>
+      <x:c r="N570" s="41" t="str">
+        <x:v>Remove low-pressure air/trimmer-line and annual universal advice.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="571" ht="66" hidden="0" customHeight="1">
+      <x:c r="A571" s="40" t="str"/>
+      <x:c r="B571" s="9" t="str"/>
+      <x:c r="C571" s="9" t="str"/>
+      <x:c r="D571" s="9" t="str"/>
+      <x:c r="E571" s="9" t="str"/>
+      <x:c r="F571" s="9" t="str"/>
+      <x:c r="G571" s="9" t="str"/>
+      <x:c r="H571" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I571" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J571" s="9" t="str">
+        <x:v>position/VIN drain parts</x:v>
+      </x:c>
+      <x:c r="K571" s="9" t="str">
+        <x:v>manufacturer parts route</x:v>
+      </x:c>
+      <x:c r="L571" s="9" t="str"/>
+      <x:c r="M571" s="9" t="str"/>
+      <x:c r="N571" s="41" t="str"/>
+    </x:row>
+    <x:row r="572" ht="422.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A572" s="40" t="n">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="B572" s="9" t="str">
+        <x:v>audi-s7-turbo-oil-strainer-2012</x:v>
+      </x:c>
+      <x:c r="C572" s="9" t="str">
+        <x:v>2013-2017 | Audi | S7 | 4.0 TFSI</x:v>
+      </x:c>
+      <x:c r="D572" s="9" t="str">
+        <x:v>Turbocharger Oil-Supply Strainer Can Block and Cause Engine Stall (Recall 22V178 / 21H7)</x:v>
+      </x:c>
+      <x:c r="E572" s="9" t="str">
+        <x:v>Check the VIN and campaign history. Audi dealers replace the oil strainer and perform an oil change free of charge under campaign 21H7. If abnormal turbo noise, loss of power, or an engine warning occurs, stop safely and arrange dealer inspection.</x:v>
+      </x:c>
+      <x:c r="F572" s="9" t="str">
+        <x:v>VIN/21H7/22V178 check; oil strainer and oil change; inspect damage per campaign</x:v>
+      </x:c>
+      <x:c r="G572" s="9" t="str">
+        <x:v>SOURCE-YEAR MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H572" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I572" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J572" s="9" t="str">
+        <x:v>2013-2017 S7 21H7</x:v>
+      </x:c>
+      <x:c r="K572" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L572" s="9" t="str"/>
+      <x:c r="M572" s="9" t="str">
+        <x:v>Free safety remedy.</x:v>
+      </x:c>
+      <x:c r="N572" s="41" t="str">
+        <x:v>Identifier says 2012; no retail strainer.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="573" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A573" s="40" t="str"/>
+      <x:c r="B573" s="9" t="str"/>
+      <x:c r="C573" s="9" t="str"/>
+      <x:c r="D573" s="9" t="str"/>
+      <x:c r="E573" s="9" t="str"/>
+      <x:c r="F573" s="9" t="str"/>
+      <x:c r="G573" s="9" t="str"/>
+      <x:c r="H573" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I573" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J573" s="9" t="str">
+        <x:v>22V178 VIN history</x:v>
+      </x:c>
+      <x:c r="K573" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L573" s="9" t="str"/>
+      <x:c r="M573" s="9" t="str"/>
+      <x:c r="N573" s="41" t="str"/>
+    </x:row>
+    <x:row r="574" ht="726" hidden="0" customHeight="1">
+      <x:c r="A574" s="40" t="n">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="B574" s="9" t="str">
+        <x:v>audi-s7-turbocharger-wastegate-linkage-rattle-underboost</x:v>
+      </x:c>
+      <x:c r="C574" s="9" t="str">
+        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+      </x:c>
+      <x:c r="D574" s="9" t="str">
+        <x:v>Turbocharger Wastegate Linkage Rattle and Underboost (4.0T V8)</x:v>
+      </x:c>
+      <x:c r="E574" s="9" t="str">
+        <x:v>Diagnose the rattle and any boost faults to confirm wastegate-arm play versus a loose heat shield. Minor play can sometimes be mitigated with a clip, but the durable factory fix is turbocharger replacement. When replacing a hot-V turbo, it is mandatory to also replace the oil feed and return lines and to prime the new unit with oil before first start to prevent immediate bearing failure. Regular oil changes and allowing turbo cool-down help reduce coking-related wear.</x:v>
+      </x:c>
+      <x:c r="F574" s="9" t="str">
+        <x:v>Confirm heat shield versus side-specific wastegate/turbo fault; boost commanded/actual and actuator tests; exact bank turbo only if failed; required lines/seals per procedure</x:v>
+      </x:c>
+      <x:c r="G574" s="9" t="str">
+        <x:v>BANK / TURBO-DIAGNOSIS GATE</x:v>
+      </x:c>
+      <x:c r="H574" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I574" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J574" s="9" t="str">
+        <x:v>2013-2018 S7 4.0T wastegate/boost diagnosis</x:v>
+      </x:c>
+      <x:c r="K574" s="9" t="str">
+        <x:v>specialist turbo service</x:v>
+      </x:c>
+      <x:c r="L574" s="9" t="str"/>
+      <x:c r="M574" s="9" t="str">
+        <x:v>Clip and turbo branches need exact fault; both oil lines not universal from source.</x:v>
+      </x:c>
+      <x:c r="N574" s="41" t="str">
+        <x:v>No clip/turbo link or cool-down/oil schedule claim without exact Audi procedure.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="575" ht="66" hidden="0" customHeight="1">
+      <x:c r="A575" s="40" t="str"/>
+      <x:c r="B575" s="9" t="str"/>
+      <x:c r="C575" s="9" t="str"/>
+      <x:c r="D575" s="9" t="str"/>
+      <x:c r="E575" s="9" t="str"/>
+      <x:c r="F575" s="9" t="str"/>
+      <x:c r="G575" s="9" t="str"/>
+      <x:c r="H575" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I575" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J575" s="9" t="str">
+        <x:v>VIN/bank turbo and required hardware</x:v>
+      </x:c>
+      <x:c r="K575" s="9" t="str">
+        <x:v>manufacturer parts route</x:v>
+      </x:c>
+      <x:c r="L575" s="9" t="str"/>
+      <x:c r="M575" s="9" t="str"/>
+      <x:c r="N575" s="41" t="str"/>
+    </x:row>
+    <x:row r="576" ht="686.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A576" s="40" t="n">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="B576" s="9" t="str">
+        <x:v>audi-s8-5-2-v10-timing-chain-tensioner-guide-wear</x:v>
+      </x:c>
+      <x:c r="C576" s="9" t="str">
+        <x:v>2007-2012 | Audi | S8 | 5.2L FSI V10 (BSM)</x:v>
+      </x:c>
+      <x:c r="D576" s="9" t="str">
+        <x:v>5.2 V10 Timing Chain Tensioner / Guide Wear (D3 Cold-Start Rattle)</x:v>
+      </x:c>
+      <x:c r="E576" s="9" t="str">
+        <x:v>Investigate any cold-start rattle promptly: inspect tensioner travel and guide condition. Replace the timing chains, tensioners, and plastic guides as a set with updated genuine parts; this is a major, labor-intensive repair (often engine-out). Strictly follow short oil-change intervals with the correct grade to maximize tensioner/guide life, and address any low-oil-pressure condition immediately. Do not drive a V10 with a persistent timing rattle.</x:v>
+      </x:c>
+      <x:c r="F576" s="9" t="str">
+        <x:v>Confirm BSM engine and timing-rattle source/oil pressure/adaptation; engine-code chain/tensioner/guide scope; engine-out only if current procedure; damage assessment</x:v>
+      </x:c>
+      <x:c r="G576" s="9" t="str">
+        <x:v>ENGINE / TIMING-DIAGNOSIS GATE</x:v>
+      </x:c>
+      <x:c r="H576" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I576" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J576" s="9" t="str">
+        <x:v>2007-2012 S8 V10 timing/oil-pressure diagnosis</x:v>
+      </x:c>
+      <x:c r="K576" s="9" t="str">
+        <x:v>specialist engine service</x:v>
+      </x:c>
+      <x:c r="L576" s="9" t="str"/>
+      <x:c r="M576" s="9" t="str">
+        <x:v>Rattle/repair scope requires proof and exact procedure.</x:v>
+      </x:c>
+      <x:c r="N576" s="41" t="str">
+        <x:v>No universal short oil interval or full kit before inspection.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="577" ht="66" hidden="0" customHeight="1">
+      <x:c r="A577" s="40" t="str"/>
+      <x:c r="B577" s="9" t="str"/>
+      <x:c r="C577" s="9" t="str"/>
+      <x:c r="D577" s="9" t="str"/>
+      <x:c r="E577" s="9" t="str"/>
+      <x:c r="F577" s="9" t="str"/>
+      <x:c r="G577" s="9" t="str"/>
+      <x:c r="H577" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I577" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J577" s="9" t="str">
+        <x:v>VIN timing parts/procedure</x:v>
+      </x:c>
+      <x:c r="K577" s="9" t="str">
+        <x:v>manufacturer parts route</x:v>
+      </x:c>
+      <x:c r="L577" s="9" t="str"/>
+      <x:c r="M577" s="9" t="str"/>
+      <x:c r="N577" s="41" t="str"/>
+    </x:row>
+    <x:row r="578" ht="198" hidden="0" customHeight="1">
+      <x:c r="A578" s="40" t="n">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="B578" s="9" t="str">
+        <x:v>audi-s8-air-suspension-2013</x:v>
+      </x:c>
+      <x:c r="C578" s="9" t="str">
+        <x:v>2013-2024 | Audi | S8</x:v>
+      </x:c>
+      <x:c r="D578" s="9" t="str">
+        <x:v>Adaptive Air Suspension Multi-Point Failure</x:v>
+      </x:c>
+      <x:c r="E578" s="9" t="str">
+        <x:v>Replace air struts as they fail. Budget for full system refresh at 80,000 miles. Arnott aftermarket struts offer cost savings.</x:v>
+      </x:c>
+      <x:c r="F578" s="9" t="str">
+        <x:v>Split generations; sag/leak/compressor/valve/J1135/wiring/height-sensor diagnosis; exact component and calibration</x:v>
+      </x:c>
+      <x:c r="G578" s="9" t="str">
+        <x:v>MULTI-GENERATION SYSTEM DIAGNOSIS</x:v>
+      </x:c>
+      <x:c r="H578" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I578" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J578" s="9" t="str">
+        <x:v>2013-2024 S8 air-suspension diagnosis</x:v>
+      </x:c>
+      <x:c r="K578" s="9" t="str">
+        <x:v>specialist suspension service</x:v>
+      </x:c>
+      <x:c r="L578" s="9" t="str"/>
+      <x:c r="M578" s="9" t="str">
+        <x:v>No 80k whole-system rule.</x:v>
+      </x:c>
+      <x:c r="N578" s="41" t="str">
+        <x:v>No Arnott link without exact generation/fitment and failure.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="579" ht="66" hidden="0" customHeight="1">
+      <x:c r="A579" s="40" t="str"/>
+      <x:c r="B579" s="9" t="str"/>
+      <x:c r="C579" s="9" t="str"/>
+      <x:c r="D579" s="9" t="str"/>
+      <x:c r="E579" s="9" t="str"/>
+      <x:c r="F579" s="9" t="str"/>
+      <x:c r="G579" s="9" t="str"/>
+      <x:c r="H579" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I579" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J579" s="9" t="str">
+        <x:v>VIN/PR-code parts/calibration</x:v>
+      </x:c>
+      <x:c r="K579" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L579" s="9" t="str"/>
+      <x:c r="M579" s="9" t="str"/>
+      <x:c r="N579" s="41" t="str"/>
+    </x:row>
+    <x:row r="580" ht="726" hidden="0" customHeight="1">
+      <x:c r="A580" s="40" t="n">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="B580" s="9" t="str">
+        <x:v>audi-s8-air-suspension-failure-2013</x:v>
+      </x:c>
+      <x:c r="C580" s="9" t="str">
+        <x:v>2020-2024 | Audi | S8</x:v>
+      </x:c>
+      <x:c r="D580" s="9" t="str">
+        <x:v>2020-2024 S8 Air-Suspension Malfunction with J1135 Communication Fault - Diagnosis Required</x:v>
+      </x:c>
+      <x:c r="E580" s="9" t="str">
+        <x:v>Read the suspension-controller DTC and symptom code, then inspect wiring, terminals and connectors between J775 and J1135 exactly as Audi specifies. If the fault is passive/sporadic, clear it and verify operation. If it remains active/static after the electrical inspection and key cycle, follow Audi testing for J1135 replacement. Diagnose vehicle sag or leak-down separately; do not order air struts, a compressor or a coil-conversion kit from the former card.</x:v>
+      </x:c>
+      <x:c r="F580" s="9" t="str">
+        <x:v>Read DTC/symptom; J775-J1135 wiring/terminals; passive clear/verify; active/static conditional J1135; separate sag/leak</x:v>
+      </x:c>
+      <x:c r="G580" s="9" t="str">
+        <x:v>SOURCE-YEAR MISMATCH / WIRING-FIRST TSB</x:v>
+      </x:c>
+      <x:c r="H580" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I580" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J580" s="9" t="str">
+        <x:v>2020-2024 S8 J1135 diagnosis</x:v>
+      </x:c>
+      <x:c r="K580" s="9" t="str">
+        <x:v>manufacturer suspension service</x:v>
+      </x:c>
+      <x:c r="L580" s="9" t="str"/>
+      <x:c r="M580" s="9" t="str">
+        <x:v>No air hardware is established.</x:v>
+      </x:c>
+      <x:c r="N580" s="41" t="str">
+        <x:v>Identifier says 2013; no strut/compressor/conversion link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="581" ht="699.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A581" s="40" t="n">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="B581" s="9" t="str">
+        <x:v>audi-s8-battery-management-energy-control-module-faults-parasitic-dr</x:v>
+      </x:c>
+      <x:c r="C581" s="9" t="str">
+        <x:v>2020-2020 | Audi | S8 | VIN-specific Emissions Service Action 27BQ; verify open action in Audi campaign lookup | 4.0T TFSI V8 mild-hybrid</x:v>
+      </x:c>
+      <x:c r="D581" s="9" t="str">
+        <x:v>2020 S8 Starter-Alternator Emissions Service Action 27BQ - VIN Check Required</x:v>
+      </x:c>
+      <x:c r="E581" s="9" t="str">
+        <x:v>Check the VIN in Audi’s recall/service-campaign lookup or ask an Audi dealer to verify 27BQ in Elsa. If open, the dealer replaces the starter-alternator under the action. Electrical-system warnings, a discharged battery, abnormal charging or overnight draw outside this exact action require battery/charging tests and a measured sleep-current diagnosis; do not replace a battery monitor, gateway or MMI module from the former card.</x:v>
+      </x:c>
+      <x:c r="F581" s="9" t="str">
+        <x:v>VIN/open 27BQ check; starter-alternator action; separate battery/charging/sleep-current diagnosis outside action</x:v>
+      </x:c>
+      <x:c r="G581" s="9" t="str">
+        <x:v>SOURCE-ID MISMATCH / 48V ACTION ROUTE</x:v>
+      </x:c>
+      <x:c r="H581" s="9" t="str">
+        <x:v>Audi recall and campaign lookup</x:v>
+      </x:c>
+      <x:c r="I581" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J581" s="9" t="str">
+        <x:v>2020 S8 27BQ</x:v>
+      </x:c>
+      <x:c r="K581" s="9" t="str">
+        <x:v>manufacturer campaign lookup</x:v>
+      </x:c>
+      <x:c r="L581" s="9" t="str"/>
+      <x:c r="M581" s="9" t="str">
+        <x:v>Action is starter-alternator, not generic parasitic drain.</x:v>
+      </x:c>
+      <x:c r="N581" s="41" t="str">
+        <x:v>No battery monitor/gateway/MMI module link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="582" ht="66" hidden="0" customHeight="1">
+      <x:c r="A582" s="40" t="str"/>
+      <x:c r="B582" s="9" t="str"/>
+      <x:c r="C582" s="9" t="str"/>
+      <x:c r="D582" s="9" t="str"/>
+      <x:c r="E582" s="9" t="str"/>
+      <x:c r="F582" s="9" t="str"/>
+      <x:c r="G582" s="9" t="str"/>
+      <x:c r="H582" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I582" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J582" s="9" t="str">
+        <x:v>action/48V diagnosis</x:v>
+      </x:c>
+      <x:c r="K582" s="9" t="str">
+        <x:v>authorized high-voltage service</x:v>
+      </x:c>
+      <x:c r="L582" s="9" t="str"/>
+      <x:c r="M582" s="9" t="str"/>
+      <x:c r="N582" s="41" t="str"/>
+    </x:row>
+    <x:row r="583" ht="211.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A583" s="40" t="n">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="B583" s="9" t="str">
+        <x:v>audi-s8-biturbo-coolant-2013</x:v>
+      </x:c>
+      <x:c r="C583" s="9" t="str">
+        <x:v>2013-2024 | Audi | S8 | 4.0T</x:v>
+      </x:c>
+      <x:c r="D583" s="9" t="str">
+        <x:v>4.0T Turbo Coolant System Degradation</x:v>
+      </x:c>
+      <x:c r="E583" s="9" t="str">
+        <x:v>Replace all turbo coolant and oil feed lines preventatively at 60,000 miles. Monitor coolant levels closely.</x:v>
+      </x:c>
+      <x:c r="F583" s="9" t="str">
+        <x:v>Split generations; pressure-test exact turbo coolant/oil line leak; VIN/bank/position component only if failed; correct fluid/bleed</x:v>
+      </x:c>
+      <x:c r="G583" s="9" t="str">
+        <x:v>MULTI-GENERATION / LEAK-SOURCE GATE</x:v>
+      </x:c>
+      <x:c r="H583" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I583" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J583" s="9" t="str">
+        <x:v>2013-2024 S8 turbo line leak diagnosis</x:v>
+      </x:c>
+      <x:c r="K583" s="9" t="str">
+        <x:v>specialist turbo/cooling service</x:v>
+      </x:c>
+      <x:c r="L583" s="9" t="str"/>
+      <x:c r="M583" s="9" t="str">
+        <x:v>No evidence supports all lines at 60k.</x:v>
+      </x:c>
+      <x:c r="N583" s="41" t="str">
+        <x:v>Remove preventive replacement/monitoring-only repair.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="584" ht="66" hidden="0" customHeight="1">
+      <x:c r="A584" s="40" t="str"/>
+      <x:c r="B584" s="9" t="str"/>
+      <x:c r="C584" s="9" t="str"/>
+      <x:c r="D584" s="9" t="str"/>
+      <x:c r="E584" s="9" t="str"/>
+      <x:c r="F584" s="9" t="str"/>
+      <x:c r="G584" s="9" t="str"/>
+      <x:c r="H584" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I584" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J584" s="9" t="str">
+        <x:v>VIN/bank/position parts</x:v>
+      </x:c>
+      <x:c r="K584" s="9" t="str">
+        <x:v>manufacturer parts route</x:v>
+      </x:c>
+      <x:c r="L584" s="9" t="str"/>
+      <x:c r="M584" s="9" t="str"/>
+      <x:c r="N584" s="41" t="str"/>
+    </x:row>
+    <x:row r="585" ht="567.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A585" s="40" t="n">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B585" s="9" t="str">
+        <x:v>audi-s8-clogged-sunroof-plenum-drains-causing-water-intrusion-electr</x:v>
+      </x:c>
+      <x:c r="C585" s="9" t="str">
+        <x:v>2007-2018 | Audi | S8 | S8, S8 Plus | 5.2 FSI V10, 4.0 TFSI twin-turbo V8 (4.0T)</x:v>
+      </x:c>
+      <x:c r="D585" s="9" t="str">
+        <x:v>Clogged Sunroof / Plenum Drains Causing Water Intrusion and Electronics Damage</x:v>
+      </x:c>
+      <x:c r="E585" s="9" t="str">
+        <x:v>Clear and flush all sunroof and plenum/cowl drains; replace cracked drain hoses, grommets, or channel connectors. Dry out saturated carpet/insulation and inspect plenum-area modules for corrosion, replacing any water-damaged control units. Preventively clean the drains at least annually and keep the cowl area free of leaves/debris.</x:v>
+      </x:c>
+      <x:c r="F585" s="9" t="str">
+        <x:v>Split D3/D4; trace sunroof/plenum/filter housing; approved drain clearing or exact hose/grommet/connector repair; dry/inspect modules</x:v>
+      </x:c>
+      <x:c r="G585" s="9" t="str">
+        <x:v>PLATFORM / LEAK-SOURCE SERVICE</x:v>
+      </x:c>
+      <x:c r="H585" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I585" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J585" s="9" t="str">
+        <x:v>2007-2009/2013-2018 S8 platform-specific water diagnosis</x:v>
+      </x:c>
+      <x:c r="K585" s="9" t="str">
+        <x:v>specialist water-leak service</x:v>
+      </x:c>
+      <x:c r="L585" s="9" t="str"/>
+      <x:c r="M585" s="9" t="str">
+        <x:v>Two platforms/paths differ.</x:v>
+      </x:c>
+      <x:c r="N585" s="41" t="str">
+        <x:v>No annual interval or module replacement until damage confirmed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="586" ht="699.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A586" s="40" t="n">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="B586" s="9" t="str">
+        <x:v>audi-s8-coolant-thermostat-leak-2013</x:v>
+      </x:c>
+      <x:c r="C586" s="9" t="str">
+        <x:v>2020-2021 | Audi | S8 | 2021 applicability ends at VIN 012194; confirm VIN and coolant-pump leak before repair | 4.0T TFSI V8</x:v>
+      </x:c>
+      <x:c r="D586" s="9" t="str">
+        <x:v>2020-Early 2021 S8 Coolant-Pump Leak - Diagnosis Required</x:v>
+      </x:c>
+      <x:c r="E586" s="9" t="str">
+        <x:v>Do not drive an overheating vehicle. Record coolant warning and temperature behavior, pressure-test the cooling system when safe, and locate the leak. Confirm the 2021 VIN boundary and apply TSB 2065040/4 only when the coolant pump is the identified source. Other thermostat, hose, turbo-line, heat-exchanger or internal-loss causes require separate diagnosis; do not order the former thermostat/water-pump bundle from this card.</x:v>
+      </x:c>
+      <x:c r="F586" s="9" t="str">
+        <x:v>Stop for overheat; pressure-test; 2021 VIN boundary; pump only if TSB-confirmed; other thermostat/hose/turbo/heat-exchanger/internal branches</x:v>
+      </x:c>
+      <x:c r="G586" s="9" t="str">
+        <x:v>SOURCE-ID/YEAR MISMATCH / VIN LEAK-SOURCE GATE</x:v>
+      </x:c>
+      <x:c r="H586" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I586" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J586" s="9" t="str">
+        <x:v>2020-early 2021 S8 TSB 2065040/4</x:v>
+      </x:c>
+      <x:c r="K586" s="9" t="str">
+        <x:v>manufacturer cooling service</x:v>
+      </x:c>
+      <x:c r="L586" s="9" t="str"/>
+      <x:c r="M586" s="9" t="str">
+        <x:v>Card concerns pump leak, not thermostat bundle.</x:v>
+      </x:c>
+      <x:c r="N586" s="41" t="str">
+        <x:v>Rename/re-key; no pump/thermostat bundle.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="587" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A587" s="40" t="str"/>
+      <x:c r="B587" s="9" t="str"/>
+      <x:c r="C587" s="9" t="str"/>
+      <x:c r="D587" s="9" t="str"/>
+      <x:c r="E587" s="9" t="str"/>
+      <x:c r="F587" s="9" t="str"/>
+      <x:c r="G587" s="9" t="str"/>
+      <x:c r="H587" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I587" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J587" s="9" t="str">
+        <x:v>pressure-test/source diagnosis</x:v>
+      </x:c>
+      <x:c r="K587" s="9" t="str">
+        <x:v>specialist cooling service</x:v>
+      </x:c>
+      <x:c r="L587" s="9" t="str"/>
+      <x:c r="M587" s="9" t="str"/>
+      <x:c r="N587" s="41" t="str"/>
+    </x:row>
+    <x:row r="588" ht="765.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A588" s="40" t="n">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="B588" s="9" t="str">
+        <x:v>audi-s8-cylinder-demand-active-engine-mount-failure-4-cylinder-mode</x:v>
+      </x:c>
+      <x:c r="C588" s="9" t="str">
+        <x:v>2013-2015 | Audi | S8 | 4.0 TFSI vehicles with reproducible 1000-3000 rpm vibration; diagnose J931 before mount replacement | 4.0T TFSI V8</x:v>
+      </x:c>
+      <x:c r="D588" s="9" t="str">
+        <x:v>2013-2015 S8 COD Vibration with J931 Basic-Setting Fault - Diagnosis Required</x:v>
+      </x:c>
+      <x:c r="E588" s="9" t="str">
+        <x:v>Reproduce the vibration under Audi’s specified driving conditions and scan J931. If the bulletin applies, verify J931 software, perform the required SVM update and basic settings, align the exhaust without tension, repeat basic settings and follow the referenced diagnosis if vibration remains. Inspect mount hardware only after the software, calibration and exhaust path. Do not disable cylinder-on-demand or replace both mounts from the former card.</x:v>
+      </x:c>
+      <x:c r="F588" s="9" t="str">
+        <x:v>Reproduce 1000-3000 rpm condition; J931 scan/software/SVM/basic settings; exhaust alignment; mount hardware only after software/calibration/exhaust</x:v>
+      </x:c>
+      <x:c r="G588" s="9" t="str">
+        <x:v>SOFTWARE/CALIBRATION-FIRST / MOUNT HOLD</x:v>
+      </x:c>
+      <x:c r="H588" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I588" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J588" s="9" t="str">
+        <x:v>2013-2015 S8 COD/J931 bulletin</x:v>
+      </x:c>
+      <x:c r="K588" s="9" t="str">
+        <x:v>manufacturer driveline service</x:v>
+      </x:c>
+      <x:c r="L588" s="9" t="str"/>
+      <x:c r="M588" s="9" t="str">
+        <x:v>Vibration does not establish failed mounts.</x:v>
+      </x:c>
+      <x:c r="N588" s="41" t="str">
+        <x:v>Do not disable COD or replace both mounts.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="589" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A589" s="40" t="str"/>
+      <x:c r="B589" s="9" t="str"/>
+      <x:c r="C589" s="9" t="str"/>
+      <x:c r="D589" s="9" t="str"/>
+      <x:c r="E589" s="9" t="str"/>
+      <x:c r="F589" s="9" t="str"/>
+      <x:c r="G589" s="9" t="str"/>
+      <x:c r="H589" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I589" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J589" s="9" t="str">
+        <x:v>J931/exhaust/mount diagnosis</x:v>
+      </x:c>
+      <x:c r="K589" s="9" t="str">
+        <x:v>specialist service</x:v>
+      </x:c>
+      <x:c r="L589" s="9" t="str"/>
+      <x:c r="M589" s="9" t="str"/>
+      <x:c r="N589" s="41" t="str"/>
+    </x:row>
+    <x:row r="590" ht="765.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A590" s="40" t="n">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="B590" s="9" t="str">
+        <x:v>audi-s8-d2-4-2-v8-timing-belt-tensioner-service</x:v>
+      </x:c>
+      <x:c r="C590" s="9" t="str">
+        <x:v>2001-2003 | Audi | S8 | 4.2L 40V V8 (AYS)</x:v>
+      </x:c>
+      <x:c r="D590" s="9" t="str">
+        <x:v>D2 4.2 V8 Timing Belt and Tensioner Service (Interference Engine)</x:v>
+      </x:c>
+      <x:c r="E590" s="9" t="str">
+        <x:v>Replace the timing belt as a complete kit — belt, tensioner, idler/guide rollers, and water pump — at or before Audi's interval (and by age regardless of mileage). Use genuine/OE-quality components and set cam/crank timing precisely with the correct locking tools; this is a front-of-engine ('service position') job. Inspect the exhaust-side chain tensioners while in there. Always confirm timing-belt history (with receipts) before buying a D2 S8; if unknown, do it immediately.</x:v>
+      </x:c>
+      <x:c r="F590" s="9" t="str">
+        <x:v>Confirm AYS and documented interval/history; complete belt/tensioner/idlers/water-pump kit; locking tools; chain tensioners inspected only by condition</x:v>
+      </x:c>
+      <x:c r="G590" s="9" t="str">
+        <x:v>ENGINE-CODE / TIMING-KIT GATE</x:v>
+      </x:c>
+      <x:c r="H590" s="9" t="str">
+        <x:v>Audi S8 timing-belt catalog</x:v>
+      </x:c>
+      <x:c r="I590" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/S8/Timing-Belt-Kit/</x:v>
+      </x:c>
+      <x:c r="J590" s="9" t="str">
+        <x:v>2001-2003 D2 S8 AYS; verify engine/VIN and kit contents</x:v>
+      </x:c>
+      <x:c r="K590" s="9" t="str">
+        <x:v>engine-specific timing catalog</x:v>
+      </x:c>
+      <x:c r="L590" s="9" t="str"/>
+      <x:c r="M590" s="9" t="str">
+        <x:v>Complete kit is named, but interval/parts require exact engine proof.</x:v>
+      </x:c>
+      <x:c r="N590" s="41" t="str">
+        <x:v>Do not automatically replace exhaust-side chain tensioners.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="591" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A591" s="40" t="str"/>
+      <x:c r="B591" s="9" t="str"/>
+      <x:c r="C591" s="9" t="str"/>
+      <x:c r="D591" s="9" t="str"/>
+      <x:c r="E591" s="9" t="str"/>
+      <x:c r="F591" s="9" t="str"/>
+      <x:c r="G591" s="9" t="str"/>
+      <x:c r="H591" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I591" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J591" s="9" t="str">
+        <x:v>service-position/locking/history</x:v>
+      </x:c>
+      <x:c r="K591" s="9" t="str">
+        <x:v>specialist timing service</x:v>
+      </x:c>
+      <x:c r="L591" s="9" t="str"/>
+      <x:c r="M591" s="9" t="str"/>
+      <x:c r="N591" s="41" t="str"/>
+    </x:row>
+    <x:row r="592" ht="844.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A592" s="40" t="n">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="B592" s="9" t="str">
+        <x:v>audi-s8-direct-injection-carbon-buildup-intake-valves</x:v>
+      </x:c>
+      <x:c r="C592" s="9" t="str">
+        <x:v>2013-2018 | Audi | S8 | 4.0T TFSI V8 (CTFA/CGTA/CWUC)</x:v>
+      </x:c>
+      <x:c r="D592" s="9" t="str">
+        <x:v>Direct-Injection Carbon Buildup on Intake Valves (Misfires / Rough Idle)</x:v>
+      </x:c>
+      <x:c r="E592" s="9" t="str">
+        <x:v>Confirm via borescope of the intake valves (and rule out coils/plugs/PCV first). The accepted repair is walnut-shell blasting: remove the intake manifold and media-blast the carbon off the valves and ports with crushed walnut shells, then reinstall with new intake gaskets. Replace spark plugs and inspect coils while the manifold is off. Preventively, keep up with oil changes, fix any PCV/oil-burning source, and consider periodic cleaning every ~40,000-60,000 miles. Catch-can solutions reduce future accumulation.</x:v>
+      </x:c>
+      <x:c r="F592" s="9" t="str">
+        <x:v>Borescope confirmation after ignition/PCV checks; engine-code intake cleaning; manifold gaskets; plugs/coils only by condition</x:v>
+      </x:c>
+      <x:c r="G592" s="9" t="str">
+        <x:v>ENGINE-CODE / CONFIRMED-DEPOSIT SERVICE</x:v>
+      </x:c>
+      <x:c r="H592" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I592" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J592" s="9" t="str">
+        <x:v>2013-2018 S8 4.0T intake diagnosis/cleaning</x:v>
+      </x:c>
+      <x:c r="K592" s="9" t="str">
+        <x:v>specialist intake service</x:v>
+      </x:c>
+      <x:c r="L592" s="9" t="str"/>
+      <x:c r="M592" s="9" t="str">
+        <x:v>Cleaning valid after proof; plugs/coils/catch can conditional.</x:v>
+      </x:c>
+      <x:c r="N592" s="41" t="str">
+        <x:v>Remove fixed interval and catch-can prevention claim.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="593" ht="686.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A593" s="40" t="n">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="B593" s="9" t="str">
+        <x:v>audi-s8-front-suspension-control-arm-bushing-sway-bar-link-wear</x:v>
+      </x:c>
+      <x:c r="C593" s="9" t="str">
+        <x:v>2020-2021 | Audi | S8 | 2021 applicability through VIN 028090; localize noise acoustically before parts | 4.0T TFSI V8 mild-hybrid</x:v>
+      </x:c>
+      <x:c r="D593" s="9" t="str">
+        <x:v>2020-Early 2021 S8 Front Lower Guide-Link Hydro-Bushing Noise - Diagnosis Required</x:v>
+      </x:c>
+      <x:c r="E593" s="9" t="str">
+        <x:v>Confirm the VIN boundary, reproduce the noise and localize it with acoustic diagnostic equipment. Inspect the lower guide-link hydro-bushings and surrounding joints. If the hydro-bushing is confirmed, follow Audi’s paired replacement procedure; complete guide links may be required when prior pressing or rework prevents the specified repair. Align the vehicle as required. Do not order a ten-arm kit or sway-bar links from the former card.</x:v>
+      </x:c>
+      <x:c r="F593" s="9" t="str">
+        <x:v>VIN boundary; reproduce/acoustically localize; inspect lower guide-link hydro-bushings/joints; paired bushing/guide-link branch; alignment</x:v>
+      </x:c>
+      <x:c r="G593" s="9" t="str">
+        <x:v>SOURCE-ID MISMATCH / VIN TSB SUSPENSION SERVICE</x:v>
+      </x:c>
+      <x:c r="H593" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I593" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J593" s="9" t="str">
+        <x:v>2020-early 2021 S8 guide-link TSB/VIN</x:v>
+      </x:c>
+      <x:c r="K593" s="9" t="str">
+        <x:v>manufacturer suspension service</x:v>
+      </x:c>
+      <x:c r="L593" s="9" t="str"/>
+      <x:c r="M593" s="9" t="str">
+        <x:v>No ten-arm/sway-link repair.</x:v>
+      </x:c>
+      <x:c r="N593" s="41" t="str">
+        <x:v>Rename/re-key to lower guide-link hydro-bushing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="594" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A594" s="40" t="str"/>
+      <x:c r="B594" s="9" t="str"/>
+      <x:c r="C594" s="9" t="str"/>
+      <x:c r="D594" s="9" t="str"/>
+      <x:c r="E594" s="9" t="str"/>
+      <x:c r="F594" s="9" t="str"/>
+      <x:c r="G594" s="9" t="str"/>
+      <x:c r="H594" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I594" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J594" s="9" t="str">
+        <x:v>acoustic localization/alignment</x:v>
+      </x:c>
+      <x:c r="K594" s="9" t="str">
+        <x:v>specialist suspension service</x:v>
+      </x:c>
+      <x:c r="L594" s="9" t="str"/>
+      <x:c r="M594" s="9" t="str"/>
+      <x:c r="N594" s="41" t="str"/>
+    </x:row>
+    <x:row r="595" ht="778.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A595" s="40" t="n">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="B595" s="9" t="str">
+        <x:v>audi-s8-high-pressure-fuel-pump-injector-internal-leak-causing-hard</x:v>
+      </x:c>
+      <x:c r="C595" s="9" t="str">
+        <x:v>2013-2018 | Audi | S8 | 4.0 TFSI; diagnosis requires ODIS values, software check and pressure-hold testing | 4.0T TFSI V8</x:v>
+      </x:c>
+      <x:c r="D595" s="9" t="str">
+        <x:v>2013-2018 S8 Warm-Soak Long-Crank or No-Start - Fuel Diagnosis Required</x:v>
+      </x:c>
+      <x:c r="E595" s="9" t="str">
+        <x:v>Have the dealer read DTCs and ODIS fuel-in-oil value, verify ECM software and perform Audi’s high- and low-pressure holding tests. If high-pressure behavior is abnormal, borescope the combustion chamber to identify a leaking injector. If low-side pressure builds correctly but drops more than 1.5 bar in the first 15 minutes, Audi says at least one HPFP may be leaking and directs replacement of both pumps plus an oil change. Select no pump or injector until the test identifies the path.</x:v>
+      </x:c>
+      <x:c r="F595" s="9" t="str">
+        <x:v>ODIS fuel-in-oil/software and high/low pressure hold tests; borescope injector path; both HPFPs+oil only for defined low-side drop path</x:v>
+      </x:c>
+      <x:c r="G595" s="9" t="str">
+        <x:v>TEST-BRANCH / PUMP-INJECTOR HOLD</x:v>
+      </x:c>
+      <x:c r="H595" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I595" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J595" s="9" t="str">
+        <x:v>2013-2018 S8 4.0T warm-soak fuel diagnosis</x:v>
+      </x:c>
+      <x:c r="K595" s="9" t="str">
+        <x:v>manufacturer fuel service</x:v>
+      </x:c>
+      <x:c r="L595" s="9" t="str"/>
+      <x:c r="M595" s="9" t="str">
+        <x:v>Injector and HPFP are mutually diagnostic branches.</x:v>
+      </x:c>
+      <x:c r="N595" s="41" t="str">
+        <x:v>No pump/injector until test path identifies it.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="596" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A596" s="40" t="str"/>
+      <x:c r="B596" s="9" t="str"/>
+      <x:c r="C596" s="9" t="str"/>
+      <x:c r="D596" s="9" t="str"/>
+      <x:c r="E596" s="9" t="str"/>
+      <x:c r="F596" s="9" t="str"/>
+      <x:c r="G596" s="9" t="str"/>
+      <x:c r="H596" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I596" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J596" s="9" t="str">
+        <x:v>pressure-hold/borescope diagnosis</x:v>
+      </x:c>
+      <x:c r="K596" s="9" t="str">
+        <x:v>specialist fuel service</x:v>
+      </x:c>
+      <x:c r="L596" s="9" t="str"/>
+      <x:c r="M596" s="9" t="str"/>
+      <x:c r="N596" s="41" t="str"/>
+    </x:row>
+    <x:row r="597" ht="673.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A597" s="40" t="n">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B597" s="9" t="str">
+        <x:v>audi-s8-mmi-upper-display-backup-camera-black-screen</x:v>
+      </x:c>
+      <x:c r="C597" s="9" t="str">
+        <x:v>2020-2026 | Audi | S8 | VIN-specific NHTSA 25V900 / Audi 90TV; verify open recall | 4.0T TFSI V8 mild-hybrid</x:v>
+      </x:c>
+      <x:c r="D597" s="9" t="str">
+        <x:v>2020-2026 S8 Rearview/Top-View Camera Image May Not Display - Recall 25V900</x:v>
+      </x:c>
+      <x:c r="E597" s="9" t="str">
+        <x:v>Check the VIN in Audi’s recall/service-campaign lookup and schedule the free 90TV software remedy if open. Use extra care when reversing until repaired and visually check the area around the vehicle. A completely dead or rebooting MMI display, missing instrument-cluster data, wiring fault or hardware failure requires separate diagnosis and must not be attributed to this recall without VIN and symptom confirmation.</x:v>
+      </x:c>
+      <x:c r="F597" s="9" t="str">
+        <x:v>VIN/90TV/25V900 check; software remedy; direct observation; separate dead/rebooting display/wiring/hardware diagnosis</x:v>
+      </x:c>
+      <x:c r="G597" s="9" t="str">
+        <x:v>RECALL ROUTES / SYMPTOM SPLIT</x:v>
+      </x:c>
+      <x:c r="H597" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I597" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J597" s="9" t="str">
+        <x:v>2020-2026 S8 90TV</x:v>
+      </x:c>
+      <x:c r="K597" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L597" s="9" t="str"/>
+      <x:c r="M597" s="9" t="str">
+        <x:v>Recall only covers camera image software.</x:v>
+      </x:c>
+      <x:c r="N597" s="41" t="str">
+        <x:v>No MMI display/hardware link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="598" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A598" s="40" t="str"/>
+      <x:c r="B598" s="9" t="str"/>
+      <x:c r="C598" s="9" t="str"/>
+      <x:c r="D598" s="9" t="str"/>
+      <x:c r="E598" s="9" t="str"/>
+      <x:c r="F598" s="9" t="str"/>
+      <x:c r="G598" s="9" t="str"/>
+      <x:c r="H598" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I598" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J598" s="9" t="str">
+        <x:v>25V900 VIN history</x:v>
+      </x:c>
+      <x:c r="K598" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L598" s="9" t="str"/>
+      <x:c r="M598" s="9" t="str"/>
+      <x:c r="N598" s="41" t="str"/>
+    </x:row>
+    <x:row r="599" ht="792" hidden="0" customHeight="1">
+      <x:c r="A599" s="40" t="n">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="B599" s="9" t="str">
+        <x:v>audi-s8-oil-consumption-2013</x:v>
+      </x:c>
+      <x:c r="C599" s="9" t="str">
+        <x:v>2020-2023 | Audi | S8 | EA825 4.0L; confirm VIN, engine and measured consumption under Audi procedure | 4.0T TFSI V8 mild-hybrid (EA825)</x:v>
+      </x:c>
+      <x:c r="D599" s="9" t="str">
+        <x:v>2020-2023 S8 High Oil Consumption and Updated Piston Rings - Diagnosis Required</x:v>
+      </x:c>
+      <x:c r="E599" s="9" t="str">
+        <x:v>Document oil-level warnings, mileage, top-up quantity, leaks and oil specification, then have an Audi dealer perform the authorized oil-consumption measurement. Repair is justified only when the measured result exceeds the applicable owner-manual limit and other leakage or operating causes are excluded. If TSB 2071114 applies, follow its VIN/engine-specific piston, ring and connecting-rod procedure. Do not change oil viscosity or authorize internal-engine work solely from the former card.</x:v>
+      </x:c>
+      <x:c r="F599" s="9" t="str">
+        <x:v>2020-2023 EA825 VIN and documented measured consumption; exclude leaks/spec/operation; conditional TSB piston/ring/rod procedure</x:v>
+      </x:c>
+      <x:c r="G599" s="9" t="str">
+        <x:v>SOURCE-YEAR MISMATCH / MEASURED-CONSUMPTION GATE</x:v>
+      </x:c>
+      <x:c r="H599" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I599" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J599" s="9" t="str">
+        <x:v>2020-2023 S8 TSB 2071114 and oil test</x:v>
+      </x:c>
+      <x:c r="K599" s="9" t="str">
+        <x:v>manufacturer engine service</x:v>
+      </x:c>
+      <x:c r="L599" s="9" t="str"/>
+      <x:c r="M599" s="9" t="str">
+        <x:v>Internal work requires measured excess and TSB applicability.</x:v>
+      </x:c>
+      <x:c r="N599" s="41" t="str">
+        <x:v>Identifier says 2013; no viscosity/internal-part link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="600" ht="646.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A600" s="40" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="B600" s="9" t="str">
+        <x:v>audi-s8-pcv-oil-separator-failure-excessive-crankcase-vacuum</x:v>
+      </x:c>
+      <x:c r="C600" s="9" t="str">
+        <x:v>2013-2016 | Audi | S8 | 4.0 TFSI; confirm warm-idle sound and filler-cap response before oil-separator replacement | 4.0T TFSI V8</x:v>
+      </x:c>
+      <x:c r="D600" s="9" t="str">
+        <x:v>2013-2016 S8 Warm-Idle Whistle from Crankcase Breather Leak - Diagnosis Required</x:v>
+      </x:c>
+      <x:c r="E600" s="9" t="str">
+        <x:v>Compare the sound with Audi’s reference condition and check whether opening the oil filler cap changes it. Read P2279/P0507 and rule out other intake leaks. When the sound matches and is affected by the filler-cap check, follow Audi’s oil-separator breather replacement procedure and renew required seals/consumables by VIN. Do not diagnose by oil-cap feel alone or order the former five-item parts list.</x:v>
+      </x:c>
+      <x:c r="F600" s="9" t="str">
+        <x:v>Warm-idle reference/filler-cap response; P2279/P0507 and other leak diagnosis; VIN oil-separator breather/seals only when matched</x:v>
+      </x:c>
+      <x:c r="G600" s="9" t="str">
+        <x:v>DIAGNOSIS / VIN PCV GATE</x:v>
+      </x:c>
+      <x:c r="H600" s="9" t="str">
+        <x:v>Audi S8 PCV catalog</x:v>
+      </x:c>
+      <x:c r="I600" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/S8/PCV/</x:v>
+      </x:c>
+      <x:c r="J600" s="9" t="str">
+        <x:v>2013-2016 S8 4.0T exact VIN after matching diagnosis</x:v>
+      </x:c>
+      <x:c r="K600" s="9" t="str">
+        <x:v>conditional PCV catalog</x:v>
+      </x:c>
+      <x:c r="L600" s="9" t="str"/>
+      <x:c r="M600" s="9" t="str">
+        <x:v>Oil-cap feel alone insufficient.</x:v>
+      </x:c>
+      <x:c r="N600" s="41" t="str">
+        <x:v>No five-item bundle.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="601" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A601" s="40" t="str"/>
+      <x:c r="B601" s="9" t="str"/>
+      <x:c r="C601" s="9" t="str"/>
+      <x:c r="D601" s="9" t="str"/>
+      <x:c r="E601" s="9" t="str"/>
+      <x:c r="F601" s="9" t="str"/>
+      <x:c r="G601" s="9" t="str"/>
+      <x:c r="H601" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I601" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J601" s="9" t="str">
+        <x:v>intake/crankcase leak diagnosis</x:v>
+      </x:c>
+      <x:c r="K601" s="9" t="str">
+        <x:v>specialist engine service</x:v>
+      </x:c>
+      <x:c r="L601" s="9" t="str"/>
+      <x:c r="M601" s="9" t="str"/>
+      <x:c r="N601" s="41" t="str"/>
+    </x:row>
+    <x:row r="602" ht="594" hidden="0" customHeight="1">
+      <x:c r="A602" s="40" t="n">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="B602" s="9" t="str">
+        <x:v>audi-s8-porous-high-pressure-fuel-supply-line-recall-nhtsa-19v057000</x:v>
+      </x:c>
+      <x:c r="C602" s="9" t="str">
+        <x:v>2013-2016 | Audi | S8 | VIN-specific NHTSA 19V057 / Audi 20BM; verify open recall | 4.0T TFSI V8</x:v>
+      </x:c>
+      <x:c r="D602" s="9" t="str">
+        <x:v>2013-2016 S8 Porous Fuel-Pump Supply Line / Fire Risk - Recall 19V057</x:v>
+      </x:c>
+      <x:c r="E602" s="9" t="str">
+        <x:v>Check the VIN for open recall 20BM and contact an Audi dealer without delay. The free remedy installs a fuel-pressure damper in the low-pressure fuel supply inside the tank. If fuel odor or visible leakage is present, avoid ignition sources, do not continue driving, and arrange dealer inspection/towing as appropriate. Do not buy a retail line or damper from the former card.</x:v>
+      </x:c>
+      <x:c r="F602" s="9" t="str">
+        <x:v>VIN/20BM/19V057 check; in-tank low-pressure damper; stop/tow for fuel odor/leak</x:v>
+      </x:c>
+      <x:c r="G602" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H602" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I602" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J602" s="9" t="str">
+        <x:v>2013-2016 S8 20BM</x:v>
+      </x:c>
+      <x:c r="K602" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L602" s="9" t="str"/>
+      <x:c r="M602" s="9" t="str">
+        <x:v>Remedy is damper, not retail line.</x:v>
+      </x:c>
+      <x:c r="N602" s="41" t="str">
+        <x:v>No line/damper product.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="603" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A603" s="40" t="str"/>
+      <x:c r="B603" s="9" t="str"/>
+      <x:c r="C603" s="9" t="str"/>
+      <x:c r="D603" s="9" t="str"/>
+      <x:c r="E603" s="9" t="str"/>
+      <x:c r="F603" s="9" t="str"/>
+      <x:c r="G603" s="9" t="str"/>
+      <x:c r="H603" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I603" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J603" s="9" t="str">
+        <x:v>19V057 VIN history</x:v>
+      </x:c>
+      <x:c r="K603" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L603" s="9" t="str"/>
+      <x:c r="M603" s="9" t="str"/>
+      <x:c r="N603" s="41" t="str"/>
+    </x:row>
+    <x:row r="604" ht="211.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A604" s="40" t="n">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="B604" s="9" t="str">
+        <x:v>audi-s8-torque-converter-2013</x:v>
+      </x:c>
+      <x:c r="C604" s="9" t="str">
+        <x:v>2013-2024 | Audi | S8</x:v>
+      </x:c>
+      <x:c r="D604" s="9" t="str">
+        <x:v>ZF 8-Speed Torque Converter and Valve Body Issues</x:v>
+      </x:c>
+      <x:c r="E604" s="9" t="str">
+        <x:v>Replace torque converter and service valve body. Full ZF fluid and filter change every 50,000 miles extends transmission life.</x:v>
+      </x:c>
+      <x:c r="F604" s="9" t="str">
+        <x:v>Split generations/ZF code; TCM faults, fluid/debris and converter-slip testing; exact service/valve-body/converter/rebuild branch</x:v>
+      </x:c>
+      <x:c r="G604" s="9" t="str">
+        <x:v>TRANSMISSION-CODE / COMPONENT GATE</x:v>
+      </x:c>
+      <x:c r="H604" s="9" t="str">
+        <x:v>Audi S8 transmission-service catalog</x:v>
+      </x:c>
+      <x:c r="I604" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/S8/Automatic-Transmission-Service/</x:v>
+      </x:c>
+      <x:c r="J604" s="9" t="str">
+        <x:v>2013-2024 exact transmission/VIN/fluid/filter</x:v>
+      </x:c>
+      <x:c r="K604" s="9" t="str">
+        <x:v>vehicle-specific transmission catalog</x:v>
+      </x:c>
+      <x:c r="L604" s="9" t="str"/>
+      <x:c r="M604" s="9" t="str">
+        <x:v>Twelve years span units and component branches.</x:v>
+      </x:c>
+      <x:c r="N604" s="41" t="str">
+        <x:v>No automatic converter+valve-body repair or universal 50k interval.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="605" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A605" s="40" t="str"/>
+      <x:c r="B605" s="9" t="str"/>
+      <x:c r="C605" s="9" t="str"/>
+      <x:c r="D605" s="9" t="str"/>
+      <x:c r="E605" s="9" t="str"/>
+      <x:c r="F605" s="9" t="str"/>
+      <x:c r="G605" s="9" t="str"/>
+      <x:c r="H605" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I605" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J605" s="9" t="str">
+        <x:v>converter/valve-body diagnosis</x:v>
+      </x:c>
+      <x:c r="K605" s="9" t="str">
+        <x:v>specialist transmission service</x:v>
+      </x:c>
+      <x:c r="L605" s="9" t="str"/>
+      <x:c r="M605" s="9" t="str"/>
+      <x:c r="N605" s="41" t="str"/>
+    </x:row>
+    <x:row r="606" ht="712.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A606" s="40" t="n">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="B606" s="9" t="str">
+        <x:v>audi-s8-turbo-oil-strainer-2013</x:v>
+      </x:c>
+      <x:c r="C606" s="9" t="str">
+        <x:v>2013-2017 | Audi | S8 | VIN-specific NHTSA 22V178 / Audi 21H7; verify open recall | 4.0T TFSI V8</x:v>
+      </x:c>
+      <x:c r="D606" s="9" t="str">
+        <x:v>2013-2017 S8 Blocked Turbocharger Oil Strainer / Stall Risk - Recall 22V178</x:v>
+      </x:c>
+      <x:c r="E606" s="9" t="str">
+        <x:v>Check the VIN for open recall 21H7 and schedule the free Audi dealer remedy, which replaces the oil strainer and performs an oil change. If EPC, MIL or oil warning lights appear with unusual turbo noise, extended cranking, rough idle, loss of power or stalling, stop safely and arrange diagnosis. Turbo damage, warranty eligibility and any additional repair must be assessed by VIN and inspection; do not buy the former retail strainer.</x:v>
+      </x:c>
+      <x:c r="F606" s="9" t="str">
+        <x:v>VIN/21H7/22V178 check; strainer/oil service; damage/coverage by inspection</x:v>
+      </x:c>
+      <x:c r="G606" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H606" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I606" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J606" s="9" t="str">
+        <x:v>2013-2017 S8 21H7</x:v>
+      </x:c>
+      <x:c r="K606" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L606" s="9" t="str"/>
+      <x:c r="M606" s="9" t="str">
+        <x:v>Free safety remedy.</x:v>
+      </x:c>
+      <x:c r="N606" s="41" t="str">
+        <x:v>No retail strainer/turbo link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="607" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A607" s="40" t="str"/>
+      <x:c r="B607" s="9" t="str"/>
+      <x:c r="C607" s="9" t="str"/>
+      <x:c r="D607" s="9" t="str"/>
+      <x:c r="E607" s="9" t="str"/>
+      <x:c r="F607" s="9" t="str"/>
+      <x:c r="G607" s="9" t="str"/>
+      <x:c r="H607" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I607" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J607" s="9" t="str">
+        <x:v>22V178 VIN history</x:v>
+      </x:c>
+      <x:c r="K607" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L607" s="9" t="str"/>
+      <x:c r="M607" s="9" t="str"/>
+      <x:c r="N607" s="41" t="str"/>
+    </x:row>
+    <x:row r="608" ht="950.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A608" s="40" t="n">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="B608" s="9" t="str">
+        <x:v>audi-s8-water-to-air-intercooler-internal-coolant-leak</x:v>
+      </x:c>
+      <x:c r="C608" s="9" t="str">
+        <x:v>2013-2018 | Audi | S8 | 4.0T TFSI V8 (CTFA/CGTA/CWUC)</x:v>
+      </x:c>
+      <x:c r="D608" s="9" t="str">
+        <x:v>Water-to-Air Intercooler Internal Coolant Leak (Coolant into Intake)</x:v>
+      </x:c>
+      <x:c r="E608" s="9" t="str">
+        <x:v>Confirm the source: pressure-test the cooling system and inspect the charge piping/intercooler outlet for coolant residue; scope for white smoke and coolant on the intake side rather than an external leak. Replace the water-to-air intercooler/charge-air cooler unit (genuine OEM core). Because access requires removing intake components in the valley, it is standard practice to also replace the turbo oil strainer, coolant valves, and PCV/oil separator while in there. Refill and bleed the cooling system per procedure. This is a high-difficulty job typically done by a specialist or dealer.</x:v>
+      </x:c>
+      <x:c r="F608" s="9" t="str">
+        <x:v>Pressure-test and confirm intake-side coolant versus external leak; exact engine/VIN charge-air cooler; other valley parts only if failed/required by procedure; bleed</x:v>
+      </x:c>
+      <x:c r="G608" s="9" t="str">
+        <x:v>LEAK-SOURCE / ENGINE-VIN INTERCOOLER GATE</x:v>
+      </x:c>
+      <x:c r="H608" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I608" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J608" s="9" t="str">
+        <x:v>2013-2018 S8 VIN charge-air cooler/valley parts</x:v>
+      </x:c>
+      <x:c r="K608" s="9" t="str">
+        <x:v>manufacturer parts route</x:v>
+      </x:c>
+      <x:c r="L608" s="9" t="str"/>
+      <x:c r="M608" s="9" t="str">
+        <x:v>Internal cooler leak must be distinguished and overlapping parts are not mandatory.</x:v>
+      </x:c>
+      <x:c r="N608" s="41" t="str">
+        <x:v>Do not bundle turbo strainer, valves and PCV unless separately due/failed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="609" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A609" s="40" t="str"/>
+      <x:c r="B609" s="9" t="str"/>
+      <x:c r="C609" s="9" t="str"/>
+      <x:c r="D609" s="9" t="str"/>
+      <x:c r="E609" s="9" t="str"/>
+      <x:c r="F609" s="9" t="str"/>
+      <x:c r="G609" s="9" t="str"/>
+      <x:c r="H609" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I609" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J609" s="9" t="str">
+        <x:v>intake-side coolant diagnosis/service</x:v>
+      </x:c>
+      <x:c r="K609" s="9" t="str">
+        <x:v>specialist engine service</x:v>
+      </x:c>
+      <x:c r="L609" s="9" t="str"/>
+      <x:c r="M609" s="9" t="str"/>
+      <x:c r="N609" s="41" t="str"/>
+    </x:row>
+    <x:row r="610" ht="475.20001220703125" hidden="0" customHeight="1">
+      <x:c r="A610" s="42" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="B610" s="43" t="str">
+        <x:v>audi-sq2-ea888-2-0-tfsi-coolant-leak-from-water-pump-thermostat-housi</x:v>
+      </x:c>
+      <x:c r="C610" s="43" t="str">
+        <x:v>2019-2024 | Audi | SQ2 | 2.0 TFSI quattro | EA888 2.0 TFSI Gen3</x:v>
+      </x:c>
+      <x:c r="D610" s="43" t="str">
+        <x:v>EA888 2.0 TFSI coolant leak from water pump / thermostat housing</x:v>
+      </x:c>
+      <x:c r="E610" s="43" t="str">
+        <x:v>Replace the failed water pump / thermostat housing assembly, ideally with the latest revised, more heat-resistant unit; many shops fit an upgraded repair kit and a new gasket. Catch it early by watching for slowly dropping coolant level and a faint sweet smell. Combine with a coolant flush and refill.</x:v>
+      </x:c>
+      <x:c r="F610" s="43" t="str">
+        <x:v>Non-US-market engine/VIN pressure test; exact pump/thermostat/housing leak source and revision; gasket/coolant/bleed</x:v>
+      </x:c>
+      <x:c r="G610" s="43" t="str">
+        <x:v>NON-US-MARKET / LEAK-SOURCE GATE</x:v>
+      </x:c>
+      <x:c r="H610" s="43" t="str">
+        <x:v>Audi UK service and maintenance</x:v>
+      </x:c>
+      <x:c r="I610" s="43" t="str">
+        <x:v>https://www.audi.co.uk/en/owners/service-and-maintenance/</x:v>
+      </x:c>
+      <x:c r="J610" s="43" t="str">
+        <x:v>2019-2024 SQ2 local-market EA888 coolant diagnosis</x:v>
+      </x:c>
+      <x:c r="K610" s="43" t="str">
+        <x:v>manufacturer-market service</x:v>
+      </x:c>
+      <x:c r="L610" s="43" t="str"/>
+      <x:c r="M610" s="43" t="str">
+        <x:v>SQ2 is non-US and exact assembly/revision requires market VIN.</x:v>
+      </x:c>
+      <x:c r="N610" s="44" t="str">
+        <x:v>No US affiliate or generic upgraded kit; do not bundle flush automatically.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18573,21 +21645,21 @@
         <x:v>Queue status</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="2" ht="396" hidden="0" customHeight="1">
       <x:c r="A2" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="9" t="str">
-        <x:v>audi-s5-thermostat-2008</x:v>
+        <x:v>audi-sq2-electro-mechanical-parking-brake-brake-pedal-weld-recalls</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
-        <x:v>2008-2025 | Audi | S5 | 3.0T</x:v>
+        <x:v>2019-2020 | Audi | SQ2</x:v>
       </x:c>
       <x:c r="D2" s="9" t="str">
-        <x:v>Thermostat and Water Pump Assembly Failure</x:v>
+        <x:v>Electro-mechanical parking brake and brake-pedal weld recalls (early build)</x:v>
       </x:c>
       <x:c r="E2" s="9" t="str">
-        <x:v>Replace thermostat/water pump assembly. Upgrade to revised housing if available.</x:v>
+        <x:v>These are recall items — have the VIN checked against the Audi/DVSA recall database and any open campaign rectified free of charge at a dealer. Report any abnormal parking-brake behaviour or a soft/abnormal brake pedal immediately.</x:v>
       </x:c>
       <x:c r="F2" s="9" t="n">
         <x:v>0</x:v>
@@ -18596,21 +21668,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="3" ht="475.20001220703125" hidden="0" customHeight="1">
       <x:c r="A3" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
-        <x:v>audi-s6-air-suspension-2013</x:v>
+        <x:v>audi-sq2-internal-fuse-box-wiring-harness-can-work-loose-causing-sudd</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
-        <x:v>2013-2013 | Audi | S6 | 4.0T</x:v>
+        <x:v>2022-2023 | Audi | SQ2 | 2.0 TFSI</x:v>
       </x:c>
       <x:c r="D3" s="9" t="str">
-        <x:v>2013 Audi S6 Air-Suspension Compressor or Relay Fault - Diagnosis Required</x:v>
+        <x:v>2022-2023 Audi SQ2 Interior Fuse-Carrier Recall GAI-3692</x:v>
       </x:c>
       <x:c r="E3" s="9" t="str">
-        <x:v>Have an Audi-qualified technician test the air-suspension compressor and inspect relay J403. Audi directs replacement of both the compressor and relay when the relay has severe contact erosion or an overheated strand; when the compressor sounds normal and the relay has only minor contact marks, replace the relay only. A sagging corner or leak-down condition requires separate leak localization before any strut is replaced. Do not order the former strut or compressor recommendations from this card.</x:v>
+        <x:v>Check the VIN and open-campaign status with an authorised Audi dealer in the vehicle’s market. The campaign remedy is dealer inspection and correction of the fuse-carrier power connection. Do not replace a fuse box or wiring harness solely from a warning lamp or this model-year summary.</x:v>
       </x:c>
       <x:c r="F3" s="9" t="n">
         <x:v>0</x:v>
@@ -18619,21 +21691,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="1359.5999755859375" hidden="0" customHeight="1">
+    <x:row r="4" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A4" s="40" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>audi-s6-c7-carbon-buildup-2013</x:v>
+        <x:v>audi-sq2-mmi-infotainment-freezing-rebooting-lost-settings</x:v>
       </x:c>
       <x:c r="C4" s="9" t="str">
-        <x:v>2013-2018 | Audi | S6 | 4.0T</x:v>
+        <x:v>2019-2024 | Audi | SQ2</x:v>
       </x:c>
       <x:c r="D4" s="9" t="str">
-        <x:v>4.0T Carbon Buildup on Intake Valves</x:v>
+        <x:v>MMI infotainment freezing, rebooting and lost settings</x:v>
       </x:c>
       <x:c r="E4" s="9" t="str">
-        <x:v>Confirm carbon buildup by scanning for misfire faults (commonly random/multiple or cylinder-specific misfires), reviewing fuel trims, and inspecting the intake valves with a borescope after removing the intake manifold or accessing the ports. The proper repair is an intake valve carbon cleaning, typically walnut shell blasting each intake port with the valves closed, then replacing intake manifold gaskets, injector seals/O-rings or any disturbed PCV-related seals as needed and clearing/adapting the ECU afterward. If buildup is severe or returns quickly, inspect the PCV/oil separator system and crankcase ventilation hoses for excessive oil carryover. Independent shops typically charge about $800-$1,500 for a full walnut blast service on the 4.0T, while dealer pricing can run roughly $1,500-$2,500 depending on labor and gasket/seal replacement.</x:v>
+        <x:v>A forced MMI restart (press and hold the on/off or volume control ~10 seconds until it reboots) clears many transient faults. Persistent issues are usually resolved by a dealer software/firmware update; check for any applicable MMI update campaigns. Only in rare cases is the MMI head unit itself replaced.</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
         <x:v>0</x:v>
@@ -18642,21 +21714,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="5" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A5" s="40" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>audi-s6-carbon-buildup-2013</x:v>
+        <x:v>audi-sq2-pcv-crankcase-ventilation-valve-diaphragm-failure-causing-ro</x:v>
       </x:c>
       <x:c r="C5" s="9" t="str">
-        <x:v>2013-2024 | Audi | S6 | 4.0T</x:v>
+        <x:v>2019-2024 | Audi | SQ2 | EA888 2.0 TFSI Gen3</x:v>
       </x:c>
       <x:c r="D5" s="9" t="str">
-        <x:v>4.0T Direct Injection Carbon Buildup</x:v>
+        <x:v>PCV / crankcase ventilation valve diaphragm failure causing rough idle and lean-running codes</x:v>
       </x:c>
       <x:c r="E5" s="9" t="str">
-        <x:v>Walnut blast all eight intake runners. Dual-injection models (2019+) are less affected.</x:v>
+        <x:v>Replace the PCV valve (or the valve-cover assembly that integrates it) with the latest revised part; some owners fit a catch-can to reduce recurrence. A quick field test — briefly covering the bleeder hole on the cap to see if idle stabilises or whistling stops — helps confirm before replacement.</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
         <x:v>0</x:v>
@@ -18665,21 +21737,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="462" hidden="0" customHeight="1">
+    <x:row r="6" ht="752.4000244140625" hidden="0" customHeight="1">
       <x:c r="A6" s="40" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>audi-s6-rearview-camera-image-failure-from-software-error</x:v>
+        <x:v>audi-sq2-s-tronic-7-speed-wet-clutch-transmission-jerky-low-speed-shi</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
-        <x:v>2020-2025 | Audi | S6</x:v>
+        <x:v>2019-2024 | Audi | SQ2 | 7-speed S tronic | DQ381 / 0GC 7-speed wet-clutch S tronic</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
-        <x:v>2020-2025 Audi S6 Rearview Camera Software Recall 25V900 / 90TV</x:v>
+        <x:v>S tronic (DQ381) 7-speed wet-clutch transmission: jerky low-speed shifts, hesitation and limp mode</x:v>
       </x:c>
       <x:c r="E6" s="9" t="str">
-        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install the more robust driver-assistance software update free of charge. Until repaired, use extra caution when reversing and do not treat a restart or temporary image recovery as completion of the recall.</x:v>
+        <x:v>First step is a proper DSG fluid-and-filter service (the wet-clutch unit needs periodic transmission oil changes — many owners do it around 40k miles even though intervals can be longer). Have the TCU scanned for stored codes; sensor or mechatronic valve replacement and re-coding/adaptation resolves many cases, while severe cases need a full mechatronic unit or clutch-pack replacement. Insist on a software/adaptation update at the dealer for driveability complaints.</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
         <x:v>0</x:v>
@@ -18688,21 +21760,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="7" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A7" s="40" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>audi-s6-takata-passenger-airbag-inflator-recall</x:v>
+        <x:v>audi-sq5-air-suspension-2018</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
-        <x:v>2007-2011 | Audi | S6</x:v>
+        <x:v>2018-2025 | Audi | SQ5</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
-        <x:v>2007-2011 Audi S6 Takata Passenger-Airbag Recall 18V427 / 69R7</x:v>
+        <x:v>Air-Suspension Warning with C1260F0 or U112100 Communication Fault</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
-        <x:v>Check the VIN for recall 18V427/69R7 and arrange the free final passenger-frontal-airbag replacement with an Audi dealer. Do not use an airbag warning light to determine recall eligibility; Audi states that the warning light is unrelated to this inflator defect.</x:v>
+        <x:v>Inspect the wiring and connector contacts between J775 and J1135 first. If no wiring fault is found, clear a first passive or sporadic fault and release the vehicle. Replace J1135 for an active or static fault, or when the same passive or sporadic fault returns a second time, following Audi workshop information and VIN-specific ETKA data.</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
         <x:v>0</x:v>
@@ -18711,20 +21783,22 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="8" ht="924" hidden="0" customHeight="1">
       <x:c r="A8" s="40" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>audi-s6-transmission-valve-body-2002</x:v>
+        <x:v>audi-sq5-carbon-buildup-2014</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
-        <x:v>2002-2004 | Audi | S6</x:v>
+        <x:v>2014-2025 | Audi | SQ5 | 3.0T Supercharged, 3.0T</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>ZF 5HP24 Tiptronic Transmission Valve Body Failure</x:v>
-      </x:c>
-      <x:c r="E8" s="9" t="str"/>
+        <x:v>Fuel-Quality or Deposit-Related Rough Running and Misfire Diagnosis</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="str">
+        <x:v>Confirm fuel quality, symptoms and stored DTCs before replacing or cleaning components. If contaminated gasoline is suspected, advise changing the fuel source; if low detergent quality is suspected, Audi recommends Top Tier detergent gasoline. Continue workshop diagnosis if symptoms persist. On 2018-2025 EA839 SQ5 models, do not recommend unapproved cleaners or additives; follow the owner manual and use only Audi-approved petrol additives. Do not prescribe routine walnut blasting, a catch can or chemical cleaning from this record.</x:v>
+      </x:c>
       <x:c r="F8" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -18732,21 +21806,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="9" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A9" s="40" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>audi-s6-turbo-coolant-2013</x:v>
+        <x:v>audi-sq5-pcv-valve-2014</x:v>
       </x:c>
       <x:c r="C9" s="9" t="str">
-        <x:v>2013-2013 | Audi | S6 | 4.0T</x:v>
+        <x:v>2014-2017 | Audi | SQ5 | 3.0T Supercharged</x:v>
       </x:c>
       <x:c r="D9" s="9" t="str">
-        <x:v>2013 Audi S6 Turbocharger Coolant-Pipe Seepage - Diagnosis Required</x:v>
+        <x:v>P052E00 Crankcase-Breather Membrane or Elbow Fault</x:v>
       </x:c>
       <x:c r="E9" s="9" t="str">
-        <x:v>Confirm the leak source and VIN applicability before ordering parts. For the TSB condition, Audi specifies replacing the coolant feed and return pipes on both cylinder banks, replacing the disturbed oil-feed-pipe O-rings, then refilling and bleeding the cooling system. Service Action 21F7 was VIN-specific and expired in 2019, so current coverage must not be assumed. Do not order the former single pipe or alleged silicone-line kit from this card.</x:v>
+        <x:v>Use Audi hand-vacuum test to distinguish a membrane leak from an elbow fault. If indicated, remove the compressor or intake manifold and inspect the membrane and the breather two metal plates. Use repair kit 06E103772H only for a confirmed membrane or plate fault. For a confirmed elbow fault, replace elbow 06E103402 and spring clip N10769401 rather than automatically replacing the complete breather. Verify current part data in ETKA before ordering.</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
         <x:v>0</x:v>
@@ -18755,21 +21829,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="290.3999938964844" hidden="0" customHeight="1">
+    <x:row r="10" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A10" s="40" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>audi-s7-air-suspension-2012</x:v>
+        <x:v>audi-sq5-supercharger-2014</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
-        <x:v>2020-2021 | Audi | S7</x:v>
+        <x:v>2014-2018 | Audi | SQ5 | 3.0T</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>Rear-Axle Lock Nut and Alignment Recall Follow-Up (21V295 / 22V034)</x:v>
+        <x:v>3.0T Supercharger Bearing and Intercooler Pump Failure</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
-        <x:v>Check the VIN for both campaigns 42L1 and 42L5. Audi dealers replace affected nuts and bolts, inspect and adjust rear alignment, and replace qualifying unevenly worn tires free of charge.</x:v>
+        <x:v>Replace supercharger nose bearing kit. Replace intercooler pump if failing. Service supercharger belt tension.</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
         <x:v>0</x:v>
@@ -18778,21 +21852,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="237.60000610351562" hidden="0" customHeight="1">
+    <x:row r="11" ht="844.7999877929688" hidden="0" customHeight="1">
       <x:c r="A11" s="40" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>audi-s7-biturbo-coolant-2012</x:v>
+        <x:v>audi-sq5-supercharger-oil-leak-2014</x:v>
       </x:c>
       <x:c r="C11" s="9" t="str">
-        <x:v>2013-2014 | Audi | S7 | 4.0 TFSI</x:v>
+        <x:v>2014-2017 | Audi | SQ5 | Premium Plus, Prestige | 3.0T Supercharged, 3.0T</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>4.0L Fuel Line Can Leak and Create a Fire Risk (Recall 13V450 / 20U6)</x:v>
+        <x:v>Supercharger Seal and Gasket Oil Leaks (3.0T)</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel line free of charge under campaign 20U6/L8. Stop driving if fuel odor or leakage is present.</x:v>
+        <x:v>JHM Motorsports sells a complete supercharger replacement seal and gasket kit for the Eaton unit in the 3.0T. Replacing all seals at once is recommended since the supercharger must be removed for access. Nose cone seal, rotor shaft seals, and manifold gaskets should all be replaced together ($300-$500 in parts, $600-$1,200 labor). While the supercharger is off, also replace the PCV valve and perform carbon cleaning. For valve cover gasket leaks (separate issue), budget $400-$800 parts and labor. Monitor oil level weekly if leaks are present.</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
         <x:v>0</x:v>
@@ -18801,21 +21875,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="264" hidden="0" customHeight="1">
+    <x:row r="12" ht="1122" hidden="0" customHeight="1">
       <x:c r="A12" s="40" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="9" t="str">
-        <x:v>audi-s7-carbon-buildup-4.0t-2012</x:v>
+        <x:v>audi-sq5-water-pump-2018</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
-        <x:v>2021-2021 | Audi | S7</x:v>
+        <x:v>2018-2024 | Audi | SQ5 | 3.0T</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>Rear Seat-Belt Retractor Can Release a Child Restraint Early (Recall 21V606 / 69CS)</x:v>
+        <x:v>Mechanical Coolant-Pump Leak with Possible N649 Vacuum-System Contamination</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers inspect and replace the affected middle-rear seat-belt assembly as necessary free of charge under campaign 69CS.</x:v>
+        <x:v>Confirm the complaint and exact vehicle criteria first. Inspect the vacuum line and N649 for coolant, then clean and dry suspected leakage, fill the cooling system correctly, inspect at idle and around 2,500 rpm, and pressure-test according to Audi workshop information. If no leak is reproduced, observe the vehicle without replacing parts. If the pump leak is confirmed, replace the failed component and document it. If fresh coolant has entered the vacuum system, inspect the remaining Audi checkpoints and replace only contaminated components; if the downstream checkpoints are clean, replace N649 and clean the line between the pump and N649 as directed by TSB 2070349/5.</x:v>
       </x:c>
       <x:c r="F12" s="9" t="n">
         <x:v>0</x:v>
@@ -18824,21 +21898,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="237.60000610351562" hidden="0" customHeight="1">
+    <x:row r="13" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A13" s="40" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="9" t="str">
-        <x:v>audi-s7-cylinder-demand-rough-running-hesitation</x:v>
+        <x:v>audi-sq7-air-susp-strut-2020</x:v>
       </x:c>
       <x:c r="C13" s="9" t="str">
-        <x:v>2021-2021 | Audi | S7</x:v>
+        <x:v>2020-2025 | Audi | SQ7 | 4.0T</x:v>
       </x:c>
       <x:c r="D13" s="9" t="str">
-        <x:v>Instrument Panel May Fail to Display Critical Safety Information (Recall 25V201 / 90VC)</x:v>
+        <x:v>2020-2025 SQ7 Air-Suspension C1260F0/U112100 Communication Fault - Diagnosis Required</x:v>
       </x:c>
       <x:c r="E13" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history. Audi dealers update the instrument-panel module software free of charge under campaign 90VC.</x:v>
+        <x:v>Inspect the wiring and connector contacts between J775 and J1135 first. If no wiring fault is found, clear a first passive or sporadic fault and release the vehicle. Replace J1135 for an active or static fault, or when the same passive or sporadic fault returns a second time, following Audi workshop information and VIN-specific ETKA data. Do not replace an air spring, strut or compressor assembly solely from the warning.</x:v>
       </x:c>
       <x:c r="F13" s="9" t="n">
         <x:v>0</x:v>
@@ -18847,21 +21921,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="316.79998779296875" hidden="0" customHeight="1">
+    <x:row r="14" ht="1122" hidden="0" customHeight="1">
       <x:c r="A14" s="40" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="9" t="str">
-        <x:v>audi-s7-ea839-2-9t-v6-water-pump-internal-leak-overheating</x:v>
+        <x:v>audi-sq7-air-suspension-2020</x:v>
       </x:c>
       <x:c r="C14" s="9" t="str">
-        <x:v>2020-2024 | Audi | S7</x:v>
+        <x:v>2020-2024 | Audi | SQ7 | Premium Plus, Prestige | 4.0T</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
-        <x:v>Rearview Camera Image May Not Display (Recall 25V900 / 90TV)</x:v>
+        <x:v>Adaptive Air Suspension Compressor and Air Spring Failures</x:v>
       </x:c>
       <x:c r="E14" s="9" t="str">
-        <x:v>Check the VIN and campaign-completion history. Audi dealers update the relevant software free of charge under campaign 90TV. Continue direct visual checks when reversing until repaired.</x:v>
+        <x:v>Diagnose specific failed component: air springs leak most commonly, followed by compressor burnout, valve block faults, and height sensor failures. Air spring replacement ($800-$1,500 per corner at independent shop). Compressor replacement ($1,200-$2,500 installed). Valve block: $500-$1,000. Height sensor: $200-$400. Check for air leaks first using soapy water spray before replacing the compressor - a $200 air spring seal may be causing a $2,000 compressor to overwork and fail. Aftermarket solutions from Arnott offer cost savings. Converting to conventional springs ($1,500-$2,500) eliminates future air suspension costs but sacrifices ride height adjustment.</x:v>
       </x:c>
       <x:c r="F14" s="9" t="n">
         <x:v>0</x:v>
@@ -18870,21 +21944,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="343.20001220703125" hidden="0" customHeight="1">
+    <x:row r="15" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A15" s="40" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="9" t="str">
-        <x:v>audi-s7-electromechanical-steering-rack-torque-sensor-failure-causin</x:v>
+        <x:v>audi-sq7-mmi-mib3-freeze-2020</x:v>
       </x:c>
       <x:c r="C15" s="9" t="str">
-        <x:v>2021-2021 | Audi | S7</x:v>
+        <x:v>2020-2026 | Audi | SQ7</x:v>
       </x:c>
       <x:c r="D15" s="9" t="str">
-        <x:v>Incorrect Brake-Fluid Reservoir Cap Label (Recall 23V601 / 47T9)</x:v>
+        <x:v>2020-2026 Audi SQ7 Rearview Camera Software Recall 25V900 / 90TV</x:v>
       </x:c>
       <x:c r="E15" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers inspect the reservoir cap and replace it when necessary free of charge under campaign 47T9. Use only the brake-fluid specification in the owner and service information.</x:v>
+        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install the more robust driver-assistance software update free of charge. Until repaired, use extra caution when reversing and do not treat a restart, bus sleep or temporary image recovery as completion of the recall.</x:v>
       </x:c>
       <x:c r="F15" s="9" t="n">
         <x:v>0</x:v>
@@ -18893,44 +21967,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="16" ht="990" hidden="0" customHeight="1">
       <x:c r="A16" s="40" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="9" t="str">
-        <x:v>audi-s7-front-control-arm-bushing-ball-joint-failure</x:v>
+        <x:v>audi-sq7-valve-cover-oil-leak-2020</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+        <x:v>2020-2024 | Audi | SQ7 | 4.0T</x:v>
       </x:c>
       <x:c r="D16" s="9" t="str">
-        <x:v>Front Control Arm Bushing and Ball Joint Failure (C7 Suspension)</x:v>
+        <x:v>2020-2024 SQ7 4.0L High Oil Consumption and Piston-Ring Diagnosis - TSB 2071114/5</x:v>
       </x:c>
       <x:c r="E16" s="9" t="str">
-        <x:v>Inspect all front control arms for play in the bushings and ball joints. Replace worn arms — many owners do the full front control-arm set (commonly a 16-piece kit covering both sides) to avoid repeat visits since the labor overlaps. Critical install notes: torque the bushing bolts at ride height (not with the suspension hanging) to avoid pre-loading and destroying the new bushings, and perform a four-wheel alignment afterward.</x:v>
+        <x:v>First inspect for visible engine-oil traces or leaks. Have an Audi dealer perform the authorized ODIS oil-consumption measurement, preserve and upload both test logs, and document the requested driving-profile data. Internal-engine repair is justified only when measured consumption exceeds the applicable limit and no other cause is found. If every TSB gate is met, follow Audi's VIN-, engine-code- and power-class-specific procedure for replacement of all eight pistons and piston rings, using current ETKA and ELSA information. Do not diagnose valve-cover gaskets or turbocharger seals from oil consumption alone.</x:v>
       </x:c>
       <x:c r="F16" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G16" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="396" hidden="0" customHeight="1">
+    <x:row r="17" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A17" s="40" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="9" t="str">
-        <x:v>audi-s7-fuel-injector-deposits-failure-causing-misfire-rough-running</x:v>
+        <x:v>audi-sq8-air-susp-compressor-2020</x:v>
       </x:c>
       <x:c r="C17" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
+        <x:v>2020-2025 | Audi | SQ8</x:v>
       </x:c>
       <x:c r="D17" s="9" t="str">
-        <x:v>Fuel Injector Deposits / Failure Causing Misfire and Rough Running (4.0T V8)</x:v>
+        <x:v>2020-2025 SQ8 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
       </x:c>
       <x:c r="E17" s="9" t="str">
-        <x:v>Pull misfire counts per cylinder to localize the fault. Inspect/replace failed or leaking injectors and renew injector seals; replace spark plugs and any weak coils as a set. Confirm fuel trims return to normal and clear codes; address intake carbon if present.</x:v>
+        <x:v>Inspect the wiring and connector contacts between J775 and J1135 before replacing a component. For a first passive or sporadic occurrence, clear the fault and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after wiring inspection, Audi directs replacement of J1135 under current repair and parts information. Do not buy struts, springs or a compressor solely from this warning.</x:v>
       </x:c>
       <x:c r="F17" s="9" t="n">
         <x:v>0</x:v>
@@ -18939,21 +22013,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="396" hidden="0" customHeight="1">
+    <x:row r="18" ht="831.5999755859375" hidden="0" customHeight="1">
       <x:c r="A18" s="40" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="9" t="str">
-        <x:v>audi-s7-gateway-control-module-shutdown-from-rear-seat-liquid-spill</x:v>
+        <x:v>audi-sq8-air-suspension-2020</x:v>
       </x:c>
       <x:c r="C18" s="9" t="str">
-        <x:v>2020-2022 | Audi | S7 | 2.9 TFSI</x:v>
+        <x:v>2020-2024 | Audi | SQ8 | Premium Plus, Prestige | 4.0T</x:v>
       </x:c>
       <x:c r="D18" s="9" t="str">
-        <x:v>Rear-Seat Liquid Spill Can Shut Down Gateway Module (Recall 22V861 / 90V2)</x:v>
+        <x:v>Adaptive Air Suspension Compressor and Air Spring Failures</x:v>
       </x:c>
       <x:c r="E18" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers install a protective gateway-module cover free of charge under campaign 90V2. If multiple warnings or reduced power occur after a spill, move out of traffic safely and arrange dealer inspection.</x:v>
+        <x:v>Same diagnostic and repair approach as SQ7 (shared 4M platform). Isolate the failed component: air springs ($800-$1,500 per corner), compressor ($1,200-$2,500), valve block ($500-$1,000), or height sensor ($200-$400). Always check for air leaks before replacing the compressor. Aftermarket air suspension components from Arnott/Strutmasters offer 40-50% savings over OEM. Annual inspection of air springs for cracking recommended, especially in hot climates where UV and heat accelerate rubber degradation.</x:v>
       </x:c>
       <x:c r="F18" s="9" t="n">
         <x:v>0</x:v>
@@ -18962,21 +22036,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="528" hidden="0" customHeight="1">
+    <x:row r="19" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A19" s="40" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="9" t="str">
-        <x:v>audi-s7-high-pressure-fuel-pump-failure-causing-hard-start-power-los</x:v>
+        <x:v>audi-sq8-airbag-mount-2023</x:v>
       </x:c>
       <x:c r="C19" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
+        <x:v>2023-2024 | Audi | SQ8 | 4.0T V8</x:v>
       </x:c>
       <x:c r="D19" s="9" t="str">
-        <x:v>High-Pressure Fuel Pump (HPFP) Failure Causing Hard Start and Power Loss (4.0T V8)</x:v>
+        <x:v>2023-2024 SQ8 Driver-Seat Side-Airbag Mount Recall 69GA (23V868)</x:v>
       </x:c>
       <x:c r="E19" s="9" t="str">
-        <x:v>Diagnose with live fuel-rail pressure data before condemning the pump, as a faulty low-pressure sensor or in-tank pump can set the same codes. Replace the failed high-pressure pump (the affected bank, or both as a set on high-mileage cars) together with the cam follower and seals. Verify low-pressure (in-tank) supply is within spec.</x:v>
+        <x:v>Check the VIN for open Audi recall 69GA and have an authorized dealer inspect the driver-seat side-airbag installation. If needed, the dealer will reinstall the airbag correctly; the recall filing says no parts are replaced. A clock spring or generic airbag part is not the recall remedy.</x:v>
       </x:c>
       <x:c r="F19" s="9" t="n">
         <x:v>0</x:v>
@@ -18985,44 +22059,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="660" hidden="0" customHeight="1">
+    <x:row r="20" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A20" s="40" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="9" t="str">
-        <x:v>audi-s7-ignition-coil-pack-failure-causing-misfires</x:v>
+        <x:v>audi-sq8-mmi-mib3-freeze-2020</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+        <x:v>2020-2026 | Audi | SQ8 | 4.0T V8</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>Ignition Coil Pack Failure Causing Misfires (4.0T V8)</x:v>
+        <x:v>2020-2026 SQ8 Rearview Camera Software Recall 90TV (25V900)</x:v>
       </x:c>
       <x:c r="E20" s="9" t="str">
-        <x:v>Confirm the failing cylinder, then swap the suspect coil to another cylinder to verify the fault follows the coil. Replace the failed coil; best practice on the 4.0T is to replace all eight coils and the spark plugs as a set since the access labor is shared and mixed-age coils tend to fail in sequence. Use OE or quality OE-equivalent coils (the 4.0T uses the 079905110-series coil). Inspect spark plugs for fouling/oil that could indicate a secondary issue.</x:v>
+        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install more robust driver-assistance software free of charge. Until repaired, use extra caution when reversing and do not treat a restart, bus sleep or temporary image recovery as completion of the recall. A generic scan tool or head-unit replacement is not the recall remedy.</x:v>
       </x:c>
       <x:c r="F20" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G20" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="237.60000610351562" hidden="0" customHeight="1">
+    <x:row r="21" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A21" s="40" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="9" t="str">
-        <x:v>audi-s7-motor-mount-failure-2012</x:v>
+        <x:v>audi-sq8-turbo-coolant-2020</x:v>
       </x:c>
       <x:c r="C21" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7</x:v>
+        <x:v>2020-2021 | Audi | SQ8 | 4.0T V8</x:v>
       </x:c>
       <x:c r="D21" s="9" t="str">
-        <x:v>Passenger Occupant Detection Mat Can Disable the Airbag (Recall 18V370 / 74D5)</x:v>
+        <x:v>2020-Early 2021 SQ8 Red Coolant Warning - Check G407 per TSB 2062951/4</x:v>
       </x:c>
       <x:c r="E21" s="9" t="str">
-        <x:v>Check VIN eligibility because seat equipment affects scope. Audi dealers install the occupant-detection repair kit free of charge under campaign 74D5.</x:v>
+        <x:v>Have the vehicle checked with Audi Guided Fault Finding and inspect G407 and its O-ring. Replace G407 only if the O-ring is damaged or pinched and the diagnosis matches the bulletin; follow the related Audi diagnostic path if additional listed faults are stored. Do not replace turbo coolant hoses, pumps or other cooling parts from this card alone.</x:v>
       </x:c>
       <x:c r="F21" s="9" t="n">
         <x:v>0</x:v>
@@ -19031,21 +22105,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="22" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A22" s="40" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="9" t="str">
-        <x:v>audi-s7-pcv-oil-separator-failure-causing-oil-consumption-whistling</x:v>
+        <x:v>audi-tt-absesp-control-module-failure-2000</x:v>
       </x:c>
       <x:c r="C22" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T | 4.0 TFSI V8 (EA824)</x:v>
+        <x:v>2000-2001 | Audi | TT</x:v>
       </x:c>
       <x:c r="D22" s="9" t="str">
-        <x:v>PCV / Oil Separator (Ölabscheider) Failure Causing Oil Consumption and Whistling (4.0T V8)</x:v>
+        <x:v>Driver Airbag Inflator May Deploy Improperly (Recall 21V470 / 69CJ)</x:v>
       </x:c>
       <x:c r="E22" s="9" t="str">
-        <x:v>Replace the failed oil separator / PCV assembly and the associated breather hose with the latest revised part. An ECM update may accompany the new part on some VINs. Confirm with a smoke test for intake-side vacuum leaks; inspect the rear main seal if oil consumption is severe, as a failed PCV is a common cause of rear main seal damage on these engines.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the driver frontal-airbag inflator with an alternative inflator free of charge under campaign 69CJ.</x:v>
       </x:c>
       <x:c r="F22" s="9" t="n">
         <x:v>0</x:v>
@@ -19054,21 +22128,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="23" ht="277.20001220703125" hidden="0" customHeight="1">
       <x:c r="A23" s="40" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="9" t="str">
-        <x:v>audi-s7-power-liftgate-motor-gas-strut-failure</x:v>
+        <x:v>audi-tt-cam-follower-2008</x:v>
       </x:c>
       <x:c r="C23" s="9" t="str">
-        <x:v>2013-2022 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824), 2.9T TFSI Biturbo V6 (EA839)</x:v>
+        <x:v>2000-2000 | Audi | TT</x:v>
       </x:c>
       <x:c r="D23" s="9" t="str">
-        <x:v>Power Liftgate Motor and Gas Strut Failure (Sportback Tailgate)</x:v>
+        <x:v>Fuel-Line Assembly Can Leak (Recall 99V222)</x:v>
       </x:c>
       <x:c r="E23" s="9" t="str">
-        <x:v>Diagnose whether the fault is the gas struts (won't stay up / weak lift), the spindle lift motors (slow or struggling travel), or the latch/cinching motor (won't release or won't pull closed — see TSB 2072431/1). Replace worn gas struts in pairs; replace failed lift or cinching motors as needed. After repair, perform the power-liftgate relearn/reset procedure so travel limits recalibrate.</x:v>
+        <x:v>Check VIN eligibility and campaign completion. Audi dealers replace the fuel-line assembly free of charge under recall 99V222. Stop driving if fuel odor or leakage is present.</x:v>
       </x:c>
       <x:c r="F23" s="9" t="n">
         <x:v>0</x:v>
@@ -19077,21 +22151,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="24" ht="198" hidden="0" customHeight="1">
       <x:c r="A24" s="40" t="n">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="9" t="str">
-        <x:v>audi-s7-premature-front-brake-rotor-warping-pad-wear</x:v>
+        <x:v>audi-tt-coil-pack-failure-and-2000</x:v>
       </x:c>
       <x:c r="C24" s="9" t="str">
-        <x:v>2013-2022 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824), 2.9T TFSI Biturbo V6 (EA839)</x:v>
+        <x:v>2000-2001 | Audi | TT</x:v>
       </x:c>
       <x:c r="D24" s="9" t="str">
-        <x:v>Premature Front Brake Rotor Warping and Pad Wear</x:v>
+        <x:v>Rear Track-Control Arm Corrosion Can Restrict Movement (Recall 01V325)</x:v>
       </x:c>
       <x:c r="E24" s="9" t="str">
-        <x:v>Replace warped/below-spec rotors and pads together; consider higher-quality coated or upgraded rotors that resist warping better than the soft OEM units. Bed in new pads/rotors properly and avoid riding the brakes to prevent uneven deposits. Ensure caliper guide pins/slides move freely so pads engage evenly. For repeat warping, an upgraded rotor-and-pad package is the durable fix; address any pulsation early before it damages new components.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the rear track-control arms free of charge under recall 01V325.</x:v>
       </x:c>
       <x:c r="F24" s="9" t="n">
         <x:v>0</x:v>
@@ -19100,21 +22174,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="25" ht="264" hidden="0" customHeight="1">
       <x:c r="A25" s="40" t="n">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="9" t="str">
-        <x:v>audi-s7-rear-differential-mount-driveshaft-center-bearing-wear-causi</x:v>
+        <x:v>audi-tt-dsg-mechatronic-2008</x:v>
       </x:c>
       <x:c r="C25" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+        <x:v>2004-2004 | Audi | TT</x:v>
       </x:c>
       <x:c r="D25" s="9" t="str">
-        <x:v>Rear Differential Mount and Driveshaft Center Bearing Wear Causing Drivetrain Clunk (C7)</x:v>
+        <x:v>Direct-Shift Gearbox Clutch Weld Can Lose Drive Torque (Recall 04V007)</x:v>
       </x:c>
       <x:c r="E25" s="9" t="str">
-        <x:v>Inspect the rear differential mount and driveshaft center support bearing for play and torn rubber. Replace worn components with OE parts, or fit billet aluminum diff/transmission mount inserts that fill the factory voids to remove the slop without adding harshness. On 4.0T cars, also check for the separate active-engine-mount software TSB before condemning a mount for a 1,000-3,000 RPM cruise vibration. Reassess the clunk after each fix since multiple sources can contribute.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers replace the affected clutch free of charge under recall 04V007. If drive torque is lost, move out of traffic safely and arrange recovery.</x:v>
       </x:c>
       <x:c r="F25" s="9" t="n">
         <x:v>0</x:v>
@@ -19123,21 +22197,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="462" hidden="0" customHeight="1">
+    <x:row r="26" ht="356.3999938964844" hidden="0" customHeight="1">
       <x:c r="A26" s="40" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="9" t="str">
-        <x:v>audi-s7-rear-view-camera-mmi-flex-harness-black-screen</x:v>
+        <x:v>audi-tt-dsg-transmission-2008</x:v>
       </x:c>
       <x:c r="C26" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7 (C7), A7 (C7) | 4.0 TFSI V8 (EA824)</x:v>
+        <x:v>2009-2009 | Audi | TT</x:v>
       </x:c>
       <x:c r="D26" s="9" t="str">
-        <x:v>Rear-View Camera / MMI Flex Harness Black Screen</x:v>
+        <x:v>DSG Temperature-Sensor Wiring Can Trigger an Abrupt Shift to Neutral (Recall 09V333)</x:v>
       </x:c>
       <x:c r="E26" s="9" t="str">
-        <x:v>Diagnose with a scan and continuity check of the tailgate-to-body flex harness before replacing the camera. Repair or replace the broken hinge-side loom conductors; if confirmed faulty, replace the camera module. For MMI freezes, apply the latest software update or reset the unit.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers reprogram the transmission control module with updated software free of charge under recall 09V333. If the gear indicator flashes or neutral engages unexpectedly, stop safely.</x:v>
       </x:c>
       <x:c r="F26" s="9" t="n">
         <x:v>0</x:v>
@@ -19146,21 +22220,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="27" ht="303.6000061035156" hidden="0" customHeight="1">
       <x:c r="A27" s="40" t="n">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="9" t="str">
-        <x:v>audi-s7-s-tronic-7-speed-dual-clutch-mechatronic-clutch-wear</x:v>
+        <x:v>audi-tt-front-control-arm-bushings-2000</x:v>
       </x:c>
       <x:c r="C27" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7 Quattro 4.0T (S-tronic / 0B5 DL501) | 4.0 TFSI V8 (EA824)</x:v>
+        <x:v>2000-2000 | Audi | TT</x:v>
       </x:c>
       <x:c r="D27" s="9" t="str">
-        <x:v>S-tronic 7-Speed Dual-Clutch (DL501/0B5) Mechatronic and Clutch Wear</x:v>
+        <x:v>High-Speed Directional-Stability Remedy (Recall 99V300)</x:v>
       </x:c>
       <x:c r="E27" s="9" t="str">
-        <x:v>Perform the S-tronic gearbox oil and filter service on schedule (roughly every 40,000-60,000 km). For judder/jerking, have the mechatronic unit tested; recondition or replace the valve body with the superseded design and adapt/replace the clutch packs as needed. Software adaptation resets can temporarily improve drivability but do not fix worn hardware.</x:v>
+        <x:v>Verify campaign completion with Audi. The factory remedy installs revised stabilizers, front control arms, firmer shock absorbers, and a rear spoiler as specified for the drivetrain configuration.</x:v>
       </x:c>
       <x:c r="F27" s="9" t="n">
         <x:v>0</x:v>
@@ -19169,21 +22243,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="28" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A28" s="40" t="n">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="9" t="str">
-        <x:v>audi-s7-shark-fin-roof-antenna-water-intrusion-causing-gps-satellite</x:v>
+        <x:v>audi-tt-haldex-awd-coupling-pumpcontroller-2000</x:v>
       </x:c>
       <x:c r="C28" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | Prestige, Premium Plus | 4.0T Biturbo V8 (4.0 TFSI)</x:v>
+        <x:v>2008-2010 | Audi | TT</x:v>
       </x:c>
       <x:c r="D28" s="9" t="str">
-        <x:v>Shark-Fin Roof Antenna Water Intrusion Causing GPS / Satellite Radio Reception Loss (C7)</x:v>
+        <x:v>Fuel-Tank Ventilation Valve Can Allow Fuel Leakage (Recall 09V377)</x:v>
       </x:c>
       <x:c r="E28" s="9" t="str">
-        <x:v>Test/replace the shark-fin antenna module with a matching OEM part number and renew the base gasket to restore a watertight seal; in many cases the official fix is a repair kit with a new FAKRA connector and adapter cable rather than a whole new antenna. Access requires partially dropping the rear headliner to reach the single mounting nut and reconnect the coax leads. Inspecting and reseating a corroded coax connection sometimes restores reception without full replacement.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel-tank ventilation valve with the improved valve free of charge under recall 09V377.</x:v>
       </x:c>
       <x:c r="F28" s="9" t="n">
         <x:v>0</x:v>
@@ -19192,21 +22266,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="752.4000244140625" hidden="0" customHeight="1">
+    <x:row r="29" ht="184.8000030517578" hidden="0" customHeight="1">
       <x:c r="A29" s="40" t="n">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="9" t="str">
-        <x:v>audi-s7-sunroof-panoramic-roof-drain-clog-causing-water-intrusion-el</x:v>
+        <x:v>audi-tt-high-speed-stability-recall-for-2000</x:v>
       </x:c>
       <x:c r="C29" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+        <x:v>2016-2019 | Audi | TT</x:v>
       </x:c>
       <x:c r="D29" s="9" t="str">
-        <x:v>Sunroof / Panoramic Roof Drain Clog Causing Water Intrusion and Electronics Damage (C7)</x:v>
+        <x:v>Fuel Tank Can Be Damaged by Heat-Shield Bracket in a Crash (Recall 20V076 / 20BX)</x:v>
       </x:c>
       <x:c r="E29" s="9" t="str">
-        <x:v>Test the drains by slowly pouring water into the channels at each corner of the sunroof and watching where it exits beneath the A- and C-pillars. Clear clogged tubes with low-pressure air or a soft trimmer line (avoid stiff wire that can puncture the tube) and reseat/secure any loose drain-tube connectors at the sunroof frame. Dry out any soaked carpet/insulation promptly and inspect floor-mounted modules for corrosion. Periodic drain cleaning is the best prevention.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers install a protective cap on the heat-shield bracket free of charge under campaign 20BX.</x:v>
       </x:c>
       <x:c r="F29" s="9" t="n">
         <x:v>0</x:v>
@@ -19215,21 +22289,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="422.3999938964844" hidden="0" customHeight="1">
+    <x:row r="30" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A30" s="40" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="9" t="str">
-        <x:v>audi-s7-turbo-oil-strainer-2012</x:v>
+        <x:v>audi-tt-instrument-cluster-pixel-failure-2000</x:v>
       </x:c>
       <x:c r="C30" s="9" t="str">
-        <x:v>2013-2017 | Audi | S7 | 4.0 TFSI</x:v>
+        <x:v>2016-2016 | Audi | TT</x:v>
       </x:c>
       <x:c r="D30" s="9" t="str">
-        <x:v>Turbocharger Oil-Supply Strainer Can Block and Cause Engine Stall (Recall 22V178 / 21H7)</x:v>
+        <x:v>Front-Passenger Airbag Module May Explode or Deploy Improperly (Recall 22V543 / 69DY)</x:v>
       </x:c>
       <x:c r="E30" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the oil strainer and perform an oil change free of charge under campaign 21H7. If abnormal turbo noise, loss of power, or an engine warning occurs, stop safely and arrange dealer inspection.</x:v>
+        <x:v>Check the VIN and campaign history. Audi dealers replace the front-passenger airbag module free of charge under campaign 69DY/61C1.</x:v>
       </x:c>
       <x:c r="F30" s="9" t="n">
         <x:v>0</x:v>
@@ -19238,21 +22312,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="726" hidden="0" customHeight="1">
+    <x:row r="31" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A31" s="40" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="9" t="str">
-        <x:v>audi-s7-turbocharger-wastegate-linkage-rattle-underboost</x:v>
+        <x:v>audi-tt-magnetic-ride-2008</x:v>
       </x:c>
       <x:c r="C31" s="9" t="str">
-        <x:v>2013-2018 | Audi | S7 | S7, S7 Sportback | 4.0T TFSI Biturbo V8 (EA824)</x:v>
+        <x:v>2023-2023 | Audi | TT</x:v>
       </x:c>
       <x:c r="D31" s="9" t="str">
-        <x:v>Turbocharger Wastegate Linkage Rattle and Underboost (4.0T V8)</x:v>
+        <x:v>Passenger-Seat Occupant Detection Connection Can Disable Airbag (Recall 24V251 / 69GU)</x:v>
       </x:c>
       <x:c r="E31" s="9" t="str">
-        <x:v>Diagnose the rattle and any boost faults to confirm wastegate-arm play versus a loose heat shield. Minor play can sometimes be mitigated with a clip, but the durable factory fix is turbocharger replacement. When replacing a hot-V turbo, it is mandatory to also replace the oil feed and return lines and to prime the new unit with oil before first start to prevent immediate bearing failure. Regular oil changes and allowing turbo cool-down help reduce coking-related wear.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers replace the passenger-seat occupant-detection control module free of charge under campaign 69GU.</x:v>
       </x:c>
       <x:c r="F31" s="9" t="n">
         <x:v>0</x:v>
@@ -19261,21 +22335,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="686.4000244140625" hidden="0" customHeight="1">
+    <x:row r="32" ht="726" hidden="0" customHeight="1">
       <x:c r="A32" s="40" t="n">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="9" t="str">
-        <x:v>audi-s8-5-2-v10-timing-chain-tensioner-guide-wear</x:v>
+        <x:v>audi-tt-tail-light-corrosion-2008</x:v>
       </x:c>
       <x:c r="C32" s="9" t="str">
-        <x:v>2007-2012 | Audi | S8 | 5.2L FSI V10 (BSM)</x:v>
+        <x:v>2008-2015 | Audi | TT</x:v>
       </x:c>
       <x:c r="D32" s="9" t="str">
-        <x:v>5.2 V10 Timing Chain Tensioner / Guide Wear (D3 Cold-Start Rattle)</x:v>
+        <x:v>Tail Light Electrical Connector Corrosion (Mk2)</x:v>
       </x:c>
       <x:c r="E32" s="9" t="str">
-        <x:v>Investigate any cold-start rattle promptly: inspect tensioner travel and guide condition. Replace the timing chains, tensioners, and plastic guides as a set with updated genuine parts; this is a major, labor-intensive repair (often engine-out). Strictly follow short oil-change intervals with the correct grade to maximize tensioner/guide life, and address any low-oil-pressure condition immediately. Do not drive a V10 with a persistent timing rattle.</x:v>
+        <x:v>Remove tail light assembly, inspect electrical connector for green corrosion. CLEAN connector with electrical contact cleaner and wire brush ($20 DIY). Apply dielectric grease to prevent future corrosion ($10). If connector is severely corroded: Replace pigtail connector ($50-$100 parts). Improve tail light seal with silicone sealant around housing ($15). This is a DIY-friendly repair taking 1-2 hours. If paying shop, costs $150-$300. Address early before corrosion causes shorts.</x:v>
       </x:c>
       <x:c r="F32" s="9" t="n">
         <x:v>0</x:v>
@@ -19284,21 +22358,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="198" hidden="0" customHeight="1">
+    <x:row r="33" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A33" s="40" t="n">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="9" t="str">
-        <x:v>audi-s8-air-suspension-2013</x:v>
+        <x:v>audi-tt-water-pump-2008</x:v>
       </x:c>
       <x:c r="C33" s="9" t="str">
-        <x:v>2013-2024 | Audi | S8</x:v>
+        <x:v>2008-2008 | Audi | TT</x:v>
       </x:c>
       <x:c r="D33" s="9" t="str">
-        <x:v>Adaptive Air Suspension Multi-Point Failure</x:v>
+        <x:v>C-Pillar Trim Cover Can Detach During Belt-Tensioner Deployment (Recall 08V064)</x:v>
       </x:c>
       <x:c r="E33" s="9" t="str">
-        <x:v>Replace air struts as they fail. Budget for full system refresh at 80,000 miles. Arnott aftermarket struts offer cost savings.</x:v>
+        <x:v>Check VIN eligibility. Audi dealers install improved C-pillar trim clips free of charge under recall 08V064.</x:v>
       </x:c>
       <x:c r="F33" s="9" t="n">
         <x:v>0</x:v>
@@ -19307,21 +22381,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="726" hidden="0" customHeight="1">
+    <x:row r="34" ht="1161.5999755859375" hidden="0" customHeight="1">
       <x:c r="A34" s="40" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="9" t="str">
-        <x:v>audi-s8-air-suspension-failure-2013</x:v>
+        <x:v>audi-tts-cam-follower-hpfp-2009</x:v>
       </x:c>
       <x:c r="C34" s="9" t="str">
-        <x:v>2020-2024 | Audi | S8</x:v>
+        <x:v>2009-2015 | Audi | TTS | TTS | EA888</x:v>
       </x:c>
       <x:c r="D34" s="9" t="str">
-        <x:v>2020-2024 S8 Air-Suspension Malfunction with J1135 Communication Fault - Diagnosis Required</x:v>
+        <x:v>HPFP Cam Follower Wear and High-Pressure Fuel Pump Failure (Mk2)</x:v>
       </x:c>
       <x:c r="E34" s="9" t="str">
-        <x:v>Read the suspension-controller DTC and symptom code, then inspect wiring, terminals and connectors between J775 and J1135 exactly as Audi specifies. If the fault is passive/sporadic, clear it and verify operation. If it remains active/static after the electrical inspection and key cycle, follow Audi testing for J1135 replacement. Diagnose vehicle sag or leak-down separately; do not order air struts, a compressor or a coil-conversion kit from the former card.</x:v>
+        <x:v>INSPECTION (every 20,000 miles): Remove HPFP (3 bolts) and inspect cam follower surface. If the hardened coating is wearing through (visible copper/brass color), replace follower immediately ($30-$50 part, 30-60 minutes labor). CRITICAL: Ensure cam lobe is at LOW point before reinstalling—if at peak, you'll compress the spring and can break the mounting bolts. If CAMSHAFT WORN (deep groove in lobe): Replace camshaft ($2,000-$4,000). If FUEL PUMP FAILED: Replace HPFP ($400-$800). PREVENTION: Inspect cam follower every 20,000 miles as routine maintenance. Add to every oil change checklist. Consider IE (Integrated Engineering) upgraded HPFP with roller follower to eliminate wear entirely.</x:v>
       </x:c>
       <x:c r="F34" s="9" t="n">
         <x:v>0</x:v>
@@ -19330,21 +22404,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="35" ht="884.4000244140625" hidden="0" customHeight="1">
       <x:c r="A35" s="40" t="n">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="9" t="str">
-        <x:v>audi-s8-battery-management-energy-control-module-faults-parasitic-dr</x:v>
+        <x:v>audi-tts-carbon-buildup-2009</x:v>
       </x:c>
       <x:c r="C35" s="9" t="str">
-        <x:v>2020-2020 | Audi | S8 | VIN-specific Emissions Service Action 27BQ; verify open action in Audi campaign lookup | 4.0T TFSI V8 mild-hybrid</x:v>
+        <x:v>2016-2017 | Audi | TTS</x:v>
       </x:c>
       <x:c r="D35" s="9" t="str">
-        <x:v>2020 S8 Starter-Alternator Emissions Service Action 27BQ - VIN Check Required</x:v>
+        <x:v>2016-2017 TTS Cold-Start Misfire DTCs Without Felt Misfire - TSB 2051384/1</x:v>
       </x:c>
       <x:c r="E35" s="9" t="str">
-        <x:v>Check the VIN in Audi’s recall/service-campaign lookup or ask an Audi dealer to verify 27BQ in Elsa. If open, the dealer replaces the starter-alternator under the action. Electrical-system warnings, a discharged battery, abnormal charging or overnight draw outside this exact action require battery/charging tests and a measured sleep-current diagnosis; do not replace a battery monitor, gateway or MMI module from the former card.</x:v>
+        <x:v>Confirm the exact cold-start timing, simultaneous-cylinder DTC pattern, absence of a felt misfire, CYFB engine and installed ECM software before using this bulletin. When applicable, an Audi-capable workshop updates ECM J623 from software part number 8S0906259C version 0001 to version 0004 or higher using SVM action 01A190, then clears the DTCs. A felt misfire, a different timing or RPM pattern, a different engine/software combination or a returning concern requires normal diagnosis rather than carbon cleaning by assumption.</x:v>
       </x:c>
       <x:c r="F35" s="9" t="n">
         <x:v>0</x:v>
@@ -19353,21 +22427,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="36" ht="910.7999877929688" hidden="0" customHeight="1">
       <x:c r="A36" s="40" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="9" t="str">
-        <x:v>audi-s8-biturbo-coolant-2013</x:v>
+        <x:v>audi-tts-dsg-mechatronic-2009</x:v>
       </x:c>
       <x:c r="C36" s="9" t="str">
-        <x:v>2013-2024 | Audi | S8 | 4.0T</x:v>
+        <x:v>2019-2023 | Audi | TTS</x:v>
       </x:c>
       <x:c r="D36" s="9" t="str">
-        <x:v>4.0T Turbo Coolant System Degradation</x:v>
+        <x:v>2019-2023 TTS Clutch K1 Overheat and Transmission DTC Diagnosis - TSB 2060560/3</x:v>
       </x:c>
       <x:c r="E36" s="9" t="str">
-        <x:v>Replace all turbo coolant and oil feed lines preventatively at 60,000 miles. Monitor coolant levels closely.</x:v>
+        <x:v>Have an Audi-capable workshop check whether TSB 2050723 applies first. If it does not resolve or control the concern, inspect the clutch-K1 maximum-temperature value and document a transmission-fluid sample. Replace the dual clutch, transmission fluid and filter only when the approximately 400 °C K1 value and burnt black or very dark fluid are both present. If those findings are absent, this bulletin does not apply and Audi directs the workshop to continue diagnosis through TAC. Any clutch repair kit must be selected by VIN and production date.</x:v>
       </x:c>
       <x:c r="F36" s="9" t="n">
         <x:v>0</x:v>
@@ -19376,21 +22450,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="37" ht="858" hidden="0" customHeight="1">
       <x:c r="A37" s="40" t="n">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="9" t="str">
-        <x:v>audi-s8-clogged-sunroof-plenum-drains-causing-water-intrusion-electr</x:v>
+        <x:v>audi-tts-magnetic-ride-2009</x:v>
       </x:c>
       <x:c r="C37" s="9" t="str">
-        <x:v>2007-2018 | Audi | S8 | S8, S8 Plus | 5.2 FSI V10, 4.0 TFSI twin-turbo V8 (4.0T)</x:v>
+        <x:v>2016-2016 | Audi | TTS</x:v>
       </x:c>
       <x:c r="D37" s="9" t="str">
-        <x:v>Clogged Sunroof / Plenum Drains Causing Water Intrusion and Electronics Damage</x:v>
+        <x:v>2016 TTS Magnetic-Ride Rear Shock-Mount Rumble - TSB 2042539/4</x:v>
       </x:c>
       <x:c r="E37" s="9" t="str">
-        <x:v>Clear and flush all sunroof and plenum/cowl drains; replace cracked drain hoses, grommets, or channel connectors. Dry out saturated carpet/insulation and inspect plenum-area modules for corrosion, replacing any water-damaged control units. Preventively clean the drains at least annually and keep the cowl area free of leaves/debris.</x:v>
+        <x:v>First reproduce the noise, verify that it comes from the rear shock mounts and confirm that the vehicle was originally equipped with mount 8S0 513 353. Only when those gates are satisfied, remove both rear shock assemblies and replace both mounts with 8V0 513 353 according to Audi workshop instructions, adapt the suspension control position and test drive to confirm the repair. If the installed mount does not match, continue Audi diagnosis. Do not replace magnetic dampers or convert the vehicle to coilovers from this noise alone.</x:v>
       </x:c>
       <x:c r="F37" s="9" t="n">
         <x:v>0</x:v>
@@ -19399,21 +22473,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="38" ht="1016.4000244140625" hidden="0" customHeight="1">
       <x:c r="A38" s="40" t="n">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="9" t="str">
-        <x:v>audi-s8-coolant-thermostat-leak-2013</x:v>
+        <x:v>audi-tts-timing-chain-tensioner-2009</x:v>
       </x:c>
       <x:c r="C38" s="9" t="str">
-        <x:v>2020-2021 | Audi | S8 | 2021 applicability ends at VIN 012194; confirm VIN and coolant-pump leak before repair | 4.0T TFSI V8</x:v>
+        <x:v>2009-2015 | Audi | TTS | TTS | EA888 Gen 1, EA888 Gen 2</x:v>
       </x:c>
       <x:c r="D38" s="9" t="str">
-        <x:v>2020-Early 2021 S8 Coolant-Pump Leak - Diagnosis Required</x:v>
+        <x:v>Timing Chain Tensioner Failure (EA888 Gen 1/2 - Mk2 TTS)</x:v>
       </x:c>
       <x:c r="E38" s="9" t="str">
-        <x:v>Do not drive an overheating vehicle. Record coolant warning and temperature behavior, pressure-test the cooling system when safe, and locate the leak. Confirm the 2021 VIN boundary and apply TSB 2065040/4 only when the coolant pump is the identified source. Other thermostat, hose, turbo-line, heat-exchanger or internal-loss causes require separate diagnosis; do not order the former thermostat/water-pump bundle from this card.</x:v>
+        <x:v>PREVENTIVE REPLACEMENT: Replace timing chain, tensioner, guides, and sprockets at 80,000-100,000 miles BEFORE symptoms appear ($2,000-$4,000). This is the MOST important preventive maintenance on the Mk2 TTS. IF RATTLING: Do NOT delay—the chain can jump at any startup. Schedule repair immediately. Use ONLY the latest OEM revised tensioner (06K109467K). IF CHAIN JUMPED: Engine likely destroyed—compression test all cylinders. Rebuild ($5,000-$8,000) or replacement engine ($6,000-$12,000). PREVENTION: Change oil every 5,000 miles with high-quality synthetic. Low oil level accelerates tensioner wear.</x:v>
       </x:c>
       <x:c r="F38" s="9" t="n">
         <x:v>0</x:v>
@@ -19422,21 +22496,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="39" ht="976.7999877929688" hidden="0" customHeight="1">
       <x:c r="A39" s="40" t="n">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="9" t="str">
-        <x:v>audi-s8-cylinder-demand-active-engine-mount-failure-4-cylinder-mode</x:v>
+        <x:v>audi-tts-water-pump-2009</x:v>
       </x:c>
       <x:c r="C39" s="9" t="str">
-        <x:v>2013-2015 | Audi | S8 | 4.0 TFSI vehicles with reproducible 1000-3000 rpm vibration; diagnose J931 before mount replacement | 4.0T TFSI V8</x:v>
+        <x:v>2012-2023 | Audi | TTS</x:v>
       </x:c>
       <x:c r="D39" s="9" t="str">
-        <x:v>2013-2015 S8 COD Vibration with J931 Basic-Setting Fault - Diagnosis Required</x:v>
+        <x:v>2012 / 2020-2023 TTS Coolant-Pump Update and Leak Diagnosis</x:v>
       </x:c>
       <x:c r="E39" s="9" t="str">
-        <x:v>Reproduce the vibration under Audi’s specified driving conditions and scan J931. If the bulletin applies, verify J931 software, perform the required SVM update and basic settings, align the exhaust without tension, repeat basic settings and follow the referenced diagnosis if vibration remains. Inspect mount hardware only after the software, calibration and exhaust path. Do not disable cylinder-on-demand or replace both mounts from the former card.</x:v>
+        <x:v>For a 2012 TTS, ask an Audi dealer to check the VIN and current campaign/action history for Update 19J2; the published update replaced the pump only when its exact criteria were met and does not promise current warranty coverage. For a 2020-2023 2.0L TTS, first exclude a low level caused by incomplete bleeding or an earlier repair, document and clean the suspected leak, refill to maximum and recheck after driving. Continue observation when no leak returns; replace only the component proven to leak when coolant reappears. Do not select a pump or thermostat assembly before VIN-, engine- and leak-specific diagnosis.</x:v>
       </x:c>
       <x:c r="F39" s="9" t="n">
         <x:v>0</x:v>
@@ -19445,1176 +22519,26 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="765.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A40" s="40" t="n">
+    <x:row r="40" ht="198" hidden="0" customHeight="1">
+      <x:c r="A40" s="42" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B40" s="9" t="str">
-        <x:v>audi-s8-d2-4-2-v8-timing-belt-tensioner-service</x:v>
-      </x:c>
-      <x:c r="C40" s="9" t="str">
-        <x:v>2001-2003 | Audi | S8 | 4.2L 40V V8 (AYS)</x:v>
-      </x:c>
-      <x:c r="D40" s="9" t="str">
-        <x:v>D2 4.2 V8 Timing Belt and Tensioner Service (Interference Engine)</x:v>
-      </x:c>
-      <x:c r="E40" s="9" t="str">
-        <x:v>Replace the timing belt as a complete kit — belt, tensioner, idler/guide rollers, and water pump — at or before Audi's interval (and by age regardless of mileage). Use genuine/OE-quality components and set cam/crank timing precisely with the correct locking tools; this is a front-of-engine ('service position') job. Inspect the exhaust-side chain tensioners while in there. Always confirm timing-belt history (with receipts) before buying a D2 S8; if unknown, do it immediately.</x:v>
-      </x:c>
-      <x:c r="F40" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G40" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" ht="844.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A41" s="40" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B41" s="9" t="str">
-        <x:v>audi-s8-direct-injection-carbon-buildup-intake-valves</x:v>
-      </x:c>
-      <x:c r="C41" s="9" t="str">
-        <x:v>2013-2018 | Audi | S8 | 4.0T TFSI V8 (CTFA/CGTA/CWUC)</x:v>
-      </x:c>
-      <x:c r="D41" s="9" t="str">
-        <x:v>Direct-Injection Carbon Buildup on Intake Valves (Misfires / Rough Idle)</x:v>
-      </x:c>
-      <x:c r="E41" s="9" t="str">
-        <x:v>Confirm via borescope of the intake valves (and rule out coils/plugs/PCV first). The accepted repair is walnut-shell blasting: remove the intake manifold and media-blast the carbon off the valves and ports with crushed walnut shells, then reinstall with new intake gaskets. Replace spark plugs and inspect coils while the manifold is off. Preventively, keep up with oil changes, fix any PCV/oil-burning source, and consider periodic cleaning every ~40,000-60,000 miles. Catch-can solutions reduce future accumulation.</x:v>
-      </x:c>
-      <x:c r="F41" s="9" t="n">
+      <x:c r="B40" s="43" t="str">
+        <x:v>audi-tts-waterpump-housing-2009</x:v>
+      </x:c>
+      <x:c r="C40" s="43" t="str">
+        <x:v>2009-2024 | Audi | TTS | EA888</x:v>
+      </x:c>
+      <x:c r="D40" s="43" t="str">
+        <x:v>Water Pump and Thermostat Housing Failure</x:v>
+      </x:c>
+      <x:c r="E40" s="43" t="str">
+        <x:v>Replace water pump, thermostat, and housing as a complete assembly. Use metal-impeller aftermarket pump if available.</x:v>
+      </x:c>
+      <x:c r="F40" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G41" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" ht="686.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A42" s="40" t="n">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B42" s="9" t="str">
-        <x:v>audi-s8-front-suspension-control-arm-bushing-sway-bar-link-wear</x:v>
-      </x:c>
-      <x:c r="C42" s="9" t="str">
-        <x:v>2020-2021 | Audi | S8 | 2021 applicability through VIN 028090; localize noise acoustically before parts | 4.0T TFSI V8 mild-hybrid</x:v>
-      </x:c>
-      <x:c r="D42" s="9" t="str">
-        <x:v>2020-Early 2021 S8 Front Lower Guide-Link Hydro-Bushing Noise - Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E42" s="9" t="str">
-        <x:v>Confirm the VIN boundary, reproduce the noise and localize it with acoustic diagnostic equipment. Inspect the lower guide-link hydro-bushings and surrounding joints. If the hydro-bushing is confirmed, follow Audi’s paired replacement procedure; complete guide links may be required when prior pressing or rework prevents the specified repair. Align the vehicle as required. Do not order a ten-arm kit or sway-bar links from the former card.</x:v>
-      </x:c>
-      <x:c r="F42" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G42" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" ht="778.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A43" s="40" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B43" s="9" t="str">
-        <x:v>audi-s8-high-pressure-fuel-pump-injector-internal-leak-causing-hard</x:v>
-      </x:c>
-      <x:c r="C43" s="9" t="str">
-        <x:v>2013-2018 | Audi | S8 | 4.0 TFSI; diagnosis requires ODIS values, software check and pressure-hold testing | 4.0T TFSI V8</x:v>
-      </x:c>
-      <x:c r="D43" s="9" t="str">
-        <x:v>2013-2018 S8 Warm-Soak Long-Crank or No-Start - Fuel Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E43" s="9" t="str">
-        <x:v>Have the dealer read DTCs and ODIS fuel-in-oil value, verify ECM software and perform Audi’s high- and low-pressure holding tests. If high-pressure behavior is abnormal, borescope the combustion chamber to identify a leaking injector. If low-side pressure builds correctly but drops more than 1.5 bar in the first 15 minutes, Audi says at least one HPFP may be leaking and directs replacement of both pumps plus an oil change. Select no pump or injector until the test identifies the path.</x:v>
-      </x:c>
-      <x:c r="F43" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G43" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" ht="673.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A44" s="40" t="n">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B44" s="9" t="str">
-        <x:v>audi-s8-mmi-upper-display-backup-camera-black-screen</x:v>
-      </x:c>
-      <x:c r="C44" s="9" t="str">
-        <x:v>2020-2026 | Audi | S8 | VIN-specific NHTSA 25V900 / Audi 90TV; verify open recall | 4.0T TFSI V8 mild-hybrid</x:v>
-      </x:c>
-      <x:c r="D44" s="9" t="str">
-        <x:v>2020-2026 S8 Rearview/Top-View Camera Image May Not Display - Recall 25V900</x:v>
-      </x:c>
-      <x:c r="E44" s="9" t="str">
-        <x:v>Check the VIN in Audi’s recall/service-campaign lookup and schedule the free 90TV software remedy if open. Use extra care when reversing until repaired and visually check the area around the vehicle. A completely dead or rebooting MMI display, missing instrument-cluster data, wiring fault or hardware failure requires separate diagnosis and must not be attributed to this recall without VIN and symptom confirmation.</x:v>
-      </x:c>
-      <x:c r="F44" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G44" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" ht="792" hidden="0" customHeight="1">
-      <x:c r="A45" s="40" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B45" s="9" t="str">
-        <x:v>audi-s8-oil-consumption-2013</x:v>
-      </x:c>
-      <x:c r="C45" s="9" t="str">
-        <x:v>2020-2023 | Audi | S8 | EA825 4.0L; confirm VIN, engine and measured consumption under Audi procedure | 4.0T TFSI V8 mild-hybrid (EA825)</x:v>
-      </x:c>
-      <x:c r="D45" s="9" t="str">
-        <x:v>2020-2023 S8 High Oil Consumption and Updated Piston Rings - Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E45" s="9" t="str">
-        <x:v>Document oil-level warnings, mileage, top-up quantity, leaks and oil specification, then have an Audi dealer perform the authorized oil-consumption measurement. Repair is justified only when the measured result exceeds the applicable owner-manual limit and other leakage or operating causes are excluded. If TSB 2071114 applies, follow its VIN/engine-specific piston, ring and connecting-rod procedure. Do not change oil viscosity or authorize internal-engine work solely from the former card.</x:v>
-      </x:c>
-      <x:c r="F45" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G45" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" ht="646.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A46" s="40" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B46" s="9" t="str">
-        <x:v>audi-s8-pcv-oil-separator-failure-excessive-crankcase-vacuum</x:v>
-      </x:c>
-      <x:c r="C46" s="9" t="str">
-        <x:v>2013-2016 | Audi | S8 | 4.0 TFSI; confirm warm-idle sound and filler-cap response before oil-separator replacement | 4.0T TFSI V8</x:v>
-      </x:c>
-      <x:c r="D46" s="9" t="str">
-        <x:v>2013-2016 S8 Warm-Idle Whistle from Crankcase Breather Leak - Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E46" s="9" t="str">
-        <x:v>Compare the sound with Audi’s reference condition and check whether opening the oil filler cap changes it. Read P2279/P0507 and rule out other intake leaks. When the sound matches and is affected by the filler-cap check, follow Audi’s oil-separator breather replacement procedure and renew required seals/consumables by VIN. Do not diagnose by oil-cap feel alone or order the former five-item parts list.</x:v>
-      </x:c>
-      <x:c r="F46" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G46" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" ht="594" hidden="0" customHeight="1">
-      <x:c r="A47" s="40" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B47" s="9" t="str">
-        <x:v>audi-s8-porous-high-pressure-fuel-supply-line-recall-nhtsa-19v057000</x:v>
-      </x:c>
-      <x:c r="C47" s="9" t="str">
-        <x:v>2013-2016 | Audi | S8 | VIN-specific NHTSA 19V057 / Audi 20BM; verify open recall | 4.0T TFSI V8</x:v>
-      </x:c>
-      <x:c r="D47" s="9" t="str">
-        <x:v>2013-2016 S8 Porous Fuel-Pump Supply Line / Fire Risk - Recall 19V057</x:v>
-      </x:c>
-      <x:c r="E47" s="9" t="str">
-        <x:v>Check the VIN for open recall 20BM and contact an Audi dealer without delay. The free remedy installs a fuel-pressure damper in the low-pressure fuel supply inside the tank. If fuel odor or visible leakage is present, avoid ignition sources, do not continue driving, and arrange dealer inspection/towing as appropriate. Do not buy a retail line or damper from the former card.</x:v>
-      </x:c>
-      <x:c r="F47" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G47" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" ht="211.1999969482422" hidden="0" customHeight="1">
-      <x:c r="A48" s="40" t="n">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B48" s="9" t="str">
-        <x:v>audi-s8-torque-converter-2013</x:v>
-      </x:c>
-      <x:c r="C48" s="9" t="str">
-        <x:v>2013-2024 | Audi | S8</x:v>
-      </x:c>
-      <x:c r="D48" s="9" t="str">
-        <x:v>ZF 8-Speed Torque Converter and Valve Body Issues</x:v>
-      </x:c>
-      <x:c r="E48" s="9" t="str">
-        <x:v>Replace torque converter and service valve body. Full ZF fluid and filter change every 50,000 miles extends transmission life.</x:v>
-      </x:c>
-      <x:c r="F48" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G48" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" ht="712.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A49" s="40" t="n">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B49" s="9" t="str">
-        <x:v>audi-s8-turbo-oil-strainer-2013</x:v>
-      </x:c>
-      <x:c r="C49" s="9" t="str">
-        <x:v>2013-2017 | Audi | S8 | VIN-specific NHTSA 22V178 / Audi 21H7; verify open recall | 4.0T TFSI V8</x:v>
-      </x:c>
-      <x:c r="D49" s="9" t="str">
-        <x:v>2013-2017 S8 Blocked Turbocharger Oil Strainer / Stall Risk - Recall 22V178</x:v>
-      </x:c>
-      <x:c r="E49" s="9" t="str">
-        <x:v>Check the VIN for open recall 21H7 and schedule the free Audi dealer remedy, which replaces the oil strainer and performs an oil change. If EPC, MIL or oil warning lights appear with unusual turbo noise, extended cranking, rough idle, loss of power or stalling, stop safely and arrange diagnosis. Turbo damage, warranty eligibility and any additional repair must be assessed by VIN and inspection; do not buy the former retail strainer.</x:v>
-      </x:c>
-      <x:c r="F49" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G49" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" ht="950.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A50" s="40" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B50" s="9" t="str">
-        <x:v>audi-s8-water-to-air-intercooler-internal-coolant-leak</x:v>
-      </x:c>
-      <x:c r="C50" s="9" t="str">
-        <x:v>2013-2018 | Audi | S8 | 4.0T TFSI V8 (CTFA/CGTA/CWUC)</x:v>
-      </x:c>
-      <x:c r="D50" s="9" t="str">
-        <x:v>Water-to-Air Intercooler Internal Coolant Leak (Coolant into Intake)</x:v>
-      </x:c>
-      <x:c r="E50" s="9" t="str">
-        <x:v>Confirm the source: pressure-test the cooling system and inspect the charge piping/intercooler outlet for coolant residue; scope for white smoke and coolant on the intake side rather than an external leak. Replace the water-to-air intercooler/charge-air cooler unit (genuine OEM core). Because access requires removing intake components in the valley, it is standard practice to also replace the turbo oil strainer, coolant valves, and PCV/oil separator while in there. Refill and bleed the cooling system per procedure. This is a high-difficulty job typically done by a specialist or dealer.</x:v>
-      </x:c>
-      <x:c r="F50" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G50" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" ht="475.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A51" s="40" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B51" s="9" t="str">
-        <x:v>audi-sq2-ea888-2-0-tfsi-coolant-leak-from-water-pump-thermostat-housi</x:v>
-      </x:c>
-      <x:c r="C51" s="9" t="str">
-        <x:v>2019-2024 | Audi | SQ2 | 2.0 TFSI quattro | EA888 2.0 TFSI Gen3</x:v>
-      </x:c>
-      <x:c r="D51" s="9" t="str">
-        <x:v>EA888 2.0 TFSI coolant leak from water pump / thermostat housing</x:v>
-      </x:c>
-      <x:c r="E51" s="9" t="str">
-        <x:v>Replace the failed water pump / thermostat housing assembly, ideally with the latest revised, more heat-resistant unit; many shops fit an upgraded repair kit and a new gasket. Catch it early by watching for slowly dropping coolant level and a faint sweet smell. Combine with a coolant flush and refill.</x:v>
-      </x:c>
-      <x:c r="F51" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G51" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" ht="396" hidden="0" customHeight="1">
-      <x:c r="A52" s="40" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B52" s="9" t="str">
-        <x:v>audi-sq2-electro-mechanical-parking-brake-brake-pedal-weld-recalls</x:v>
-      </x:c>
-      <x:c r="C52" s="9" t="str">
-        <x:v>2019-2020 | Audi | SQ2</x:v>
-      </x:c>
-      <x:c r="D52" s="9" t="str">
-        <x:v>Electro-mechanical parking brake and brake-pedal weld recalls (early build)</x:v>
-      </x:c>
-      <x:c r="E52" s="9" t="str">
-        <x:v>These are recall items — have the VIN checked against the Audi/DVSA recall database and any open campaign rectified free of charge at a dealer. Report any abnormal parking-brake behaviour or a soft/abnormal brake pedal immediately.</x:v>
-      </x:c>
-      <x:c r="F52" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G52" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" ht="475.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A53" s="40" t="n">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B53" s="9" t="str">
-        <x:v>audi-sq2-internal-fuse-box-wiring-harness-can-work-loose-causing-sudd</x:v>
-      </x:c>
-      <x:c r="C53" s="9" t="str">
-        <x:v>2022-2023 | Audi | SQ2 | 2.0 TFSI</x:v>
-      </x:c>
-      <x:c r="D53" s="9" t="str">
-        <x:v>2022-2023 Audi SQ2 Interior Fuse-Carrier Recall GAI-3692</x:v>
-      </x:c>
-      <x:c r="E53" s="9" t="str">
-        <x:v>Check the VIN and open-campaign status with an authorised Audi dealer in the vehicle’s market. The campaign remedy is dealer inspection and correction of the fuse-carrier power connection. Do not replace a fuse box or wiring harness solely from a warning lamp or this model-year summary.</x:v>
-      </x:c>
-      <x:c r="F53" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G53" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A54" s="40" t="n">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B54" s="9" t="str">
-        <x:v>audi-sq2-mmi-infotainment-freezing-rebooting-lost-settings</x:v>
-      </x:c>
-      <x:c r="C54" s="9" t="str">
-        <x:v>2019-2024 | Audi | SQ2</x:v>
-      </x:c>
-      <x:c r="D54" s="9" t="str">
-        <x:v>MMI infotainment freezing, rebooting and lost settings</x:v>
-      </x:c>
-      <x:c r="E54" s="9" t="str">
-        <x:v>A forced MMI restart (press and hold the on/off or volume control ~10 seconds until it reboots) clears many transient faults. Persistent issues are usually resolved by a dealer software/firmware update; check for any applicable MMI update campaigns. Only in rare cases is the MMI head unit itself replaced.</x:v>
-      </x:c>
-      <x:c r="F54" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G54" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A55" s="40" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B55" s="9" t="str">
-        <x:v>audi-sq2-pcv-crankcase-ventilation-valve-diaphragm-failure-causing-ro</x:v>
-      </x:c>
-      <x:c r="C55" s="9" t="str">
-        <x:v>2019-2024 | Audi | SQ2 | EA888 2.0 TFSI Gen3</x:v>
-      </x:c>
-      <x:c r="D55" s="9" t="str">
-        <x:v>PCV / crankcase ventilation valve diaphragm failure causing rough idle and lean-running codes</x:v>
-      </x:c>
-      <x:c r="E55" s="9" t="str">
-        <x:v>Replace the PCV valve (or the valve-cover assembly that integrates it) with the latest revised part; some owners fit a catch-can to reduce recurrence. A quick field test — briefly covering the bleeder hole on the cap to see if idle stabilises or whistling stops — helps confirm before replacement.</x:v>
-      </x:c>
-      <x:c r="F55" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G55" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" ht="752.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A56" s="40" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B56" s="9" t="str">
-        <x:v>audi-sq2-s-tronic-7-speed-wet-clutch-transmission-jerky-low-speed-shi</x:v>
-      </x:c>
-      <x:c r="C56" s="9" t="str">
-        <x:v>2019-2024 | Audi | SQ2 | 7-speed S tronic | DQ381 / 0GC 7-speed wet-clutch S tronic</x:v>
-      </x:c>
-      <x:c r="D56" s="9" t="str">
-        <x:v>S tronic (DQ381) 7-speed wet-clutch transmission: jerky low-speed shifts, hesitation and limp mode</x:v>
-      </x:c>
-      <x:c r="E56" s="9" t="str">
-        <x:v>First step is a proper DSG fluid-and-filter service (the wet-clutch unit needs periodic transmission oil changes — many owners do it around 40k miles even though intervals can be longer). Have the TCU scanned for stored codes; sensor or mechatronic valve replacement and re-coding/adaptation resolves many cases, while severe cases need a full mechatronic unit or clutch-pack replacement. Insist on a software/adaptation update at the dealer for driveability complaints.</x:v>
-      </x:c>
-      <x:c r="F56" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G56" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" ht="541.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A57" s="40" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B57" s="9" t="str">
-        <x:v>audi-sq5-air-suspension-2018</x:v>
-      </x:c>
-      <x:c r="C57" s="9" t="str">
-        <x:v>2018-2025 | Audi | SQ5</x:v>
-      </x:c>
-      <x:c r="D57" s="9" t="str">
-        <x:v>Air-Suspension Warning with C1260F0 or U112100 Communication Fault</x:v>
-      </x:c>
-      <x:c r="E57" s="9" t="str">
-        <x:v>Inspect the wiring and connector contacts between J775 and J1135 first. If no wiring fault is found, clear a first passive or sporadic fault and release the vehicle. Replace J1135 for an active or static fault, or when the same passive or sporadic fault returns a second time, following Audi workshop information and VIN-specific ETKA data.</x:v>
-      </x:c>
-      <x:c r="F57" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G57" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" ht="924" hidden="0" customHeight="1">
-      <x:c r="A58" s="40" t="n">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B58" s="9" t="str">
-        <x:v>audi-sq5-carbon-buildup-2014</x:v>
-      </x:c>
-      <x:c r="C58" s="9" t="str">
-        <x:v>2014-2025 | Audi | SQ5 | 3.0T Supercharged, 3.0T</x:v>
-      </x:c>
-      <x:c r="D58" s="9" t="str">
-        <x:v>Fuel-Quality or Deposit-Related Rough Running and Misfire Diagnosis</x:v>
-      </x:c>
-      <x:c r="E58" s="9" t="str">
-        <x:v>Confirm fuel quality, symptoms and stored DTCs before replacing or cleaning components. If contaminated gasoline is suspected, advise changing the fuel source; if low detergent quality is suspected, Audi recommends Top Tier detergent gasoline. Continue workshop diagnosis if symptoms persist. On 2018-2025 EA839 SQ5 models, do not recommend unapproved cleaners or additives; follow the owner manual and use only Audi-approved petrol additives. Do not prescribe routine walnut blasting, a catch can or chemical cleaning from this record.</x:v>
-      </x:c>
-      <x:c r="F58" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G58" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" ht="765.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A59" s="40" t="n">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="B59" s="9" t="str">
-        <x:v>audi-sq5-pcv-valve-2014</x:v>
-      </x:c>
-      <x:c r="C59" s="9" t="str">
-        <x:v>2014-2017 | Audi | SQ5 | 3.0T Supercharged</x:v>
-      </x:c>
-      <x:c r="D59" s="9" t="str">
-        <x:v>P052E00 Crankcase-Breather Membrane or Elbow Fault</x:v>
-      </x:c>
-      <x:c r="E59" s="9" t="str">
-        <x:v>Use Audi hand-vacuum test to distinguish a membrane leak from an elbow fault. If indicated, remove the compressor or intake manifold and inspect the membrane and the breather two metal plates. Use repair kit 06E103772H only for a confirmed membrane or plate fault. For a confirmed elbow fault, replace elbow 06E103402 and spring clip N10769401 rather than automatically replacing the complete breather. Verify current part data in ETKA before ordering.</x:v>
-      </x:c>
-      <x:c r="F59" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G59" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" ht="171.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A60" s="40" t="n">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B60" s="9" t="str">
-        <x:v>audi-sq5-supercharger-2014</x:v>
-      </x:c>
-      <x:c r="C60" s="9" t="str">
-        <x:v>2014-2018 | Audi | SQ5 | 3.0T</x:v>
-      </x:c>
-      <x:c r="D60" s="9" t="str">
-        <x:v>3.0T Supercharger Bearing and Intercooler Pump Failure</x:v>
-      </x:c>
-      <x:c r="E60" s="9" t="str">
-        <x:v>Replace supercharger nose bearing kit. Replace intercooler pump if failing. Service supercharger belt tension.</x:v>
-      </x:c>
-      <x:c r="F60" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G60" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" ht="844.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A61" s="40" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B61" s="9" t="str">
-        <x:v>audi-sq5-supercharger-oil-leak-2014</x:v>
-      </x:c>
-      <x:c r="C61" s="9" t="str">
-        <x:v>2014-2017 | Audi | SQ5 | Premium Plus, Prestige | 3.0T Supercharged, 3.0T</x:v>
-      </x:c>
-      <x:c r="D61" s="9" t="str">
-        <x:v>Supercharger Seal and Gasket Oil Leaks (3.0T)</x:v>
-      </x:c>
-      <x:c r="E61" s="9" t="str">
-        <x:v>JHM Motorsports sells a complete supercharger replacement seal and gasket kit for the Eaton unit in the 3.0T. Replacing all seals at once is recommended since the supercharger must be removed for access. Nose cone seal, rotor shaft seals, and manifold gaskets should all be replaced together ($300-$500 in parts, $600-$1,200 labor). While the supercharger is off, also replace the PCV valve and perform carbon cleaning. For valve cover gasket leaks (separate issue), budget $400-$800 parts and labor. Monitor oil level weekly if leaks are present.</x:v>
-      </x:c>
-      <x:c r="F61" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G61" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" ht="1122" hidden="0" customHeight="1">
-      <x:c r="A62" s="40" t="n">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B62" s="9" t="str">
-        <x:v>audi-sq5-water-pump-2018</x:v>
-      </x:c>
-      <x:c r="C62" s="9" t="str">
-        <x:v>2018-2024 | Audi | SQ5 | 3.0T</x:v>
-      </x:c>
-      <x:c r="D62" s="9" t="str">
-        <x:v>Mechanical Coolant-Pump Leak with Possible N649 Vacuum-System Contamination</x:v>
-      </x:c>
-      <x:c r="E62" s="9" t="str">
-        <x:v>Confirm the complaint and exact vehicle criteria first. Inspect the vacuum line and N649 for coolant, then clean and dry suspected leakage, fill the cooling system correctly, inspect at idle and around 2,500 rpm, and pressure-test according to Audi workshop information. If no leak is reproduced, observe the vehicle without replacing parts. If the pump leak is confirmed, replace the failed component and document it. If fresh coolant has entered the vacuum system, inspect the remaining Audi checkpoints and replace only contaminated components; if the downstream checkpoints are clean, replace N649 and clean the line between the pump and N649 as directed by TSB 2070349/5.</x:v>
-      </x:c>
-      <x:c r="F62" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G62" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" ht="673.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A63" s="40" t="n">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B63" s="9" t="str">
-        <x:v>audi-sq7-air-susp-strut-2020</x:v>
-      </x:c>
-      <x:c r="C63" s="9" t="str">
-        <x:v>2020-2025 | Audi | SQ7 | 4.0T</x:v>
-      </x:c>
-      <x:c r="D63" s="9" t="str">
-        <x:v>2020-2025 SQ7 Air-Suspension C1260F0/U112100 Communication Fault - Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E63" s="9" t="str">
-        <x:v>Inspect the wiring and connector contacts between J775 and J1135 first. If no wiring fault is found, clear a first passive or sporadic fault and release the vehicle. Replace J1135 for an active or static fault, or when the same passive or sporadic fault returns a second time, following Audi workshop information and VIN-specific ETKA data. Do not replace an air spring, strut or compressor assembly solely from the warning.</x:v>
-      </x:c>
-      <x:c r="F63" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G63" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" ht="1122" hidden="0" customHeight="1">
-      <x:c r="A64" s="40" t="n">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="B64" s="9" t="str">
-        <x:v>audi-sq7-air-suspension-2020</x:v>
-      </x:c>
-      <x:c r="C64" s="9" t="str">
-        <x:v>2020-2024 | Audi | SQ7 | Premium Plus, Prestige | 4.0T</x:v>
-      </x:c>
-      <x:c r="D64" s="9" t="str">
-        <x:v>Adaptive Air Suspension Compressor and Air Spring Failures</x:v>
-      </x:c>
-      <x:c r="E64" s="9" t="str">
-        <x:v>Diagnose specific failed component: air springs leak most commonly, followed by compressor burnout, valve block faults, and height sensor failures. Air spring replacement ($800-$1,500 per corner at independent shop). Compressor replacement ($1,200-$2,500 installed). Valve block: $500-$1,000. Height sensor: $200-$400. Check for air leaks first using soapy water spray before replacing the compressor - a $200 air spring seal may be causing a $2,000 compressor to overwork and fail. Aftermarket solutions from Arnott offer cost savings. Converting to conventional springs ($1,500-$2,500) eliminates future air suspension costs but sacrifices ride height adjustment.</x:v>
-      </x:c>
-      <x:c r="F64" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G64" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A65" s="40" t="n">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="B65" s="9" t="str">
-        <x:v>audi-sq7-mmi-mib3-freeze-2020</x:v>
-      </x:c>
-      <x:c r="C65" s="9" t="str">
-        <x:v>2020-2026 | Audi | SQ7</x:v>
-      </x:c>
-      <x:c r="D65" s="9" t="str">
-        <x:v>2020-2026 Audi SQ7 Rearview Camera Software Recall 25V900 / 90TV</x:v>
-      </x:c>
-      <x:c r="E65" s="9" t="str">
-        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install the more robust driver-assistance software update free of charge. Until repaired, use extra caution when reversing and do not treat a restart, bus sleep or temporary image recovery as completion of the recall.</x:v>
-      </x:c>
-      <x:c r="F65" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G65" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" ht="990" hidden="0" customHeight="1">
-      <x:c r="A66" s="40" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B66" s="9" t="str">
-        <x:v>audi-sq7-valve-cover-oil-leak-2020</x:v>
-      </x:c>
-      <x:c r="C66" s="9" t="str">
-        <x:v>2020-2024 | Audi | SQ7 | 4.0T</x:v>
-      </x:c>
-      <x:c r="D66" s="9" t="str">
-        <x:v>2020-2024 SQ7 4.0L High Oil Consumption and Piston-Ring Diagnosis - TSB 2071114/5</x:v>
-      </x:c>
-      <x:c r="E66" s="9" t="str">
-        <x:v>First inspect for visible engine-oil traces or leaks. Have an Audi dealer perform the authorized ODIS oil-consumption measurement, preserve and upload both test logs, and document the requested driving-profile data. Internal-engine repair is justified only when measured consumption exceeds the applicable limit and no other cause is found. If every TSB gate is met, follow Audi's VIN-, engine-code- and power-class-specific procedure for replacement of all eight pistons and piston rings, using current ETKA and ELSA information. Do not diagnose valve-cover gaskets or turbocharger seals from oil consumption alone.</x:v>
-      </x:c>
-      <x:c r="F66" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G66" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" ht="686.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A67" s="40" t="n">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B67" s="9" t="str">
-        <x:v>audi-sq8-air-susp-compressor-2020</x:v>
-      </x:c>
-      <x:c r="C67" s="9" t="str">
-        <x:v>2020-2025 | Audi | SQ8</x:v>
-      </x:c>
-      <x:c r="D67" s="9" t="str">
-        <x:v>2020-2025 SQ8 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
-      </x:c>
-      <x:c r="E67" s="9" t="str">
-        <x:v>Inspect the wiring and connector contacts between J775 and J1135 before replacing a component. For a first passive or sporadic occurrence, clear the fault and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after wiring inspection, Audi directs replacement of J1135 under current repair and parts information. Do not buy struts, springs or a compressor solely from this warning.</x:v>
-      </x:c>
-      <x:c r="F67" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G67" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" ht="831.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A68" s="40" t="n">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="B68" s="9" t="str">
-        <x:v>audi-sq8-air-suspension-2020</x:v>
-      </x:c>
-      <x:c r="C68" s="9" t="str">
-        <x:v>2020-2024 | Audi | SQ8 | Premium Plus, Prestige | 4.0T</x:v>
-      </x:c>
-      <x:c r="D68" s="9" t="str">
-        <x:v>Adaptive Air Suspension Compressor and Air Spring Failures</x:v>
-      </x:c>
-      <x:c r="E68" s="9" t="str">
-        <x:v>Same diagnostic and repair approach as SQ7 (shared 4M platform). Isolate the failed component: air springs ($800-$1,500 per corner), compressor ($1,200-$2,500), valve block ($500-$1,000), or height sensor ($200-$400). Always check for air leaks before replacing the compressor. Aftermarket air suspension components from Arnott/Strutmasters offer 40-50% savings over OEM. Annual inspection of air springs for cracking recommended, especially in hot climates where UV and heat accelerate rubber degradation.</x:v>
-      </x:c>
-      <x:c r="F68" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G68" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" ht="448.79998779296875" hidden="0" customHeight="1">
-      <x:c r="A69" s="40" t="n">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="B69" s="9" t="str">
-        <x:v>audi-sq8-airbag-mount-2023</x:v>
-      </x:c>
-      <x:c r="C69" s="9" t="str">
-        <x:v>2023-2024 | Audi | SQ8 | 4.0T V8</x:v>
-      </x:c>
-      <x:c r="D69" s="9" t="str">
-        <x:v>2023-2024 SQ8 Driver-Seat Side-Airbag Mount Recall 69GA (23V868)</x:v>
-      </x:c>
-      <x:c r="E69" s="9" t="str">
-        <x:v>Check the VIN for open Audi recall 69GA and have an authorized dealer inspect the driver-seat side-airbag installation. If needed, the dealer will reinstall the airbag correctly; the recall filing says no parts are replaced. A clock spring or generic airbag part is not the recall remedy.</x:v>
-      </x:c>
-      <x:c r="F69" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G69" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" ht="580.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A70" s="40" t="n">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="B70" s="9" t="str">
-        <x:v>audi-sq8-mmi-mib3-freeze-2020</x:v>
-      </x:c>
-      <x:c r="C70" s="9" t="str">
-        <x:v>2020-2026 | Audi | SQ8 | 4.0T V8</x:v>
-      </x:c>
-      <x:c r="D70" s="9" t="str">
-        <x:v>2020-2026 SQ8 Rearview Camera Software Recall 90TV (25V900)</x:v>
-      </x:c>
-      <x:c r="E70" s="9" t="str">
-        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install more robust driver-assistance software free of charge. Until repaired, use extra caution when reversing and do not treat a restart, bus sleep or temporary image recovery as completion of the recall. A generic scan tool or head-unit replacement is not the recall remedy.</x:v>
-      </x:c>
-      <x:c r="F70" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G70" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" ht="567.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A71" s="40" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="B71" s="9" t="str">
-        <x:v>audi-sq8-turbo-coolant-2020</x:v>
-      </x:c>
-      <x:c r="C71" s="9" t="str">
-        <x:v>2020-2021 | Audi | SQ8 | 4.0T V8</x:v>
-      </x:c>
-      <x:c r="D71" s="9" t="str">
-        <x:v>2020-Early 2021 SQ8 Red Coolant Warning - Check G407 per TSB 2062951/4</x:v>
-      </x:c>
-      <x:c r="E71" s="9" t="str">
-        <x:v>Have the vehicle checked with Audi Guided Fault Finding and inspect G407 and its O-ring. Replace G407 only if the O-ring is damaged or pinched and the diagnosis matches the bulletin; follow the related Audi diagnostic path if additional listed faults are stored. Do not replace turbo coolant hoses, pumps or other cooling parts from this card alone.</x:v>
-      </x:c>
-      <x:c r="F71" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G71" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" ht="250.8000030517578" hidden="0" customHeight="1">
-      <x:c r="A72" s="40" t="n">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="B72" s="9" t="str">
-        <x:v>audi-tt-absesp-control-module-failure-2000</x:v>
-      </x:c>
-      <x:c r="C72" s="9" t="str">
-        <x:v>2000-2001 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D72" s="9" t="str">
-        <x:v>Driver Airbag Inflator May Deploy Improperly (Recall 21V470 / 69CJ)</x:v>
-      </x:c>
-      <x:c r="E72" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the driver frontal-airbag inflator with an alternative inflator free of charge under campaign 69CJ.</x:v>
-      </x:c>
-      <x:c r="F72" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G72" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" ht="277.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A73" s="40" t="n">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B73" s="9" t="str">
-        <x:v>audi-tt-cam-follower-2008</x:v>
-      </x:c>
-      <x:c r="C73" s="9" t="str">
-        <x:v>2000-2000 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D73" s="9" t="str">
-        <x:v>Fuel-Line Assembly Can Leak (Recall 99V222)</x:v>
-      </x:c>
-      <x:c r="E73" s="9" t="str">
-        <x:v>Check VIN eligibility and campaign completion. Audi dealers replace the fuel-line assembly free of charge under recall 99V222. Stop driving if fuel odor or leakage is present.</x:v>
-      </x:c>
-      <x:c r="F73" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G73" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" ht="198" hidden="0" customHeight="1">
-      <x:c r="A74" s="40" t="n">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B74" s="9" t="str">
-        <x:v>audi-tt-coil-pack-failure-and-2000</x:v>
-      </x:c>
-      <x:c r="C74" s="9" t="str">
-        <x:v>2000-2001 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D74" s="9" t="str">
-        <x:v>Rear Track-Control Arm Corrosion Can Restrict Movement (Recall 01V325)</x:v>
-      </x:c>
-      <x:c r="E74" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the rear track-control arms free of charge under recall 01V325.</x:v>
-      </x:c>
-      <x:c r="F74" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G74" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" ht="264" hidden="0" customHeight="1">
-      <x:c r="A75" s="40" t="n">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="B75" s="9" t="str">
-        <x:v>audi-tt-dsg-mechatronic-2008</x:v>
-      </x:c>
-      <x:c r="C75" s="9" t="str">
-        <x:v>2004-2004 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D75" s="9" t="str">
-        <x:v>Direct-Shift Gearbox Clutch Weld Can Lose Drive Torque (Recall 04V007)</x:v>
-      </x:c>
-      <x:c r="E75" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers replace the affected clutch free of charge under recall 04V007. If drive torque is lost, move out of traffic safely and arrange recovery.</x:v>
-      </x:c>
-      <x:c r="F75" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G75" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" ht="356.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A76" s="40" t="n">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B76" s="9" t="str">
-        <x:v>audi-tt-dsg-transmission-2008</x:v>
-      </x:c>
-      <x:c r="C76" s="9" t="str">
-        <x:v>2009-2009 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D76" s="9" t="str">
-        <x:v>DSG Temperature-Sensor Wiring Can Trigger an Abrupt Shift to Neutral (Recall 09V333)</x:v>
-      </x:c>
-      <x:c r="E76" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers reprogram the transmission control module with updated software free of charge under recall 09V333. If the gear indicator flashes or neutral engages unexpectedly, stop safely.</x:v>
-      </x:c>
-      <x:c r="F76" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G76" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" ht="303.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A77" s="40" t="n">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="B77" s="9" t="str">
-        <x:v>audi-tt-front-control-arm-bushings-2000</x:v>
-      </x:c>
-      <x:c r="C77" s="9" t="str">
-        <x:v>2000-2000 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D77" s="9" t="str">
-        <x:v>High-Speed Directional-Stability Remedy (Recall 99V300)</x:v>
-      </x:c>
-      <x:c r="E77" s="9" t="str">
-        <x:v>Verify campaign completion with Audi. The factory remedy installs revised stabilizers, front control arms, firmer shock absorbers, and a rear spoiler as specified for the drivetrain configuration.</x:v>
-      </x:c>
-      <x:c r="F77" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G77" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" ht="237.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A78" s="40" t="n">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B78" s="9" t="str">
-        <x:v>audi-tt-haldex-awd-coupling-pumpcontroller-2000</x:v>
-      </x:c>
-      <x:c r="C78" s="9" t="str">
-        <x:v>2008-2010 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D78" s="9" t="str">
-        <x:v>Fuel-Tank Ventilation Valve Can Allow Fuel Leakage (Recall 09V377)</x:v>
-      </x:c>
-      <x:c r="E78" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel-tank ventilation valve with the improved valve free of charge under recall 09V377.</x:v>
-      </x:c>
-      <x:c r="F78" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G78" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" ht="184.8000030517578" hidden="0" customHeight="1">
-      <x:c r="A79" s="40" t="n">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="B79" s="9" t="str">
-        <x:v>audi-tt-high-speed-stability-recall-for-2000</x:v>
-      </x:c>
-      <x:c r="C79" s="9" t="str">
-        <x:v>2016-2019 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D79" s="9" t="str">
-        <x:v>Fuel Tank Can Be Damaged by Heat-Shield Bracket in a Crash (Recall 20V076 / 20BX)</x:v>
-      </x:c>
-      <x:c r="E79" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers install a protective cap on the heat-shield bracket free of charge under campaign 20BX.</x:v>
-      </x:c>
-      <x:c r="F79" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G79" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" ht="237.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A80" s="40" t="n">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B80" s="9" t="str">
-        <x:v>audi-tt-instrument-cluster-pixel-failure-2000</x:v>
-      </x:c>
-      <x:c r="C80" s="9" t="str">
-        <x:v>2016-2016 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D80" s="9" t="str">
-        <x:v>Front-Passenger Airbag Module May Explode or Deploy Improperly (Recall 22V543 / 69DY)</x:v>
-      </x:c>
-      <x:c r="E80" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the front-passenger airbag module free of charge under campaign 69DY/61C1.</x:v>
-      </x:c>
-      <x:c r="F80" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G80" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" ht="224.39999389648438" hidden="0" customHeight="1">
-      <x:c r="A81" s="40" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="B81" s="9" t="str">
-        <x:v>audi-tt-magnetic-ride-2008</x:v>
-      </x:c>
-      <x:c r="C81" s="9" t="str">
-        <x:v>2023-2023 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D81" s="9" t="str">
-        <x:v>Passenger-Seat Occupant Detection Connection Can Disable Airbag (Recall 24V251 / 69GU)</x:v>
-      </x:c>
-      <x:c r="E81" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers replace the passenger-seat occupant-detection control module free of charge under campaign 69GU.</x:v>
-      </x:c>
-      <x:c r="F81" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G81" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" ht="726" hidden="0" customHeight="1">
-      <x:c r="A82" s="40" t="n">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B82" s="9" t="str">
-        <x:v>audi-tt-tail-light-corrosion-2008</x:v>
-      </x:c>
-      <x:c r="C82" s="9" t="str">
-        <x:v>2008-2015 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D82" s="9" t="str">
-        <x:v>Tail Light Electrical Connector Corrosion (Mk2)</x:v>
-      </x:c>
-      <x:c r="E82" s="9" t="str">
-        <x:v>Remove tail light assembly, inspect electrical connector for green corrosion. CLEAN connector with electrical contact cleaner and wire brush ($20 DIY). Apply dielectric grease to prevent future corrosion ($10). If connector is severely corroded: Replace pigtail connector ($50-$100 parts). Improve tail light seal with silicone sealant around housing ($15). This is a DIY-friendly repair taking 1-2 hours. If paying shop, costs $150-$300. Address early before corrosion causes shorts.</x:v>
-      </x:c>
-      <x:c r="F82" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G82" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" ht="171.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A83" s="40" t="n">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B83" s="9" t="str">
-        <x:v>audi-tt-water-pump-2008</x:v>
-      </x:c>
-      <x:c r="C83" s="9" t="str">
-        <x:v>2008-2008 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D83" s="9" t="str">
-        <x:v>C-Pillar Trim Cover Can Detach During Belt-Tensioner Deployment (Recall 08V064)</x:v>
-      </x:c>
-      <x:c r="E83" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers install improved C-pillar trim clips free of charge under recall 08V064.</x:v>
-      </x:c>
-      <x:c r="F83" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G83" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" ht="1161.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A84" s="40" t="n">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="B84" s="9" t="str">
-        <x:v>audi-tts-cam-follower-hpfp-2009</x:v>
-      </x:c>
-      <x:c r="C84" s="9" t="str">
-        <x:v>2009-2015 | Audi | TTS | TTS | EA888</x:v>
-      </x:c>
-      <x:c r="D84" s="9" t="str">
-        <x:v>HPFP Cam Follower Wear and High-Pressure Fuel Pump Failure (Mk2)</x:v>
-      </x:c>
-      <x:c r="E84" s="9" t="str">
-        <x:v>INSPECTION (every 20,000 miles): Remove HPFP (3 bolts) and inspect cam follower surface. If the hardened coating is wearing through (visible copper/brass color), replace follower immediately ($30-$50 part, 30-60 minutes labor). CRITICAL: Ensure cam lobe is at LOW point before reinstalling—if at peak, you'll compress the spring and can break the mounting bolts. If CAMSHAFT WORN (deep groove in lobe): Replace camshaft ($2,000-$4,000). If FUEL PUMP FAILED: Replace HPFP ($400-$800). PREVENTION: Inspect cam follower every 20,000 miles as routine maintenance. Add to every oil change checklist. Consider IE (Integrated Engineering) upgraded HPFP with roller follower to eliminate wear entirely.</x:v>
-      </x:c>
-      <x:c r="F84" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G84" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" ht="884.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A85" s="40" t="n">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="B85" s="9" t="str">
-        <x:v>audi-tts-carbon-buildup-2009</x:v>
-      </x:c>
-      <x:c r="C85" s="9" t="str">
-        <x:v>2016-2017 | Audi | TTS</x:v>
-      </x:c>
-      <x:c r="D85" s="9" t="str">
-        <x:v>2016-2017 TTS Cold-Start Misfire DTCs Without Felt Misfire - TSB 2051384/1</x:v>
-      </x:c>
-      <x:c r="E85" s="9" t="str">
-        <x:v>Confirm the exact cold-start timing, simultaneous-cylinder DTC pattern, absence of a felt misfire, CYFB engine and installed ECM software before using this bulletin. When applicable, an Audi-capable workshop updates ECM J623 from software part number 8S0906259C version 0001 to version 0004 or higher using SVM action 01A190, then clears the DTCs. A felt misfire, a different timing or RPM pattern, a different engine/software combination or a returning concern requires normal diagnosis rather than carbon cleaning by assumption.</x:v>
-      </x:c>
-      <x:c r="F85" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G85" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" ht="910.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A86" s="40" t="n">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B86" s="9" t="str">
-        <x:v>audi-tts-dsg-mechatronic-2009</x:v>
-      </x:c>
-      <x:c r="C86" s="9" t="str">
-        <x:v>2019-2023 | Audi | TTS</x:v>
-      </x:c>
-      <x:c r="D86" s="9" t="str">
-        <x:v>2019-2023 TTS Clutch K1 Overheat and Transmission DTC Diagnosis - TSB 2060560/3</x:v>
-      </x:c>
-      <x:c r="E86" s="9" t="str">
-        <x:v>Have an Audi-capable workshop check whether TSB 2050723 applies first. If it does not resolve or control the concern, inspect the clutch-K1 maximum-temperature value and document a transmission-fluid sample. Replace the dual clutch, transmission fluid and filter only when the approximately 400 °C K1 value and burnt black or very dark fluid are both present. If those findings are absent, this bulletin does not apply and Audi directs the workshop to continue diagnosis through TAC. Any clutch repair kit must be selected by VIN and production date.</x:v>
-      </x:c>
-      <x:c r="F86" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G86" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" ht="858" hidden="0" customHeight="1">
-      <x:c r="A87" s="40" t="n">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="B87" s="9" t="str">
-        <x:v>audi-tts-magnetic-ride-2009</x:v>
-      </x:c>
-      <x:c r="C87" s="9" t="str">
-        <x:v>2016-2016 | Audi | TTS</x:v>
-      </x:c>
-      <x:c r="D87" s="9" t="str">
-        <x:v>2016 TTS Magnetic-Ride Rear Shock-Mount Rumble - TSB 2042539/4</x:v>
-      </x:c>
-      <x:c r="E87" s="9" t="str">
-        <x:v>First reproduce the noise, verify that it comes from the rear shock mounts and confirm that the vehicle was originally equipped with mount 8S0 513 353. Only when those gates are satisfied, remove both rear shock assemblies and replace both mounts with 8V0 513 353 according to Audi workshop instructions, adapt the suspension control position and test drive to confirm the repair. If the installed mount does not match, continue Audi diagnosis. Do not replace magnetic dampers or convert the vehicle to coilovers from this noise alone.</x:v>
-      </x:c>
-      <x:c r="F87" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G87" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" ht="1016.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A88" s="40" t="n">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B88" s="9" t="str">
-        <x:v>audi-tts-timing-chain-tensioner-2009</x:v>
-      </x:c>
-      <x:c r="C88" s="9" t="str">
-        <x:v>2009-2015 | Audi | TTS | TTS | EA888 Gen 1, EA888 Gen 2</x:v>
-      </x:c>
-      <x:c r="D88" s="9" t="str">
-        <x:v>Timing Chain Tensioner Failure (EA888 Gen 1/2 - Mk2 TTS)</x:v>
-      </x:c>
-      <x:c r="E88" s="9" t="str">
-        <x:v>PREVENTIVE REPLACEMENT: Replace timing chain, tensioner, guides, and sprockets at 80,000-100,000 miles BEFORE symptoms appear ($2,000-$4,000). This is the MOST important preventive maintenance on the Mk2 TTS. IF RATTLING: Do NOT delay—the chain can jump at any startup. Schedule repair immediately. Use ONLY the latest OEM revised tensioner (06K109467K). IF CHAIN JUMPED: Engine likely destroyed—compression test all cylinders. Rebuild ($5,000-$8,000) or replacement engine ($6,000-$12,000). PREVENTION: Change oil every 5,000 miles with high-quality synthetic. Low oil level accelerates tensioner wear.</x:v>
-      </x:c>
-      <x:c r="F88" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G88" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" ht="976.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A89" s="40" t="n">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="B89" s="9" t="str">
-        <x:v>audi-tts-water-pump-2009</x:v>
-      </x:c>
-      <x:c r="C89" s="9" t="str">
-        <x:v>2012-2023 | Audi | TTS</x:v>
-      </x:c>
-      <x:c r="D89" s="9" t="str">
-        <x:v>2012 / 2020-2023 TTS Coolant-Pump Update and Leak Diagnosis</x:v>
-      </x:c>
-      <x:c r="E89" s="9" t="str">
-        <x:v>For a 2012 TTS, ask an Audi dealer to check the VIN and current campaign/action history for Update 19J2; the published update replaced the pump only when its exact criteria were met and does not promise current warranty coverage. For a 2020-2023 2.0L TTS, first exclude a low level caused by incomplete bleeding or an earlier repair, document and clean the suspected leak, refill to maximum and recheck after driving. Continue observation when no leak returns; replace only the component proven to leak when coolant reappears. Do not select a pump or thermostat assembly before VIN-, engine- and leak-specific diagnosis.</x:v>
-      </x:c>
-      <x:c r="F89" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G89" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" ht="198" hidden="0" customHeight="1">
-      <x:c r="A90" s="42" t="n">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="B90" s="43" t="str">
-        <x:v>audi-tts-waterpump-housing-2009</x:v>
-      </x:c>
-      <x:c r="C90" s="43" t="str">
-        <x:v>2009-2024 | Audi | TTS | EA888</x:v>
-      </x:c>
-      <x:c r="D90" s="43" t="str">
-        <x:v>Water Pump and Thermostat Housing Failure</x:v>
-      </x:c>
-      <x:c r="E90" s="43" t="str">
-        <x:v>Replace water pump, thermostat, and housing as a complete assembly. Use metal-impeller aftermarket pump if available.</x:v>
-      </x:c>
-      <x:c r="F90" s="43" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G90" s="44" t="str">
+      <x:c r="G40" s="44" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>

--- a/outputs/audi-repair-first-review/Audi-repair-first-fitment-review.xlsx
+++ b/outputs/audi-repair-first-review/Audi-repair-first-fitment-review.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Re236912b51844fae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audi Review" sheetId="2" r:id="Re5774462ba8747fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Queue" sheetId="3" r:id="Rf8f873359b384a8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" r:id="R5e7c561b84ab4128"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R8d564973ed8a4154"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audi Review" sheetId="2" r:id="R8d81e17349944e77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Queue" sheetId="3" r:id="R28856ca671bf4e5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" r:id="R5964678d3fbb4ac3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -90,7 +90,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="9">
+  <x:borders count="12">
     <x:border/>
     <x:border>
       <x:left/>
@@ -120,11 +120,25 @@
       <x:right/>
       <x:bottom/>
     </x:border>
+    <x:border>
+      <x:left/>
+      <x:top/>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:top/>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="50">
+  <x:cellXfs count="53">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -215,6 +229,15 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
@@ -484,7 +507,7 @@
         <x:v>Reviewed in this batch</x:v>
       </x:c>
       <x:c r="B5" s="13" t="n">
-        <x:v>350</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="C5" s="11"/>
       <x:c r="D5" s="11"/>
@@ -498,7 +521,7 @@
         <x:v>Remaining queue</x:v>
       </x:c>
       <x:c r="B6" s="13" t="n">
-        <x:v>39</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C6" s="11"/>
       <x:c r="D6" s="11"/>
@@ -512,7 +535,7 @@
         <x:v>Issues with destinations</x:v>
       </x:c>
       <x:c r="B7" s="13" t="n">
-        <x:v>344</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="C7" s="11"/>
       <x:c r="D7" s="11"/>
@@ -526,7 +549,7 @@
         <x:v>Destination entries</x:v>
       </x:c>
       <x:c r="B8" s="13" t="n">
-        <x:v>603</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="C8" s="11"/>
       <x:c r="D8" s="11"/>
@@ -540,7 +563,7 @@
         <x:v>Distinct URLs</x:v>
       </x:c>
       <x:c r="B9" s="13" t="n">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C9" s="11"/>
       <x:c r="D9" s="11"/>
@@ -21563,46 +21586,2380 @@
       <x:c r="N609" s="41" t="str"/>
     </x:row>
     <x:row r="610" ht="475.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A610" s="42" t="n">
+      <x:c r="A610" s="40" t="n">
         <x:v>350</x:v>
       </x:c>
-      <x:c r="B610" s="43" t="str">
+      <x:c r="B610" s="9" t="str">
         <x:v>audi-sq2-ea888-2-0-tfsi-coolant-leak-from-water-pump-thermostat-housi</x:v>
       </x:c>
-      <x:c r="C610" s="43" t="str">
+      <x:c r="C610" s="9" t="str">
         <x:v>2019-2024 | Audi | SQ2 | 2.0 TFSI quattro | EA888 2.0 TFSI Gen3</x:v>
       </x:c>
-      <x:c r="D610" s="43" t="str">
+      <x:c r="D610" s="9" t="str">
         <x:v>EA888 2.0 TFSI coolant leak from water pump / thermostat housing</x:v>
       </x:c>
-      <x:c r="E610" s="43" t="str">
+      <x:c r="E610" s="9" t="str">
         <x:v>Replace the failed water pump / thermostat housing assembly, ideally with the latest revised, more heat-resistant unit; many shops fit an upgraded repair kit and a new gasket. Catch it early by watching for slowly dropping coolant level and a faint sweet smell. Combine with a coolant flush and refill.</x:v>
       </x:c>
-      <x:c r="F610" s="43" t="str">
+      <x:c r="F610" s="9" t="str">
         <x:v>Non-US-market engine/VIN pressure test; exact pump/thermostat/housing leak source and revision; gasket/coolant/bleed</x:v>
       </x:c>
-      <x:c r="G610" s="43" t="str">
+      <x:c r="G610" s="9" t="str">
         <x:v>NON-US-MARKET / LEAK-SOURCE GATE</x:v>
       </x:c>
-      <x:c r="H610" s="43" t="str">
+      <x:c r="H610" s="9" t="str">
         <x:v>Audi UK service and maintenance</x:v>
       </x:c>
-      <x:c r="I610" s="43" t="str">
+      <x:c r="I610" s="9" t="str">
         <x:v>https://www.audi.co.uk/en/owners/service-and-maintenance/</x:v>
       </x:c>
-      <x:c r="J610" s="43" t="str">
+      <x:c r="J610" s="9" t="str">
         <x:v>2019-2024 SQ2 local-market EA888 coolant diagnosis</x:v>
       </x:c>
-      <x:c r="K610" s="43" t="str">
+      <x:c r="K610" s="9" t="str">
         <x:v>manufacturer-market service</x:v>
       </x:c>
-      <x:c r="L610" s="43" t="str"/>
-      <x:c r="M610" s="43" t="str">
+      <x:c r="L610" s="9" t="str"/>
+      <x:c r="M610" s="9" t="str">
         <x:v>SQ2 is non-US and exact assembly/revision requires market VIN.</x:v>
       </x:c>
-      <x:c r="N610" s="44" t="str">
+      <x:c r="N610" s="41" t="str">
         <x:v>No US affiliate or generic upgraded kit; do not bundle flush automatically.</x:v>
       </x:c>
+    </x:row>
+    <x:row r="611" ht="396" hidden="0" customHeight="1">
+      <x:c r="A611" s="40" t="n">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="B611" s="9" t="str">
+        <x:v>audi-sq2-electro-mechanical-parking-brake-brake-pedal-weld-recalls</x:v>
+      </x:c>
+      <x:c r="C611" s="9" t="str">
+        <x:v>2019-2020 | Audi | SQ2</x:v>
+      </x:c>
+      <x:c r="D611" s="9" t="str">
+        <x:v>Electro-mechanical parking brake and brake-pedal weld recalls (early build)</x:v>
+      </x:c>
+      <x:c r="E611" s="9" t="str">
+        <x:v>These are recall items — have the VIN checked against the Audi/DVSA recall database and any open campaign rectified free of charge at a dealer. Report any abnormal parking-brake behaviour or a soft/abnormal brake pedal immediately.</x:v>
+      </x:c>
+      <x:c r="F611" s="9" t="str">
+        <x:v>Local-market VIN recall check; dealer parking-brake and brake-pedal campaign remedy; urgent inspection for abnormal operation</x:v>
+      </x:c>
+      <x:c r="G611" s="9" t="str">
+        <x:v>NON-US RECALL ROUTE</x:v>
+      </x:c>
+      <x:c r="H611" s="9" t="str">
+        <x:v>Audi UK service and maintenance</x:v>
+      </x:c>
+      <x:c r="I611" s="9" t="str">
+        <x:v>https://www.audi.co.uk/en/owners/service-and-maintenance/</x:v>
+      </x:c>
+      <x:c r="J611" s="9" t="str">
+        <x:v>2019-2020 SQ2 local-market recall/VIN check</x:v>
+      </x:c>
+      <x:c r="K611" s="9" t="str">
+        <x:v>manufacturer-market campaign service</x:v>
+      </x:c>
+      <x:c r="L611" s="9" t="str"/>
+      <x:c r="M611" s="9" t="str">
+        <x:v>Safety campaign remedy is dealer-controlled and market/VIN specific.</x:v>
+      </x:c>
+      <x:c r="N611" s="41" t="str">
+        <x:v>No parking-brake module or pedal product link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="612" ht="475.20001220703125" hidden="0" customHeight="1">
+      <x:c r="A612" s="40" t="n">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="B612" s="9" t="str">
+        <x:v>audi-sq2-internal-fuse-box-wiring-harness-can-work-loose-causing-sudd</x:v>
+      </x:c>
+      <x:c r="C612" s="9" t="str">
+        <x:v>2022-2023 | Audi | SQ2 | 2.0 TFSI</x:v>
+      </x:c>
+      <x:c r="D612" s="9" t="str">
+        <x:v>2022-2023 Audi SQ2 Interior Fuse-Carrier Recall GAI-3692</x:v>
+      </x:c>
+      <x:c r="E612" s="9" t="str">
+        <x:v>Check the VIN and open-campaign status with an authorised Audi dealer in the vehicle’s market. The campaign remedy is dealer inspection and correction of the fuse-carrier power connection. Do not replace a fuse box or wiring harness solely from a warning lamp or this model-year summary.</x:v>
+      </x:c>
+      <x:c r="F612" s="9" t="str">
+        <x:v>Local-market VIN/GAI-3692 check; dealer fuse-carrier inspection and campaign correction</x:v>
+      </x:c>
+      <x:c r="G612" s="9" t="str">
+        <x:v>NON-US RECALL ROUTE</x:v>
+      </x:c>
+      <x:c r="H612" s="9" t="str">
+        <x:v>Audi UK service and maintenance</x:v>
+      </x:c>
+      <x:c r="I612" s="9" t="str">
+        <x:v>https://www.audi.co.uk/en/owners/service-and-maintenance/</x:v>
+      </x:c>
+      <x:c r="J612" s="9" t="str">
+        <x:v>2022-2023 SQ2 local-market fuse-carrier campaign</x:v>
+      </x:c>
+      <x:c r="K612" s="9" t="str">
+        <x:v>manufacturer-market campaign service</x:v>
+      </x:c>
+      <x:c r="L612" s="9" t="str"/>
+      <x:c r="M612" s="9" t="str">
+        <x:v>The campaign defines the inspection/correction.</x:v>
+      </x:c>
+      <x:c r="N612" s="41" t="str">
+        <x:v>No fuse box or harness product link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="613" ht="488.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A613" s="40" t="n">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="B613" s="9" t="str">
+        <x:v>audi-sq2-mmi-infotainment-freezing-rebooting-lost-settings</x:v>
+      </x:c>
+      <x:c r="C613" s="9" t="str">
+        <x:v>2019-2024 | Audi | SQ2</x:v>
+      </x:c>
+      <x:c r="D613" s="9" t="str">
+        <x:v>MMI infotainment freezing, rebooting and lost settings</x:v>
+      </x:c>
+      <x:c r="E613" s="9" t="str">
+        <x:v>A forced MMI restart (press and hold the on/off or volume control ~10 seconds until it reboots) clears many transient faults. Persistent issues are usually resolved by a dealer software/firmware update; check for any applicable MMI update campaigns. Only in rare cases is the MMI head unit itself replaced.</x:v>
+      </x:c>
+      <x:c r="F613" s="9" t="str">
+        <x:v>Safe restart; local-market software/version diagnosis; head unit only after hardware failure is proven</x:v>
+      </x:c>
+      <x:c r="G613" s="9" t="str">
+        <x:v>NON-US SOFTWARE-FIRST SERVICE</x:v>
+      </x:c>
+      <x:c r="H613" s="9" t="str">
+        <x:v>Audi UK service and maintenance</x:v>
+      </x:c>
+      <x:c r="I613" s="9" t="str">
+        <x:v>https://www.audi.co.uk/en/owners/service-and-maintenance/</x:v>
+      </x:c>
+      <x:c r="J613" s="9" t="str">
+        <x:v>2019-2024 SQ2 MMI software and hardware diagnosis</x:v>
+      </x:c>
+      <x:c r="K613" s="9" t="str">
+        <x:v>manufacturer-market service</x:v>
+      </x:c>
+      <x:c r="L613" s="9" t="str"/>
+      <x:c r="M613" s="9" t="str">
+        <x:v>Rebooting does not establish a failed head unit.</x:v>
+      </x:c>
+      <x:c r="N613" s="41" t="str">
+        <x:v>No generic module or scanner link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="614" ht="488.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A614" s="40" t="n">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="B614" s="9" t="str">
+        <x:v>audi-sq2-pcv-crankcase-ventilation-valve-diaphragm-failure-causing-ro</x:v>
+      </x:c>
+      <x:c r="C614" s="9" t="str">
+        <x:v>2019-2024 | Audi | SQ2 | EA888 2.0 TFSI Gen3</x:v>
+      </x:c>
+      <x:c r="D614" s="9" t="str">
+        <x:v>PCV / crankcase ventilation valve diaphragm failure causing rough idle and lean-running codes</x:v>
+      </x:c>
+      <x:c r="E614" s="9" t="str">
+        <x:v>Replace the PCV valve (or the valve-cover assembly that integrates it) with the latest revised part; some owners fit a catch-can to reduce recurrence. A quick field test — briefly covering the bleeder hole on the cap to see if idle stabilises or whistling stops — helps confirm before replacement.</x:v>
+      </x:c>
+      <x:c r="F614" s="9" t="str">
+        <x:v>Measured crankcase vacuum and intake/smoke diagnosis; exact engine/VIN PCV valve or valve-cover assembly only after proof</x:v>
+      </x:c>
+      <x:c r="G614" s="9" t="str">
+        <x:v>NON-US ENGINE / PCV DIAGNOSIS GATE</x:v>
+      </x:c>
+      <x:c r="H614" s="9" t="str">
+        <x:v>Audi UK service and maintenance</x:v>
+      </x:c>
+      <x:c r="I614" s="9" t="str">
+        <x:v>https://www.audi.co.uk/en/owners/service-and-maintenance/</x:v>
+      </x:c>
+      <x:c r="J614" s="9" t="str">
+        <x:v>2019-2024 SQ2 engine-specific crankcase diagnosis</x:v>
+      </x:c>
+      <x:c r="K614" s="9" t="str">
+        <x:v>manufacturer-market service</x:v>
+      </x:c>
+      <x:c r="L614" s="9" t="str"/>
+      <x:c r="M614" s="9" t="str">
+        <x:v>Oil-cap feel alone cannot select a valve or complete cover.</x:v>
+      </x:c>
+      <x:c r="N614" s="41" t="str">
+        <x:v>No catch-can prevention claim or universal cover replacement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="615" ht="752.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A615" s="40" t="n">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="B615" s="9" t="str">
+        <x:v>audi-sq2-s-tronic-7-speed-wet-clutch-transmission-jerky-low-speed-shi</x:v>
+      </x:c>
+      <x:c r="C615" s="9" t="str">
+        <x:v>2019-2024 | Audi | SQ2 | 7-speed S tronic | DQ381 / 0GC 7-speed wet-clutch S tronic</x:v>
+      </x:c>
+      <x:c r="D615" s="9" t="str">
+        <x:v>S tronic (DQ381) 7-speed wet-clutch transmission: jerky low-speed shifts, hesitation and limp mode</x:v>
+      </x:c>
+      <x:c r="E615" s="9" t="str">
+        <x:v>First step is a proper DSG fluid-and-filter service (the wet-clutch unit needs periodic transmission oil changes — many owners do it around 40k miles even though intervals can be longer). Have the TCU scanned for stored codes; sensor or mechatronic valve replacement and re-coding/adaptation resolves many cases, while severe cases need a full mechatronic unit or clutch-pack replacement. Insist on a software/adaptation update at the dealer for driveability complaints.</x:v>
+      </x:c>
+      <x:c r="F615" s="9" t="str">
+        <x:v>Confirm DQ381/0GC code; faults/fluid condition; exact market service schedule; software/adaptation; mechatronic or clutch only by test</x:v>
+      </x:c>
+      <x:c r="G615" s="9" t="str">
+        <x:v>NON-US TRANSMISSION-CODE / COMPONENT GATE</x:v>
+      </x:c>
+      <x:c r="H615" s="9" t="str">
+        <x:v>Audi UK service and maintenance</x:v>
+      </x:c>
+      <x:c r="I615" s="9" t="str">
+        <x:v>https://www.audi.co.uk/en/owners/service-and-maintenance/</x:v>
+      </x:c>
+      <x:c r="J615" s="9" t="str">
+        <x:v>2019-2024 SQ2 transmission-code service and diagnosis</x:v>
+      </x:c>
+      <x:c r="K615" s="9" t="str">
+        <x:v>manufacturer-market service</x:v>
+      </x:c>
+      <x:c r="L615" s="9" t="str"/>
+      <x:c r="M615" s="9" t="str">
+        <x:v>Service, software, mechatronic and clutch are different branches.</x:v>
+      </x:c>
+      <x:c r="N615" s="41" t="str">
+        <x:v>No generic DSG kit or fixed interval without exact local manual.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="616" ht="541.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A616" s="40" t="n">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="B616" s="9" t="str">
+        <x:v>audi-sq5-air-suspension-2018</x:v>
+      </x:c>
+      <x:c r="C616" s="9" t="str">
+        <x:v>2018-2025 | Audi | SQ5</x:v>
+      </x:c>
+      <x:c r="D616" s="9" t="str">
+        <x:v>Air-Suspension Warning with C1260F0 or U112100 Communication Fault</x:v>
+      </x:c>
+      <x:c r="E616" s="9" t="str">
+        <x:v>Inspect the wiring and connector contacts between J775 and J1135 first. If no wiring fault is found, clear a first passive or sporadic fault and release the vehicle. Replace J1135 for an active or static fault, or when the same passive or sporadic fault returns a second time, following Audi workshop information and VIN-specific ETKA data.</x:v>
+      </x:c>
+      <x:c r="F616" s="9" t="str">
+        <x:v>J775-J1135 wiring/contact inspection; occurrence-state logic; J1135 only after active/static or repeated passive fault</x:v>
+      </x:c>
+      <x:c r="G616" s="9" t="str">
+        <x:v>WIRING-FIRST TSB / CONTROL-UNIT GATE</x:v>
+      </x:c>
+      <x:c r="H616" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I616" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J616" s="9" t="str">
+        <x:v>2018-2025 SQ5 J1135 guided diagnosis</x:v>
+      </x:c>
+      <x:c r="K616" s="9" t="str">
+        <x:v>manufacturer suspension service</x:v>
+      </x:c>
+      <x:c r="L616" s="9" t="str"/>
+      <x:c r="M616" s="9" t="str">
+        <x:v>The procedure does not establish a failed strut or compressor.</x:v>
+      </x:c>
+      <x:c r="N616" s="41" t="str">
+        <x:v>No air-suspension hardware link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="617" ht="924" hidden="0" customHeight="1">
+      <x:c r="A617" s="40" t="n">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="B617" s="9" t="str">
+        <x:v>audi-sq5-carbon-buildup-2014</x:v>
+      </x:c>
+      <x:c r="C617" s="9" t="str">
+        <x:v>2014-2025 | Audi | SQ5 | 3.0T Supercharged, 3.0T</x:v>
+      </x:c>
+      <x:c r="D617" s="9" t="str">
+        <x:v>Fuel-Quality or Deposit-Related Rough Running and Misfire Diagnosis</x:v>
+      </x:c>
+      <x:c r="E617" s="9" t="str">
+        <x:v>Confirm fuel quality, symptoms and stored DTCs before replacing or cleaning components. If contaminated gasoline is suspected, advise changing the fuel source; if low detergent quality is suspected, Audi recommends Top Tier detergent gasoline. Continue workshop diagnosis if symptoms persist. On 2018-2025 EA839 SQ5 models, do not recommend unapproved cleaners or additives; follow the owner manual and use only Audi-approved petrol additives. Do not prescribe routine walnut blasting, a catch can or chemical cleaning from this record.</x:v>
+      </x:c>
+      <x:c r="F617" s="9" t="str">
+        <x:v>Split supercharged/turbo engines; ignition/fuel/air diagnosis before deposit confirmation; use detergent-standard gasoline</x:v>
+      </x:c>
+      <x:c r="G617" s="9" t="str">
+        <x:v>ENGINE-GENERATION / DIAGNOSIS GATE</x:v>
+      </x:c>
+      <x:c r="H617" s="9" t="str">
+        <x:v>TOP TIER gasoline stations</x:v>
+      </x:c>
+      <x:c r="I617" s="9" t="str">
+        <x:v>https://www.toptiergas.com/gasoline-brands/</x:v>
+      </x:c>
+      <x:c r="J617" s="9" t="str">
+        <x:v>2014-2025 SQ5 fuel-quality maintenance</x:v>
+      </x:c>
+      <x:c r="K617" s="9" t="str">
+        <x:v>standards-based fuel locator</x:v>
+      </x:c>
+      <x:c r="L617" s="9" t="str"/>
+      <x:c r="M617" s="9" t="str">
+        <x:v>The range spans different engines and symptoms do not prove deposits.</x:v>
+      </x:c>
+      <x:c r="N617" s="41" t="str">
+        <x:v>No walnut blasting, additive or catch-can link before confirmation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="618" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A618" s="40" t="str"/>
+      <x:c r="B618" s="9" t="str"/>
+      <x:c r="C618" s="9" t="str"/>
+      <x:c r="D618" s="9" t="str"/>
+      <x:c r="E618" s="9" t="str"/>
+      <x:c r="F618" s="9" t="str"/>
+      <x:c r="G618" s="9" t="str"/>
+      <x:c r="H618" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I618" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J618" s="9" t="str">
+        <x:v>SQ5 engine-specific rough-running/deposit diagnosis</x:v>
+      </x:c>
+      <x:c r="K618" s="9" t="str">
+        <x:v>specialist intake service</x:v>
+      </x:c>
+      <x:c r="L618" s="9" t="str"/>
+      <x:c r="M618" s="9" t="str"/>
+      <x:c r="N618" s="41" t="str"/>
+    </x:row>
+    <x:row r="619" ht="765.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A619" s="40" t="n">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="B619" s="9" t="str">
+        <x:v>audi-sq5-pcv-valve-2014</x:v>
+      </x:c>
+      <x:c r="C619" s="9" t="str">
+        <x:v>2014-2017 | Audi | SQ5 | 3.0T Supercharged</x:v>
+      </x:c>
+      <x:c r="D619" s="9" t="str">
+        <x:v>P052E00 Crankcase-Breather Membrane or Elbow Fault</x:v>
+      </x:c>
+      <x:c r="E619" s="9" t="str">
+        <x:v>Use Audi hand-vacuum test to distinguish a membrane leak from an elbow fault. If indicated, remove the compressor or intake manifold and inspect the membrane and the breather two metal plates. Use repair kit 06E103772H only for a confirmed membrane or plate fault. For a confirmed elbow fault, replace elbow 06E103402 and spring clip N10769401 rather than automatically replacing the complete breather. Verify current part data in ETKA before ordering.</x:v>
+      </x:c>
+      <x:c r="F619" s="9" t="str">
+        <x:v>Hand-vacuum test of membrane versus breather elbow; exact engine/VIN 06E103772H repair kit or 06E103402 elbow plus N10769401 clip by branch</x:v>
+      </x:c>
+      <x:c r="G619" s="9" t="str">
+        <x:v>SUPERCHARGED ENGINE / TEST-BRANCH GATE</x:v>
+      </x:c>
+      <x:c r="H619" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I619" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J619" s="9" t="str">
+        <x:v>2014-2017 SQ5 VIN-specific PCV membrane/elbow parts</x:v>
+      </x:c>
+      <x:c r="K619" s="9" t="str">
+        <x:v>manufacturer parts route</x:v>
+      </x:c>
+      <x:c r="L619" s="9" t="str"/>
+      <x:c r="M619" s="9" t="str">
+        <x:v>Membrane and elbow failures require different parts.</x:v>
+      </x:c>
+      <x:c r="N619" s="41" t="str">
+        <x:v>Hold retail kit until live fitment and contents are verified for VIN.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="620" ht="66" hidden="0" customHeight="1">
+      <x:c r="A620" s="40" t="str"/>
+      <x:c r="B620" s="9" t="str"/>
+      <x:c r="C620" s="9" t="str"/>
+      <x:c r="D620" s="9" t="str"/>
+      <x:c r="E620" s="9" t="str"/>
+      <x:c r="F620" s="9" t="str"/>
+      <x:c r="G620" s="9" t="str"/>
+      <x:c r="H620" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I620" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J620" s="9" t="str">
+        <x:v>vacuum test and branch-specific repair</x:v>
+      </x:c>
+      <x:c r="K620" s="9" t="str">
+        <x:v>specialist engine service</x:v>
+      </x:c>
+      <x:c r="L620" s="9" t="str"/>
+      <x:c r="M620" s="9" t="str"/>
+      <x:c r="N620" s="41" t="str"/>
+    </x:row>
+    <x:row r="621" ht="250.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A621" s="40" t="n">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="B621" s="9" t="str">
+        <x:v>audi-sq5-supercharger-2014</x:v>
+      </x:c>
+      <x:c r="C621" s="9" t="str">
+        <x:v>2014-2018 | Audi | SQ5 | 3.0T</x:v>
+      </x:c>
+      <x:c r="D621" s="9" t="str">
+        <x:v>3.0T Supercharger Bearing and Intercooler Pump Failure</x:v>
+      </x:c>
+      <x:c r="E621" s="9" t="str">
+        <x:v>Replace supercharger nose bearing kit. Replace intercooler pump if failing. Service supercharger belt tension.</x:v>
+      </x:c>
+      <x:c r="F621" s="9" t="str">
+        <x:v>Correct generation; diagnose accessory drive, supercharger nose/clutch and charge-cooling circuit separately; exact component only after proof</x:v>
+      </x:c>
+      <x:c r="G621" s="9" t="str">
+        <x:v>SOURCE RANGE ERROR / COMPONENT GATE</x:v>
+      </x:c>
+      <x:c r="H621" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I621" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J621" s="9" t="str">
+        <x:v>2014-2017 supercharged SQ5 noise/cooling diagnosis</x:v>
+      </x:c>
+      <x:c r="K621" s="9" t="str">
+        <x:v>specialist engine service</x:v>
+      </x:c>
+      <x:c r="L621" s="9" t="str"/>
+      <x:c r="M621" s="9" t="str">
+        <x:v>2018 SQ5 uses a turbocharged EA839, not the described supercharger.</x:v>
+      </x:c>
+      <x:c r="N621" s="41" t="str">
+        <x:v>No supercharger kit, pump or belt until generation and failed component are corrected.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="622" ht="66" hidden="0" customHeight="1">
+      <x:c r="A622" s="40" t="str"/>
+      <x:c r="B622" s="9" t="str"/>
+      <x:c r="C622" s="9" t="str"/>
+      <x:c r="D622" s="9" t="str"/>
+      <x:c r="E622" s="9" t="str"/>
+      <x:c r="F622" s="9" t="str"/>
+      <x:c r="G622" s="9" t="str"/>
+      <x:c r="H622" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I622" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J622" s="9" t="str">
+        <x:v>VIN component/procedure</x:v>
+      </x:c>
+      <x:c r="K622" s="9" t="str">
+        <x:v>manufacturer parts route</x:v>
+      </x:c>
+      <x:c r="L622" s="9" t="str"/>
+      <x:c r="M622" s="9" t="str"/>
+      <x:c r="N622" s="41" t="str"/>
+    </x:row>
+    <x:row r="623" ht="844.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A623" s="40" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="B623" s="9" t="str">
+        <x:v>audi-sq5-supercharger-oil-leak-2014</x:v>
+      </x:c>
+      <x:c r="C623" s="9" t="str">
+        <x:v>2014-2017 | Audi | SQ5 | Premium Plus, Prestige | 3.0T Supercharged, 3.0T</x:v>
+      </x:c>
+      <x:c r="D623" s="9" t="str">
+        <x:v>Supercharger Seal and Gasket Oil Leaks (3.0T)</x:v>
+      </x:c>
+      <x:c r="E623" s="9" t="str">
+        <x:v>JHM Motorsports sells a complete supercharger replacement seal and gasket kit for the Eaton unit in the 3.0T. Replacing all seals at once is recommended since the supercharger must be removed for access. Nose cone seal, rotor shaft seals, and manifold gaskets should all be replaced together ($300-$500 in parts, $600-$1,200 labor). While the supercharger is off, also replace the PCV valve and perform carbon cleaning. For valve cover gasket leaks (separate issue), budget $400-$800 parts and labor. Monitor oil level weekly if leaks are present.</x:v>
+      </x:c>
+      <x:c r="F623" s="9" t="str">
+        <x:v>Clean and trace exact supercharger/engine leak; engine-specific seal scope; PCV and intake deposits only as separate confirmed work</x:v>
+      </x:c>
+      <x:c r="G623" s="9" t="str">
+        <x:v>LEAK-SOURCE / ENGINE GATE</x:v>
+      </x:c>
+      <x:c r="H623" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I623" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J623" s="9" t="str">
+        <x:v>2014-2017 SQ5 supercharger leak diagnosis/reseal</x:v>
+      </x:c>
+      <x:c r="K623" s="9" t="str">
+        <x:v>specialist engine service</x:v>
+      </x:c>
+      <x:c r="L623" s="9" t="str"/>
+      <x:c r="M623" s="9" t="str">
+        <x:v>A complete aftermarket seal kit and all overlapping work were not proven necessary.</x:v>
+      </x:c>
+      <x:c r="N623" s="41" t="str">
+        <x:v>Hold JHM kit until the live page proves SQ5 engine fitment and complete contents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="624" ht="66" hidden="0" customHeight="1">
+      <x:c r="A624" s="40" t="str"/>
+      <x:c r="B624" s="9" t="str"/>
+      <x:c r="C624" s="9" t="str"/>
+      <x:c r="D624" s="9" t="str"/>
+      <x:c r="E624" s="9" t="str"/>
+      <x:c r="F624" s="9" t="str"/>
+      <x:c r="G624" s="9" t="str"/>
+      <x:c r="H624" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I624" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J624" s="9" t="str">
+        <x:v>VIN seal diagrams and parts</x:v>
+      </x:c>
+      <x:c r="K624" s="9" t="str">
+        <x:v>manufacturer parts route</x:v>
+      </x:c>
+      <x:c r="L624" s="9" t="str"/>
+      <x:c r="M624" s="9" t="str"/>
+      <x:c r="N624" s="41" t="str"/>
+    </x:row>
+    <x:row r="625" ht="1122" hidden="0" customHeight="1">
+      <x:c r="A625" s="40" t="n">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="B625" s="9" t="str">
+        <x:v>audi-sq5-water-pump-2018</x:v>
+      </x:c>
+      <x:c r="C625" s="9" t="str">
+        <x:v>2018-2024 | Audi | SQ5 | 3.0T</x:v>
+      </x:c>
+      <x:c r="D625" s="9" t="str">
+        <x:v>Mechanical Coolant-Pump Leak with Possible N649 Vacuum-System Contamination</x:v>
+      </x:c>
+      <x:c r="E625" s="9" t="str">
+        <x:v>Confirm the complaint and exact vehicle criteria first. Inspect the vacuum line and N649 for coolant, then clean and dry suspected leakage, fill the cooling system correctly, inspect at idle and around 2,500 rpm, and pressure-test according to Audi workshop information. If no leak is reproduced, observe the vehicle without replacing parts. If the pump leak is confirmed, replace the failed component and document it. If fresh coolant has entered the vacuum system, inspect the remaining Audi checkpoints and replace only contaminated components; if the downstream checkpoints are clean, replace N649 and clean the line between the pump and N649 as directed by TSB 2070349/5.</x:v>
+      </x:c>
+      <x:c r="F625" s="9" t="str">
+        <x:v>TSB N649 contamination check; clean/dry/fill and idle/2500-rpm pressure test; pump only for confirmed leak; downstream checkpoint and N649 branch when applicable</x:v>
+      </x:c>
+      <x:c r="G625" s="9" t="str">
+        <x:v>TSB TEST-SEQUENCE / CONFIRMED-PUMP GATE</x:v>
+      </x:c>
+      <x:c r="H625" s="9" t="str">
+        <x:v>Audi SQ5 water-pump catalog</x:v>
+      </x:c>
+      <x:c r="I625" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/SQ5/Water-Pump/</x:v>
+      </x:c>
+      <x:c r="J625" s="9" t="str">
+        <x:v>2018-2024 SQ5 exact engine/VIN only after pump leak confirmation</x:v>
+      </x:c>
+      <x:c r="K625" s="9" t="str">
+        <x:v>conditional vehicle-specific pump catalog</x:v>
+      </x:c>
+      <x:c r="L625" s="9" t="str"/>
+      <x:c r="M625" s="9" t="str">
+        <x:v>The bulletin requires testing before pump or N649 replacement.</x:v>
+      </x:c>
+      <x:c r="N625" s="41" t="str">
+        <x:v>No pump, valve or line bundle before the defined branch is reached.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="626" ht="66" hidden="0" customHeight="1">
+      <x:c r="A626" s="40" t="str"/>
+      <x:c r="B626" s="9" t="str"/>
+      <x:c r="C626" s="9" t="str"/>
+      <x:c r="D626" s="9" t="str"/>
+      <x:c r="E626" s="9" t="str"/>
+      <x:c r="F626" s="9" t="str"/>
+      <x:c r="G626" s="9" t="str"/>
+      <x:c r="H626" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I626" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J626" s="9" t="str">
+        <x:v>TSB/VIN cooling diagnosis</x:v>
+      </x:c>
+      <x:c r="K626" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L626" s="9" t="str"/>
+      <x:c r="M626" s="9" t="str"/>
+      <x:c r="N626" s="41" t="str"/>
+    </x:row>
+    <x:row r="627" ht="673.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A627" s="40" t="n">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="B627" s="9" t="str">
+        <x:v>audi-sq7-air-susp-strut-2020</x:v>
+      </x:c>
+      <x:c r="C627" s="9" t="str">
+        <x:v>2020-2025 | Audi | SQ7 | 4.0T</x:v>
+      </x:c>
+      <x:c r="D627" s="9" t="str">
+        <x:v>2020-2025 SQ7 Air-Suspension C1260F0/U112100 Communication Fault - Diagnosis Required</x:v>
+      </x:c>
+      <x:c r="E627" s="9" t="str">
+        <x:v>Inspect the wiring and connector contacts between J775 and J1135 first. If no wiring fault is found, clear a first passive or sporadic fault and release the vehicle. Replace J1135 for an active or static fault, or when the same passive or sporadic fault returns a second time, following Audi workshop information and VIN-specific ETKA data. Do not replace an air spring, strut or compressor assembly solely from the warning.</x:v>
+      </x:c>
+      <x:c r="F627" s="9" t="str">
+        <x:v>J775-J1135 wiring/contact inspection; occurrence-state logic; conditional J1135 only after defined repeated/active fault</x:v>
+      </x:c>
+      <x:c r="G627" s="9" t="str">
+        <x:v>WIRING-FIRST TSB / CONTROL-UNIT GATE</x:v>
+      </x:c>
+      <x:c r="H627" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I627" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J627" s="9" t="str">
+        <x:v>2020-2025 SQ7 J1135 guided diagnosis</x:v>
+      </x:c>
+      <x:c r="K627" s="9" t="str">
+        <x:v>manufacturer suspension service</x:v>
+      </x:c>
+      <x:c r="L627" s="9" t="str"/>
+      <x:c r="M627" s="9" t="str">
+        <x:v>The cited procedure does not diagnose a strut.</x:v>
+      </x:c>
+      <x:c r="N627" s="41" t="str">
+        <x:v>Rename/re-key; no strut or compressor product.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="628" ht="1122" hidden="0" customHeight="1">
+      <x:c r="A628" s="40" t="n">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="B628" s="9" t="str">
+        <x:v>audi-sq7-air-suspension-2020</x:v>
+      </x:c>
+      <x:c r="C628" s="9" t="str">
+        <x:v>2020-2024 | Audi | SQ7 | Premium Plus, Prestige | 4.0T</x:v>
+      </x:c>
+      <x:c r="D628" s="9" t="str">
+        <x:v>Adaptive Air Suspension Compressor and Air Spring Failures</x:v>
+      </x:c>
+      <x:c r="E628" s="9" t="str">
+        <x:v>Diagnose specific failed component: air springs leak most commonly, followed by compressor burnout, valve block faults, and height sensor failures. Air spring replacement ($800-$1,500 per corner at independent shop). Compressor replacement ($1,200-$2,500 installed). Valve block: $500-$1,000. Height sensor: $200-$400. Check for air leaks first using soapy water spray before replacing the compressor - a $200 air spring seal may be causing a $2,000 compressor to overwork and fail. Aftermarket solutions from Arnott offer cost savings. Converting to conventional springs ($1,500-$2,500) eliminates future air suspension costs but sacrifices ride height adjustment.</x:v>
+      </x:c>
+      <x:c r="F628" s="9" t="str">
+        <x:v>Leak/sag and pressure diagnosis; split air spring, compressor, valve block and height sensor; exact VIN/PR-code component and calibration</x:v>
+      </x:c>
+      <x:c r="G628" s="9" t="str">
+        <x:v>SYSTEM DIAGNOSIS / COMPONENT GATE</x:v>
+      </x:c>
+      <x:c r="H628" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I628" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J628" s="9" t="str">
+        <x:v>2020-2024 SQ7 air-suspension leak/component diagnosis</x:v>
+      </x:c>
+      <x:c r="K628" s="9" t="str">
+        <x:v>specialist suspension service</x:v>
+      </x:c>
+      <x:c r="L628" s="9" t="str"/>
+      <x:c r="M628" s="9" t="str">
+        <x:v>Whole-system replacement and conversion are not established.</x:v>
+      </x:c>
+      <x:c r="N628" s="41" t="str">
+        <x:v>No Arnott or conversion link without exact component/kit fitment and calibration plan.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="629" ht="66" hidden="0" customHeight="1">
+      <x:c r="A629" s="40" t="str"/>
+      <x:c r="B629" s="9" t="str"/>
+      <x:c r="C629" s="9" t="str"/>
+      <x:c r="D629" s="9" t="str"/>
+      <x:c r="E629" s="9" t="str"/>
+      <x:c r="F629" s="9" t="str"/>
+      <x:c r="G629" s="9" t="str"/>
+      <x:c r="H629" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I629" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J629" s="9" t="str">
+        <x:v>VIN/PR-code parts and calibration</x:v>
+      </x:c>
+      <x:c r="K629" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L629" s="9" t="str"/>
+      <x:c r="M629" s="9" t="str"/>
+      <x:c r="N629" s="41" t="str"/>
+    </x:row>
+    <x:row r="630" ht="488.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A630" s="40" t="n">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="B630" s="9" t="str">
+        <x:v>audi-sq7-mmi-mib3-freeze-2020</x:v>
+      </x:c>
+      <x:c r="C630" s="9" t="str">
+        <x:v>2020-2026 | Audi | SQ7</x:v>
+      </x:c>
+      <x:c r="D630" s="9" t="str">
+        <x:v>2020-2026 Audi SQ7 Rearview Camera Software Recall 25V900 / 90TV</x:v>
+      </x:c>
+      <x:c r="E630" s="9" t="str">
+        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install the more robust driver-assistance software update free of charge. Until repaired, use extra caution when reversing and do not treat a restart, bus sleep or temporary image recovery as completion of the recall.</x:v>
+      </x:c>
+      <x:c r="F630" s="9" t="str">
+        <x:v>VIN/90TV/25V900 check; rearview-camera software remedy; direct observation; separate MMI freeze diagnosis</x:v>
+      </x:c>
+      <x:c r="G630" s="9" t="str">
+        <x:v>SOURCE-ID MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H630" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I630" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J630" s="9" t="str">
+        <x:v>2020-2026 SQ7 90TV</x:v>
+      </x:c>
+      <x:c r="K630" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L630" s="9" t="str"/>
+      <x:c r="M630" s="9" t="str">
+        <x:v>The cited action covers camera-image software, not general MMI freezing.</x:v>
+      </x:c>
+      <x:c r="N630" s="41" t="str">
+        <x:v>Rename/re-key; no head-unit link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="631" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A631" s="40" t="str"/>
+      <x:c r="B631" s="9" t="str"/>
+      <x:c r="C631" s="9" t="str"/>
+      <x:c r="D631" s="9" t="str"/>
+      <x:c r="E631" s="9" t="str"/>
+      <x:c r="F631" s="9" t="str"/>
+      <x:c r="G631" s="9" t="str"/>
+      <x:c r="H631" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I631" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J631" s="9" t="str">
+        <x:v>25V900 VIN history</x:v>
+      </x:c>
+      <x:c r="K631" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L631" s="9" t="str"/>
+      <x:c r="M631" s="9" t="str"/>
+      <x:c r="N631" s="41" t="str"/>
+    </x:row>
+    <x:row r="632" ht="990" hidden="0" customHeight="1">
+      <x:c r="A632" s="40" t="n">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="B632" s="9" t="str">
+        <x:v>audi-sq7-valve-cover-oil-leak-2020</x:v>
+      </x:c>
+      <x:c r="C632" s="9" t="str">
+        <x:v>2020-2024 | Audi | SQ7 | 4.0T</x:v>
+      </x:c>
+      <x:c r="D632" s="9" t="str">
+        <x:v>2020-2024 SQ7 4.0L High Oil Consumption and Piston-Ring Diagnosis - TSB 2071114/5</x:v>
+      </x:c>
+      <x:c r="E632" s="9" t="str">
+        <x:v>First inspect for visible engine-oil traces or leaks. Have an Audi dealer perform the authorized ODIS oil-consumption measurement, preserve and upload both test logs, and document the requested driving-profile data. Internal-engine repair is justified only when measured consumption exceeds the applicable limit and no other cause is found. If every TSB gate is met, follow Audi's VIN-, engine-code- and power-class-specific procedure for replacement of all eight pistons and piston rings, using current ETKA and ELSA information. Do not diagnose valve-cover gaskets or turbocharger seals from oil consumption alone.</x:v>
+      </x:c>
+      <x:c r="F632" s="9" t="str">
+        <x:v>Document measured oil consumption; exclude external leaks/spec/operation; apply TSB piston-ring diagnosis; internal repair only if all gates pass</x:v>
+      </x:c>
+      <x:c r="G632" s="9" t="str">
+        <x:v>SOURCE-ID MISMATCH / MEASURED-CONSUMPTION GATE</x:v>
+      </x:c>
+      <x:c r="H632" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I632" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J632" s="9" t="str">
+        <x:v>2020-2023 SQ7 TSB 2071114 oil-consumption test</x:v>
+      </x:c>
+      <x:c r="K632" s="9" t="str">
+        <x:v>manufacturer engine service</x:v>
+      </x:c>
+      <x:c r="L632" s="9" t="str"/>
+      <x:c r="M632" s="9" t="str">
+        <x:v>The source is an oil-consumption/piston-ring procedure, not valve-cover leakage.</x:v>
+      </x:c>
+      <x:c r="N632" s="41" t="str">
+        <x:v>Rename/re-key; no valve-cover gasket or internal parts link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="633" ht="686.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A633" s="40" t="n">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="B633" s="9" t="str">
+        <x:v>audi-sq8-air-susp-compressor-2020</x:v>
+      </x:c>
+      <x:c r="C633" s="9" t="str">
+        <x:v>2020-2025 | Audi | SQ8</x:v>
+      </x:c>
+      <x:c r="D633" s="9" t="str">
+        <x:v>2020-2025 SQ8 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
+      </x:c>
+      <x:c r="E633" s="9" t="str">
+        <x:v>Inspect the wiring and connector contacts between J775 and J1135 before replacing a component. For a first passive or sporadic occurrence, clear the fault and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after wiring inspection, Audi directs replacement of J1135 under current repair and parts information. Do not buy struts, springs or a compressor solely from this warning.</x:v>
+      </x:c>
+      <x:c r="F633" s="9" t="str">
+        <x:v>J775-J1135 wiring/contact inspection; occurrence-state logic; conditional J1135 only after defined fault recurrence</x:v>
+      </x:c>
+      <x:c r="G633" s="9" t="str">
+        <x:v>WIRING-FIRST TSB / CONTROL-UNIT GATE</x:v>
+      </x:c>
+      <x:c r="H633" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I633" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J633" s="9" t="str">
+        <x:v>2020-2025 SQ8 J1135 guided diagnosis</x:v>
+      </x:c>
+      <x:c r="K633" s="9" t="str">
+        <x:v>manufacturer suspension service</x:v>
+      </x:c>
+      <x:c r="L633" s="9" t="str"/>
+      <x:c r="M633" s="9" t="str">
+        <x:v>The cited procedure does not diagnose the compressor.</x:v>
+      </x:c>
+      <x:c r="N633" s="41" t="str">
+        <x:v>Rename/re-key; no compressor link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="634" ht="831.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A634" s="40" t="n">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="B634" s="9" t="str">
+        <x:v>audi-sq8-air-suspension-2020</x:v>
+      </x:c>
+      <x:c r="C634" s="9" t="str">
+        <x:v>2020-2024 | Audi | SQ8 | Premium Plus, Prestige | 4.0T</x:v>
+      </x:c>
+      <x:c r="D634" s="9" t="str">
+        <x:v>Adaptive Air Suspension Compressor and Air Spring Failures</x:v>
+      </x:c>
+      <x:c r="E634" s="9" t="str">
+        <x:v>Same diagnostic and repair approach as SQ7 (shared 4M platform). Isolate the failed component: air springs ($800-$1,500 per corner), compressor ($1,200-$2,500), valve block ($500-$1,000), or height sensor ($200-$400). Always check for air leaks before replacing the compressor. Aftermarket air suspension components from Arnott/Strutmasters offer 40-50% savings over OEM. Annual inspection of air springs for cracking recommended, especially in hot climates where UV and heat accelerate rubber degradation.</x:v>
+      </x:c>
+      <x:c r="F634" s="9" t="str">
+        <x:v>Leak/sag and pressure diagnosis; split air spring, compressor, valve block and height sensor; exact VIN/PR-code component and calibration</x:v>
+      </x:c>
+      <x:c r="G634" s="9" t="str">
+        <x:v>SYSTEM DIAGNOSIS / COMPONENT GATE</x:v>
+      </x:c>
+      <x:c r="H634" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I634" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J634" s="9" t="str">
+        <x:v>2020-2024 SQ8 air-suspension diagnosis</x:v>
+      </x:c>
+      <x:c r="K634" s="9" t="str">
+        <x:v>specialist suspension service</x:v>
+      </x:c>
+      <x:c r="L634" s="9" t="str"/>
+      <x:c r="M634" s="9" t="str">
+        <x:v>System-wide replacement is not supported by the symptom.</x:v>
+      </x:c>
+      <x:c r="N634" s="41" t="str">
+        <x:v>No named hardware/conversion link or lifespan claim without exact proof.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="635" ht="66" hidden="0" customHeight="1">
+      <x:c r="A635" s="40" t="str"/>
+      <x:c r="B635" s="9" t="str"/>
+      <x:c r="C635" s="9" t="str"/>
+      <x:c r="D635" s="9" t="str"/>
+      <x:c r="E635" s="9" t="str"/>
+      <x:c r="F635" s="9" t="str"/>
+      <x:c r="G635" s="9" t="str"/>
+      <x:c r="H635" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I635" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J635" s="9" t="str">
+        <x:v>VIN/PR-code parts and calibration</x:v>
+      </x:c>
+      <x:c r="K635" s="9" t="str">
+        <x:v>manufacturer service</x:v>
+      </x:c>
+      <x:c r="L635" s="9" t="str"/>
+      <x:c r="M635" s="9" t="str"/>
+      <x:c r="N635" s="41" t="str"/>
+    </x:row>
+    <x:row r="636" ht="448.79998779296875" hidden="0" customHeight="1">
+      <x:c r="A636" s="40" t="n">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="B636" s="9" t="str">
+        <x:v>audi-sq8-airbag-mount-2023</x:v>
+      </x:c>
+      <x:c r="C636" s="9" t="str">
+        <x:v>2023-2024 | Audi | SQ8 | 4.0T V8</x:v>
+      </x:c>
+      <x:c r="D636" s="9" t="str">
+        <x:v>2023-2024 SQ8 Driver-Seat Side-Airbag Mount Recall 69GA (23V868)</x:v>
+      </x:c>
+      <x:c r="E636" s="9" t="str">
+        <x:v>Check the VIN for open Audi recall 69GA and have an authorized dealer inspect the driver-seat side-airbag installation. If needed, the dealer will reinstall the airbag correctly; the recall filing says no parts are replaced. A clock spring or generic airbag part is not the recall remedy.</x:v>
+      </x:c>
+      <x:c r="F636" s="9" t="str">
+        <x:v>VIN/69GA/23V868 check; dealer driver-seat side-airbag installation inspection and reinstall</x:v>
+      </x:c>
+      <x:c r="G636" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H636" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I636" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J636" s="9" t="str">
+        <x:v>2023-2024 SQ8 69GA</x:v>
+      </x:c>
+      <x:c r="K636" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L636" s="9" t="str"/>
+      <x:c r="M636" s="9" t="str">
+        <x:v>Pyrotechnic restraint work is campaign-controlled.</x:v>
+      </x:c>
+      <x:c r="N636" s="41" t="str">
+        <x:v>No airbag or mounting-hardware commerce link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="637" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A637" s="40" t="str"/>
+      <x:c r="B637" s="9" t="str"/>
+      <x:c r="C637" s="9" t="str"/>
+      <x:c r="D637" s="9" t="str"/>
+      <x:c r="E637" s="9" t="str"/>
+      <x:c r="F637" s="9" t="str"/>
+      <x:c r="G637" s="9" t="str"/>
+      <x:c r="H637" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I637" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J637" s="9" t="str">
+        <x:v>23V868 VIN history</x:v>
+      </x:c>
+      <x:c r="K637" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L637" s="9" t="str"/>
+      <x:c r="M637" s="9" t="str"/>
+      <x:c r="N637" s="41" t="str"/>
+    </x:row>
+    <x:row r="638" ht="580.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A638" s="40" t="n">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="B638" s="9" t="str">
+        <x:v>audi-sq8-mmi-mib3-freeze-2020</x:v>
+      </x:c>
+      <x:c r="C638" s="9" t="str">
+        <x:v>2020-2026 | Audi | SQ8 | 4.0T V8</x:v>
+      </x:c>
+      <x:c r="D638" s="9" t="str">
+        <x:v>2020-2026 SQ8 Rearview Camera Software Recall 90TV (25V900)</x:v>
+      </x:c>
+      <x:c r="E638" s="9" t="str">
+        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install more robust driver-assistance software free of charge. Until repaired, use extra caution when reversing and do not treat a restart, bus sleep or temporary image recovery as completion of the recall. A generic scan tool or head-unit replacement is not the recall remedy.</x:v>
+      </x:c>
+      <x:c r="F638" s="9" t="str">
+        <x:v>VIN/90TV/25V900 check; camera-image software remedy; direct observation; separate MMI freeze diagnosis</x:v>
+      </x:c>
+      <x:c r="G638" s="9" t="str">
+        <x:v>SOURCE-ID MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H638" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I638" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J638" s="9" t="str">
+        <x:v>2020-2026 SQ8 90TV</x:v>
+      </x:c>
+      <x:c r="K638" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L638" s="9" t="str"/>
+      <x:c r="M638" s="9" t="str">
+        <x:v>The cited recall covers rearview-camera display software only.</x:v>
+      </x:c>
+      <x:c r="N638" s="41" t="str">
+        <x:v>Rename/re-key; no head-unit or generic scanner link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="639" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A639" s="40" t="str"/>
+      <x:c r="B639" s="9" t="str"/>
+      <x:c r="C639" s="9" t="str"/>
+      <x:c r="D639" s="9" t="str"/>
+      <x:c r="E639" s="9" t="str"/>
+      <x:c r="F639" s="9" t="str"/>
+      <x:c r="G639" s="9" t="str"/>
+      <x:c r="H639" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I639" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J639" s="9" t="str">
+        <x:v>25V900 VIN history</x:v>
+      </x:c>
+      <x:c r="K639" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L639" s="9" t="str"/>
+      <x:c r="M639" s="9" t="str"/>
+      <x:c r="N639" s="41" t="str"/>
+    </x:row>
+    <x:row r="640" ht="567.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A640" s="40" t="n">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B640" s="9" t="str">
+        <x:v>audi-sq8-turbo-coolant-2020</x:v>
+      </x:c>
+      <x:c r="C640" s="9" t="str">
+        <x:v>2020-2021 | Audi | SQ8 | 4.0T V8</x:v>
+      </x:c>
+      <x:c r="D640" s="9" t="str">
+        <x:v>2020-Early 2021 SQ8 Red Coolant Warning - Check G407 per TSB 2062951/4</x:v>
+      </x:c>
+      <x:c r="E640" s="9" t="str">
+        <x:v>Have the vehicle checked with Audi Guided Fault Finding and inspect G407 and its O-ring. Replace G407 only if the O-ring is damaged or pinched and the diagnosis matches the bulletin; follow the related Audi diagnostic path if additional listed faults are stored. Do not replace turbo coolant hoses, pumps or other cooling parts from this card alone.</x:v>
+      </x:c>
+      <x:c r="F640" s="9" t="str">
+        <x:v>Guided fault finding for G407 circuit and exact leak; inspect sensor O-ring; replace G407 only if seal is pinched/damaged; bleed/test</x:v>
+      </x:c>
+      <x:c r="G640" s="9" t="str">
+        <x:v>TSB SENSOR-SEAL TEST BRANCH</x:v>
+      </x:c>
+      <x:c r="H640" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I640" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J640" s="9" t="str">
+        <x:v>2020-early 2021 SQ8 TSB 2062951/4 G407 diagnosis</x:v>
+      </x:c>
+      <x:c r="K640" s="9" t="str">
+        <x:v>manufacturer cooling service</x:v>
+      </x:c>
+      <x:c r="L640" s="9" t="str"/>
+      <x:c r="M640" s="9" t="str">
+        <x:v>The bulletin identifies a conditional sensor-seal path, not general turbo coolant plumbing.</x:v>
+      </x:c>
+      <x:c r="N640" s="41" t="str">
+        <x:v>No hose, pump or sensor until the TSB branch confirms it.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="641" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A641" s="40" t="str"/>
+      <x:c r="B641" s="9" t="str"/>
+      <x:c r="C641" s="9" t="str"/>
+      <x:c r="D641" s="9" t="str"/>
+      <x:c r="E641" s="9" t="str"/>
+      <x:c r="F641" s="9" t="str"/>
+      <x:c r="G641" s="9" t="str"/>
+      <x:c r="H641" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I641" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J641" s="9" t="str">
+        <x:v>guided leak/sensor diagnosis</x:v>
+      </x:c>
+      <x:c r="K641" s="9" t="str">
+        <x:v>specialist cooling service</x:v>
+      </x:c>
+      <x:c r="L641" s="9" t="str"/>
+      <x:c r="M641" s="9" t="str"/>
+      <x:c r="N641" s="41" t="str"/>
+    </x:row>
+    <x:row r="642" ht="250.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A642" s="40" t="n">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="B642" s="9" t="str">
+        <x:v>audi-tt-absesp-control-module-failure-2000</x:v>
+      </x:c>
+      <x:c r="C642" s="9" t="str">
+        <x:v>2000-2001 | Audi | TT</x:v>
+      </x:c>
+      <x:c r="D642" s="9" t="str">
+        <x:v>Driver Airbag Inflator May Deploy Improperly (Recall 21V470 / 69CJ)</x:v>
+      </x:c>
+      <x:c r="E642" s="9" t="str">
+        <x:v>Check the VIN and campaign history. Audi dealers replace the driver frontal-airbag inflator with an alternative inflator free of charge under campaign 69CJ.</x:v>
+      </x:c>
+      <x:c r="F642" s="9" t="str">
+        <x:v>VIN/69CJ/21V470 check; free driver-airbag remedy</x:v>
+      </x:c>
+      <x:c r="G642" s="9" t="str">
+        <x:v>SOURCE-ID MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H642" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I642" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J642" s="9" t="str">
+        <x:v>2000-2001 TT 69CJ</x:v>
+      </x:c>
+      <x:c r="K642" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L642" s="9" t="str"/>
+      <x:c r="M642" s="9" t="str">
+        <x:v>The source is an airbag recall, not ABS/ESP control-module failure.</x:v>
+      </x:c>
+      <x:c r="N642" s="41" t="str">
+        <x:v>Rename/re-key; no ABS module link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="643" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A643" s="40" t="str"/>
+      <x:c r="B643" s="9" t="str"/>
+      <x:c r="C643" s="9" t="str"/>
+      <x:c r="D643" s="9" t="str"/>
+      <x:c r="E643" s="9" t="str"/>
+      <x:c r="F643" s="9" t="str"/>
+      <x:c r="G643" s="9" t="str"/>
+      <x:c r="H643" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I643" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J643" s="9" t="str">
+        <x:v>21V470 VIN history</x:v>
+      </x:c>
+      <x:c r="K643" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L643" s="9" t="str"/>
+      <x:c r="M643" s="9" t="str"/>
+      <x:c r="N643" s="41" t="str"/>
+    </x:row>
+    <x:row r="644" ht="277.20001220703125" hidden="0" customHeight="1">
+      <x:c r="A644" s="40" t="n">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="B644" s="9" t="str">
+        <x:v>audi-tt-cam-follower-2008</x:v>
+      </x:c>
+      <x:c r="C644" s="9" t="str">
+        <x:v>2000-2000 | Audi | TT</x:v>
+      </x:c>
+      <x:c r="D644" s="9" t="str">
+        <x:v>Fuel-Line Assembly Can Leak (Recall 99V222)</x:v>
+      </x:c>
+      <x:c r="E644" s="9" t="str">
+        <x:v>Check VIN eligibility and campaign completion. Audi dealers replace the fuel-line assembly free of charge under recall 99V222. Stop driving if fuel odor or leakage is present.</x:v>
+      </x:c>
+      <x:c r="F644" s="9" t="str">
+        <x:v>VIN/99V222 check; dealer fuel-line recall remedy; stop for fuel odor/leak</x:v>
+      </x:c>
+      <x:c r="G644" s="9" t="str">
+        <x:v>SOURCE-ID/YEAR MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H644" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I644" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J644" s="9" t="str">
+        <x:v>2000 TT fuel-line recall</x:v>
+      </x:c>
+      <x:c r="K644" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L644" s="9" t="str"/>
+      <x:c r="M644" s="9" t="str">
+        <x:v>The source is a 2000 fuel-line recall, not a 2008 cam-follower repair.</x:v>
+      </x:c>
+      <x:c r="N644" s="41" t="str">
+        <x:v>Rename/re-key; no cam follower product.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="645" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A645" s="40" t="str"/>
+      <x:c r="B645" s="9" t="str"/>
+      <x:c r="C645" s="9" t="str"/>
+      <x:c r="D645" s="9" t="str"/>
+      <x:c r="E645" s="9" t="str"/>
+      <x:c r="F645" s="9" t="str"/>
+      <x:c r="G645" s="9" t="str"/>
+      <x:c r="H645" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I645" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J645" s="9" t="str">
+        <x:v>99V222 VIN history</x:v>
+      </x:c>
+      <x:c r="K645" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L645" s="9" t="str"/>
+      <x:c r="M645" s="9" t="str"/>
+      <x:c r="N645" s="41" t="str"/>
+    </x:row>
+    <x:row r="646" ht="198" hidden="0" customHeight="1">
+      <x:c r="A646" s="40" t="n">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="B646" s="9" t="str">
+        <x:v>audi-tt-coil-pack-failure-and-2000</x:v>
+      </x:c>
+      <x:c r="C646" s="9" t="str">
+        <x:v>2000-2001 | Audi | TT</x:v>
+      </x:c>
+      <x:c r="D646" s="9" t="str">
+        <x:v>Rear Track-Control Arm Corrosion Can Restrict Movement (Recall 01V325)</x:v>
+      </x:c>
+      <x:c r="E646" s="9" t="str">
+        <x:v>Check the VIN and campaign history. Audi dealers replace the rear track-control arms free of charge under recall 01V325.</x:v>
+      </x:c>
+      <x:c r="F646" s="9" t="str">
+        <x:v>VIN/01V325 check; dealer rear track-control-arm inspection/remedy</x:v>
+      </x:c>
+      <x:c r="G646" s="9" t="str">
+        <x:v>SOURCE-ID MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H646" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I646" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J646" s="9" t="str">
+        <x:v>2000-2001 TT rear control-arm recall</x:v>
+      </x:c>
+      <x:c r="K646" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L646" s="9" t="str"/>
+      <x:c r="M646" s="9" t="str">
+        <x:v>The source does not describe ignition-coil failure.</x:v>
+      </x:c>
+      <x:c r="N646" s="41" t="str">
+        <x:v>Rename/re-key; no coil pack link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="647" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A647" s="40" t="str"/>
+      <x:c r="B647" s="9" t="str"/>
+      <x:c r="C647" s="9" t="str"/>
+      <x:c r="D647" s="9" t="str"/>
+      <x:c r="E647" s="9" t="str"/>
+      <x:c r="F647" s="9" t="str"/>
+      <x:c r="G647" s="9" t="str"/>
+      <x:c r="H647" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I647" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J647" s="9" t="str">
+        <x:v>01V325 VIN history</x:v>
+      </x:c>
+      <x:c r="K647" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L647" s="9" t="str"/>
+      <x:c r="M647" s="9" t="str"/>
+      <x:c r="N647" s="41" t="str"/>
+    </x:row>
+    <x:row r="648" ht="264" hidden="0" customHeight="1">
+      <x:c r="A648" s="40" t="n">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="B648" s="9" t="str">
+        <x:v>audi-tt-dsg-mechatronic-2008</x:v>
+      </x:c>
+      <x:c r="C648" s="9" t="str">
+        <x:v>2004-2004 | Audi | TT</x:v>
+      </x:c>
+      <x:c r="D648" s="9" t="str">
+        <x:v>Direct-Shift Gearbox Clutch Weld Can Lose Drive Torque (Recall 04V007)</x:v>
+      </x:c>
+      <x:c r="E648" s="9" t="str">
+        <x:v>Check VIN eligibility. Audi dealers replace the affected clutch free of charge under recall 04V007. If drive torque is lost, move out of traffic safely and arrange recovery.</x:v>
+      </x:c>
+      <x:c r="F648" s="9" t="str">
+        <x:v>VIN/04V007 check; dealer DSG clutch-weld recall remedy</x:v>
+      </x:c>
+      <x:c r="G648" s="9" t="str">
+        <x:v>SOURCE-ID/YEAR MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H648" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I648" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J648" s="9" t="str">
+        <x:v>2004 TT DSG clutch recall</x:v>
+      </x:c>
+      <x:c r="K648" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L648" s="9" t="str"/>
+      <x:c r="M648" s="9" t="str">
+        <x:v>The source is a campaign, not a general 2008 mechatronic diagnosis.</x:v>
+      </x:c>
+      <x:c r="N648" s="41" t="str">
+        <x:v>Rename/re-key; no mechatronic product.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="649" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A649" s="40" t="str"/>
+      <x:c r="B649" s="9" t="str"/>
+      <x:c r="C649" s="9" t="str"/>
+      <x:c r="D649" s="9" t="str"/>
+      <x:c r="E649" s="9" t="str"/>
+      <x:c r="F649" s="9" t="str"/>
+      <x:c r="G649" s="9" t="str"/>
+      <x:c r="H649" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I649" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J649" s="9" t="str">
+        <x:v>04V007 VIN history</x:v>
+      </x:c>
+      <x:c r="K649" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L649" s="9" t="str"/>
+      <x:c r="M649" s="9" t="str"/>
+      <x:c r="N649" s="41" t="str"/>
+    </x:row>
+    <x:row r="650" ht="356.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A650" s="40" t="n">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="B650" s="9" t="str">
+        <x:v>audi-tt-dsg-transmission-2008</x:v>
+      </x:c>
+      <x:c r="C650" s="9" t="str">
+        <x:v>2009-2009 | Audi | TT</x:v>
+      </x:c>
+      <x:c r="D650" s="9" t="str">
+        <x:v>DSG Temperature-Sensor Wiring Can Trigger an Abrupt Shift to Neutral (Recall 09V333)</x:v>
+      </x:c>
+      <x:c r="E650" s="9" t="str">
+        <x:v>Check the VIN and campaign history. Audi dealers reprogram the transmission control module with updated software free of charge under recall 09V333. If the gear indicator flashes or neutral engages unexpectedly, stop safely.</x:v>
+      </x:c>
+      <x:c r="F650" s="9" t="str">
+        <x:v>VIN/09V333 check; dealer temperature-sensor wiring/TCM software remedy</x:v>
+      </x:c>
+      <x:c r="G650" s="9" t="str">
+        <x:v>SOURCE-ID/YEAR MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H650" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I650" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J650" s="9" t="str">
+        <x:v>2009 TT DSG temperature-sensor campaign</x:v>
+      </x:c>
+      <x:c r="K650" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L650" s="9" t="str"/>
+      <x:c r="M650" s="9" t="str">
+        <x:v>The recall specifies wiring/software, not wholesale transmission replacement.</x:v>
+      </x:c>
+      <x:c r="N650" s="41" t="str">
+        <x:v>Rename/re-key; no DSG hardware link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="651" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A651" s="40" t="str"/>
+      <x:c r="B651" s="9" t="str"/>
+      <x:c r="C651" s="9" t="str"/>
+      <x:c r="D651" s="9" t="str"/>
+      <x:c r="E651" s="9" t="str"/>
+      <x:c r="F651" s="9" t="str"/>
+      <x:c r="G651" s="9" t="str"/>
+      <x:c r="H651" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I651" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J651" s="9" t="str">
+        <x:v>09V333 VIN history</x:v>
+      </x:c>
+      <x:c r="K651" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L651" s="9" t="str"/>
+      <x:c r="M651" s="9" t="str"/>
+      <x:c r="N651" s="41" t="str"/>
+    </x:row>
+    <x:row r="652" ht="303.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A652" s="40" t="n">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="B652" s="9" t="str">
+        <x:v>audi-tt-front-control-arm-bushings-2000</x:v>
+      </x:c>
+      <x:c r="C652" s="9" t="str">
+        <x:v>2000-2000 | Audi | TT</x:v>
+      </x:c>
+      <x:c r="D652" s="9" t="str">
+        <x:v>High-Speed Directional-Stability Remedy (Recall 99V300)</x:v>
+      </x:c>
+      <x:c r="E652" s="9" t="str">
+        <x:v>Verify campaign completion with Audi. The factory remedy installs revised stabilizers, front control arms, firmer shock absorbers, and a rear spoiler as specified for the drivetrain configuration.</x:v>
+      </x:c>
+      <x:c r="F652" s="9" t="str">
+        <x:v>VIN/99V300 check; drivetrain-specific dealer stability remedy with specified suspension/spoiler components</x:v>
+      </x:c>
+      <x:c r="G652" s="9" t="str">
+        <x:v>SOURCE-ID MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H652" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I652" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J652" s="9" t="str">
+        <x:v>2000 TT high-speed-stability remedy</x:v>
+      </x:c>
+      <x:c r="K652" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L652" s="9" t="str"/>
+      <x:c r="M652" s="9" t="str">
+        <x:v>The multi-component remedy depends on drivetrain and campaign status.</x:v>
+      </x:c>
+      <x:c r="N652" s="41" t="str">
+        <x:v>No isolated control-arm bushing link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="653" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A653" s="40" t="str"/>
+      <x:c r="B653" s="9" t="str"/>
+      <x:c r="C653" s="9" t="str"/>
+      <x:c r="D653" s="9" t="str"/>
+      <x:c r="E653" s="9" t="str"/>
+      <x:c r="F653" s="9" t="str"/>
+      <x:c r="G653" s="9" t="str"/>
+      <x:c r="H653" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I653" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J653" s="9" t="str">
+        <x:v>99V300 VIN history</x:v>
+      </x:c>
+      <x:c r="K653" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L653" s="9" t="str"/>
+      <x:c r="M653" s="9" t="str"/>
+      <x:c r="N653" s="41" t="str"/>
+    </x:row>
+    <x:row r="654" ht="237.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A654" s="40" t="n">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="B654" s="9" t="str">
+        <x:v>audi-tt-haldex-awd-coupling-pumpcontroller-2000</x:v>
+      </x:c>
+      <x:c r="C654" s="9" t="str">
+        <x:v>2008-2010 | Audi | TT</x:v>
+      </x:c>
+      <x:c r="D654" s="9" t="str">
+        <x:v>Fuel-Tank Ventilation Valve Can Allow Fuel Leakage (Recall 09V377)</x:v>
+      </x:c>
+      <x:c r="E654" s="9" t="str">
+        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel-tank ventilation valve with the improved valve free of charge under recall 09V377.</x:v>
+      </x:c>
+      <x:c r="F654" s="9" t="str">
+        <x:v>VIN/09V377 check; dealer fuel-tank vent-valve remedy; stop for fuel odor/leak</x:v>
+      </x:c>
+      <x:c r="G654" s="9" t="str">
+        <x:v>SOURCE-ID/YEAR MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H654" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I654" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J654" s="9" t="str">
+        <x:v>2008-2010 TT vent-valve recall</x:v>
+      </x:c>
+      <x:c r="K654" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L654" s="9" t="str"/>
+      <x:c r="M654" s="9" t="str">
+        <x:v>The source is a fuel-system recall, not a Haldex pump/controller repair.</x:v>
+      </x:c>
+      <x:c r="N654" s="41" t="str">
+        <x:v>Rename/re-key; no AWD coupling product.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="655" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A655" s="40" t="str"/>
+      <x:c r="B655" s="9" t="str"/>
+      <x:c r="C655" s="9" t="str"/>
+      <x:c r="D655" s="9" t="str"/>
+      <x:c r="E655" s="9" t="str"/>
+      <x:c r="F655" s="9" t="str"/>
+      <x:c r="G655" s="9" t="str"/>
+      <x:c r="H655" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I655" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J655" s="9" t="str">
+        <x:v>09V377 VIN history</x:v>
+      </x:c>
+      <x:c r="K655" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L655" s="9" t="str"/>
+      <x:c r="M655" s="9" t="str"/>
+      <x:c r="N655" s="41" t="str"/>
+    </x:row>
+    <x:row r="656" ht="184.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A656" s="40" t="n">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="B656" s="9" t="str">
+        <x:v>audi-tt-high-speed-stability-recall-for-2000</x:v>
+      </x:c>
+      <x:c r="C656" s="9" t="str">
+        <x:v>2016-2019 | Audi | TT</x:v>
+      </x:c>
+      <x:c r="D656" s="9" t="str">
+        <x:v>Fuel Tank Can Be Damaged by Heat-Shield Bracket in a Crash (Recall 20V076 / 20BX)</x:v>
+      </x:c>
+      <x:c r="E656" s="9" t="str">
+        <x:v>Check VIN eligibility. Audi dealers install a protective cap on the heat-shield bracket free of charge under campaign 20BX.</x:v>
+      </x:c>
+      <x:c r="F656" s="9" t="str">
+        <x:v>VIN/20BX/20V076 check; dealer heat-shield bracket protective-cap remedy</x:v>
+      </x:c>
+      <x:c r="G656" s="9" t="str">
+        <x:v>SOURCE-YEAR MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H656" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I656" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J656" s="9" t="str">
+        <x:v>2016-2019 TT 20BX</x:v>
+      </x:c>
+      <x:c r="K656" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L656" s="9" t="str"/>
+      <x:c r="M656" s="9" t="str">
+        <x:v>The cited source is a heat-shield campaign, not the 2000 stability recall.</x:v>
+      </x:c>
+      <x:c r="N656" s="41" t="str">
+        <x:v>Rename/re-key/year; no suspension product.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="657" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A657" s="40" t="str"/>
+      <x:c r="B657" s="9" t="str"/>
+      <x:c r="C657" s="9" t="str"/>
+      <x:c r="D657" s="9" t="str"/>
+      <x:c r="E657" s="9" t="str"/>
+      <x:c r="F657" s="9" t="str"/>
+      <x:c r="G657" s="9" t="str"/>
+      <x:c r="H657" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I657" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J657" s="9" t="str">
+        <x:v>20V076 VIN history</x:v>
+      </x:c>
+      <x:c r="K657" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L657" s="9" t="str"/>
+      <x:c r="M657" s="9" t="str"/>
+      <x:c r="N657" s="41" t="str"/>
+    </x:row>
+    <x:row r="658" ht="237.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A658" s="40" t="n">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="B658" s="9" t="str">
+        <x:v>audi-tt-instrument-cluster-pixel-failure-2000</x:v>
+      </x:c>
+      <x:c r="C658" s="9" t="str">
+        <x:v>2016-2016 | Audi | TT</x:v>
+      </x:c>
+      <x:c r="D658" s="9" t="str">
+        <x:v>Front-Passenger Airbag Module May Explode or Deploy Improperly (Recall 22V543 / 69DY)</x:v>
+      </x:c>
+      <x:c r="E658" s="9" t="str">
+        <x:v>Check the VIN and campaign history. Audi dealers replace the front-passenger airbag module free of charge under campaign 69DY/61C1.</x:v>
+      </x:c>
+      <x:c r="F658" s="9" t="str">
+        <x:v>VIN/69DY/22V543 check; free passenger-airbag module remedy</x:v>
+      </x:c>
+      <x:c r="G658" s="9" t="str">
+        <x:v>SOURCE-ID/YEAR MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H658" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I658" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J658" s="9" t="str">
+        <x:v>2016 TT passenger-airbag recall</x:v>
+      </x:c>
+      <x:c r="K658" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L658" s="9" t="str"/>
+      <x:c r="M658" s="9" t="str">
+        <x:v>The source is an airbag recall, not cluster pixel failure.</x:v>
+      </x:c>
+      <x:c r="N658" s="41" t="str">
+        <x:v>Rename/re-key; no cluster product.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="659" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A659" s="40" t="str"/>
+      <x:c r="B659" s="9" t="str"/>
+      <x:c r="C659" s="9" t="str"/>
+      <x:c r="D659" s="9" t="str"/>
+      <x:c r="E659" s="9" t="str"/>
+      <x:c r="F659" s="9" t="str"/>
+      <x:c r="G659" s="9" t="str"/>
+      <x:c r="H659" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I659" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J659" s="9" t="str">
+        <x:v>22V543 VIN history</x:v>
+      </x:c>
+      <x:c r="K659" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L659" s="9" t="str"/>
+      <x:c r="M659" s="9" t="str"/>
+      <x:c r="N659" s="41" t="str"/>
+    </x:row>
+    <x:row r="660" ht="224.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A660" s="40" t="n">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="B660" s="9" t="str">
+        <x:v>audi-tt-magnetic-ride-2008</x:v>
+      </x:c>
+      <x:c r="C660" s="9" t="str">
+        <x:v>2023-2023 | Audi | TT</x:v>
+      </x:c>
+      <x:c r="D660" s="9" t="str">
+        <x:v>Passenger-Seat Occupant Detection Connection Can Disable Airbag (Recall 24V251 / 69GU)</x:v>
+      </x:c>
+      <x:c r="E660" s="9" t="str">
+        <x:v>Check VIN eligibility. Audi dealers replace the passenger-seat occupant-detection control module free of charge under campaign 69GU.</x:v>
+      </x:c>
+      <x:c r="F660" s="9" t="str">
+        <x:v>VIN/69GU/24V251 check; dealer passenger ODS module remedy</x:v>
+      </x:c>
+      <x:c r="G660" s="9" t="str">
+        <x:v>SOURCE-ID/YEAR MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H660" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I660" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J660" s="9" t="str">
+        <x:v>2023 TT ODS recall</x:v>
+      </x:c>
+      <x:c r="K660" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L660" s="9" t="str"/>
+      <x:c r="M660" s="9" t="str">
+        <x:v>The source concerns occupant detection, not magnetic-ride suspension.</x:v>
+      </x:c>
+      <x:c r="N660" s="41" t="str">
+        <x:v>Rename/re-key; no damper link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="661" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A661" s="40" t="str"/>
+      <x:c r="B661" s="9" t="str"/>
+      <x:c r="C661" s="9" t="str"/>
+      <x:c r="D661" s="9" t="str"/>
+      <x:c r="E661" s="9" t="str"/>
+      <x:c r="F661" s="9" t="str"/>
+      <x:c r="G661" s="9" t="str"/>
+      <x:c r="H661" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I661" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J661" s="9" t="str">
+        <x:v>24V251 VIN history</x:v>
+      </x:c>
+      <x:c r="K661" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L661" s="9" t="str"/>
+      <x:c r="M661" s="9" t="str"/>
+      <x:c r="N661" s="41" t="str"/>
+    </x:row>
+    <x:row r="662" ht="726" hidden="0" customHeight="1">
+      <x:c r="A662" s="40" t="n">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="B662" s="9" t="str">
+        <x:v>audi-tt-tail-light-corrosion-2008</x:v>
+      </x:c>
+      <x:c r="C662" s="9" t="str">
+        <x:v>2008-2015 | Audi | TT</x:v>
+      </x:c>
+      <x:c r="D662" s="9" t="str">
+        <x:v>Tail Light Electrical Connector Corrosion (Mk2)</x:v>
+      </x:c>
+      <x:c r="E662" s="9" t="str">
+        <x:v>Remove tail light assembly, inspect electrical connector for green corrosion. CLEAN connector with electrical contact cleaner and wire brush ($20 DIY). Apply dielectric grease to prevent future corrosion ($10). If connector is severely corroded: Replace pigtail connector ($50-$100 parts). Improve tail light seal with silicone sealant around housing ($15). This is a DIY-friendly repair taking 1-2 hours. If paying shop, costs $150-$300. Address early before corrosion causes shorts.</x:v>
+      </x:c>
+      <x:c r="F662" s="9" t="str">
+        <x:v>Identify side and water-entry source; inspect ground/connector/circuit; clean/repair terminals or exact connector/loom; lamp only if failed; reseal with compatible material and water-test</x:v>
+      </x:c>
+      <x:c r="G662" s="9" t="str">
+        <x:v>SIDE / CONNECTOR / LEAK-SOURCE GATE</x:v>
+      </x:c>
+      <x:c r="H662" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I662" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J662" s="9" t="str">
+        <x:v>2008-2015 TT tail-lamp circuit and water-ingress diagnosis</x:v>
+      </x:c>
+      <x:c r="K662" s="9" t="str">
+        <x:v>specialist electrical service</x:v>
+      </x:c>
+      <x:c r="L662" s="9" t="str"/>
+      <x:c r="M662" s="9" t="str">
+        <x:v>Corroded terminals, wiring, ground and lamp are different branches.</x:v>
+      </x:c>
+      <x:c r="N662" s="41" t="str">
+        <x:v>No generic silicone or full lamp before side, leak source and failed component are known.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="663" ht="66" hidden="0" customHeight="1">
+      <x:c r="A663" s="40" t="str"/>
+      <x:c r="B663" s="9" t="str"/>
+      <x:c r="C663" s="9" t="str"/>
+      <x:c r="D663" s="9" t="str"/>
+      <x:c r="E663" s="9" t="str"/>
+      <x:c r="F663" s="9" t="str"/>
+      <x:c r="G663" s="9" t="str"/>
+      <x:c r="H663" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I663" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J663" s="9" t="str">
+        <x:v>VIN/side connector, loom and lamp parts</x:v>
+      </x:c>
+      <x:c r="K663" s="9" t="str">
+        <x:v>manufacturer parts route</x:v>
+      </x:c>
+      <x:c r="L663" s="9" t="str"/>
+      <x:c r="M663" s="9" t="str"/>
+      <x:c r="N663" s="41" t="str"/>
+    </x:row>
+    <x:row r="664" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A664" s="40" t="n">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="B664" s="9" t="str">
+        <x:v>audi-tt-water-pump-2008</x:v>
+      </x:c>
+      <x:c r="C664" s="9" t="str">
+        <x:v>2008-2008 | Audi | TT</x:v>
+      </x:c>
+      <x:c r="D664" s="9" t="str">
+        <x:v>C-Pillar Trim Cover Can Detach During Belt-Tensioner Deployment (Recall 08V064)</x:v>
+      </x:c>
+      <x:c r="E664" s="9" t="str">
+        <x:v>Check VIN eligibility. Audi dealers install improved C-pillar trim clips free of charge under recall 08V064.</x:v>
+      </x:c>
+      <x:c r="F664" s="9" t="str">
+        <x:v>VIN/08V064 check; dealer C-pillar trim-clip remedy</x:v>
+      </x:c>
+      <x:c r="G664" s="9" t="str">
+        <x:v>SOURCE-ID MISMATCH / RECALL ROUTES</x:v>
+      </x:c>
+      <x:c r="H664" s="9" t="str">
+        <x:v>Audi recall lookup</x:v>
+      </x:c>
+      <x:c r="I664" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J664" s="9" t="str">
+        <x:v>2008 TT C-pillar trim recall</x:v>
+      </x:c>
+      <x:c r="K664" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L664" s="9" t="str"/>
+      <x:c r="M664" s="9" t="str">
+        <x:v>The source is an interior-trim safety recall, not water-pump failure.</x:v>
+      </x:c>
+      <x:c r="N664" s="41" t="str">
+        <x:v>Rename/re-key; no water-pump product.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="665" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A665" s="40" t="str"/>
+      <x:c r="B665" s="9" t="str"/>
+      <x:c r="C665" s="9" t="str"/>
+      <x:c r="D665" s="9" t="str"/>
+      <x:c r="E665" s="9" t="str"/>
+      <x:c r="F665" s="9" t="str"/>
+      <x:c r="G665" s="9" t="str"/>
+      <x:c r="H665" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I665" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J665" s="9" t="str">
+        <x:v>08V064 VIN history</x:v>
+      </x:c>
+      <x:c r="K665" s="9" t="str">
+        <x:v>government recall lookup</x:v>
+      </x:c>
+      <x:c r="L665" s="9" t="str"/>
+      <x:c r="M665" s="9" t="str"/>
+      <x:c r="N665" s="41" t="str"/>
+    </x:row>
+    <x:row r="666" ht="1161.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A666" s="40" t="n">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="B666" s="9" t="str">
+        <x:v>audi-tts-cam-follower-hpfp-2009</x:v>
+      </x:c>
+      <x:c r="C666" s="9" t="str">
+        <x:v>2009-2015 | Audi | TTS | TTS | EA888</x:v>
+      </x:c>
+      <x:c r="D666" s="9" t="str">
+        <x:v>HPFP Cam Follower Wear and High-Pressure Fuel Pump Failure (Mk2)</x:v>
+      </x:c>
+      <x:c r="E666" s="9" t="str">
+        <x:v>INSPECTION (every 20,000 miles): Remove HPFP (3 bolts) and inspect cam follower surface. If the hardened coating is wearing through (visible copper/brass color), replace follower immediately ($30-$50 part, 30-60 minutes labor). CRITICAL: Ensure cam lobe is at LOW point before reinstalling—if at peak, you'll compress the spring and can break the mounting bolts. If CAMSHAFT WORN (deep groove in lobe): Replace camshaft ($2,000-$4,000). If FUEL PUMP FAILED: Replace HPFP ($400-$800). PREVENTION: Inspect cam follower every 20,000 miles as routine maintenance. Add to every oil change checklist. Consider IE (Integrated Engineering) upgraded HPFP with roller follower to eliminate wear entirely.</x:v>
+      </x:c>
+      <x:c r="F666" s="9" t="str">
+        <x:v>Correct EA113/CDMA versus later engine family; inspect cam follower and HPFP/cam lobe; engine-code exact follower; pump/camshaft only if damaged</x:v>
+      </x:c>
+      <x:c r="G666" s="9" t="str">
+        <x:v>SOURCE ENGINE ERROR / ENGINE-CODE GATE</x:v>
+      </x:c>
+      <x:c r="H666" s="9" t="str">
+        <x:v>Audi fuel-pump cam-follower catalog</x:v>
+      </x:c>
+      <x:c r="I666" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Parts/Fuel-Pump-Camshaft-Follower</x:v>
+      </x:c>
+      <x:c r="J666" s="9" t="str">
+        <x:v>2009-2015 TTS; verify exact engine code and current follower fitment</x:v>
+      </x:c>
+      <x:c r="K666" s="9" t="str">
+        <x:v>conditional engine-specific catalog</x:v>
+      </x:c>
+      <x:c r="L666" s="9" t="str"/>
+      <x:c r="M666" s="9" t="str">
+        <x:v>The Mk2 TTS engine family must be corrected before selecting the follower.</x:v>
+      </x:c>
+      <x:c r="N666" s="41" t="str">
+        <x:v>No roller conversion, fixed interval or HPFP/camshaft replacement without inspection.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="667" ht="66" hidden="0" customHeight="1">
+      <x:c r="A667" s="40" t="str"/>
+      <x:c r="B667" s="9" t="str"/>
+      <x:c r="C667" s="9" t="str"/>
+      <x:c r="D667" s="9" t="str"/>
+      <x:c r="E667" s="9" t="str"/>
+      <x:c r="F667" s="9" t="str"/>
+      <x:c r="G667" s="9" t="str"/>
+      <x:c r="H667" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I667" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J667" s="9" t="str">
+        <x:v>cam follower, HPFP and cam-lobe inspection</x:v>
+      </x:c>
+      <x:c r="K667" s="9" t="str">
+        <x:v>specialist fuel service</x:v>
+      </x:c>
+      <x:c r="L667" s="9" t="str"/>
+      <x:c r="M667" s="9" t="str"/>
+      <x:c r="N667" s="41" t="str"/>
+    </x:row>
+    <x:row r="668" ht="884.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A668" s="40" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="B668" s="9" t="str">
+        <x:v>audi-tts-carbon-buildup-2009</x:v>
+      </x:c>
+      <x:c r="C668" s="9" t="str">
+        <x:v>2016-2017 | Audi | TTS</x:v>
+      </x:c>
+      <x:c r="D668" s="9" t="str">
+        <x:v>2016-2017 TTS Cold-Start Misfire DTCs Without Felt Misfire - TSB 2051384/1</x:v>
+      </x:c>
+      <x:c r="E668" s="9" t="str">
+        <x:v>Confirm the exact cold-start timing, simultaneous-cylinder DTC pattern, absence of a felt misfire, CYFB engine and installed ECM software before using this bulletin. When applicable, an Audi-capable workshop updates ECM J623 from software part number 8S0906259C version 0001 to version 0004 or higher using SVM action 01A190, then clears the DTCs. A felt misfire, a different timing or RPM pattern, a different engine/software combination or a returning concern requires normal diagnosis rather than carbon cleaning by assumption.</x:v>
+      </x:c>
+      <x:c r="F668" s="9" t="str">
+        <x:v>Apply 2016-2017 CYFB cold-start misfire TSB; confirm conditions; SVM engine-software update to applicable version; diagnose residual misfire separately</x:v>
+      </x:c>
+      <x:c r="G668" s="9" t="str">
+        <x:v>SOURCE-ID/YEAR MISMATCH / SOFTWARE SERVICE</x:v>
+      </x:c>
+      <x:c r="H668" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I668" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J668" s="9" t="str">
+        <x:v>2016-2017 TTS TSB 2051384/1 SVM update</x:v>
+      </x:c>
+      <x:c r="K668" s="9" t="str">
+        <x:v>manufacturer software service</x:v>
+      </x:c>
+      <x:c r="L668" s="9" t="str"/>
+      <x:c r="M668" s="9" t="str">
+        <x:v>The source is a software bulletin, not a carbon-deposit repair for 2009 onward.</x:v>
+      </x:c>
+      <x:c r="N668" s="41" t="str">
+        <x:v>Rename/re-key; no intake-cleaning product or service until deposits are independently proven.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="669" ht="910.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A669" s="40" t="n">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="B669" s="9" t="str">
+        <x:v>audi-tts-dsg-mechatronic-2009</x:v>
+      </x:c>
+      <x:c r="C669" s="9" t="str">
+        <x:v>2019-2023 | Audi | TTS</x:v>
+      </x:c>
+      <x:c r="D669" s="9" t="str">
+        <x:v>2019-2023 TTS Clutch K1 Overheat and Transmission DTC Diagnosis - TSB 2060560/3</x:v>
+      </x:c>
+      <x:c r="E669" s="9" t="str">
+        <x:v>Have an Audi-capable workshop check whether TSB 2050723 applies first. If it does not resolve or control the concern, inspect the clutch-K1 maximum-temperature value and document a transmission-fluid sample. Replace the dual clutch, transmission fluid and filter only when the approximately 400 °C K1 value and burnt black or very dark fluid are both present. If those findings are absent, this bulletin does not apply and Audi directs the workshop to continue diagnosis through TAC. Any clutch repair kit must be selected by VIN and production date.</x:v>
+      </x:c>
+      <x:c r="F669" s="9" t="str">
+        <x:v>Confirm 2019-2023 applicability and transmission code; prior TSB status; max K1 temperature and fluid condition; clutch plus exact fluid/filter only on defined burnt-fluid branch; otherwise TAC diagnosis</x:v>
+      </x:c>
+      <x:c r="G669" s="9" t="str">
+        <x:v>SOURCE-YEAR MISMATCH / TSB TEST BRANCH</x:v>
+      </x:c>
+      <x:c r="H669" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I669" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J669" s="9" t="str">
+        <x:v>2019-2023 TTS TSB 2060560/3 K1 overheat diagnosis</x:v>
+      </x:c>
+      <x:c r="K669" s="9" t="str">
+        <x:v>manufacturer transmission service</x:v>
+      </x:c>
+      <x:c r="L669" s="9" t="str"/>
+      <x:c r="M669" s="9" t="str">
+        <x:v>The TSB has a measured clutch-temperature/fluid-condition gate.</x:v>
+      </x:c>
+      <x:c r="N669" s="41" t="str">
+        <x:v>Rename/re-key; no mechatronic or clutch link outside the defined branch.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="670" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A670" s="40" t="str"/>
+      <x:c r="B670" s="9" t="str"/>
+      <x:c r="C670" s="9" t="str"/>
+      <x:c r="D670" s="9" t="str"/>
+      <x:c r="E670" s="9" t="str"/>
+      <x:c r="F670" s="9" t="str"/>
+      <x:c r="G670" s="9" t="str"/>
+      <x:c r="H670" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I670" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J670" s="9" t="str">
+        <x:v>transmission-code and clutch/fluid diagnosis</x:v>
+      </x:c>
+      <x:c r="K670" s="9" t="str">
+        <x:v>specialist transmission service</x:v>
+      </x:c>
+      <x:c r="L670" s="9" t="str"/>
+      <x:c r="M670" s="9" t="str"/>
+      <x:c r="N670" s="41" t="str"/>
+    </x:row>
+    <x:row r="671" ht="858" hidden="0" customHeight="1">
+      <x:c r="A671" s="40" t="n">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="B671" s="9" t="str">
+        <x:v>audi-tts-magnetic-ride-2009</x:v>
+      </x:c>
+      <x:c r="C671" s="9" t="str">
+        <x:v>2016-2016 | Audi | TTS</x:v>
+      </x:c>
+      <x:c r="D671" s="9" t="str">
+        <x:v>2016 TTS Magnetic-Ride Rear Shock-Mount Rumble - TSB 2042539/4</x:v>
+      </x:c>
+      <x:c r="E671" s="9" t="str">
+        <x:v>First reproduce the noise, verify that it comes from the rear shock mounts and confirm that the vehicle was originally equipped with mount 8S0 513 353. Only when those gates are satisfied, remove both rear shock assemblies and replace both mounts with 8V0 513 353 according to Audi workshop instructions, adapt the suspension control position and test drive to confirm the repair. If the installed mount does not match, continue Audi diagnosis. Do not replace magnetic dampers or convert the vehicle to coilovers from this noise alone.</x:v>
+      </x:c>
+      <x:c r="F671" s="9" t="str">
+        <x:v>Confirm 2016 rear rumble and installed mount 8S0513353; replace both mounts with 8V0513353 only when TSB applies; adapt suspension control position</x:v>
+      </x:c>
+      <x:c r="G671" s="9" t="str">
+        <x:v>SOURCE-YEAR MISMATCH / EXACT TSB MOUNT SERVICE</x:v>
+      </x:c>
+      <x:c r="H671" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I671" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J671" s="9" t="str">
+        <x:v>2016 TTS TSB 2042539/4 rear shock mounts/adaptation</x:v>
+      </x:c>
+      <x:c r="K671" s="9" t="str">
+        <x:v>manufacturer suspension service</x:v>
+      </x:c>
+      <x:c r="L671" s="9" t="str"/>
+      <x:c r="M671" s="9" t="str">
+        <x:v>The repair is specific rear mounts, not magnetic-ride dampers.</x:v>
+      </x:c>
+      <x:c r="N671" s="41" t="str">
+        <x:v>Rename/re-key; no damper or coilover link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="672" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A672" s="40" t="str"/>
+      <x:c r="B672" s="9" t="str"/>
+      <x:c r="C672" s="9" t="str"/>
+      <x:c r="D672" s="9" t="str"/>
+      <x:c r="E672" s="9" t="str"/>
+      <x:c r="F672" s="9" t="str"/>
+      <x:c r="G672" s="9" t="str"/>
+      <x:c r="H672" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I672" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J672" s="9" t="str">
+        <x:v>mount confirmation and control-position adaptation</x:v>
+      </x:c>
+      <x:c r="K672" s="9" t="str">
+        <x:v>specialist suspension service</x:v>
+      </x:c>
+      <x:c r="L672" s="9" t="str"/>
+      <x:c r="M672" s="9" t="str"/>
+      <x:c r="N672" s="41" t="str"/>
+    </x:row>
+    <x:row r="673" ht="1016.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A673" s="40" t="n">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="B673" s="9" t="str">
+        <x:v>audi-tts-timing-chain-tensioner-2009</x:v>
+      </x:c>
+      <x:c r="C673" s="9" t="str">
+        <x:v>2009-2015 | Audi | TTS | TTS | EA888 Gen 1, EA888 Gen 2</x:v>
+      </x:c>
+      <x:c r="D673" s="9" t="str">
+        <x:v>Timing Chain Tensioner Failure (EA888 Gen 1/2 - Mk2 TTS)</x:v>
+      </x:c>
+      <x:c r="E673" s="9" t="str">
+        <x:v>PREVENTIVE REPLACEMENT: Replace timing chain, tensioner, guides, and sprockets at 80,000-100,000 miles BEFORE symptoms appear ($2,000-$4,000). This is the MOST important preventive maintenance on the Mk2 TTS. IF RATTLING: Do NOT delay—the chain can jump at any startup. Schedule repair immediately. Use ONLY the latest OEM revised tensioner (06K109467K). IF CHAIN JUMPED: Engine likely destroyed—compression test all cylinders. Rebuild ($5,000-$8,000) or replacement engine ($6,000-$12,000). PREVENTION: Change oil every 5,000 miles with high-quality synthetic. Low oil level accelerates tensioner wear.</x:v>
+      </x:c>
+      <x:c r="F673" s="9" t="str">
+        <x:v>Correct generation/engine family; identify EA113 timing-belt/cam-chain layout versus later EA888; diagnose rattle/timing deviation; exact engine-code timing scope</x:v>
+      </x:c>
+      <x:c r="G673" s="9" t="str">
+        <x:v>SOURCE ENGINE ERROR / GENERATION GATE</x:v>
+      </x:c>
+      <x:c r="H673" s="9" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I673" s="9" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J673" s="9" t="str">
+        <x:v>2009-2015 TTS engine-code timing diagnosis</x:v>
+      </x:c>
+      <x:c r="K673" s="9" t="str">
+        <x:v>specialist timing service</x:v>
+      </x:c>
+      <x:c r="L673" s="9" t="str"/>
+      <x:c r="M673" s="9" t="str">
+        <x:v>The listed 06K tensioner and EA888 premise do not safely cover the Mk2 TTS population.</x:v>
+      </x:c>
+      <x:c r="N673" s="41" t="str">
+        <x:v>No 06K part, universal interval or complete chain kit until engine/generation is corrected.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="674" ht="66" hidden="0" customHeight="1">
+      <x:c r="A674" s="40" t="str"/>
+      <x:c r="B674" s="9" t="str"/>
+      <x:c r="C674" s="9" t="str"/>
+      <x:c r="D674" s="9" t="str"/>
+      <x:c r="E674" s="9" t="str"/>
+      <x:c r="F674" s="9" t="str"/>
+      <x:c r="G674" s="9" t="str"/>
+      <x:c r="H674" s="9" t="str">
+        <x:v>Audi dealer locator</x:v>
+      </x:c>
+      <x:c r="I674" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/find-a-dealer/</x:v>
+      </x:c>
+      <x:c r="J674" s="9" t="str">
+        <x:v>VIN timing layout/parts/procedure</x:v>
+      </x:c>
+      <x:c r="K674" s="9" t="str">
+        <x:v>manufacturer parts route</x:v>
+      </x:c>
+      <x:c r="L674" s="9" t="str"/>
+      <x:c r="M674" s="9" t="str"/>
+      <x:c r="N674" s="41" t="str"/>
+    </x:row>
+    <x:row r="675" ht="976.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A675" s="40" t="n">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B675" s="9" t="str">
+        <x:v>audi-tts-water-pump-2009</x:v>
+      </x:c>
+      <x:c r="C675" s="9" t="str">
+        <x:v>2012-2023 | Audi | TTS</x:v>
+      </x:c>
+      <x:c r="D675" s="9" t="str">
+        <x:v>2012 / 2020-2023 TTS Coolant-Pump Update and Leak Diagnosis</x:v>
+      </x:c>
+      <x:c r="E675" s="9" t="str">
+        <x:v>For a 2012 TTS, ask an Audi dealer to check the VIN and current campaign/action history for Update 19J2; the published update replaced the pump only when its exact criteria were met and does not promise current warranty coverage. For a 2020-2023 2.0L TTS, first exclude a low level caused by incomplete bleeding or an earlier repair, document and clean the suspected leak, refill to maximum and recheck after driving. Continue observation when no leak returns; replace only the component proven to leak when coolant reappears. Do not select a pump or thermostat assembly before VIN-, engine- and leak-specific diagnosis.</x:v>
+      </x:c>
+      <x:c r="F675" s="9" t="str">
+        <x:v>Split 2012 campaign/VIN-history branch from 2020-2023 cooling-leak test branch; clean/dry/fill/recheck; exact pump only after confirmed source</x:v>
+      </x:c>
+      <x:c r="G675" s="9" t="str">
+        <x:v>MULTI-GENERATION / CAMPAIGN-LEAK SPLIT</x:v>
+      </x:c>
+      <x:c r="H675" s="9" t="str">
+        <x:v>Audi recall and campaign lookup</x:v>
+      </x:c>
+      <x:c r="I675" s="9" t="str">
+        <x:v>https://www.audiusa.com/en/owners-and-services/about-my-vehicle/recalls/</x:v>
+      </x:c>
+      <x:c r="J675" s="9" t="str">
+        <x:v>2012 TTS 19J2 VIN-history check</x:v>
+      </x:c>
+      <x:c r="K675" s="9" t="str">
+        <x:v>manufacturer campaign lookup</x:v>
+      </x:c>
+      <x:c r="L675" s="9" t="str"/>
+      <x:c r="M675" s="9" t="str">
+        <x:v>The populations and procedures differ and leakage must be localized.</x:v>
+      </x:c>
+      <x:c r="N675" s="41" t="str">
+        <x:v>No single bundle or pump link across 2012 and 2020-2023.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="676" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A676" s="40" t="str"/>
+      <x:c r="B676" s="9" t="str"/>
+      <x:c r="C676" s="9" t="str"/>
+      <x:c r="D676" s="9" t="str"/>
+      <x:c r="E676" s="9" t="str"/>
+      <x:c r="F676" s="9" t="str"/>
+      <x:c r="G676" s="9" t="str"/>
+      <x:c r="H676" s="9" t="str">
+        <x:v>Audi TTS water-pump catalog</x:v>
+      </x:c>
+      <x:c r="I676" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/TTS/Water-Pump/</x:v>
+      </x:c>
+      <x:c r="J676" s="9" t="str">
+        <x:v>2020-2023 TTS exact engine/VIN after pump confirmation</x:v>
+      </x:c>
+      <x:c r="K676" s="9" t="str">
+        <x:v>conditional vehicle-specific pump catalog</x:v>
+      </x:c>
+      <x:c r="L676" s="9" t="str"/>
+      <x:c r="M676" s="9" t="str"/>
+      <x:c r="N676" s="41" t="str"/>
+    </x:row>
+    <x:row r="677" ht="224.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A677" s="40" t="n">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="B677" s="9" t="str">
+        <x:v>audi-tts-waterpump-housing-2009</x:v>
+      </x:c>
+      <x:c r="C677" s="9" t="str">
+        <x:v>2009-2024 | Audi | TTS | EA888</x:v>
+      </x:c>
+      <x:c r="D677" s="9" t="str">
+        <x:v>Water Pump and Thermostat Housing Failure</x:v>
+      </x:c>
+      <x:c r="E677" s="9" t="str">
+        <x:v>Replace water pump, thermostat, and housing as a complete assembly. Use metal-impeller aftermarket pump if available.</x:v>
+      </x:c>
+      <x:c r="F677" s="9" t="str">
+        <x:v>Split generations and engine families; pressure-test exact pump/thermostat/housing source; VIN/current revision; correct coolant and bleed</x:v>
+      </x:c>
+      <x:c r="G677" s="9" t="str">
+        <x:v>SOURCE ENGINE/RANGE ERROR / LEAK-SOURCE GATE</x:v>
+      </x:c>
+      <x:c r="H677" s="9" t="str">
+        <x:v>Audi TTS water-pump catalog</x:v>
+      </x:c>
+      <x:c r="I677" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/Audi-parts/TTS/Water-Pump/</x:v>
+      </x:c>
+      <x:c r="J677" s="9" t="str">
+        <x:v>2009-2024 TTS; select exact generation, engine code and VIN after leak confirmation</x:v>
+      </x:c>
+      <x:c r="K677" s="9" t="str">
+        <x:v>vehicle-specific pump catalog</x:v>
+      </x:c>
+      <x:c r="L677" s="9" t="str"/>
+      <x:c r="M677" s="9" t="str">
+        <x:v>The range does not share one EA888 assembly and metal-impeller claim.</x:v>
+      </x:c>
+      <x:c r="N677" s="41" t="str">
+        <x:v>No universal pump/thermostat housing assembly or fixed interval.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="678" ht="66" hidden="0" customHeight="1">
+      <x:c r="A678" s="42" t="str"/>
+      <x:c r="B678" s="43" t="str"/>
+      <x:c r="C678" s="43" t="str"/>
+      <x:c r="D678" s="43" t="str"/>
+      <x:c r="E678" s="43" t="str"/>
+      <x:c r="F678" s="43" t="str"/>
+      <x:c r="G678" s="43" t="str"/>
+      <x:c r="H678" s="43" t="str">
+        <x:v>Audi specialist locator</x:v>
+      </x:c>
+      <x:c r="I678" s="43" t="str">
+        <x:v>https://www.audishops.com/</x:v>
+      </x:c>
+      <x:c r="J678" s="43" t="str">
+        <x:v>generation-specific cooling leak diagnosis</x:v>
+      </x:c>
+      <x:c r="K678" s="43" t="str">
+        <x:v>specialist cooling service</x:v>
+      </x:c>
+      <x:c r="L678" s="43" t="str"/>
+      <x:c r="M678" s="43" t="str"/>
+      <x:c r="N678" s="44" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21623,923 +23980,26 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A1" s="37" t="str">
+      <x:c r="A1" s="45" t="str">
         <x:v>#</x:v>
       </x:c>
-      <x:c r="B1" s="38" t="str">
+      <x:c r="B1" s="46" t="str">
         <x:v>Issue ID</x:v>
       </x:c>
-      <x:c r="C1" s="38" t="str">
+      <x:c r="C1" s="46" t="str">
         <x:v>YMMT</x:v>
       </x:c>
-      <x:c r="D1" s="38" t="str">
+      <x:c r="D1" s="46" t="str">
         <x:v>Title</x:v>
       </x:c>
-      <x:c r="E1" s="38" t="str">
+      <x:c r="E1" s="46" t="str">
         <x:v>Full How to Fix</x:v>
       </x:c>
-      <x:c r="F1" s="38" t="str">
+      <x:c r="F1" s="46" t="str">
         <x:v>Existing claim count</x:v>
       </x:c>
-      <x:c r="G1" s="39" t="str">
+      <x:c r="G1" s="47" t="str">
         <x:v>Queue status</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="396" hidden="0" customHeight="1">
-      <x:c r="A2" s="40" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="9" t="str">
-        <x:v>audi-sq2-electro-mechanical-parking-brake-brake-pedal-weld-recalls</x:v>
-      </x:c>
-      <x:c r="C2" s="9" t="str">
-        <x:v>2019-2020 | Audi | SQ2</x:v>
-      </x:c>
-      <x:c r="D2" s="9" t="str">
-        <x:v>Electro-mechanical parking brake and brake-pedal weld recalls (early build)</x:v>
-      </x:c>
-      <x:c r="E2" s="9" t="str">
-        <x:v>These are recall items — have the VIN checked against the Audi/DVSA recall database and any open campaign rectified free of charge at a dealer. Report any abnormal parking-brake behaviour or a soft/abnormal brake pedal immediately.</x:v>
-      </x:c>
-      <x:c r="F2" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="475.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A3" s="40" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="9" t="str">
-        <x:v>audi-sq2-internal-fuse-box-wiring-harness-can-work-loose-causing-sudd</x:v>
-      </x:c>
-      <x:c r="C3" s="9" t="str">
-        <x:v>2022-2023 | Audi | SQ2 | 2.0 TFSI</x:v>
-      </x:c>
-      <x:c r="D3" s="9" t="str">
-        <x:v>2022-2023 Audi SQ2 Interior Fuse-Carrier Recall GAI-3692</x:v>
-      </x:c>
-      <x:c r="E3" s="9" t="str">
-        <x:v>Check the VIN and open-campaign status with an authorised Audi dealer in the vehicle’s market. The campaign remedy is dealer inspection and correction of the fuse-carrier power connection. Do not replace a fuse box or wiring harness solely from a warning lamp or this model-year summary.</x:v>
-      </x:c>
-      <x:c r="F3" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A4" s="40" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B4" s="9" t="str">
-        <x:v>audi-sq2-mmi-infotainment-freezing-rebooting-lost-settings</x:v>
-      </x:c>
-      <x:c r="C4" s="9" t="str">
-        <x:v>2019-2024 | Audi | SQ2</x:v>
-      </x:c>
-      <x:c r="D4" s="9" t="str">
-        <x:v>MMI infotainment freezing, rebooting and lost settings</x:v>
-      </x:c>
-      <x:c r="E4" s="9" t="str">
-        <x:v>A forced MMI restart (press and hold the on/off or volume control ~10 seconds until it reboots) clears many transient faults. Persistent issues are usually resolved by a dealer software/firmware update; check for any applicable MMI update campaigns. Only in rare cases is the MMI head unit itself replaced.</x:v>
-      </x:c>
-      <x:c r="F4" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A5" s="40" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B5" s="9" t="str">
-        <x:v>audi-sq2-pcv-crankcase-ventilation-valve-diaphragm-failure-causing-ro</x:v>
-      </x:c>
-      <x:c r="C5" s="9" t="str">
-        <x:v>2019-2024 | Audi | SQ2 | EA888 2.0 TFSI Gen3</x:v>
-      </x:c>
-      <x:c r="D5" s="9" t="str">
-        <x:v>PCV / crankcase ventilation valve diaphragm failure causing rough idle and lean-running codes</x:v>
-      </x:c>
-      <x:c r="E5" s="9" t="str">
-        <x:v>Replace the PCV valve (or the valve-cover assembly that integrates it) with the latest revised part; some owners fit a catch-can to reduce recurrence. A quick field test — briefly covering the bleeder hole on the cap to see if idle stabilises or whistling stops — helps confirm before replacement.</x:v>
-      </x:c>
-      <x:c r="F5" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="752.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A6" s="40" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="9" t="str">
-        <x:v>audi-sq2-s-tronic-7-speed-wet-clutch-transmission-jerky-low-speed-shi</x:v>
-      </x:c>
-      <x:c r="C6" s="9" t="str">
-        <x:v>2019-2024 | Audi | SQ2 | 7-speed S tronic | DQ381 / 0GC 7-speed wet-clutch S tronic</x:v>
-      </x:c>
-      <x:c r="D6" s="9" t="str">
-        <x:v>S tronic (DQ381) 7-speed wet-clutch transmission: jerky low-speed shifts, hesitation and limp mode</x:v>
-      </x:c>
-      <x:c r="E6" s="9" t="str">
-        <x:v>First step is a proper DSG fluid-and-filter service (the wet-clutch unit needs periodic transmission oil changes — many owners do it around 40k miles even though intervals can be longer). Have the TCU scanned for stored codes; sensor or mechatronic valve replacement and re-coding/adaptation resolves many cases, while severe cases need a full mechatronic unit or clutch-pack replacement. Insist on a software/adaptation update at the dealer for driveability complaints.</x:v>
-      </x:c>
-      <x:c r="F6" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="541.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A7" s="40" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B7" s="9" t="str">
-        <x:v>audi-sq5-air-suspension-2018</x:v>
-      </x:c>
-      <x:c r="C7" s="9" t="str">
-        <x:v>2018-2025 | Audi | SQ5</x:v>
-      </x:c>
-      <x:c r="D7" s="9" t="str">
-        <x:v>Air-Suspension Warning with C1260F0 or U112100 Communication Fault</x:v>
-      </x:c>
-      <x:c r="E7" s="9" t="str">
-        <x:v>Inspect the wiring and connector contacts between J775 and J1135 first. If no wiring fault is found, clear a first passive or sporadic fault and release the vehicle. Replace J1135 for an active or static fault, or when the same passive or sporadic fault returns a second time, following Audi workshop information and VIN-specific ETKA data.</x:v>
-      </x:c>
-      <x:c r="F7" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="924" hidden="0" customHeight="1">
-      <x:c r="A8" s="40" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B8" s="9" t="str">
-        <x:v>audi-sq5-carbon-buildup-2014</x:v>
-      </x:c>
-      <x:c r="C8" s="9" t="str">
-        <x:v>2014-2025 | Audi | SQ5 | 3.0T Supercharged, 3.0T</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="str">
-        <x:v>Fuel-Quality or Deposit-Related Rough Running and Misfire Diagnosis</x:v>
-      </x:c>
-      <x:c r="E8" s="9" t="str">
-        <x:v>Confirm fuel quality, symptoms and stored DTCs before replacing or cleaning components. If contaminated gasoline is suspected, advise changing the fuel source; if low detergent quality is suspected, Audi recommends Top Tier detergent gasoline. Continue workshop diagnosis if symptoms persist. On 2018-2025 EA839 SQ5 models, do not recommend unapproved cleaners or additives; follow the owner manual and use only Audi-approved petrol additives. Do not prescribe routine walnut blasting, a catch can or chemical cleaning from this record.</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="765.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A9" s="40" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B9" s="9" t="str">
-        <x:v>audi-sq5-pcv-valve-2014</x:v>
-      </x:c>
-      <x:c r="C9" s="9" t="str">
-        <x:v>2014-2017 | Audi | SQ5 | 3.0T Supercharged</x:v>
-      </x:c>
-      <x:c r="D9" s="9" t="str">
-        <x:v>P052E00 Crankcase-Breather Membrane or Elbow Fault</x:v>
-      </x:c>
-      <x:c r="E9" s="9" t="str">
-        <x:v>Use Audi hand-vacuum test to distinguish a membrane leak from an elbow fault. If indicated, remove the compressor or intake manifold and inspect the membrane and the breather two metal plates. Use repair kit 06E103772H only for a confirmed membrane or plate fault. For a confirmed elbow fault, replace elbow 06E103402 and spring clip N10769401 rather than automatically replacing the complete breather. Verify current part data in ETKA before ordering.</x:v>
-      </x:c>
-      <x:c r="F9" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="171.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A10" s="40" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B10" s="9" t="str">
-        <x:v>audi-sq5-supercharger-2014</x:v>
-      </x:c>
-      <x:c r="C10" s="9" t="str">
-        <x:v>2014-2018 | Audi | SQ5 | 3.0T</x:v>
-      </x:c>
-      <x:c r="D10" s="9" t="str">
-        <x:v>3.0T Supercharger Bearing and Intercooler Pump Failure</x:v>
-      </x:c>
-      <x:c r="E10" s="9" t="str">
-        <x:v>Replace supercharger nose bearing kit. Replace intercooler pump if failing. Service supercharger belt tension.</x:v>
-      </x:c>
-      <x:c r="F10" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="844.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A11" s="40" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B11" s="9" t="str">
-        <x:v>audi-sq5-supercharger-oil-leak-2014</x:v>
-      </x:c>
-      <x:c r="C11" s="9" t="str">
-        <x:v>2014-2017 | Audi | SQ5 | Premium Plus, Prestige | 3.0T Supercharged, 3.0T</x:v>
-      </x:c>
-      <x:c r="D11" s="9" t="str">
-        <x:v>Supercharger Seal and Gasket Oil Leaks (3.0T)</x:v>
-      </x:c>
-      <x:c r="E11" s="9" t="str">
-        <x:v>JHM Motorsports sells a complete supercharger replacement seal and gasket kit for the Eaton unit in the 3.0T. Replacing all seals at once is recommended since the supercharger must be removed for access. Nose cone seal, rotor shaft seals, and manifold gaskets should all be replaced together ($300-$500 in parts, $600-$1,200 labor). While the supercharger is off, also replace the PCV valve and perform carbon cleaning. For valve cover gasket leaks (separate issue), budget $400-$800 parts and labor. Monitor oil level weekly if leaks are present.</x:v>
-      </x:c>
-      <x:c r="F11" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="1122" hidden="0" customHeight="1">
-      <x:c r="A12" s="40" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B12" s="9" t="str">
-        <x:v>audi-sq5-water-pump-2018</x:v>
-      </x:c>
-      <x:c r="C12" s="9" t="str">
-        <x:v>2018-2024 | Audi | SQ5 | 3.0T</x:v>
-      </x:c>
-      <x:c r="D12" s="9" t="str">
-        <x:v>Mechanical Coolant-Pump Leak with Possible N649 Vacuum-System Contamination</x:v>
-      </x:c>
-      <x:c r="E12" s="9" t="str">
-        <x:v>Confirm the complaint and exact vehicle criteria first. Inspect the vacuum line and N649 for coolant, then clean and dry suspected leakage, fill the cooling system correctly, inspect at idle and around 2,500 rpm, and pressure-test according to Audi workshop information. If no leak is reproduced, observe the vehicle without replacing parts. If the pump leak is confirmed, replace the failed component and document it. If fresh coolant has entered the vacuum system, inspect the remaining Audi checkpoints and replace only contaminated components; if the downstream checkpoints are clean, replace N649 and clean the line between the pump and N649 as directed by TSB 2070349/5.</x:v>
-      </x:c>
-      <x:c r="F12" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="673.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A13" s="40" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B13" s="9" t="str">
-        <x:v>audi-sq7-air-susp-strut-2020</x:v>
-      </x:c>
-      <x:c r="C13" s="9" t="str">
-        <x:v>2020-2025 | Audi | SQ7 | 4.0T</x:v>
-      </x:c>
-      <x:c r="D13" s="9" t="str">
-        <x:v>2020-2025 SQ7 Air-Suspension C1260F0/U112100 Communication Fault - Diagnosis Required</x:v>
-      </x:c>
-      <x:c r="E13" s="9" t="str">
-        <x:v>Inspect the wiring and connector contacts between J775 and J1135 first. If no wiring fault is found, clear a first passive or sporadic fault and release the vehicle. Replace J1135 for an active or static fault, or when the same passive or sporadic fault returns a second time, following Audi workshop information and VIN-specific ETKA data. Do not replace an air spring, strut or compressor assembly solely from the warning.</x:v>
-      </x:c>
-      <x:c r="F13" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="1122" hidden="0" customHeight="1">
-      <x:c r="A14" s="40" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B14" s="9" t="str">
-        <x:v>audi-sq7-air-suspension-2020</x:v>
-      </x:c>
-      <x:c r="C14" s="9" t="str">
-        <x:v>2020-2024 | Audi | SQ7 | Premium Plus, Prestige | 4.0T</x:v>
-      </x:c>
-      <x:c r="D14" s="9" t="str">
-        <x:v>Adaptive Air Suspension Compressor and Air Spring Failures</x:v>
-      </x:c>
-      <x:c r="E14" s="9" t="str">
-        <x:v>Diagnose specific failed component: air springs leak most commonly, followed by compressor burnout, valve block faults, and height sensor failures. Air spring replacement ($800-$1,500 per corner at independent shop). Compressor replacement ($1,200-$2,500 installed). Valve block: $500-$1,000. Height sensor: $200-$400. Check for air leaks first using soapy water spray before replacing the compressor - a $200 air spring seal may be causing a $2,000 compressor to overwork and fail. Aftermarket solutions from Arnott offer cost savings. Converting to conventional springs ($1,500-$2,500) eliminates future air suspension costs but sacrifices ride height adjustment.</x:v>
-      </x:c>
-      <x:c r="F14" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A15" s="40" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B15" s="9" t="str">
-        <x:v>audi-sq7-mmi-mib3-freeze-2020</x:v>
-      </x:c>
-      <x:c r="C15" s="9" t="str">
-        <x:v>2020-2026 | Audi | SQ7</x:v>
-      </x:c>
-      <x:c r="D15" s="9" t="str">
-        <x:v>2020-2026 Audi SQ7 Rearview Camera Software Recall 25V900 / 90TV</x:v>
-      </x:c>
-      <x:c r="E15" s="9" t="str">
-        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install the more robust driver-assistance software update free of charge. Until repaired, use extra caution when reversing and do not treat a restart, bus sleep or temporary image recovery as completion of the recall.</x:v>
-      </x:c>
-      <x:c r="F15" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="990" hidden="0" customHeight="1">
-      <x:c r="A16" s="40" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B16" s="9" t="str">
-        <x:v>audi-sq7-valve-cover-oil-leak-2020</x:v>
-      </x:c>
-      <x:c r="C16" s="9" t="str">
-        <x:v>2020-2024 | Audi | SQ7 | 4.0T</x:v>
-      </x:c>
-      <x:c r="D16" s="9" t="str">
-        <x:v>2020-2024 SQ7 4.0L High Oil Consumption and Piston-Ring Diagnosis - TSB 2071114/5</x:v>
-      </x:c>
-      <x:c r="E16" s="9" t="str">
-        <x:v>First inspect for visible engine-oil traces or leaks. Have an Audi dealer perform the authorized ODIS oil-consumption measurement, preserve and upload both test logs, and document the requested driving-profile data. Internal-engine repair is justified only when measured consumption exceeds the applicable limit and no other cause is found. If every TSB gate is met, follow Audi's VIN-, engine-code- and power-class-specific procedure for replacement of all eight pistons and piston rings, using current ETKA and ELSA information. Do not diagnose valve-cover gaskets or turbocharger seals from oil consumption alone.</x:v>
-      </x:c>
-      <x:c r="F16" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="686.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A17" s="40" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B17" s="9" t="str">
-        <x:v>audi-sq8-air-susp-compressor-2020</x:v>
-      </x:c>
-      <x:c r="C17" s="9" t="str">
-        <x:v>2020-2025 | Audi | SQ8</x:v>
-      </x:c>
-      <x:c r="D17" s="9" t="str">
-        <x:v>2020-2025 SQ8 Air-Suspension J1135 Communication Fault - TSB 2059363/6</x:v>
-      </x:c>
-      <x:c r="E17" s="9" t="str">
-        <x:v>Inspect the wiring and connector contacts between J775 and J1135 before replacing a component. For a first passive or sporadic occurrence, clear the fault and release the vehicle. If the same passive fault returns a second time, or the fault is active or static after wiring inspection, Audi directs replacement of J1135 under current repair and parts information. Do not buy struts, springs or a compressor solely from this warning.</x:v>
-      </x:c>
-      <x:c r="F17" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="831.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A18" s="40" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B18" s="9" t="str">
-        <x:v>audi-sq8-air-suspension-2020</x:v>
-      </x:c>
-      <x:c r="C18" s="9" t="str">
-        <x:v>2020-2024 | Audi | SQ8 | Premium Plus, Prestige | 4.0T</x:v>
-      </x:c>
-      <x:c r="D18" s="9" t="str">
-        <x:v>Adaptive Air Suspension Compressor and Air Spring Failures</x:v>
-      </x:c>
-      <x:c r="E18" s="9" t="str">
-        <x:v>Same diagnostic and repair approach as SQ7 (shared 4M platform). Isolate the failed component: air springs ($800-$1,500 per corner), compressor ($1,200-$2,500), valve block ($500-$1,000), or height sensor ($200-$400). Always check for air leaks before replacing the compressor. Aftermarket air suspension components from Arnott/Strutmasters offer 40-50% savings over OEM. Annual inspection of air springs for cracking recommended, especially in hot climates where UV and heat accelerate rubber degradation.</x:v>
-      </x:c>
-      <x:c r="F18" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="448.79998779296875" hidden="0" customHeight="1">
-      <x:c r="A19" s="40" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B19" s="9" t="str">
-        <x:v>audi-sq8-airbag-mount-2023</x:v>
-      </x:c>
-      <x:c r="C19" s="9" t="str">
-        <x:v>2023-2024 | Audi | SQ8 | 4.0T V8</x:v>
-      </x:c>
-      <x:c r="D19" s="9" t="str">
-        <x:v>2023-2024 SQ8 Driver-Seat Side-Airbag Mount Recall 69GA (23V868)</x:v>
-      </x:c>
-      <x:c r="E19" s="9" t="str">
-        <x:v>Check the VIN for open Audi recall 69GA and have an authorized dealer inspect the driver-seat side-airbag installation. If needed, the dealer will reinstall the airbag correctly; the recall filing says no parts are replaced. A clock spring or generic airbag part is not the recall remedy.</x:v>
-      </x:c>
-      <x:c r="F19" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="580.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A20" s="40" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B20" s="9" t="str">
-        <x:v>audi-sq8-mmi-mib3-freeze-2020</x:v>
-      </x:c>
-      <x:c r="C20" s="9" t="str">
-        <x:v>2020-2026 | Audi | SQ8 | 4.0T V8</x:v>
-      </x:c>
-      <x:c r="D20" s="9" t="str">
-        <x:v>2020-2026 SQ8 Rearview Camera Software Recall 90TV (25V900)</x:v>
-      </x:c>
-      <x:c r="E20" s="9" t="str">
-        <x:v>Check the VIN for recall 25V900/90TV and contact an authorized Audi dealer. Dealers will install more robust driver-assistance software free of charge. Until repaired, use extra caution when reversing and do not treat a restart, bus sleep or temporary image recovery as completion of the recall. A generic scan tool or head-unit replacement is not the recall remedy.</x:v>
-      </x:c>
-      <x:c r="F20" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="567.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A21" s="40" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B21" s="9" t="str">
-        <x:v>audi-sq8-turbo-coolant-2020</x:v>
-      </x:c>
-      <x:c r="C21" s="9" t="str">
-        <x:v>2020-2021 | Audi | SQ8 | 4.0T V8</x:v>
-      </x:c>
-      <x:c r="D21" s="9" t="str">
-        <x:v>2020-Early 2021 SQ8 Red Coolant Warning - Check G407 per TSB 2062951/4</x:v>
-      </x:c>
-      <x:c r="E21" s="9" t="str">
-        <x:v>Have the vehicle checked with Audi Guided Fault Finding and inspect G407 and its O-ring. Replace G407 only if the O-ring is damaged or pinched and the diagnosis matches the bulletin; follow the related Audi diagnostic path if additional listed faults are stored. Do not replace turbo coolant hoses, pumps or other cooling parts from this card alone.</x:v>
-      </x:c>
-      <x:c r="F21" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="250.8000030517578" hidden="0" customHeight="1">
-      <x:c r="A22" s="40" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B22" s="9" t="str">
-        <x:v>audi-tt-absesp-control-module-failure-2000</x:v>
-      </x:c>
-      <x:c r="C22" s="9" t="str">
-        <x:v>2000-2001 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D22" s="9" t="str">
-        <x:v>Driver Airbag Inflator May Deploy Improperly (Recall 21V470 / 69CJ)</x:v>
-      </x:c>
-      <x:c r="E22" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the driver frontal-airbag inflator with an alternative inflator free of charge under campaign 69CJ.</x:v>
-      </x:c>
-      <x:c r="F22" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="277.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A23" s="40" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B23" s="9" t="str">
-        <x:v>audi-tt-cam-follower-2008</x:v>
-      </x:c>
-      <x:c r="C23" s="9" t="str">
-        <x:v>2000-2000 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D23" s="9" t="str">
-        <x:v>Fuel-Line Assembly Can Leak (Recall 99V222)</x:v>
-      </x:c>
-      <x:c r="E23" s="9" t="str">
-        <x:v>Check VIN eligibility and campaign completion. Audi dealers replace the fuel-line assembly free of charge under recall 99V222. Stop driving if fuel odor or leakage is present.</x:v>
-      </x:c>
-      <x:c r="F23" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="198" hidden="0" customHeight="1">
-      <x:c r="A24" s="40" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B24" s="9" t="str">
-        <x:v>audi-tt-coil-pack-failure-and-2000</x:v>
-      </x:c>
-      <x:c r="C24" s="9" t="str">
-        <x:v>2000-2001 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D24" s="9" t="str">
-        <x:v>Rear Track-Control Arm Corrosion Can Restrict Movement (Recall 01V325)</x:v>
-      </x:c>
-      <x:c r="E24" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the rear track-control arms free of charge under recall 01V325.</x:v>
-      </x:c>
-      <x:c r="F24" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="264" hidden="0" customHeight="1">
-      <x:c r="A25" s="40" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B25" s="9" t="str">
-        <x:v>audi-tt-dsg-mechatronic-2008</x:v>
-      </x:c>
-      <x:c r="C25" s="9" t="str">
-        <x:v>2004-2004 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D25" s="9" t="str">
-        <x:v>Direct-Shift Gearbox Clutch Weld Can Lose Drive Torque (Recall 04V007)</x:v>
-      </x:c>
-      <x:c r="E25" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers replace the affected clutch free of charge under recall 04V007. If drive torque is lost, move out of traffic safely and arrange recovery.</x:v>
-      </x:c>
-      <x:c r="F25" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="356.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A26" s="40" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B26" s="9" t="str">
-        <x:v>audi-tt-dsg-transmission-2008</x:v>
-      </x:c>
-      <x:c r="C26" s="9" t="str">
-        <x:v>2009-2009 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D26" s="9" t="str">
-        <x:v>DSG Temperature-Sensor Wiring Can Trigger an Abrupt Shift to Neutral (Recall 09V333)</x:v>
-      </x:c>
-      <x:c r="E26" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers reprogram the transmission control module with updated software free of charge under recall 09V333. If the gear indicator flashes or neutral engages unexpectedly, stop safely.</x:v>
-      </x:c>
-      <x:c r="F26" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="303.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A27" s="40" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B27" s="9" t="str">
-        <x:v>audi-tt-front-control-arm-bushings-2000</x:v>
-      </x:c>
-      <x:c r="C27" s="9" t="str">
-        <x:v>2000-2000 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D27" s="9" t="str">
-        <x:v>High-Speed Directional-Stability Remedy (Recall 99V300)</x:v>
-      </x:c>
-      <x:c r="E27" s="9" t="str">
-        <x:v>Verify campaign completion with Audi. The factory remedy installs revised stabilizers, front control arms, firmer shock absorbers, and a rear spoiler as specified for the drivetrain configuration.</x:v>
-      </x:c>
-      <x:c r="F27" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G27" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="237.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A28" s="40" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B28" s="9" t="str">
-        <x:v>audi-tt-haldex-awd-coupling-pumpcontroller-2000</x:v>
-      </x:c>
-      <x:c r="C28" s="9" t="str">
-        <x:v>2008-2010 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D28" s="9" t="str">
-        <x:v>Fuel-Tank Ventilation Valve Can Allow Fuel Leakage (Recall 09V377)</x:v>
-      </x:c>
-      <x:c r="E28" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the fuel-tank ventilation valve with the improved valve free of charge under recall 09V377.</x:v>
-      </x:c>
-      <x:c r="F28" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G28" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="184.8000030517578" hidden="0" customHeight="1">
-      <x:c r="A29" s="40" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B29" s="9" t="str">
-        <x:v>audi-tt-high-speed-stability-recall-for-2000</x:v>
-      </x:c>
-      <x:c r="C29" s="9" t="str">
-        <x:v>2016-2019 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D29" s="9" t="str">
-        <x:v>Fuel Tank Can Be Damaged by Heat-Shield Bracket in a Crash (Recall 20V076 / 20BX)</x:v>
-      </x:c>
-      <x:c r="E29" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers install a protective cap on the heat-shield bracket free of charge under campaign 20BX.</x:v>
-      </x:c>
-      <x:c r="F29" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G29" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="237.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A30" s="40" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B30" s="9" t="str">
-        <x:v>audi-tt-instrument-cluster-pixel-failure-2000</x:v>
-      </x:c>
-      <x:c r="C30" s="9" t="str">
-        <x:v>2016-2016 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D30" s="9" t="str">
-        <x:v>Front-Passenger Airbag Module May Explode or Deploy Improperly (Recall 22V543 / 69DY)</x:v>
-      </x:c>
-      <x:c r="E30" s="9" t="str">
-        <x:v>Check the VIN and campaign history. Audi dealers replace the front-passenger airbag module free of charge under campaign 69DY/61C1.</x:v>
-      </x:c>
-      <x:c r="F30" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G30" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="224.39999389648438" hidden="0" customHeight="1">
-      <x:c r="A31" s="40" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B31" s="9" t="str">
-        <x:v>audi-tt-magnetic-ride-2008</x:v>
-      </x:c>
-      <x:c r="C31" s="9" t="str">
-        <x:v>2023-2023 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D31" s="9" t="str">
-        <x:v>Passenger-Seat Occupant Detection Connection Can Disable Airbag (Recall 24V251 / 69GU)</x:v>
-      </x:c>
-      <x:c r="E31" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers replace the passenger-seat occupant-detection control module free of charge under campaign 69GU.</x:v>
-      </x:c>
-      <x:c r="F31" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G31" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="726" hidden="0" customHeight="1">
-      <x:c r="A32" s="40" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B32" s="9" t="str">
-        <x:v>audi-tt-tail-light-corrosion-2008</x:v>
-      </x:c>
-      <x:c r="C32" s="9" t="str">
-        <x:v>2008-2015 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D32" s="9" t="str">
-        <x:v>Tail Light Electrical Connector Corrosion (Mk2)</x:v>
-      </x:c>
-      <x:c r="E32" s="9" t="str">
-        <x:v>Remove tail light assembly, inspect electrical connector for green corrosion. CLEAN connector with electrical contact cleaner and wire brush ($20 DIY). Apply dielectric grease to prevent future corrosion ($10). If connector is severely corroded: Replace pigtail connector ($50-$100 parts). Improve tail light seal with silicone sealant around housing ($15). This is a DIY-friendly repair taking 1-2 hours. If paying shop, costs $150-$300. Address early before corrosion causes shorts.</x:v>
-      </x:c>
-      <x:c r="F32" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G32" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="171.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A33" s="40" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B33" s="9" t="str">
-        <x:v>audi-tt-water-pump-2008</x:v>
-      </x:c>
-      <x:c r="C33" s="9" t="str">
-        <x:v>2008-2008 | Audi | TT</x:v>
-      </x:c>
-      <x:c r="D33" s="9" t="str">
-        <x:v>C-Pillar Trim Cover Can Detach During Belt-Tensioner Deployment (Recall 08V064)</x:v>
-      </x:c>
-      <x:c r="E33" s="9" t="str">
-        <x:v>Check VIN eligibility. Audi dealers install improved C-pillar trim clips free of charge under recall 08V064.</x:v>
-      </x:c>
-      <x:c r="F33" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G33" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="1161.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A34" s="40" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B34" s="9" t="str">
-        <x:v>audi-tts-cam-follower-hpfp-2009</x:v>
-      </x:c>
-      <x:c r="C34" s="9" t="str">
-        <x:v>2009-2015 | Audi | TTS | TTS | EA888</x:v>
-      </x:c>
-      <x:c r="D34" s="9" t="str">
-        <x:v>HPFP Cam Follower Wear and High-Pressure Fuel Pump Failure (Mk2)</x:v>
-      </x:c>
-      <x:c r="E34" s="9" t="str">
-        <x:v>INSPECTION (every 20,000 miles): Remove HPFP (3 bolts) and inspect cam follower surface. If the hardened coating is wearing through (visible copper/brass color), replace follower immediately ($30-$50 part, 30-60 minutes labor). CRITICAL: Ensure cam lobe is at LOW point before reinstalling—if at peak, you'll compress the spring and can break the mounting bolts. If CAMSHAFT WORN (deep groove in lobe): Replace camshaft ($2,000-$4,000). If FUEL PUMP FAILED: Replace HPFP ($400-$800). PREVENTION: Inspect cam follower every 20,000 miles as routine maintenance. Add to every oil change checklist. Consider IE (Integrated Engineering) upgraded HPFP with roller follower to eliminate wear entirely.</x:v>
-      </x:c>
-      <x:c r="F34" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G34" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="884.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A35" s="40" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B35" s="9" t="str">
-        <x:v>audi-tts-carbon-buildup-2009</x:v>
-      </x:c>
-      <x:c r="C35" s="9" t="str">
-        <x:v>2016-2017 | Audi | TTS</x:v>
-      </x:c>
-      <x:c r="D35" s="9" t="str">
-        <x:v>2016-2017 TTS Cold-Start Misfire DTCs Without Felt Misfire - TSB 2051384/1</x:v>
-      </x:c>
-      <x:c r="E35" s="9" t="str">
-        <x:v>Confirm the exact cold-start timing, simultaneous-cylinder DTC pattern, absence of a felt misfire, CYFB engine and installed ECM software before using this bulletin. When applicable, an Audi-capable workshop updates ECM J623 from software part number 8S0906259C version 0001 to version 0004 or higher using SVM action 01A190, then clears the DTCs. A felt misfire, a different timing or RPM pattern, a different engine/software combination or a returning concern requires normal diagnosis rather than carbon cleaning by assumption.</x:v>
-      </x:c>
-      <x:c r="F35" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G35" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="910.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A36" s="40" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B36" s="9" t="str">
-        <x:v>audi-tts-dsg-mechatronic-2009</x:v>
-      </x:c>
-      <x:c r="C36" s="9" t="str">
-        <x:v>2019-2023 | Audi | TTS</x:v>
-      </x:c>
-      <x:c r="D36" s="9" t="str">
-        <x:v>2019-2023 TTS Clutch K1 Overheat and Transmission DTC Diagnosis - TSB 2060560/3</x:v>
-      </x:c>
-      <x:c r="E36" s="9" t="str">
-        <x:v>Have an Audi-capable workshop check whether TSB 2050723 applies first. If it does not resolve or control the concern, inspect the clutch-K1 maximum-temperature value and document a transmission-fluid sample. Replace the dual clutch, transmission fluid and filter only when the approximately 400 °C K1 value and burnt black or very dark fluid are both present. If those findings are absent, this bulletin does not apply and Audi directs the workshop to continue diagnosis through TAC. Any clutch repair kit must be selected by VIN and production date.</x:v>
-      </x:c>
-      <x:c r="F36" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G36" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="858" hidden="0" customHeight="1">
-      <x:c r="A37" s="40" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B37" s="9" t="str">
-        <x:v>audi-tts-magnetic-ride-2009</x:v>
-      </x:c>
-      <x:c r="C37" s="9" t="str">
-        <x:v>2016-2016 | Audi | TTS</x:v>
-      </x:c>
-      <x:c r="D37" s="9" t="str">
-        <x:v>2016 TTS Magnetic-Ride Rear Shock-Mount Rumble - TSB 2042539/4</x:v>
-      </x:c>
-      <x:c r="E37" s="9" t="str">
-        <x:v>First reproduce the noise, verify that it comes from the rear shock mounts and confirm that the vehicle was originally equipped with mount 8S0 513 353. Only when those gates are satisfied, remove both rear shock assemblies and replace both mounts with 8V0 513 353 according to Audi workshop instructions, adapt the suspension control position and test drive to confirm the repair. If the installed mount does not match, continue Audi diagnosis. Do not replace magnetic dampers or convert the vehicle to coilovers from this noise alone.</x:v>
-      </x:c>
-      <x:c r="F37" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G37" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="1016.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A38" s="40" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B38" s="9" t="str">
-        <x:v>audi-tts-timing-chain-tensioner-2009</x:v>
-      </x:c>
-      <x:c r="C38" s="9" t="str">
-        <x:v>2009-2015 | Audi | TTS | TTS | EA888 Gen 1, EA888 Gen 2</x:v>
-      </x:c>
-      <x:c r="D38" s="9" t="str">
-        <x:v>Timing Chain Tensioner Failure (EA888 Gen 1/2 - Mk2 TTS)</x:v>
-      </x:c>
-      <x:c r="E38" s="9" t="str">
-        <x:v>PREVENTIVE REPLACEMENT: Replace timing chain, tensioner, guides, and sprockets at 80,000-100,000 miles BEFORE symptoms appear ($2,000-$4,000). This is the MOST important preventive maintenance on the Mk2 TTS. IF RATTLING: Do NOT delay—the chain can jump at any startup. Schedule repair immediately. Use ONLY the latest OEM revised tensioner (06K109467K). IF CHAIN JUMPED: Engine likely destroyed—compression test all cylinders. Rebuild ($5,000-$8,000) or replacement engine ($6,000-$12,000). PREVENTION: Change oil every 5,000 miles with high-quality synthetic. Low oil level accelerates tensioner wear.</x:v>
-      </x:c>
-      <x:c r="F38" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G38" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" ht="976.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A39" s="40" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B39" s="9" t="str">
-        <x:v>audi-tts-water-pump-2009</x:v>
-      </x:c>
-      <x:c r="C39" s="9" t="str">
-        <x:v>2012-2023 | Audi | TTS</x:v>
-      </x:c>
-      <x:c r="D39" s="9" t="str">
-        <x:v>2012 / 2020-2023 TTS Coolant-Pump Update and Leak Diagnosis</x:v>
-      </x:c>
-      <x:c r="E39" s="9" t="str">
-        <x:v>For a 2012 TTS, ask an Audi dealer to check the VIN and current campaign/action history for Update 19J2; the published update replaced the pump only when its exact criteria were met and does not promise current warranty coverage. For a 2020-2023 2.0L TTS, first exclude a low level caused by incomplete bleeding or an earlier repair, document and clean the suspected leak, refill to maximum and recheck after driving. Continue observation when no leak returns; replace only the component proven to leak when coolant reappears. Do not select a pump or thermostat assembly before VIN-, engine- and leak-specific diagnosis.</x:v>
-      </x:c>
-      <x:c r="F39" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G39" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" ht="198" hidden="0" customHeight="1">
-      <x:c r="A40" s="42" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B40" s="43" t="str">
-        <x:v>audi-tts-waterpump-housing-2009</x:v>
-      </x:c>
-      <x:c r="C40" s="43" t="str">
-        <x:v>2009-2024 | Audi | TTS | EA888</x:v>
-      </x:c>
-      <x:c r="D40" s="43" t="str">
-        <x:v>Water Pump and Thermostat Housing Failure</x:v>
-      </x:c>
-      <x:c r="E40" s="43" t="str">
-        <x:v>Replace water pump, thermostat, and housing as a complete assembly. Use metal-impeller aftermarket pump if available.</x:v>
-      </x:c>
-      <x:c r="F40" s="43" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G40" s="44" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -22574,7 +24034,7 @@
       <x:c r="F2" s="28"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="45" t="str">
+      <x:c r="A3" s="48" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="15" t="str">
@@ -22586,7 +24046,7 @@
       <x:c r="F3" s="28"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="45" t="str">
+      <x:c r="A4" s="48" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="15" t="str">
@@ -22598,7 +24058,7 @@
       <x:c r="F4" s="28"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="45" t="str">
+      <x:c r="A5" s="48" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="15" t="str">
@@ -22610,7 +24070,7 @@
       <x:c r="F5" s="28"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="45" t="str">
+      <x:c r="A6" s="48" t="str">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B6" s="15" t="str">
@@ -22622,7 +24082,7 @@
       <x:c r="F6" s="28"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="45" t="str">
+      <x:c r="A7" s="48" t="str">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B7" s="15" t="str">
@@ -22634,7 +24094,7 @@
       <x:c r="F7" s="28"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="45" t="str">
+      <x:c r="A8" s="48" t="str">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B8" s="15" t="str">
@@ -22646,7 +24106,7 @@
       <x:c r="F8" s="28"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="45" t="str">
+      <x:c r="A9" s="48" t="str">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B9" s="15" t="str">
@@ -22658,7 +24118,7 @@
       <x:c r="F9" s="28"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="45" t="str">
+      <x:c r="A10" s="48" t="str">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B10" s="15" t="str">
@@ -22678,7 +24138,7 @@
       <x:c r="F11" s="28"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="46" t="str">
+      <x:c r="A12" s="49" t="str">
         <x:v>Artifact state</x:v>
       </x:c>
       <x:c r="B12" s="11" t="str">
@@ -22690,7 +24150,7 @@
       <x:c r="F12" s="28"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="46" t="str">
+      <x:c r="A13" s="49" t="str">
         <x:v>Source</x:v>
       </x:c>
       <x:c r="B13" s="11" t="str">
@@ -22702,7 +24162,7 @@
       <x:c r="F13" s="28"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="46" t="str">
+      <x:c r="A14" s="49" t="str">
         <x:v>Review input</x:v>
       </x:c>
       <x:c r="B14" s="11" t="str">
@@ -22714,16 +24174,16 @@
       <x:c r="F14" s="28"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="47" t="str">
+      <x:c r="A15" s="50" t="str">
         <x:v>Generated ledger</x:v>
       </x:c>
-      <x:c r="B15" s="48" t="str">
+      <x:c r="B15" s="51" t="str">
         <x:v>data\audi-repair-first-review\review-ledger.json</x:v>
       </x:c>
-      <x:c r="C15" s="48"/>
-      <x:c r="D15" s="48"/>
-      <x:c r="E15" s="48"/>
-      <x:c r="F15" s="49"/>
+      <x:c r="C15" s="51"/>
+      <x:c r="D15" s="51"/>
+      <x:c r="E15" s="51"/>
+      <x:c r="F15" s="52"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
